--- a/docs/downloads/latest.xlsx
+++ b/docs/downloads/latest.xlsx
@@ -93,7 +93,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L65"/>
+  <dimension ref="A1:L138"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -3559,13 +3559,3955 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B66" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C66" s="0">
+        <v>1</v>
+      </c>
+      <c r="D66" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000607</t>
+        </is>
+      </c>
+      <c r="E66" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华媒控股</t>
+        </is>
+      </c>
+      <c r="F66" s="0">
+        <v>4.53</v>
+      </c>
+      <c r="G66" s="4">
+        <v>0.09951456310679617</v>
+      </c>
+      <c r="H66" s="4">
+        <v>0.4652418066589123</v>
+      </c>
+      <c r="I66" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华媒控股（000607）归入“文化传媒+AI应用+国企”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 10.0%）。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B67" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C67" s="0">
+        <v>2</v>
+      </c>
+      <c r="D67" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600825</t>
+        </is>
+      </c>
+      <c r="E67" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新华传媒</t>
+        </is>
+      </c>
+      <c r="F67" s="0">
+        <v>5.84</v>
+      </c>
+      <c r="G67" s="4">
+        <v>0.09981167608286266</v>
+      </c>
+      <c r="H67" s="4">
+        <v>0.46339117758857357</v>
+      </c>
+      <c r="I67" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 新华传媒（600825）归入“资产重组+复牌+图书发行+上海国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 10.0%）。截至运行时成交量约为20日均量的 0.3 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B68" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C68" s="0">
+        <v>3</v>
+      </c>
+      <c r="D68" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002614</t>
+        </is>
+      </c>
+      <c r="E68" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奥佳华</t>
+        </is>
+      </c>
+      <c r="F68" s="0">
+        <v>6.25</v>
+      </c>
+      <c r="G68" s="4">
+        <v>0.10035211267605648</v>
+      </c>
+      <c r="H68" s="4">
+        <v>0.37674420222437527</v>
+      </c>
+      <c r="I68" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 奥佳华（002614）归入“股份转让+具身智能+智能按摩椅+大健康品牌”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 9.2%）。截至运行时成交量约为20日均量的 0.7 倍，量能未出现极端放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B69" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C69" s="0">
+        <v>4</v>
+      </c>
+      <c r="D69" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600743</t>
+        </is>
+      </c>
+      <c r="E69" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华远控股</t>
+        </is>
+      </c>
+      <c r="F69" s="0">
+        <v>2.33</v>
+      </c>
+      <c r="G69" s="4">
+        <v>0.09905660377358494</v>
+      </c>
+      <c r="H69" s="4">
+        <v>0.33858885816024553</v>
+      </c>
+      <c r="I69" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华远控股（600743）归入“控股变更+物业管理+酒店管理”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 9.9%）。截至运行时成交量约为20日均量的 0.5 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B70" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C70" s="0">
+        <v>5</v>
+      </c>
+      <c r="D70" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600301</t>
+        </is>
+      </c>
+      <c r="E70" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华锡有色</t>
+        </is>
+      </c>
+      <c r="F70" s="0">
+        <v>49.97</v>
+      </c>
+      <c r="G70" s="4">
+        <v>0.09993396434074399</v>
+      </c>
+      <c r="H70" s="4">
+        <v>0.2342618480988038</v>
+      </c>
+      <c r="I70" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华锡有色（600301）归入“控制权变更+锡锑铟+业绩增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 10.0%）。截至运行时成交量约为20日均量的 0.6 倍，量能未出现极端放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B71" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C71" s="0">
+        <v>6</v>
+      </c>
+      <c r="D71" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002303</t>
+        </is>
+      </c>
+      <c r="E71" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">美盈森</t>
+        </is>
+      </c>
+      <c r="F71" s="0">
+        <v>6.27</v>
+      </c>
+      <c r="G71" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H71" s="4">
+        <v>0.1950828698236118</v>
+      </c>
+      <c r="I71" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 美盈森（002303）归入“包装一体化+消费电子包装+模切业务+海外产能”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.6 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B72" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C72" s="0">
+        <v>7</v>
+      </c>
+      <c r="D72" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002585</t>
+        </is>
+      </c>
+      <c r="E72" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">双星新材</t>
+        </is>
+      </c>
+      <c r="F72" s="0">
+        <v>12.71</v>
+      </c>
+      <c r="G72" s="4">
+        <v>0.10043290043290053</v>
+      </c>
+      <c r="H72" s="4">
+        <v>0.18885269109174457</v>
+      </c>
+      <c r="I72" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 双星新材（002585）归入“MLCC离型膜+复合铜箔+聚酯薄膜”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.5 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B73" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C73" s="0">
+        <v>8</v>
+      </c>
+      <c r="D73" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002172</t>
+        </is>
+      </c>
+      <c r="E73" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">澳洋健康</t>
+        </is>
+      </c>
+      <c r="F73" s="0">
+        <v>5.81</v>
+      </c>
+      <c r="G73" s="4">
+        <v>0.10037878787878786</v>
+      </c>
+      <c r="H73" s="4">
+        <v>0.17677673435453747</v>
+      </c>
+      <c r="I73" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 澳洋健康（002172）归入“脑机接口+医疗服务+国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.6 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B74" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C74" s="0">
+        <v>9</v>
+      </c>
+      <c r="D74" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001201</t>
+        </is>
+      </c>
+      <c r="E74" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东瑞股份</t>
+        </is>
+      </c>
+      <c r="F74" s="0">
+        <v>16.08</v>
+      </c>
+      <c r="G74" s="4">
+        <v>0.09986320109439116</v>
+      </c>
+      <c r="H74" s="4">
+        <v>0.15556029997125023</v>
+      </c>
+      <c r="I74" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 东瑞股份（001201）归入“生猪养殖+供港活猪+降本增效”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B75" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C75" s="0">
+        <v>10</v>
+      </c>
+      <c r="D75" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002084</t>
+        </is>
+      </c>
+      <c r="E75" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">海鸥住工</t>
+        </is>
+      </c>
+      <c r="F75" s="0">
+        <v>6.12</v>
+      </c>
+      <c r="G75" s="4">
+        <v>0.10071942446043171</v>
+      </c>
+      <c r="H75" s="4">
+        <v>0.1543190939107268</v>
+      </c>
+      <c r="I75" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 海鸥住工（002084）归入“控制权拟变更+装配式厨卫+越南制造”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.6 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C76" s="0">
+        <v>11</v>
+      </c>
+      <c r="D76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603042</t>
+        </is>
+      </c>
+      <c r="E76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华脉科技</t>
+        </is>
+      </c>
+      <c r="F76" s="0">
+        <v>19.03</v>
+      </c>
+      <c r="G76" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H76" s="4">
+        <v>0.14686166753756646</v>
+      </c>
+      <c r="I76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华脉科技（603042）归入“光纤光缆+扭亏为盈+6G布局”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B77" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C77" s="0">
+        <v>12</v>
+      </c>
+      <c r="D77" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603663</t>
+        </is>
+      </c>
+      <c r="E77" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">三祥新材</t>
+        </is>
+      </c>
+      <c r="F77" s="0">
+        <v>49.82</v>
+      </c>
+      <c r="G77" s="4">
+        <v>0.1000220799293443</v>
+      </c>
+      <c r="H77" s="4">
+        <v>0.14652972517382876</v>
+      </c>
+      <c r="I77" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 三祥新材（603663）归入“锆铪分离+半导体+海绵锆”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B78" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C78" s="0">
+        <v>13</v>
+      </c>
+      <c r="D78" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002388</t>
+        </is>
+      </c>
+      <c r="E78" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新亚制程</t>
+        </is>
+      </c>
+      <c r="F78" s="0">
+        <v>7.95</v>
+      </c>
+      <c r="G78" s="4">
+        <v>0.09958506224066375</v>
+      </c>
+      <c r="H78" s="4">
+        <v>0.1410810028618283</v>
+      </c>
+      <c r="I78" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 新亚制程（002388）归入“AI服务器电源+胶粘剂+六氟磷酸锂”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B79" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C79" s="0">
+        <v>14</v>
+      </c>
+      <c r="D79" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002724</t>
+        </is>
+      </c>
+      <c r="E79" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">海洋王</t>
+        </is>
+      </c>
+      <c r="F79" s="0">
+        <v>7.84</v>
+      </c>
+      <c r="G79" s="4">
+        <v>0.09957924263674611</v>
+      </c>
+      <c r="H79" s="4">
+        <v>0.14094176062559174</v>
+      </c>
+      <c r="I79" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 海洋王（002724）归入“AI照明+工业照明+应急救援”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.5 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C80" s="0">
+        <v>15</v>
+      </c>
+      <c r="D80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603819</t>
+        </is>
+      </c>
+      <c r="E80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神力股份</t>
+        </is>
+      </c>
+      <c r="F80" s="0">
+        <v>17.33</v>
+      </c>
+      <c r="G80" s="4">
+        <v>0.10031746031746014</v>
+      </c>
+      <c r="H80" s="4">
+        <v>0.1360845517633556</v>
+      </c>
+      <c r="I80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 神力股份（603819）归入“电机铁芯+风电+电梯配件+半年报增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B81" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C81" s="0">
+        <v>16</v>
+      </c>
+      <c r="D81" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603319</t>
+        </is>
+      </c>
+      <c r="E81" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">XD美湖股份</t>
+        </is>
+      </c>
+      <c r="F81" s="0">
+        <v>32.18</v>
+      </c>
+      <c r="G81" s="4">
+        <v>0.10017094017094008</v>
+      </c>
+      <c r="H81" s="4">
+        <v>0.1345846761414189</v>
+      </c>
+      <c r="I81" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 XD美湖股份（603319）归入“机器人执行器+服务器液冷+泵类龙头”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.8 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B82" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C82" s="0">
+        <v>17</v>
+      </c>
+      <c r="D82" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002080</t>
+        </is>
+      </c>
+      <c r="E82" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中材科技</t>
+        </is>
+      </c>
+      <c r="F82" s="0">
+        <v>66.24</v>
+      </c>
+      <c r="G82" s="4">
+        <v>0.09996678844237783</v>
+      </c>
+      <c r="H82" s="4">
+        <v>0.1343407096372262</v>
+      </c>
+      <c r="I82" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 中材科技（002080）归入“低介电纤维布+高频高速PCB+玻纤主业”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.4 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B83" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C83" s="0">
+        <v>18</v>
+      </c>
+      <c r="D83" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002367</t>
+        </is>
+      </c>
+      <c r="E83" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">康力电梯</t>
+        </is>
+      </c>
+      <c r="F83" s="0">
+        <v>6.28</v>
+      </c>
+      <c r="G83" s="4">
+        <v>0.09982486865148864</v>
+      </c>
+      <c r="H83" s="4">
+        <v>0.13114815737366875</v>
+      </c>
+      <c r="I83" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 康力电梯（002367）归入“旧梯更新+轨道交通+智能电梯”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.9 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B84" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C84" s="0">
+        <v>19</v>
+      </c>
+      <c r="D84" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000560</t>
+        </is>
+      </c>
+      <c r="E84" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">我爱我家</t>
+        </is>
+      </c>
+      <c r="F84" s="0">
+        <v>3.19</v>
+      </c>
+      <c r="G84" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H84" s="4">
+        <v>0.12987375444567673</v>
+      </c>
+      <c r="I84" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 我爱我家（000560）归入“房产经纪+AI应用+净利增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B85" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C85" s="0">
+        <v>20</v>
+      </c>
+      <c r="D85" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600712</t>
+        </is>
+      </c>
+      <c r="E85" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南宁百货</t>
+        </is>
+      </c>
+      <c r="F85" s="0">
+        <v>5.89</v>
+      </c>
+      <c r="G85" s="4">
+        <v>0.10093457943925245</v>
+      </c>
+      <c r="H85" s="4">
+        <v>0.12873773638560287</v>
+      </c>
+      <c r="I85" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 南宁百货（600712）归入“百货零售+平陆运河+扭亏为盈”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.8 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B86" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C86" s="0">
+        <v>21</v>
+      </c>
+      <c r="D86" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600664</t>
+        </is>
+      </c>
+      <c r="E86" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">哈药股份</t>
+        </is>
+      </c>
+      <c r="F86" s="0">
+        <v>8.25</v>
+      </c>
+      <c r="G86" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H86" s="4">
+        <v>0.12766536973531</v>
+      </c>
+      <c r="I86" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 哈药股份（600664）归入“创新药研发+医药工业+业绩增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.5 倍，量能未出现极端放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B87" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C87" s="0">
+        <v>22</v>
+      </c>
+      <c r="D87" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001234</t>
+        </is>
+      </c>
+      <c r="E87" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">泰慕士</t>
+        </is>
+      </c>
+      <c r="F87" s="0">
+        <v>26.59</v>
+      </c>
+      <c r="G87" s="4">
+        <v>0.10012412081092247</v>
+      </c>
+      <c r="H87" s="4">
+        <v>0.12764818270936235</v>
+      </c>
+      <c r="I87" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 泰慕士（001234）归入“针织服装+服装贴牌+广州国资入主”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.2 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B88" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C88" s="0">
+        <v>23</v>
+      </c>
+      <c r="D88" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002792</t>
+        </is>
+      </c>
+      <c r="E88" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通宇通讯</t>
+        </is>
+      </c>
+      <c r="F88" s="0">
+        <v>34.54</v>
+      </c>
+      <c r="G88" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H88" s="4">
+        <v>0.12699105645561096</v>
+      </c>
+      <c r="I88" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 通宇通讯（002792）归入“卫星通信+基站天线+海外业务”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.6 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B89" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C89" s="0">
+        <v>24</v>
+      </c>
+      <c r="D89" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001389</t>
+        </is>
+      </c>
+      <c r="E89" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">广合科技</t>
+        </is>
+      </c>
+      <c r="F89" s="0">
+        <v>185.93</v>
+      </c>
+      <c r="G89" s="4">
+        <v>0.09998225167130093</v>
+      </c>
+      <c r="H89" s="4">
+        <v>0.12614165188586235</v>
+      </c>
+      <c r="I89" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 广合科技（001389）归入“算力PCB+高端产能+业绩增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C90" s="0">
+        <v>25</v>
+      </c>
+      <c r="D90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002963</t>
+        </is>
+      </c>
+      <c r="E90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">豪尔赛</t>
+        </is>
+      </c>
+      <c r="F90" s="0">
+        <v>22.62</v>
+      </c>
+      <c r="G90" s="4">
+        <v>0.10019455252918297</v>
+      </c>
+      <c r="H90" s="4">
+        <v>0.1242262874871728</v>
+      </c>
+      <c r="I90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 豪尔赛（002963）归入“智慧能源+照明工程+拟收购新能动力+澄清液冷”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.8 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C91" s="0">
+        <v>26</v>
+      </c>
+      <c r="D91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600857</t>
+        </is>
+      </c>
+      <c r="E91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">宁波中百</t>
+        </is>
+      </c>
+      <c r="F91" s="0">
+        <v>23.41</v>
+      </c>
+      <c r="G91" s="4">
+        <v>0.10009398496240607</v>
+      </c>
+      <c r="H91" s="4">
+        <v>0.12335097963154369</v>
+      </c>
+      <c r="I91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 宁波中百（600857）归入“商业零售+黄金珠宝+杭州金帝入主”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B92" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C92" s="0">
+        <v>27</v>
+      </c>
+      <c r="D92" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002246</t>
+        </is>
+      </c>
+      <c r="E92" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">北化股份</t>
+        </is>
+      </c>
+      <c r="F92" s="0">
+        <v>26.27</v>
+      </c>
+      <c r="G92" s="4">
+        <v>0.10008375209380226</v>
+      </c>
+      <c r="H92" s="4">
+        <v>0.12259349734404079</v>
+      </c>
+      <c r="I92" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 北化股份（002246）归入“硝化棉+商业航天+央企”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.4 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L92" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B93" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C93" s="0">
+        <v>28</v>
+      </c>
+      <c r="D93" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603020</t>
+        </is>
+      </c>
+      <c r="E93" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">爱普股份</t>
+        </is>
+      </c>
+      <c r="F93" s="0">
+        <v>12.57</v>
+      </c>
+      <c r="G93" s="4">
+        <v>0.09973753280839892</v>
+      </c>
+      <c r="H93" s="4">
+        <v>0.12196322877452691</v>
+      </c>
+      <c r="I93" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 爱普股份（603020）归入“半导体材料+香精香料+鱼油原料”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L93" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B94" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C94" s="0">
+        <v>29</v>
+      </c>
+      <c r="D94" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605566</t>
+        </is>
+      </c>
+      <c r="E94" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">福莱蒽特</t>
+        </is>
+      </c>
+      <c r="F94" s="0">
+        <v>30.44</v>
+      </c>
+      <c r="G94" s="4">
+        <v>0.10010842067220803</v>
+      </c>
+      <c r="H94" s="4">
+        <v>0.1216132115219928</v>
+      </c>
+      <c r="I94" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 福莱蒽特（605566）归入“分散染料+服务器采购+机器人皮肤”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.4 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B95" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C95" s="0">
+        <v>30</v>
+      </c>
+      <c r="D95" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000020</t>
+        </is>
+      </c>
+      <c r="E95" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">深华发Ａ</t>
+        </is>
+      </c>
+      <c r="F95" s="0">
+        <v>14.26</v>
+      </c>
+      <c r="G95" s="4">
+        <v>0.10030864197530853</v>
+      </c>
+      <c r="H95" s="4">
+        <v>0.12084880643633285</v>
+      </c>
+      <c r="I95" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 深华发Ａ（000020）归入“定制显示器+深圳旧改+物业经营+注塑业务”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C96" s="0">
+        <v>31</v>
+      </c>
+      <c r="D96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600593</t>
+        </is>
+      </c>
+      <c r="E96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大连圣亚</t>
+        </is>
+      </c>
+      <c r="F96" s="0">
+        <v>48.57</v>
+      </c>
+      <c r="G96" s="4">
+        <v>0.10011325028312568</v>
+      </c>
+      <c r="H96" s="4">
+        <v>0.12028803328689865</v>
+      </c>
+      <c r="I96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 大连圣亚（600593）归入“旅游经营+海洋公园+业绩扭亏”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.4 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C97" s="0">
+        <v>32</v>
+      </c>
+      <c r="D97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603151</t>
+        </is>
+      </c>
+      <c r="E97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">邦基科技股份</t>
+        </is>
+      </c>
+      <c r="F97" s="0">
+        <v>18.35</v>
+      </c>
+      <c r="G97" s="4">
+        <v>0.10011990407673865</v>
+      </c>
+      <c r="H97" s="4">
+        <v>0.12016408243019151</v>
+      </c>
+      <c r="I97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 邦基科技股份（603151）归入“猪饲料+生猪养殖+产业链一体化”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.8 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L97" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B98" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C98" s="0">
+        <v>33</v>
+      </c>
+      <c r="D98" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002321</t>
+        </is>
+      </c>
+      <c r="E98" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华英农业</t>
+        </is>
+      </c>
+      <c r="F98" s="0">
+        <v>2.3</v>
+      </c>
+      <c r="G98" s="4">
+        <v>0.10047846889952151</v>
+      </c>
+      <c r="H98" s="4">
+        <v>0.11799329681958166</v>
+      </c>
+      <c r="I98" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华英农业（002321）归入“鸭业全产业链+羽绒出口+控制权变更”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.5 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B99" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C99" s="0">
+        <v>34</v>
+      </c>
+      <c r="D99" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603093</t>
+        </is>
+      </c>
+      <c r="E99" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南华期货</t>
+        </is>
+      </c>
+      <c r="F99" s="0">
+        <v>13.99</v>
+      </c>
+      <c r="G99" s="4">
+        <v>0.09984276729559749</v>
+      </c>
+      <c r="H99" s="4">
+        <v>0.1178917621278945</v>
+      </c>
+      <c r="I99" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 南华期货（603093）归入“境外金融服务+境外清算+期货经纪”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C100" s="0">
+        <v>35</v>
+      </c>
+      <c r="D100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600721</t>
+        </is>
+      </c>
+      <c r="E100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">百花医药</t>
+        </is>
+      </c>
+      <c r="F100" s="0">
+        <v>13.15</v>
+      </c>
+      <c r="G100" s="4">
+        <v>0.10041841004184103</v>
+      </c>
+      <c r="H100" s="4">
+        <v>0.11730331242139477</v>
+      </c>
+      <c r="I100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 百花医药（600721）归入“CRO+复杂制剂+国资背景”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C101" s="0">
+        <v>36</v>
+      </c>
+      <c r="D101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603175</t>
+        </is>
+      </c>
+      <c r="E101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">超颖电子</t>
+        </is>
+      </c>
+      <c r="F101" s="0">
+        <v>110.17</v>
+      </c>
+      <c r="G101" s="4">
+        <v>0.10004992511233146</v>
+      </c>
+      <c r="H101" s="4">
+        <v>0.11683520091249867</v>
+      </c>
+      <c r="I101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 超颖电子（603175）归入“AI算力PCB+存储芯片+汽车电子板”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.9 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B102" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C102" s="0">
+        <v>37</v>
+      </c>
+      <c r="D102" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001373</t>
+        </is>
+      </c>
+      <c r="E102" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">翔腾新材</t>
+        </is>
+      </c>
+      <c r="F102" s="0">
+        <v>32.44</v>
+      </c>
+      <c r="G102" s="4">
+        <v>0.1000339097999321</v>
+      </c>
+      <c r="H102" s="4">
+        <v>0.11517526054749688</v>
+      </c>
+      <c r="I102" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 翔腾新材（001373）归入“偏光片+光学膜片+MiniLED”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.9 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B103" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C103" s="0">
+        <v>38</v>
+      </c>
+      <c r="D103" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600325</t>
+        </is>
+      </c>
+      <c r="E103" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华发股份</t>
+        </is>
+      </c>
+      <c r="F103" s="0">
+        <v>2.73</v>
+      </c>
+      <c r="G103" s="4">
+        <v>0.10080645161290323</v>
+      </c>
+      <c r="H103" s="4">
+        <v>0.11363207665999002</v>
+      </c>
+      <c r="I103" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华发股份（600325）归入“房地产+冰雪经济+定增”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.9 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B104" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C104" s="0">
+        <v>39</v>
+      </c>
+      <c r="D104" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002860</t>
+        </is>
+      </c>
+      <c r="E104" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">星帅尔</t>
+        </is>
+      </c>
+      <c r="F104" s="0">
+        <v>18.39</v>
+      </c>
+      <c r="G104" s="4">
+        <v>0.09988038277511979</v>
+      </c>
+      <c r="H104" s="4">
+        <v>0.11309807028350415</v>
+      </c>
+      <c r="I104" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 星帅尔（002860）归入“光伏组件+家电零部件+高效电机”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.8 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C105" s="0">
+        <v>40</v>
+      </c>
+      <c r="D105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603258</t>
+        </is>
+      </c>
+      <c r="E105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">电魂网络</t>
+        </is>
+      </c>
+      <c r="F105" s="0">
+        <v>14.19</v>
+      </c>
+      <c r="G105" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H105" s="4">
+        <v>0.11224237226615294</v>
+      </c>
+      <c r="I105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 电魂网络（603258）归入“人工智能游戏+修仙时代+网络游戏”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C106" s="0">
+        <v>41</v>
+      </c>
+      <c r="D106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002795</t>
+        </is>
+      </c>
+      <c r="E106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">永和智控</t>
+        </is>
+      </c>
+      <c r="F106" s="0">
+        <v>8.04</v>
+      </c>
+      <c r="G106" s="4">
+        <v>0.09986320109439116</v>
+      </c>
+      <c r="H106" s="4">
+        <v>0.11179183978497693</v>
+      </c>
+      <c r="I106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 永和智控（002795）归入“水暖阀门+医疗器械+资产出售+业绩扭亏”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.6 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B107" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C107" s="0">
+        <v>42</v>
+      </c>
+      <c r="D107" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600714</t>
+        </is>
+      </c>
+      <c r="E107" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金瑞矿业</t>
+        </is>
+      </c>
+      <c r="F107" s="0">
+        <v>19.25</v>
+      </c>
+      <c r="G107" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H107" s="4">
+        <v>0.10888589363275825</v>
+      </c>
+      <c r="I107" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 金瑞矿业（600714）归入“碳酸锶+锶盐扩产+玻璃基板+国家电投”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.6 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L107" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C108" s="0">
+        <v>43</v>
+      </c>
+      <c r="D108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600785</t>
+        </is>
+      </c>
+      <c r="E108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新华百货</t>
+        </is>
+      </c>
+      <c r="F108" s="0">
+        <v>11.35</v>
+      </c>
+      <c r="G108" s="4">
+        <v>0.09980620155038755</v>
+      </c>
+      <c r="H108" s="4">
+        <v>0.10654790904146405</v>
+      </c>
+      <c r="I108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 新华百货（600785）归入“零售+智能家居+股份回购”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K108" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.5 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L108" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C109" s="0">
+        <v>44</v>
+      </c>
+      <c r="D109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603580</t>
+        </is>
+      </c>
+      <c r="E109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">艾艾精工</t>
+        </is>
+      </c>
+      <c r="F109" s="0">
+        <v>71.53</v>
+      </c>
+      <c r="G109" s="4">
+        <v>0.09995386744579428</v>
+      </c>
+      <c r="H109" s="4">
+        <v>0.10652378462237674</v>
+      </c>
+      <c r="I109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 艾艾精工（603580）归入“轻型输送带+精密金属结构件+控制权拟变更”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K109" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.8 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L109" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C110" s="0">
+        <v>45</v>
+      </c>
+      <c r="D110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002349</t>
+        </is>
+      </c>
+      <c r="E110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">精华制药</t>
+        </is>
+      </c>
+      <c r="F110" s="0">
+        <v>8.71</v>
+      </c>
+      <c r="G110" s="4">
+        <v>0.09974747474747492</v>
+      </c>
+      <c r="H110" s="4">
+        <v>0.10627334237847577</v>
+      </c>
+      <c r="I110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 精华制药（002349）归入“中药独家品种+AI制药+外用剂型”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K110" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L110" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C111" s="0">
+        <v>46</v>
+      </c>
+      <c r="D111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603395</t>
+        </is>
+      </c>
+      <c r="E111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中盐红四方</t>
+        </is>
+      </c>
+      <c r="F111" s="0">
+        <v>28.14</v>
+      </c>
+      <c r="G111" s="4">
+        <v>0.10007818608287744</v>
+      </c>
+      <c r="H111" s="4">
+        <v>0.10535244752672822</v>
+      </c>
+      <c r="I111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 中盐红四方（603395）归入“复合肥+新疆项目+央企”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L111" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C112" s="0">
+        <v>47</v>
+      </c>
+      <c r="D112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002622</t>
+        </is>
+      </c>
+      <c r="E112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">皓宸医疗</t>
+        </is>
+      </c>
+      <c r="F112" s="0">
+        <v>2.72</v>
+      </c>
+      <c r="G112" s="4">
+        <v>0.10121457489878537</v>
+      </c>
+      <c r="H112" s="4">
+        <v>0.10512519825974313</v>
+      </c>
+      <c r="I112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 皓宸医疗（002622）归入“口腔医疗+连锁服务+半年报减亏”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K112" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.9 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L112" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C113" s="0">
+        <v>48</v>
+      </c>
+      <c r="D113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605196</t>
+        </is>
+      </c>
+      <c r="E113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华通线缆</t>
+        </is>
+      </c>
+      <c r="F113" s="0">
+        <v>34.62</v>
+      </c>
+      <c r="G113" s="4">
+        <v>0.100095328884652</v>
+      </c>
+      <c r="H113" s="4">
+        <v>0.10421138398395025</v>
+      </c>
+      <c r="I113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华通线缆（605196）归入“电线电缆+电解铝+油服产品+海外订单”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.5 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L113" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C114" s="0">
+        <v>49</v>
+      </c>
+      <c r="D114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000756</t>
+        </is>
+      </c>
+      <c r="E114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新华制药</t>
+        </is>
+      </c>
+      <c r="F114" s="0">
+        <v>14.67</v>
+      </c>
+      <c r="G114" s="4">
+        <v>0.09970014992503738</v>
+      </c>
+      <c r="H114" s="4">
+        <v>0.10355953792160928</v>
+      </c>
+      <c r="I114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 新华制药（000756）归入“药品注册+阿尔茨海默病+解热镇痛”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K114" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.7 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L114" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C115" s="0">
+        <v>50</v>
+      </c>
+      <c r="D115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603289</t>
+        </is>
+      </c>
+      <c r="E115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">泰瑞机器</t>
+        </is>
+      </c>
+      <c r="F115" s="0">
+        <v>10.51</v>
+      </c>
+      <c r="G115" s="4">
+        <v>0.10052356020942387</v>
+      </c>
+      <c r="H115" s="4">
+        <v>0.10309535830565501</v>
+      </c>
+      <c r="I115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 泰瑞机器（603289）归入“一体化压铸+汽车注塑+海外业务”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K115" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.3 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L115" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C116" s="0">
+        <v>51</v>
+      </c>
+      <c r="D116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603958</t>
+        </is>
+      </c>
+      <c r="E116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">哈森股份</t>
+        </is>
+      </c>
+      <c r="F116" s="0">
+        <v>18.37</v>
+      </c>
+      <c r="G116" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H116" s="4">
+        <v>0.10098199942322085</v>
+      </c>
+      <c r="I116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 哈森股份（603958）归入“3D打印+苹果产业链+机器人+资产重组”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K116" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L116" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B117" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C117" s="0">
+        <v>52</v>
+      </c>
+      <c r="D117" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600503</t>
+        </is>
+      </c>
+      <c r="E117" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华丽家族</t>
+        </is>
+      </c>
+      <c r="F117" s="0">
+        <v>2.43</v>
+      </c>
+      <c r="G117" s="4">
+        <v>0.09954751131221728</v>
+      </c>
+      <c r="H117" s="4">
+        <v>0.09767660906243784</v>
+      </c>
+      <c r="I117" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华丽家族（600503）归入“房地产+创新药+机器人”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K117" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.6 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L117" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B118" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C118" s="0">
+        <v>53</v>
+      </c>
+      <c r="D118" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600613</t>
+        </is>
+      </c>
+      <c r="E118" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神奇制药</t>
+        </is>
+      </c>
+      <c r="F118" s="0">
+        <v>9.25</v>
+      </c>
+      <c r="G118" s="4">
+        <v>0.0998810939357908</v>
+      </c>
+      <c r="H118" s="4">
+        <v>0.09672551632117354</v>
+      </c>
+      <c r="I118" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 神奇制药（600613）归入“抗肿瘤药+化学制药+研发推进”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K118" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.8 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L118" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B119" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C119" s="0">
+        <v>54</v>
+      </c>
+      <c r="D119" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002900</t>
+        </is>
+      </c>
+      <c r="E119" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">哈三联</t>
+        </is>
+      </c>
+      <c r="F119" s="0">
+        <v>13.04</v>
+      </c>
+      <c r="G119" s="4">
+        <v>0.10042194092827007</v>
+      </c>
+      <c r="H119" s="4">
+        <v>0.09543416738935327</v>
+      </c>
+      <c r="I119" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 哈三联（002900）归入“创新药+化学制药+半年报减亏”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K119" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.5 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L119" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B120" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C120" s="0">
+        <v>55</v>
+      </c>
+      <c r="D120" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000829</t>
+        </is>
+      </c>
+      <c r="E120" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天音控股</t>
+        </is>
+      </c>
+      <c r="F120" s="0">
+        <v>9.77</v>
+      </c>
+      <c r="G120" s="4">
+        <v>0.10022522522522515</v>
+      </c>
+      <c r="H120" s="4">
+        <v>0.09437593703049083</v>
+      </c>
+      <c r="I120" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 天音控股（000829）归入“智能终端销售+鸿蒙生态+零售电商”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K120" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.8 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L120" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B121" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C121" s="0">
+        <v>56</v>
+      </c>
+      <c r="D121" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000566</t>
+        </is>
+      </c>
+      <c r="E121" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">海南海药</t>
+        </is>
+      </c>
+      <c r="F121" s="0">
+        <v>5.07</v>
+      </c>
+      <c r="G121" s="4">
+        <v>0.09978308026030369</v>
+      </c>
+      <c r="H121" s="4">
+        <v>0.09245835384523732</v>
+      </c>
+      <c r="I121" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 海南海药（000566）归入“创新药+化学制药+脑机接口+国资背景”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K121" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L121" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B122" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C122" s="0">
+        <v>57</v>
+      </c>
+      <c r="D122" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000995</t>
+        </is>
+      </c>
+      <c r="E122" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">皇台酒业</t>
+        </is>
+      </c>
+      <c r="F122" s="0">
+        <v>11.92</v>
+      </c>
+      <c r="G122" s="4">
+        <v>0.09963099630996307</v>
+      </c>
+      <c r="H122" s="4">
+        <v>0.09219350106048056</v>
+      </c>
+      <c r="I122" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 皇台酒业（000995）归入“白酒+区域品牌+线上渠道”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K122" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L122" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B123" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C123" s="0">
+        <v>58</v>
+      </c>
+      <c r="D123" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600992</t>
+        </is>
+      </c>
+      <c r="E123" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">贵绳股份</t>
+        </is>
+      </c>
+      <c r="F123" s="0">
+        <v>10.57</v>
+      </c>
+      <c r="G123" s="4">
+        <v>0.09989594172736747</v>
+      </c>
+      <c r="H123" s="4">
+        <v>0.089757982561971</v>
+      </c>
+      <c r="I123" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 贵绳股份（600992）归入“商业航天+钢丝绳+军工+贵州国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K123" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.3 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L123" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B124" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C124" s="0">
+        <v>59</v>
+      </c>
+      <c r="D124" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002907</t>
+        </is>
+      </c>
+      <c r="E124" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华森制药</t>
+        </is>
+      </c>
+      <c r="F124" s="0">
+        <v>15.25</v>
+      </c>
+      <c r="G124" s="4">
+        <v>0.1002886002886003</v>
+      </c>
+      <c r="H124" s="4">
+        <v>0.08924696878323685</v>
+      </c>
+      <c r="I124" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华森制药（002907）归入“创新药+青光眼+基本药物+中成药”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K124" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L124" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B125" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C125" s="0">
+        <v>60</v>
+      </c>
+      <c r="D125" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002869</t>
+        </is>
+      </c>
+      <c r="E125" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金溢科技</t>
+        </is>
+      </c>
+      <c r="F125" s="0">
+        <v>17.04</v>
+      </c>
+      <c r="G125" s="4">
+        <v>0.1000645577792123</v>
+      </c>
+      <c r="H125" s="4">
+        <v>0.08510548454553901</v>
+      </c>
+      <c r="I125" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 金溢科技（002869）归入“车路协同+电子收费+低空智联”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K125" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.0 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L125" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B126" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C126" s="0">
+        <v>61</v>
+      </c>
+      <c r="D126" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600894</t>
+        </is>
+      </c>
+      <c r="E126" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">广日股份</t>
+        </is>
+      </c>
+      <c r="F126" s="0">
+        <v>7.92</v>
+      </c>
+      <c r="G126" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H126" s="4">
+        <v>0.08414283872293986</v>
+      </c>
+      <c r="I126" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 广日股份（600894）归入“电梯+智慧楼宇+国资背景”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K126" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.1 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L126" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B127" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C127" s="0">
+        <v>62</v>
+      </c>
+      <c r="D127" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600281</t>
+        </is>
+      </c>
+      <c r="E127" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华阳新材</t>
+        </is>
+      </c>
+      <c r="F127" s="0">
+        <v>4.98</v>
+      </c>
+      <c r="G127" s="4">
+        <v>0.09933774834437091</v>
+      </c>
+      <c r="H127" s="4">
+        <v>0.08157317788116751</v>
+      </c>
+      <c r="I127" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华阳新材（600281）归入“贵金属回收+铂族金属加工+山西国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K127" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L127" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B128" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C128" s="0">
+        <v>63</v>
+      </c>
+      <c r="D128" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002178</t>
+        </is>
+      </c>
+      <c r="E128" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">延华智能</t>
+        </is>
+      </c>
+      <c r="F128" s="0">
+        <v>5.08</v>
+      </c>
+      <c r="G128" s="4">
+        <v>0.09956709956709965</v>
+      </c>
+      <c r="H128" s="4">
+        <v>0.0797134481063416</v>
+      </c>
+      <c r="I128" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 延华智能（002178）归入“AI医疗+智慧城市+智慧康养”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K128" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.9 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L128" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B129" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C129" s="0">
+        <v>64</v>
+      </c>
+      <c r="D129" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002755</t>
+        </is>
+      </c>
+      <c r="E129" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奥赛康</t>
+        </is>
+      </c>
+      <c r="F129" s="0">
+        <v>12.45</v>
+      </c>
+      <c r="G129" s="4">
+        <v>0.09982332155477014</v>
+      </c>
+      <c r="H129" s="4">
+        <v>0.0760852895041779</v>
+      </c>
+      <c r="I129" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 奥赛康（002755）归入“创新药+抗感染药+肿瘤管线”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K129" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.8 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L129" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B130" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C130" s="0">
+        <v>65</v>
+      </c>
+      <c r="D130" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002259</t>
+        </is>
+      </c>
+      <c r="E130" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">升达林业</t>
+        </is>
+      </c>
+      <c r="F130" s="0">
+        <v>4.52</v>
+      </c>
+      <c r="G130" s="4">
+        <v>0.09975669099756669</v>
+      </c>
+      <c r="H130" s="4">
+        <v>0.07587901403200374</v>
+      </c>
+      <c r="I130" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 升达林业（002259）归入“天然气+LNG加工”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K130" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.8 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L130" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B131" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C131" s="0">
+        <v>66</v>
+      </c>
+      <c r="D131" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002022</t>
+        </is>
+      </c>
+      <c r="E131" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">科华生物</t>
+        </is>
+      </c>
+      <c r="F131" s="0">
+        <v>6.17</v>
+      </c>
+      <c r="G131" s="4">
+        <v>0.09982174688057042</v>
+      </c>
+      <c r="H131" s="4">
+        <v>0.07350526141615919</v>
+      </c>
+      <c r="I131" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 科华生物（002022）归入“体外诊断+流感检测+海外拓展”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.9 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B132" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C132" s="0">
+        <v>67</v>
+      </c>
+      <c r="D132" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002042</t>
+        </is>
+      </c>
+      <c r="E132" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华孚时尚</t>
+        </is>
+      </c>
+      <c r="F132" s="0">
+        <v>4.22</v>
+      </c>
+      <c r="G132" s="4">
+        <v>0.09895833333333325</v>
+      </c>
+      <c r="H132" s="4">
+        <v>0.07342317012570491</v>
+      </c>
+      <c r="I132" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华孚时尚（002042）归入“算力租赁+色纺纱+半年报增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K132" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.4 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L132" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B133" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C133" s="0">
+        <v>68</v>
+      </c>
+      <c r="D133" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600812</t>
+        </is>
+      </c>
+      <c r="E133" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华北制药</t>
+        </is>
+      </c>
+      <c r="F133" s="0">
+        <v>5.08</v>
+      </c>
+      <c r="G133" s="4">
+        <v>0.09956709956709965</v>
+      </c>
+      <c r="H133" s="4">
+        <v>0.07219771331434721</v>
+      </c>
+      <c r="I133" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华北制药（600812）归入“抗生素+创新药+海外市场”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K133" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.5 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L133" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B134" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C134" s="0">
+        <v>69</v>
+      </c>
+      <c r="D134" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000402</t>
+        </is>
+      </c>
+      <c r="E134" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金 融 街</t>
+        </is>
+      </c>
+      <c r="F134" s="0">
+        <v>2.77</v>
+      </c>
+      <c r="G134" s="4">
+        <v>0.0992063492063493</v>
+      </c>
+      <c r="H134" s="4">
+        <v>0.07181074637154793</v>
+      </c>
+      <c r="I134" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 金 融 街（000402）归入“房地产+城市更新+北京国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K134" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.8 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L134" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B135" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C135" s="0">
+        <v>70</v>
+      </c>
+      <c r="D135" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600587</t>
+        </is>
+      </c>
+      <c r="E135" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新华医疗</t>
+        </is>
+      </c>
+      <c r="F135" s="0">
+        <v>13.4</v>
+      </c>
+      <c r="G135" s="4">
+        <v>0.10016420361247945</v>
+      </c>
+      <c r="H135" s="4">
+        <v>0.06955262861834076</v>
+      </c>
+      <c r="I135" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 新华医疗（600587）归入“康复医疗+医疗器械+脑机接口+康复机器人”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K135" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.9 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L135" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B136" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C136" s="0">
+        <v>71</v>
+      </c>
+      <c r="D136" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603636</t>
+        </is>
+      </c>
+      <c r="E136" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南威软件</t>
+        </is>
+      </c>
+      <c r="F136" s="0">
+        <v>7.28</v>
+      </c>
+      <c r="G136" s="4">
+        <v>0.09969788519637458</v>
+      </c>
+      <c r="H136" s="4">
+        <v>0.06324280779073169</v>
+      </c>
+      <c r="I136" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 南威软件（603636）归入“AI应用+算力租赁+政务数字化”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K136" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.9 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L136" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B137" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C137" s="0">
+        <v>72</v>
+      </c>
+      <c r="D137" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600218</t>
+        </is>
+      </c>
+      <c r="E137" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全柴动力</t>
+        </is>
+      </c>
+      <c r="F137" s="0">
+        <v>8.27</v>
+      </c>
+      <c r="G137" s="4">
+        <v>0.0997340425531914</v>
+      </c>
+      <c r="H137" s="4">
+        <v>0.06154928384555261</v>
+      </c>
+      <c r="I137" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J137" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 全柴动力（600218）归入“柴油机+氢燃料电池+国企背景”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K137" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 5.6 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L137" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B138" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C138" s="0">
+        <v>73</v>
+      </c>
+      <c r="D138" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600383</t>
+        </is>
+      </c>
+      <c r="E138" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金地集团</t>
+        </is>
+      </c>
+      <c r="F138" s="0">
+        <v>2.47</v>
+      </c>
+      <c r="G138" s="4">
+        <v>0.09777777777777796</v>
+      </c>
+      <c r="H138" s="4">
+        <v>0.03521197211194885</v>
+      </c>
+      <c r="I138" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no_verified_event</t>
+        </is>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">事件证据层未找到与当日涨停直接匹配的公告或新闻；系统不把概念标签、技术形态或主观猜测当成涨停原因。</t>
+        </is>
+      </c>
+      <c r="K138" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">截至运行时成交量约为20日均量的 3.4 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 94 家涨停，其中首板 73 家、2板及以上 21 家。</t>
+        </is>
+      </c>
+      <c r="L138" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M13"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -3688,6 +7630,596 @@
       <c r="M3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">次日收盘价</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001376</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">百通能源</t>
+        </is>
+      </c>
+      <c r="F4" s="4">
+        <v>0.4337329973097727</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0.09715639810426535</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.10031595576619279</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.10031595576619279</v>
+      </c>
+      <c r="J4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +10.03%</t>
+        </is>
+      </c>
+      <c r="L4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603686</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">福龙马</t>
+        </is>
+      </c>
+      <c r="F5" s="4">
+        <v>0.4142972475302373</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0.08920491273432463</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.08920491273432463</v>
+      </c>
+      <c r="I5" s="4">
+        <v>-0.01616031027795739</v>
+      </c>
+      <c r="J5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -1.62%</t>
+        </is>
+      </c>
+      <c r="L5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601579</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">会稽山</t>
+        </is>
+      </c>
+      <c r="F6" s="4">
+        <v>0.19249348873054756</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0.020097442143726996</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.09987819732034087</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.09987819732034087</v>
+      </c>
+      <c r="J6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +9.99%</t>
+        </is>
+      </c>
+      <c r="L6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601086</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">国芳集团</t>
+        </is>
+      </c>
+      <c r="F7" s="4">
+        <v>0.17189143699227655</v>
+      </c>
+      <c r="G7" s="4">
+        <v>0.03175591531755928</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.10024906600249084</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.10024906600249084</v>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +10.02%</t>
+        </is>
+      </c>
+      <c r="L7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002631</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">德尔未来</t>
+        </is>
+      </c>
+      <c r="F8" s="4">
+        <v>0.15676554518539035</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0.0045351473922901064</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.08843537414965996</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.06878306878306883</v>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +6.88%</t>
+        </is>
+      </c>
+      <c r="L8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603353</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">和顺石油</t>
+        </is>
+      </c>
+      <c r="F9" s="4">
+        <v>0.1561549742231579</v>
+      </c>
+      <c r="G9" s="4">
+        <v>0.015036045314109181</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.06405767250257455</v>
+      </c>
+      <c r="I9" s="4">
+        <v>-0.04449021627188454</v>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -4.45%</t>
+        </is>
+      </c>
+      <c r="L9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001212</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中旗新材</t>
+        </is>
+      </c>
+      <c r="F10" s="4">
+        <v>0.1560505754187151</v>
+      </c>
+      <c r="G10" s="4">
+        <v>-0.005265929436545469</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.018957345971564177</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.00868878357030023</v>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +0.87%</t>
+        </is>
+      </c>
+      <c r="L10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603138</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">海量数据</t>
+        </is>
+      </c>
+      <c r="F11" s="4">
+        <v>0.15416750520049954</v>
+      </c>
+      <c r="G11" s="4">
+        <v>0.026974951830443183</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.04688503532434174</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.010918432883750828</v>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +1.09%</t>
+        </is>
+      </c>
+      <c r="L11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15.74</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600343</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">航天动力</t>
+        </is>
+      </c>
+      <c r="F12" s="4">
+        <v>0.15170675706937384</v>
+      </c>
+      <c r="G12" s="4">
+        <v>-0.014305491462851982</v>
+      </c>
+      <c r="H12" s="4">
+        <v>-0.006460544531610601</v>
+      </c>
+      <c r="I12" s="4">
+        <v>-0.029072450392247484</v>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -2.91%</t>
+        </is>
+      </c>
+      <c r="L12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603316</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">诚邦股份</t>
+        </is>
+      </c>
+      <c r="F13" s="4">
+        <v>0.14909280780204942</v>
+      </c>
+      <c r="G13" s="4">
+        <v>0.046135410425404366</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.10005991611743537</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.10005991611743537</v>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +10.01%</t>
+        </is>
+      </c>
+      <c r="L13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18.36</t>
         </is>
       </c>
     </row>
@@ -3779,21 +8311,29 @@
         </is>
       </c>
       <c r="B3" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="0">
-        <v>0</v>
-      </c>
-      <c r="E3" s="0"/>
-      <c r="F3" s="0"/>
-      <c r="G3" s="0"/>
+        <v>1</v>
+      </c>
+      <c r="E3" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0.20967741935483872</v>
+      </c>
+      <c r="G3" s="0">
+        <v>4.769230769230769</v>
+      </c>
       <c r="H3" s="0">
-        <v>0</v>
-      </c>
-      <c r="I3" s="0"/>
+        <v>1</v>
+      </c>
+      <c r="I3" s="4">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
@@ -3802,21 +8342,29 @@
         </is>
       </c>
       <c r="B4" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="0">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D4" s="0">
-        <v>0</v>
-      </c>
-      <c r="E4" s="0"/>
-      <c r="F4" s="0"/>
-      <c r="G4" s="0"/>
+        <v>2</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0.20967741935483872</v>
+      </c>
+      <c r="G4" s="0">
+        <v>3.1794871794871793</v>
+      </c>
       <c r="H4" s="0">
-        <v>0</v>
-      </c>
-      <c r="I4" s="0"/>
+        <v>1</v>
+      </c>
+      <c r="I4" s="4">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
@@ -3825,21 +8373,29 @@
         </is>
       </c>
       <c r="B5" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="0">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D5" s="0">
-        <v>0</v>
-      </c>
-      <c r="E5" s="0"/>
-      <c r="F5" s="0"/>
-      <c r="G5" s="0"/>
+        <v>3</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0.20967741935483872</v>
+      </c>
+      <c r="G5" s="0">
+        <v>2.3846153846153846</v>
+      </c>
       <c r="H5" s="0">
-        <v>0</v>
-      </c>
-      <c r="I5" s="0"/>
+        <v>1</v>
+      </c>
+      <c r="I5" s="4">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
@@ -3848,21 +8404,29 @@
         </is>
       </c>
       <c r="B6" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" s="0">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D6" s="0">
-        <v>0</v>
-      </c>
-      <c r="E6" s="0"/>
-      <c r="F6" s="0"/>
-      <c r="G6" s="0"/>
+        <v>4</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.20967741935483872</v>
+      </c>
+      <c r="G6" s="0">
+        <v>1.9076923076923078</v>
+      </c>
       <c r="H6" s="0">
-        <v>0</v>
-      </c>
-      <c r="I6" s="0"/>
+        <v>1</v>
+      </c>
+      <c r="I6" s="4">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">

--- a/docs/downloads/latest.xlsx
+++ b/docs/downloads/latest.xlsx
@@ -3590,7 +3590,7 @@
         <v>0.09951456310679617</v>
       </c>
       <c r="H66" s="4">
-        <v>0.4652418066589123</v>
+        <v>0.4611881460878557</v>
       </c>
       <c r="I66" s="0" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>0.09981167608286266</v>
       </c>
       <c r="H67" s="4">
-        <v>0.46339117758857357</v>
+        <v>0.45933979110887185</v>
       </c>
       <c r="I67" s="0" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>0.10035211267605648</v>
       </c>
       <c r="H68" s="4">
-        <v>0.37674420222437527</v>
+        <v>0.3729238945976068</v>
       </c>
       <c r="I68" s="0" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>0.09905660377358494</v>
       </c>
       <c r="H69" s="4">
-        <v>0.33858885816024553</v>
+        <v>0.33494752781400194</v>
       </c>
       <c r="I69" s="0" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         <v>0.09993396434074399</v>
       </c>
       <c r="H70" s="4">
-        <v>0.2342618480988038</v>
+        <v>0.2313500472020358</v>
       </c>
       <c r="I70" s="0" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>0.09999999999999985</v>
       </c>
       <c r="H71" s="4">
-        <v>0.1950828698236118</v>
+        <v>0.19253560544550263</v>
       </c>
       <c r="I71" s="0" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 美盈森（002303）归入“包装一体化+消费电子包装+模切业务+海外产能”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 美盈森（002303）归入“导热凝胶+模切业务+消费电子包装+海外产能”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K71" s="3" t="inlineStr">
@@ -3914,7 +3914,7 @@
         <v>0.10043290043290053</v>
       </c>
       <c r="H72" s="4">
-        <v>0.18885269109174457</v>
+        <v>0.18636794088290495</v>
       </c>
       <c r="I72" s="0" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>0.10037878787878786</v>
       </c>
       <c r="H73" s="4">
-        <v>0.17677673435453747</v>
+        <v>0.17441670443211496</v>
       </c>
       <c r="I73" s="0" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>0.09986320109439116</v>
       </c>
       <c r="H74" s="4">
-        <v>0.15556029997125023</v>
+        <v>0.15343072575789812</v>
       </c>
       <c r="I74" s="0" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>0.10071942446043171</v>
       </c>
       <c r="H75" s="4">
-        <v>0.1543190939107268</v>
+        <v>0.1522034488145214</v>
       </c>
       <c r="I75" s="0" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>0.10000000000000009</v>
       </c>
       <c r="H76" s="4">
-        <v>0.14686166753756646</v>
+        <v>0.14483075118638725</v>
       </c>
       <c r="I76" s="0" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         <v>0.1000220799293443</v>
       </c>
       <c r="H77" s="4">
-        <v>0.14652972517382876</v>
+        <v>0.1445026216737178</v>
       </c>
       <c r="I77" s="0" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>0.09958506224066375</v>
       </c>
       <c r="H78" s="4">
-        <v>0.1410810028618283</v>
+        <v>0.13911699066655248</v>
       </c>
       <c r="I78" s="0" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>0.09957924263674611</v>
       </c>
       <c r="H79" s="4">
-        <v>0.14094176062559174</v>
+        <v>0.13897937319510964</v>
       </c>
       <c r="I79" s="0" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>0.10031746031746014</v>
       </c>
       <c r="H80" s="4">
-        <v>0.1360845517633556</v>
+        <v>0.1341792299812645</v>
       </c>
       <c r="I80" s="0" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>0.10017094017094008</v>
       </c>
       <c r="H81" s="4">
-        <v>0.1345846761414189</v>
+        <v>0.1326971285803063</v>
       </c>
       <c r="I81" s="0" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>0.09996678844237783</v>
       </c>
       <c r="H82" s="4">
-        <v>0.1343407096372262</v>
+        <v>0.13245606000517549</v>
       </c>
       <c r="I82" s="0" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>0.09982486865148864</v>
       </c>
       <c r="H83" s="4">
-        <v>0.13114815737366875</v>
+        <v>0.12930160579892241</v>
       </c>
       <c r="I83" s="0" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>0.10000000000000009</v>
       </c>
       <c r="H84" s="4">
-        <v>0.12987375444567673</v>
+        <v>0.128042502000851</v>
       </c>
       <c r="I84" s="0" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         <v>0.10093457943925245</v>
       </c>
       <c r="H85" s="4">
-        <v>0.12873773638560287</v>
+        <v>0.1269201656086359</v>
       </c>
       <c r="I85" s="0" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>0.10000000000000009</v>
       </c>
       <c r="H86" s="4">
-        <v>0.12766536973531</v>
+        <v>0.1258607519512354</v>
       </c>
       <c r="I86" s="0" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>0.10012412081092247</v>
       </c>
       <c r="H87" s="4">
-        <v>0.12764818270936235</v>
+        <v>0.1258437728251673</v>
       </c>
       <c r="I87" s="0" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>0.10000000000000009</v>
       </c>
       <c r="H88" s="4">
-        <v>0.12699105645561096</v>
+        <v>0.1251946024785319</v>
       </c>
       <c r="I88" s="0" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>0.09998225167130093</v>
       </c>
       <c r="H89" s="4">
-        <v>0.12614165188586235</v>
+        <v>0.12435550223703382</v>
       </c>
       <c r="I89" s="0" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>0.10019455252918297</v>
       </c>
       <c r="H90" s="4">
-        <v>0.1242262874871728</v>
+        <v>0.12246345834260695</v>
       </c>
       <c r="I90" s="0" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>0.10009398496240607</v>
       </c>
       <c r="H91" s="4">
-        <v>0.12335097963154369</v>
+        <v>0.12159884688835206</v>
       </c>
       <c r="I91" s="0" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>0.10008375209380226</v>
       </c>
       <c r="H92" s="4">
-        <v>0.12259349734404079</v>
+        <v>0.1208506409500566</v>
       </c>
       <c r="I92" s="0" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>0.09973753280839892</v>
       </c>
       <c r="H93" s="4">
-        <v>0.12196322877452691</v>
+        <v>0.1202281048317061</v>
       </c>
       <c r="I93" s="0" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>0.10010842067220803</v>
       </c>
       <c r="H94" s="4">
-        <v>0.1216132115219928</v>
+        <v>0.11988238725771433</v>
       </c>
       <c r="I94" s="0" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>0.10030864197530853</v>
       </c>
       <c r="H95" s="4">
-        <v>0.12084880643633285</v>
+        <v>0.11912738590244411</v>
       </c>
       <c r="I95" s="0" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>0.10011325028312568</v>
       </c>
       <c r="H96" s="4">
-        <v>0.12028803328689865</v>
+        <v>0.11857352329046723</v>
       </c>
       <c r="I96" s="0" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>0.10011990407673865</v>
       </c>
       <c r="H97" s="4">
-        <v>0.12016408243019151</v>
+        <v>0.11845110126706428</v>
       </c>
       <c r="I97" s="0" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>0.10047846889952151</v>
       </c>
       <c r="H98" s="4">
-        <v>0.11799329681958166</v>
+        <v>0.11630717024809666</v>
       </c>
       <c r="I98" s="0" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>0.09984276729559749</v>
       </c>
       <c r="H99" s="4">
-        <v>0.1178917621278945</v>
+        <v>0.11620689532465875</v>
       </c>
       <c r="I99" s="0" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>0.10041841004184103</v>
       </c>
       <c r="H100" s="4">
-        <v>0.11730331242139477</v>
+        <v>0.11562575316860425</v>
       </c>
       <c r="I100" s="0" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>0.10004992511233146</v>
       </c>
       <c r="H101" s="4">
-        <v>0.11683520091249867</v>
+        <v>0.11516346272672053</v>
       </c>
       <c r="I101" s="0" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>0.1000339097999321</v>
       </c>
       <c r="H102" s="4">
-        <v>0.11517526054749688</v>
+        <v>0.11352422059347794</v>
       </c>
       <c r="I102" s="0" t="inlineStr">
         <is>
@@ -5588,7 +5588,7 @@
         <v>0.10080645161290323</v>
       </c>
       <c r="H103" s="4">
-        <v>0.11363207665999002</v>
+        <v>0.11200035815162764</v>
       </c>
       <c r="I103" s="0" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>0.09988038277511979</v>
       </c>
       <c r="H104" s="4">
-        <v>0.11309807028350415</v>
+        <v>0.11147305555111292</v>
       </c>
       <c r="I104" s="0" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>0.09999999999999985</v>
       </c>
       <c r="H105" s="4">
-        <v>0.11224237226615294</v>
+        <v>0.11062811876511529</v>
       </c>
       <c r="I105" s="0" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         <v>0.09986320109439116</v>
       </c>
       <c r="H106" s="4">
-        <v>0.11179183978497693</v>
+        <v>0.11018326158009552</v>
       </c>
       <c r="I106" s="0" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>0.10000000000000009</v>
       </c>
       <c r="H107" s="4">
-        <v>0.10888589363275825</v>
+        <v>0.10731407724855241</v>
       </c>
       <c r="I107" s="0" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>0.09980620155038755</v>
       </c>
       <c r="H108" s="4">
-        <v>0.10654790904146405</v>
+        <v>0.10500586553860758</v>
       </c>
       <c r="I108" s="0" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>0.09995386744579428</v>
       </c>
       <c r="H109" s="4">
-        <v>0.10652378462237674</v>
+        <v>0.10498204924136273</v>
       </c>
       <c r="I109" s="0" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>0.09974747474747492</v>
       </c>
       <c r="H110" s="4">
-        <v>0.10627334237847577</v>
+        <v>0.10473480679487733</v>
       </c>
       <c r="I110" s="0" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>0.10007818608287744</v>
       </c>
       <c r="H111" s="4">
-        <v>0.10535244752672822</v>
+        <v>0.10382569508703109</v>
       </c>
       <c r="I111" s="0" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>0.10121457489878537</v>
       </c>
       <c r="H112" s="4">
-        <v>0.10512519825974313</v>
+        <v>0.10360135771934445</v>
       </c>
       <c r="I112" s="0" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>0.100095328884652</v>
       </c>
       <c r="H113" s="4">
-        <v>0.10421138398395025</v>
+        <v>0.10269926944056101</v>
       </c>
       <c r="I113" s="0" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>0.09970014992503738</v>
       </c>
       <c r="H114" s="4">
-        <v>0.10355953792160928</v>
+        <v>0.10205580413752809</v>
       </c>
       <c r="I114" s="0" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>0.10052356020942387</v>
       </c>
       <c r="H115" s="4">
-        <v>0.10309535830565501</v>
+        <v>0.10159760074389468</v>
       </c>
       <c r="I115" s="0" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>0.10000000000000009</v>
       </c>
       <c r="H116" s="4">
-        <v>0.10098199942322085</v>
+        <v>0.09951153804098263</v>
       </c>
       <c r="I116" s="0" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>0.09954751131221728</v>
       </c>
       <c r="H117" s="4">
-        <v>0.09767660906243784</v>
+        <v>0.09624912650656824</v>
       </c>
       <c r="I117" s="0" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>0.0998810939357908</v>
       </c>
       <c r="H118" s="4">
-        <v>0.09672551632117354</v>
+        <v>0.09531046520357281</v>
       </c>
       <c r="I118" s="0" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>0.10042194092827007</v>
       </c>
       <c r="H119" s="4">
-        <v>0.09543416738935327</v>
+        <v>0.09403604137953116</v>
       </c>
       <c r="I119" s="0" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
         <v>0.10022522522522515</v>
       </c>
       <c r="H120" s="4">
-        <v>0.09437593703049083</v>
+        <v>0.09299172049279736</v>
       </c>
       <c r="I120" s="0" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>0.09978308026030369</v>
       </c>
       <c r="H121" s="4">
-        <v>0.09245835384523732</v>
+        <v>0.09109943338820196</v>
       </c>
       <c r="I121" s="0" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>0.09963099630996307</v>
       </c>
       <c r="H122" s="4">
-        <v>0.09219350106048056</v>
+        <v>0.09083808368549665</v>
       </c>
       <c r="I122" s="0" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
         <v>0.09989594172736747</v>
       </c>
       <c r="H123" s="4">
-        <v>0.089757982561971</v>
+        <v>0.08843488373202364</v>
       </c>
       <c r="I123" s="0" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         <v>0.1002886002886003</v>
       </c>
       <c r="H124" s="4">
-        <v>0.08924696878323685</v>
+        <v>0.08793067500163357</v>
       </c>
       <c r="I124" s="0" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>0.1000645577792123</v>
       </c>
       <c r="H125" s="4">
-        <v>0.08510548454553901</v>
+        <v>0.08384464977696893</v>
       </c>
       <c r="I125" s="0" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>0.09999999999999985</v>
       </c>
       <c r="H126" s="4">
-        <v>0.08414283872293986</v>
+        <v>0.08289497333455417</v>
       </c>
       <c r="I126" s="0" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>0.09933774834437091</v>
       </c>
       <c r="H127" s="4">
-        <v>0.08157317788116751</v>
+        <v>0.08036007760043166</v>
       </c>
       <c r="I127" s="0" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>0.09956709956709965</v>
       </c>
       <c r="H128" s="4">
-        <v>0.0797134481063416</v>
+        <v>0.07852563980387312</v>
       </c>
       <c r="I128" s="0" t="inlineStr">
         <is>
@@ -6992,7 +6992,7 @@
         <v>0.09982332155477014</v>
       </c>
       <c r="H129" s="4">
-        <v>0.0760852895041779</v>
+        <v>0.07494714147046568</v>
       </c>
       <c r="I129" s="0" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>0.09975669099756669</v>
       </c>
       <c r="H130" s="4">
-        <v>0.07587901403200374</v>
+        <v>0.07474370201588984</v>
       </c>
       <c r="I130" s="0" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>0.09982174688057042</v>
       </c>
       <c r="H131" s="4">
-        <v>0.07350526141615919</v>
+        <v>0.07240268318002151</v>
       </c>
       <c r="I131" s="0" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>0.09895833333333325</v>
       </c>
       <c r="H132" s="4">
-        <v>0.07342317012570491</v>
+        <v>0.07232172713812761</v>
       </c>
       <c r="I132" s="0" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>0.09956709956709965</v>
       </c>
       <c r="H133" s="4">
-        <v>0.07219771331434721</v>
+        <v>0.0711132428727198</v>
       </c>
       <c r="I133" s="0" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>0.0992063492063493</v>
       </c>
       <c r="H134" s="4">
-        <v>0.07181074637154793</v>
+        <v>0.07073164537399511</v>
       </c>
       <c r="I134" s="0" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>0.10016420361247945</v>
       </c>
       <c r="H135" s="4">
-        <v>0.06955262861834076</v>
+        <v>0.06850495597917687</v>
       </c>
       <c r="I135" s="0" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>0.09969788519637458</v>
       </c>
       <c r="H136" s="4">
-        <v>0.06324280779073169</v>
+        <v>0.062283817833349395</v>
       </c>
       <c r="I136" s="0" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>0.0997340425531914</v>
       </c>
       <c r="H137" s="4">
-        <v>0.06154928384555261</v>
+        <v>0.060614312182228076</v>
       </c>
       <c r="I137" s="0" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>0.09777777777777796</v>
       </c>
       <c r="H138" s="4">
-        <v>0.03521197211194885</v>
+        <v>0.03466230326882426</v>
       </c>
       <c r="I138" s="0" t="inlineStr">
         <is>

--- a/docs/downloads/latest.xlsx
+++ b/docs/downloads/latest.xlsx
@@ -93,7 +93,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L138"/>
+  <dimension ref="A1:L174"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -7501,13 +7501,1957 @@
         </is>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B139" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C139" s="0">
+        <v>1</v>
+      </c>
+      <c r="D139" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002290</t>
+        </is>
+      </c>
+      <c r="E139" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">禾盛新材</t>
+        </is>
+      </c>
+      <c r="F139" s="0">
+        <v>77.85</v>
+      </c>
+      <c r="G139" s="4">
+        <v>0.10004239084357769</v>
+      </c>
+      <c r="H139" s="4">
+        <v>0.4502221241559218</v>
+      </c>
+      <c r="I139" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 禾盛新材（002290）归入“参股CPU+算力+家电复材”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K139" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 10.0%）。截至运行时成交量约为20日均量的 0.5 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L139" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B140" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C140" s="0">
+        <v>2</v>
+      </c>
+      <c r="D140" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600770</t>
+        </is>
+      </c>
+      <c r="E140" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">综艺股份</t>
+        </is>
+      </c>
+      <c r="F140" s="0">
+        <v>6.63</v>
+      </c>
+      <c r="G140" s="4">
+        <v>0.09950248756218905</v>
+      </c>
+      <c r="H140" s="4">
+        <v>0.43390615253804576</v>
+      </c>
+      <c r="I140" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 综艺股份（600770）归入“参股神州龙芯（CPU）+功率半导体IDM+金刚石散热”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K140" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 10.0%）。截至运行时成交量约为20日均量的 0.4 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L140" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B141" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C141" s="0">
+        <v>3</v>
+      </c>
+      <c r="D141" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600641</t>
+        </is>
+      </c>
+      <c r="E141" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">先导基电</t>
+        </is>
+      </c>
+      <c r="F141" s="0">
+        <v>43.74</v>
+      </c>
+      <c r="G141" s="4">
+        <v>0.10010060362173047</v>
+      </c>
+      <c r="H141" s="4">
+        <v>0.20667295309450376</v>
+      </c>
+      <c r="I141" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 先导基电（600641）归入“半导体材料+离子注入机+半年报增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K141" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L141" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">近5日涨幅偏高，短线获利盘压力更大</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B142" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C142" s="0">
+        <v>4</v>
+      </c>
+      <c r="D142" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000676</t>
+        </is>
+      </c>
+      <c r="E142" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">智度股份</t>
+        </is>
+      </c>
+      <c r="F142" s="0">
+        <v>7.45</v>
+      </c>
+      <c r="G142" s="4">
+        <v>0.10044313146233395</v>
+      </c>
+      <c r="H142" s="4">
+        <v>0.19883952200365676</v>
+      </c>
+      <c r="I142" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 智度股份（000676）归入“数字营销+人工智能+中报增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K142" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 8.4%）。截至运行时成交量约为20日均量的 3.1 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L142" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B143" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C143" s="0">
+        <v>5</v>
+      </c>
+      <c r="D143" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605058</t>
+        </is>
+      </c>
+      <c r="E143" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">澳弘电子</t>
+        </is>
+      </c>
+      <c r="F143" s="0">
+        <v>53.27</v>
+      </c>
+      <c r="G143" s="4">
+        <v>0.09993805492463359</v>
+      </c>
+      <c r="H143" s="4">
+        <v>0.1846622218762648</v>
+      </c>
+      <c r="I143" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 澳弘电子（605058）归入“PCB+HDI板+服务器电源”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K143" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.8 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L143" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；近10日涨幅偏高</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B144" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C144" s="0">
+        <v>6</v>
+      </c>
+      <c r="D144" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605258</t>
+        </is>
+      </c>
+      <c r="E144" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">协和电子</t>
+        </is>
+      </c>
+      <c r="F144" s="0">
+        <v>42.16</v>
+      </c>
+      <c r="G144" s="4">
+        <v>0.0999217323245498</v>
+      </c>
+      <c r="H144" s="4">
+        <v>0.15343903800093306</v>
+      </c>
+      <c r="I144" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 协和电子（605258）归入“PCB+高频通讯+新能源电池”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K144" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L144" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B145" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C145" s="0">
+        <v>7</v>
+      </c>
+      <c r="D145" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603221</t>
+        </is>
+      </c>
+      <c r="E145" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">爱丽家居</t>
+        </is>
+      </c>
+      <c r="F145" s="0">
+        <v>33.55</v>
+      </c>
+      <c r="G145" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H145" s="4">
+        <v>0.12656930475570644</v>
+      </c>
+      <c r="I145" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 爱丽家居（603221）归入“存储测试+拟收欧康诺+弹性地板”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K145" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L145" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B146" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C146" s="0">
+        <v>8</v>
+      </c>
+      <c r="D146" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002768</t>
+        </is>
+      </c>
+      <c r="E146" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">国恩股份</t>
+        </is>
+      </c>
+      <c r="F146" s="0">
+        <v>74.86</v>
+      </c>
+      <c r="G146" s="4">
+        <v>0.10007347538574575</v>
+      </c>
+      <c r="H146" s="4">
+        <v>0.1254908486037569</v>
+      </c>
+      <c r="I146" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 国恩股份（002768）归入“化工新材料+人形机器人+业绩增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K146" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.9 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L146" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B147" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C147" s="0">
+        <v>9</v>
+      </c>
+      <c r="D147" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002757</t>
+        </is>
+      </c>
+      <c r="E147" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南兴股份</t>
+        </is>
+      </c>
+      <c r="F147" s="0">
+        <v>19.86</v>
+      </c>
+      <c r="G147" s="4">
+        <v>0.10027700831024934</v>
+      </c>
+      <c r="H147" s="4">
+        <v>0.12386960359956992</v>
+      </c>
+      <c r="I147" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 南兴股份（002757）归入“AI智算+AIDC+家具智能装备”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K147" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L147" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B148" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C148" s="0">
+        <v>10</v>
+      </c>
+      <c r="D148" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002564</t>
+        </is>
+      </c>
+      <c r="E148" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天沃科技</t>
+        </is>
+      </c>
+      <c r="F148" s="0">
+        <v>5.45</v>
+      </c>
+      <c r="G148" s="4">
+        <v>0.10101010101010101</v>
+      </c>
+      <c r="H148" s="4">
+        <v>0.12366445888872842</v>
+      </c>
+      <c r="I148" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 天沃科技（002564）归入“光热风电+电力设计+高端装备”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K148" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L148" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B149" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C149" s="0">
+        <v>11</v>
+      </c>
+      <c r="D149" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605179</t>
+        </is>
+      </c>
+      <c r="E149" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一鸣食品</t>
+        </is>
+      </c>
+      <c r="F149" s="0">
+        <v>30.04</v>
+      </c>
+      <c r="G149" s="4">
+        <v>0.09996338337605269</v>
+      </c>
+      <c r="H149" s="4">
+        <v>0.12149828070899099</v>
+      </c>
+      <c r="I149" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J149" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 一鸣食品（605179）归入“低温乳品+大消费+业绩改善”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K149" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，量能未出现极端放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L149" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B150" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C150" s="0">
+        <v>12</v>
+      </c>
+      <c r="D150" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002141</t>
+        </is>
+      </c>
+      <c r="E150" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">贤丰控股</t>
+        </is>
+      </c>
+      <c r="F150" s="0">
+        <v>7.43</v>
+      </c>
+      <c r="G150" s="4">
+        <v>0.1007407407407408</v>
+      </c>
+      <c r="H150" s="4">
+        <v>0.11659962631952028</v>
+      </c>
+      <c r="I150" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 贤丰控股（002141）归入“覆铜板+印制电路板+动物保健”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K150" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L150" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B151" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C151" s="0">
+        <v>13</v>
+      </c>
+      <c r="D151" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002672</t>
+        </is>
+      </c>
+      <c r="E151" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东江环保</t>
+        </is>
+      </c>
+      <c r="F151" s="0">
+        <v>4.03</v>
+      </c>
+      <c r="G151" s="4">
+        <v>0.1010928961748634</v>
+      </c>
+      <c r="H151" s="4">
+        <v>0.1157017053314146</v>
+      </c>
+      <c r="I151" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 东江环保（002672）归入“危废资源化+稀贵金属回收+含氟废液资源化”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K151" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.4 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L151" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B152" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C152" s="0">
+        <v>14</v>
+      </c>
+      <c r="D152" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603893</t>
+        </is>
+      </c>
+      <c r="E152" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瑞芯微</t>
+        </is>
+      </c>
+      <c r="F152" s="0">
+        <v>217.8</v>
+      </c>
+      <c r="G152" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H152" s="4">
+        <v>0.11241120215955598</v>
+      </c>
+      <c r="I152" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no_verified_event</t>
+        </is>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">事件证据层未找到与当日涨停直接匹配的公告或新闻；系统不把概念标签、技术形态或主观猜测当成涨停原因。</t>
+        </is>
+      </c>
+      <c r="K152" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L152" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B153" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C153" s="0">
+        <v>15</v>
+      </c>
+      <c r="D153" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605178</t>
+        </is>
+      </c>
+      <c r="E153" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时空科技</t>
+        </is>
+      </c>
+      <c r="F153" s="0">
+        <v>74.79</v>
+      </c>
+      <c r="G153" s="4">
+        <v>0.10001470804530088</v>
+      </c>
+      <c r="H153" s="4">
+        <v>0.1115478307784586</v>
+      </c>
+      <c r="I153" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 时空科技（605178）归入“存储芯片+拟收购嘉合劲威+照明工程”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K153" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，量能未出现极端放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L153" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B154" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C154" s="0">
+        <v>16</v>
+      </c>
+      <c r="D154" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601949</t>
+        </is>
+      </c>
+      <c r="E154" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中国出版</t>
+        </is>
+      </c>
+      <c r="F154" s="0">
+        <v>6.62</v>
+      </c>
+      <c r="G154" s="4">
+        <v>0.09966777408637872</v>
+      </c>
+      <c r="H154" s="4">
+        <v>0.10989435091165331</v>
+      </c>
+      <c r="I154" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 中国出版（601949）归入“AI出版+图书出版+中国出版集团”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K154" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L154" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B155" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C155" s="0">
+        <v>17</v>
+      </c>
+      <c r="D155" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605218</t>
+        </is>
+      </c>
+      <c r="E155" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">伟时电子</t>
+        </is>
+      </c>
+      <c r="F155" s="0">
+        <v>15.94</v>
+      </c>
+      <c r="G155" s="4">
+        <v>0.10006901311249126</v>
+      </c>
+      <c r="H155" s="4">
+        <v>0.10855580337764112</v>
+      </c>
+      <c r="I155" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 伟时电子（605218）归入“背光显示模组+MiniLED+车载显示”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K155" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.7 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L155" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B156" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C156" s="0">
+        <v>18</v>
+      </c>
+      <c r="D156" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002301</t>
+        </is>
+      </c>
+      <c r="E156" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">齐心集团</t>
+        </is>
+      </c>
+      <c r="F156" s="0">
+        <v>9.27</v>
+      </c>
+      <c r="G156" s="4">
+        <v>0.09964412811387892</v>
+      </c>
+      <c r="H156" s="4">
+        <v>0.10851466163083029</v>
+      </c>
+      <c r="I156" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 齐心集团（002301）归入“AI应用+B2B集采+MRO工业品”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K156" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.2 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L156" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B157" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C157" s="0">
+        <v>19</v>
+      </c>
+      <c r="D157" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600403</t>
+        </is>
+      </c>
+      <c r="E157" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大有能源</t>
+        </is>
+      </c>
+      <c r="F157" s="0">
+        <v>7.6</v>
+      </c>
+      <c r="G157" s="4">
+        <v>0.09985528219971052</v>
+      </c>
+      <c r="H157" s="4">
+        <v>0.10749344084910167</v>
+      </c>
+      <c r="I157" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 大有能源（600403）归入“煤炭+产销增长+吸收合并”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K157" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L157" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B158" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C158" s="0">
+        <v>20</v>
+      </c>
+      <c r="D158" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002912</t>
+        </is>
+      </c>
+      <c r="E158" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中新赛克</t>
+        </is>
+      </c>
+      <c r="F158" s="0">
+        <v>26.38</v>
+      </c>
+      <c r="G158" s="4">
+        <v>0.10008340283569626</v>
+      </c>
+      <c r="H158" s="4">
+        <v>0.10367510516621449</v>
+      </c>
+      <c r="I158" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 中新赛克（002912）归入“AI安全+网络安全+间接投资机器人+深圳国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K158" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.9 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L158" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B159" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C159" s="0">
+        <v>21</v>
+      </c>
+      <c r="D159" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002313</t>
+        </is>
+      </c>
+      <c r="E159" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">日海智能</t>
+        </is>
+      </c>
+      <c r="F159" s="0">
+        <v>9.3</v>
+      </c>
+      <c r="G159" s="4">
+        <v>0.10059171597633142</v>
+      </c>
+      <c r="H159" s="4">
+        <v>0.10161852735092247</v>
+      </c>
+      <c r="I159" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J159" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 日海智能（002313）归入“端侧AI智能模组+机器人+半年报扭亏+珠海国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K159" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L159" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B160" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C160" s="0">
+        <v>22</v>
+      </c>
+      <c r="D160" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600815</t>
+        </is>
+      </c>
+      <c r="E160" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">厦工股份</t>
+        </is>
+      </c>
+      <c r="F160" s="0">
+        <v>4.19</v>
+      </c>
+      <c r="G160" s="4">
+        <v>0.09973753280839916</v>
+      </c>
+      <c r="H160" s="4">
+        <v>0.09832480772433612</v>
+      </c>
+      <c r="I160" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 厦工股份（600815）归入“工程机械+智能矿卡+盾构机”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K160" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L160" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B161" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C161" s="0">
+        <v>23</v>
+      </c>
+      <c r="D161" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001268</t>
+        </is>
+      </c>
+      <c r="E161" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">联合精密</t>
+        </is>
+      </c>
+      <c r="F161" s="0">
+        <v>26.57</v>
+      </c>
+      <c r="G161" s="4">
+        <v>0.10020703933747409</v>
+      </c>
+      <c r="H161" s="4">
+        <v>0.09602081687383678</v>
+      </c>
+      <c r="I161" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J161" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 联合精密（001268）归入“航空制造+精密零部件+拟定增”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K161" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.8 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L161" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C162" s="0">
+        <v>24</v>
+      </c>
+      <c r="D162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001260</t>
+        </is>
+      </c>
+      <c r="E162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">坤泰股份</t>
+        </is>
+      </c>
+      <c r="F162" s="0">
+        <v>20.28</v>
+      </c>
+      <c r="G162" s="4">
+        <v>0.09978308026030369</v>
+      </c>
+      <c r="H162" s="4">
+        <v>0.09462423923460407</v>
+      </c>
+      <c r="I162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 坤泰股份（001260）归入“汽车软内饰+新能源客户+海外产能”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K162" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.9 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L162" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B163" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C163" s="0">
+        <v>25</v>
+      </c>
+      <c r="D163" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605398</t>
+        </is>
+      </c>
+      <c r="E163" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新炬网络</t>
+        </is>
+      </c>
+      <c r="F163" s="0">
+        <v>23.63</v>
+      </c>
+      <c r="G163" s="4">
+        <v>0.10009310986964604</v>
+      </c>
+      <c r="H163" s="4">
+        <v>0.09449514765255292</v>
+      </c>
+      <c r="I163" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J163" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 新炬网络（605398）归入“AI运维+数据中心运维+短剧营销”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K163" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.5 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L163" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B164" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C164" s="0">
+        <v>26</v>
+      </c>
+      <c r="D164" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600479</t>
+        </is>
+      </c>
+      <c r="E164" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">千金药业</t>
+        </is>
+      </c>
+      <c r="F164" s="0">
+        <v>13.57</v>
+      </c>
+      <c r="G164" s="4">
+        <v>0.09967585089141018</v>
+      </c>
+      <c r="H164" s="4">
+        <v>0.0910778945423946</v>
+      </c>
+      <c r="I164" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 千金药业（600479）归入“女性健康+创新药+药材种植+中报增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K164" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L164" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B165" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C165" s="0">
+        <v>27</v>
+      </c>
+      <c r="D165" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600418</t>
+        </is>
+      </c>
+      <c r="E165" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">江淮汽车</t>
+        </is>
+      </c>
+      <c r="F165" s="0">
+        <v>21.32</v>
+      </c>
+      <c r="G165" s="4">
+        <v>0.10010319917440658</v>
+      </c>
+      <c r="H165" s="4">
+        <v>0.08972117243049423</v>
+      </c>
+      <c r="I165" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J165" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 江淮汽车（600418）归入“汽车整车+尊界高端+华为合作+智能制造”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K165" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.2 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L165" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B166" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C166" s="0">
+        <v>28</v>
+      </c>
+      <c r="D166" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603903</t>
+        </is>
+      </c>
+      <c r="E166" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中持股份</t>
+        </is>
+      </c>
+      <c r="F166" s="0">
+        <v>15.27</v>
+      </c>
+      <c r="G166" s="4">
+        <v>0.10014409221902</v>
+      </c>
+      <c r="H166" s="4">
+        <v>0.08891420628426912</v>
+      </c>
+      <c r="I166" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 中持股份（603903）归入“半导体设备+污水处理+芯长征入主”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K166" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.6 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L166" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B167" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C167" s="0">
+        <v>29</v>
+      </c>
+      <c r="D167" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002238</t>
+        </is>
+      </c>
+      <c r="E167" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天威视讯</t>
+        </is>
+      </c>
+      <c r="F167" s="0">
+        <v>6.96</v>
+      </c>
+      <c r="G167" s="4">
+        <v>0.09952606635071092</v>
+      </c>
+      <c r="H167" s="4">
+        <v>0.0864820764173997</v>
+      </c>
+      <c r="I167" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J167" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 天威视讯（002238）归入“文化传媒+数据中心+深圳国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K167" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L167" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B168" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C168" s="0">
+        <v>30</v>
+      </c>
+      <c r="D168" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001266</t>
+        </is>
+      </c>
+      <c r="E168" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">宏英智能</t>
+        </is>
+      </c>
+      <c r="F168" s="0">
+        <v>37.75</v>
+      </c>
+      <c r="G168" s="4">
+        <v>0.09994172494172492</v>
+      </c>
+      <c r="H168" s="4">
+        <v>0.08604253644019423</v>
+      </c>
+      <c r="I168" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 宏英智能（001266）归入“液冷储能+智能电控+业绩增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K168" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.7 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L168" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B169" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C169" s="0">
+        <v>31</v>
+      </c>
+      <c r="D169" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603216</t>
+        </is>
+      </c>
+      <c r="E169" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">梦天家居</t>
+        </is>
+      </c>
+      <c r="F169" s="0">
+        <v>22.75</v>
+      </c>
+      <c r="G169" s="4">
+        <v>0.10009671179883937</v>
+      </c>
+      <c r="H169" s="4">
+        <v>0.08479925119475966</v>
+      </c>
+      <c r="I169" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J169" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 梦天家居（603216）归入“功率半导体投资+全屋定制+智能制造”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K169" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L169" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B170" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C170" s="0">
+        <v>32</v>
+      </c>
+      <c r="D170" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603039</t>
+        </is>
+      </c>
+      <c r="E170" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">XD泛微网络</t>
+        </is>
+      </c>
+      <c r="F170" s="0">
+        <v>39.7</v>
+      </c>
+      <c r="G170" s="4">
+        <v>0.10002770850651155</v>
+      </c>
+      <c r="H170" s="4">
+        <v>0.08402443508855546</v>
+      </c>
+      <c r="I170" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J170" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 XD泛微网络（603039）归入“AI应用+协同办公+鸿蒙办公”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K170" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.4 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L170" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B171" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C171" s="0">
+        <v>33</v>
+      </c>
+      <c r="D171" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603598</t>
+        </is>
+      </c>
+      <c r="E171" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">引力传媒</t>
+        </is>
+      </c>
+      <c r="F171" s="0">
+        <v>18.96</v>
+      </c>
+      <c r="G171" s="4">
+        <v>0.09976798143851529</v>
+      </c>
+      <c r="H171" s="4">
+        <v>0.08080101093762072</v>
+      </c>
+      <c r="I171" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J171" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 引力传媒（603598）归入“AI营销+AI短剧+全域营销”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K171" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.8 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L171" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B172" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C172" s="0">
+        <v>34</v>
+      </c>
+      <c r="D172" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000595</t>
+        </is>
+      </c>
+      <c r="E172" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新能股份</t>
+        </is>
+      </c>
+      <c r="F172" s="0">
+        <v>5.85</v>
+      </c>
+      <c r="G172" s="4">
+        <v>0.09962406015037573</v>
+      </c>
+      <c r="H172" s="4">
+        <v>0.07614193495978024</v>
+      </c>
+      <c r="I172" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J172" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 新能股份（000595）归入“风光储+装机增长+国资增持”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K172" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L172" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B173" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C173" s="0">
+        <v>35</v>
+      </c>
+      <c r="D173" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001322</t>
+        </is>
+      </c>
+      <c r="E173" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">箭牌家居</t>
+        </is>
+      </c>
+      <c r="F173" s="0">
+        <v>6.95</v>
+      </c>
+      <c r="G173" s="4">
+        <v>0.09968354430379754</v>
+      </c>
+      <c r="H173" s="4">
+        <v>0.06695018679630341</v>
+      </c>
+      <c r="I173" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J173" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 箭牌家居（001322）归入“智能卫浴+鸿蒙智选+智能马桶”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K173" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.8 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L173" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B174" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C174" s="0">
+        <v>36</v>
+      </c>
+      <c r="D174" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002467</t>
+        </is>
+      </c>
+      <c r="E174" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">二六三</t>
+        </is>
+      </c>
+      <c r="F174" s="0">
+        <v>5.09</v>
+      </c>
+      <c r="G174" s="4">
+        <v>0.09935205183585305</v>
+      </c>
+      <c r="H174" s="4">
+        <v>0.06294405098563571</v>
+      </c>
+      <c r="I174" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J174" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 二六三（002467）归入“AI智能通信+云网融合+跨境通信”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K174" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.1 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 59 家涨停，其中首板 36 家、2板及以上 23 家。</t>
+        </is>
+      </c>
+      <c r="L174" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M23"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -8220,6 +10164,596 @@
       <c r="M13" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">18.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000607</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华媒控股</t>
+        </is>
+      </c>
+      <c r="F14" s="4">
+        <v>0.4611881460878557</v>
+      </c>
+      <c r="G14" s="4">
+        <v>0.09933774834437092</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.09933774834437092</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.09933774834437092</v>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +9.93%</t>
+        </is>
+      </c>
+      <c r="L14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600825</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新华传媒</t>
+        </is>
+      </c>
+      <c r="F15" s="4">
+        <v>0.45933979110887185</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0.09931506849315075</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.09931506849315075</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.09931506849315075</v>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +9.93%</t>
+        </is>
+      </c>
+      <c r="L15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002614</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奥佳华</t>
+        </is>
+      </c>
+      <c r="F16" s="4">
+        <v>0.3729238945976068</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0.1008</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.1008</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.1008</v>
+      </c>
+      <c r="J16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +10.08%</t>
+        </is>
+      </c>
+      <c r="L16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600743</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华远控股</t>
+        </is>
+      </c>
+      <c r="F17" s="4">
+        <v>0.33494752781400194</v>
+      </c>
+      <c r="G17" s="4">
+        <v>0.09871244635193133</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.09871244635193133</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.09871244635193133</v>
+      </c>
+      <c r="J17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +9.87%</t>
+        </is>
+      </c>
+      <c r="L17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600301</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华锡有色</t>
+        </is>
+      </c>
+      <c r="F18" s="4">
+        <v>0.2313500472020358</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0.09965979587752649</v>
+      </c>
+      <c r="H18" s="4">
+        <v>0.09965979587752649</v>
+      </c>
+      <c r="I18" s="4">
+        <v>-0.02201320792475492</v>
+      </c>
+      <c r="J18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -2.20%</t>
+        </is>
+      </c>
+      <c r="L18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48.87</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002303</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">美盈森</t>
+        </is>
+      </c>
+      <c r="F19" s="4">
+        <v>0.19253560544550263</v>
+      </c>
+      <c r="G19" s="4">
+        <v>0.10047846889952172</v>
+      </c>
+      <c r="H19" s="4">
+        <v>0.10047846889952172</v>
+      </c>
+      <c r="I19" s="4">
+        <v>0.10047846889952172</v>
+      </c>
+      <c r="J19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +10.05%</t>
+        </is>
+      </c>
+      <c r="L19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002585</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">双星新材</t>
+        </is>
+      </c>
+      <c r="F20" s="4">
+        <v>0.18636794088290495</v>
+      </c>
+      <c r="G20" s="4">
+        <v>-0.01730920535011804</v>
+      </c>
+      <c r="H20" s="4">
+        <v>-0.01730920535011804</v>
+      </c>
+      <c r="I20" s="4">
+        <v>-0.06372934697088906</v>
+      </c>
+      <c r="J20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -6.37%</t>
+        </is>
+      </c>
+      <c r="L20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002172</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">澳洋健康</t>
+        </is>
+      </c>
+      <c r="F21" s="4">
+        <v>0.17441670443211496</v>
+      </c>
+      <c r="G21" s="4">
+        <v>0.030981067125645634</v>
+      </c>
+      <c r="H21" s="4">
+        <v>0.0791738382099827</v>
+      </c>
+      <c r="I21" s="4">
+        <v>-0.03614457831325302</v>
+      </c>
+      <c r="J21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -3.61%</t>
+        </is>
+      </c>
+      <c r="L21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="D22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001201</t>
+        </is>
+      </c>
+      <c r="E22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东瑞股份</t>
+        </is>
+      </c>
+      <c r="F22" s="4">
+        <v>0.15343072575789812</v>
+      </c>
+      <c r="G22" s="4">
+        <v>-0.004975124378109319</v>
+      </c>
+      <c r="H22" s="4">
+        <v>0.024875621890547484</v>
+      </c>
+      <c r="I22" s="4">
+        <v>0.013681592039801238</v>
+      </c>
+      <c r="J22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +1.37%</t>
+        </is>
+      </c>
+      <c r="L22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="D23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002084</t>
+        </is>
+      </c>
+      <c r="E23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">海鸥住工</t>
+        </is>
+      </c>
+      <c r="F23" s="4">
+        <v>0.1522034488145214</v>
+      </c>
+      <c r="G23" s="4">
+        <v>0.0016339869281045694</v>
+      </c>
+      <c r="H23" s="4">
+        <v>0.08986928104575154</v>
+      </c>
+      <c r="I23" s="4">
+        <v>0.045751633986928164</v>
+      </c>
+      <c r="J23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +4.58%</t>
+        </is>
+      </c>
+      <c r="L23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.4</t>
         </is>
       </c>
     </row>
@@ -8311,25 +10845,25 @@
         </is>
       </c>
       <c r="B3" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="4">
         <v>1.0</v>
       </c>
       <c r="F3" s="4">
-        <v>0.20967741935483872</v>
+        <v>0.2191780821917808</v>
       </c>
       <c r="G3" s="0">
-        <v>4.769230769230769</v>
+        <v>4.5625</v>
       </c>
       <c r="H3" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" s="4">
         <v>1.0</v>
@@ -8342,25 +10876,25 @@
         </is>
       </c>
       <c r="B4" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="0">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D4" s="0">
+        <v>5</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0.2191780821917808</v>
+      </c>
+      <c r="G4" s="0">
+        <v>3.802083333333334</v>
+      </c>
+      <c r="H4" s="0">
         <v>2</v>
-      </c>
-      <c r="E4" s="4">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="F4" s="4">
-        <v>0.20967741935483872</v>
-      </c>
-      <c r="G4" s="0">
-        <v>3.1794871794871793</v>
-      </c>
-      <c r="H4" s="0">
-        <v>1</v>
       </c>
       <c r="I4" s="4">
         <v>1.0</v>
@@ -8373,25 +10907,25 @@
         </is>
       </c>
       <c r="B5" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="0">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D5" s="0">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E5" s="4">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F5" s="4">
-        <v>0.20967741935483872</v>
+        <v>0.2191780821917808</v>
       </c>
       <c r="G5" s="0">
-        <v>2.3846153846153846</v>
+        <v>3.0416666666666665</v>
       </c>
       <c r="H5" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" s="4">
         <v>1.0</v>
@@ -8404,25 +10938,25 @@
         </is>
       </c>
       <c r="B6" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="0">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D6" s="0">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E6" s="4">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="F6" s="4">
-        <v>0.20967741935483872</v>
+        <v>0.2191780821917808</v>
       </c>
       <c r="G6" s="0">
-        <v>1.9076923076923078</v>
+        <v>2.053125</v>
       </c>
       <c r="H6" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" s="4">
         <v>1.0</v>

--- a/docs/downloads/latest.xlsx
+++ b/docs/downloads/latest.xlsx
@@ -7532,7 +7532,7 @@
         <v>0.10004239084357769</v>
       </c>
       <c r="H139" s="4">
-        <v>0.4502221241559218</v>
+        <v>0.4521823729436992</v>
       </c>
       <c r="I139" s="0" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>0.09950248756218905</v>
       </c>
       <c r="H140" s="4">
-        <v>0.43390615253804576</v>
+        <v>0.43585168045039163</v>
       </c>
       <c r="I140" s="0" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>0.10010060362173047</v>
       </c>
       <c r="H141" s="4">
-        <v>0.20667295309450376</v>
+        <v>0.2079739356633824</v>
       </c>
       <c r="I141" s="0" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>0.10044313146233395</v>
       </c>
       <c r="H142" s="4">
-        <v>0.19883952200365676</v>
+        <v>0.20010363179239432</v>
       </c>
       <c r="I142" s="0" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>0.09993805492463359</v>
       </c>
       <c r="H143" s="4">
-        <v>0.1846622218762648</v>
+        <v>0.18585710946579106</v>
       </c>
       <c r="I143" s="0" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>0.0999217323245498</v>
       </c>
       <c r="H144" s="4">
-        <v>0.15343903800093306</v>
+        <v>0.15447016738052205</v>
       </c>
       <c r="I144" s="0" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>0.09999999999999985</v>
       </c>
       <c r="H145" s="4">
-        <v>0.12656930475570644</v>
+        <v>0.12744705012017377</v>
       </c>
       <c r="I145" s="0" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>0.10007347538574575</v>
       </c>
       <c r="H146" s="4">
-        <v>0.1254908486037569</v>
+        <v>0.12636219699378118</v>
       </c>
       <c r="I146" s="0" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>0.10027700831024934</v>
       </c>
       <c r="H147" s="4">
-        <v>0.12386960359956992</v>
+        <v>0.12473130044823456</v>
       </c>
       <c r="I147" s="0" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>0.10101010101010101</v>
       </c>
       <c r="H148" s="4">
-        <v>0.12366445888872842</v>
+        <v>0.12452493148415227</v>
       </c>
       <c r="I148" s="0" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>0.09996338337605269</v>
       </c>
       <c r="H149" s="4">
-        <v>0.12149828070899099</v>
+        <v>0.12234578505547863</v>
       </c>
       <c r="I149" s="0" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>0.1007407407407408</v>
       </c>
       <c r="H150" s="4">
-        <v>0.11659962631952028</v>
+        <v>0.11741752746407454</v>
       </c>
       <c r="I150" s="0" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         <v>0.1010928961748634</v>
       </c>
       <c r="H151" s="4">
-        <v>0.1157017053314146</v>
+        <v>0.11651413864419655</v>
       </c>
       <c r="I151" s="0" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>0.10000000000000009</v>
       </c>
       <c r="H152" s="4">
-        <v>0.11241120215955598</v>
+        <v>0.11320348806035796</v>
       </c>
       <c r="I152" s="0" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>0.10001470804530088</v>
       </c>
       <c r="H153" s="4">
-        <v>0.1115478307784586</v>
+        <v>0.11233480169252615</v>
       </c>
       <c r="I153" s="0" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>0.09966777408637872</v>
       </c>
       <c r="H154" s="4">
-        <v>0.10989435091165331</v>
+        <v>0.11067110961483739</v>
       </c>
       <c r="I154" s="0" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>0.10006901311249126</v>
       </c>
       <c r="H155" s="4">
-        <v>0.10855580337764112</v>
+        <v>0.10932426295303412</v>
       </c>
       <c r="I155" s="0" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>0.09964412811387892</v>
       </c>
       <c r="H156" s="4">
-        <v>0.10851466163083029</v>
+        <v>0.10928286566975563</v>
       </c>
       <c r="I156" s="0" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>0.09985528219971052</v>
       </c>
       <c r="H157" s="4">
-        <v>0.10749344084910167</v>
+        <v>0.1082552932909008</v>
       </c>
       <c r="I157" s="0" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>0.10008340283569626</v>
       </c>
       <c r="H158" s="4">
-        <v>0.10367510516621449</v>
+        <v>0.1044130613811366</v>
       </c>
       <c r="I158" s="0" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>0.10059171597633142</v>
       </c>
       <c r="H159" s="4">
-        <v>0.10161852735092247</v>
+        <v>0.10234351636866519</v>
       </c>
       <c r="I159" s="0" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>0.09973753280839916</v>
       </c>
       <c r="H160" s="4">
-        <v>0.09832480772433612</v>
+        <v>0.0990288882479485</v>
       </c>
       <c r="I160" s="0" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>0.10020703933747409</v>
       </c>
       <c r="H161" s="4">
-        <v>0.09602081687383678</v>
+        <v>0.09671016861442376</v>
       </c>
       <c r="I161" s="0" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>0.09978308026030369</v>
       </c>
       <c r="H162" s="4">
-        <v>0.09462423923460407</v>
+        <v>0.09530462172958663</v>
       </c>
       <c r="I162" s="0" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>0.10009310986964604</v>
       </c>
       <c r="H163" s="4">
-        <v>0.09449514765255292</v>
+        <v>0.09517469950799955</v>
       </c>
       <c r="I163" s="0" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>0.09967585089141018</v>
       </c>
       <c r="H164" s="4">
-        <v>0.0910778945423946</v>
+        <v>0.09173536122187265</v>
       </c>
       <c r="I164" s="0" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
         <v>0.10010319917440658</v>
       </c>
       <c r="H165" s="4">
-        <v>0.08972117243049423</v>
+        <v>0.09036981905222696</v>
       </c>
       <c r="I165" s="0" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 江淮汽车（600418）归入“汽车整车+尊界高端+华为合作+智能制造”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 江淮汽车（600418）归入“尊界+华为合作+玛莎拉蒂合作传闻”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K165" s="3" t="inlineStr">
@@ -8990,7 +8990,7 @@
         <v>0.10014409221902</v>
       </c>
       <c r="H166" s="4">
-        <v>0.08891420628426912</v>
+        <v>0.08955759285730544</v>
       </c>
       <c r="I166" s="0" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>0.09952606635071092</v>
       </c>
       <c r="H167" s="4">
-        <v>0.0864820764173997</v>
+        <v>0.08710954665747574</v>
       </c>
       <c r="I167" s="0" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>0.09994172494172492</v>
       </c>
       <c r="H168" s="4">
-        <v>0.08604253644019423</v>
+        <v>0.08666712015419115</v>
       </c>
       <c r="I168" s="0" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>0.10009671179883937</v>
       </c>
       <c r="H169" s="4">
-        <v>0.08479925119475966</v>
+        <v>0.08541565333827117</v>
       </c>
       <c r="I169" s="0" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>0.10002770850651155</v>
       </c>
       <c r="H170" s="4">
-        <v>0.08402443508855546</v>
+        <v>0.08463572597135184</v>
       </c>
       <c r="I170" s="0" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>0.09976798143851529</v>
       </c>
       <c r="H171" s="4">
-        <v>0.08080101093762072</v>
+        <v>0.08139093468675525</v>
       </c>
       <c r="I171" s="0" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>0.09962406015037573</v>
       </c>
       <c r="H172" s="4">
-        <v>0.07614193495978024</v>
+        <v>0.07670068141782992</v>
       </c>
       <c r="I172" s="0" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         <v>0.09968354430379754</v>
       </c>
       <c r="H173" s="4">
-        <v>0.06695018679630341</v>
+        <v>0.06744640643931202</v>
       </c>
       <c r="I173" s="0" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         <v>0.09935205183585305</v>
       </c>
       <c r="H174" s="4">
-        <v>0.06294405098563571</v>
+        <v>0.06341259604381731</v>
       </c>
       <c r="I174" s="0" t="inlineStr">
         <is>

--- a/docs/downloads/latest.xlsx
+++ b/docs/downloads/latest.xlsx
@@ -93,7 +93,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L174"/>
+  <dimension ref="A1:L206"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -9445,13 +9445,1741 @@
         </is>
       </c>
     </row>
+    <row r="175">
+      <c r="A175" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B175" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C175" s="0">
+        <v>1</v>
+      </c>
+      <c r="D175" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600371</t>
+        </is>
+      </c>
+      <c r="E175" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">万向德农</t>
+        </is>
+      </c>
+      <c r="F175" s="0">
+        <v>17.28</v>
+      </c>
+      <c r="G175" s="4">
+        <v>0.09993634627625723</v>
+      </c>
+      <c r="H175" s="4">
+        <v>0.21891221355127635</v>
+      </c>
+      <c r="I175" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J175" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 万向德农（600371）归入“玉米种业+转基因玉米+新品研发”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K175" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 44 家涨停，其中首板 32 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L175" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B176" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C176" s="0">
+        <v>2</v>
+      </c>
+      <c r="D176" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002849</t>
+        </is>
+      </c>
+      <c r="E176" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">威星智能</t>
+        </is>
+      </c>
+      <c r="F176" s="0">
+        <v>23.0</v>
+      </c>
+      <c r="G176" s="4">
+        <v>0.09995217599234806</v>
+      </c>
+      <c r="H176" s="4">
+        <v>0.21750753584913232</v>
+      </c>
+      <c r="I176" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J176" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 威星智能（002849）归入“智能燃气表+智慧能源基地+海外拓展”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K176" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.9 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 44 家涨停，其中首板 32 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L176" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B177" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C177" s="0">
+        <v>3</v>
+      </c>
+      <c r="D177" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600293</t>
+        </is>
+      </c>
+      <c r="E177" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">三峡新材</t>
+        </is>
+      </c>
+      <c r="F177" s="0">
+        <v>3.7</v>
+      </c>
+      <c r="G177" s="4">
+        <v>0.10119047619047628</v>
+      </c>
+      <c r="H177" s="4">
+        <v>0.20799850136451822</v>
+      </c>
+      <c r="I177" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J177" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 三峡新材（600293）归入“电子玻璃+汽车玻璃+客户拓展”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K177" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 44 家涨停，其中首板 32 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L177" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B178" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C178" s="0">
+        <v>4</v>
+      </c>
+      <c r="D178" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603803</t>
+        </is>
+      </c>
+      <c r="E178" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瑞斯康达</t>
+        </is>
+      </c>
+      <c r="F178" s="0">
+        <v>12.87</v>
+      </c>
+      <c r="G178" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H178" s="4">
+        <v>0.15918216332685062</v>
+      </c>
+      <c r="I178" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J178" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 瑞斯康达（603803）归入“交换机+光网络+海外业务”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K178" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 44 家涨停，其中首板 32 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L178" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B179" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C179" s="0">
+        <v>5</v>
+      </c>
+      <c r="D179" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002119</t>
+        </is>
+      </c>
+      <c r="E179" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">康强电子</t>
+        </is>
+      </c>
+      <c r="F179" s="0">
+        <v>26.92</v>
+      </c>
+      <c r="G179" s="4">
+        <v>0.10012259910094003</v>
+      </c>
+      <c r="H179" s="4">
+        <v>0.15704338939409795</v>
+      </c>
+      <c r="I179" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J179" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 康强电子（002119）归入“封装材料+存储芯片+产能扩建”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K179" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 44 家涨停，其中首板 32 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L179" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B180" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C180" s="0">
+        <v>6</v>
+      </c>
+      <c r="D180" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002909</t>
+        </is>
+      </c>
+      <c r="E180" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">集泰股份</t>
+        </is>
+      </c>
+      <c r="F180" s="0">
+        <v>7.54</v>
+      </c>
+      <c r="G180" s="4">
+        <v>0.10072992700729945</v>
+      </c>
+      <c r="H180" s="4">
+        <v>0.1470142347254036</v>
+      </c>
+      <c r="I180" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J180" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 集泰股份（002909）归入“液冷硅油+PCB三防漆+胶粘剂涂料+新能源用胶”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K180" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 44 家涨停，其中首板 32 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L180" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B181" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C181" s="0">
+        <v>7</v>
+      </c>
+      <c r="D181" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600802</t>
+        </is>
+      </c>
+      <c r="E181" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">福建水泥</t>
+        </is>
+      </c>
+      <c r="F181" s="0">
+        <v>6.02</v>
+      </c>
+      <c r="G181" s="4">
+        <v>0.1005484460694699</v>
+      </c>
+      <c r="H181" s="4">
+        <v>0.14425097983612348</v>
+      </c>
+      <c r="I181" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J181" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 福建水泥（600802）归入“水泥熟料+房地产产业链+福建国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K181" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 44 家涨停，其中首板 32 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L181" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B182" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C182" s="0">
+        <v>8</v>
+      </c>
+      <c r="D182" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603773</t>
+        </is>
+      </c>
+      <c r="E182" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">沃格光电</t>
+        </is>
+      </c>
+      <c r="F182" s="0">
+        <v>102.5</v>
+      </c>
+      <c r="G182" s="4">
+        <v>0.1000214638334407</v>
+      </c>
+      <c r="H182" s="4">
+        <v>0.14357005113002186</v>
+      </c>
+      <c r="I182" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J182" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 沃格光电（603773）归入“玻璃基板+先进封装+算力硬件”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K182" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.2 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 44 家涨停，其中首板 32 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L182" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B183" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C183" s="0">
+        <v>9</v>
+      </c>
+      <c r="D183" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603328</t>
+        </is>
+      </c>
+      <c r="E183" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">依顿电子</t>
+        </is>
+      </c>
+      <c r="F183" s="0">
+        <v>15.2</v>
+      </c>
+      <c r="G183" s="4">
+        <v>0.09985528219971052</v>
+      </c>
+      <c r="H183" s="4">
+        <v>0.14269176878796544</v>
+      </c>
+      <c r="I183" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J183" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 依顿电子（603328）归入“高端PCB+AI算力+绵阳国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K183" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.4 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 44 家涨停，其中首板 32 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L183" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B184" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C184" s="0">
+        <v>10</v>
+      </c>
+      <c r="D184" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603396</t>
+        </is>
+      </c>
+      <c r="E184" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金辰股份</t>
+        </is>
+      </c>
+      <c r="F184" s="0">
+        <v>32.4</v>
+      </c>
+      <c r="G184" s="4">
+        <v>0.10016977928692693</v>
+      </c>
+      <c r="H184" s="4">
+        <v>0.14248526939389763</v>
+      </c>
+      <c r="I184" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J184" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 金辰股份（603396）归入“半导体装备+玻璃基封装+光伏设备”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K184" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.8 倍，量能未出现极端放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 44 家涨停，其中首板 32 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L184" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B185" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C185" s="0">
+        <v>11</v>
+      </c>
+      <c r="D185" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603373</t>
+        </is>
+      </c>
+      <c r="E185" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">安邦护卫集团股份</t>
+        </is>
+      </c>
+      <c r="F185" s="0">
+        <v>47.96</v>
+      </c>
+      <c r="G185" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H185" s="4">
+        <v>0.14027274352472915</v>
+      </c>
+      <c r="I185" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J185" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 安邦护卫集团股份（603373）归入“低空安全+智能安防+业绩增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K185" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 44 家涨停，其中首板 32 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L185" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B186" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C186" s="0">
+        <v>12</v>
+      </c>
+      <c r="D186" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603991</t>
+        </is>
+      </c>
+      <c r="E186" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">领先股份</t>
+        </is>
+      </c>
+      <c r="F186" s="0">
+        <v>185.57</v>
+      </c>
+      <c r="G186" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H186" s="4">
+        <v>0.1402559763066618</v>
+      </c>
+      <c r="I186" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J186" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 领先股份（603991）归入“半导体引线框架+全球第二+业绩扭亏”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K186" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.4 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 44 家涨停，其中首板 32 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L186" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B187" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C187" s="0">
+        <v>13</v>
+      </c>
+      <c r="D187" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002989</t>
+        </is>
+      </c>
+      <c r="E187" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中天精装</t>
+        </is>
+      </c>
+      <c r="F187" s="0">
+        <v>27.96</v>
+      </c>
+      <c r="G187" s="4">
+        <v>0.09992132179386302</v>
+      </c>
+      <c r="H187" s="4">
+        <v>0.13656594213735457</v>
+      </c>
+      <c r="I187" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J187" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 中天精装（002989）归入“FCBGA封装基板+半导体转型+批量精装修”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K187" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.9 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 44 家涨停，其中首板 32 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L187" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B188" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C188" s="0">
+        <v>14</v>
+      </c>
+      <c r="D188" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002819</t>
+        </is>
+      </c>
+      <c r="E188" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东方中科</t>
+        </is>
+      </c>
+      <c r="F188" s="0">
+        <v>24.24</v>
+      </c>
+      <c r="G188" s="4">
+        <v>0.09981851179673316</v>
+      </c>
+      <c r="H188" s="4">
+        <v>0.13508607786137344</v>
+      </c>
+      <c r="I188" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J188" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 东方中科（002819）归入“网络分析仪+半导体测试+具身智能”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K188" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.6 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 44 家涨停，其中首板 32 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L188" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B189" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C189" s="0">
+        <v>15</v>
+      </c>
+      <c r="D189" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603124</t>
+        </is>
+      </c>
+      <c r="E189" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">江南新材</t>
+        </is>
+      </c>
+      <c r="F189" s="0">
+        <v>145.0</v>
+      </c>
+      <c r="G189" s="4">
+        <v>0.09998482779547867</v>
+      </c>
+      <c r="H189" s="4">
+        <v>0.13383875839087656</v>
+      </c>
+      <c r="I189" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J189" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 江南新材（603124）归入“液冷散热+PCB概念+高纯铜粉+铜基新材”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K189" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 44 家涨停，其中首板 32 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L189" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B190" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C190" s="0">
+        <v>16</v>
+      </c>
+      <c r="D190" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600605</t>
+        </is>
+      </c>
+      <c r="E190" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汇通能源</t>
+        </is>
+      </c>
+      <c r="F190" s="0">
+        <v>31.61</v>
+      </c>
+      <c r="G190" s="4">
+        <v>0.09986082115518435</v>
+      </c>
+      <c r="H190" s="4">
+        <v>0.1290358831056225</v>
+      </c>
+      <c r="I190" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J190" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 汇通能源（600605）归入“房屋租赁+液冷散热+半导体光罩+存储芯片”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K190" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.9 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 44 家涨停，其中首板 32 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L190" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B191" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C191" s="0">
+        <v>17</v>
+      </c>
+      <c r="D191" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603067</t>
+        </is>
+      </c>
+      <c r="E191" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">振华股份</t>
+        </is>
+      </c>
+      <c r="F191" s="0">
+        <v>39.86</v>
+      </c>
+      <c r="G191" s="4">
+        <v>0.09988962472406172</v>
+      </c>
+      <c r="H191" s="4">
+        <v>0.12800977103971523</v>
+      </c>
+      <c r="I191" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J191" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 振华股份（603067）归入“SOFC+金属铬+铬盐龙头”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K191" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.4 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 44 家涨停，其中首板 32 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L191" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B192" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C192" s="0">
+        <v>18</v>
+      </c>
+      <c r="D192" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002638</t>
+        </is>
+      </c>
+      <c r="E192" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">勤上股份</t>
+        </is>
+      </c>
+      <c r="F192" s="0">
+        <v>4.74</v>
+      </c>
+      <c r="G192" s="4">
+        <v>0.09976798143851529</v>
+      </c>
+      <c r="H192" s="4">
+        <v>0.12624037580403413</v>
+      </c>
+      <c r="I192" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J192" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 勤上股份（002638）归入“半导体照明+LED照明+车路云协同+储能”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K192" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 44 家涨停，其中首板 32 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L192" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B193" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C193" s="0">
+        <v>19</v>
+      </c>
+      <c r="D193" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603949</t>
+        </is>
+      </c>
+      <c r="E193" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雪龙集团</t>
+        </is>
+      </c>
+      <c r="F193" s="0">
+        <v>15.36</v>
+      </c>
+      <c r="G193" s="4">
+        <v>0.10028653295128918</v>
+      </c>
+      <c r="H193" s="4">
+        <v>0.12323019808406208</v>
+      </c>
+      <c r="I193" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J193" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 雪龙集团（603949）归入“商用车热管理+新能源风扇+业绩增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K193" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 44 家涨停，其中首板 32 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L193" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B194" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C194" s="0">
+        <v>20</v>
+      </c>
+      <c r="D194" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002635</t>
+        </is>
+      </c>
+      <c r="E194" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">安洁科技</t>
+        </is>
+      </c>
+      <c r="F194" s="0">
+        <v>16.79</v>
+      </c>
+      <c r="G194" s="4">
+        <v>0.10026212319790308</v>
+      </c>
+      <c r="H194" s="4">
+        <v>0.12227309835958293</v>
+      </c>
+      <c r="I194" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J194" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 安洁科技（002635）归入“光模块基座+PCB配套+消费电子”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K194" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.3 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 44 家涨停，其中首板 32 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L194" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B195" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C195" s="0">
+        <v>21</v>
+      </c>
+      <c r="D195" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002633</t>
+        </is>
+      </c>
+      <c r="E195" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">申科股份</t>
+        </is>
+      </c>
+      <c r="F195" s="0">
+        <v>15.87</v>
+      </c>
+      <c r="G195" s="4">
+        <v>0.0997920997920998</v>
+      </c>
+      <c r="H195" s="4">
+        <v>0.12011784111988556</v>
+      </c>
+      <c r="I195" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J195" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 申科股份（002633）归入“回购+燃气轮机+厚壁滑动轴承”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K195" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.1 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 44 家涨停，其中首板 32 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L195" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B196" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C196" s="0">
+        <v>22</v>
+      </c>
+      <c r="D196" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002935</t>
+        </is>
+      </c>
+      <c r="E196" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天奥电子</t>
+        </is>
+      </c>
+      <c r="F196" s="0">
+        <v>17.52</v>
+      </c>
+      <c r="G196" s="4">
+        <v>0.09981167608286245</v>
+      </c>
+      <c r="H196" s="4">
+        <v>0.11930907153823256</v>
+      </c>
+      <c r="I196" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J196" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 天奥电子（002935）归入“商业航天+时间频率+存储芯片”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K196" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.2 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 44 家涨停，其中首板 32 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L196" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B197" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C197" s="0">
+        <v>23</v>
+      </c>
+      <c r="D197" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000850</t>
+        </is>
+      </c>
+      <c r="E197" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华茂股份</t>
+        </is>
+      </c>
+      <c r="F197" s="0">
+        <v>4.65</v>
+      </c>
+      <c r="G197" s="4">
+        <v>0.09929078014184389</v>
+      </c>
+      <c r="H197" s="4">
+        <v>0.11930587386173491</v>
+      </c>
+      <c r="I197" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J197" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华茂股份（000850）归入“纺织主业+矿业整合+国企改革+“华”字辈”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K197" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 44 家涨停，其中首板 32 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L197" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B198" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C198" s="0">
+        <v>24</v>
+      </c>
+      <c r="D198" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600230</t>
+        </is>
+      </c>
+      <c r="E198" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">沧州大化</t>
+        </is>
+      </c>
+      <c r="F198" s="0">
+        <v>14.82</v>
+      </c>
+      <c r="G198" s="4">
+        <v>0.10022271714922049</v>
+      </c>
+      <c r="H198" s="4">
+        <v>0.11861193283845427</v>
+      </c>
+      <c r="I198" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J198" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 沧州大化（600230）归入“TDI+特种PC+化工新材料”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K198" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 44 家涨停，其中首板 32 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L198" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B199" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C199" s="0">
+        <v>25</v>
+      </c>
+      <c r="D199" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002937</t>
+        </is>
+      </c>
+      <c r="E199" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">兴瑞科技</t>
+        </is>
+      </c>
+      <c r="F199" s="0">
+        <v>30.13</v>
+      </c>
+      <c r="G199" s="4">
+        <v>0.10003650967506372</v>
+      </c>
+      <c r="H199" s="4">
+        <v>0.11734716051263883</v>
+      </c>
+      <c r="I199" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J199" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 兴瑞科技（002937）归入“服务器液冷+新能源汽车电子+电驱合作”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K199" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.1 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 44 家涨停，其中首板 32 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L199" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B200" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C200" s="0">
+        <v>26</v>
+      </c>
+      <c r="D200" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603937</t>
+        </is>
+      </c>
+      <c r="E200" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">丽岛新材</t>
+        </is>
+      </c>
+      <c r="F200" s="0">
+        <v>12.97</v>
+      </c>
+      <c r="G200" s="4">
+        <v>0.10008481764206965</v>
+      </c>
+      <c r="H200" s="4">
+        <v>0.11651115645871853</v>
+      </c>
+      <c r="I200" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J200" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 丽岛新材（603937）归入“电池铝箔+业绩扭亏+彩涂铝”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K200" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.9 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 44 家涨停，其中首板 32 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L200" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B201" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C201" s="0">
+        <v>27</v>
+      </c>
+      <c r="D201" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002286</t>
+        </is>
+      </c>
+      <c r="E201" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">保龄宝</t>
+        </is>
+      </c>
+      <c r="F201" s="0">
+        <v>8.75</v>
+      </c>
+      <c r="G201" s="4">
+        <v>0.10062893081761004</v>
+      </c>
+      <c r="H201" s="4">
+        <v>0.11452287814462443</v>
+      </c>
+      <c r="I201" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J201" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 保龄宝（002286）归入“功能糖+乳果糖原料药+膳食纤维”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K201" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.8 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 44 家涨停，其中首板 32 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L201" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B202" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C202" s="0">
+        <v>28</v>
+      </c>
+      <c r="D202" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603222</t>
+        </is>
+      </c>
+      <c r="E202" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">济民健康</t>
+        </is>
+      </c>
+      <c r="F202" s="0">
+        <v>8.94</v>
+      </c>
+      <c r="G202" s="4">
+        <v>0.09963099630996286</v>
+      </c>
+      <c r="H202" s="4">
+        <v>0.10700924400305328</v>
+      </c>
+      <c r="I202" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J202" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 济民健康（603222）归入“创新药+医疗器械+跨界芯片”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K202" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.8 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 44 家涨停，其中首板 32 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L202" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B203" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C203" s="0">
+        <v>29</v>
+      </c>
+      <c r="D203" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600653</t>
+        </is>
+      </c>
+      <c r="E203" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">申华控股</t>
+        </is>
+      </c>
+      <c r="F203" s="0">
+        <v>1.87</v>
+      </c>
+      <c r="G203" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H203" s="4">
+        <v>0.10666822360739006</v>
+      </c>
+      <c r="I203" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J203" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 申华控股（600653）归入“宝马经销+物业租赁+并购布局+“华”字辈”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K203" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.9 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 44 家涨停，其中首板 32 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L203" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B204" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C204" s="0">
+        <v>30</v>
+      </c>
+      <c r="D204" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002426</t>
+        </is>
+      </c>
+      <c r="E204" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">胜利精密</t>
+        </is>
+      </c>
+      <c r="F204" s="0">
+        <v>2.96</v>
+      </c>
+      <c r="G204" s="4">
+        <v>0.1003717472118959</v>
+      </c>
+      <c r="H204" s="4">
+        <v>0.1066482627321424</v>
+      </c>
+      <c r="I204" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J204" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 胜利精密（002426）归入“复合铜箔+消费电子+车载显示”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K204" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.3 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 44 家涨停，其中首板 32 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L204" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B205" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C205" s="0">
+        <v>31</v>
+      </c>
+      <c r="D205" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002541</t>
+        </is>
+      </c>
+      <c r="E205" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">鸿路钢构</t>
+        </is>
+      </c>
+      <c r="F205" s="0">
+        <v>19.69</v>
+      </c>
+      <c r="G205" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H205" s="4">
+        <v>0.10359624007152382</v>
+      </c>
+      <c r="I205" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J205" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 鸿路钢构（002541）归入“钢结构+焊接机器人+智能制造+重大合同”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K205" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.7 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 44 家涨停，其中首板 32 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L205" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B206" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C206" s="0">
+        <v>32</v>
+      </c>
+      <c r="D206" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600843</t>
+        </is>
+      </c>
+      <c r="E206" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上工申贝</t>
+        </is>
+      </c>
+      <c r="F206" s="0">
+        <v>7.61</v>
+      </c>
+      <c r="G206" s="4">
+        <v>0.0997109826589595</v>
+      </c>
+      <c r="H206" s="4">
+        <v>0.10198378739051381</v>
+      </c>
+      <c r="I206" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J206" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 上工申贝（600843）归入“机器人缝制+低空经济+智能制造”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K206" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.3 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 44 家涨停，其中首板 32 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L206" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M33"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -10754,6 +12482,596 @@
       <c r="M23" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">6.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002290</t>
+        </is>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">禾盛新材</t>
+        </is>
+      </c>
+      <c r="F24" s="4">
+        <v>0.4521823729436992</v>
+      </c>
+      <c r="G24" s="4">
+        <v>-0.03917790622992934</v>
+      </c>
+      <c r="H24" s="4">
+        <v>0.00282594733461794</v>
+      </c>
+      <c r="I24" s="4">
+        <v>-0.04110468850353233</v>
+      </c>
+      <c r="J24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -4.11%</t>
+        </is>
+      </c>
+      <c r="L24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600770</t>
+        </is>
+      </c>
+      <c r="E25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">综艺股份</t>
+        </is>
+      </c>
+      <c r="F25" s="4">
+        <v>0.43585168045039163</v>
+      </c>
+      <c r="G25" s="4">
+        <v>0.05128205128205132</v>
+      </c>
+      <c r="H25" s="4">
+        <v>0.05128205128205132</v>
+      </c>
+      <c r="I25" s="4">
+        <v>-0.018099547511312264</v>
+      </c>
+      <c r="J25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -1.81%</t>
+        </is>
+      </c>
+      <c r="L25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.51</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="D26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600641</t>
+        </is>
+      </c>
+      <c r="E26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">先导基电</t>
+        </is>
+      </c>
+      <c r="F26" s="4">
+        <v>0.2079739356633824</v>
+      </c>
+      <c r="G26" s="4">
+        <v>0.017375400091449444</v>
+      </c>
+      <c r="H26" s="4">
+        <v>0.09990855052583436</v>
+      </c>
+      <c r="I26" s="4">
+        <v>0.09282121627800621</v>
+      </c>
+      <c r="J26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +9.28%</t>
+        </is>
+      </c>
+      <c r="L26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="D27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000676</t>
+        </is>
+      </c>
+      <c r="E27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">智度股份</t>
+        </is>
+      </c>
+      <c r="F27" s="4">
+        <v>0.20010363179239432</v>
+      </c>
+      <c r="G27" s="4">
+        <v>0.04026845637583887</v>
+      </c>
+      <c r="H27" s="4">
+        <v>0.0724832214765101</v>
+      </c>
+      <c r="I27" s="4">
+        <v>-0.02684563758389269</v>
+      </c>
+      <c r="J27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -2.68%</t>
+        </is>
+      </c>
+      <c r="L27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="D28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605058</t>
+        </is>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">澳弘电子</t>
+        </is>
+      </c>
+      <c r="F28" s="4">
+        <v>0.18585710946579106</v>
+      </c>
+      <c r="G28" s="4">
+        <v>-0.01201426694199359</v>
+      </c>
+      <c r="H28" s="4">
+        <v>0.10005631687629046</v>
+      </c>
+      <c r="I28" s="4">
+        <v>0.10005631687629046</v>
+      </c>
+      <c r="J28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +10.01%</t>
+        </is>
+      </c>
+      <c r="L28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="D29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605258</t>
+        </is>
+      </c>
+      <c r="E29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">协和电子</t>
+        </is>
+      </c>
+      <c r="F29" s="4">
+        <v>0.15447016738052205</v>
+      </c>
+      <c r="G29" s="4">
+        <v>0.020398481973434635</v>
+      </c>
+      <c r="H29" s="4">
+        <v>0.08562618595825433</v>
+      </c>
+      <c r="I29" s="4">
+        <v>0.035341555977229655</v>
+      </c>
+      <c r="J29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +3.53%</t>
+        </is>
+      </c>
+      <c r="L29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">43.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="D30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603221</t>
+        </is>
+      </c>
+      <c r="E30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">爱丽家居</t>
+        </is>
+      </c>
+      <c r="F30" s="4">
+        <v>0.12744705012017377</v>
+      </c>
+      <c r="G30" s="4">
+        <v>0.0005961251862891537</v>
+      </c>
+      <c r="H30" s="4">
+        <v>0.009538002980626015</v>
+      </c>
+      <c r="I30" s="4">
+        <v>-0.025633383010432165</v>
+      </c>
+      <c r="J30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -2.56%</t>
+        </is>
+      </c>
+      <c r="L30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32.69</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="D31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002768</t>
+        </is>
+      </c>
+      <c r="E31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">国恩股份</t>
+        </is>
+      </c>
+      <c r="F31" s="4">
+        <v>0.12636219699378118</v>
+      </c>
+      <c r="G31" s="4">
+        <v>0.015228426395939021</v>
+      </c>
+      <c r="H31" s="4">
+        <v>0.06505476890195028</v>
+      </c>
+      <c r="I31" s="4">
+        <v>0.05557039807640929</v>
+      </c>
+      <c r="J31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +5.56%</t>
+        </is>
+      </c>
+      <c r="L31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="D32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002757</t>
+        </is>
+      </c>
+      <c r="E32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南兴股份</t>
+        </is>
+      </c>
+      <c r="F32" s="4">
+        <v>0.12473130044823456</v>
+      </c>
+      <c r="G32" s="4">
+        <v>0.002014098690835908</v>
+      </c>
+      <c r="H32" s="4">
+        <v>0.10020140986908377</v>
+      </c>
+      <c r="I32" s="4">
+        <v>0.021148036253776592</v>
+      </c>
+      <c r="J32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +2.11%</t>
+        </is>
+      </c>
+      <c r="L32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="B33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="C33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="D33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002564</t>
+        </is>
+      </c>
+      <c r="E33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天沃科技</t>
+        </is>
+      </c>
+      <c r="F33" s="4">
+        <v>0.12452493148415227</v>
+      </c>
+      <c r="G33" s="4">
+        <v>0.016513761467889854</v>
+      </c>
+      <c r="H33" s="4">
+        <v>0.10091743119266061</v>
+      </c>
+      <c r="I33" s="4">
+        <v>0.007339449541284404</v>
+      </c>
+      <c r="J33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +0.73%</t>
+        </is>
+      </c>
+      <c r="L33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.49</t>
         </is>
       </c>
     </row>
@@ -10845,28 +13163,28 @@
         </is>
       </c>
       <c r="B3" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="0">
         <v>2</v>
       </c>
       <c r="E3" s="4">
-        <v>1.0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F3" s="4">
-        <v>0.2191780821917808</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G3" s="0">
-        <v>4.5625</v>
+        <v>8.0</v>
       </c>
       <c r="H3" s="0">
         <v>2</v>
       </c>
       <c r="I3" s="4">
-        <v>1.0</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="4">
@@ -10876,28 +13194,28 @@
         </is>
       </c>
       <c r="B4" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="0">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D4" s="0">
         <v>5</v>
       </c>
       <c r="E4" s="4">
-        <v>0.8333333333333334</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="F4" s="4">
-        <v>0.2191780821917808</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G4" s="0">
-        <v>3.802083333333334</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="H4" s="0">
         <v>2</v>
       </c>
       <c r="I4" s="4">
-        <v>1.0</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="5">
@@ -10907,25 +13225,25 @@
         </is>
       </c>
       <c r="B5" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D5" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="4">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="F5" s="4">
-        <v>0.2191780821917808</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G5" s="0">
-        <v>3.0416666666666665</v>
+        <v>6.0</v>
       </c>
       <c r="H5" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" s="4">
         <v>1.0</v>
@@ -10938,25 +13256,25 @@
         </is>
       </c>
       <c r="B6" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" s="0">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D6" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" s="4">
-        <v>0.45</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F6" s="4">
-        <v>0.2191780821917808</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G6" s="0">
-        <v>2.053125</v>
+        <v>4.0</v>
       </c>
       <c r="H6" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" s="4">
         <v>1.0</v>

--- a/docs/downloads/latest.xlsx
+++ b/docs/downloads/latest.xlsx
@@ -93,7 +93,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L206"/>
+  <dimension ref="A1:L239"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -11173,13 +11173,1795 @@
         </is>
       </c>
     </row>
+    <row r="207">
+      <c r="A207" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B207" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C207" s="0">
+        <v>1</v>
+      </c>
+      <c r="D207" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601567</t>
+        </is>
+      </c>
+      <c r="E207" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">三星电气</t>
+        </is>
+      </c>
+      <c r="F207" s="0">
+        <v>16.25</v>
+      </c>
+      <c r="G207" s="4">
+        <v>0.10020311442112394</v>
+      </c>
+      <c r="H207" s="4">
+        <v>0.44571114111201915</v>
+      </c>
+      <c r="I207" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J207" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 三星电气（601567）归入“数据中心+变压器+海外配电”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K207" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 10.0%）。截至运行时成交量约为20日均量的 0.6 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L207" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B208" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C208" s="0">
+        <v>2</v>
+      </c>
+      <c r="D208" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603230</t>
+        </is>
+      </c>
+      <c r="E208" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">内蒙新华</t>
+        </is>
+      </c>
+      <c r="F208" s="0">
+        <v>18.47</v>
+      </c>
+      <c r="G208" s="4">
+        <v>0.10005955926146504</v>
+      </c>
+      <c r="H208" s="4">
+        <v>0.19847201017672383</v>
+      </c>
+      <c r="I208" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J208" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 内蒙新华（603230）归入“出版发行+教材教辅+文化消费+“华”字辈”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K208" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.4 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L208" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；近5日涨幅偏高，短线获利盘压力更大；近10日涨幅偏高</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B209" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C209" s="0">
+        <v>3</v>
+      </c>
+      <c r="D209" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000498</t>
+        </is>
+      </c>
+      <c r="E209" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">山东路桥</t>
+        </is>
+      </c>
+      <c r="F209" s="0">
+        <v>5.65</v>
+      </c>
+      <c r="G209" s="4">
+        <v>0.09922178988326857</v>
+      </c>
+      <c r="H209" s="4">
+        <v>0.19661365155619412</v>
+      </c>
+      <c r="I209" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J209" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 山东路桥（000498）归入“大股东增持+基建工程+海外业务”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K209" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 9.9%）。截至运行时成交量约为20日均量的 4.8 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L209" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B210" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C210" s="0">
+        <v>4</v>
+      </c>
+      <c r="D210" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603122</t>
+        </is>
+      </c>
+      <c r="E210" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合富中国</t>
+        </is>
+      </c>
+      <c r="F210" s="0">
+        <v>14.93</v>
+      </c>
+      <c r="G210" s="4">
+        <v>0.10022107590272666</v>
+      </c>
+      <c r="H210" s="4">
+        <v>0.16518948446489815</v>
+      </c>
+      <c r="I210" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J210" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 合富中国（603122）归入“海峡两岸+AI医疗+体外诊断”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K210" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L210" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B211" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C211" s="0">
+        <v>5</v>
+      </c>
+      <c r="D211" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002836</t>
+        </is>
+      </c>
+      <c r="E211" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新宏泽</t>
+        </is>
+      </c>
+      <c r="F211" s="0">
+        <v>12.27</v>
+      </c>
+      <c r="G211" s="4">
+        <v>0.10044843049327357</v>
+      </c>
+      <c r="H211" s="4">
+        <v>0.15999820850515603</v>
+      </c>
+      <c r="I211" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J211" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 新宏泽（002836）归入“烟标印刷+员工持股+多元化布局”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K211" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.7 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L211" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B212" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C212" s="0">
+        <v>6</v>
+      </c>
+      <c r="D212" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000790</t>
+        </is>
+      </c>
+      <c r="E212" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华神科技</t>
+        </is>
+      </c>
+      <c r="F212" s="0">
+        <v>4.68</v>
+      </c>
+      <c r="G212" s="4">
+        <v>0.1011764705882352</v>
+      </c>
+      <c r="H212" s="4">
+        <v>0.14996879486331935</v>
+      </c>
+      <c r="I212" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J212" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华神科技（000790）归入“中药大健康+独家中药+定增审核”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K212" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L212" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B213" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C213" s="0">
+        <v>7</v>
+      </c>
+      <c r="D213" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000710</t>
+        </is>
+      </c>
+      <c r="E213" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">贝瑞基因</t>
+        </is>
+      </c>
+      <c r="F213" s="0">
+        <v>11.01</v>
+      </c>
+      <c r="G213" s="4">
+        <v>0.09990009990009983</v>
+      </c>
+      <c r="H213" s="4">
+        <v>0.14898708752842263</v>
+      </c>
+      <c r="I213" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J213" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 贝瑞基因（000710）归入“AI医疗+基因检测+三代测序”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K213" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.4 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L213" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B214" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C214" s="0">
+        <v>8</v>
+      </c>
+      <c r="D214" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001317</t>
+        </is>
+      </c>
+      <c r="E214" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">三羊马</t>
+        </is>
+      </c>
+      <c r="F214" s="0">
+        <v>65.3</v>
+      </c>
+      <c r="G214" s="4">
+        <v>0.1000673854447438</v>
+      </c>
+      <c r="H214" s="4">
+        <v>0.1479572327765633</v>
+      </c>
+      <c r="I214" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no_verified_event</t>
+        </is>
+      </c>
+      <c r="J214" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">事件证据层未找到与当日涨停直接匹配的公告或新闻；系统不把概念标签、技术形态或主观猜测当成涨停原因。</t>
+        </is>
+      </c>
+      <c r="K214" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.5 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L214" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B215" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C215" s="0">
+        <v>9</v>
+      </c>
+      <c r="D215" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603375</t>
+        </is>
+      </c>
+      <c r="E215" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">盛景微电子</t>
+        </is>
+      </c>
+      <c r="F215" s="0">
+        <v>49.25</v>
+      </c>
+      <c r="G215" s="4">
+        <v>0.10006700915791811</v>
+      </c>
+      <c r="H215" s="4">
+        <v>0.14730689877745717</v>
+      </c>
+      <c r="I215" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J215" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 盛景微电子（603375）归入“模拟芯片+电子雷管+低空经济”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K215" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L215" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B216" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C216" s="0">
+        <v>10</v>
+      </c>
+      <c r="D216" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002321</t>
+        </is>
+      </c>
+      <c r="E216" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华英农业</t>
+        </is>
+      </c>
+      <c r="F216" s="0">
+        <v>2.27</v>
+      </c>
+      <c r="G216" s="4">
+        <v>0.10194174757281547</v>
+      </c>
+      <c r="H216" s="4">
+        <v>0.14678562388140695</v>
+      </c>
+      <c r="I216" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J216" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华英农业（002321）归入“鸭业全产业链+羽绒出口+控制权变更+“华”字辈”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K216" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L216" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B217" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C217" s="0">
+        <v>11</v>
+      </c>
+      <c r="D217" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000592</t>
+        </is>
+      </c>
+      <c r="E217" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">平潭发展</t>
+        </is>
+      </c>
+      <c r="F217" s="0">
+        <v>8.78</v>
+      </c>
+      <c r="G217" s="4">
+        <v>0.1002506265664158</v>
+      </c>
+      <c r="H217" s="4">
+        <v>0.14077602704811568</v>
+      </c>
+      <c r="I217" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J217" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 平潭发展（000592）归入“海峡两岸+平潭开发+林板一体化”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K217" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L217" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B218" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C218" s="0">
+        <v>12</v>
+      </c>
+      <c r="D218" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002164</t>
+        </is>
+      </c>
+      <c r="E218" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">宁波东力</t>
+        </is>
+      </c>
+      <c r="F218" s="0">
+        <v>13.06</v>
+      </c>
+      <c r="G218" s="4">
+        <v>0.10025273799494538</v>
+      </c>
+      <c r="H218" s="4">
+        <v>0.13392752981308975</v>
+      </c>
+      <c r="I218" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J218" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 宁波东力（002164）归入“股东增持+机器人减速器+定增扩产”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K218" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.7 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L218" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B219" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C219" s="0">
+        <v>13</v>
+      </c>
+      <c r="D219" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600792</t>
+        </is>
+      </c>
+      <c r="E219" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">云煤能源</t>
+        </is>
+      </c>
+      <c r="F219" s="0">
+        <v>5.7</v>
+      </c>
+      <c r="G219" s="4">
+        <v>0.10038610038610042</v>
+      </c>
+      <c r="H219" s="4">
+        <v>0.13179200499926916</v>
+      </c>
+      <c r="I219" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J219" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 云煤能源（600792）归入“焦炭+钢企直供+销量增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K219" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.5 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L219" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B220" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C220" s="0">
+        <v>14</v>
+      </c>
+      <c r="D220" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002622</t>
+        </is>
+      </c>
+      <c r="E220" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">皓宸医疗</t>
+        </is>
+      </c>
+      <c r="F220" s="0">
+        <v>2.72</v>
+      </c>
+      <c r="G220" s="4">
+        <v>0.10121457489878537</v>
+      </c>
+      <c r="H220" s="4">
+        <v>0.1289795552790257</v>
+      </c>
+      <c r="I220" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J220" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 皓宸医疗（002622）归入“口腔医疗+连锁服务+半年报减亏”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K220" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.8 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L220" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B221" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C221" s="0">
+        <v>15</v>
+      </c>
+      <c r="D221" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600189</t>
+        </is>
+      </c>
+      <c r="E221" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">泉阳泉</t>
+        </is>
+      </c>
+      <c r="F221" s="0">
+        <v>9.1</v>
+      </c>
+      <c r="G221" s="4">
+        <v>0.10036275695284157</v>
+      </c>
+      <c r="H221" s="4">
+        <v>0.12860784083612745</v>
+      </c>
+      <c r="I221" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J221" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 泉阳泉（600189）归入“园林剥离+天然矿泉水+全国扩张”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K221" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.9 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L221" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B222" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C222" s="0">
+        <v>16</v>
+      </c>
+      <c r="D222" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603500</t>
+        </is>
+      </c>
+      <c r="E222" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">祥和实业</t>
+        </is>
+      </c>
+      <c r="F222" s="0">
+        <v>10.42</v>
+      </c>
+      <c r="G222" s="4">
+        <v>0.10031678986272441</v>
+      </c>
+      <c r="H222" s="4">
+        <v>0.1186787348225923</v>
+      </c>
+      <c r="I222" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J222" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 祥和实业（603500）归入“铁路扣件合同+电容配件+半年报增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K222" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.2 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L222" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B223" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C223" s="0">
+        <v>17</v>
+      </c>
+      <c r="D223" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000753</t>
+        </is>
+      </c>
+      <c r="E223" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">漳州发展</t>
+        </is>
+      </c>
+      <c r="F223" s="0">
+        <v>5.35</v>
+      </c>
+      <c r="G223" s="4">
+        <v>0.10082304526748963</v>
+      </c>
+      <c r="H223" s="4">
+        <v>0.11804445069732804</v>
+      </c>
+      <c r="I223" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J223" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 漳州发展（000753）归入“海峡两岸+福建国资+绿色电力”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K223" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L223" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B224" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C224" s="0">
+        <v>18</v>
+      </c>
+      <c r="D224" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603042</t>
+        </is>
+      </c>
+      <c r="E224" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华脉科技</t>
+        </is>
+      </c>
+      <c r="F224" s="0">
+        <v>18.73</v>
+      </c>
+      <c r="G224" s="4">
+        <v>0.09982384028185542</v>
+      </c>
+      <c r="H224" s="4">
+        <v>0.1123836659766526</v>
+      </c>
+      <c r="I224" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J224" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华脉科技（603042）归入“光纤光缆+扭亏为盈+6G通信+“华”字辈”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K224" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.9 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L224" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B225" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C225" s="0">
+        <v>19</v>
+      </c>
+      <c r="D225" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000905</t>
+        </is>
+      </c>
+      <c r="E225" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">厦门港务</t>
+        </is>
+      </c>
+      <c r="F225" s="0">
+        <v>9.81</v>
+      </c>
+      <c r="G225" s="4">
+        <v>0.09977578475336335</v>
+      </c>
+      <c r="H225" s="4">
+        <v>0.10750473874532188</v>
+      </c>
+      <c r="I225" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J225" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 厦门港务（000905）归入“海峡两岸+港口物流+资产重组”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K225" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L225" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B226" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C226" s="0">
+        <v>20</v>
+      </c>
+      <c r="D226" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603065</t>
+        </is>
+      </c>
+      <c r="E226" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">宿迁联盛</t>
+        </is>
+      </c>
+      <c r="F226" s="0">
+        <v>16.27</v>
+      </c>
+      <c r="G226" s="4">
+        <v>0.10006761325219739</v>
+      </c>
+      <c r="H226" s="4">
+        <v>0.10593871684636261</v>
+      </c>
+      <c r="I226" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J226" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 宿迁联盛（603065）归入“磷化铟衬底+光稳定剂”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K226" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.8 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L226" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B227" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C227" s="0">
+        <v>21</v>
+      </c>
+      <c r="D227" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002205</t>
+        </is>
+      </c>
+      <c r="E227" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">国统股份</t>
+        </is>
+      </c>
+      <c r="F227" s="0">
+        <v>12.78</v>
+      </c>
+      <c r="G227" s="4">
+        <v>0.09982788296041312</v>
+      </c>
+      <c r="H227" s="4">
+        <v>0.10283351763941186</v>
+      </c>
+      <c r="I227" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J227" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 国统股份（002205）归入“风电混塔+PCCP管道+央企控股”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K227" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.9 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L227" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B228" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C228" s="0">
+        <v>22</v>
+      </c>
+      <c r="D228" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605018</t>
+        </is>
+      </c>
+      <c r="E228" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">长华集团</t>
+        </is>
+      </c>
+      <c r="F228" s="0">
+        <v>12.74</v>
+      </c>
+      <c r="G228" s="4">
+        <v>0.10017271157167527</v>
+      </c>
+      <c r="H228" s="4">
+        <v>0.10042012091062585</v>
+      </c>
+      <c r="I228" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J228" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 长华集团（605018）归入“人形机器人+汽车零部件+新能源定点”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K228" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.9 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L228" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B229" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C229" s="0">
+        <v>23</v>
+      </c>
+      <c r="D229" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002029</t>
+        </is>
+      </c>
+      <c r="E229" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">七 匹 狼</t>
+        </is>
+      </c>
+      <c r="F229" s="0">
+        <v>9.26</v>
+      </c>
+      <c r="G229" s="4">
+        <v>0.09976247030878849</v>
+      </c>
+      <c r="H229" s="4">
+        <v>0.10021985911483856</v>
+      </c>
+      <c r="I229" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J229" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 七 匹 狼（002029）归入“投资半导体及机器人+男装夹克+海峡两岸”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K229" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.5 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L229" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B230" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C230" s="0">
+        <v>24</v>
+      </c>
+      <c r="D230" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601218</t>
+        </is>
+      </c>
+      <c r="E230" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">吉鑫科技</t>
+        </is>
+      </c>
+      <c r="F230" s="0">
+        <v>5.5</v>
+      </c>
+      <c r="G230" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H230" s="4">
+        <v>0.09977903577199</v>
+      </c>
+      <c r="I230" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J230" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 吉鑫科技（601218）归入“风电铸件+风电轴承+半年报增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K230" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.8 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L230" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B231" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C231" s="0">
+        <v>25</v>
+      </c>
+      <c r="D231" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603970</t>
+        </is>
+      </c>
+      <c r="E231" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中农立华</t>
+        </is>
+      </c>
+      <c r="F231" s="0">
+        <v>12.17</v>
+      </c>
+      <c r="G231" s="4">
+        <v>0.10036166365280286</v>
+      </c>
+      <c r="H231" s="4">
+        <v>0.09922778148522855</v>
+      </c>
+      <c r="I231" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J231" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 中农立华（603970）归入“农药流通+作物解决方案+海外市场+“华”字辈”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K231" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L231" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B232" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C232" s="0">
+        <v>26</v>
+      </c>
+      <c r="D232" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002679</t>
+        </is>
+      </c>
+      <c r="E232" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">福建金森</t>
+        </is>
+      </c>
+      <c r="F232" s="0">
+        <v>11.58</v>
+      </c>
+      <c r="G232" s="4">
+        <v>0.09971509971509974</v>
+      </c>
+      <c r="H232" s="4">
+        <v>0.09616258396218563</v>
+      </c>
+      <c r="I232" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J232" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 福建金森（002679）归入“海峡两岸+福建国资+林业主业”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K232" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L232" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B233" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C233" s="0">
+        <v>27</v>
+      </c>
+      <c r="D233" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002413</t>
+        </is>
+      </c>
+      <c r="E233" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雷科防务</t>
+        </is>
+      </c>
+      <c r="F233" s="0">
+        <v>8.97</v>
+      </c>
+      <c r="G233" s="4">
+        <v>0.10061349693251544</v>
+      </c>
+      <c r="H233" s="4">
+        <v>0.09399103055133627</v>
+      </c>
+      <c r="I233" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J233" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 雷科防务（002413）归入“商业航天+卫星智算+存储芯片+股权激励”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K233" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.4 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L233" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B234" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C234" s="0">
+        <v>28</v>
+      </c>
+      <c r="D234" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002395</t>
+        </is>
+      </c>
+      <c r="E234" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">双象股份</t>
+        </is>
+      </c>
+      <c r="F234" s="0">
+        <v>14.05</v>
+      </c>
+      <c r="G234" s="4">
+        <v>0.10023492560689128</v>
+      </c>
+      <c r="H234" s="4">
+        <v>0.08921276247648101</v>
+      </c>
+      <c r="I234" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J234" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 双象股份（002395）归入“合成革+光学级PMMA+足球革”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K234" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.9 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L234" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B235" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C235" s="0">
+        <v>29</v>
+      </c>
+      <c r="D235" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603278</t>
+        </is>
+      </c>
+      <c r="E235" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大业股份</t>
+        </is>
+      </c>
+      <c r="F235" s="0">
+        <v>9.8</v>
+      </c>
+      <c r="G235" s="4">
+        <v>0.09988776655443331</v>
+      </c>
+      <c r="H235" s="4">
+        <v>0.08754802211700012</v>
+      </c>
+      <c r="I235" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J235" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 大业股份（603278）归入“人形机器人+胎圈钢丝+全球销售”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K235" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.3 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L235" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B236" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C236" s="0">
+        <v>30</v>
+      </c>
+      <c r="D236" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600815</t>
+        </is>
+      </c>
+      <c r="E236" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">厦工股份</t>
+        </is>
+      </c>
+      <c r="F236" s="0">
+        <v>4.65</v>
+      </c>
+      <c r="G236" s="4">
+        <v>0.09929078014184389</v>
+      </c>
+      <c r="H236" s="4">
+        <v>0.079229359835591</v>
+      </c>
+      <c r="I236" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J236" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 厦工股份（600815）归入“海峡两岸+工程机械+盾构机+智能矿卡”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K236" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.6 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L236" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B237" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C237" s="0">
+        <v>31</v>
+      </c>
+      <c r="D237" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000678</t>
+        </is>
+      </c>
+      <c r="E237" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">襄阳轴承</t>
+        </is>
+      </c>
+      <c r="F237" s="0">
+        <v>9.68</v>
+      </c>
+      <c r="G237" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H237" s="4">
+        <v>0.07787172385815416</v>
+      </c>
+      <c r="I237" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J237" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 襄阳轴承（000678）归入“机器人轴承+汽车轴承+湖北国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K237" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.6 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L237" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B238" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C238" s="0">
+        <v>32</v>
+      </c>
+      <c r="D238" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603767</t>
+        </is>
+      </c>
+      <c r="E238" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中马传动</t>
+        </is>
+      </c>
+      <c r="F238" s="0">
+        <v>14.74</v>
+      </c>
+      <c r="G238" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H238" s="4">
+        <v>0.07698951115192605</v>
+      </c>
+      <c r="I238" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J238" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 中马传动（603767）归入“减速器+汽车变速器+农机齿轮”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K238" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.0 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L238" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B239" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C239" s="0">
+        <v>33</v>
+      </c>
+      <c r="D239" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600358</t>
+        </is>
+      </c>
+      <c r="E239" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">国旅联合</t>
+        </is>
+      </c>
+      <c r="F239" s="0">
+        <v>5.72</v>
+      </c>
+      <c r="G239" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H239" s="4">
+        <v>0.0723723430137557</v>
+      </c>
+      <c r="I239" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J239" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 国旅联合（600358）归入“互联网营销+饮用水+跨境电商”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K239" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 5.1 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L239" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M43"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -13072,6 +14854,596 @@
       <c r="M33" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">5.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600371</t>
+        </is>
+      </c>
+      <c r="E34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">万向德农</t>
+        </is>
+      </c>
+      <c r="F34" s="4">
+        <v>0.21891221355127635</v>
+      </c>
+      <c r="G34" s="4">
+        <v>0.04629629629629606</v>
+      </c>
+      <c r="H34" s="4">
+        <v>0.07060185185185186</v>
+      </c>
+      <c r="I34" s="4">
+        <v>-0.08275462962962976</v>
+      </c>
+      <c r="J34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -8.28%</t>
+        </is>
+      </c>
+      <c r="L34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002849</t>
+        </is>
+      </c>
+      <c r="E35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">威星智能</t>
+        </is>
+      </c>
+      <c r="F35" s="4">
+        <v>0.21750753584913232</v>
+      </c>
+      <c r="G35" s="4">
+        <v>-0.00043478260869567187</v>
+      </c>
+      <c r="H35" s="4">
+        <v>0.09478260869565225</v>
+      </c>
+      <c r="I35" s="4">
+        <v>0.07608695652173902</v>
+      </c>
+      <c r="J35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +7.61%</t>
+        </is>
+      </c>
+      <c r="L35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="D36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600293</t>
+        </is>
+      </c>
+      <c r="E36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">三峡新材</t>
+        </is>
+      </c>
+      <c r="F36" s="4">
+        <v>0.20799850136451822</v>
+      </c>
+      <c r="G36" s="4">
+        <v>0.00540540540540535</v>
+      </c>
+      <c r="H36" s="4">
+        <v>0.09729729729729719</v>
+      </c>
+      <c r="I36" s="4">
+        <v>0.021621621621621623</v>
+      </c>
+      <c r="J36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +2.16%</t>
+        </is>
+      </c>
+      <c r="L36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="D37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603803</t>
+        </is>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瑞斯康达</t>
+        </is>
+      </c>
+      <c r="F37" s="4">
+        <v>0.15918216332685062</v>
+      </c>
+      <c r="G37" s="4">
+        <v>0.02331002331002341</v>
+      </c>
+      <c r="H37" s="4">
+        <v>0.035742035742035716</v>
+      </c>
+      <c r="I37" s="4">
+        <v>-0.041181041181041156</v>
+      </c>
+      <c r="J37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -4.12%</t>
+        </is>
+      </c>
+      <c r="L37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12.34</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="D38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002119</t>
+        </is>
+      </c>
+      <c r="E38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">康强电子</t>
+        </is>
+      </c>
+      <c r="F38" s="4">
+        <v>0.15704338939409795</v>
+      </c>
+      <c r="G38" s="4">
+        <v>0.059435364041604766</v>
+      </c>
+      <c r="H38" s="4">
+        <v>0.09992570579494786</v>
+      </c>
+      <c r="I38" s="4">
+        <v>0.09992570579494786</v>
+      </c>
+      <c r="J38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +9.99%</t>
+        </is>
+      </c>
+      <c r="L38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="D39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002909</t>
+        </is>
+      </c>
+      <c r="E39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">集泰股份</t>
+        </is>
+      </c>
+      <c r="F39" s="4">
+        <v>0.1470142347254036</v>
+      </c>
+      <c r="G39" s="4">
+        <v>0.01724137931034475</v>
+      </c>
+      <c r="H39" s="4">
+        <v>0.09946949602122013</v>
+      </c>
+      <c r="I39" s="4">
+        <v>0.09946949602122013</v>
+      </c>
+      <c r="J39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +9.95%</t>
+        </is>
+      </c>
+      <c r="L39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="D40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600802</t>
+        </is>
+      </c>
+      <c r="E40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">福建水泥</t>
+        </is>
+      </c>
+      <c r="F40" s="4">
+        <v>0.14425097983612348</v>
+      </c>
+      <c r="G40" s="4">
+        <v>-0.03654485049833878</v>
+      </c>
+      <c r="H40" s="4">
+        <v>0.09966777408637872</v>
+      </c>
+      <c r="I40" s="4">
+        <v>0.09966777408637872</v>
+      </c>
+      <c r="J40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +9.97%</t>
+        </is>
+      </c>
+      <c r="L40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="D41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603773</t>
+        </is>
+      </c>
+      <c r="E41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">沃格光电</t>
+        </is>
+      </c>
+      <c r="F41" s="4">
+        <v>0.14357005113002186</v>
+      </c>
+      <c r="G41" s="4">
+        <v>0.004975609756097565</v>
+      </c>
+      <c r="H41" s="4">
+        <v>0.014536585365853671</v>
+      </c>
+      <c r="I41" s="4">
+        <v>-0.04682926829268286</v>
+      </c>
+      <c r="J41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -4.68%</t>
+        </is>
+      </c>
+      <c r="L41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">97.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="D42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603328</t>
+        </is>
+      </c>
+      <c r="E42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">依顿电子</t>
+        </is>
+      </c>
+      <c r="F42" s="4">
+        <v>0.14269176878796544</v>
+      </c>
+      <c r="G42" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H42" s="4">
+        <v>0.005921052631578938</v>
+      </c>
+      <c r="I42" s="4">
+        <v>-0.06184210526315781</v>
+      </c>
+      <c r="J42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -6.18%</t>
+        </is>
+      </c>
+      <c r="L42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="C43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="D43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603396</t>
+        </is>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金辰股份</t>
+        </is>
+      </c>
+      <c r="F43" s="4">
+        <v>0.14248526939389763</v>
+      </c>
+      <c r="G43" s="4">
+        <v>0.01141975308641996</v>
+      </c>
+      <c r="H43" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="I43" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="J43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +10.00%</t>
+        </is>
+      </c>
+      <c r="L43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35.64</t>
         </is>
       </c>
     </row>
@@ -13163,28 +15535,28 @@
         </is>
       </c>
       <c r="B3" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="0">
         <v>2</v>
       </c>
       <c r="E3" s="4">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="F3" s="4">
-        <v>0.08333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="G3" s="0">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="H3" s="0">
         <v>2</v>
       </c>
       <c r="I3" s="4">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4">
@@ -13194,28 +15566,28 @@
         </is>
       </c>
       <c r="B4" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="0">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D4" s="0">
         <v>5</v>
       </c>
       <c r="E4" s="4">
-        <v>0.5555555555555556</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="F4" s="4">
-        <v>0.08333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="G4" s="0">
-        <v>6.666666666666667</v>
+        <v>1.6666666666666667</v>
       </c>
       <c r="H4" s="0">
         <v>2</v>
       </c>
       <c r="I4" s="4">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
@@ -13225,25 +15597,25 @@
         </is>
       </c>
       <c r="B5" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" s="0">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D5" s="0">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E5" s="4">
-        <v>0.5</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="F5" s="4">
-        <v>0.08333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="G5" s="0">
-        <v>6.0</v>
+        <v>1.8333333333333333</v>
       </c>
       <c r="H5" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5" s="4">
         <v>1.0</v>
@@ -13256,25 +15628,25 @@
         </is>
       </c>
       <c r="B6" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" s="0">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D6" s="0">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E6" s="4">
-        <v>0.3333333333333333</v>
+        <v>0.35</v>
       </c>
       <c r="F6" s="4">
-        <v>0.08333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="G6" s="0">
-        <v>4.0</v>
+        <v>1.4</v>
       </c>
       <c r="H6" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6" s="4">
         <v>1.0</v>

--- a/docs/downloads/latest.xlsx
+++ b/docs/downloads/latest.xlsx
@@ -11204,7 +11204,7 @@
         <v>0.10020311442112394</v>
       </c>
       <c r="H207" s="4">
-        <v>0.44571114111201915</v>
+        <v>0.44531545034917097</v>
       </c>
       <c r="I207" s="0" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>0.10005955926146504</v>
       </c>
       <c r="H208" s="4">
-        <v>0.19847201017672383</v>
+        <v>0.19821731994305916</v>
       </c>
       <c r="I208" s="0" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         <v>0.09922178988326857</v>
       </c>
       <c r="H209" s="4">
-        <v>0.19661365155619412</v>
+        <v>0.1963607618479557</v>
       </c>
       <c r="I209" s="0" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>0.10022107590272666</v>
       </c>
       <c r="H210" s="4">
-        <v>0.16518948446489815</v>
+        <v>0.16496871373250488</v>
       </c>
       <c r="I210" s="0" t="inlineStr">
         <is>
@@ -11420,7 +11420,7 @@
         <v>0.10044843049327357</v>
       </c>
       <c r="H211" s="4">
-        <v>0.15999820850515603</v>
+        <v>0.15978304782300495</v>
       </c>
       <c r="I211" s="0" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>0.1011764705882352</v>
       </c>
       <c r="H212" s="4">
-        <v>0.14996879486331935</v>
+        <v>0.14976471677473008</v>
       </c>
       <c r="I212" s="0" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>0.09990009990009983</v>
       </c>
       <c r="H213" s="4">
-        <v>0.14898708752842263</v>
+        <v>0.14878411152134657</v>
       </c>
       <c r="I213" s="0" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>0.1000673854447438</v>
       </c>
       <c r="H214" s="4">
-        <v>0.1479572327765633</v>
+        <v>0.14775541621480762</v>
       </c>
       <c r="I214" s="0" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>0.10006700915791811</v>
       </c>
       <c r="H215" s="4">
-        <v>0.14730689877745717</v>
+        <v>0.1471058161310053</v>
       </c>
       <c r="I215" s="0" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>0.10194174757281547</v>
       </c>
       <c r="H216" s="4">
-        <v>0.14678562388140695</v>
+        <v>0.14658513048100635</v>
       </c>
       <c r="I216" s="0" t="inlineStr">
         <is>
@@ -11744,7 +11744,7 @@
         <v>0.1002506265664158</v>
       </c>
       <c r="H217" s="4">
-        <v>0.14077602704811568</v>
+        <v>0.1405823896198422</v>
       </c>
       <c r="I217" s="0" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>0.10025273799494538</v>
       </c>
       <c r="H218" s="4">
-        <v>0.13392752981308975</v>
+        <v>0.13374184621323681</v>
       </c>
       <c r="I218" s="0" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>0.10038610038610042</v>
       </c>
       <c r="H219" s="4">
-        <v>0.13179200499926916</v>
+        <v>0.13160883227027417</v>
       </c>
       <c r="I219" s="0" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>0.10121457489878537</v>
       </c>
       <c r="H220" s="4">
-        <v>0.1289795552790257</v>
+        <v>0.12879971157496886</v>
       </c>
       <c r="I220" s="0" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>0.10036275695284157</v>
       </c>
       <c r="H221" s="4">
-        <v>0.12860784083612745</v>
+        <v>0.12842843901346937</v>
       </c>
       <c r="I221" s="0" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
         <v>0.10031678986272441</v>
       </c>
       <c r="H222" s="4">
-        <v>0.1186787348225923</v>
+        <v>0.11851129991365686</v>
       </c>
       <c r="I222" s="0" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>0.10082304526748963</v>
       </c>
       <c r="H223" s="4">
-        <v>0.11804445069732804</v>
+        <v>0.1178777909630794</v>
       </c>
       <c r="I223" s="0" t="inlineStr">
         <is>
@@ -12122,7 +12122,7 @@
         <v>0.09982384028185542</v>
       </c>
       <c r="H224" s="4">
-        <v>0.1123836659766526</v>
+        <v>0.11222398140521615</v>
       </c>
       <c r="I224" s="0" t="inlineStr">
         <is>
@@ -12176,7 +12176,7 @@
         <v>0.09977578475336335</v>
       </c>
       <c r="H225" s="4">
-        <v>0.10750473874532188</v>
+        <v>0.10735114815420436</v>
       </c>
       <c r="I225" s="0" t="inlineStr">
         <is>
@@ -12230,7 +12230,7 @@
         <v>0.10006761325219739</v>
       </c>
       <c r="H226" s="4">
-        <v>0.10593871684636261</v>
+        <v>0.10578709841717987</v>
       </c>
       <c r="I226" s="0" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>0.09982788296041312</v>
       </c>
       <c r="H227" s="4">
-        <v>0.10283351763941186</v>
+        <v>0.10268583291748018</v>
       </c>
       <c r="I227" s="0" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         <v>0.10017271157167527</v>
       </c>
       <c r="H228" s="4">
-        <v>0.10042012091062585</v>
+        <v>0.10027551480426382</v>
       </c>
       <c r="I228" s="0" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>0.09976247030878849</v>
       </c>
       <c r="H229" s="4">
-        <v>0.10021985911483856</v>
+        <v>0.10007550930641185</v>
       </c>
       <c r="I229" s="0" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>0.10000000000000009</v>
       </c>
       <c r="H230" s="4">
-        <v>0.09977903577199</v>
+        <v>0.09963525058744073</v>
       </c>
       <c r="I230" s="0" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>0.10036166365280286</v>
       </c>
       <c r="H231" s="4">
-        <v>0.09922778148522855</v>
+        <v>0.09908470324316535</v>
       </c>
       <c r="I231" s="0" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>0.09971509971509974</v>
       </c>
       <c r="H232" s="4">
-        <v>0.09616258396218563</v>
+        <v>0.09602345432897672</v>
       </c>
       <c r="I232" s="0" t="inlineStr">
         <is>
@@ -12608,7 +12608,7 @@
         <v>0.10061349693251544</v>
       </c>
       <c r="H233" s="4">
-        <v>0.09399103055133627</v>
+        <v>0.0938547165084135</v>
       </c>
       <c r="I233" s="0" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>0.10023492560689128</v>
       </c>
       <c r="H234" s="4">
-        <v>0.08921276247648101</v>
+        <v>0.0890826969233504</v>
       </c>
       <c r="I234" s="0" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
         <v>0.09988776655443331</v>
       </c>
       <c r="H235" s="4">
-        <v>0.08754802211700012</v>
+        <v>0.08742015067378184</v>
       </c>
       <c r="I235" s="0" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>0.09929078014184389</v>
       </c>
       <c r="H236" s="4">
-        <v>0.079229359835591</v>
+        <v>0.0791125850609737</v>
       </c>
       <c r="I236" s="0" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>0.09999999999999985</v>
       </c>
       <c r="H237" s="4">
-        <v>0.07787172385815416</v>
+        <v>0.07775678110045835</v>
       </c>
       <c r="I237" s="0" t="inlineStr">
         <is>
@@ -12878,7 +12878,7 @@
         <v>0.10000000000000009</v>
       </c>
       <c r="H238" s="4">
-        <v>0.07698951115192605</v>
+        <v>0.07687576202570982</v>
       </c>
       <c r="I238" s="0" t="inlineStr">
         <is>
@@ -12932,7 +12932,7 @@
         <v>0.09999999999999985</v>
       </c>
       <c r="H239" s="4">
-        <v>0.0723723430137557</v>
+        <v>0.07226488149291152</v>
       </c>
       <c r="I239" s="0" t="inlineStr">
         <is>

--- a/docs/downloads/latest.xlsx
+++ b/docs/downloads/latest.xlsx
@@ -93,7 +93,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L239"/>
+  <dimension ref="A1:L263"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -12955,13 +12955,1309 @@
         </is>
       </c>
     </row>
+    <row r="240">
+      <c r="A240" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="B240" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="C240" s="0">
+        <v>1</v>
+      </c>
+      <c r="D240" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001330</t>
+        </is>
+      </c>
+      <c r="E240" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">博纳影业</t>
+        </is>
+      </c>
+      <c r="F240" s="0">
+        <v>6.36</v>
+      </c>
+      <c r="G240" s="4">
+        <v>0.10034602076124566</v>
+      </c>
+      <c r="H240" s="4">
+        <v>0.46904660227015416</v>
+      </c>
+      <c r="I240" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J240" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 博纳影业（001330）归入“首部AI电影上映+《三星堆：未来往事》”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K240" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 10.0%）。截至运行时成交量约为20日均量的 0.3 倍，量能未出现极端放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 31 家涨停，其中首板 24 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L240" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="B241" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="C241" s="0">
+        <v>2</v>
+      </c>
+      <c r="D241" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601579</t>
+        </is>
+      </c>
+      <c r="E241" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">会稽山</t>
+        </is>
+      </c>
+      <c r="F241" s="0">
+        <v>41.84</v>
+      </c>
+      <c r="G241" s="4">
+        <v>0.09989484752891699</v>
+      </c>
+      <c r="H241" s="4">
+        <v>0.24770917505433532</v>
+      </c>
+      <c r="I241" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J241" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 会稽山（601579）归入“高端黄酒+全国化扩张+中高端增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K241" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 31 家涨停，其中首板 24 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L241" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">近10日涨幅偏高</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="B242" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="C242" s="0">
+        <v>3</v>
+      </c>
+      <c r="D242" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002912</t>
+        </is>
+      </c>
+      <c r="E242" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中新赛克</t>
+        </is>
+      </c>
+      <c r="F242" s="0">
+        <v>26.47</v>
+      </c>
+      <c r="G242" s="4">
+        <v>0.10016625103906908</v>
+      </c>
+      <c r="H242" s="4">
+        <v>0.21277869537940503</v>
+      </c>
+      <c r="I242" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J242" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 中新赛克（002912）归入“AI安全+网络安全+数据安全”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K242" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.6 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 31 家涨停，其中首板 24 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L242" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="B243" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="C243" s="0">
+        <v>4</v>
+      </c>
+      <c r="D243" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001201</t>
+        </is>
+      </c>
+      <c r="E243" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东瑞股份</t>
+        </is>
+      </c>
+      <c r="F243" s="0">
+        <v>16.13</v>
+      </c>
+      <c r="G243" s="4">
+        <v>0.10027285129604359</v>
+      </c>
+      <c r="H243" s="4">
+        <v>0.19510729246964234</v>
+      </c>
+      <c r="I243" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J243" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 东瑞股份（001201）归入“生猪养殖+供港活猪+降本增效”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K243" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 31 家涨停，其中首板 24 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L243" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="B244" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="C244" s="0">
+        <v>5</v>
+      </c>
+      <c r="D244" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001368</t>
+        </is>
+      </c>
+      <c r="E244" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通达创智</t>
+        </is>
+      </c>
+      <c r="F244" s="0">
+        <v>41.8</v>
+      </c>
+      <c r="G244" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H244" s="4">
+        <v>0.18511876321457663</v>
+      </c>
+      <c r="I244" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J244" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 通达创智（001368）归入“体育户外+AI玩具+海外产能”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K244" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.3 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 31 家涨停，其中首板 24 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L244" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="B245" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="C245" s="0">
+        <v>6</v>
+      </c>
+      <c r="D245" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600418</t>
+        </is>
+      </c>
+      <c r="E245" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">江淮汽车</t>
+        </is>
+      </c>
+      <c r="F245" s="0">
+        <v>25.22</v>
+      </c>
+      <c r="G245" s="4">
+        <v>0.09986916703009152</v>
+      </c>
+      <c r="H245" s="4">
+        <v>0.17714854940653763</v>
+      </c>
+      <c r="I245" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J245" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 江淮汽车（600418）归入“尊界+华为合作+玛莎拉蒂合作传闻”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K245" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 31 家涨停，其中首板 24 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L245" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="B246" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="C246" s="0">
+        <v>7</v>
+      </c>
+      <c r="D246" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002242</t>
+        </is>
+      </c>
+      <c r="E246" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">九阳股份</t>
+        </is>
+      </c>
+      <c r="F246" s="0">
+        <v>10.33</v>
+      </c>
+      <c r="G246" s="4">
+        <v>0.10010649627263035</v>
+      </c>
+      <c r="H246" s="4">
+        <v>0.17227945942556677</v>
+      </c>
+      <c r="I246" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J246" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 九阳股份（002242）归入“机器人+太空科技+厨房小家电”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K246" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.5 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 31 家涨停，其中首板 24 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L246" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="B247" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="C247" s="0">
+        <v>8</v>
+      </c>
+      <c r="D247" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000020</t>
+        </is>
+      </c>
+      <c r="E247" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">深华发Ａ</t>
+        </is>
+      </c>
+      <c r="F247" s="0">
+        <v>14.64</v>
+      </c>
+      <c r="G247" s="4">
+        <v>0.09992486851990989</v>
+      </c>
+      <c r="H247" s="4">
+        <v>0.170827085314805</v>
+      </c>
+      <c r="I247" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J247" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 深华发Ａ（000020）归入“深圳旧改+物业经营+定制显示器+注塑业务”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K247" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 31 家涨停，其中首板 24 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L247" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="B248" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="C248" s="0">
+        <v>9</v>
+      </c>
+      <c r="D248" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002640</t>
+        </is>
+      </c>
+      <c r="E248" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">跨境通</t>
+        </is>
+      </c>
+      <c r="F248" s="0">
+        <v>3.96</v>
+      </c>
+      <c r="G248" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H248" s="4">
+        <v>0.166134967767185</v>
+      </c>
+      <c r="I248" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J248" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 跨境通（002640）归入“跨境电商+品牌运营+中报扭亏”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K248" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.8 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 31 家涨停，其中首板 24 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L248" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="B249" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="C249" s="0">
+        <v>10</v>
+      </c>
+      <c r="D249" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000011</t>
+        </is>
+      </c>
+      <c r="E249" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">深物业A</t>
+        </is>
+      </c>
+      <c r="F249" s="0">
+        <v>10.12</v>
+      </c>
+      <c r="G249" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H249" s="4">
+        <v>0.15010641913890024</v>
+      </c>
+      <c r="I249" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J249" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 深物业A（000011）归入“房地产开发+物业管理+深圳国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K249" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.8 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 31 家涨停，其中首板 24 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L249" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="B250" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="C250" s="0">
+        <v>11</v>
+      </c>
+      <c r="D250" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600488</t>
+        </is>
+      </c>
+      <c r="E250" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">津药药业</t>
+        </is>
+      </c>
+      <c r="F250" s="0">
+        <v>6.27</v>
+      </c>
+      <c r="G250" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H250" s="4">
+        <v>0.14732739579312448</v>
+      </c>
+      <c r="I250" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J250" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 津药药业（600488）归入“食欲素+药品注册+氨基酸制剂+国际化布局”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K250" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 31 家涨停，其中首板 24 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L250" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="B251" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="C251" s="0">
+        <v>12</v>
+      </c>
+      <c r="D251" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002852</t>
+        </is>
+      </c>
+      <c r="E251" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">道道全</t>
+        </is>
+      </c>
+      <c r="F251" s="0">
+        <v>8.9</v>
+      </c>
+      <c r="G251" s="4">
+        <v>0.10012360939431408</v>
+      </c>
+      <c r="H251" s="4">
+        <v>0.14118448069283046</v>
+      </c>
+      <c r="I251" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J251" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 道道全（002852）归入“菜籽油+渠道拓展+高端油品”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K251" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 31 家涨停，其中首板 24 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L251" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="B252" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="C252" s="0">
+        <v>13</v>
+      </c>
+      <c r="D252" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605366</t>
+        </is>
+      </c>
+      <c r="E252" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">宏柏新材</t>
+        </is>
+      </c>
+      <c r="F252" s="0">
+        <v>10.14</v>
+      </c>
+      <c r="G252" s="4">
+        <v>0.09978308026030369</v>
+      </c>
+      <c r="H252" s="4">
+        <v>0.13856279938978025</v>
+      </c>
+      <c r="I252" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J252" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 宏柏新材（605366）归入“高纯四氯化硅+功能性硅烷+电子化学品”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K252" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.6 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 31 家涨停，其中首板 24 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L252" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="B253" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="C253" s="0">
+        <v>14</v>
+      </c>
+      <c r="D253" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002342</t>
+        </is>
+      </c>
+      <c r="E253" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">巨力索具</t>
+        </is>
+      </c>
+      <c r="F253" s="0">
+        <v>8.68</v>
+      </c>
+      <c r="G253" s="4">
+        <v>0.10012674271229403</v>
+      </c>
+      <c r="H253" s="4">
+        <v>0.13830540924426665</v>
+      </c>
+      <c r="I253" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J253" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 巨力索具（002342）归入“商业航天+索具龙头+深海系泊”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K253" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.1 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 31 家涨停，其中首板 24 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L253" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="B254" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="C254" s="0">
+        <v>15</v>
+      </c>
+      <c r="D254" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000513</t>
+        </is>
+      </c>
+      <c r="E254" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">丽珠集团</t>
+        </is>
+      </c>
+      <c r="F254" s="0">
+        <v>30.34</v>
+      </c>
+      <c r="G254" s="4">
+        <v>0.1000725163161713</v>
+      </c>
+      <c r="H254" s="4">
+        <v>0.1331276003856741</v>
+      </c>
+      <c r="I254" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J254" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 丽珠集团（000513）归入“创新药+海外拓展+高分红”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K254" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.4 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 31 家涨停，其中首板 24 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L254" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="B255" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="C255" s="0">
+        <v>16</v>
+      </c>
+      <c r="D255" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603968</t>
+        </is>
+      </c>
+      <c r="E255" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">醋化股份</t>
+        </is>
+      </c>
+      <c r="F255" s="0">
+        <v>11.63</v>
+      </c>
+      <c r="G255" s="4">
+        <v>0.1002838221381268</v>
+      </c>
+      <c r="H255" s="4">
+        <v>0.12356458329363552</v>
+      </c>
+      <c r="I255" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J255" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 醋化股份（603968）归入“染料+安赛蜜+精细化工+食品饲料添加剂”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K255" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.1 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 31 家涨停，其中首板 24 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L255" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="B256" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="C256" s="0">
+        <v>17</v>
+      </c>
+      <c r="D256" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002232</t>
+        </is>
+      </c>
+      <c r="E256" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">启明信息</t>
+        </is>
+      </c>
+      <c r="F256" s="0">
+        <v>16.28</v>
+      </c>
+      <c r="G256" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H256" s="4">
+        <v>0.12236272297949849</v>
+      </c>
+      <c r="I256" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J256" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 启明信息（002232）归入“网络安全+车联网+一汽配套”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K256" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.4 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 31 家涨停，其中首板 24 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L256" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="B257" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="C257" s="0">
+        <v>18</v>
+      </c>
+      <c r="D257" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000503</t>
+        </is>
+      </c>
+      <c r="E257" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">国新健康</t>
+        </is>
+      </c>
+      <c r="F257" s="0">
+        <v>7.44</v>
+      </c>
+      <c r="G257" s="4">
+        <v>0.10059171597633142</v>
+      </c>
+      <c r="H257" s="4">
+        <v>0.11917608669835966</v>
+      </c>
+      <c r="I257" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J257" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 国新健康（000503）归入“AI医疗+个人医保云+医保支付改革”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K257" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.7 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 31 家涨停，其中首板 24 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L257" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="B258" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="C258" s="0">
+        <v>19</v>
+      </c>
+      <c r="D258" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002962</t>
+        </is>
+      </c>
+      <c r="E258" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">五方光电</t>
+        </is>
+      </c>
+      <c r="F258" s="0">
+        <v>14.76</v>
+      </c>
+      <c r="G258" s="4">
+        <v>0.09985096870342769</v>
+      </c>
+      <c r="H258" s="4">
+        <v>0.11747236583269122</v>
+      </c>
+      <c r="I258" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J258" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 五方光电（002962）归入“TGV光学+微棱镜+AR/VR”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K258" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.6 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 31 家涨停，其中首板 24 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L258" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="B259" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="C259" s="0">
+        <v>20</v>
+      </c>
+      <c r="D259" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600032</t>
+        </is>
+      </c>
+      <c r="E259" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">浙江新能</t>
+        </is>
+      </c>
+      <c r="F259" s="0">
+        <v>7.43</v>
+      </c>
+      <c r="G259" s="4">
+        <v>0.1007407407407408</v>
+      </c>
+      <c r="H259" s="4">
+        <v>0.10997208884040086</v>
+      </c>
+      <c r="I259" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J259" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 浙江新能（600032）归入“绿色电力+风电+智慧运维”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K259" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.2 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 31 家涨停，其中首板 24 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L259" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="B260" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="C260" s="0">
+        <v>21</v>
+      </c>
+      <c r="D260" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000980</t>
+        </is>
+      </c>
+      <c r="E260" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">众泰汽车</t>
+        </is>
+      </c>
+      <c r="F260" s="0">
+        <v>2.24</v>
+      </c>
+      <c r="G260" s="4">
+        <v>0.0980392156862746</v>
+      </c>
+      <c r="H260" s="4">
+        <v>0.09504538421951775</v>
+      </c>
+      <c r="I260" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J260" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 众泰汽车（000980）归入“汽车整车+A0车型+海外布局”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K260" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 31 家涨停，其中首板 24 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L260" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="B261" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="C261" s="0">
+        <v>22</v>
+      </c>
+      <c r="D261" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002480</t>
+        </is>
+      </c>
+      <c r="E261" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新筑股份</t>
+        </is>
+      </c>
+      <c r="F261" s="0">
+        <v>5.65</v>
+      </c>
+      <c r="G261" s="4">
+        <v>0.09922178988326857</v>
+      </c>
+      <c r="H261" s="4">
+        <v>0.09148531014284494</v>
+      </c>
+      <c r="I261" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J261" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 新筑股份（002480）归入“重大重组+清洁能源+四川国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K261" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.0 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 31 家涨停，其中首板 24 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L261" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="B262" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="C262" s="0">
+        <v>23</v>
+      </c>
+      <c r="D262" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002347</t>
+        </is>
+      </c>
+      <c r="E262" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">泰尔股份</t>
+        </is>
+      </c>
+      <c r="F262" s="0">
+        <v>6.42</v>
+      </c>
+      <c r="G262" s="4">
+        <v>0.09931506849315073</v>
+      </c>
+      <c r="H262" s="4">
+        <v>0.09143451223161997</v>
+      </c>
+      <c r="I262" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J262" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 泰尔股份（002347）归入“工业机器人+激光装备+冶金装备”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K262" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.2 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 31 家涨停，其中首板 24 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L262" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="B263" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="C263" s="0">
+        <v>24</v>
+      </c>
+      <c r="D263" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600241</t>
+        </is>
+      </c>
+      <c r="E263" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时代万恒</t>
+        </is>
+      </c>
+      <c r="F263" s="0">
+        <v>8.04</v>
+      </c>
+      <c r="G263" s="4">
+        <v>0.09986320109439116</v>
+      </c>
+      <c r="H263" s="4">
+        <v>0.08285579382734717</v>
+      </c>
+      <c r="I263" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J263" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 时代万恒（600241）归入“BBU备用电源+锂电池+镍氢电池+辽宁国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K263" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.7 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 31 家涨停，其中首板 24 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L263" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M53"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -15444,6 +16740,596 @@
       <c r="M43" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">35.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="B44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601567</t>
+        </is>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">三星电气</t>
+        </is>
+      </c>
+      <c r="F44" s="4">
+        <v>0.44531545034917097</v>
+      </c>
+      <c r="G44" s="4">
+        <v>-0.01538461538461533</v>
+      </c>
+      <c r="H44" s="4">
+        <v>-0.01538461538461533</v>
+      </c>
+      <c r="I44" s="4">
+        <v>-0.09969230769230764</v>
+      </c>
+      <c r="J44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -9.97%</t>
+        </is>
+      </c>
+      <c r="L44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="B45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603230</t>
+        </is>
+      </c>
+      <c r="E45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">内蒙新华</t>
+        </is>
+      </c>
+      <c r="F45" s="4">
+        <v>0.19821731994305916</v>
+      </c>
+      <c r="G45" s="4">
+        <v>-0.0259880887926367</v>
+      </c>
+      <c r="H45" s="4">
+        <v>-0.005414185165132479</v>
+      </c>
+      <c r="I45" s="4">
+        <v>-0.10016242555495392</v>
+      </c>
+      <c r="J45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -10.02%</t>
+        </is>
+      </c>
+      <c r="L45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="B46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="D46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000498</t>
+        </is>
+      </c>
+      <c r="E46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">山东路桥</t>
+        </is>
+      </c>
+      <c r="F46" s="4">
+        <v>0.1963607618479557</v>
+      </c>
+      <c r="G46" s="4">
+        <v>-0.005309734513274433</v>
+      </c>
+      <c r="H46" s="4">
+        <v>0.04070796460176984</v>
+      </c>
+      <c r="I46" s="4">
+        <v>0.019469026548672552</v>
+      </c>
+      <c r="J46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +1.95%</t>
+        </is>
+      </c>
+      <c r="L46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.76</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="B47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="D47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603122</t>
+        </is>
+      </c>
+      <c r="E47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合富中国</t>
+        </is>
+      </c>
+      <c r="F47" s="4">
+        <v>0.16496871373250488</v>
+      </c>
+      <c r="G47" s="4">
+        <v>-0.06965840589417271</v>
+      </c>
+      <c r="H47" s="4">
+        <v>0.06363027461486936</v>
+      </c>
+      <c r="I47" s="4">
+        <v>-0.021433355659745468</v>
+      </c>
+      <c r="J47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -2.14%</t>
+        </is>
+      </c>
+      <c r="L47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="B48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="D48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002836</t>
+        </is>
+      </c>
+      <c r="E48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新宏泽</t>
+        </is>
+      </c>
+      <c r="F48" s="4">
+        <v>0.15978304782300495</v>
+      </c>
+      <c r="G48" s="4">
+        <v>0.018744906275468765</v>
+      </c>
+      <c r="H48" s="4">
+        <v>0.03748981255093731</v>
+      </c>
+      <c r="I48" s="4">
+        <v>-0.05704971475142617</v>
+      </c>
+      <c r="J48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -5.70%</t>
+        </is>
+      </c>
+      <c r="L48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="B49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="D49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000790</t>
+        </is>
+      </c>
+      <c r="E49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华神科技</t>
+        </is>
+      </c>
+      <c r="F49" s="4">
+        <v>0.14976471677473008</v>
+      </c>
+      <c r="G49" s="4">
+        <v>0.10042735042735051</v>
+      </c>
+      <c r="H49" s="4">
+        <v>0.10042735042735051</v>
+      </c>
+      <c r="I49" s="4">
+        <v>-0.05555555555555547</v>
+      </c>
+      <c r="J49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -5.56%</t>
+        </is>
+      </c>
+      <c r="L49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="B50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="D50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000710</t>
+        </is>
+      </c>
+      <c r="E50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">贝瑞基因</t>
+        </is>
+      </c>
+      <c r="F50" s="4">
+        <v>0.14878411152134657</v>
+      </c>
+      <c r="G50" s="4">
+        <v>-0.009990917347865502</v>
+      </c>
+      <c r="H50" s="4">
+        <v>-0.0009082652134423386</v>
+      </c>
+      <c r="I50" s="4">
+        <v>-0.06630336058128983</v>
+      </c>
+      <c r="J50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -6.63%</t>
+        </is>
+      </c>
+      <c r="L50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="B51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="D51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001317</t>
+        </is>
+      </c>
+      <c r="E51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">三羊马</t>
+        </is>
+      </c>
+      <c r="F51" s="4">
+        <v>0.14775541621480762</v>
+      </c>
+      <c r="G51" s="4">
+        <v>0.0003062787136294265</v>
+      </c>
+      <c r="H51" s="4">
+        <v>0.09800918836140893</v>
+      </c>
+      <c r="I51" s="4">
+        <v>-0.015313935681470103</v>
+      </c>
+      <c r="J51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -1.53%</t>
+        </is>
+      </c>
+      <c r="L51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="B52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="D52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603375</t>
+        </is>
+      </c>
+      <c r="E52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">盛景微电子</t>
+        </is>
+      </c>
+      <c r="F52" s="4">
+        <v>0.1471058161310053</v>
+      </c>
+      <c r="G52" s="4">
+        <v>-0.010152284263959421</v>
+      </c>
+      <c r="H52" s="4">
+        <v>0.0050761421319796</v>
+      </c>
+      <c r="I52" s="4">
+        <v>-0.013401015228426294</v>
+      </c>
+      <c r="J52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -1.34%</t>
+        </is>
+      </c>
+      <c r="L52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="B53" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28</t>
+        </is>
+      </c>
+      <c r="C53" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="D53" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002321</t>
+        </is>
+      </c>
+      <c r="E53" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华英农业</t>
+        </is>
+      </c>
+      <c r="F53" s="4">
+        <v>0.14658513048100635</v>
+      </c>
+      <c r="G53" s="4">
+        <v>0.017621145374449254</v>
+      </c>
+      <c r="H53" s="4">
+        <v>0.048458149779735615</v>
+      </c>
+      <c r="I53" s="4">
+        <v>-0.06607929515418498</v>
+      </c>
+      <c r="J53" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K53" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -6.61%</t>
+        </is>
+      </c>
+      <c r="L53" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M53" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.12</t>
         </is>
       </c>
     </row>
@@ -15535,28 +17421,28 @@
         </is>
       </c>
       <c r="B3" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="0">
         <v>2</v>
       </c>
       <c r="E3" s="4">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F3" s="4">
-        <v>0.25</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="G3" s="0">
-        <v>2.0</v>
+        <v>4.4</v>
       </c>
       <c r="H3" s="0">
         <v>2</v>
       </c>
       <c r="I3" s="4">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="4">
@@ -15566,28 +17452,28 @@
         </is>
       </c>
       <c r="B4" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="0">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D4" s="0">
         <v>5</v>
       </c>
       <c r="E4" s="4">
-        <v>0.4166666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F4" s="4">
-        <v>0.25</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="G4" s="0">
-        <v>1.6666666666666667</v>
+        <v>3.6666666666666665</v>
       </c>
       <c r="H4" s="0">
         <v>2</v>
       </c>
       <c r="I4" s="4">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="5">
@@ -15597,28 +17483,28 @@
         </is>
       </c>
       <c r="B5" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" s="0">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D5" s="0">
         <v>11</v>
       </c>
       <c r="E5" s="4">
-        <v>0.4583333333333333</v>
+        <v>0.36666666666666664</v>
       </c>
       <c r="F5" s="4">
-        <v>0.25</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="G5" s="0">
-        <v>1.8333333333333333</v>
+        <v>4.033333333333333</v>
       </c>
       <c r="H5" s="0">
         <v>4</v>
       </c>
       <c r="I5" s="4">
-        <v>1.0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="6">
@@ -15628,28 +17514,28 @@
         </is>
       </c>
       <c r="B6" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" s="0">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D6" s="0">
         <v>14</v>
       </c>
       <c r="E6" s="4">
-        <v>0.35</v>
+        <v>0.28</v>
       </c>
       <c r="F6" s="4">
-        <v>0.25</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="G6" s="0">
-        <v>1.4</v>
+        <v>3.08</v>
       </c>
       <c r="H6" s="0">
         <v>4</v>
       </c>
       <c r="I6" s="4">
-        <v>1.0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="7">

--- a/docs/downloads/latest.xlsx
+++ b/docs/downloads/latest.xlsx
@@ -93,7 +93,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L263"/>
+  <dimension ref="A1:L305"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -14251,13 +14251,2281 @@
         </is>
       </c>
     </row>
+    <row r="264">
+      <c r="A264" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B264" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C264" s="0">
+        <v>1</v>
+      </c>
+      <c r="D264" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601238</t>
+        </is>
+      </c>
+      <c r="E264" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">广汽集团</t>
+        </is>
+      </c>
+      <c r="F264" s="0">
+        <v>5.6</v>
+      </c>
+      <c r="G264" s="4">
+        <v>0.10019646365422386</v>
+      </c>
+      <c r="H264" s="4">
+        <v>0.3998428659240021</v>
+      </c>
+      <c r="I264" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J264" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 广汽集团（601238）归入“拟购买一汽丰田50%股权+复牌+南北丰田+新能源车”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K264" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 10.0%）。截至运行时成交量约为20日均量的 0.2 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L264" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B265" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C265" s="0">
+        <v>2</v>
+      </c>
+      <c r="D265" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605303</t>
+        </is>
+      </c>
+      <c r="E265" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">园林股份</t>
+        </is>
+      </c>
+      <c r="F265" s="0">
+        <v>26.05</v>
+      </c>
+      <c r="G265" s="4">
+        <v>0.10008445945945944</v>
+      </c>
+      <c r="H265" s="4">
+        <v>0.36542213410613905</v>
+      </c>
+      <c r="I265" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J265" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 园林股份（605303）归入“复牌+重大资产重组+存储芯片+园林工程”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K265" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 10.0%）。截至运行时成交量约为20日均量的 0.1 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L265" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B266" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C266" s="0">
+        <v>3</v>
+      </c>
+      <c r="D266" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603636</t>
+        </is>
+      </c>
+      <c r="E266" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南威软件</t>
+        </is>
+      </c>
+      <c r="F266" s="0">
+        <v>7.87</v>
+      </c>
+      <c r="G266" s="4">
+        <v>0.10069930069930066</v>
+      </c>
+      <c r="H266" s="4">
+        <v>0.17017701435935537</v>
+      </c>
+      <c r="I266" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J266" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 南威软件（603636）归入“网络安全+政务智能体+AI出海+算力”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K266" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.8 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L266" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B267" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C267" s="0">
+        <v>4</v>
+      </c>
+      <c r="D267" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000823</t>
+        </is>
+      </c>
+      <c r="E267" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">超声电子</t>
+        </is>
+      </c>
+      <c r="F267" s="0">
+        <v>24.4</v>
+      </c>
+      <c r="G267" s="4">
+        <v>0.10009017132551845</v>
+      </c>
+      <c r="H267" s="4">
+        <v>0.15747604530021253</v>
+      </c>
+      <c r="I267" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J267" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 超声电子（000823）归入“PCB+高阶HDI+覆铜板”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K267" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L267" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B268" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C268" s="0">
+        <v>5</v>
+      </c>
+      <c r="D268" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601811</t>
+        </is>
+      </c>
+      <c r="E268" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新华文轩</t>
+        </is>
+      </c>
+      <c r="F268" s="0">
+        <v>20.37</v>
+      </c>
+      <c r="G268" s="4">
+        <v>0.09989200863930892</v>
+      </c>
+      <c r="H268" s="4">
+        <v>0.15645848508023655</v>
+      </c>
+      <c r="I268" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J268" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 新华文轩（601811）归入“拟收购民族出版社+教科书发行+数字教育+“华”字辈”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K268" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.5 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L268" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；近10日涨幅偏高</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B269" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C269" s="0">
+        <v>6</v>
+      </c>
+      <c r="D269" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605058</t>
+        </is>
+      </c>
+      <c r="E269" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">澳弘电子</t>
+        </is>
+      </c>
+      <c r="F269" s="0">
+        <v>59.6</v>
+      </c>
+      <c r="G269" s="4">
+        <v>0.1000369139904025</v>
+      </c>
+      <c r="H269" s="4">
+        <v>0.15301046582118683</v>
+      </c>
+      <c r="I269" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J269" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 澳弘电子（605058）归入“PCB+HDI板+AI服务器电源+具身智能”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K269" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.8 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L269" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大；近10日涨幅偏高</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B270" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C270" s="0">
+        <v>7</v>
+      </c>
+      <c r="D270" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000607</t>
+        </is>
+      </c>
+      <c r="E270" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华媒控股</t>
+        </is>
+      </c>
+      <c r="F270" s="0">
+        <v>4.13</v>
+      </c>
+      <c r="G270" s="4">
+        <v>0.10133333333333328</v>
+      </c>
+      <c r="H270" s="4">
+        <v>0.15145502144939724</v>
+      </c>
+      <c r="I270" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J270" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华媒控股（000607）归入“文化传媒+AI漫剧+杭州日报+“华”字辈”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K270" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.4 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L270" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B271" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C271" s="0">
+        <v>8</v>
+      </c>
+      <c r="D271" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000002</t>
+        </is>
+      </c>
+      <c r="E271" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">万 科Ａ</t>
+        </is>
+      </c>
+      <c r="F271" s="0">
+        <v>4.08</v>
+      </c>
+      <c r="G271" s="4">
+        <v>0.09973045822102433</v>
+      </c>
+      <c r="H271" s="4">
+        <v>0.1489633983079168</v>
+      </c>
+      <c r="I271" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J271" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 万 科Ａ（000002）归入“房地产开发+城市更新+深铁支持”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K271" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.4 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L271" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B272" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C272" s="0">
+        <v>9</v>
+      </c>
+      <c r="D272" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600325</t>
+        </is>
+      </c>
+      <c r="E272" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华发股份</t>
+        </is>
+      </c>
+      <c r="F272" s="0">
+        <v>2.95</v>
+      </c>
+      <c r="G272" s="4">
+        <v>0.10074626865671643</v>
+      </c>
+      <c r="H272" s="4">
+        <v>0.14175137906615248</v>
+      </c>
+      <c r="I272" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J272" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华发股份（600325）归入“房地产+冰雪经济+定增支持+“华”字辈”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K272" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L272" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B273" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C273" s="0">
+        <v>10</v>
+      </c>
+      <c r="D273" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002913</t>
+        </is>
+      </c>
+      <c r="E273" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奥士康</t>
+        </is>
+      </c>
+      <c r="F273" s="0">
+        <v>91.08</v>
+      </c>
+      <c r="G273" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H273" s="4">
+        <v>0.14000022186122588</v>
+      </c>
+      <c r="I273" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J273" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 奥士康（002913）归入“高端PCB+AI服务器+可转债”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K273" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.7 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L273" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B274" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C274" s="0">
+        <v>11</v>
+      </c>
+      <c r="D274" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600189</t>
+        </is>
+      </c>
+      <c r="E274" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">泉阳泉</t>
+        </is>
+      </c>
+      <c r="F274" s="0">
+        <v>9.01</v>
+      </c>
+      <c r="G274" s="4">
+        <v>0.10012210012210021</v>
+      </c>
+      <c r="H274" s="4">
+        <v>0.13717429477232027</v>
+      </c>
+      <c r="I274" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J274" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 泉阳泉（600189）归入“天然矿泉水+园林剥离+全国扩张”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K274" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.4 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L274" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B275" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C275" s="0">
+        <v>12</v>
+      </c>
+      <c r="D275" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600657</t>
+        </is>
+      </c>
+      <c r="E275" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">信达地产</t>
+        </is>
+      </c>
+      <c r="F275" s="0">
+        <v>3.38</v>
+      </c>
+      <c r="G275" s="4">
+        <v>0.10097719869706845</v>
+      </c>
+      <c r="H275" s="4">
+        <v>0.13497029058587662</v>
+      </c>
+      <c r="I275" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J275" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 信达地产（600657）归入“房地产开发+轻资产代建+信达资源”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K275" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.8 倍，量能未出现极端放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L275" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B276" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C276" s="0">
+        <v>13</v>
+      </c>
+      <c r="D276" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603328</t>
+        </is>
+      </c>
+      <c r="E276" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">依顿电子</t>
+        </is>
+      </c>
+      <c r="F276" s="0">
+        <v>14.44</v>
+      </c>
+      <c r="G276" s="4">
+        <v>0.09977151561309959</v>
+      </c>
+      <c r="H276" s="4">
+        <v>0.13425855112941298</v>
+      </c>
+      <c r="I276" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J276" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 依顿电子（603328）归入“高端PCB+AI算力+控股股东增持”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K276" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.5 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L276" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B277" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C277" s="0">
+        <v>14</v>
+      </c>
+      <c r="D277" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002074</t>
+        </is>
+      </c>
+      <c r="E277" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">国轩高科</t>
+        </is>
+      </c>
+      <c r="F277" s="0">
+        <v>28.68</v>
+      </c>
+      <c r="G277" s="4">
+        <v>0.10011507479861903</v>
+      </c>
+      <c r="H277" s="4">
+        <v>0.13355196184173268</v>
+      </c>
+      <c r="I277" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J277" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 国轩高科（002074）归入“海外扩产+固态电池+大众合作”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K277" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L277" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B278" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C278" s="0">
+        <v>15</v>
+      </c>
+      <c r="D278" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605258</t>
+        </is>
+      </c>
+      <c r="E278" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">协和电子</t>
+        </is>
+      </c>
+      <c r="F278" s="0">
+        <v>44.01</v>
+      </c>
+      <c r="G278" s="4">
+        <v>0.09997500624843791</v>
+      </c>
+      <c r="H278" s="4">
+        <v>0.12967610792906506</v>
+      </c>
+      <c r="I278" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J278" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 协和电子（605258）归入“PCB+高频通讯+新能源电池”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K278" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L278" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B279" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C279" s="0">
+        <v>16</v>
+      </c>
+      <c r="D279" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605198</t>
+        </is>
+      </c>
+      <c r="E279" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">安德利</t>
+        </is>
+      </c>
+      <c r="F279" s="0">
+        <v>65.68</v>
+      </c>
+      <c r="G279" s="4">
+        <v>0.09998325238653492</v>
+      </c>
+      <c r="H279" s="4">
+        <v>0.12689243208078468</v>
+      </c>
+      <c r="I279" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J279" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 安德利（605198）归入“浓缩果汁+覆铜板+并购重组”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K279" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L279" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B280" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C280" s="0">
+        <v>17</v>
+      </c>
+      <c r="D280" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002303</t>
+        </is>
+      </c>
+      <c r="E280" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">美盈森</t>
+        </is>
+      </c>
+      <c r="F280" s="0">
+        <v>6.7</v>
+      </c>
+      <c r="G280" s="4">
+        <v>0.10016420361247945</v>
+      </c>
+      <c r="H280" s="4">
+        <v>0.12265081493817563</v>
+      </c>
+      <c r="I280" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J280" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 美盈森（002303）归入“导热凝胶+模切业务+消费电子包装+海外产能”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K280" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.8 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L280" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B281" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C281" s="0">
+        <v>18</v>
+      </c>
+      <c r="D281" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002815</t>
+        </is>
+      </c>
+      <c r="E281" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">崇达技术</t>
+        </is>
+      </c>
+      <c r="F281" s="0">
+        <v>24.44</v>
+      </c>
+      <c r="G281" s="4">
+        <v>0.09990999099909992</v>
+      </c>
+      <c r="H281" s="4">
+        <v>0.12261144164024648</v>
+      </c>
+      <c r="I281" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J281" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 崇达技术（002815）归入“高端PCB+服务器PCB+封装基板”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K281" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L281" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B282" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C282" s="0">
+        <v>19</v>
+      </c>
+      <c r="D282" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603322</t>
+        </is>
+      </c>
+      <c r="E282" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">超讯科技</t>
+        </is>
+      </c>
+      <c r="F282" s="0">
+        <v>29.1</v>
+      </c>
+      <c r="G282" s="4">
+        <v>0.10018903591682428</v>
+      </c>
+      <c r="H282" s="4">
+        <v>0.12176010151949233</v>
+      </c>
+      <c r="I282" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J282" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 超讯科技（603322）归入“国产算力+智算业务+算力租赁”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K282" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L282" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B283" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C283" s="0">
+        <v>20</v>
+      </c>
+      <c r="D283" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603598</t>
+        </is>
+      </c>
+      <c r="E283" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">引力传媒</t>
+        </is>
+      </c>
+      <c r="F283" s="0">
+        <v>19.13</v>
+      </c>
+      <c r="G283" s="4">
+        <v>0.10005750431282333</v>
+      </c>
+      <c r="H283" s="4">
+        <v>0.11346295300924364</v>
+      </c>
+      <c r="I283" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J283" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 引力传媒（603598）归入“AI短剧+全域营销+业绩增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K283" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L283" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B284" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C284" s="0">
+        <v>21</v>
+      </c>
+      <c r="D284" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002244</t>
+        </is>
+      </c>
+      <c r="E284" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">滨江集团</t>
+        </is>
+      </c>
+      <c r="F284" s="0">
+        <v>9.46</v>
+      </c>
+      <c r="G284" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H284" s="4">
+        <v>0.11171541951383138</v>
+      </c>
+      <c r="I284" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J284" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 滨江集团（002244）归入“房地产开发+杭州地产+固态电池”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K284" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L284" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B285" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C285" s="0">
+        <v>22</v>
+      </c>
+      <c r="D285" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600982</t>
+        </is>
+      </c>
+      <c r="E285" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">宁波能源</t>
+        </is>
+      </c>
+      <c r="F285" s="0">
+        <v>5.49</v>
+      </c>
+      <c r="G285" s="4">
+        <v>0.10020040080160332</v>
+      </c>
+      <c r="H285" s="4">
+        <v>0.11166030256492736</v>
+      </c>
+      <c r="I285" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J285" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 宁波能源（600982）归入“风电收购+热电联产+业绩增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K285" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.5 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L285" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B286" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C286" s="0">
+        <v>23</v>
+      </c>
+      <c r="D286" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002813</t>
+        </is>
+      </c>
+      <c r="E286" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">路畅科技</t>
+        </is>
+      </c>
+      <c r="F286" s="0">
+        <v>26.38</v>
+      </c>
+      <c r="G286" s="4">
+        <v>0.10008340283569626</v>
+      </c>
+      <c r="H286" s="4">
+        <v>0.11101064476675578</v>
+      </c>
+      <c r="I286" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J286" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 路畅科技（002813）归入“智能驾驶+智能座舱+汽车电子前装”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K286" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.5 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L286" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B287" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C287" s="0">
+        <v>24</v>
+      </c>
+      <c r="D287" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601949</t>
+        </is>
+      </c>
+      <c r="E287" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中国出版</t>
+        </is>
+      </c>
+      <c r="F287" s="0">
+        <v>6.01</v>
+      </c>
+      <c r="G287" s="4">
+        <v>0.10073260073260058</v>
+      </c>
+      <c r="H287" s="4">
+        <v>0.107505047297468</v>
+      </c>
+      <c r="I287" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J287" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 中国出版（601949）归入“AI出版+图书出版+中国出版集团”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K287" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L287" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B288" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C288" s="0">
+        <v>25</v>
+      </c>
+      <c r="D288" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603188</t>
+        </is>
+      </c>
+      <c r="E288" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">亚邦股份</t>
+        </is>
+      </c>
+      <c r="F288" s="0">
+        <v>4.91</v>
+      </c>
+      <c r="G288" s="4">
+        <v>0.10089686098654704</v>
+      </c>
+      <c r="H288" s="4">
+        <v>0.10514308216063505</v>
+      </c>
+      <c r="I288" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J288" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 亚邦股份（603188）归入“染料中间体+染料产业链+业绩增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K288" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.5 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L288" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B289" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C289" s="0">
+        <v>26</v>
+      </c>
+      <c r="D289" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002866</t>
+        </is>
+      </c>
+      <c r="E289" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">传艺科技</t>
+        </is>
+      </c>
+      <c r="F289" s="0">
+        <v>15.36</v>
+      </c>
+      <c r="G289" s="4">
+        <v>0.10028653295128918</v>
+      </c>
+      <c r="H289" s="4">
+        <v>0.10463343936034204</v>
+      </c>
+      <c r="I289" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J289" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 传艺科技（002866）归入“钠离子电池+固态电池+AI PC键盘”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K289" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.5 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L289" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B290" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C290" s="0">
+        <v>27</v>
+      </c>
+      <c r="D290" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002058</t>
+        </is>
+      </c>
+      <c r="E290" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">紫竹高科</t>
+        </is>
+      </c>
+      <c r="F290" s="0">
+        <v>18.36</v>
+      </c>
+      <c r="G290" s="4">
+        <v>0.10005991611743535</v>
+      </c>
+      <c r="H290" s="4">
+        <v>0.10440695434897848</v>
+      </c>
+      <c r="I290" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J290" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 紫竹高科（002058）归入“铝塑膜+固态电池+客户供货”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K290" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L290" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B291" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C291" s="0">
+        <v>28</v>
+      </c>
+      <c r="D291" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000036</t>
+        </is>
+      </c>
+      <c r="E291" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华联控股</t>
+        </is>
+      </c>
+      <c r="F291" s="0">
+        <v>4.21</v>
+      </c>
+      <c r="G291" s="4">
+        <v>0.09921671018276769</v>
+      </c>
+      <c r="H291" s="4">
+        <v>0.10403638525003489</v>
+      </c>
+      <c r="I291" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J291" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华联控股（000036）归入“盐湖提锂+房地产开发+业绩增长+“华”字辈”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K291" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L291" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B292" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C292" s="0">
+        <v>29</v>
+      </c>
+      <c r="D292" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603200</t>
+        </is>
+      </c>
+      <c r="E292" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上海洗霸</t>
+        </is>
+      </c>
+      <c r="F292" s="0">
+        <v>40.67</v>
+      </c>
+      <c r="G292" s="4">
+        <v>0.10008114687584534</v>
+      </c>
+      <c r="H292" s="4">
+        <v>0.10122829279175984</v>
+      </c>
+      <c r="I292" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J292" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 上海洗霸（603200）归入“固态电池+液冷服务器+水处理”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K292" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.5 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L292" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B293" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C293" s="0">
+        <v>30</v>
+      </c>
+      <c r="D293" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002846</t>
+        </is>
+      </c>
+      <c r="E293" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">英联股份</t>
+        </is>
+      </c>
+      <c r="F293" s="0">
+        <v>11.88</v>
+      </c>
+      <c r="G293" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H293" s="4">
+        <v>0.09971938710268438</v>
+      </c>
+      <c r="I293" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J293" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 英联股份（002846）归入“固态电池+复合集流体+金属包装”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K293" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L293" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B294" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C294" s="0">
+        <v>31</v>
+      </c>
+      <c r="D294" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603980</t>
+        </is>
+      </c>
+      <c r="E294" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">吉华集团</t>
+        </is>
+      </c>
+      <c r="F294" s="0">
+        <v>8.84</v>
+      </c>
+      <c r="G294" s="4">
+        <v>0.09950248756218905</v>
+      </c>
+      <c r="H294" s="4">
+        <v>0.09919028632501233</v>
+      </c>
+      <c r="I294" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J294" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 吉华集团（603980）归入“染料涨价+控制权变更+业绩增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K294" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.8 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L294" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B295" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C295" s="0">
+        <v>32</v>
+      </c>
+      <c r="D295" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605388</t>
+        </is>
+      </c>
+      <c r="E295" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">均瑶健康</t>
+        </is>
+      </c>
+      <c r="F295" s="0">
+        <v>6.72</v>
+      </c>
+      <c r="G295" s="4">
+        <v>0.09983633387888702</v>
+      </c>
+      <c r="H295" s="4">
+        <v>0.09813895885269432</v>
+      </c>
+      <c r="I295" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J295" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 均瑶健康（605388）归入“益生菌+乳酸菌饮料+电商增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K295" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L295" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B296" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C296" s="0">
+        <v>33</v>
+      </c>
+      <c r="D296" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002205</t>
+        </is>
+      </c>
+      <c r="E296" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">国统股份</t>
+        </is>
+      </c>
+      <c r="F296" s="0">
+        <v>12.76</v>
+      </c>
+      <c r="G296" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H296" s="4">
+        <v>0.09640011665983844</v>
+      </c>
+      <c r="I296" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J296" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 国统股份（002205）归入“风电混塔+PCCP水利管道+央企控股”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K296" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.9 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L296" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B297" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C297" s="0">
+        <v>34</v>
+      </c>
+      <c r="D297" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601519</t>
+        </is>
+      </c>
+      <c r="E297" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大智慧</t>
+        </is>
+      </c>
+      <c r="F297" s="0">
+        <v>9.01</v>
+      </c>
+      <c r="G297" s="4">
+        <v>0.10012210012210021</v>
+      </c>
+      <c r="H297" s="4">
+        <v>0.09443842091046009</v>
+      </c>
+      <c r="I297" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J297" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 大智慧（601519）归入“互联网金融+湘财吸收合并+人工智能”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K297" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.4 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L297" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B298" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C298" s="0">
+        <v>35</v>
+      </c>
+      <c r="D298" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002799</t>
+        </is>
+      </c>
+      <c r="E298" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">环球印务</t>
+        </is>
+      </c>
+      <c r="F298" s="0">
+        <v>7.55</v>
+      </c>
+      <c r="G298" s="4">
+        <v>0.10058309037900859</v>
+      </c>
+      <c r="H298" s="4">
+        <v>0.09358204390761832</v>
+      </c>
+      <c r="I298" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J298" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 环球印务（002799）归入“医药包装+智慧制造+互联网营销（拟收缩）”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K298" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.1 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L298" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B299" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C299" s="0">
+        <v>36</v>
+      </c>
+      <c r="D299" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603533</t>
+        </is>
+      </c>
+      <c r="E299" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">掌阅科技</t>
+        </is>
+      </c>
+      <c r="F299" s="0">
+        <v>23.65</v>
+      </c>
+      <c r="G299" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H299" s="4">
+        <v>0.09286123219906349</v>
+      </c>
+      <c r="I299" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J299" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 掌阅科技（603533）归入“AI短剧+短剧出海+数字阅读”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K299" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.7 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L299" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B300" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C300" s="0">
+        <v>37</v>
+      </c>
+      <c r="D300" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603630</t>
+        </is>
+      </c>
+      <c r="E300" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">拉芳家化</t>
+        </is>
+      </c>
+      <c r="F300" s="0">
+        <v>15.57</v>
+      </c>
+      <c r="G300" s="4">
+        <v>0.10035335689045934</v>
+      </c>
+      <c r="H300" s="4">
+        <v>0.0909277281258187</v>
+      </c>
+      <c r="I300" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J300" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 拉芳家化（603630）归入“洗护用品+品牌优化+业绩改善”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K300" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.4 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L300" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B301" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C301" s="0">
+        <v>38</v>
+      </c>
+      <c r="D301" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002494</t>
+        </is>
+      </c>
+      <c r="E301" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华斯股份</t>
+        </is>
+      </c>
+      <c r="F301" s="0">
+        <v>5.32</v>
+      </c>
+      <c r="G301" s="4">
+        <v>0.09917355371900838</v>
+      </c>
+      <c r="H301" s="4">
+        <v>0.08428600057117622</v>
+      </c>
+      <c r="I301" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J301" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华斯股份（002494）归入“裘皮服饰+海外销售+业绩改善+“华”字辈”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K301" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.3 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L301" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B302" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C302" s="0">
+        <v>39</v>
+      </c>
+      <c r="D302" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000068</t>
+        </is>
+      </c>
+      <c r="E302" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华控赛格</t>
+        </is>
+      </c>
+      <c r="F302" s="0">
+        <v>3.54</v>
+      </c>
+      <c r="G302" s="4">
+        <v>0.09937888198757762</v>
+      </c>
+      <c r="H302" s="4">
+        <v>0.08418742370254993</v>
+      </c>
+      <c r="I302" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J302" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华控赛格（000068）归入“锂电负极+海绵城市+山西国资+“华”字辈”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K302" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.5 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L302" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B303" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C303" s="0">
+        <v>40</v>
+      </c>
+      <c r="D303" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002882</t>
+        </is>
+      </c>
+      <c r="E303" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金龙羽</t>
+        </is>
+      </c>
+      <c r="F303" s="0">
+        <v>24.51</v>
+      </c>
+      <c r="G303" s="4">
+        <v>0.10008976660682233</v>
+      </c>
+      <c r="H303" s="4">
+        <v>0.08272719829443018</v>
+      </c>
+      <c r="I303" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J303" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 金龙羽（002882）归入“固态电池+机器人电池+电线电缆”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K303" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L303" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B304" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C304" s="0">
+        <v>41</v>
+      </c>
+      <c r="D304" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603602</t>
+        </is>
+      </c>
+      <c r="E304" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">纵横通信</t>
+        </is>
+      </c>
+      <c r="F304" s="0">
+        <v>12.71</v>
+      </c>
+      <c r="G304" s="4">
+        <v>0.10043290043290053</v>
+      </c>
+      <c r="H304" s="4">
+        <v>0.0825214808937549</v>
+      </c>
+      <c r="I304" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J304" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 纵横通信（603602）归入“AI营销+AI短剧+字节概念+低空经济”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K304" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.8 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L304" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B305" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C305" s="0">
+        <v>42</v>
+      </c>
+      <c r="D305" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600152</t>
+        </is>
+      </c>
+      <c r="E305" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">维科技术</t>
+        </is>
+      </c>
+      <c r="F305" s="0">
+        <v>8.32</v>
+      </c>
+      <c r="G305" s="4">
+        <v>0.10052910052910068</v>
+      </c>
+      <c r="H305" s="4">
+        <v>0.07454181628416796</v>
+      </c>
+      <c r="I305" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J305" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 维科技术（600152）归入“钠电储能+AIDC电源+消费电池”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K305" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.8 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 51 家涨停，其中首板 42 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L305" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M63"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -17330,6 +19598,596 @@
       <c r="M53" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">2.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B54" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="C54" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D54" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001330</t>
+        </is>
+      </c>
+      <c r="E54" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">博纳影业</t>
+        </is>
+      </c>
+      <c r="F54" s="4">
+        <v>0.46904660227015416</v>
+      </c>
+      <c r="G54" s="4">
+        <v>0.0691823899371069</v>
+      </c>
+      <c r="H54" s="4">
+        <v>0.09591194968553451</v>
+      </c>
+      <c r="I54" s="4">
+        <v>0.04245283018867907</v>
+      </c>
+      <c r="J54" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K54" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +4.25%</t>
+        </is>
+      </c>
+      <c r="L54" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M54" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B55" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="C55" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D55" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601579</t>
+        </is>
+      </c>
+      <c r="E55" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">会稽山</t>
+        </is>
+      </c>
+      <c r="F55" s="4">
+        <v>0.24770917505433532</v>
+      </c>
+      <c r="G55" s="4">
+        <v>-0.009799235181644494</v>
+      </c>
+      <c r="H55" s="4">
+        <v>-0.009799235181644494</v>
+      </c>
+      <c r="I55" s="4">
+        <v>-0.09990439770554504</v>
+      </c>
+      <c r="J55" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K55" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -9.99%</t>
+        </is>
+      </c>
+      <c r="L55" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M55" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37.66</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="C56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="D56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002912</t>
+        </is>
+      </c>
+      <c r="E56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中新赛克</t>
+        </is>
+      </c>
+      <c r="F56" s="4">
+        <v>0.21277869537940503</v>
+      </c>
+      <c r="G56" s="4">
+        <v>0.04080090668681535</v>
+      </c>
+      <c r="H56" s="4">
+        <v>0.10011333585190796</v>
+      </c>
+      <c r="I56" s="4">
+        <v>0.10011333585190796</v>
+      </c>
+      <c r="J56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +10.01%</t>
+        </is>
+      </c>
+      <c r="L56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="C57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="D57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001201</t>
+        </is>
+      </c>
+      <c r="E57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东瑞股份</t>
+        </is>
+      </c>
+      <c r="F57" s="4">
+        <v>0.19510729246964234</v>
+      </c>
+      <c r="G57" s="4">
+        <v>0.009919404835709855</v>
+      </c>
+      <c r="H57" s="4">
+        <v>0.022318660880347174</v>
+      </c>
+      <c r="I57" s="4">
+        <v>-0.025418474891506393</v>
+      </c>
+      <c r="J57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -2.54%</t>
+        </is>
+      </c>
+      <c r="L57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15.72</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="C58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="D58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001368</t>
+        </is>
+      </c>
+      <c r="E58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通达创智</t>
+        </is>
+      </c>
+      <c r="F58" s="4">
+        <v>0.18511876321457663</v>
+      </c>
+      <c r="G58" s="4">
+        <v>-0.04976076555023923</v>
+      </c>
+      <c r="H58" s="4">
+        <v>-0.04976076555023923</v>
+      </c>
+      <c r="I58" s="4">
+        <v>-0.09999999999999998</v>
+      </c>
+      <c r="J58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -10.00%</t>
+        </is>
+      </c>
+      <c r="L58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B59" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="C59" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="D59" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600418</t>
+        </is>
+      </c>
+      <c r="E59" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">江淮汽车</t>
+        </is>
+      </c>
+      <c r="F59" s="4">
+        <v>0.17714854940653763</v>
+      </c>
+      <c r="G59" s="4">
+        <v>0.018636003172085802</v>
+      </c>
+      <c r="H59" s="4">
+        <v>0.06621728786677239</v>
+      </c>
+      <c r="I59" s="4">
+        <v>0.032513877874702724</v>
+      </c>
+      <c r="J59" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K59" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +3.25%</t>
+        </is>
+      </c>
+      <c r="L59" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M59" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B60" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="C60" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="D60" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002242</t>
+        </is>
+      </c>
+      <c r="E60" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">九阳股份</t>
+        </is>
+      </c>
+      <c r="F60" s="4">
+        <v>0.17227945942556677</v>
+      </c>
+      <c r="G60" s="4">
+        <v>0.06969990319457886</v>
+      </c>
+      <c r="H60" s="4">
+        <v>0.09970958373668926</v>
+      </c>
+      <c r="I60" s="4">
+        <v>0.09970958373668926</v>
+      </c>
+      <c r="J60" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K60" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +9.97%</t>
+        </is>
+      </c>
+      <c r="L60" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M60" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B61" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="C61" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="D61" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000020</t>
+        </is>
+      </c>
+      <c r="E61" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">深华发Ａ</t>
+        </is>
+      </c>
+      <c r="F61" s="4">
+        <v>0.170827085314805</v>
+      </c>
+      <c r="G61" s="4">
+        <v>0.024590163934426146</v>
+      </c>
+      <c r="H61" s="4">
+        <v>0.0997267759562841</v>
+      </c>
+      <c r="I61" s="4">
+        <v>0.000683060109289535</v>
+      </c>
+      <c r="J61" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K61" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +0.07%</t>
+        </is>
+      </c>
+      <c r="L61" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M61" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B62" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="C62" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="D62" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002640</t>
+        </is>
+      </c>
+      <c r="E62" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">跨境通</t>
+        </is>
+      </c>
+      <c r="F62" s="4">
+        <v>0.166134967767185</v>
+      </c>
+      <c r="G62" s="4">
+        <v>0.022727272727272707</v>
+      </c>
+      <c r="H62" s="4">
+        <v>0.06565656565656552</v>
+      </c>
+      <c r="I62" s="4">
+        <v>-0.005050505050505083</v>
+      </c>
+      <c r="J62" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K62" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -0.51%</t>
+        </is>
+      </c>
+      <c r="L62" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M62" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.94</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="B63" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="C63" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="D63" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000011</t>
+        </is>
+      </c>
+      <c r="E63" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">深物业A</t>
+        </is>
+      </c>
+      <c r="F63" s="4">
+        <v>0.15010641913890024</v>
+      </c>
+      <c r="G63" s="4">
+        <v>0.09980237154150218</v>
+      </c>
+      <c r="H63" s="4">
+        <v>0.09980237154150218</v>
+      </c>
+      <c r="I63" s="4">
+        <v>0.09980237154150218</v>
+      </c>
+      <c r="J63" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K63" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +9.98%</t>
+        </is>
+      </c>
+      <c r="L63" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M63" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.13</t>
         </is>
       </c>
     </row>
@@ -17421,28 +20279,28 @@
         </is>
       </c>
       <c r="B3" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" s="0">
         <v>2</v>
       </c>
       <c r="E3" s="4">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F3" s="4">
-        <v>0.09090909090909091</v>
+        <v>0.25</v>
       </c>
       <c r="G3" s="0">
-        <v>4.4</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="H3" s="0">
         <v>2</v>
       </c>
       <c r="I3" s="4">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -17452,28 +20310,28 @@
         </is>
       </c>
       <c r="B4" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D4" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4" s="4">
         <v>0.3333333333333333</v>
       </c>
       <c r="F4" s="4">
-        <v>0.09090909090909091</v>
+        <v>0.25</v>
       </c>
       <c r="G4" s="0">
-        <v>3.6666666666666665</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="H4" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" s="4">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
@@ -17483,28 +20341,28 @@
         </is>
       </c>
       <c r="B5" s="0">
+        <v>6</v>
+      </c>
+      <c r="C5" s="0">
+        <v>36</v>
+      </c>
+      <c r="D5" s="0">
+        <v>12</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="G5" s="0">
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="H5" s="0">
         <v>5</v>
       </c>
-      <c r="C5" s="0">
-        <v>30</v>
-      </c>
-      <c r="D5" s="0">
-        <v>11</v>
-      </c>
-      <c r="E5" s="4">
-        <v>0.36666666666666664</v>
-      </c>
-      <c r="F5" s="4">
-        <v>0.09090909090909091</v>
-      </c>
-      <c r="G5" s="0">
-        <v>4.033333333333333</v>
-      </c>
-      <c r="H5" s="0">
-        <v>4</v>
-      </c>
       <c r="I5" s="4">
-        <v>0.8</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="6">
@@ -17514,28 +20372,28 @@
         </is>
       </c>
       <c r="B6" s="0">
+        <v>6</v>
+      </c>
+      <c r="C6" s="0">
+        <v>60</v>
+      </c>
+      <c r="D6" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0.2833333333333333</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="0">
+        <v>1.1333333333333333</v>
+      </c>
+      <c r="H6" s="0">
         <v>5</v>
       </c>
-      <c r="C6" s="0">
-        <v>50</v>
-      </c>
-      <c r="D6" s="0">
-        <v>14</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0.28</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0.09090909090909091</v>
-      </c>
-      <c r="G6" s="0">
-        <v>3.08</v>
-      </c>
-      <c r="H6" s="0">
-        <v>4</v>
-      </c>
       <c r="I6" s="4">
-        <v>0.8</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="7">

--- a/docs/downloads/latest.xlsx
+++ b/docs/downloads/latest.xlsx
@@ -93,7 +93,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L305"/>
+  <dimension ref="A1:L343"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -16519,13 +16519,2065 @@
         </is>
       </c>
     </row>
+    <row r="306">
+      <c r="A306" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B306" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C306" s="0">
+        <v>1</v>
+      </c>
+      <c r="D306" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001206</t>
+        </is>
+      </c>
+      <c r="E306" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">依依股份</t>
+        </is>
+      </c>
+      <c r="F306" s="0">
+        <v>18.62</v>
+      </c>
+      <c r="G306" s="4">
+        <v>0.0998227997637331</v>
+      </c>
+      <c r="H306" s="4">
+        <v>0.2534808383755009</v>
+      </c>
+      <c r="I306" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J306" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 依依股份（001206）归入“协议转让+宠物护理+海外产能”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K306" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 8.2%）。截至运行时成交量约为20日均量的 1.4 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L306" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B307" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C307" s="0">
+        <v>2</v>
+      </c>
+      <c r="D307" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601118</t>
+        </is>
+      </c>
+      <c r="E307" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">海南橡胶</t>
+        </is>
+      </c>
+      <c r="F307" s="0">
+        <v>6.37</v>
+      </c>
+      <c r="G307" s="4">
+        <v>0.10017271157167527</v>
+      </c>
+      <c r="H307" s="4">
+        <v>0.25281070521125687</v>
+      </c>
+      <c r="I307" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J307" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 海南橡胶（601118）归入“天然橡胶+全球龙头+全产业链”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K307" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 8.5%）。截至运行时成交量约为20日均量的 0.4 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L307" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B308" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C308" s="0">
+        <v>3</v>
+      </c>
+      <c r="D308" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002164</t>
+        </is>
+      </c>
+      <c r="E308" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">宁波东力</t>
+        </is>
+      </c>
+      <c r="F308" s="0">
+        <v>13.26</v>
+      </c>
+      <c r="G308" s="4">
+        <v>0.10041493775933595</v>
+      </c>
+      <c r="H308" s="4">
+        <v>0.1821818877553951</v>
+      </c>
+      <c r="I308" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J308" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 宁波东力（002164）归入“具身智能+精密减速器+股东增持”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K308" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.4 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L308" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B309" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C309" s="0">
+        <v>4</v>
+      </c>
+      <c r="D309" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000504</t>
+        </is>
+      </c>
+      <c r="E309" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南华生物</t>
+        </is>
+      </c>
+      <c r="F309" s="0">
+        <v>12.42</v>
+      </c>
+      <c r="G309" s="4">
+        <v>0.10008857395925608</v>
+      </c>
+      <c r="H309" s="4">
+        <v>0.18182410134085636</v>
+      </c>
+      <c r="I309" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J309" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 南华生物（000504）归入“细胞存储+生物医药+中报扭亏”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K309" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.9 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L309" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B310" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C310" s="0">
+        <v>5</v>
+      </c>
+      <c r="D310" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002388</t>
+        </is>
+      </c>
+      <c r="E310" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新亚制程</t>
+        </is>
+      </c>
+      <c r="F310" s="0">
+        <v>9.1</v>
+      </c>
+      <c r="G310" s="4">
+        <v>0.10036275695284157</v>
+      </c>
+      <c r="H310" s="4">
+        <v>0.180071742795729</v>
+      </c>
+      <c r="I310" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J310" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 新亚制程（002388）归入“固态电池+AI服务器电源+锂电材料”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K310" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.8 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L310" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B311" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C311" s="0">
+        <v>6</v>
+      </c>
+      <c r="D311" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000710</t>
+        </is>
+      </c>
+      <c r="E311" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">贝瑞基因</t>
+        </is>
+      </c>
+      <c r="F311" s="0">
+        <v>10.87</v>
+      </c>
+      <c r="G311" s="4">
+        <v>0.10020242914979738</v>
+      </c>
+      <c r="H311" s="4">
+        <v>0.17880618320808775</v>
+      </c>
+      <c r="I311" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J311" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 贝瑞基因（000710）归入“AI医疗+基因检测+三代测序”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K311" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L311" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B312" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C312" s="0">
+        <v>7</v>
+      </c>
+      <c r="D312" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600059</t>
+        </is>
+      </c>
+      <c r="E312" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">古越龙山</t>
+        </is>
+      </c>
+      <c r="F312" s="0">
+        <v>12.27</v>
+      </c>
+      <c r="G312" s="4">
+        <v>0.10044843049327357</v>
+      </c>
+      <c r="H312" s="4">
+        <v>0.17040237956161344</v>
+      </c>
+      <c r="I312" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J312" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 古越龙山（600059）归入“高端黄酒+全国化+年轻化”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K312" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L312" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B313" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C313" s="0">
+        <v>8</v>
+      </c>
+      <c r="D313" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605577</t>
+        </is>
+      </c>
+      <c r="E313" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">龙版传媒</t>
+        </is>
+      </c>
+      <c r="F313" s="0">
+        <v>16.28</v>
+      </c>
+      <c r="G313" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H313" s="4">
+        <v>0.1616046093658782</v>
+      </c>
+      <c r="I313" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J313" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 龙版传媒（605577）归入“AI漫剧+出版发行+黑龙江国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K313" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.3 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L313" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B314" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C314" s="0">
+        <v>9</v>
+      </c>
+      <c r="D314" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600356</t>
+        </is>
+      </c>
+      <c r="E314" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">恒丰纸业</t>
+        </is>
+      </c>
+      <c r="F314" s="0">
+        <v>11.46</v>
+      </c>
+      <c r="G314" s="4">
+        <v>0.0998080614203456</v>
+      </c>
+      <c r="H314" s="4">
+        <v>0.16099975536391362</v>
+      </c>
+      <c r="I314" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J314" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 恒丰纸业（600356）归入“新型烟草+卷烟纸+业绩增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K314" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L314" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B315" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C315" s="0">
+        <v>10</v>
+      </c>
+      <c r="D315" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600663</t>
+        </is>
+      </c>
+      <c r="E315" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">陆家嘴</t>
+        </is>
+      </c>
+      <c r="F315" s="0">
+        <v>10.11</v>
+      </c>
+      <c r="G315" s="4">
+        <v>0.10010881392818272</v>
+      </c>
+      <c r="H315" s="4">
+        <v>0.1520921357706909</v>
+      </c>
+      <c r="I315" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J315" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 陆家嘴（600663）归入“房地产开发+商办物业+浦东国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K315" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.5 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L315" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B316" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C316" s="0">
+        <v>11</v>
+      </c>
+      <c r="D316" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002962</t>
+        </is>
+      </c>
+      <c r="E316" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">五方光电</t>
+        </is>
+      </c>
+      <c r="F316" s="0">
+        <v>16.17</v>
+      </c>
+      <c r="G316" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H316" s="4">
+        <v>0.13957410698688955</v>
+      </c>
+      <c r="I316" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J316" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 五方光电（002962）归入“TGV光学+微棱镜+AR/VR”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K316" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.9 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L316" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B317" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C317" s="0">
+        <v>12</v>
+      </c>
+      <c r="D317" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002188</t>
+        </is>
+      </c>
+      <c r="E317" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中天服务</t>
+        </is>
+      </c>
+      <c r="F317" s="0">
+        <v>6.4</v>
+      </c>
+      <c r="G317" s="4">
+        <v>0.09965635738831624</v>
+      </c>
+      <c r="H317" s="4">
+        <v>0.13161481152665738</v>
+      </c>
+      <c r="I317" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J317" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 中天服务（002188）归入“物业管理+社区养老+股份回购”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K317" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.3 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L317" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B318" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C318" s="0">
+        <v>13</v>
+      </c>
+      <c r="D318" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605288</t>
+        </is>
+      </c>
+      <c r="E318" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">凯迪股份</t>
+        </is>
+      </c>
+      <c r="F318" s="0">
+        <v>71.83</v>
+      </c>
+      <c r="G318" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H318" s="4">
+        <v>0.13087850175445917</v>
+      </c>
+      <c r="I318" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J318" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 凯迪股份（605288）归入“具身机器人送样+智能线性驱动+汽车零部件”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K318" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L318" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B319" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C319" s="0">
+        <v>14</v>
+      </c>
+      <c r="D319" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001266</t>
+        </is>
+      </c>
+      <c r="E319" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">宏英智能</t>
+        </is>
+      </c>
+      <c r="F319" s="0">
+        <v>39.96</v>
+      </c>
+      <c r="G319" s="4">
+        <v>0.09991742361684564</v>
+      </c>
+      <c r="H319" s="4">
+        <v>0.12891765626062643</v>
+      </c>
+      <c r="I319" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J319" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 宏英智能（001266）归入“液冷储能+智能电控+业绩增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K319" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.2 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L319" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B320" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C320" s="0">
+        <v>15</v>
+      </c>
+      <c r="D320" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603928</t>
+        </is>
+      </c>
+      <c r="E320" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">兴业股份</t>
+        </is>
+      </c>
+      <c r="F320" s="0">
+        <v>13.07</v>
+      </c>
+      <c r="G320" s="4">
+        <v>0.10016835016835014</v>
+      </c>
+      <c r="H320" s="4">
+        <v>0.126950628697666</v>
+      </c>
+      <c r="I320" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J320" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 兴业股份（603928）归入“光刻胶树脂+合成树脂+业绩增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K320" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L320" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B321" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C321" s="0">
+        <v>16</v>
+      </c>
+      <c r="D321" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603538</t>
+        </is>
+      </c>
+      <c r="E321" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">美诺华</t>
+        </is>
+      </c>
+      <c r="F321" s="0">
+        <v>28.59</v>
+      </c>
+      <c r="G321" s="4">
+        <v>0.10003847633705278</v>
+      </c>
+      <c r="H321" s="4">
+        <v>0.12286903470293435</v>
+      </c>
+      <c r="I321" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J321" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 美诺华（603538）归入“JH389+医药CDMO+制剂一体化”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K321" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L321" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B322" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C322" s="0">
+        <v>17</v>
+      </c>
+      <c r="D322" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603127</t>
+        </is>
+      </c>
+      <c r="E322" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">昭衍新药</t>
+        </is>
+      </c>
+      <c r="F322" s="0">
+        <v>49.3</v>
+      </c>
+      <c r="G322" s="4">
+        <v>0.09995537706381065</v>
+      </c>
+      <c r="H322" s="4">
+        <v>0.12171708481000572</v>
+      </c>
+      <c r="I322" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J322" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 昭衍新药（603127）归入“创新药CRO+实验猴+订单回暖”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K322" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L322" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B323" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C323" s="0">
+        <v>18</v>
+      </c>
+      <c r="D323" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603948</t>
+        </is>
+      </c>
+      <c r="E323" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">建业股份</t>
+        </is>
+      </c>
+      <c r="F323" s="0">
+        <v>21.36</v>
+      </c>
+      <c r="G323" s="4">
+        <v>0.09989701338825929</v>
+      </c>
+      <c r="H323" s="4">
+        <v>0.11916071967796997</v>
+      </c>
+      <c r="I323" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J323" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 建业股份（603948）归入“电子化学品+超纯氨+环保增塑剂”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K323" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L323" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B324" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C324" s="0">
+        <v>19</v>
+      </c>
+      <c r="D324" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600592</t>
+        </is>
+      </c>
+      <c r="E324" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">龙溪股份</t>
+        </is>
+      </c>
+      <c r="F324" s="0">
+        <v>16.2</v>
+      </c>
+      <c r="G324" s="4">
+        <v>0.09979633401221989</v>
+      </c>
+      <c r="H324" s="4">
+        <v>0.11782513734150028</v>
+      </c>
+      <c r="I324" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J324" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 龙溪股份（600592）归入“人形机器人+关节轴承+国企背景”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K324" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.5 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L324" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B325" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C325" s="0">
+        <v>20</v>
+      </c>
+      <c r="D325" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605011</t>
+        </is>
+      </c>
+      <c r="E325" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">杭州热电</t>
+        </is>
+      </c>
+      <c r="F325" s="0">
+        <v>19.21</v>
+      </c>
+      <c r="G325" s="4">
+        <v>0.10022909507445599</v>
+      </c>
+      <c r="H325" s="4">
+        <v>0.11606993835149837</v>
+      </c>
+      <c r="I325" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J325" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 杭州热电（605011）归入“热电联产+集中供热+综合能源”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K325" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L325" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B326" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C326" s="0">
+        <v>21</v>
+      </c>
+      <c r="D326" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000668</t>
+        </is>
+      </c>
+      <c r="E326" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">荣丰控股</t>
+        </is>
+      </c>
+      <c r="F326" s="0">
+        <v>18.69</v>
+      </c>
+      <c r="G326" s="4">
+        <v>0.09941176470588253</v>
+      </c>
+      <c r="H326" s="4">
+        <v>0.11595904258359595</v>
+      </c>
+      <c r="I326" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no_verified_event</t>
+        </is>
+      </c>
+      <c r="J326" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">事件证据层未找到与当日涨停直接匹配的公告或新闻；系统不把概念标签、技术形态或主观猜测当成涨停原因。</t>
+        </is>
+      </c>
+      <c r="K326" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L326" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B327" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C327" s="0">
+        <v>22</v>
+      </c>
+      <c r="D327" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002454</t>
+        </is>
+      </c>
+      <c r="E327" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">松芝股份</t>
+        </is>
+      </c>
+      <c r="F327" s="0">
+        <v>5.61</v>
+      </c>
+      <c r="G327" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H327" s="4">
+        <v>0.11555601802652743</v>
+      </c>
+      <c r="I327" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J327" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 松芝股份（002454）归入“储能热管理+汽车热管理+海外拓展”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K327" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.5 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L327" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B328" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C328" s="0">
+        <v>23</v>
+      </c>
+      <c r="D328" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600081</t>
+        </is>
+      </c>
+      <c r="E328" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东风科技</t>
+        </is>
+      </c>
+      <c r="F328" s="0">
+        <v>11.89</v>
+      </c>
+      <c r="G328" s="4">
+        <v>0.09990749306197966</v>
+      </c>
+      <c r="H328" s="4">
+        <v>0.11263144890824388</v>
+      </c>
+      <c r="I328" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J328" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 东风科技（600081）归入“汽车电子+一体化压铸+业绩预增”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K328" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.4 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L328" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B329" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C329" s="0">
+        <v>24</v>
+      </c>
+      <c r="D329" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002316</t>
+        </is>
+      </c>
+      <c r="E329" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">亚联发展</t>
+        </is>
+      </c>
+      <c r="F329" s="0">
+        <v>4.95</v>
+      </c>
+      <c r="G329" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H329" s="4">
+        <v>0.11262637919183865</v>
+      </c>
+      <c r="I329" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J329" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 亚联发展（002316）归入“诉讼进展+智慧电网+生物纤维素”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K329" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L329" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B330" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C330" s="0">
+        <v>25</v>
+      </c>
+      <c r="D330" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603739</t>
+        </is>
+      </c>
+      <c r="E330" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">蔚蓝生物</t>
+        </is>
+      </c>
+      <c r="F330" s="0">
+        <v>14.04</v>
+      </c>
+      <c r="G330" s="4">
+        <v>0.1003134796238243</v>
+      </c>
+      <c r="H330" s="4">
+        <v>0.1073299776197685</v>
+      </c>
+      <c r="I330" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J330" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 蔚蓝生物（603739）归入“新兽药注册+动物保健+酶制剂”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K330" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L330" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B331" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C331" s="0">
+        <v>26</v>
+      </c>
+      <c r="D331" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002755</t>
+        </is>
+      </c>
+      <c r="E331" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奥赛康</t>
+        </is>
+      </c>
+      <c r="F331" s="0">
+        <v>13.55</v>
+      </c>
+      <c r="G331" s="4">
+        <v>0.09983766233766245</v>
+      </c>
+      <c r="H331" s="4">
+        <v>0.10689717727840223</v>
+      </c>
+      <c r="I331" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J331" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 奥赛康（002755）归入“创新药+抗感染药+肿瘤管线”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K331" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.4 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L331" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B332" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C332" s="0">
+        <v>27</v>
+      </c>
+      <c r="D332" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001318</t>
+        </is>
+      </c>
+      <c r="E332" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">阳光乳业</t>
+        </is>
+      </c>
+      <c r="F332" s="0">
+        <v>13.04</v>
+      </c>
+      <c r="G332" s="4">
+        <v>0.10042194092827007</v>
+      </c>
+      <c r="H332" s="4">
+        <v>0.10502346106856535</v>
+      </c>
+      <c r="I332" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J332" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 阳光乳业（001318）归入“乳业+低温乳品+冷链物流”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K332" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.0 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L332" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B333" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C333" s="0">
+        <v>28</v>
+      </c>
+      <c r="D333" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000692</t>
+        </is>
+      </c>
+      <c r="E333" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">惠天热电</t>
+        </is>
+      </c>
+      <c r="F333" s="0">
+        <v>4.59</v>
+      </c>
+      <c r="G333" s="4">
+        <v>0.10071942446043171</v>
+      </c>
+      <c r="H333" s="4">
+        <v>0.10151623589770742</v>
+      </c>
+      <c r="I333" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J333" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 惠天热电（000692）归入“供热+风电+供热工程”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K333" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.3 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L333" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B334" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C334" s="0">
+        <v>29</v>
+      </c>
+      <c r="D334" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600072</t>
+        </is>
+      </c>
+      <c r="E334" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中船科技</t>
+        </is>
+      </c>
+      <c r="F334" s="0">
+        <v>9.7</v>
+      </c>
+      <c r="G334" s="4">
+        <v>0.09977324263038545</v>
+      </c>
+      <c r="H334" s="4">
+        <v>0.0991227800701282</v>
+      </c>
+      <c r="I334" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J334" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 中船科技（600072）归入“风电主机+绿色燃料+中船系”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K334" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L334" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B335" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C335" s="0">
+        <v>30</v>
+      </c>
+      <c r="D335" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603590</t>
+        </is>
+      </c>
+      <c r="E335" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">康辰药业</t>
+        </is>
+      </c>
+      <c r="F335" s="0">
+        <v>32.11</v>
+      </c>
+      <c r="G335" s="4">
+        <v>0.10003425830763944</v>
+      </c>
+      <c r="H335" s="4">
+        <v>0.0982536995072766</v>
+      </c>
+      <c r="I335" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J335" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 康辰药业（603590）归入“创新药+血凝酶+肿瘤管线+业绩增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K335" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.5 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L335" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B336" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C336" s="0">
+        <v>31</v>
+      </c>
+      <c r="D336" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603185</t>
+        </is>
+      </c>
+      <c r="E336" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">弘元绿能</t>
+        </is>
+      </c>
+      <c r="F336" s="0">
+        <v>15.15</v>
+      </c>
+      <c r="G336" s="4">
+        <v>0.1002178649237473</v>
+      </c>
+      <c r="H336" s="4">
+        <v>0.09526733560407744</v>
+      </c>
+      <c r="I336" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J336" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 弘元绿能（603185）归入“硅料硅片+光伏一体化+TOPCon组件+高端装备”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K336" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.4 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L336" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B337" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C337" s="0">
+        <v>32</v>
+      </c>
+      <c r="D337" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002041</t>
+        </is>
+      </c>
+      <c r="E337" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">登海种业</t>
+        </is>
+      </c>
+      <c r="F337" s="0">
+        <v>10.23</v>
+      </c>
+      <c r="G337" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H337" s="4">
+        <v>0.0895339492614325</v>
+      </c>
+      <c r="I337" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J337" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 登海种业（002041）归入“玉米种业+转基因玉米+业绩增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K337" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.7 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L337" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B338" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C338" s="0">
+        <v>33</v>
+      </c>
+      <c r="D338" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603906</t>
+        </is>
+      </c>
+      <c r="E338" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">龙蟠科技</t>
+        </is>
+      </c>
+      <c r="F338" s="0">
+        <v>19.04</v>
+      </c>
+      <c r="G338" s="4">
+        <v>0.09994222992489889</v>
+      </c>
+      <c r="H338" s="4">
+        <v>0.08883285011191144</v>
+      </c>
+      <c r="I338" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J338" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 龙蟠科技（603906）归入“磷酸铁锂+固态电池材料+液冷+半年报扭亏”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K338" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.8 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L338" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B339" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C339" s="0">
+        <v>34</v>
+      </c>
+      <c r="D339" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002226</t>
+        </is>
+      </c>
+      <c r="E339" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">江南化工</t>
+        </is>
+      </c>
+      <c r="F339" s="0">
+        <v>5.34</v>
+      </c>
+      <c r="G339" s="4">
+        <v>0.10103092783505163</v>
+      </c>
+      <c r="H339" s="4">
+        <v>0.08834417784933744</v>
+      </c>
+      <c r="I339" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J339" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 江南化工（002226）归入“风电+民爆重组+西藏民爆”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K339" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.0 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L339" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B340" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C340" s="0">
+        <v>35</v>
+      </c>
+      <c r="D340" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002419</t>
+        </is>
+      </c>
+      <c r="E340" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天虹股份</t>
+        </is>
+      </c>
+      <c r="F340" s="0">
+        <v>5.09</v>
+      </c>
+      <c r="G340" s="4">
+        <v>0.09935205183585305</v>
+      </c>
+      <c r="H340" s="4">
+        <v>0.08300889620926664</v>
+      </c>
+      <c r="I340" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J340" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 天虹股份（002419）归入“资产出售+AI应用+零售调改”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K340" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.3 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L340" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B341" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C341" s="0">
+        <v>36</v>
+      </c>
+      <c r="D341" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605287</t>
+        </is>
+      </c>
+      <c r="E341" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">德才股份</t>
+        </is>
+      </c>
+      <c r="F341" s="0">
+        <v>37.39</v>
+      </c>
+      <c r="G341" s="4">
+        <v>0.10002942041776987</v>
+      </c>
+      <c r="H341" s="4">
+        <v>0.08230356985336675</v>
+      </c>
+      <c r="I341" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J341" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 德才股份（605287）归入“AI漫剧+火山引擎合作+建筑装饰”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K341" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.4 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L341" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B342" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C342" s="0">
+        <v>37</v>
+      </c>
+      <c r="D342" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603919</t>
+        </is>
+      </c>
+      <c r="E342" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金徽酒</t>
+        </is>
+      </c>
+      <c r="F342" s="0">
+        <v>17.4</v>
+      </c>
+      <c r="G342" s="4">
+        <v>0.09987357774968375</v>
+      </c>
+      <c r="H342" s="4">
+        <v>0.07902202869997625</v>
+      </c>
+      <c r="I342" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J342" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 金徽酒（603919）归入“白酒+全国化扩张+产品升级”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K342" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.5 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L342" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B343" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C343" s="0">
+        <v>38</v>
+      </c>
+      <c r="D343" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600131</t>
+        </is>
+      </c>
+      <c r="E343" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">国网信通</t>
+        </is>
+      </c>
+      <c r="F343" s="0">
+        <v>15.39</v>
+      </c>
+      <c r="G343" s="4">
+        <v>0.10007147962830597</v>
+      </c>
+      <c r="H343" s="4">
+        <v>0.07721722687622024</v>
+      </c>
+      <c r="I343" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J343" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 国网信通（600131）归入“电力人工智能+能源数字化+股份划转完成”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K343" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.1 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 49 家涨停，其中首板 38 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L343" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M73"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -20188,6 +22240,596 @@
       <c r="M63" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">11.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B64" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C64" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D64" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601238</t>
+        </is>
+      </c>
+      <c r="E64" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">广汽集团</t>
+        </is>
+      </c>
+      <c r="F64" s="4">
+        <v>0.3998428659240021</v>
+      </c>
+      <c r="G64" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H64" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="I64" s="4">
+        <v>0.04285714285714293</v>
+      </c>
+      <c r="J64" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K64" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +4.29%</t>
+        </is>
+      </c>
+      <c r="L64" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M64" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B65" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C65" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D65" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605303</t>
+        </is>
+      </c>
+      <c r="E65" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">园林股份</t>
+        </is>
+      </c>
+      <c r="F65" s="4">
+        <v>0.36542213410613905</v>
+      </c>
+      <c r="G65" s="4">
+        <v>0.10019193857965458</v>
+      </c>
+      <c r="H65" s="4">
+        <v>0.10019193857965458</v>
+      </c>
+      <c r="I65" s="4">
+        <v>0.10019193857965458</v>
+      </c>
+      <c r="J65" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K65" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +10.02%</t>
+        </is>
+      </c>
+      <c r="L65" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M65" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.66</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B66" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C66" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="D66" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603636</t>
+        </is>
+      </c>
+      <c r="E66" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南威软件</t>
+        </is>
+      </c>
+      <c r="F66" s="4">
+        <v>0.17017701435935537</v>
+      </c>
+      <c r="G66" s="4">
+        <v>0.02668360864040653</v>
+      </c>
+      <c r="H66" s="4">
+        <v>0.04193138500635318</v>
+      </c>
+      <c r="I66" s="4">
+        <v>-0.02541296060991105</v>
+      </c>
+      <c r="J66" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K66" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -2.54%</t>
+        </is>
+      </c>
+      <c r="L66" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M66" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B67" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C67" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="D67" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000823</t>
+        </is>
+      </c>
+      <c r="E67" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">超声电子</t>
+        </is>
+      </c>
+      <c r="F67" s="4">
+        <v>0.15747604530021253</v>
+      </c>
+      <c r="G67" s="4">
+        <v>0.004098360655737654</v>
+      </c>
+      <c r="H67" s="4">
+        <v>0.00819672131147553</v>
+      </c>
+      <c r="I67" s="4">
+        <v>-0.04590163934426217</v>
+      </c>
+      <c r="J67" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K67" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -4.59%</t>
+        </is>
+      </c>
+      <c r="L67" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M67" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B68" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C68" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="D68" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601811</t>
+        </is>
+      </c>
+      <c r="E68" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新华文轩</t>
+        </is>
+      </c>
+      <c r="F68" s="4">
+        <v>0.15645848508023655</v>
+      </c>
+      <c r="G68" s="4">
+        <v>-0.01816396661757491</v>
+      </c>
+      <c r="H68" s="4">
+        <v>0.09474717722140391</v>
+      </c>
+      <c r="I68" s="4">
+        <v>0.036818851251841034</v>
+      </c>
+      <c r="J68" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K68" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +3.68%</t>
+        </is>
+      </c>
+      <c r="L68" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M68" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B69" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C69" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="D69" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605058</t>
+        </is>
+      </c>
+      <c r="E69" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">澳弘电子</t>
+        </is>
+      </c>
+      <c r="F69" s="4">
+        <v>0.15301046582118683</v>
+      </c>
+      <c r="G69" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H69" s="4">
+        <v>0.006711409395973034</v>
+      </c>
+      <c r="I69" s="4">
+        <v>-0.09999999999999998</v>
+      </c>
+      <c r="J69" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K69" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -10.00%</t>
+        </is>
+      </c>
+      <c r="L69" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M69" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">53.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B70" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C70" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="D70" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000607</t>
+        </is>
+      </c>
+      <c r="E70" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华媒控股</t>
+        </is>
+      </c>
+      <c r="F70" s="4">
+        <v>0.15145502144939724</v>
+      </c>
+      <c r="G70" s="4">
+        <v>-0.024213075060532607</v>
+      </c>
+      <c r="H70" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I70" s="4">
+        <v>-0.041162227602905554</v>
+      </c>
+      <c r="J70" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K70" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -4.12%</t>
+        </is>
+      </c>
+      <c r="L70" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M70" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.96</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B71" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C71" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="D71" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000002</t>
+        </is>
+      </c>
+      <c r="E71" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">万 科Ａ</t>
+        </is>
+      </c>
+      <c r="F71" s="4">
+        <v>0.1489633983079168</v>
+      </c>
+      <c r="G71" s="4">
+        <v>-0.06862745098039225</v>
+      </c>
+      <c r="H71" s="4">
+        <v>0.07843137254901977</v>
+      </c>
+      <c r="I71" s="4">
+        <v>0.04411764705882337</v>
+      </c>
+      <c r="J71" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K71" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +4.41%</t>
+        </is>
+      </c>
+      <c r="L71" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M71" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B72" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C72" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="D72" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600325</t>
+        </is>
+      </c>
+      <c r="E72" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华发股份</t>
+        </is>
+      </c>
+      <c r="F72" s="4">
+        <v>0.14175137906615248</v>
+      </c>
+      <c r="G72" s="4">
+        <v>-0.013559322033898313</v>
+      </c>
+      <c r="H72" s="4">
+        <v>0.006779661016949268</v>
+      </c>
+      <c r="I72" s="4">
+        <v>-0.01016949152542379</v>
+      </c>
+      <c r="J72" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K72" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -1.02%</t>
+        </is>
+      </c>
+      <c r="L72" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M72" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="B73" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="C73" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="D73" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002913</t>
+        </is>
+      </c>
+      <c r="E73" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奥士康</t>
+        </is>
+      </c>
+      <c r="F73" s="4">
+        <v>0.14000022186122588</v>
+      </c>
+      <c r="G73" s="4">
+        <v>0.04095300834431281</v>
+      </c>
+      <c r="H73" s="4">
+        <v>0.07795344751866495</v>
+      </c>
+      <c r="I73" s="4">
+        <v>0.013394817742643728</v>
+      </c>
+      <c r="J73" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K73" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +1.34%</t>
+        </is>
+      </c>
+      <c r="L73" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M73" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92.3</t>
         </is>
       </c>
     </row>
@@ -20279,28 +22921,28 @@
         </is>
       </c>
       <c r="B3" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" s="0">
         <v>2</v>
       </c>
       <c r="E3" s="4">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="F3" s="4">
-        <v>0.25</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="G3" s="0">
-        <v>1.3333333333333333</v>
+        <v>2.0</v>
       </c>
       <c r="H3" s="0">
         <v>2</v>
       </c>
       <c r="I3" s="4">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="4">
@@ -20310,28 +22952,28 @@
         </is>
       </c>
       <c r="B4" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="0">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D4" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" s="4">
         <v>0.3333333333333333</v>
       </c>
       <c r="F4" s="4">
-        <v>0.25</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="G4" s="0">
-        <v>1.3333333333333333</v>
+        <v>2.3333333333333335</v>
       </c>
       <c r="H4" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I4" s="4">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="5">
@@ -20341,28 +22983,28 @@
         </is>
       </c>
       <c r="B5" s="0">
+        <v>7</v>
+      </c>
+      <c r="C5" s="0">
+        <v>42</v>
+      </c>
+      <c r="D5" s="0">
+        <v>13</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0.30952380952380953</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="G5" s="0">
+        <v>2.166666666666667</v>
+      </c>
+      <c r="H5" s="0">
         <v>6</v>
       </c>
-      <c r="C5" s="0">
-        <v>36</v>
-      </c>
-      <c r="D5" s="0">
-        <v>12</v>
-      </c>
-      <c r="E5" s="4">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="F5" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="G5" s="0">
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="H5" s="0">
-        <v>5</v>
-      </c>
       <c r="I5" s="4">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="6">
@@ -20372,28 +23014,28 @@
         </is>
       </c>
       <c r="B6" s="0">
+        <v>7</v>
+      </c>
+      <c r="C6" s="0">
+        <v>70</v>
+      </c>
+      <c r="D6" s="0">
+        <v>18</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0.2571428571428571</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="G6" s="0">
+        <v>1.7999999999999998</v>
+      </c>
+      <c r="H6" s="0">
         <v>6</v>
       </c>
-      <c r="C6" s="0">
-        <v>60</v>
-      </c>
-      <c r="D6" s="0">
-        <v>17</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0.2833333333333333</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="G6" s="0">
-        <v>1.1333333333333333</v>
-      </c>
-      <c r="H6" s="0">
-        <v>5</v>
-      </c>
       <c r="I6" s="4">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="7">

--- a/docs/downloads/latest.xlsx
+++ b/docs/downloads/latest.xlsx
@@ -16550,7 +16550,7 @@
         <v>0.0998227997637331</v>
       </c>
       <c r="H306" s="4">
-        <v>0.2534808383755009</v>
+        <v>0.2531984616723712</v>
       </c>
       <c r="I306" s="0" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>0.10017271157167527</v>
       </c>
       <c r="H307" s="4">
-        <v>0.25281070521125687</v>
+        <v>0.25252882250287984</v>
       </c>
       <c r="I307" s="0" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>0.10041493775933595</v>
       </c>
       <c r="H308" s="4">
-        <v>0.1821818877553951</v>
+        <v>0.18195957801753443</v>
       </c>
       <c r="I308" s="0" t="inlineStr">
         <is>
@@ -16712,7 +16712,7 @@
         <v>0.10008857395925608</v>
       </c>
       <c r="H309" s="4">
-        <v>0.18182410134085636</v>
+        <v>0.18160213124780664</v>
       </c>
       <c r="I309" s="0" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>0.10036275695284157</v>
       </c>
       <c r="H310" s="4">
-        <v>0.180071742795729</v>
+        <v>0.1798514417197831</v>
       </c>
       <c r="I310" s="0" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>0.10020242914979738</v>
       </c>
       <c r="H311" s="4">
-        <v>0.17880618320808775</v>
+        <v>0.17858709319562907</v>
       </c>
       <c r="I311" s="0" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>0.10044843049327357</v>
       </c>
       <c r="H312" s="4">
-        <v>0.17040237956161344</v>
+        <v>0.1701914526063405</v>
       </c>
       <c r="I312" s="0" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>0.10000000000000009</v>
       </c>
       <c r="H313" s="4">
-        <v>0.1616046093658782</v>
+        <v>0.16140245372896947</v>
       </c>
       <c r="I313" s="0" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>0.0998080614203456</v>
       </c>
       <c r="H314" s="4">
-        <v>0.16099975536391362</v>
+        <v>0.1607982112395598</v>
       </c>
       <c r="I314" s="0" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
         <v>0.10010881392818272</v>
       </c>
       <c r="H315" s="4">
-        <v>0.1520921357706909</v>
+        <v>0.15189972362268037</v>
       </c>
       <c r="I315" s="0" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>0.10000000000000009</v>
       </c>
       <c r="H316" s="4">
-        <v>0.13957410698688955</v>
+        <v>0.1393949279145532</v>
       </c>
       <c r="I316" s="0" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>0.09965635738831624</v>
       </c>
       <c r="H317" s="4">
-        <v>0.13161481152665738</v>
+        <v>0.13144428930945687</v>
       </c>
       <c r="I317" s="0" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>0.10000000000000009</v>
       </c>
       <c r="H318" s="4">
-        <v>0.13087850175445917</v>
+        <v>0.13070878992012533</v>
       </c>
       <c r="I318" s="0" t="inlineStr">
         <is>
@@ -17252,7 +17252,7 @@
         <v>0.09991742361684564</v>
       </c>
       <c r="H319" s="4">
-        <v>0.12891765626062643</v>
+        <v>0.12875011041566564</v>
       </c>
       <c r="I319" s="0" t="inlineStr">
         <is>
@@ -17306,7 +17306,7 @@
         <v>0.10016835016835014</v>
       </c>
       <c r="H320" s="4">
-        <v>0.126950628697666</v>
+        <v>0.1267852671855112</v>
       </c>
       <c r="I320" s="0" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>0.10003847633705278</v>
       </c>
       <c r="H321" s="4">
-        <v>0.12286903470293435</v>
+        <v>0.12270824248716977</v>
       </c>
       <c r="I321" s="0" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>0.09995537706381065</v>
       </c>
       <c r="H322" s="4">
-        <v>0.12171708481000572</v>
+        <v>0.12155759117320847</v>
       </c>
       <c r="I322" s="0" t="inlineStr">
         <is>
@@ -17468,7 +17468,7 @@
         <v>0.09989701338825929</v>
       </c>
       <c r="H323" s="4">
-        <v>0.11916071967796997</v>
+        <v>0.11900412192769391</v>
       </c>
       <c r="I323" s="0" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>0.09979633401221989</v>
       </c>
       <c r="H324" s="4">
-        <v>0.11782513734150028</v>
+        <v>0.11767006030416122</v>
       </c>
       <c r="I324" s="0" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         <v>0.10022909507445599</v>
       </c>
       <c r="H325" s="4">
-        <v>0.11606993835149837</v>
+        <v>0.11591686789306037</v>
       </c>
       <c r="I325" s="0" t="inlineStr">
         <is>
@@ -17630,7 +17630,7 @@
         <v>0.09941176470588253</v>
       </c>
       <c r="H326" s="4">
-        <v>0.11595904258359595</v>
+        <v>0.1158060992118311</v>
       </c>
       <c r="I326" s="0" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>0.10000000000000009</v>
       </c>
       <c r="H327" s="4">
-        <v>0.11555601802652743</v>
+        <v>0.11540353683001435</v>
       </c>
       <c r="I327" s="0" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>0.09990749306197966</v>
       </c>
       <c r="H328" s="4">
-        <v>0.11263144890824388</v>
+        <v>0.11248233601359192</v>
       </c>
       <c r="I328" s="0" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         <v>0.10000000000000009</v>
       </c>
       <c r="H329" s="4">
-        <v>0.11262637919183865</v>
+        <v>0.11247727215824357</v>
       </c>
       <c r="I329" s="0" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>0.1003134796238243</v>
       </c>
       <c r="H330" s="4">
-        <v>0.1073299776197685</v>
+        <v>0.10718703555490533</v>
       </c>
       <c r="I330" s="0" t="inlineStr">
         <is>
@@ -17900,7 +17900,7 @@
         <v>0.09983766233766245</v>
       </c>
       <c r="H331" s="4">
-        <v>0.10689717727840223</v>
+        <v>0.10675474268472603</v>
       </c>
       <c r="I331" s="0" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         <v>0.10042194092827007</v>
       </c>
       <c r="H332" s="4">
-        <v>0.10502346106856535</v>
+        <v>0.10488322990267397</v>
       </c>
       <c r="I332" s="0" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>0.10071942446043171</v>
       </c>
       <c r="H333" s="4">
-        <v>0.10151623589770742</v>
+        <v>0.10138015723425262</v>
       </c>
       <c r="I333" s="0" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
         <v>0.09977324263038545</v>
       </c>
       <c r="H334" s="4">
-        <v>0.0991227800701282</v>
+        <v>0.09898955626810614</v>
       </c>
       <c r="I334" s="0" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
         <v>0.10003425830763944</v>
       </c>
       <c r="H335" s="4">
-        <v>0.0982536995072766</v>
+        <v>0.09812151655054399</v>
       </c>
       <c r="I335" s="0" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>0.1002178649237473</v>
       </c>
       <c r="H336" s="4">
-        <v>0.09526733560407744</v>
+        <v>0.09513874639181483</v>
       </c>
       <c r="I336" s="0" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         <v>0.09999999999999985</v>
       </c>
       <c r="H337" s="4">
-        <v>0.0895339492614325</v>
+        <v>0.08941233401356255</v>
       </c>
       <c r="I337" s="0" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>0.09994222992489889</v>
       </c>
       <c r="H338" s="4">
-        <v>0.08883285011191144</v>
+        <v>0.08871209438758175</v>
       </c>
       <c r="I338" s="0" t="inlineStr">
         <is>
@@ -18332,7 +18332,7 @@
         <v>0.10103092783505163</v>
       </c>
       <c r="H339" s="4">
-        <v>0.08834417784933744</v>
+        <v>0.08822402208679331</v>
       </c>
       <c r="I339" s="0" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>0.09935205183585305</v>
       </c>
       <c r="H340" s="4">
-        <v>0.08300889620926664</v>
+        <v>0.08289533707704207</v>
       </c>
       <c r="I340" s="0" t="inlineStr">
         <is>
@@ -18440,7 +18440,7 @@
         <v>0.10002942041776987</v>
       </c>
       <c r="H341" s="4">
-        <v>0.08230356985336675</v>
+        <v>0.08219088914671045</v>
       </c>
       <c r="I341" s="0" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>0.09987357774968375</v>
       </c>
       <c r="H342" s="4">
-        <v>0.07902202869997625</v>
+        <v>0.07891345437495695</v>
       </c>
       <c r="I342" s="0" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>0.10007147962830597</v>
       </c>
       <c r="H343" s="4">
-        <v>0.07721722687622024</v>
+        <v>0.07711092468169133</v>
       </c>
       <c r="I343" s="0" t="inlineStr">
         <is>

--- a/docs/downloads/latest.xlsx
+++ b/docs/downloads/latest.xlsx
@@ -93,7 +93,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L343"/>
+  <dimension ref="A1:L372"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -18571,13 +18571,1579 @@
         </is>
       </c>
     </row>
+    <row r="344">
+      <c r="A344" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B344" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C344" s="0">
+        <v>1</v>
+      </c>
+      <c r="D344" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600812</t>
+        </is>
+      </c>
+      <c r="E344" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华北制药</t>
+        </is>
+      </c>
+      <c r="F344" s="0">
+        <v>5.48</v>
+      </c>
+      <c r="G344" s="4">
+        <v>0.10040160642570273</v>
+      </c>
+      <c r="H344" s="4">
+        <v>0.3070699843902628</v>
+      </c>
+      <c r="I344" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J344" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华北制药（600812）归入“鼠疫+抗生素+创新药+集采”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K344" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 10.0%）。截至运行时成交量约为20日均量的 1.9 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 39 家涨停，其中首板 29 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L344" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B345" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C345" s="0">
+        <v>2</v>
+      </c>
+      <c r="D345" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603073</t>
+        </is>
+      </c>
+      <c r="E345" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">彩蝶实业</t>
+        </is>
+      </c>
+      <c r="F345" s="0">
+        <v>22.97</v>
+      </c>
+      <c r="G345" s="4">
+        <v>0.10009578544061304</v>
+      </c>
+      <c r="H345" s="4">
+        <v>0.1663143750377855</v>
+      </c>
+      <c r="I345" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J345" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 彩蝶实业（603073）归入“涤纶面料+功能性面料+埃及产能”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K345" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 5.1 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 39 家涨停，其中首板 29 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L345" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B346" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C346" s="0">
+        <v>3</v>
+      </c>
+      <c r="D346" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002774</t>
+        </is>
+      </c>
+      <c r="E346" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">快意电梯</t>
+        </is>
+      </c>
+      <c r="F346" s="0">
+        <v>19.04</v>
+      </c>
+      <c r="G346" s="4">
+        <v>0.09994222992489889</v>
+      </c>
+      <c r="H346" s="4">
+        <v>0.16450409509853967</v>
+      </c>
+      <c r="I346" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J346" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 快意电梯（002774）归入“旧梯更新+海外电梯+高速电梯”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K346" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.6 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 39 家涨停，其中首板 29 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L346" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B347" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C347" s="0">
+        <v>4</v>
+      </c>
+      <c r="D347" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600026</t>
+        </is>
+      </c>
+      <c r="E347" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中远海能</t>
+        </is>
+      </c>
+      <c r="F347" s="0">
+        <v>22.62</v>
+      </c>
+      <c r="G347" s="4">
+        <v>0.10019455252918297</v>
+      </c>
+      <c r="H347" s="4">
+        <v>0.16172007665372992</v>
+      </c>
+      <c r="I347" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J347" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 中远海能（600026）归入“油运景气+LNG运输+上海LNG增资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K347" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.5 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 39 家涨停，其中首板 29 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L347" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B348" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C348" s="0">
+        <v>5</v>
+      </c>
+      <c r="D348" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601956</t>
+        </is>
+      </c>
+      <c r="E348" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东贝集团</t>
+        </is>
+      </c>
+      <c r="F348" s="0">
+        <v>5.52</v>
+      </c>
+      <c r="G348" s="4">
+        <v>0.09960159362549792</v>
+      </c>
+      <c r="H348" s="4">
+        <v>0.1445400213740262</v>
+      </c>
+      <c r="I348" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J348" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 东贝集团（601956）归入“制冷压缩机+机器人电机+高效变频”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K348" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.8 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 39 家涨停，其中首板 29 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L348" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B349" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C349" s="0">
+        <v>6</v>
+      </c>
+      <c r="D349" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002869</t>
+        </is>
+      </c>
+      <c r="E349" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金溢科技</t>
+        </is>
+      </c>
+      <c r="F349" s="0">
+        <v>19.14</v>
+      </c>
+      <c r="G349" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H349" s="4">
+        <v>0.1411004859874679</v>
+      </c>
+      <c r="I349" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J349" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 金溢科技（002869）归入“车路协同+电子收费+低空智联”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K349" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 39 家涨停，其中首板 29 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L349" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B350" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C350" s="0">
+        <v>7</v>
+      </c>
+      <c r="D350" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002687</t>
+        </is>
+      </c>
+      <c r="E350" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">乔治白</t>
+        </is>
+      </c>
+      <c r="F350" s="0">
+        <v>6.14</v>
+      </c>
+      <c r="G350" s="4">
+        <v>0.10035842293906792</v>
+      </c>
+      <c r="H350" s="4">
+        <v>0.13926416884083795</v>
+      </c>
+      <c r="I350" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J350" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 乔治白（002687）归入“职业装+校服+通勤服”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K350" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 39 家涨停，其中首板 29 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L350" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B351" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C351" s="0">
+        <v>8</v>
+      </c>
+      <c r="D351" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601975</t>
+        </is>
+      </c>
+      <c r="E351" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">招商南油</t>
+        </is>
+      </c>
+      <c r="F351" s="0">
+        <v>4.97</v>
+      </c>
+      <c r="G351" s="4">
+        <v>0.0995575221238938</v>
+      </c>
+      <c r="H351" s="4">
+        <v>0.13805473884436545</v>
+      </c>
+      <c r="I351" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J351" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 招商南油（601975）归入“成品油运输+MR船队+业绩增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K351" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.4 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 39 家涨停，其中首板 29 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L351" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B352" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C352" s="0">
+        <v>9</v>
+      </c>
+      <c r="D352" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002951</t>
+        </is>
+      </c>
+      <c r="E352" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金时科技</t>
+        </is>
+      </c>
+      <c r="F352" s="0">
+        <v>17.17</v>
+      </c>
+      <c r="G352" s="4">
+        <v>0.09993593850096104</v>
+      </c>
+      <c r="H352" s="4">
+        <v>0.1378956851839974</v>
+      </c>
+      <c r="I352" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J352" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 金时科技（002951）归入“超级电容+复合储能+独立储能电站”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K352" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 39 家涨停，其中首板 29 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L352" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B353" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C353" s="0">
+        <v>10</v>
+      </c>
+      <c r="D353" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600617</t>
+        </is>
+      </c>
+      <c r="E353" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">国新能源</t>
+        </is>
+      </c>
+      <c r="F353" s="0">
+        <v>3.74</v>
+      </c>
+      <c r="G353" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H353" s="4">
+        <v>0.13339166666491956</v>
+      </c>
+      <c r="I353" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J353" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 国新能源（600617）归入“天然气管网+新能源+业绩增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K353" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.5 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 39 家涨停，其中首板 29 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L353" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B354" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C354" s="0">
+        <v>11</v>
+      </c>
+      <c r="D354" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001300</t>
+        </is>
+      </c>
+      <c r="E354" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">三柏硕</t>
+        </is>
+      </c>
+      <c r="F354" s="0">
+        <v>13.51</v>
+      </c>
+      <c r="G354" s="4">
+        <v>0.10016286644951133</v>
+      </c>
+      <c r="H354" s="4">
+        <v>0.12959731457972476</v>
+      </c>
+      <c r="I354" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J354" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 三柏硕（001300）归入“蹦床+健身器材+外销”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K354" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 39 家涨停，其中首板 29 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L354" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B355" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C355" s="0">
+        <v>12</v>
+      </c>
+      <c r="D355" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605378</t>
+        </is>
+      </c>
+      <c r="E355" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">野马电池</t>
+        </is>
+      </c>
+      <c r="F355" s="0">
+        <v>17.27</v>
+      </c>
+      <c r="G355" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H355" s="4">
+        <v>0.12856976686596705</v>
+      </c>
+      <c r="I355" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J355" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 野马电池（605378）归入“锌锰电池+锂电池+海外基地”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K355" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.9 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 39 家涨停，其中首板 29 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L355" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B356" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C356" s="0">
+        <v>13</v>
+      </c>
+      <c r="D356" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000869</t>
+        </is>
+      </c>
+      <c r="E356" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">张 裕Ａ</t>
+        </is>
+      </c>
+      <c r="F356" s="0">
+        <v>18.76</v>
+      </c>
+      <c r="G356" s="4">
+        <v>0.10029325513196487</v>
+      </c>
+      <c r="H356" s="4">
+        <v>0.12156633018866617</v>
+      </c>
+      <c r="I356" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J356" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 张 裕Ａ（000869）归入“葡萄酒+营收增长+回购注销”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K356" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.0 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 39 家涨停，其中首板 29 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L356" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B357" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C357" s="0">
+        <v>14</v>
+      </c>
+      <c r="D357" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600400</t>
+        </is>
+      </c>
+      <c r="E357" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">红豆股份</t>
+        </is>
+      </c>
+      <c r="F357" s="0">
+        <v>3.62</v>
+      </c>
+      <c r="G357" s="4">
+        <v>0.10030395136778125</v>
+      </c>
+      <c r="H357" s="4">
+        <v>0.12014280315107088</v>
+      </c>
+      <c r="I357" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J357" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 红豆股份（600400）归入“牛散持股+服装+养老机器人”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K357" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.5 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 39 家涨停，其中首板 29 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L357" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B358" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C358" s="0">
+        <v>15</v>
+      </c>
+      <c r="D358" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002702</t>
+        </is>
+      </c>
+      <c r="E358" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">海欣食品</t>
+        </is>
+      </c>
+      <c r="F358" s="0">
+        <v>5.92</v>
+      </c>
+      <c r="G358" s="4">
+        <v>0.1003717472118959</v>
+      </c>
+      <c r="H358" s="4">
+        <v>0.11962496053437896</v>
+      </c>
+      <c r="I358" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J358" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 海欣食品（002702）归入“速冻食品+山姆渠道+营收增长+海峡两岸”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K358" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 39 家涨停，其中首板 29 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L358" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B359" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C359" s="0">
+        <v>16</v>
+      </c>
+      <c r="D359" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001336</t>
+        </is>
+      </c>
+      <c r="E359" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">楚环科技</t>
+        </is>
+      </c>
+      <c r="F359" s="0">
+        <v>20.65</v>
+      </c>
+      <c r="G359" s="4">
+        <v>0.10015982951518376</v>
+      </c>
+      <c r="H359" s="4">
+        <v>0.11723782034453822</v>
+      </c>
+      <c r="I359" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J359" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 楚环科技（001336）归入“废气治理+半导体环保+航空航天投资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K359" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.4 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 39 家涨停，其中首板 29 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L359" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B360" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C360" s="0">
+        <v>17</v>
+      </c>
+      <c r="D360" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002565</t>
+        </is>
+      </c>
+      <c r="E360" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">顺灏股份</t>
+        </is>
+      </c>
+      <c r="F360" s="0">
+        <v>9.28</v>
+      </c>
+      <c r="G360" s="4">
+        <v>0.09952606635071092</v>
+      </c>
+      <c r="H360" s="4">
+        <v>0.11558924930574901</v>
+      </c>
+      <c r="I360" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J360" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 顺灏股份（002565）归入“太空算力+新型烟草+环保包装”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K360" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.2 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 39 家涨停，其中首板 29 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L360" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B361" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C361" s="0">
+        <v>18</v>
+      </c>
+      <c r="D361" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600722</t>
+        </is>
+      </c>
+      <c r="E361" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金牛化工</t>
+        </is>
+      </c>
+      <c r="F361" s="0">
+        <v>16.19</v>
+      </c>
+      <c r="G361" s="4">
+        <v>0.0998641304347827</v>
+      </c>
+      <c r="H361" s="4">
+        <v>0.11478081811952483</v>
+      </c>
+      <c r="I361" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J361" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 金牛化工（600722）归入“甲醇+甲醇价格+风电项目”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K361" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.7 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 39 家涨停，其中首板 29 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L361" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B362" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C362" s="0">
+        <v>19</v>
+      </c>
+      <c r="D362" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600408</t>
+        </is>
+      </c>
+      <c r="E362" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">安泰集团</t>
+        </is>
+      </c>
+      <c r="F362" s="0">
+        <v>3.44</v>
+      </c>
+      <c r="G362" s="4">
+        <v>0.09904153354632594</v>
+      </c>
+      <c r="H362" s="4">
+        <v>0.11435186006576759</v>
+      </c>
+      <c r="I362" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J362" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 安泰集团（600408）归入“焦炭+型钢+受托加工”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K362" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 39 家涨停，其中首板 29 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L362" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B363" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C363" s="0">
+        <v>20</v>
+      </c>
+      <c r="D363" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600310</t>
+        </is>
+      </c>
+      <c r="E363" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">广西能源</t>
+        </is>
+      </c>
+      <c r="F363" s="0">
+        <v>4.97</v>
+      </c>
+      <c r="G363" s="4">
+        <v>0.0995575221238938</v>
+      </c>
+      <c r="H363" s="4">
+        <v>0.11176242100439186</v>
+      </c>
+      <c r="I363" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J363" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 广西能源（600310）归入“电力主业+业绩扭亏+抽水蓄能”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K363" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 39 家涨停，其中首板 29 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L363" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B364" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C364" s="0">
+        <v>21</v>
+      </c>
+      <c r="D364" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600513</t>
+        </is>
+      </c>
+      <c r="E364" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">联环药业</t>
+        </is>
+      </c>
+      <c r="F364" s="0">
+        <v>16.6</v>
+      </c>
+      <c r="G364" s="4">
+        <v>0.10006626905235262</v>
+      </c>
+      <c r="H364" s="4">
+        <v>0.11002682074944709</v>
+      </c>
+      <c r="I364" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J364" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 联环药业（600513）归入““超级细菌”+创新药+仿创结合”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K364" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 5.2 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 39 家涨停，其中首板 29 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L364" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B365" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C365" s="0">
+        <v>22</v>
+      </c>
+      <c r="D365" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603863</t>
+        </is>
+      </c>
+      <c r="E365" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">松炀资源</t>
+        </is>
+      </c>
+      <c r="F365" s="0">
+        <v>13.62</v>
+      </c>
+      <c r="G365" s="4">
+        <v>0.10016155088852985</v>
+      </c>
+      <c r="H365" s="4">
+        <v>0.10874879468075957</v>
+      </c>
+      <c r="I365" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J365" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 松炀资源（603863）归入“高强瓦楞纸+主业调整+业绩减亏”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K365" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 39 家涨停，其中首板 29 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L365" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B366" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C366" s="0">
+        <v>23</v>
+      </c>
+      <c r="D366" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002805</t>
+        </is>
+      </c>
+      <c r="E366" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">丰元股份</t>
+        </is>
+      </c>
+      <c r="F366" s="0">
+        <v>17.67</v>
+      </c>
+      <c r="G366" s="4">
+        <v>0.10024906600249084</v>
+      </c>
+      <c r="H366" s="4">
+        <v>0.10814263397268466</v>
+      </c>
+      <c r="I366" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J366" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 丰元股份（002805）归入“磷酸铁锂+固态电池+产能扩张”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K366" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.6 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 39 家涨停，其中首板 29 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L366" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B367" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C367" s="0">
+        <v>24</v>
+      </c>
+      <c r="D367" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002733</t>
+        </is>
+      </c>
+      <c r="E367" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雄韬股份</t>
+        </is>
+      </c>
+      <c r="F367" s="0">
+        <v>18.89</v>
+      </c>
+      <c r="G367" s="4">
+        <v>0.10017472335468834</v>
+      </c>
+      <c r="H367" s="4">
+        <v>0.10414597478350573</v>
+      </c>
+      <c r="I367" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J367" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 雄韬股份（002733）归入“数据中心UPS+固态电池+锂电池”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K367" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.5 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 39 家涨停，其中首板 29 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L367" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B368" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C368" s="0">
+        <v>25</v>
+      </c>
+      <c r="D368" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603137</t>
+        </is>
+      </c>
+      <c r="E368" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">恒尚节能</t>
+        </is>
+      </c>
+      <c r="F368" s="0">
+        <v>19.56</v>
+      </c>
+      <c r="G368" s="4">
+        <v>0.10011248593925748</v>
+      </c>
+      <c r="H368" s="4">
+        <v>0.0982799234224634</v>
+      </c>
+      <c r="I368" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J368" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 恒尚节能（603137）归入“存储模组+建筑幕墙+光伏幕墙”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K368" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.8 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 39 家涨停，其中首板 29 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L368" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B369" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C369" s="0">
+        <v>26</v>
+      </c>
+      <c r="D369" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603823</t>
+        </is>
+      </c>
+      <c r="E369" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">百合花</t>
+        </is>
+      </c>
+      <c r="F369" s="0">
+        <v>46.59</v>
+      </c>
+      <c r="G369" s="4">
+        <v>0.09856165998585255</v>
+      </c>
+      <c r="H369" s="4">
+        <v>0.09793439763501519</v>
+      </c>
+      <c r="I369" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no_verified_event</t>
+        </is>
+      </c>
+      <c r="J369" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">事件证据层未找到与当日涨停直接匹配的公告或新闻；系统不把概念标签、技术形态或主观猜测当成涨停原因。</t>
+        </is>
+      </c>
+      <c r="K369" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 39 家涨停，其中首板 29 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L369" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B370" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C370" s="0">
+        <v>27</v>
+      </c>
+      <c r="D370" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605298</t>
+        </is>
+      </c>
+      <c r="E370" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">必得科技</t>
+        </is>
+      </c>
+      <c r="F370" s="0">
+        <v>44.97</v>
+      </c>
+      <c r="G370" s="4">
+        <v>0.10004892367906049</v>
+      </c>
+      <c r="H370" s="4">
+        <v>0.0891348693032855</v>
+      </c>
+      <c r="I370" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J370" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 必得科技（605298）归入“轨道交通+半导体注入猜测+股份转让”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K370" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 39 家涨停，其中首板 29 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L370" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B371" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C371" s="0">
+        <v>28</v>
+      </c>
+      <c r="D371" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002490</t>
+        </is>
+      </c>
+      <c r="E371" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">山东墨龙</t>
+        </is>
+      </c>
+      <c r="F371" s="0">
+        <v>7.6</v>
+      </c>
+      <c r="G371" s="4">
+        <v>0.09985528219971052</v>
+      </c>
+      <c r="H371" s="4">
+        <v>0.08419113515405865</v>
+      </c>
+      <c r="I371" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J371" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 山东墨龙（002490）归入“油气装备+海外订单+H股配售”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K371" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 39 家涨停，其中首板 29 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L371" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B372" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C372" s="0">
+        <v>29</v>
+      </c>
+      <c r="D372" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603788</t>
+        </is>
+      </c>
+      <c r="E372" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">宁波高发</t>
+        </is>
+      </c>
+      <c r="F372" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="G372" s="4">
+        <v>0.0997067448680351</v>
+      </c>
+      <c r="H372" s="4">
+        <v>0.06883117970216682</v>
+      </c>
+      <c r="I372" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J372" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 宁波高发（603788）归入“制动踏板+汽车控制系统+摩洛哥基地”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K372" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 7.7 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 39 家涨停，其中首板 29 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L372" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:M83"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -22830,6 +24396,586 @@
       <c r="M73" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">92.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B74" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C74" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D74" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001206</t>
+        </is>
+      </c>
+      <c r="E74" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">依依股份</t>
+        </is>
+      </c>
+      <c r="F74" s="4">
+        <v>0.2531984616723712</v>
+      </c>
+      <c r="G74" s="4">
+        <v>-0.004833512352309333</v>
+      </c>
+      <c r="H74" s="4">
+        <v>0.09022556390977443</v>
+      </c>
+      <c r="I74" s="4">
+        <v>0.027389903329752885</v>
+      </c>
+      <c r="J74" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K74" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +2.74%</t>
+        </is>
+      </c>
+      <c r="L74" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M74" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B75" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C75" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D75" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601118</t>
+        </is>
+      </c>
+      <c r="E75" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">海南橡胶</t>
+        </is>
+      </c>
+      <c r="F75" s="4">
+        <v>0.25252882250287984</v>
+      </c>
+      <c r="G75" s="4">
+        <v>0.020408163265306145</v>
+      </c>
+      <c r="H75" s="4">
+        <v>0.06907378335949765</v>
+      </c>
+      <c r="I75" s="4">
+        <v>0.0219780219780219</v>
+      </c>
+      <c r="J75" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K75" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +2.20%</t>
+        </is>
+      </c>
+      <c r="L75" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M75" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.51</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="D76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002164</t>
+        </is>
+      </c>
+      <c r="E76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">宁波东力</t>
+        </is>
+      </c>
+      <c r="F76" s="4">
+        <v>0.18195957801753443</v>
+      </c>
+      <c r="G76" s="4">
+        <v>-0.02564102564102566</v>
+      </c>
+      <c r="H76" s="4">
+        <v>-0.002262443438914019</v>
+      </c>
+      <c r="I76" s="4">
+        <v>-0.03242835595776772</v>
+      </c>
+      <c r="J76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -3.24%</t>
+        </is>
+      </c>
+      <c r="L76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B77" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C77" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="D77" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000504</t>
+        </is>
+      </c>
+      <c r="E77" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南华生物</t>
+        </is>
+      </c>
+      <c r="F77" s="4">
+        <v>0.18160213124780664</v>
+      </c>
+      <c r="G77" s="4">
+        <v>0.004025764895330131</v>
+      </c>
+      <c r="H77" s="4">
+        <v>0.04669887278582929</v>
+      </c>
+      <c r="I77" s="4">
+        <v>-0.0780998389694042</v>
+      </c>
+      <c r="J77" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K77" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -7.81%</t>
+        </is>
+      </c>
+      <c r="L77" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M77" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B78" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C78" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="D78" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002388</t>
+        </is>
+      </c>
+      <c r="E78" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新亚制程</t>
+        </is>
+      </c>
+      <c r="F78" s="4">
+        <v>0.1798514417197831</v>
+      </c>
+      <c r="G78" s="0"/>
+      <c r="H78" s="0"/>
+      <c r="I78" s="0"/>
+      <c r="J78" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K78" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板</t>
+        </is>
+      </c>
+      <c r="L78" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M78" s="0"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B79" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C79" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="D79" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000710</t>
+        </is>
+      </c>
+      <c r="E79" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">贝瑞基因</t>
+        </is>
+      </c>
+      <c r="F79" s="4">
+        <v>0.17858709319562907</v>
+      </c>
+      <c r="G79" s="4">
+        <v>0.10027598896044165</v>
+      </c>
+      <c r="H79" s="4">
+        <v>0.10027598896044165</v>
+      </c>
+      <c r="I79" s="4">
+        <v>-0.05519779208831643</v>
+      </c>
+      <c r="J79" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K79" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -5.52%</t>
+        </is>
+      </c>
+      <c r="L79" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M79" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.27</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="D80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600059</t>
+        </is>
+      </c>
+      <c r="E80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">古越龙山</t>
+        </is>
+      </c>
+      <c r="F80" s="4">
+        <v>0.1701914526063405</v>
+      </c>
+      <c r="G80" s="4">
+        <v>-0.03178484107579449</v>
+      </c>
+      <c r="H80" s="4">
+        <v>0.032599837000814924</v>
+      </c>
+      <c r="I80" s="4">
+        <v>-0.03178484107579449</v>
+      </c>
+      <c r="J80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -3.18%</t>
+        </is>
+      </c>
+      <c r="L80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B81" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C81" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="D81" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605577</t>
+        </is>
+      </c>
+      <c r="E81" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">龙版传媒</t>
+        </is>
+      </c>
+      <c r="F81" s="4">
+        <v>0.16140245372896947</v>
+      </c>
+      <c r="G81" s="4">
+        <v>0.013513513513513375</v>
+      </c>
+      <c r="H81" s="4">
+        <v>0.01842751842751822</v>
+      </c>
+      <c r="I81" s="4">
+        <v>-0.0952088452088452</v>
+      </c>
+      <c r="J81" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K81" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -9.52%</t>
+        </is>
+      </c>
+      <c r="L81" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M81" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B82" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C82" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="D82" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600356</t>
+        </is>
+      </c>
+      <c r="E82" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">恒丰纸业</t>
+        </is>
+      </c>
+      <c r="F82" s="4">
+        <v>0.1607982112395598</v>
+      </c>
+      <c r="G82" s="4">
+        <v>-0.016579406631762716</v>
+      </c>
+      <c r="H82" s="4">
+        <v>-0.009598603839441666</v>
+      </c>
+      <c r="I82" s="4">
+        <v>-0.05759162303664922</v>
+      </c>
+      <c r="J82" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K82" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -5.76%</t>
+        </is>
+      </c>
+      <c r="L82" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M82" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B83" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="C83" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="D83" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600663</t>
+        </is>
+      </c>
+      <c r="E83" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">陆家嘴</t>
+        </is>
+      </c>
+      <c r="F83" s="4">
+        <v>0.15189972362268037</v>
+      </c>
+      <c r="G83" s="4">
+        <v>0.049455984174085144</v>
+      </c>
+      <c r="H83" s="4">
+        <v>0.09990108803165176</v>
+      </c>
+      <c r="I83" s="4">
+        <v>0.09990108803165176</v>
+      </c>
+      <c r="J83" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K83" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +9.99%</t>
+        </is>
+      </c>
+      <c r="L83" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M83" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.12</t>
         </is>
       </c>
     </row>
@@ -22921,28 +25067,28 @@
         </is>
       </c>
       <c r="B3" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" s="0">
         <v>2</v>
       </c>
       <c r="E3" s="4">
-        <v>0.2857142857142857</v>
+        <v>0.25</v>
       </c>
       <c r="F3" s="4">
-        <v>0.14285714285714285</v>
+        <v>0.07894736842105263</v>
       </c>
       <c r="G3" s="0">
-        <v>2.0</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="H3" s="0">
         <v>2</v>
       </c>
       <c r="I3" s="4">
-        <v>0.2857142857142857</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="4">
@@ -22952,28 +25098,28 @@
         </is>
       </c>
       <c r="B4" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="0">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D4" s="0">
         <v>7</v>
       </c>
       <c r="E4" s="4">
-        <v>0.3333333333333333</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="F4" s="4">
-        <v>0.14285714285714285</v>
+        <v>0.07894736842105263</v>
       </c>
       <c r="G4" s="0">
-        <v>2.3333333333333335</v>
+        <v>3.694444444444445</v>
       </c>
       <c r="H4" s="0">
         <v>4</v>
       </c>
       <c r="I4" s="4">
-        <v>0.5714285714285714</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
@@ -22983,28 +25129,28 @@
         </is>
       </c>
       <c r="B5" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="0">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D5" s="0">
         <v>13</v>
       </c>
       <c r="E5" s="4">
-        <v>0.30952380952380953</v>
+        <v>0.2708333333333333</v>
       </c>
       <c r="F5" s="4">
-        <v>0.14285714285714285</v>
+        <v>0.07894736842105263</v>
       </c>
       <c r="G5" s="0">
-        <v>2.166666666666667</v>
+        <v>3.4305555555555554</v>
       </c>
       <c r="H5" s="0">
         <v>6</v>
       </c>
       <c r="I5" s="4">
-        <v>0.8571428571428571</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="6">
@@ -23014,28 +25160,28 @@
         </is>
       </c>
       <c r="B6" s="0">
+        <v>8</v>
+      </c>
+      <c r="C6" s="0">
+        <v>80</v>
+      </c>
+      <c r="D6" s="0">
+        <v>19</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0.2375</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.07894736842105263</v>
+      </c>
+      <c r="G6" s="0">
+        <v>3.0083333333333333</v>
+      </c>
+      <c r="H6" s="0">
         <v>7</v>
       </c>
-      <c r="C6" s="0">
-        <v>70</v>
-      </c>
-      <c r="D6" s="0">
-        <v>18</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0.2571428571428571</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0.14285714285714285</v>
-      </c>
-      <c r="G6" s="0">
-        <v>1.7999999999999998</v>
-      </c>
-      <c r="H6" s="0">
-        <v>6</v>
-      </c>
       <c r="I6" s="4">
-        <v>0.8571428571428571</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="7">

--- a/docs/downloads/latest.xlsx
+++ b/docs/downloads/latest.xlsx
@@ -93,7 +93,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L372"/>
+  <dimension ref="A1:L392"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -20132,6 +20132,1086 @@
         </is>
       </c>
       <c r="L372" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B373" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C373" s="0">
+        <v>1</v>
+      </c>
+      <c r="D373" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600207</t>
+        </is>
+      </c>
+      <c r="E373" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">安彩高科</t>
+        </is>
+      </c>
+      <c r="F373" s="0">
+        <v>5.6</v>
+      </c>
+      <c r="G373" s="4">
+        <v>0.10019646365422386</v>
+      </c>
+      <c r="H373" s="4">
+        <v>0.18154521411766936</v>
+      </c>
+      <c r="I373" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J373" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 安彩高科（600207）归入“光伏玻璃+资产出售+高透产品”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K373" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L373" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B374" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C374" s="0">
+        <v>2</v>
+      </c>
+      <c r="D374" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002212</t>
+        </is>
+      </c>
+      <c r="E374" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天融信</t>
+        </is>
+      </c>
+      <c r="F374" s="0">
+        <v>7.56</v>
+      </c>
+      <c r="G374" s="4">
+        <v>0.10043668122270732</v>
+      </c>
+      <c r="H374" s="4">
+        <v>0.15200281332457335</v>
+      </c>
+      <c r="I374" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J374" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 天融信（002212）归入“人工智能安全+智算云+网络安全”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K374" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 0.8 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L374" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B375" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C375" s="0">
+        <v>3</v>
+      </c>
+      <c r="D375" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605136</t>
+        </is>
+      </c>
+      <c r="E375" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">丽人丽妆</t>
+        </is>
+      </c>
+      <c r="F375" s="0">
+        <v>9.44</v>
+      </c>
+      <c r="G375" s="4">
+        <v>0.10023310023310007</v>
+      </c>
+      <c r="H375" s="4">
+        <v>0.14286966439297724</v>
+      </c>
+      <c r="I375" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J375" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 丽人丽妆（605136）归入“化妆品电商+海外总代+业绩扭亏”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K375" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L375" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B376" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C376" s="0">
+        <v>4</v>
+      </c>
+      <c r="D376" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603067</t>
+        </is>
+      </c>
+      <c r="E376" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">振华股份</t>
+        </is>
+      </c>
+      <c r="F376" s="0">
+        <v>42.31</v>
+      </c>
+      <c r="G376" s="4">
+        <v>0.1001040041601664</v>
+      </c>
+      <c r="H376" s="4">
+        <v>0.13867173777063957</v>
+      </c>
+      <c r="I376" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no_verified_event</t>
+        </is>
+      </c>
+      <c r="J376" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">事件证据层未找到与当日涨停直接匹配的公告或新闻；系统不把概念标签、技术形态或主观猜测当成涨停原因。</t>
+        </is>
+      </c>
+      <c r="K376" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 0.8 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L376" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B377" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C377" s="0">
+        <v>5</v>
+      </c>
+      <c r="D377" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601086</t>
+        </is>
+      </c>
+      <c r="E377" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">国芳集团</t>
+        </is>
+      </c>
+      <c r="F377" s="0">
+        <v>14.94</v>
+      </c>
+      <c r="G377" s="4">
+        <v>0.10014727540500722</v>
+      </c>
+      <c r="H377" s="4">
+        <v>0.1341990776015942</v>
+      </c>
+      <c r="I377" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J377" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 国芳集团（601086）归入“连锁零售+消费场景+营收增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K377" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 0.8 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L377" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B378" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C378" s="0">
+        <v>6</v>
+      </c>
+      <c r="D378" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605399</t>
+        </is>
+      </c>
+      <c r="E378" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晨光新材</t>
+        </is>
+      </c>
+      <c r="F378" s="0">
+        <v>13.06</v>
+      </c>
+      <c r="G378" s="4">
+        <v>0.10025273799494538</v>
+      </c>
+      <c r="H378" s="4">
+        <v>0.12877242358933152</v>
+      </c>
+      <c r="I378" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J378" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 晨光新材（605399）归入“功能性硅烷+多基地产能”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K378" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L378" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B379" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C379" s="0">
+        <v>7</v>
+      </c>
+      <c r="D379" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600629</t>
+        </is>
+      </c>
+      <c r="E379" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华建集团</t>
+        </is>
+      </c>
+      <c r="F379" s="0">
+        <v>18.02</v>
+      </c>
+      <c r="G379" s="4">
+        <v>0.10012210012210021</v>
+      </c>
+      <c r="H379" s="4">
+        <v>0.11379703504926737</v>
+      </c>
+      <c r="I379" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J379" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华建集团（600629）归入“上海微电子相关+工程设计+子公司重整获批+上海国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K379" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L379" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B380" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C380" s="0">
+        <v>8</v>
+      </c>
+      <c r="D380" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600371</t>
+        </is>
+      </c>
+      <c r="E380" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">万向德农</t>
+        </is>
+      </c>
+      <c r="F380" s="0">
+        <v>14.97</v>
+      </c>
+      <c r="G380" s="4">
+        <v>0.09992652461425422</v>
+      </c>
+      <c r="H380" s="4">
+        <v>0.11189968597838655</v>
+      </c>
+      <c r="I380" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J380" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 万向德农（600371）归入“玉米种业+转基因玉米+新品研发”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K380" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L380" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B381" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C381" s="0">
+        <v>9</v>
+      </c>
+      <c r="D381" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600865</t>
+        </is>
+      </c>
+      <c r="E381" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">百大集团</t>
+        </is>
+      </c>
+      <c r="F381" s="0">
+        <v>11.51</v>
+      </c>
+      <c r="G381" s="4">
+        <v>0.10038240917782026</v>
+      </c>
+      <c r="H381" s="4">
+        <v>0.10668858014305989</v>
+      </c>
+      <c r="I381" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J381" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 百大集团（600865）归入“商业零售+物业租赁+政府补助”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K381" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L381" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B382" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C382" s="0">
+        <v>10</v>
+      </c>
+      <c r="D382" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600127</t>
+        </is>
+      </c>
+      <c r="E382" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金健米业</t>
+        </is>
+      </c>
+      <c r="F382" s="0">
+        <v>15.18</v>
+      </c>
+      <c r="G382" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H382" s="4">
+        <v>0.1047979819965369</v>
+      </c>
+      <c r="I382" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J382" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 金健米业（600127）归入“粮油食品+健康食品+粮食储备”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K382" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L382" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B383" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C383" s="0">
+        <v>11</v>
+      </c>
+      <c r="D383" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603101</t>
+        </is>
+      </c>
+      <c r="E383" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汇嘉时代</t>
+        </is>
+      </c>
+      <c r="F383" s="0">
+        <v>7.99</v>
+      </c>
+      <c r="G383" s="4">
+        <v>0.1005509641873279</v>
+      </c>
+      <c r="H383" s="4">
+        <v>0.1036234843409614</v>
+      </c>
+      <c r="I383" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J383" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 汇嘉时代（603101）归入“超市调改+新疆零售+商业综合体”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K383" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 2.2 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L383" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B384" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C384" s="0">
+        <v>12</v>
+      </c>
+      <c r="D384" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600843</t>
+        </is>
+      </c>
+      <c r="E384" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上工申贝</t>
+        </is>
+      </c>
+      <c r="F384" s="0">
+        <v>8.18</v>
+      </c>
+      <c r="G384" s="4">
+        <v>0.09946236559139777</v>
+      </c>
+      <c r="H384" s="4">
+        <v>0.09811465247056991</v>
+      </c>
+      <c r="I384" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J384" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 上工申贝（600843）归入“缝制设备+机器人缝制+轻型飞机”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K384" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 2.2 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L384" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B385" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C385" s="0">
+        <v>13</v>
+      </c>
+      <c r="D385" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600882</t>
+        </is>
+      </c>
+      <c r="E385" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">妙可蓝多</t>
+        </is>
+      </c>
+      <c r="F385" s="0">
+        <v>21.13</v>
+      </c>
+      <c r="G385" s="4">
+        <v>0.09994794377928162</v>
+      </c>
+      <c r="H385" s="4">
+        <v>0.09662631620345155</v>
+      </c>
+      <c r="I385" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J385" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 妙可蓝多（600882）归入“业绩增长+奶酪深加工+奶酪产品”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K385" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 3.2 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L385" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B386" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C386" s="0">
+        <v>14</v>
+      </c>
+      <c r="D386" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603155</t>
+        </is>
+      </c>
+      <c r="E386" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新亚强</t>
+        </is>
+      </c>
+      <c r="F386" s="0">
+        <v>15.43</v>
+      </c>
+      <c r="G386" s="4">
+        <v>0.09978617248752686</v>
+      </c>
+      <c r="H386" s="4">
+        <v>0.09190682678873706</v>
+      </c>
+      <c r="I386" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J386" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 新亚强（603155）归入“有机硅+电子化学品+国资控股”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K386" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L386" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B387" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C387" s="0">
+        <v>15</v>
+      </c>
+      <c r="D387" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002692</t>
+        </is>
+      </c>
+      <c r="E387" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">远程股份</t>
+        </is>
+      </c>
+      <c r="F387" s="0">
+        <v>4.76</v>
+      </c>
+      <c r="G387" s="4">
+        <v>0.09930715935334877</v>
+      </c>
+      <c r="H387" s="4">
+        <v>0.09072806040585052</v>
+      </c>
+      <c r="I387" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J387" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 远程股份（002692）归入“电线电缆+电网应用+数据中心电缆+参股半导体”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K387" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L387" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B388" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C388" s="0">
+        <v>16</v>
+      </c>
+      <c r="D388" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600478</t>
+        </is>
+      </c>
+      <c r="E388" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">科力远</t>
+        </is>
+      </c>
+      <c r="F388" s="0">
+        <v>5.1</v>
+      </c>
+      <c r="G388" s="4">
+        <v>0.09913793103448265</v>
+      </c>
+      <c r="H388" s="4">
+        <v>0.09050562679436464</v>
+      </c>
+      <c r="I388" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J388" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 科力远（600478）归入“固态电池+储能电站+电池材料”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K388" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 2.6 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L388" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B389" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C389" s="0">
+        <v>17</v>
+      </c>
+      <c r="D389" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605188</t>
+        </is>
+      </c>
+      <c r="E389" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">国光连锁</t>
+        </is>
+      </c>
+      <c r="F389" s="0">
+        <v>13.84</v>
+      </c>
+      <c r="G389" s="4">
+        <v>0.10015898251192358</v>
+      </c>
+      <c r="H389" s="4">
+        <v>0.08682078043267394</v>
+      </c>
+      <c r="I389" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J389" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 国光连锁（605188）归入“零售主业+商业综合体+半年报增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K389" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L389" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B390" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C390" s="0">
+        <v>18</v>
+      </c>
+      <c r="D390" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002709</t>
+        </is>
+      </c>
+      <c r="E390" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天赐材料</t>
+        </is>
+      </c>
+      <c r="F390" s="0">
+        <v>35.96</v>
+      </c>
+      <c r="G390" s="4">
+        <v>0.10003059039461615</v>
+      </c>
+      <c r="H390" s="4">
+        <v>0.08409192647883802</v>
+      </c>
+      <c r="I390" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J390" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 天赐材料（002709）归入“H股上市+电解液+固态电池+业绩增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K390" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 3.6 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L390" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B391" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C391" s="0">
+        <v>19</v>
+      </c>
+      <c r="D391" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000546</t>
+        </is>
+      </c>
+      <c r="E391" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金圆股份</t>
+        </is>
+      </c>
+      <c r="F391" s="0">
+        <v>4.77</v>
+      </c>
+      <c r="G391" s="4">
+        <v>0.09907834101382473</v>
+      </c>
+      <c r="H391" s="4">
+        <v>0.08021758528687543</v>
+      </c>
+      <c r="I391" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J391" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 金圆股份（000546）归入“盐湖提锂+锂矿布局+固废危废资源化”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K391" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 2.3 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L391" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B392" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C392" s="0">
+        <v>20</v>
+      </c>
+      <c r="D392" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002675</t>
+        </is>
+      </c>
+      <c r="E392" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东诚药业</t>
+        </is>
+      </c>
+      <c r="F392" s="0">
+        <v>13.89</v>
+      </c>
+      <c r="G392" s="4">
+        <v>0.09976247030878849</v>
+      </c>
+      <c r="H392" s="4">
+        <v>0.07674861464578389</v>
+      </c>
+      <c r="I392" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J392" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 东诚药业（002675）归入“核医药+创新药+股份回购”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K392" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 5.4 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L392" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
         </is>

--- a/docs/downloads/latest.xlsx
+++ b/docs/downloads/latest.xlsx
@@ -93,7 +93,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L392"/>
+  <dimension ref="A1:L399"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -20153,22 +20153,22 @@
       </c>
       <c r="D373" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">600207</t>
+          <t xml:space="preserve">002912</t>
         </is>
       </c>
       <c r="E373" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">安彩高科</t>
+          <t xml:space="preserve">中新赛克</t>
         </is>
       </c>
       <c r="F373" s="0">
-        <v>5.6</v>
+        <v>28.55</v>
       </c>
       <c r="G373" s="4">
-        <v>0.10019646365422386</v>
+        <v>0.10019267822736033</v>
       </c>
       <c r="H373" s="4">
-        <v>0.18154521411766936</v>
+        <v>0.19945544248552788</v>
       </c>
       <c r="I373" s="0" t="inlineStr">
         <is>
@@ -20177,12 +20177,12 @@
       </c>
       <c r="J373" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 安彩高科（600207）归入“光伏玻璃+资产出售+高透产品”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 中新赛克（002912）归入“AI安全+网络安全+数据安全”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K373" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 1.4 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
         </is>
       </c>
       <c r="L373" s="3" t="inlineStr">
@@ -20207,22 +20207,22 @@
       </c>
       <c r="D374" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">002212</t>
+          <t xml:space="preserve">600207</t>
         </is>
       </c>
       <c r="E374" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">天融信</t>
+          <t xml:space="preserve">安彩高科</t>
         </is>
       </c>
       <c r="F374" s="0">
-        <v>7.56</v>
+        <v>5.6</v>
       </c>
       <c r="G374" s="4">
-        <v>0.10043668122270732</v>
+        <v>0.10019646365422386</v>
       </c>
       <c r="H374" s="4">
-        <v>0.15200281332457335</v>
+        <v>0.1836824136959978</v>
       </c>
       <c r="I374" s="0" t="inlineStr">
         <is>
@@ -20231,12 +20231,12 @@
       </c>
       <c r="J374" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 天融信（002212）归入“人工智能安全+智算云+网络安全”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 安彩高科（600207）归入“光伏玻璃+资产出售+高透产品”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K374" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 0.8 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
         </is>
       </c>
       <c r="L374" s="3" t="inlineStr">
@@ -20261,22 +20261,22 @@
       </c>
       <c r="D375" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">605136</t>
+          <t xml:space="preserve">605177</t>
         </is>
       </c>
       <c r="E375" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">丽人丽妆</t>
+          <t xml:space="preserve">东亚药业</t>
         </is>
       </c>
       <c r="F375" s="0">
-        <v>9.44</v>
+        <v>28.29</v>
       </c>
       <c r="G375" s="4">
-        <v>0.10023310023310007</v>
+        <v>0.09992223950233292</v>
       </c>
       <c r="H375" s="4">
-        <v>0.14286966439297724</v>
+        <v>0.17687868405795468</v>
       </c>
       <c r="I375" s="0" t="inlineStr">
         <is>
@@ -20285,17 +20285,17 @@
       </c>
       <c r="J375" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 丽人丽妆（605136）归入“化妆品电商+海外总代+业绩扭亏”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 东亚药业（605177）归入“抗生素+头孢产品+制剂一体化”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K375" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
         </is>
       </c>
       <c r="L375" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+          <t xml:space="preserve">当日振幅较大</t>
         </is>
       </c>
     </row>
@@ -20315,36 +20315,36 @@
       </c>
       <c r="D376" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">603067</t>
+          <t xml:space="preserve">002212</t>
         </is>
       </c>
       <c r="E376" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">振华股份</t>
+          <t xml:space="preserve">天融信</t>
         </is>
       </c>
       <c r="F376" s="0">
-        <v>42.31</v>
+        <v>7.56</v>
       </c>
       <c r="G376" s="4">
-        <v>0.1001040041601664</v>
+        <v>0.10043668122270732</v>
       </c>
       <c r="H376" s="4">
-        <v>0.13867173777063957</v>
+        <v>0.15264207255627008</v>
       </c>
       <c r="I376" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">no_verified_event</t>
+          <t xml:space="preserve">theme_only</t>
         </is>
       </c>
       <c r="J376" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">事件证据层未找到与当日涨停直接匹配的公告或新闻；系统不把概念标签、技术形态或主观猜测当成涨停原因。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 天融信（002212）归入“人工智能安全+智算云+网络安全”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K376" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 0.8 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
         </is>
       </c>
       <c r="L376" s="3" t="inlineStr">
@@ -20369,22 +20369,22 @@
       </c>
       <c r="D377" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">601086</t>
+          <t xml:space="preserve">605136</t>
         </is>
       </c>
       <c r="E377" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">国芳集团</t>
+          <t xml:space="preserve">丽人丽妆</t>
         </is>
       </c>
       <c r="F377" s="0">
-        <v>14.94</v>
+        <v>9.44</v>
       </c>
       <c r="G377" s="4">
-        <v>0.10014727540500722</v>
+        <v>0.10023310023310007</v>
       </c>
       <c r="H377" s="4">
-        <v>0.1341990776015942</v>
+        <v>0.14476014873848486</v>
       </c>
       <c r="I377" s="0" t="inlineStr">
         <is>
@@ -20393,12 +20393,12 @@
       </c>
       <c r="J377" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 国芳集团（601086）归入“连锁零售+消费场景+营收增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 丽人丽妆（605136）归入“化妆品电商+海外总代+业绩扭亏”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K377" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 0.8 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
         </is>
       </c>
       <c r="L377" s="3" t="inlineStr">
@@ -20423,22 +20423,22 @@
       </c>
       <c r="D378" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">605399</t>
+          <t xml:space="preserve">603067</t>
         </is>
       </c>
       <c r="E378" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">晨光新材</t>
+          <t xml:space="preserve">振华股份</t>
         </is>
       </c>
       <c r="F378" s="0">
-        <v>13.06</v>
+        <v>42.31</v>
       </c>
       <c r="G378" s="4">
-        <v>0.10025273799494538</v>
+        <v>0.1001040041601664</v>
       </c>
       <c r="H378" s="4">
-        <v>0.12877242358933152</v>
+        <v>0.13939720779864948</v>
       </c>
       <c r="I378" s="0" t="inlineStr">
         <is>
@@ -20447,17 +20447,17 @@
       </c>
       <c r="J378" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 晨光新材（605399）归入“功能性硅烷+多基地产能”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 振华股份（603067）归入“SOFC+金属铬+铬盐龙头”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K378" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
         </is>
       </c>
       <c r="L378" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+          <t xml:space="preserve">当日振幅较大</t>
         </is>
       </c>
     </row>
@@ -20477,22 +20477,22 @@
       </c>
       <c r="D379" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">600629</t>
+          <t xml:space="preserve">601086</t>
         </is>
       </c>
       <c r="E379" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">华建集团</t>
+          <t xml:space="preserve">国芳集团</t>
         </is>
       </c>
       <c r="F379" s="0">
-        <v>18.02</v>
+        <v>14.94</v>
       </c>
       <c r="G379" s="4">
-        <v>0.10012210012210021</v>
+        <v>0.10014727540500722</v>
       </c>
       <c r="H379" s="4">
-        <v>0.11379703504926737</v>
+        <v>0.13608736294818338</v>
       </c>
       <c r="I379" s="0" t="inlineStr">
         <is>
@@ -20501,12 +20501,12 @@
       </c>
       <c r="J379" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 华建集团（600629）归入“上海微电子相关+工程设计+子公司重整获批+上海国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 国芳集团（601086）归入“连锁零售+消费场景+营收增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K379" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 0.8 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
         </is>
       </c>
       <c r="L379" s="3" t="inlineStr">
@@ -20531,22 +20531,22 @@
       </c>
       <c r="D380" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">600371</t>
+          <t xml:space="preserve">605399</t>
         </is>
       </c>
       <c r="E380" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">万向德农</t>
+          <t xml:space="preserve">晨光新材</t>
         </is>
       </c>
       <c r="F380" s="0">
-        <v>14.97</v>
+        <v>13.06</v>
       </c>
       <c r="G380" s="4">
-        <v>0.09992652461425422</v>
+        <v>0.10025273799494538</v>
       </c>
       <c r="H380" s="4">
-        <v>0.11189968597838655</v>
+        <v>0.13044684341641602</v>
       </c>
       <c r="I380" s="0" t="inlineStr">
         <is>
@@ -20555,17 +20555,17 @@
       </c>
       <c r="J380" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 万向德农（600371）归入“玉米种业+转基因玉米+新品研发”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 晨光新材（605399）归入“功能性硅烷+多基地产能”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K380" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
         </is>
       </c>
       <c r="L380" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">当日振幅较大</t>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
         </is>
       </c>
     </row>
@@ -20585,22 +20585,22 @@
       </c>
       <c r="D381" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">600865</t>
+          <t xml:space="preserve">002105</t>
         </is>
       </c>
       <c r="E381" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">百大集团</t>
+          <t xml:space="preserve">信隆健康</t>
         </is>
       </c>
       <c r="F381" s="0">
-        <v>11.51</v>
+        <v>6.79</v>
       </c>
       <c r="G381" s="4">
-        <v>0.10038240917782026</v>
+        <v>0.10048622366288494</v>
       </c>
       <c r="H381" s="4">
-        <v>0.10668858014305989</v>
+        <v>0.12291838234398976</v>
       </c>
       <c r="I381" s="0" t="inlineStr">
         <is>
@@ -20609,17 +20609,17 @@
       </c>
       <c r="J381" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 百大集团（600865）归入“商业零售+物业租赁+政府补助”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 信隆健康（002105）归入“外骨骼机器人+自行车配件+半年报扭亏”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K381" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 2.2 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
         </is>
       </c>
       <c r="L381" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
         </is>
       </c>
     </row>
@@ -20639,22 +20639,22 @@
       </c>
       <c r="D382" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">600127</t>
+          <t xml:space="preserve">600354</t>
         </is>
       </c>
       <c r="E382" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">金健米业</t>
+          <t xml:space="preserve">敦煌种业</t>
         </is>
       </c>
       <c r="F382" s="0">
-        <v>15.18</v>
+        <v>9.99</v>
       </c>
       <c r="G382" s="4">
-        <v>0.09999999999999985</v>
+        <v>0.10022026431718058</v>
       </c>
       <c r="H382" s="4">
-        <v>0.1047979819965369</v>
+        <v>0.11671494650603292</v>
       </c>
       <c r="I382" s="0" t="inlineStr">
         <is>
@@ -20663,17 +20663,17 @@
       </c>
       <c r="J382" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 金健米业（600127）归入“粮油食品+健康食品+粮食储备”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 敦煌种业（600354）归入“玉米种业+核心品种+商业化育种”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K382" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
         </is>
       </c>
       <c r="L382" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">当日振幅较大</t>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
         </is>
       </c>
     </row>
@@ -20693,22 +20693,22 @@
       </c>
       <c r="D383" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">603101</t>
+          <t xml:space="preserve">600629</t>
         </is>
       </c>
       <c r="E383" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">汇嘉时代</t>
+          <t xml:space="preserve">华建集团</t>
         </is>
       </c>
       <c r="F383" s="0">
-        <v>7.99</v>
+        <v>18.02</v>
       </c>
       <c r="G383" s="4">
-        <v>0.1005509641873279</v>
+        <v>0.10012210012210021</v>
       </c>
       <c r="H383" s="4">
-        <v>0.1036234843409614</v>
+        <v>0.1153786870969825</v>
       </c>
       <c r="I383" s="0" t="inlineStr">
         <is>
@@ -20717,12 +20717,12 @@
       </c>
       <c r="J383" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 汇嘉时代（603101）归入“超市调改+新疆零售+商业综合体”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华建集团（600629）归入“上海微电子相关+工程设计+子公司重整获批+上海国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K383" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 2.2 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
         </is>
       </c>
       <c r="L383" s="3" t="inlineStr">
@@ -20747,22 +20747,22 @@
       </c>
       <c r="D384" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">600843</t>
+          <t xml:space="preserve">600371</t>
         </is>
       </c>
       <c r="E384" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">上工申贝</t>
+          <t xml:space="preserve">万向德农</t>
         </is>
       </c>
       <c r="F384" s="0">
-        <v>8.18</v>
+        <v>14.97</v>
       </c>
       <c r="G384" s="4">
-        <v>0.09946236559139777</v>
+        <v>0.09992652461425422</v>
       </c>
       <c r="H384" s="4">
-        <v>0.09811465247056991</v>
+        <v>0.11351905409843502</v>
       </c>
       <c r="I384" s="0" t="inlineStr">
         <is>
@@ -20771,17 +20771,17 @@
       </c>
       <c r="J384" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 上工申贝（600843）归入“缝制设备+机器人缝制+轻型飞机”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 万向德农（600371）归入“玉米种业+转基因玉米+新品研发”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K384" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 2.2 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
         </is>
       </c>
       <c r="L384" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+          <t xml:space="preserve">当日振幅较大</t>
         </is>
       </c>
     </row>
@@ -20801,22 +20801,22 @@
       </c>
       <c r="D385" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">600882</t>
+          <t xml:space="preserve">600865</t>
         </is>
       </c>
       <c r="E385" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">妙可蓝多</t>
+          <t xml:space="preserve">百大集团</t>
         </is>
       </c>
       <c r="F385" s="0">
-        <v>21.13</v>
+        <v>11.51</v>
       </c>
       <c r="G385" s="4">
-        <v>0.09994794377928162</v>
+        <v>0.10038240917782026</v>
       </c>
       <c r="H385" s="4">
-        <v>0.09662631620345155</v>
+        <v>0.10812020936100711</v>
       </c>
       <c r="I385" s="0" t="inlineStr">
         <is>
@@ -20825,17 +20825,17 @@
       </c>
       <c r="J385" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 妙可蓝多（600882）归入“业绩增长+奶酪深加工+奶酪产品”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 百大集团（600865）归入“商业零售+物业租赁+政府补助”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K385" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 3.2 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
         </is>
       </c>
       <c r="L385" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
         </is>
       </c>
     </row>
@@ -20855,22 +20855,22 @@
       </c>
       <c r="D386" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">603155</t>
+          <t xml:space="preserve">600127</t>
         </is>
       </c>
       <c r="E386" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">新亚强</t>
+          <t xml:space="preserve">金健米业</t>
         </is>
       </c>
       <c r="F386" s="0">
-        <v>15.43</v>
+        <v>15.18</v>
       </c>
       <c r="G386" s="4">
-        <v>0.09978617248752686</v>
+        <v>0.09999999999999985</v>
       </c>
       <c r="H386" s="4">
-        <v>0.09190682678873706</v>
+        <v>0.1063382154715076</v>
       </c>
       <c r="I386" s="0" t="inlineStr">
         <is>
@@ -20879,12 +20879,12 @@
       </c>
       <c r="J386" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 新亚强（603155）归入“有机硅+电子化学品+国资控股”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 金健米业（600127）归入“粮油食品+健康食品+粮食储备”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K386" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
         </is>
       </c>
       <c r="L386" s="3" t="inlineStr">
@@ -20909,22 +20909,22 @@
       </c>
       <c r="D387" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">002692</t>
+          <t xml:space="preserve">603101</t>
         </is>
       </c>
       <c r="E387" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">远程股份</t>
+          <t xml:space="preserve">汇嘉时代</t>
         </is>
       </c>
       <c r="F387" s="0">
-        <v>4.76</v>
+        <v>7.99</v>
       </c>
       <c r="G387" s="4">
-        <v>0.09930715935334877</v>
+        <v>0.1005509641873279</v>
       </c>
       <c r="H387" s="4">
-        <v>0.09072806040585052</v>
+        <v>0.10500141405285064</v>
       </c>
       <c r="I387" s="0" t="inlineStr">
         <is>
@@ -20933,12 +20933,12 @@
       </c>
       <c r="J387" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 远程股份（002692）归入“电线电缆+电网应用+数据中心电缆+参股半导体”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 汇嘉时代（603101）归入“超市调改+新疆零售+商业综合体”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K387" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 2.2 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
         </is>
       </c>
       <c r="L387" s="3" t="inlineStr">
@@ -20963,22 +20963,22 @@
       </c>
       <c r="D388" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">600478</t>
+          <t xml:space="preserve">601519</t>
         </is>
       </c>
       <c r="E388" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">科力远</t>
+          <t xml:space="preserve">大智慧</t>
         </is>
       </c>
       <c r="F388" s="0">
-        <v>5.1</v>
+        <v>9.17</v>
       </c>
       <c r="G388" s="4">
-        <v>0.09913793103448265</v>
+        <v>0.0995203836930456</v>
       </c>
       <c r="H388" s="4">
-        <v>0.09050562679436464</v>
+        <v>0.10092080653982519</v>
       </c>
       <c r="I388" s="0" t="inlineStr">
         <is>
@@ -20987,17 +20987,17 @@
       </c>
       <c r="J388" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 科力远（600478）归入“固态电池+储能电站+电池材料”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 大智慧（601519）归入“互联网金融+湘财吸收合并+人工智能”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K388" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 2.6 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
         </is>
       </c>
       <c r="L388" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
         </is>
       </c>
     </row>
@@ -21017,22 +21017,22 @@
       </c>
       <c r="D389" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">605188</t>
+          <t xml:space="preserve">600843</t>
         </is>
       </c>
       <c r="E389" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">国光连锁</t>
+          <t xml:space="preserve">上工申贝</t>
         </is>
       </c>
       <c r="F389" s="0">
-        <v>13.84</v>
+        <v>8.18</v>
       </c>
       <c r="G389" s="4">
-        <v>0.10015898251192358</v>
+        <v>0.09946236559139777</v>
       </c>
       <c r="H389" s="4">
-        <v>0.08682078043267394</v>
+        <v>0.09946147616709738</v>
       </c>
       <c r="I389" s="0" t="inlineStr">
         <is>
@@ -21041,17 +21041,17 @@
       </c>
       <c r="J389" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 国光连锁（605188）归入“零售主业+商业综合体+半年报增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 上工申贝（600843）归入“缝制设备+机器人缝制+轻型飞机”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K389" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 2.3 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
         </is>
       </c>
       <c r="L389" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
         </is>
       </c>
     </row>
@@ -21071,22 +21071,22 @@
       </c>
       <c r="D390" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">002709</t>
+          <t xml:space="preserve">600882</t>
         </is>
       </c>
       <c r="E390" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">天赐材料</t>
+          <t xml:space="preserve">妙可蓝多</t>
         </is>
       </c>
       <c r="F390" s="0">
-        <v>35.96</v>
+        <v>21.13</v>
       </c>
       <c r="G390" s="4">
-        <v>0.10003059039461615</v>
+        <v>0.09994794377928162</v>
       </c>
       <c r="H390" s="4">
-        <v>0.08409192647883802</v>
+        <v>0.09737566995195442</v>
       </c>
       <c r="I390" s="0" t="inlineStr">
         <is>
@@ -21095,12 +21095,12 @@
       </c>
       <c r="J390" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 天赐材料（002709）归入“H股上市+电解液+固态电池+业绩增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 妙可蓝多（600882）归入“业绩增长+奶酪深加工+奶酪产品”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K390" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 3.6 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 3.3 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
         </is>
       </c>
       <c r="L390" s="3" t="inlineStr">
@@ -21125,22 +21125,22 @@
       </c>
       <c r="D391" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">000546</t>
+          <t xml:space="preserve">603155</t>
         </is>
       </c>
       <c r="E391" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">金圆股份</t>
+          <t xml:space="preserve">新亚强</t>
         </is>
       </c>
       <c r="F391" s="0">
-        <v>4.77</v>
+        <v>15.43</v>
       </c>
       <c r="G391" s="4">
-        <v>0.09907834101382473</v>
+        <v>0.09978617248752686</v>
       </c>
       <c r="H391" s="4">
-        <v>0.08021758528687543</v>
+        <v>0.093100809118559</v>
       </c>
       <c r="I391" s="0" t="inlineStr">
         <is>
@@ -21149,17 +21149,17 @@
       </c>
       <c r="J391" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 金圆股份（000546）归入“盐湖提锂+锂矿布局+固废危废资源化”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 新亚强（603155）归入“有机硅+电子化学品+国资控股”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K391" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 2.3 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
         </is>
       </c>
       <c r="L391" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+          <t xml:space="preserve">当日振幅较大</t>
         </is>
       </c>
     </row>
@@ -21179,39 +21179,417 @@
       </c>
       <c r="D392" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">002692</t>
+        </is>
+      </c>
+      <c r="E392" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">远程股份</t>
+        </is>
+      </c>
+      <c r="F392" s="0">
+        <v>4.76</v>
+      </c>
+      <c r="G392" s="4">
+        <v>0.09930715935334877</v>
+      </c>
+      <c r="H392" s="4">
+        <v>0.09197641965414466</v>
+      </c>
+      <c r="I392" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J392" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 远程股份（002692）归入“电线电缆+电网应用+数据中心电缆+参股半导体”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K392" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L392" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B393" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C393" s="0">
+        <v>21</v>
+      </c>
+      <c r="D393" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600478</t>
+        </is>
+      </c>
+      <c r="E393" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">科力远</t>
+        </is>
+      </c>
+      <c r="F393" s="0">
+        <v>5.1</v>
+      </c>
+      <c r="G393" s="4">
+        <v>0.09913793103448265</v>
+      </c>
+      <c r="H393" s="4">
+        <v>0.09163868997374895</v>
+      </c>
+      <c r="I393" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J393" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 科力远（600478）归入“固态电池+储能电站+电池材料”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K393" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 2.6 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L393" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B394" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C394" s="0">
+        <v>22</v>
+      </c>
+      <c r="D394" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601069</t>
+        </is>
+      </c>
+      <c r="E394" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">西部黄金</t>
+        </is>
+      </c>
+      <c r="F394" s="0">
+        <v>26.55</v>
+      </c>
+      <c r="G394" s="4">
+        <v>0.09983429991715</v>
+      </c>
+      <c r="H394" s="4">
+        <v>0.0893103099953754</v>
+      </c>
+      <c r="I394" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J394" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 西部黄金（601069）归入“黄金业务+股东合并+业绩增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K394" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L394" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B395" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C395" s="0">
+        <v>23</v>
+      </c>
+      <c r="D395" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600621</t>
+        </is>
+      </c>
+      <c r="E395" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华鑫股份</t>
+        </is>
+      </c>
+      <c r="F395" s="0">
+        <v>14.48</v>
+      </c>
+      <c r="G395" s="4">
+        <v>0.10030395136778125</v>
+      </c>
+      <c r="H395" s="4">
+        <v>0.08895869470161645</v>
+      </c>
+      <c r="I395" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J395" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华鑫股份（600621）归入“证券经纪+金融科技+上海国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K395" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 2.3 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L395" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B396" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C396" s="0">
+        <v>24</v>
+      </c>
+      <c r="D396" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605188</t>
+        </is>
+      </c>
+      <c r="E396" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">国光连锁</t>
+        </is>
+      </c>
+      <c r="F396" s="0">
+        <v>13.84</v>
+      </c>
+      <c r="G396" s="4">
+        <v>0.10015898251192358</v>
+      </c>
+      <c r="H396" s="4">
+        <v>0.08770315332017303</v>
+      </c>
+      <c r="I396" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J396" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 国光连锁（605188）归入“零售主业+商业综合体+半年报增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K396" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L396" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B397" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C397" s="0">
+        <v>25</v>
+      </c>
+      <c r="D397" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000546</t>
+        </is>
+      </c>
+      <c r="E397" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金圆股份</t>
+        </is>
+      </c>
+      <c r="F397" s="0">
+        <v>4.77</v>
+      </c>
+      <c r="G397" s="4">
+        <v>0.09907834101382473</v>
+      </c>
+      <c r="H397" s="4">
+        <v>0.08104958860869282</v>
+      </c>
+      <c r="I397" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J397" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 金圆股份（000546）归入“盐湖提锂+锂矿布局+固废危废资源化”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K397" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 2.3 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L397" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B398" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C398" s="0">
+        <v>26</v>
+      </c>
+      <c r="D398" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">002675</t>
         </is>
       </c>
-      <c r="E392" s="0" t="inlineStr">
+      <c r="E398" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">东诚药业</t>
         </is>
       </c>
-      <c r="F392" s="0">
+      <c r="F398" s="0">
         <v>13.89</v>
       </c>
-      <c r="G392" s="4">
+      <c r="G398" s="4">
         <v>0.09976247030878849</v>
       </c>
-      <c r="H392" s="4">
-        <v>0.07674861464578389</v>
-      </c>
-      <c r="I392" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">theme_only</t>
-        </is>
-      </c>
-      <c r="J392" s="3" t="inlineStr">
+      <c r="H398" s="4">
+        <v>0.07732817978102424</v>
+      </c>
+      <c r="I398" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J398" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">题材归因标签只能说明当日市场将 东诚药业（002675）归入“核医药+创新药+股份回购”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
-      <c r="K392" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 5.4 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
-        </is>
-      </c>
-      <c r="L392" s="3" t="inlineStr">
+      <c r="K398" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 5.4 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L398" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B399" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C399" s="0">
+        <v>27</v>
+      </c>
+      <c r="D399" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000420</t>
+        </is>
+      </c>
+      <c r="E399" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">吉林化纤</t>
+        </is>
+      </c>
+      <c r="F399" s="0">
+        <v>3.81</v>
+      </c>
+      <c r="G399" s="4">
+        <v>0.10115606936416179</v>
+      </c>
+      <c r="H399" s="4">
+        <v>0.07660923967091054</v>
+      </c>
+      <c r="I399" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J399" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 吉林化纤（000420）归入“碳纤维+粘胶长丝+国企”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K399" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 4.1 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L399" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
         </is>

--- a/docs/downloads/latest.xlsx
+++ b/docs/downloads/latest.xlsx
@@ -93,7 +93,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L399"/>
+  <dimension ref="A1:L423"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -20168,7 +20168,7 @@
         <v>0.10019267822736033</v>
       </c>
       <c r="H373" s="4">
-        <v>0.19945544248552788</v>
+        <v>0.20573179563641128</v>
       </c>
       <c r="I373" s="0" t="inlineStr">
         <is>
@@ -20182,7 +20182,7 @@
       </c>
       <c r="K373" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 1.4 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.4 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
         </is>
       </c>
       <c r="L373" s="3" t="inlineStr">
@@ -20222,7 +20222,7 @@
         <v>0.10019646365422386</v>
       </c>
       <c r="H374" s="4">
-        <v>0.1836824136959978</v>
+        <v>0.19015571837609968</v>
       </c>
       <c r="I374" s="0" t="inlineStr">
         <is>
@@ -20236,7 +20236,7 @@
       </c>
       <c r="K374" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
         </is>
       </c>
       <c r="L374" s="3" t="inlineStr">
@@ -20261,22 +20261,22 @@
       </c>
       <c r="D375" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">605177</t>
+          <t xml:space="preserve">601811</t>
         </is>
       </c>
       <c r="E375" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">东亚药业</t>
+          <t xml:space="preserve">新华文轩</t>
         </is>
       </c>
       <c r="F375" s="0">
-        <v>28.29</v>
+        <v>20.91</v>
       </c>
       <c r="G375" s="4">
-        <v>0.09992223950233292</v>
+        <v>0.09994739610731183</v>
       </c>
       <c r="H375" s="4">
-        <v>0.17687868405795468</v>
+        <v>0.1859243286736807</v>
       </c>
       <c r="I375" s="0" t="inlineStr">
         <is>
@@ -20285,17 +20285,17 @@
       </c>
       <c r="J375" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 东亚药业（605177）归入“抗生素+头孢产品+制剂一体化”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 新华文轩（601811）归入“教科书发行+数字教育+收购整合”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K375" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.7 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
         </is>
       </c>
       <c r="L375" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">当日振幅较大</t>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大；近10日涨幅偏高</t>
         </is>
       </c>
     </row>
@@ -20315,22 +20315,22 @@
       </c>
       <c r="D376" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">002212</t>
+          <t xml:space="preserve">605177</t>
         </is>
       </c>
       <c r="E376" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">天融信</t>
+          <t xml:space="preserve">东亚药业</t>
         </is>
       </c>
       <c r="F376" s="0">
-        <v>7.56</v>
+        <v>28.29</v>
       </c>
       <c r="G376" s="4">
-        <v>0.10043668122270732</v>
+        <v>0.09992223950233292</v>
       </c>
       <c r="H376" s="4">
-        <v>0.15264207255627008</v>
+        <v>0.18283374681498385</v>
       </c>
       <c r="I376" s="0" t="inlineStr">
         <is>
@@ -20339,12 +20339,12 @@
       </c>
       <c r="J376" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 天融信（002212）归入“人工智能安全+智算云+网络安全”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 东亚药业（605177）归入“抗生素+头孢产品+制剂一体化”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K376" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.4 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
         </is>
       </c>
       <c r="L376" s="3" t="inlineStr">
@@ -20369,22 +20369,22 @@
       </c>
       <c r="D377" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">605136</t>
+          <t xml:space="preserve">605058</t>
         </is>
       </c>
       <c r="E377" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">丽人丽妆</t>
+          <t xml:space="preserve">澳弘电子</t>
         </is>
       </c>
       <c r="F377" s="0">
-        <v>9.44</v>
+        <v>53.35</v>
       </c>
       <c r="G377" s="4">
-        <v>0.10023310023310007</v>
+        <v>0.10000000000000009</v>
       </c>
       <c r="H377" s="4">
-        <v>0.14476014873848486</v>
+        <v>0.15804911220917978</v>
       </c>
       <c r="I377" s="0" t="inlineStr">
         <is>
@@ -20393,17 +20393,17 @@
       </c>
       <c r="J377" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 丽人丽妆（605136）归入“化妆品电商+海外总代+业绩扭亏”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 澳弘电子（605058）归入“PCB+AI服务器电源+具身智能”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K377" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.4 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
         </is>
       </c>
       <c r="L377" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+          <t xml:space="preserve">当日振幅较大</t>
         </is>
       </c>
     </row>
@@ -20423,22 +20423,22 @@
       </c>
       <c r="D378" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">603067</t>
+          <t xml:space="preserve">002212</t>
         </is>
       </c>
       <c r="E378" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">振华股份</t>
+          <t xml:space="preserve">天融信</t>
         </is>
       </c>
       <c r="F378" s="0">
-        <v>42.31</v>
+        <v>7.56</v>
       </c>
       <c r="G378" s="4">
-        <v>0.1001040041601664</v>
+        <v>0.10043668122270732</v>
       </c>
       <c r="H378" s="4">
-        <v>0.13939720779864948</v>
+        <v>0.15732083460475293</v>
       </c>
       <c r="I378" s="0" t="inlineStr">
         <is>
@@ -20447,12 +20447,12 @@
       </c>
       <c r="J378" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 振华股份（603067）归入“SOFC+金属铬+铬盐龙头”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 天融信（002212）归入“人工智能安全+智算云+网络安全”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K378" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
         </is>
       </c>
       <c r="L378" s="3" t="inlineStr">
@@ -20477,22 +20477,22 @@
       </c>
       <c r="D379" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">601086</t>
+          <t xml:space="preserve">605136</t>
         </is>
       </c>
       <c r="E379" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">国芳集团</t>
+          <t xml:space="preserve">丽人丽妆</t>
         </is>
       </c>
       <c r="F379" s="0">
-        <v>14.94</v>
+        <v>9.44</v>
       </c>
       <c r="G379" s="4">
-        <v>0.10014727540500722</v>
+        <v>0.10023310023310007</v>
       </c>
       <c r="H379" s="4">
-        <v>0.13608736294818338</v>
+        <v>0.1500063889703599</v>
       </c>
       <c r="I379" s="0" t="inlineStr">
         <is>
@@ -20501,12 +20501,12 @@
       </c>
       <c r="J379" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 国芳集团（601086）归入“连锁零售+消费场景+营收增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 丽人丽妆（605136）归入“化妆品电商+海外总代+业绩扭亏”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K379" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 0.8 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
         </is>
       </c>
       <c r="L379" s="3" t="inlineStr">
@@ -20531,22 +20531,22 @@
       </c>
       <c r="D380" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">605399</t>
+          <t xml:space="preserve">001330</t>
         </is>
       </c>
       <c r="E380" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">晨光新材</t>
+          <t xml:space="preserve">博纳影业</t>
         </is>
       </c>
       <c r="F380" s="0">
-        <v>13.06</v>
+        <v>6.97</v>
       </c>
       <c r="G380" s="4">
-        <v>0.10025273799494538</v>
+        <v>0.09936908517350161</v>
       </c>
       <c r="H380" s="4">
-        <v>0.13044684341641602</v>
+        <v>0.14962503029396548</v>
       </c>
       <c r="I380" s="0" t="inlineStr">
         <is>
@@ -20555,12 +20555,12 @@
       </c>
       <c r="J380" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 晨光新材（605399）归入“功能性硅烷+多基地产能”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 博纳影业（001330）归入“AI短剧+AIGC+电影制作+院线影院”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K380" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
         </is>
       </c>
       <c r="L380" s="3" t="inlineStr">
@@ -20585,22 +20585,22 @@
       </c>
       <c r="D381" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">002105</t>
+          <t xml:space="preserve">603232</t>
         </is>
       </c>
       <c r="E381" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">信隆健康</t>
+          <t xml:space="preserve">格尔软件</t>
         </is>
       </c>
       <c r="F381" s="0">
-        <v>6.79</v>
+        <v>16.98</v>
       </c>
       <c r="G381" s="4">
-        <v>0.10048622366288494</v>
+        <v>0.09974093264248719</v>
       </c>
       <c r="H381" s="4">
-        <v>0.12291838234398976</v>
+        <v>0.14907665277852725</v>
       </c>
       <c r="I381" s="0" t="inlineStr">
         <is>
@@ -20609,17 +20609,17 @@
       </c>
       <c r="J381" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 信隆健康（002105）归入“外骨骼机器人+自行车配件+半年报扭亏”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 格尔软件（603232）归入“AI安全+抗量子密码+PKI安全”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K381" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 2.2 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
         </is>
       </c>
       <c r="L381" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+          <t xml:space="preserve">当日振幅较大</t>
         </is>
       </c>
     </row>
@@ -20639,22 +20639,22 @@
       </c>
       <c r="D382" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">600354</t>
+          <t xml:space="preserve">603096</t>
         </is>
       </c>
       <c r="E382" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">敦煌种业</t>
+          <t xml:space="preserve">新经典</t>
         </is>
       </c>
       <c r="F382" s="0">
-        <v>9.99</v>
+        <v>17.33</v>
       </c>
       <c r="G382" s="4">
-        <v>0.10022026431718058</v>
+        <v>0.10031746031746014</v>
       </c>
       <c r="H382" s="4">
-        <v>0.11671494650603292</v>
+        <v>0.14832804194544053</v>
       </c>
       <c r="I382" s="0" t="inlineStr">
         <is>
@@ -20663,17 +20663,17 @@
       </c>
       <c r="J382" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 敦煌种业（600354）归入“玉米种业+核心品种+商业化育种”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 新经典（603096）归入“图书出版+AI应用+内容IP”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K382" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.9 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
         </is>
       </c>
       <c r="L382" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+          <t xml:space="preserve">当日振幅较大</t>
         </is>
       </c>
     </row>
@@ -20693,22 +20693,22 @@
       </c>
       <c r="D383" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">600629</t>
+          <t xml:space="preserve">601086</t>
         </is>
       </c>
       <c r="E383" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">华建集团</t>
+          <t xml:space="preserve">国芳集团</t>
         </is>
       </c>
       <c r="F383" s="0">
-        <v>18.02</v>
+        <v>14.94</v>
       </c>
       <c r="G383" s="4">
-        <v>0.10012210012210021</v>
+        <v>0.10014727540500722</v>
       </c>
       <c r="H383" s="4">
-        <v>0.1153786870969825</v>
+        <v>0.1414878545492124</v>
       </c>
       <c r="I383" s="0" t="inlineStr">
         <is>
@@ -20717,12 +20717,12 @@
       </c>
       <c r="J383" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 华建集团（600629）归入“上海微电子相关+工程设计+子公司重整获批+上海国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 国芳集团（601086）归入“连锁零售+消费场景+营收增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K383" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.8 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
         </is>
       </c>
       <c r="L383" s="3" t="inlineStr">
@@ -20747,22 +20747,22 @@
       </c>
       <c r="D384" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">600371</t>
+          <t xml:space="preserve">603067</t>
         </is>
       </c>
       <c r="E384" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">万向德农</t>
+          <t xml:space="preserve">振华股份</t>
         </is>
       </c>
       <c r="F384" s="0">
-        <v>14.97</v>
+        <v>42.31</v>
       </c>
       <c r="G384" s="4">
-        <v>0.09992652461425422</v>
+        <v>0.1001040041601664</v>
       </c>
       <c r="H384" s="4">
-        <v>0.11351905409843502</v>
+        <v>0.141151030675333</v>
       </c>
       <c r="I384" s="0" t="inlineStr">
         <is>
@@ -20771,12 +20771,12 @@
       </c>
       <c r="J384" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 万向德农（600371）归入“玉米种业+转基因玉米+新品研发”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 振华股份（603067）归入“SOFC+金属铬+铬盐龙头”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K384" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
         </is>
       </c>
       <c r="L384" s="3" t="inlineStr">
@@ -20801,22 +20801,22 @@
       </c>
       <c r="D385" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">600865</t>
+          <t xml:space="preserve">605577</t>
         </is>
       </c>
       <c r="E385" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">百大集团</t>
+          <t xml:space="preserve">龙版传媒</t>
         </is>
       </c>
       <c r="F385" s="0">
-        <v>11.51</v>
+        <v>16.2</v>
       </c>
       <c r="G385" s="4">
-        <v>0.10038240917782026</v>
+        <v>0.09979633401221989</v>
       </c>
       <c r="H385" s="4">
-        <v>0.10812020936100711</v>
+        <v>0.13719229357415072</v>
       </c>
       <c r="I385" s="0" t="inlineStr">
         <is>
@@ -20825,12 +20825,12 @@
       </c>
       <c r="J385" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 百大集团（600865）归入“商业零售+物业租赁+政府补助”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 龙版传媒（605577）归入“AI漫剧+出版发行+黑龙江国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K385" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
         </is>
       </c>
       <c r="L385" s="3" t="inlineStr">
@@ -20855,22 +20855,22 @@
       </c>
       <c r="D386" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">600127</t>
+          <t xml:space="preserve">605399</t>
         </is>
       </c>
       <c r="E386" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">金健米业</t>
+          <t xml:space="preserve">晨光新材</t>
         </is>
       </c>
       <c r="F386" s="0">
-        <v>15.18</v>
+        <v>13.06</v>
       </c>
       <c r="G386" s="4">
-        <v>0.09999999999999985</v>
+        <v>0.10025273799494538</v>
       </c>
       <c r="H386" s="4">
-        <v>0.1063382154715076</v>
+        <v>0.13472828135501905</v>
       </c>
       <c r="I386" s="0" t="inlineStr">
         <is>
@@ -20879,17 +20879,17 @@
       </c>
       <c r="J386" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 金健米业（600127）归入“粮油食品+健康食品+粮食储备”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 晨光新材（605399）归入“功能性硅烷+多基地产能”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K386" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.8 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
         </is>
       </c>
       <c r="L386" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">当日振幅较大</t>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
         </is>
       </c>
     </row>
@@ -20909,22 +20909,22 @@
       </c>
       <c r="D387" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">603101</t>
+          <t xml:space="preserve">002811</t>
         </is>
       </c>
       <c r="E387" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">汇嘉时代</t>
+          <t xml:space="preserve">郑中设计</t>
         </is>
       </c>
       <c r="F387" s="0">
-        <v>7.99</v>
+        <v>18.4</v>
       </c>
       <c r="G387" s="4">
-        <v>0.1005509641873279</v>
+        <v>0.09982068141063948</v>
       </c>
       <c r="H387" s="4">
-        <v>0.10500141405285064</v>
+        <v>0.13432758200419617</v>
       </c>
       <c r="I387" s="0" t="inlineStr">
         <is>
@@ -20933,17 +20933,17 @@
       </c>
       <c r="J387" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 汇嘉时代（603101）归入“超市调改+新疆零售+商业综合体”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 郑中设计（002811）归入“半导体投资+室内设计+软装增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K387" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 2.2 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.5 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
         </is>
       </c>
       <c r="L387" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+          <t xml:space="preserve">当日振幅较大</t>
         </is>
       </c>
     </row>
@@ -20963,22 +20963,22 @@
       </c>
       <c r="D388" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">601519</t>
+          <t xml:space="preserve">002480</t>
         </is>
       </c>
       <c r="E388" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">大智慧</t>
+          <t xml:space="preserve">新筑股份</t>
         </is>
       </c>
       <c r="F388" s="0">
-        <v>9.17</v>
+        <v>6.0</v>
       </c>
       <c r="G388" s="4">
-        <v>0.0995203836930456</v>
+        <v>0.10091743119266061</v>
       </c>
       <c r="H388" s="4">
-        <v>0.10092080653982519</v>
+        <v>0.13094730552935016</v>
       </c>
       <c r="I388" s="0" t="inlineStr">
         <is>
@@ -20987,17 +20987,17 @@
       </c>
       <c r="J388" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 大智慧（601519）归入“互联网金融+湘财吸收合并+人工智能”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 新筑股份（002480）归入“清洁能源+重大重组+四川国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K388" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.0 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
         </is>
       </c>
       <c r="L388" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
         </is>
       </c>
     </row>
@@ -21017,22 +21017,22 @@
       </c>
       <c r="D389" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">600843</t>
+          <t xml:space="preserve">603533</t>
         </is>
       </c>
       <c r="E389" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">上工申贝</t>
+          <t xml:space="preserve">掌阅科技</t>
         </is>
       </c>
       <c r="F389" s="0">
-        <v>8.18</v>
+        <v>25.44</v>
       </c>
       <c r="G389" s="4">
-        <v>0.09946236559139777</v>
+        <v>0.09987029831387817</v>
       </c>
       <c r="H389" s="4">
-        <v>0.09946147616709738</v>
+        <v>0.1307683309027502</v>
       </c>
       <c r="I389" s="0" t="inlineStr">
         <is>
@@ -21041,17 +21041,17 @@
       </c>
       <c r="J389" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 上工申贝（600843）归入“缝制设备+机器人缝制+轻型飞机”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 掌阅科技（603533）归入“AI短剧+短剧出海+数字阅读”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K389" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 2.3 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
         </is>
       </c>
       <c r="L389" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+          <t xml:space="preserve">当日振幅较大</t>
         </is>
       </c>
     </row>
@@ -21071,22 +21071,22 @@
       </c>
       <c r="D390" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">600882</t>
+          <t xml:space="preserve">002696</t>
         </is>
       </c>
       <c r="E390" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">妙可蓝多</t>
+          <t xml:space="preserve">百洋股份</t>
         </is>
       </c>
       <c r="F390" s="0">
-        <v>21.13</v>
+        <v>7.32</v>
       </c>
       <c r="G390" s="4">
-        <v>0.09994794377928162</v>
+        <v>0.10075187969924816</v>
       </c>
       <c r="H390" s="4">
-        <v>0.09737566995195442</v>
+        <v>0.1301776451903817</v>
       </c>
       <c r="I390" s="0" t="inlineStr">
         <is>
@@ -21095,17 +21095,17 @@
       </c>
       <c r="J390" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 妙可蓝多（600882）归入“业绩增长+奶酪深加工+奶酪产品”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 百洋股份（002696）归入“水产品加工+水产饲料+青岛国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K390" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 3.3 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
         </is>
       </c>
       <c r="L390" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+          <t xml:space="preserve">当日振幅较大</t>
         </is>
       </c>
     </row>
@@ -21125,22 +21125,22 @@
       </c>
       <c r="D391" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">603155</t>
+          <t xml:space="preserve">000710</t>
         </is>
       </c>
       <c r="E391" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">新亚强</t>
+          <t xml:space="preserve">贝瑞基因</t>
         </is>
       </c>
       <c r="F391" s="0">
-        <v>15.43</v>
+        <v>11.3</v>
       </c>
       <c r="G391" s="4">
-        <v>0.09978617248752686</v>
+        <v>0.10029211295034092</v>
       </c>
       <c r="H391" s="4">
-        <v>0.093100809118559</v>
+        <v>0.12541445320678993</v>
       </c>
       <c r="I391" s="0" t="inlineStr">
         <is>
@@ -21149,17 +21149,17 @@
       </c>
       <c r="J391" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 新亚强（603155）归入“有机硅+电子化学品+国资控股”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 贝瑞基因（000710）归入“AI医疗+三代测序+基因检测”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K391" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.6 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
         </is>
       </c>
       <c r="L391" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">当日振幅较大</t>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
         </is>
       </c>
     </row>
@@ -21179,22 +21179,22 @@
       </c>
       <c r="D392" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">002692</t>
+          <t xml:space="preserve">605287</t>
         </is>
       </c>
       <c r="E392" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">远程股份</t>
+          <t xml:space="preserve">德才股份</t>
         </is>
       </c>
       <c r="F392" s="0">
-        <v>4.76</v>
+        <v>40.18</v>
       </c>
       <c r="G392" s="4">
-        <v>0.09930715935334877</v>
+        <v>0.09991787571858746</v>
       </c>
       <c r="H392" s="4">
-        <v>0.09197641965414466</v>
+        <v>0.12511875881442747</v>
       </c>
       <c r="I392" s="0" t="inlineStr">
         <is>
@@ -21203,17 +21203,17 @@
       </c>
       <c r="J392" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 远程股份（002692）归入“电线电缆+电网应用+数据中心电缆+参股半导体”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 德才股份（605287）归入“AI漫剧+火山引擎合作+建筑装饰”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K392" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.6 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
         </is>
       </c>
       <c r="L392" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
         </is>
       </c>
     </row>
@@ -21233,22 +21233,22 @@
       </c>
       <c r="D393" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">600478</t>
+          <t xml:space="preserve">605168</t>
         </is>
       </c>
       <c r="E393" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">科力远</t>
+          <t xml:space="preserve">三人行</t>
         </is>
       </c>
       <c r="F393" s="0">
-        <v>5.1</v>
+        <v>52.1</v>
       </c>
       <c r="G393" s="4">
-        <v>0.09913793103448265</v>
+        <v>0.10008445945945944</v>
       </c>
       <c r="H393" s="4">
-        <v>0.09163868997374895</v>
+        <v>0.1219243685436212</v>
       </c>
       <c r="I393" s="0" t="inlineStr">
         <is>
@@ -21257,17 +21257,17 @@
       </c>
       <c r="J393" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 科力远（600478）归入“固态电池+储能电站+电池材料”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 三人行（605168）归入“数据中心+AI营销+体育营销”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K393" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 2.6 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
         </is>
       </c>
       <c r="L393" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+          <t xml:space="preserve">当日振幅较大</t>
         </is>
       </c>
     </row>
@@ -21287,22 +21287,22 @@
       </c>
       <c r="D394" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">601069</t>
+          <t xml:space="preserve">600354</t>
         </is>
       </c>
       <c r="E394" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">西部黄金</t>
+          <t xml:space="preserve">敦煌种业</t>
         </is>
       </c>
       <c r="F394" s="0">
-        <v>26.55</v>
+        <v>9.99</v>
       </c>
       <c r="G394" s="4">
-        <v>0.09983429991715</v>
+        <v>0.10022026431718058</v>
       </c>
       <c r="H394" s="4">
-        <v>0.0893103099953754</v>
+        <v>0.12136476202095832</v>
       </c>
       <c r="I394" s="0" t="inlineStr">
         <is>
@@ -21311,12 +21311,12 @@
       </c>
       <c r="J394" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 西部黄金（601069）归入“黄金业务+股东合并+业绩增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 敦煌种业（600354）归入“玉米种业+核心品种+商业化育种”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K394" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
         </is>
       </c>
       <c r="L394" s="3" t="inlineStr">
@@ -21341,22 +21341,22 @@
       </c>
       <c r="D395" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">600621</t>
+          <t xml:space="preserve">601929</t>
         </is>
       </c>
       <c r="E395" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">华鑫股份</t>
+          <t xml:space="preserve">吉视传媒</t>
         </is>
       </c>
       <c r="F395" s="0">
-        <v>14.48</v>
+        <v>2.5</v>
       </c>
       <c r="G395" s="4">
-        <v>0.10030395136778125</v>
+        <v>0.10132158590308361</v>
       </c>
       <c r="H395" s="4">
-        <v>0.08895869470161645</v>
+        <v>0.12062836714957566</v>
       </c>
       <c r="I395" s="0" t="inlineStr">
         <is>
@@ -21365,17 +21365,17 @@
       </c>
       <c r="J395" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 华鑫股份（600621）归入“证券经纪+金融科技+上海国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 吉视传媒（601929）归入“智慧广电+AI微短剧+AI应用+算力租赁”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K395" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 2.3 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.5 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
         </is>
       </c>
       <c r="L395" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
         </is>
       </c>
     </row>
@@ -21395,22 +21395,22 @@
       </c>
       <c r="D396" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">605188</t>
+          <t xml:space="preserve">600629</t>
         </is>
       </c>
       <c r="E396" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">国光连锁</t>
+          <t xml:space="preserve">华建集团</t>
         </is>
       </c>
       <c r="F396" s="0">
-        <v>13.84</v>
+        <v>18.02</v>
       </c>
       <c r="G396" s="4">
-        <v>0.10015898251192358</v>
+        <v>0.10012210012210021</v>
       </c>
       <c r="H396" s="4">
-        <v>0.08770315332017303</v>
+        <v>0.11996099391712531</v>
       </c>
       <c r="I396" s="0" t="inlineStr">
         <is>
@@ -21419,12 +21419,12 @@
       </c>
       <c r="J396" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 国光连锁（605188）归入“零售主业+商业综合体+半年报增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华建集团（600629）归入“上海微电子相关+工程设计+子公司重整获批+上海国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K396" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
         </is>
       </c>
       <c r="L396" s="3" t="inlineStr">
@@ -21449,22 +21449,22 @@
       </c>
       <c r="D397" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">000546</t>
+          <t xml:space="preserve">000736</t>
         </is>
       </c>
       <c r="E397" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">金圆股份</t>
+          <t xml:space="preserve">中交发展</t>
         </is>
       </c>
       <c r="F397" s="0">
-        <v>4.77</v>
+        <v>5.21</v>
       </c>
       <c r="G397" s="4">
-        <v>0.09907834101382473</v>
+        <v>0.09915611814345994</v>
       </c>
       <c r="H397" s="4">
-        <v>0.08104958860869282</v>
+        <v>0.11873847888032196</v>
       </c>
       <c r="I397" s="0" t="inlineStr">
         <is>
@@ -21473,17 +21473,17 @@
       </c>
       <c r="J397" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 金圆股份（000546）归入“盐湖提锂+锂矿布局+固废危废资源化”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 中交发展（000736）归入“轻资产运营+物业服务+中交集团协同”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K397" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 2.3 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.3 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
         </is>
       </c>
       <c r="L397" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
         </is>
       </c>
     </row>
@@ -21503,22 +21503,22 @@
       </c>
       <c r="D398" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">002675</t>
+          <t xml:space="preserve">000892</t>
         </is>
       </c>
       <c r="E398" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">东诚药业</t>
+          <t xml:space="preserve">欢瑞世纪</t>
         </is>
       </c>
       <c r="F398" s="0">
-        <v>13.89</v>
+        <v>4.85</v>
       </c>
       <c r="G398" s="4">
-        <v>0.09976247030878849</v>
+        <v>0.09977324263038545</v>
       </c>
       <c r="H398" s="4">
-        <v>0.07732817978102424</v>
+        <v>0.1182517835158854</v>
       </c>
       <c r="I398" s="0" t="inlineStr">
         <is>
@@ -21527,17 +21527,17 @@
       </c>
       <c r="J398" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">题材归因标签只能说明当日市场将 东诚药业（002675）归入“核医药+创新药+股份回购”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 欢瑞世纪（000892）归入“AI漫剧+互动影游+影视制作”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
       <c r="K398" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 5.4 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
         </is>
       </c>
       <c r="L398" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+          <t xml:space="preserve">当日振幅较大</t>
         </is>
       </c>
     </row>
@@ -21557,39 +21557,1335 @@
       </c>
       <c r="D399" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">600371</t>
+        </is>
+      </c>
+      <c r="E399" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">万向德农</t>
+        </is>
+      </c>
+      <c r="F399" s="0">
+        <v>14.97</v>
+      </c>
+      <c r="G399" s="4">
+        <v>0.09992652461425422</v>
+      </c>
+      <c r="H399" s="4">
+        <v>0.11819095093567711</v>
+      </c>
+      <c r="I399" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J399" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 万向德农（600371）归入“玉米种业+转基因玉米+新品研发”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K399" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L399" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B400" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C400" s="0">
+        <v>28</v>
+      </c>
+      <c r="D400" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600865</t>
+        </is>
+      </c>
+      <c r="E400" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">百大集团</t>
+        </is>
+      </c>
+      <c r="F400" s="0">
+        <v>11.51</v>
+      </c>
+      <c r="G400" s="4">
+        <v>0.10038240917782026</v>
+      </c>
+      <c r="H400" s="4">
+        <v>0.11253880769948402</v>
+      </c>
+      <c r="I400" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J400" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 百大集团（600865）归入“商业零售+物业租赁+政府补助”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K400" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L400" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B401" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C401" s="0">
+        <v>29</v>
+      </c>
+      <c r="D401" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600127</t>
+        </is>
+      </c>
+      <c r="E401" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金健米业</t>
+        </is>
+      </c>
+      <c r="F401" s="0">
+        <v>15.18</v>
+      </c>
+      <c r="G401" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H401" s="4">
+        <v>0.11078260170710075</v>
+      </c>
+      <c r="I401" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J401" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 金健米业（600127）归入“粮油食品+健康食品+粮食储备”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K401" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L401" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B402" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C402" s="0">
+        <v>30</v>
+      </c>
+      <c r="D402" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002979</t>
+        </is>
+      </c>
+      <c r="E402" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雷赛智能</t>
+        </is>
+      </c>
+      <c r="F402" s="0">
+        <v>55.58</v>
+      </c>
+      <c r="G402" s="4">
+        <v>0.09994062932911142</v>
+      </c>
+      <c r="H402" s="4">
+        <v>0.11071269004021964</v>
+      </c>
+      <c r="I402" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J402" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 雷赛智能（002979）归入“人形机器人+伺服系统+半年报增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K402" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.3 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L402" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B403" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C403" s="0">
+        <v>31</v>
+      </c>
+      <c r="D403" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601595</t>
+        </is>
+      </c>
+      <c r="E403" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上海电影</t>
+        </is>
+      </c>
+      <c r="F403" s="0">
+        <v>24.74</v>
+      </c>
+      <c r="G403" s="4">
+        <v>0.10004446420631385</v>
+      </c>
+      <c r="H403" s="4">
+        <v>0.11000936591426773</v>
+      </c>
+      <c r="I403" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J403" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 上海电影（601595）归入“AI影视+知识产权运营+院线经营”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K403" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.7 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L403" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B404" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C404" s="0">
+        <v>32</v>
+      </c>
+      <c r="D404" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603216</t>
+        </is>
+      </c>
+      <c r="E404" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">梦天家居</t>
+        </is>
+      </c>
+      <c r="F404" s="0">
+        <v>24.1</v>
+      </c>
+      <c r="G404" s="4">
+        <v>0.09995435874030134</v>
+      </c>
+      <c r="H404" s="4">
+        <v>0.10876559498356105</v>
+      </c>
+      <c r="I404" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J404" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 梦天家居（603216）归入“全屋定制+智能制造+功率半导体投资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K404" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L404" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B405" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C405" s="0">
+        <v>33</v>
+      </c>
+      <c r="D405" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603101</t>
+        </is>
+      </c>
+      <c r="E405" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汇嘉时代</t>
+        </is>
+      </c>
+      <c r="F405" s="0">
+        <v>7.99</v>
+      </c>
+      <c r="G405" s="4">
+        <v>0.1005509641873279</v>
+      </c>
+      <c r="H405" s="4">
+        <v>0.10853574281193065</v>
+      </c>
+      <c r="I405" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J405" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 汇嘉时代（603101）归入“超市调改+新疆零售+商业综合体”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K405" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.3 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L405" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B406" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C406" s="0">
+        <v>34</v>
+      </c>
+      <c r="D406" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600843</t>
+        </is>
+      </c>
+      <c r="E406" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上工申贝</t>
+        </is>
+      </c>
+      <c r="F406" s="0">
+        <v>8.18</v>
+      </c>
+      <c r="G406" s="4">
+        <v>0.09946236559139777</v>
+      </c>
+      <c r="H406" s="4">
+        <v>0.10318542009689037</v>
+      </c>
+      <c r="I406" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J406" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 上工申贝（600843）归入“缝制设备+机器人缝制+轻型飞机”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K406" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.3 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L406" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B407" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C407" s="0">
+        <v>35</v>
+      </c>
+      <c r="D407" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601519</t>
+        </is>
+      </c>
+      <c r="E407" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大智慧</t>
+        </is>
+      </c>
+      <c r="F407" s="0">
+        <v>9.17</v>
+      </c>
+      <c r="G407" s="4">
+        <v>0.0995203836930456</v>
+      </c>
+      <c r="H407" s="4">
+        <v>0.10269695615024685</v>
+      </c>
+      <c r="I407" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J407" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 大智慧（601519）归入“互联网金融+湘财吸收合并+人工智能”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K407" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.3 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L407" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B408" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C408" s="0">
+        <v>36</v>
+      </c>
+      <c r="D408" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600882</t>
+        </is>
+      </c>
+      <c r="E408" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">妙可蓝多</t>
+        </is>
+      </c>
+      <c r="F408" s="0">
+        <v>21.13</v>
+      </c>
+      <c r="G408" s="4">
+        <v>0.09994794377928162</v>
+      </c>
+      <c r="H408" s="4">
+        <v>0.10012582153928166</v>
+      </c>
+      <c r="I408" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J408" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 妙可蓝多（600882）归入“业绩增长+奶酪深加工+奶酪产品”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K408" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.4 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L408" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B409" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C409" s="0">
+        <v>37</v>
+      </c>
+      <c r="D409" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002181</t>
+        </is>
+      </c>
+      <c r="E409" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">粤 传 媒</t>
+        </is>
+      </c>
+      <c r="F409" s="0">
+        <v>9.39</v>
+      </c>
+      <c r="G409" s="4">
+        <v>0.09953161592505877</v>
+      </c>
+      <c r="H409" s="4">
+        <v>0.09728202926319825</v>
+      </c>
+      <c r="I409" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J409" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 粤 传 媒（002181）归入“AI视频+微短剧+体育传媒”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K409" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L409" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B410" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C410" s="0">
+        <v>38</v>
+      </c>
+      <c r="D410" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603155</t>
+        </is>
+      </c>
+      <c r="E410" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新亚强</t>
+        </is>
+      </c>
+      <c r="F410" s="0">
+        <v>15.43</v>
+      </c>
+      <c r="G410" s="4">
+        <v>0.09978617248752686</v>
+      </c>
+      <c r="H410" s="4">
+        <v>0.09667024747193552</v>
+      </c>
+      <c r="I410" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J410" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 新亚强（603155）归入“有机硅+电子化学品+国资控股”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K410" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.2 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L410" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B411" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C411" s="0">
+        <v>39</v>
+      </c>
+      <c r="D411" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002692</t>
+        </is>
+      </c>
+      <c r="E411" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">远程股份</t>
+        </is>
+      </c>
+      <c r="F411" s="0">
+        <v>4.76</v>
+      </c>
+      <c r="G411" s="4">
+        <v>0.09930715935334877</v>
+      </c>
+      <c r="H411" s="4">
+        <v>0.09538162018676917</v>
+      </c>
+      <c r="I411" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J411" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 远程股份（002692）归入“电线电缆+电网应用+数据中心电缆+参股半导体”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K411" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.4 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L411" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B412" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C412" s="0">
+        <v>40</v>
+      </c>
+      <c r="D412" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002343</t>
+        </is>
+      </c>
+      <c r="E412" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">慈文传媒</t>
+        </is>
+      </c>
+      <c r="F412" s="0">
+        <v>6.08</v>
+      </c>
+      <c r="G412" s="4">
+        <v>0.09945750452079573</v>
+      </c>
+      <c r="H412" s="4">
+        <v>0.09538027477552043</v>
+      </c>
+      <c r="I412" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J412" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 慈文传媒（002343）归入“微短剧+影视IP+泛文化”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K412" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L412" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B413" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C413" s="0">
+        <v>41</v>
+      </c>
+      <c r="D413" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002317</t>
+        </is>
+      </c>
+      <c r="E413" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">众生药业</t>
+        </is>
+      </c>
+      <c r="F413" s="0">
+        <v>25.49</v>
+      </c>
+      <c r="G413" s="4">
+        <v>0.10012947777298219</v>
+      </c>
+      <c r="H413" s="4">
+        <v>0.09447223988922465</v>
+      </c>
+      <c r="I413" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J413" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 众生药业（002317）归入“减肥药+脂肪肝药+创新药”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K413" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.3 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L413" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B414" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C414" s="0">
+        <v>42</v>
+      </c>
+      <c r="D414" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600478</t>
+        </is>
+      </c>
+      <c r="E414" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">科力远</t>
+        </is>
+      </c>
+      <c r="F414" s="0">
+        <v>5.1</v>
+      </c>
+      <c r="G414" s="4">
+        <v>0.09913793103448265</v>
+      </c>
+      <c r="H414" s="4">
+        <v>0.09445534071005474</v>
+      </c>
+      <c r="I414" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J414" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 科力远（600478）归入“固态电池+储能电站+电池材料”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K414" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.7 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L414" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B415" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C415" s="0">
+        <v>43</v>
+      </c>
+      <c r="D415" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601118</t>
+        </is>
+      </c>
+      <c r="E415" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">海南橡胶</t>
+        </is>
+      </c>
+      <c r="F415" s="0">
+        <v>7.16</v>
+      </c>
+      <c r="G415" s="4">
+        <v>0.09984639016897079</v>
+      </c>
+      <c r="H415" s="4">
+        <v>0.0938975325373546</v>
+      </c>
+      <c r="I415" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J415" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 海南橡胶（601118）归入“天然橡胶+全产业链+橡胶科技”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K415" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L415" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B416" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C416" s="0">
+        <v>44</v>
+      </c>
+      <c r="D416" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601069</t>
+        </is>
+      </c>
+      <c r="E416" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">西部黄金</t>
+        </is>
+      </c>
+      <c r="F416" s="0">
+        <v>26.55</v>
+      </c>
+      <c r="G416" s="4">
+        <v>0.09983429991715</v>
+      </c>
+      <c r="H416" s="4">
+        <v>0.0922009503734087</v>
+      </c>
+      <c r="I416" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J416" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 西部黄金（601069）归入“黄金业务+股东合并+业绩增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K416" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L416" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B417" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C417" s="0">
+        <v>45</v>
+      </c>
+      <c r="D417" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605188</t>
+        </is>
+      </c>
+      <c r="E417" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">国光连锁</t>
+        </is>
+      </c>
+      <c r="F417" s="0">
+        <v>13.84</v>
+      </c>
+      <c r="G417" s="4">
+        <v>0.10015898251192358</v>
+      </c>
+      <c r="H417" s="4">
+        <v>0.09126095642228424</v>
+      </c>
+      <c r="I417" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J417" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 国光连锁（605188）归入“零售主业+商业综合体+半年报增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K417" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L417" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B418" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C418" s="0">
+        <v>46</v>
+      </c>
+      <c r="D418" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600621</t>
+        </is>
+      </c>
+      <c r="E418" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华鑫股份</t>
+        </is>
+      </c>
+      <c r="F418" s="0">
+        <v>14.48</v>
+      </c>
+      <c r="G418" s="4">
+        <v>0.10030395136778125</v>
+      </c>
+      <c r="H418" s="4">
+        <v>0.09090271444867465</v>
+      </c>
+      <c r="I418" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J418" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华鑫股份（600621）归入“证券经纪+金融科技+上海国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K418" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.5 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L418" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B419" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C419" s="0">
+        <v>47</v>
+      </c>
+      <c r="D419" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601566</t>
+        </is>
+      </c>
+      <c r="E419" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">九牧王</t>
+        </is>
+      </c>
+      <c r="F419" s="0">
+        <v>10.14</v>
+      </c>
+      <c r="G419" s="4">
+        <v>0.09978308026030369</v>
+      </c>
+      <c r="H419" s="4">
+        <v>0.08888876719384292</v>
+      </c>
+      <c r="I419" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J419" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 九牧王（601566）归入“男裤龙头+零售消费+太空裤”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K419" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L419" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B420" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C420" s="0">
+        <v>48</v>
+      </c>
+      <c r="D420" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000546</t>
+        </is>
+      </c>
+      <c r="E420" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金圆股份</t>
+        </is>
+      </c>
+      <c r="F420" s="0">
+        <v>4.77</v>
+      </c>
+      <c r="G420" s="4">
+        <v>0.09907834101382473</v>
+      </c>
+      <c r="H420" s="4">
+        <v>0.0837232523675397</v>
+      </c>
+      <c r="I420" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J420" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 金圆股份（000546）归入“盐湖提锂+锂矿布局+固废危废资源化”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K420" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.4 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L420" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B421" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C421" s="0">
+        <v>49</v>
+      </c>
+      <c r="D421" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600715</t>
+        </is>
+      </c>
+      <c r="E421" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文投控股</t>
+        </is>
+      </c>
+      <c r="F421" s="0">
+        <v>1.76</v>
+      </c>
+      <c r="G421" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H421" s="4">
+        <v>0.0804549045784452</v>
+      </c>
+      <c r="I421" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J421" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 文投控股（600715）归入“AI漫剧+影视院线+北京国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K421" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.7 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L421" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B422" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C422" s="0">
+        <v>50</v>
+      </c>
+      <c r="D422" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002675</t>
+        </is>
+      </c>
+      <c r="E422" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东诚药业</t>
+        </is>
+      </c>
+      <c r="F422" s="0">
+        <v>13.89</v>
+      </c>
+      <c r="G422" s="4">
+        <v>0.09976247030878849</v>
+      </c>
+      <c r="H422" s="4">
+        <v>0.07907411772557696</v>
+      </c>
+      <c r="I422" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J422" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 东诚药业（002675）归入“核医药+创新药+股份回购”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K422" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 5.6 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L422" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B423" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
+        </is>
+      </c>
+      <c r="C423" s="0">
+        <v>51</v>
+      </c>
+      <c r="D423" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">000420</t>
         </is>
       </c>
-      <c r="E399" s="0" t="inlineStr">
+      <c r="E423" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">吉林化纤</t>
         </is>
       </c>
-      <c r="F399" s="0">
+      <c r="F423" s="0">
         <v>3.81</v>
       </c>
-      <c r="G399" s="4">
+      <c r="G423" s="4">
         <v>0.10115606936416179</v>
       </c>
-      <c r="H399" s="4">
-        <v>0.07660923967091054</v>
-      </c>
-      <c r="I399" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">theme_only</t>
-        </is>
-      </c>
-      <c r="J399" s="3" t="inlineStr">
+      <c r="H423" s="4">
+        <v>0.07732300998646234</v>
+      </c>
+      <c r="I423" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J423" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">题材归因标签只能说明当日市场将 吉林化纤（000420）归入“碳纤维+粘胶长丝+国企”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
         </is>
       </c>
-      <c r="K399" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">截至运行时当前价格贴近日内最高价，盘中价格维持强势。截至运行时成交量约为20日均量的 4.1 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 37 家涨停，其中首板 27 家、2板及以上 10 家。</t>
-        </is>
-      </c>
-      <c r="L399" s="3" t="inlineStr">
+      <c r="K423" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.4 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 63 家涨停，其中首板 51 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L423" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
         </is>
@@ -21601,7 +22897,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M83"/>
+  <dimension ref="A1:M93"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -26434,6 +27730,596 @@
       <c r="M83" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">11.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B84" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C84" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D84" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600812</t>
+        </is>
+      </c>
+      <c r="E84" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华北制药</t>
+        </is>
+      </c>
+      <c r="F84" s="4">
+        <v>0.3070699843902628</v>
+      </c>
+      <c r="G84" s="4">
+        <v>0.021897810218977964</v>
+      </c>
+      <c r="H84" s="4">
+        <v>0.10036496350364965</v>
+      </c>
+      <c r="I84" s="4">
+        <v>0.10036496350364965</v>
+      </c>
+      <c r="J84" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K84" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +10.04%</t>
+        </is>
+      </c>
+      <c r="L84" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M84" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B85" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C85" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D85" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603073</t>
+        </is>
+      </c>
+      <c r="E85" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">彩蝶实业</t>
+        </is>
+      </c>
+      <c r="F85" s="4">
+        <v>0.1663143750377855</v>
+      </c>
+      <c r="G85" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H85" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I85" s="4">
+        <v>-0.10013060513713523</v>
+      </c>
+      <c r="J85" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K85" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -10.01%</t>
+        </is>
+      </c>
+      <c r="L85" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M85" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B86" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C86" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="D86" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002774</t>
+        </is>
+      </c>
+      <c r="E86" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">快意电梯</t>
+        </is>
+      </c>
+      <c r="F86" s="4">
+        <v>0.16450409509853967</v>
+      </c>
+      <c r="G86" s="4">
+        <v>-0.009453781512605008</v>
+      </c>
+      <c r="H86" s="4">
+        <v>0.01313025210084029</v>
+      </c>
+      <c r="I86" s="4">
+        <v>-0.011029411764705954</v>
+      </c>
+      <c r="J86" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K86" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -1.10%</t>
+        </is>
+      </c>
+      <c r="L86" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M86" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B87" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C87" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="D87" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600026</t>
+        </is>
+      </c>
+      <c r="E87" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中远海能</t>
+        </is>
+      </c>
+      <c r="F87" s="4">
+        <v>0.16172007665372992</v>
+      </c>
+      <c r="G87" s="4">
+        <v>0.019893899204243892</v>
+      </c>
+      <c r="H87" s="4">
+        <v>0.043324491600353676</v>
+      </c>
+      <c r="I87" s="4">
+        <v>0.038461538461538325</v>
+      </c>
+      <c r="J87" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K87" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +3.85%</t>
+        </is>
+      </c>
+      <c r="L87" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M87" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B88" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C88" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="D88" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601956</t>
+        </is>
+      </c>
+      <c r="E88" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东贝集团</t>
+        </is>
+      </c>
+      <c r="F88" s="4">
+        <v>0.1445400213740262</v>
+      </c>
+      <c r="G88" s="4">
+        <v>0.0126811594202898</v>
+      </c>
+      <c r="H88" s="4">
+        <v>0.0126811594202898</v>
+      </c>
+      <c r="I88" s="4">
+        <v>-0.03623188405797084</v>
+      </c>
+      <c r="J88" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K88" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -3.62%</t>
+        </is>
+      </c>
+      <c r="L88" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M88" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B89" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C89" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="D89" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002869</t>
+        </is>
+      </c>
+      <c r="E89" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金溢科技</t>
+        </is>
+      </c>
+      <c r="F89" s="4">
+        <v>0.1411004859874679</v>
+      </c>
+      <c r="G89" s="4">
+        <v>-0.04493207941483801</v>
+      </c>
+      <c r="H89" s="4">
+        <v>0.03343782654127492</v>
+      </c>
+      <c r="I89" s="4">
+        <v>0.016196447230929945</v>
+      </c>
+      <c r="J89" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K89" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +1.62%</t>
+        </is>
+      </c>
+      <c r="L89" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M89" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="D90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002687</t>
+        </is>
+      </c>
+      <c r="E90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">乔治白</t>
+        </is>
+      </c>
+      <c r="F90" s="4">
+        <v>0.13926416884083795</v>
+      </c>
+      <c r="G90" s="4">
+        <v>0.043973941368078195</v>
+      </c>
+      <c r="H90" s="4">
+        <v>0.07003257328990231</v>
+      </c>
+      <c r="I90" s="4">
+        <v>0.019543973941368087</v>
+      </c>
+      <c r="J90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +1.95%</t>
+        </is>
+      </c>
+      <c r="L90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="D91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601975</t>
+        </is>
+      </c>
+      <c r="E91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">招商南油</t>
+        </is>
+      </c>
+      <c r="F91" s="4">
+        <v>0.13805473884436545</v>
+      </c>
+      <c r="G91" s="4">
+        <v>0.00201207243460777</v>
+      </c>
+      <c r="H91" s="4">
+        <v>0.02213279678068414</v>
+      </c>
+      <c r="I91" s="4">
+        <v>-0.03822937625754519</v>
+      </c>
+      <c r="J91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -3.82%</t>
+        </is>
+      </c>
+      <c r="L91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B92" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C92" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="D92" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002951</t>
+        </is>
+      </c>
+      <c r="E92" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金时科技</t>
+        </is>
+      </c>
+      <c r="F92" s="4">
+        <v>0.1378956851839974</v>
+      </c>
+      <c r="G92" s="4">
+        <v>0.04834012813046007</v>
+      </c>
+      <c r="H92" s="4">
+        <v>0.06930693069306915</v>
+      </c>
+      <c r="I92" s="4">
+        <v>-0.03028538147932458</v>
+      </c>
+      <c r="J92" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K92" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -3.03%</t>
+        </is>
+      </c>
+      <c r="L92" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M92" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="B93" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="C93" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="D93" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600617</t>
+        </is>
+      </c>
+      <c r="E93" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">国新能源</t>
+        </is>
+      </c>
+      <c r="F93" s="4">
+        <v>0.13339166666491956</v>
+      </c>
+      <c r="G93" s="4">
+        <v>0.09625668449197855</v>
+      </c>
+      <c r="H93" s="4">
+        <v>0.09625668449197855</v>
+      </c>
+      <c r="I93" s="4">
+        <v>-0.005347593582887722</v>
+      </c>
+      <c r="J93" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K93" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -0.53%</t>
+        </is>
+      </c>
+      <c r="L93" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M93" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.72</t>
         </is>
       </c>
     </row>
@@ -26525,28 +28411,28 @@
         </is>
       </c>
       <c r="B3" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" s="4">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F3" s="4">
-        <v>0.07894736842105263</v>
+        <v>0.2413793103448276</v>
       </c>
       <c r="G3" s="0">
-        <v>3.166666666666667</v>
+        <v>1.3809523809523807</v>
       </c>
       <c r="H3" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" s="4">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -26556,28 +28442,28 @@
         </is>
       </c>
       <c r="B4" s="0">
+        <v>9</v>
+      </c>
+      <c r="C4" s="0">
+        <v>27</v>
+      </c>
+      <c r="D4" s="0">
         <v>8</v>
       </c>
-      <c r="C4" s="0">
-        <v>24</v>
-      </c>
-      <c r="D4" s="0">
-        <v>7</v>
-      </c>
       <c r="E4" s="4">
-        <v>0.2916666666666667</v>
+        <v>0.2962962962962963</v>
       </c>
       <c r="F4" s="4">
-        <v>0.07894736842105263</v>
+        <v>0.2413793103448276</v>
       </c>
       <c r="G4" s="0">
-        <v>3.694444444444445</v>
+        <v>1.2275132275132274</v>
       </c>
       <c r="H4" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I4" s="4">
-        <v>0.5</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="5">
@@ -26587,28 +28473,28 @@
         </is>
       </c>
       <c r="B5" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="0">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D5" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" s="4">
-        <v>0.2708333333333333</v>
+        <v>0.25925925925925924</v>
       </c>
       <c r="F5" s="4">
-        <v>0.07894736842105263</v>
+        <v>0.2413793103448276</v>
       </c>
       <c r="G5" s="0">
-        <v>3.4305555555555554</v>
+        <v>1.074074074074074</v>
       </c>
       <c r="H5" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I5" s="4">
-        <v>0.75</v>
+        <v>0.7777777777777778</v>
       </c>
     </row>
     <row r="6">
@@ -26618,28 +28504,28 @@
         </is>
       </c>
       <c r="B6" s="0">
+        <v>9</v>
+      </c>
+      <c r="C6" s="0">
+        <v>90</v>
+      </c>
+      <c r="D6" s="0">
+        <v>20</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.2413793103448276</v>
+      </c>
+      <c r="G6" s="0">
+        <v>0.9206349206349206</v>
+      </c>
+      <c r="H6" s="0">
         <v>8</v>
       </c>
-      <c r="C6" s="0">
-        <v>80</v>
-      </c>
-      <c r="D6" s="0">
-        <v>19</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0.2375</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0.07894736842105263</v>
-      </c>
-      <c r="G6" s="0">
-        <v>3.0083333333333333</v>
-      </c>
-      <c r="H6" s="0">
-        <v>7</v>
-      </c>
       <c r="I6" s="4">
-        <v>0.875</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="7">

--- a/docs/downloads/latest.xlsx
+++ b/docs/downloads/latest.xlsx
@@ -20168,7 +20168,7 @@
         <v>0.10019267822736033</v>
       </c>
       <c r="H373" s="4">
-        <v>0.20573179563641128</v>
+        <v>0.2041876142540754</v>
       </c>
       <c r="I373" s="0" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         <v>0.10019646365422386</v>
       </c>
       <c r="H374" s="4">
-        <v>0.19015571837609968</v>
+        <v>0.18870067242964758</v>
       </c>
       <c r="I374" s="0" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>0.09994739610731183</v>
       </c>
       <c r="H375" s="4">
-        <v>0.1859243286736807</v>
+        <v>0.18449428456738695</v>
       </c>
       <c r="I375" s="0" t="inlineStr">
         <is>
@@ -20330,7 +20330,7 @@
         <v>0.09992223950233292</v>
       </c>
       <c r="H376" s="4">
-        <v>0.18283374681498385</v>
+        <v>0.18142217643889993</v>
       </c>
       <c r="I376" s="0" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>0.10000000000000009</v>
       </c>
       <c r="H377" s="4">
-        <v>0.15804911220917978</v>
+        <v>0.15679217700793713</v>
       </c>
       <c r="I377" s="0" t="inlineStr">
         <is>
@@ -20438,7 +20438,7 @@
         <v>0.10043668122270732</v>
       </c>
       <c r="H378" s="4">
-        <v>0.15732083460475293</v>
+        <v>0.156068617649732</v>
       </c>
       <c r="I378" s="0" t="inlineStr">
         <is>
@@ -20492,7 +20492,7 @@
         <v>0.10023310023310007</v>
       </c>
       <c r="H379" s="4">
-        <v>0.1500063889703599</v>
+        <v>0.1488021116835222</v>
       </c>
       <c r="I379" s="0" t="inlineStr">
         <is>
@@ -20546,7 +20546,7 @@
         <v>0.09936908517350161</v>
       </c>
       <c r="H380" s="4">
-        <v>0.14962503029396548</v>
+        <v>0.14842328001109517</v>
       </c>
       <c r="I380" s="0" t="inlineStr">
         <is>
@@ -20600,7 +20600,7 @@
         <v>0.09974093264248719</v>
       </c>
       <c r="H381" s="4">
-        <v>0.14907665277852725</v>
+        <v>0.14787854100314873</v>
       </c>
       <c r="I381" s="0" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>0.10031746031746014</v>
       </c>
       <c r="H382" s="4">
-        <v>0.14832804194544053</v>
+        <v>0.14713490634341067</v>
       </c>
       <c r="I382" s="0" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>0.10014727540500722</v>
       </c>
       <c r="H383" s="4">
-        <v>0.1414878545492124</v>
+        <v>0.14034067408810774</v>
       </c>
       <c r="I383" s="0" t="inlineStr">
         <is>
@@ -20762,7 +20762,7 @@
         <v>0.1001040041601664</v>
       </c>
       <c r="H384" s="4">
-        <v>0.141151030675333</v>
+        <v>0.14000613580991667</v>
       </c>
       <c r="I384" s="0" t="inlineStr">
         <is>
@@ -20816,7 +20816,7 @@
         <v>0.09979633401221989</v>
       </c>
       <c r="H385" s="4">
-        <v>0.13719229357415072</v>
+        <v>0.13607442113045184</v>
       </c>
       <c r="I385" s="0" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>0.10025273799494538</v>
       </c>
       <c r="H386" s="4">
-        <v>0.13472828135501905</v>
+        <v>0.13362737674194355</v>
       </c>
       <c r="I386" s="0" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>0.09982068141063948</v>
       </c>
       <c r="H387" s="4">
-        <v>0.13432758200419617</v>
+        <v>0.1332294474768585</v>
       </c>
       <c r="I387" s="0" t="inlineStr">
         <is>
@@ -20978,7 +20978,7 @@
         <v>0.10091743119266061</v>
       </c>
       <c r="H388" s="4">
-        <v>0.13094730552935016</v>
+        <v>0.1298726591423671</v>
       </c>
       <c r="I388" s="0" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>0.09987029831387817</v>
       </c>
       <c r="H389" s="4">
-        <v>0.1307683309027502</v>
+        <v>0.12969493410998403</v>
       </c>
       <c r="I389" s="0" t="inlineStr">
         <is>
@@ -21086,7 +21086,7 @@
         <v>0.10075187969924816</v>
       </c>
       <c r="H390" s="4">
-        <v>0.1301776451903817</v>
+        <v>0.12910837680655898</v>
       </c>
       <c r="I390" s="0" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>0.10029211295034092</v>
       </c>
       <c r="H391" s="4">
-        <v>0.12541445320678993</v>
+        <v>0.12437871475319434</v>
       </c>
       <c r="I391" s="0" t="inlineStr">
         <is>
@@ -21194,7 +21194,7 @@
         <v>0.09991787571858746</v>
       </c>
       <c r="H392" s="4">
-        <v>0.12511875881442747</v>
+        <v>0.12408511589260389</v>
       </c>
       <c r="I392" s="0" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         <v>0.10008445945945944</v>
       </c>
       <c r="H393" s="4">
-        <v>0.1219243685436212</v>
+        <v>0.12091346820333326</v>
       </c>
       <c r="I393" s="0" t="inlineStr">
         <is>
@@ -21302,7 +21302,7 @@
         <v>0.10022026431718058</v>
       </c>
       <c r="H394" s="4">
-        <v>0.12136476202095832</v>
+        <v>0.1203578655153879</v>
       </c>
       <c r="I394" s="0" t="inlineStr">
         <is>
@@ -21356,7 +21356,7 @@
         <v>0.10132158590308361</v>
       </c>
       <c r="H395" s="4">
-        <v>0.12062836714957566</v>
+        <v>0.1196267482990051</v>
       </c>
       <c r="I395" s="0" t="inlineStr">
         <is>
@@ -21410,7 +21410,7 @@
         <v>0.10012210012210021</v>
       </c>
       <c r="H396" s="4">
-        <v>0.11996099391712531</v>
+        <v>0.11896416683412896</v>
       </c>
       <c r="I396" s="0" t="inlineStr">
         <is>
@@ -21464,7 +21464,7 @@
         <v>0.09915611814345994</v>
       </c>
       <c r="H397" s="4">
-        <v>0.11873847888032196</v>
+        <v>0.11775045116491538</v>
       </c>
       <c r="I397" s="0" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>0.09977324263038545</v>
       </c>
       <c r="H398" s="4">
-        <v>0.1182517835158854</v>
+        <v>0.11726726671406837</v>
       </c>
       <c r="I398" s="0" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>0.09992652461425422</v>
       </c>
       <c r="H399" s="4">
-        <v>0.11819095093567711</v>
+        <v>0.11720687327897432</v>
       </c>
       <c r="I399" s="0" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         <v>0.10038240917782026</v>
       </c>
       <c r="H400" s="4">
-        <v>0.11253880769948402</v>
+        <v>0.11159583504894414</v>
       </c>
       <c r="I400" s="0" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
         <v>0.09999999999999985</v>
       </c>
       <c r="H401" s="4">
-        <v>0.11078260170710075</v>
+        <v>0.1098525229466765</v>
       </c>
       <c r="I401" s="0" t="inlineStr">
         <is>
@@ -21734,7 +21734,7 @@
         <v>0.09994062932911142</v>
       </c>
       <c r="H402" s="4">
-        <v>0.11071269004021964</v>
+        <v>0.10978312576083049</v>
       </c>
       <c r="I402" s="0" t="inlineStr">
         <is>
@@ -21788,7 +21788,7 @@
         <v>0.10004446420631385</v>
       </c>
       <c r="H403" s="4">
-        <v>0.11000936591426773</v>
+        <v>0.10908498250476134</v>
       </c>
       <c r="I403" s="0" t="inlineStr">
         <is>
@@ -21842,7 +21842,7 @@
         <v>0.09995435874030134</v>
       </c>
       <c r="H404" s="4">
-        <v>0.10876559498356105</v>
+        <v>0.10785039621273386</v>
       </c>
       <c r="I404" s="0" t="inlineStr">
         <is>
@@ -21896,7 +21896,7 @@
         <v>0.1005509641873279</v>
       </c>
       <c r="H405" s="4">
-        <v>0.10853574281193065</v>
+        <v>0.1076222445610207</v>
       </c>
       <c r="I405" s="0" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>0.09946236559139777</v>
       </c>
       <c r="H406" s="4">
-        <v>0.10318542009689037</v>
+        <v>0.10231178502240412</v>
       </c>
       <c r="I406" s="0" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
         <v>0.0995203836930456</v>
       </c>
       <c r="H407" s="4">
-        <v>0.10269695615024685</v>
+        <v>0.10182698715569265</v>
       </c>
       <c r="I407" s="0" t="inlineStr">
         <is>
@@ -22058,7 +22058,7 @@
         <v>0.09994794377928162</v>
       </c>
       <c r="H408" s="4">
-        <v>0.10012582153928166</v>
+        <v>0.09927522344960338</v>
       </c>
       <c r="I408" s="0" t="inlineStr">
         <is>
@@ -22112,7 +22112,7 @@
         <v>0.09953161592505877</v>
       </c>
       <c r="H409" s="4">
-        <v>0.09728202926319825</v>
+        <v>0.09645300055373822</v>
       </c>
       <c r="I409" s="0" t="inlineStr">
         <is>
@@ -22166,7 +22166,7 @@
         <v>0.09978617248752686</v>
       </c>
       <c r="H410" s="4">
-        <v>0.09667024747193552</v>
+        <v>0.09584587876446625</v>
       </c>
       <c r="I410" s="0" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>0.09930715935334877</v>
       </c>
       <c r="H411" s="4">
-        <v>0.09538162018676917</v>
+        <v>0.09456709002186756</v>
       </c>
       <c r="I411" s="0" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         <v>0.09945750452079573</v>
       </c>
       <c r="H412" s="4">
-        <v>0.09538027477552043</v>
+        <v>0.09456575489896</v>
       </c>
       <c r="I412" s="0" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>0.10012947777298219</v>
       </c>
       <c r="H413" s="4">
-        <v>0.09447223988922465</v>
+        <v>0.09366467147834634</v>
       </c>
       <c r="I413" s="0" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>0.09913793103448265</v>
       </c>
       <c r="H414" s="4">
-        <v>0.09445534071005474</v>
+        <v>0.0936479018173523</v>
       </c>
       <c r="I414" s="0" t="inlineStr">
         <is>
@@ -22436,7 +22436,7 @@
         <v>0.09984639016897079</v>
       </c>
       <c r="H415" s="4">
-        <v>0.0938975325373546</v>
+        <v>0.09309437178415378</v>
       </c>
       <c r="I415" s="0" t="inlineStr">
         <is>
@@ -22490,7 +22490,7 @@
         <v>0.09983429991715</v>
       </c>
       <c r="H416" s="4">
-        <v>0.0922009503734087</v>
+        <v>0.09141083747565922</v>
       </c>
       <c r="I416" s="0" t="inlineStr">
         <is>
@@ -22544,7 +22544,7 @@
         <v>0.10015898251192358</v>
       </c>
       <c r="H417" s="4">
-        <v>0.09126095642228424</v>
+        <v>0.09047809592407818</v>
       </c>
       <c r="I417" s="0" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>0.10030395136778125</v>
       </c>
       <c r="H418" s="4">
-        <v>0.09090271444867465</v>
+        <v>0.09012262227561267</v>
       </c>
       <c r="I418" s="0" t="inlineStr">
         <is>
@@ -22652,7 +22652,7 @@
         <v>0.09978308026030369</v>
       </c>
       <c r="H419" s="4">
-        <v>0.08888876719384292</v>
+        <v>0.08812428260459179</v>
       </c>
       <c r="I419" s="0" t="inlineStr">
         <is>
@@ -22706,7 +22706,7 @@
         <v>0.09907834101382473</v>
       </c>
       <c r="H420" s="4">
-        <v>0.0837232523675397</v>
+        <v>0.08299914655771</v>
       </c>
       <c r="I420" s="0" t="inlineStr">
         <is>
@@ -22760,7 +22760,7 @@
         <v>0.09999999999999985</v>
       </c>
       <c r="H421" s="4">
-        <v>0.0804549045784452</v>
+        <v>0.07975660555590841</v>
       </c>
       <c r="I421" s="0" t="inlineStr">
         <is>
@@ -22814,7 +22814,7 @@
         <v>0.09976247030878849</v>
       </c>
       <c r="H422" s="4">
-        <v>0.07907411772557696</v>
+        <v>0.07838678147203354</v>
       </c>
       <c r="I422" s="0" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>0.10115606936416179</v>
       </c>
       <c r="H423" s="4">
-        <v>0.07732300998646234</v>
+        <v>0.07664962802020016</v>
       </c>
       <c r="I423" s="0" t="inlineStr">
         <is>

--- a/docs/downloads/latest.xlsx
+++ b/docs/downloads/latest.xlsx
@@ -93,7 +93,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L423"/>
+  <dimension ref="A1:L476"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -22886,6 +22886,2868 @@
         </is>
       </c>
       <c r="L423" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B424" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C424" s="0">
+        <v>1</v>
+      </c>
+      <c r="D424" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002917</t>
+        </is>
+      </c>
+      <c r="E424" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金奥博</t>
+        </is>
+      </c>
+      <c r="F424" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="G424" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H424" s="4">
+        <v>0.2532364290908264</v>
+      </c>
+      <c r="I424" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J424" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 金奥博（002917）归入“拟收购+民爆+西藏客户+机器人概念”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K424" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 10.0%）。截至运行时成交量约为20日均量的 4.1 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L424" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B425" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C425" s="0">
+        <v>2</v>
+      </c>
+      <c r="D425" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002322</t>
+        </is>
+      </c>
+      <c r="E425" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">理工能科</t>
+        </is>
+      </c>
+      <c r="F425" s="0">
+        <v>13.08</v>
+      </c>
+      <c r="G425" s="4">
+        <v>0.1000841042893188</v>
+      </c>
+      <c r="H425" s="4">
+        <v>0.24909064874301617</v>
+      </c>
+      <c r="I425" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J425" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 理工能科（002322）归入“业绩预增+电力造价+高分红”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K425" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 10.0%）。截至运行时成交量约为20日均量的 4.3 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L425" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B426" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C426" s="0">
+        <v>3</v>
+      </c>
+      <c r="D426" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603188</t>
+        </is>
+      </c>
+      <c r="E426" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">亚邦股份</t>
+        </is>
+      </c>
+      <c r="F426" s="0">
+        <v>5.46</v>
+      </c>
+      <c r="G426" s="4">
+        <v>0.10080645161290323</v>
+      </c>
+      <c r="H426" s="4">
+        <v>0.18066471930035738</v>
+      </c>
+      <c r="I426" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J426" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 亚邦股份（603188）归入“染料中间体+染料产业链+业绩修复”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K426" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.4 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L426" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B427" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C427" s="0">
+        <v>4</v>
+      </c>
+      <c r="D427" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600847</t>
+        </is>
+      </c>
+      <c r="E427" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">万里股份</t>
+        </is>
+      </c>
+      <c r="F427" s="0">
+        <v>14.03</v>
+      </c>
+      <c r="G427" s="4">
+        <v>0.10039215686274507</v>
+      </c>
+      <c r="H427" s="4">
+        <v>0.17154647722411606</v>
+      </c>
+      <c r="I427" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J427" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 万里股份（600847）归入“新能源锂电池+储能+铅酸电池”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K427" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L427" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B428" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C428" s="0">
+        <v>5</v>
+      </c>
+      <c r="D428" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002811</t>
+        </is>
+      </c>
+      <c r="E428" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">郑中设计</t>
+        </is>
+      </c>
+      <c r="F428" s="0">
+        <v>20.27</v>
+      </c>
+      <c r="G428" s="4">
+        <v>0.09983722192078126</v>
+      </c>
+      <c r="H428" s="4">
+        <v>0.1680074240151696</v>
+      </c>
+      <c r="I428" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J428" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 郑中设计（002811）归入“半导体投资+室内设计+软装增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K428" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.8 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L428" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B429" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C429" s="0">
+        <v>6</v>
+      </c>
+      <c r="D429" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603980</t>
+        </is>
+      </c>
+      <c r="E429" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">吉华集团</t>
+        </is>
+      </c>
+      <c r="F429" s="0">
+        <v>10.67</v>
+      </c>
+      <c r="G429" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H429" s="4">
+        <v>0.16537005312848457</v>
+      </c>
+      <c r="I429" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J429" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 吉华集团（603980）归入“染料+控制权变更”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K429" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L429" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B430" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C430" s="0">
+        <v>7</v>
+      </c>
+      <c r="D430" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603386</t>
+        </is>
+      </c>
+      <c r="E430" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">骏亚科技</t>
+        </is>
+      </c>
+      <c r="F430" s="0">
+        <v>17.47</v>
+      </c>
+      <c r="G430" s="4">
+        <v>0.10012594458438272</v>
+      </c>
+      <c r="H430" s="4">
+        <v>0.16262410879927341</v>
+      </c>
+      <c r="I430" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J430" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 骏亚科技（603386）归入“PCB+高多层HDI+人形机器人”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K430" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.6 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L430" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B431" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C431" s="0">
+        <v>8</v>
+      </c>
+      <c r="D431" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001318</t>
+        </is>
+      </c>
+      <c r="E431" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">阳光乳业</t>
+        </is>
+      </c>
+      <c r="F431" s="0">
+        <v>14.03</v>
+      </c>
+      <c r="G431" s="4">
+        <v>0.10039215686274507</v>
+      </c>
+      <c r="H431" s="4">
+        <v>0.1583942009374842</v>
+      </c>
+      <c r="I431" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J431" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 阳光乳业（001318）归入“低温乳品+冷链物流+新品研发”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K431" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.6 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L431" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B432" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C432" s="0">
+        <v>9</v>
+      </c>
+      <c r="D432" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605058</t>
+        </is>
+      </c>
+      <c r="E432" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">澳弘电子</t>
+        </is>
+      </c>
+      <c r="F432" s="0">
+        <v>60.39</v>
+      </c>
+      <c r="G432" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H432" s="4">
+        <v>0.1554379886943238</v>
+      </c>
+      <c r="I432" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J432" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 澳弘电子（605058）归入“PCB+AI服务器电源+具身智能”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K432" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L432" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B433" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C433" s="0">
+        <v>10</v>
+      </c>
+      <c r="D433" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600802</t>
+        </is>
+      </c>
+      <c r="E433" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">福建水泥</t>
+        </is>
+      </c>
+      <c r="F433" s="0">
+        <v>7.16</v>
+      </c>
+      <c r="G433" s="4">
+        <v>0.09984639016897079</v>
+      </c>
+      <c r="H433" s="4">
+        <v>0.15266801915501513</v>
+      </c>
+      <c r="I433" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J433" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 福建水泥（600802）归入“水泥熟料+重点工程+福建国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K433" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L433" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B434" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C434" s="0">
+        <v>11</v>
+      </c>
+      <c r="D434" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002693</t>
+        </is>
+      </c>
+      <c r="E434" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">双成药业</t>
+        </is>
+      </c>
+      <c r="F434" s="0">
+        <v>10.32</v>
+      </c>
+      <c r="G434" s="4">
+        <v>0.10021321961620465</v>
+      </c>
+      <c r="H434" s="4">
+        <v>0.14987413398039218</v>
+      </c>
+      <c r="I434" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J434" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 双成药业（002693）归入“多肽药+药品出海+受托加工”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K434" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L434" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B435" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C435" s="0">
+        <v>12</v>
+      </c>
+      <c r="D435" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000823</t>
+        </is>
+      </c>
+      <c r="E435" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">超声电子</t>
+        </is>
+      </c>
+      <c r="F435" s="0">
+        <v>22.32</v>
+      </c>
+      <c r="G435" s="4">
+        <v>0.10004928536224744</v>
+      </c>
+      <c r="H435" s="4">
+        <v>0.14740051016840255</v>
+      </c>
+      <c r="I435" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J435" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 超声电子（000823）归入“三季报预增+覆铜板+印制板+高阶HDI”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K435" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.3 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L435" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B436" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C436" s="0">
+        <v>13</v>
+      </c>
+      <c r="D436" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000833</t>
+        </is>
+      </c>
+      <c r="E436" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">粤桂股份</t>
+        </is>
+      </c>
+      <c r="F436" s="0">
+        <v>20.65</v>
+      </c>
+      <c r="G436" s="4">
+        <v>0.10015982951518376</v>
+      </c>
+      <c r="H436" s="4">
+        <v>0.14248684326677233</v>
+      </c>
+      <c r="I436" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J436" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 粤桂股份（000833）归入“业绩预增+硫铁矿+新能源材料”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K436" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L436" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B437" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C437" s="0">
+        <v>14</v>
+      </c>
+      <c r="D437" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002172</t>
+        </is>
+      </c>
+      <c r="E437" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">澳洋健康</t>
+        </is>
+      </c>
+      <c r="F437" s="0">
+        <v>5.92</v>
+      </c>
+      <c r="G437" s="4">
+        <v>0.1003717472118959</v>
+      </c>
+      <c r="H437" s="4">
+        <v>0.14190742312371663</v>
+      </c>
+      <c r="I437" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J437" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 澳洋健康（002172）归入“脑机接口+医疗服务+国资控股+“羊”字辈”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K437" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.8 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L437" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B438" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C438" s="0">
+        <v>15</v>
+      </c>
+      <c r="D438" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000995</t>
+        </is>
+      </c>
+      <c r="E438" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">皇台酒业</t>
+        </is>
+      </c>
+      <c r="F438" s="0">
+        <v>12.25</v>
+      </c>
+      <c r="G438" s="4">
+        <v>0.09964093357271085</v>
+      </c>
+      <c r="H438" s="4">
+        <v>0.13824860042785028</v>
+      </c>
+      <c r="I438" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J438" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 皇台酒业（000995）归入“白酒+区域品牌+线上营销”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K438" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L438" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B439" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C439" s="0">
+        <v>16</v>
+      </c>
+      <c r="D439" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600593</t>
+        </is>
+      </c>
+      <c r="E439" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大连圣亚</t>
+        </is>
+      </c>
+      <c r="F439" s="0">
+        <v>49.83</v>
+      </c>
+      <c r="G439" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H439" s="4">
+        <v>0.13545347076165898</v>
+      </c>
+      <c r="I439" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J439" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 大连圣亚（600593）归入“哈尔滨景区+景区经营+海洋馆”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K439" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L439" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B440" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C440" s="0">
+        <v>17</v>
+      </c>
+      <c r="D440" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603956</t>
+        </is>
+      </c>
+      <c r="E440" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">威派格</t>
+        </is>
+      </c>
+      <c r="F440" s="0">
+        <v>8.15</v>
+      </c>
+      <c r="G440" s="4">
+        <v>0.09986504723346833</v>
+      </c>
+      <c r="H440" s="4">
+        <v>0.13377266152173714</v>
+      </c>
+      <c r="I440" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J440" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 威派格（603956）归入“PCB钻针+智慧水务+河图平台”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K440" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.8 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L440" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B441" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C441" s="0">
+        <v>18</v>
+      </c>
+      <c r="D441" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">003037</t>
+        </is>
+      </c>
+      <c r="E441" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">三和管桩</t>
+        </is>
+      </c>
+      <c r="F441" s="0">
+        <v>6.45</v>
+      </c>
+      <c r="G441" s="4">
+        <v>0.10068259385665534</v>
+      </c>
+      <c r="H441" s="4">
+        <v>0.13364416697841547</v>
+      </c>
+      <c r="I441" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J441" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 三和管桩（003037）归入“水利技术+新能源管桩+海工桩”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K441" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.6 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L441" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B442" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C442" s="0">
+        <v>19</v>
+      </c>
+      <c r="D442" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603099</t>
+        </is>
+      </c>
+      <c r="E442" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">长白山</t>
+        </is>
+      </c>
+      <c r="F442" s="0">
+        <v>45.85</v>
+      </c>
+      <c r="G442" s="4">
+        <v>0.1000479846449136</v>
+      </c>
+      <c r="H442" s="4">
+        <v>0.13290402513729196</v>
+      </c>
+      <c r="I442" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J442" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 长白山（603099）归入“冰雪旅游+旅游客运+温泉度假”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K442" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L442" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B443" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C443" s="0">
+        <v>20</v>
+      </c>
+      <c r="D443" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603767</t>
+        </is>
+      </c>
+      <c r="E443" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中马传动</t>
+        </is>
+      </c>
+      <c r="F443" s="0">
+        <v>15.72</v>
+      </c>
+      <c r="G443" s="4">
+        <v>0.10006997900629822</v>
+      </c>
+      <c r="H443" s="4">
+        <v>0.12470512463333759</v>
+      </c>
+      <c r="I443" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J443" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 中马传动（603767）归入“新能源汽车减速器+汽车变速器+净利润增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K443" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L443" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B444" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C444" s="0">
+        <v>21</v>
+      </c>
+      <c r="D444" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603042</t>
+        </is>
+      </c>
+      <c r="E444" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华脉科技</t>
+        </is>
+      </c>
+      <c r="F444" s="0">
+        <v>16.12</v>
+      </c>
+      <c r="G444" s="4">
+        <v>0.1003412969283277</v>
+      </c>
+      <c r="H444" s="4">
+        <v>0.1234607329501963</v>
+      </c>
+      <c r="I444" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J444" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华脉科技（603042）归入“光纤光缆+扭亏为盈+6G通信”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K444" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.7 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L444" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B445" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C445" s="0">
+        <v>22</v>
+      </c>
+      <c r="D445" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603466</t>
+        </is>
+      </c>
+      <c r="E445" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">风语筑</t>
+        </is>
+      </c>
+      <c r="F445" s="0">
+        <v>13.57</v>
+      </c>
+      <c r="G445" s="4">
+        <v>0.09967585089141018</v>
+      </c>
+      <c r="H445" s="4">
+        <v>0.12192741092534297</v>
+      </c>
+      <c r="I445" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J445" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 风语筑（603466）归入“AI视频+数字展示+具身智能+人工智能教育”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K445" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.5 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L445" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B446" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C446" s="0">
+        <v>23</v>
+      </c>
+      <c r="D446" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600228</t>
+        </is>
+      </c>
+      <c r="E446" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">返利科技</t>
+        </is>
+      </c>
+      <c r="F446" s="0">
+        <v>10.14</v>
+      </c>
+      <c r="G446" s="4">
+        <v>0.09978308026030369</v>
+      </c>
+      <c r="H446" s="4">
+        <v>0.1206485837403856</v>
+      </c>
+      <c r="I446" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J446" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 返利科技（600228）归入“在线导购+人工智能应用”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K446" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L446" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B447" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C447" s="0">
+        <v>24</v>
+      </c>
+      <c r="D447" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002623</t>
+        </is>
+      </c>
+      <c r="E447" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">亚玛顿</t>
+        </is>
+      </c>
+      <c r="F447" s="0">
+        <v>19.23</v>
+      </c>
+      <c r="G447" s="4">
+        <v>0.10011441647597262</v>
+      </c>
+      <c r="H447" s="4">
+        <v>0.12057248641175045</v>
+      </c>
+      <c r="I447" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J447" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 亚玛顿（002623）归入“玻璃基板+光伏玻璃+钙钛矿玻璃”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K447" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L447" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B448" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C448" s="0">
+        <v>25</v>
+      </c>
+      <c r="D448" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605258</t>
+        </is>
+      </c>
+      <c r="E448" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">协和电子</t>
+        </is>
+      </c>
+      <c r="F448" s="0">
+        <v>40.55</v>
+      </c>
+      <c r="G448" s="4">
+        <v>0.10010851871947901</v>
+      </c>
+      <c r="H448" s="4">
+        <v>0.12033634217125405</v>
+      </c>
+      <c r="I448" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J448" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 协和电子（605258）归入“PCB+高频通讯+新能源电池”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K448" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.7 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L448" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B449" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C449" s="0">
+        <v>26</v>
+      </c>
+      <c r="D449" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600712</t>
+        </is>
+      </c>
+      <c r="E449" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南宁百货</t>
+        </is>
+      </c>
+      <c r="F449" s="0">
+        <v>5.91</v>
+      </c>
+      <c r="G449" s="4">
+        <v>0.1005586592178771</v>
+      </c>
+      <c r="H449" s="4">
+        <v>0.11505434306136206</v>
+      </c>
+      <c r="I449" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J449" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 南宁百货（600712）归入“百货零售+平陆运河+扭亏为盈”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K449" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.6 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L449" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B450" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C450" s="0">
+        <v>27</v>
+      </c>
+      <c r="D450" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002748</t>
+        </is>
+      </c>
+      <c r="E450" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">世龙实业</t>
+        </is>
+      </c>
+      <c r="F450" s="0">
+        <v>13.1</v>
+      </c>
+      <c r="G450" s="4">
+        <v>0.09991603694374461</v>
+      </c>
+      <c r="H450" s="4">
+        <v>0.11359663057831353</v>
+      </c>
+      <c r="I450" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J450" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 世龙实业（002748）归入“氯化亚砜+染料产业链+业绩增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K450" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.8 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L450" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B451" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C451" s="0">
+        <v>28</v>
+      </c>
+      <c r="D451" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002430</t>
+        </is>
+      </c>
+      <c r="E451" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">杭氧股份</t>
+        </is>
+      </c>
+      <c r="F451" s="0">
+        <v>27.52</v>
+      </c>
+      <c r="G451" s="4">
+        <v>0.0999200639488409</v>
+      </c>
+      <c r="H451" s="4">
+        <v>0.11177788498166995</v>
+      </c>
+      <c r="I451" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J451" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 杭氧股份（002430）归入“电子气体+工业气体+空分设备”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K451" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.2 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L451" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B452" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C452" s="0">
+        <v>29</v>
+      </c>
+      <c r="D452" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600391</t>
+        </is>
+      </c>
+      <c r="E452" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">航发科技</t>
+        </is>
+      </c>
+      <c r="F452" s="0">
+        <v>38.78</v>
+      </c>
+      <c r="G452" s="4">
+        <v>0.10014184397163127</v>
+      </c>
+      <c r="H452" s="4">
+        <v>0.11163379670396496</v>
+      </c>
+      <c r="I452" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J452" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 航发科技（600391）归入“航空发动机+长江1000A+外贸配套”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K452" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L452" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B453" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C453" s="0">
+        <v>30</v>
+      </c>
+      <c r="D453" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002949</t>
+        </is>
+      </c>
+      <c r="E453" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华阳国际</t>
+        </is>
+      </c>
+      <c r="F453" s="0">
+        <v>14.32</v>
+      </c>
+      <c r="G453" s="4">
+        <v>0.09984639016897079</v>
+      </c>
+      <c r="H453" s="4">
+        <v>0.11117656044976616</v>
+      </c>
+      <c r="I453" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J453" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华阳国际（002949）归入“AI设计+建筑设计+城市更新”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K453" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L453" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B454" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C454" s="0">
+        <v>31</v>
+      </c>
+      <c r="D454" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002184</t>
+        </is>
+      </c>
+      <c r="E454" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">海得控制</t>
+        </is>
+      </c>
+      <c r="F454" s="0">
+        <v>11.07</v>
+      </c>
+      <c r="G454" s="4">
+        <v>0.1003976143141152</v>
+      </c>
+      <c r="H454" s="4">
+        <v>0.1110340151092708</v>
+      </c>
+      <c r="I454" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J454" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 海得控制（002184）归入“工业自动化+工业AI+算力基础设施”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K454" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.2 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L454" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B455" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C455" s="0">
+        <v>32</v>
+      </c>
+      <c r="D455" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000715</t>
+        </is>
+      </c>
+      <c r="E455" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中兴商业</t>
+        </is>
+      </c>
+      <c r="F455" s="0">
+        <v>5.78</v>
+      </c>
+      <c r="G455" s="4">
+        <v>0.10095238095238092</v>
+      </c>
+      <c r="H455" s="4">
+        <v>0.11086640802378167</v>
+      </c>
+      <c r="I455" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J455" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 中兴商业（000715）归入“百货零售+冰雪消费+恐龙文旅”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K455" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.9 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L455" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B456" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C456" s="0">
+        <v>33</v>
+      </c>
+      <c r="D456" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603328</t>
+        </is>
+      </c>
+      <c r="E456" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">依顿电子</t>
+        </is>
+      </c>
+      <c r="F456" s="0">
+        <v>13.34</v>
+      </c>
+      <c r="G456" s="4">
+        <v>0.09975267930750187</v>
+      </c>
+      <c r="H456" s="4">
+        <v>0.11023918482997103</v>
+      </c>
+      <c r="I456" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J456" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 依顿电子（603328）归入“股权激励+印制电路板+算力PCB”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K456" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L456" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B457" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C457" s="0">
+        <v>34</v>
+      </c>
+      <c r="D457" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600237</t>
+        </is>
+      </c>
+      <c r="E457" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">铜峰电子</t>
+        </is>
+      </c>
+      <c r="F457" s="0">
+        <v>9.03</v>
+      </c>
+      <c r="G457" s="4">
+        <v>0.09987819732034087</v>
+      </c>
+      <c r="H457" s="4">
+        <v>0.10889208552704456</v>
+      </c>
+      <c r="I457" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J457" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 铜峰电子（600237）归入“薄膜电容器+薄膜材料+复合铜箔基膜”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K457" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L457" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B458" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C458" s="0">
+        <v>35</v>
+      </c>
+      <c r="D458" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002980</t>
+        </is>
+      </c>
+      <c r="E458" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华盛昌</t>
+        </is>
+      </c>
+      <c r="F458" s="0">
+        <v>116.05</v>
+      </c>
+      <c r="G458" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H458" s="4">
+        <v>0.10877413728715286</v>
+      </c>
+      <c r="I458" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J458" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华盛昌（002980）归入“光通信测试+硅光产品+伽蓝特收购”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K458" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.4 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L458" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B459" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C459" s="0">
+        <v>36</v>
+      </c>
+      <c r="D459" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002640</t>
+        </is>
+      </c>
+      <c r="E459" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">跨境通</t>
+        </is>
+      </c>
+      <c r="F459" s="0">
+        <v>3.89</v>
+      </c>
+      <c r="G459" s="4">
+        <v>0.09887005649717517</v>
+      </c>
+      <c r="H459" s="4">
+        <v>0.10814884748053771</v>
+      </c>
+      <c r="I459" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J459" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 跨境通（002640）归入“跨境电商+AI应用+中报扭亏”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K459" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L459" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B460" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C460" s="0">
+        <v>37</v>
+      </c>
+      <c r="D460" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002639</t>
+        </is>
+      </c>
+      <c r="E460" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雪人集团</t>
+        </is>
+      </c>
+      <c r="F460" s="0">
+        <v>14.59</v>
+      </c>
+      <c r="G460" s="4">
+        <v>0.10030165912518862</v>
+      </c>
+      <c r="H460" s="4">
+        <v>0.10713623621665887</v>
+      </c>
+      <c r="I460" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J460" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 雪人集团（002639）归入“制冰系统+数据中心冷却+海外制冷”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K460" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L460" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B461" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C461" s="0">
+        <v>38</v>
+      </c>
+      <c r="D461" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000530</t>
+        </is>
+      </c>
+      <c r="E461" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">冰山冷热</t>
+        </is>
+      </c>
+      <c r="F461" s="0">
+        <v>5.73</v>
+      </c>
+      <c r="G461" s="4">
+        <v>0.0998080614203456</v>
+      </c>
+      <c r="H461" s="4">
+        <v>0.10595635913280706</v>
+      </c>
+      <c r="I461" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J461" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 冰山冷热（000530）归入“数据中心液冷+储能温控+冷热设备+冰雪工程”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K461" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.5 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L461" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B462" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C462" s="0">
+        <v>39</v>
+      </c>
+      <c r="D462" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603001</t>
+        </is>
+      </c>
+      <c r="E462" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奥康国际</t>
+        </is>
+      </c>
+      <c r="F462" s="0">
+        <v>11.91</v>
+      </c>
+      <c r="G462" s="4">
+        <v>0.09972299168975063</v>
+      </c>
+      <c r="H462" s="4">
+        <v>0.10457171309048417</v>
+      </c>
+      <c r="I462" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J462" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 奥康国际（603001）归入“皮鞋皮具+业绩扭亏+股权转让”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K462" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L462" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B463" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C463" s="0">
+        <v>40</v>
+      </c>
+      <c r="D463" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002579</t>
+        </is>
+      </c>
+      <c r="E463" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中京电子</t>
+        </is>
+      </c>
+      <c r="F463" s="0">
+        <v>16.43</v>
+      </c>
+      <c r="G463" s="4">
+        <v>0.0997322623828647</v>
+      </c>
+      <c r="H463" s="4">
+        <v>0.10094844613391399</v>
+      </c>
+      <c r="I463" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J463" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 中京电子（002579）归入“高阶HDI+高端PCB+存储算力”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K463" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.7 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L463" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B464" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C464" s="0">
+        <v>41</v>
+      </c>
+      <c r="D464" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600202</t>
+        </is>
+      </c>
+      <c r="E464" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">哈空调</t>
+        </is>
+      </c>
+      <c r="F464" s="0">
+        <v>5.59</v>
+      </c>
+      <c r="G464" s="4">
+        <v>0.10039370078740163</v>
+      </c>
+      <c r="H464" s="4">
+        <v>0.09685129830310697</v>
+      </c>
+      <c r="I464" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J464" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 哈空调（600202）归入“空冷设备+飞翼式空冷+道达尔供应商”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K464" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.3 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L464" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B465" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C465" s="0">
+        <v>42</v>
+      </c>
+      <c r="D465" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603353</t>
+        </is>
+      </c>
+      <c r="E465" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">和顺石油</t>
+        </is>
+      </c>
+      <c r="F465" s="0">
+        <v>37.9</v>
+      </c>
+      <c r="G465" s="4">
+        <v>0.10014513788098679</v>
+      </c>
+      <c r="H465" s="4">
+        <v>0.09551956036673573</v>
+      </c>
+      <c r="I465" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J465" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 和顺石油（603353）归入“半导体IP+成品油”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K465" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L465" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B466" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C466" s="0">
+        <v>43</v>
+      </c>
+      <c r="D466" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600281</t>
+        </is>
+      </c>
+      <c r="E466" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华阳新材</t>
+        </is>
+      </c>
+      <c r="F466" s="0">
+        <v>4.98</v>
+      </c>
+      <c r="G466" s="4">
+        <v>0.09933774834437091</v>
+      </c>
+      <c r="H466" s="4">
+        <v>0.09472231293849767</v>
+      </c>
+      <c r="I466" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J466" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华阳新材（600281）归入“贵金属回收+铂族金属加工+山西国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K466" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.8 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L466" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B467" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C467" s="0">
+        <v>44</v>
+      </c>
+      <c r="D467" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002549</t>
+        </is>
+      </c>
+      <c r="E467" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">凯美特气</t>
+        </is>
+      </c>
+      <c r="F467" s="0">
+        <v>14.25</v>
+      </c>
+      <c r="G467" s="4">
+        <v>0.10038610038610042</v>
+      </c>
+      <c r="H467" s="4">
+        <v>0.09298911650843339</v>
+      </c>
+      <c r="I467" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J467" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 凯美特气（002549）归入“光刻气+电子特气+尾气回收”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K467" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.7 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L467" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B468" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C468" s="0">
+        <v>45</v>
+      </c>
+      <c r="D468" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002878</t>
+        </is>
+      </c>
+      <c r="E468" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">元隆雅图</t>
+        </is>
+      </c>
+      <c r="F468" s="0">
+        <v>14.33</v>
+      </c>
+      <c r="G468" s="4">
+        <v>0.09976976208749043</v>
+      </c>
+      <c r="H468" s="4">
+        <v>0.09202578136915171</v>
+      </c>
+      <c r="I468" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J468" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 元隆雅图（002878）归入“冰雪经济+IP文创+短剧游戏+AI应用”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K468" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.2 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L468" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B469" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C469" s="0">
+        <v>46</v>
+      </c>
+      <c r="D469" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600199</t>
+        </is>
+      </c>
+      <c r="E469" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金种子酒</t>
+        </is>
+      </c>
+      <c r="F469" s="0">
+        <v>7.6</v>
+      </c>
+      <c r="G469" s="4">
+        <v>0.09985528219971052</v>
+      </c>
+      <c r="H469" s="4">
+        <v>0.09181847408838673</v>
+      </c>
+      <c r="I469" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J469" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 金种子酒（600199）归入“白酒主业+啤白融合+亏损收窄”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K469" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.0 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L469" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B470" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C470" s="0">
+        <v>47</v>
+      </c>
+      <c r="D470" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000558</t>
+        </is>
+      </c>
+      <c r="E470" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天府文旅</t>
+        </is>
+      </c>
+      <c r="F470" s="0">
+        <v>3.84</v>
+      </c>
+      <c r="G470" s="4">
+        <v>0.10028653295128918</v>
+      </c>
+      <c r="H470" s="4">
+        <v>0.09042400665116047</v>
+      </c>
+      <c r="I470" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J470" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 天府文旅（000558）归入“冰雪旅游+毕棚沟收购+影旅融合”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K470" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.8 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L470" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B471" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C471" s="0">
+        <v>48</v>
+      </c>
+      <c r="D471" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601188</t>
+        </is>
+      </c>
+      <c r="E471" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">龙江交通</t>
+        </is>
+      </c>
+      <c r="F471" s="0">
+        <v>3.21</v>
+      </c>
+      <c r="G471" s="4">
+        <v>0.09931506849315073</v>
+      </c>
+      <c r="H471" s="4">
+        <v>0.08841677107151441</v>
+      </c>
+      <c r="I471" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J471" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 龙江交通（601188）归入“冰雪旅游保障+高速公路运营”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K471" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.6 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L471" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B472" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C472" s="0">
+        <v>49</v>
+      </c>
+      <c r="D472" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001229</t>
+        </is>
+      </c>
+      <c r="E472" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">魅视科技</t>
+        </is>
+      </c>
+      <c r="F472" s="0">
+        <v>41.76</v>
+      </c>
+      <c r="G472" s="4">
+        <v>0.1001053740779767</v>
+      </c>
+      <c r="H472" s="4">
+        <v>0.08783467149029954</v>
+      </c>
+      <c r="I472" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J472" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 魅视科技（001229）归入“磷化铟+专业视听+AI视觉”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K472" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L472" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B473" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C473" s="0">
+        <v>50</v>
+      </c>
+      <c r="D473" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002862</t>
+        </is>
+      </c>
+      <c r="E473" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">实丰文化</t>
+        </is>
+      </c>
+      <c r="F473" s="0">
+        <v>15.95</v>
+      </c>
+      <c r="G473" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H473" s="4">
+        <v>0.086885980874681</v>
+      </c>
+      <c r="I473" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J473" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 实丰文化（002862）归入“AI玩具+IP潮玩+玩具制造”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K473" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L473" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B474" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C474" s="0">
+        <v>51</v>
+      </c>
+      <c r="D474" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002587</t>
+        </is>
+      </c>
+      <c r="E474" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奥拓电子</t>
+        </is>
+      </c>
+      <c r="F474" s="0">
+        <v>5.76</v>
+      </c>
+      <c r="G474" s="4">
+        <v>0.09923664122137389</v>
+      </c>
+      <c r="H474" s="4">
+        <v>0.07506513372010312</v>
+      </c>
+      <c r="I474" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J474" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 奥拓电子（002587）归入“AI视讯+虚拟拍摄+电影屏”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K474" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.6 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L474" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B475" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C475" s="0">
+        <v>52</v>
+      </c>
+      <c r="D475" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600853</t>
+        </is>
+      </c>
+      <c r="E475" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">龙建股份</t>
+        </is>
+      </c>
+      <c r="F475" s="0">
+        <v>3.65</v>
+      </c>
+      <c r="G475" s="4">
+        <v>0.0993975903614459</v>
+      </c>
+      <c r="H475" s="4">
+        <v>0.06584679111641867</v>
+      </c>
+      <c r="I475" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J475" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 龙建股份（600853）归入“冰雪经济+公路市政+海外基建+寒区施工”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K475" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 6.1 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L475" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B476" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C476" s="0">
+        <v>53</v>
+      </c>
+      <c r="D476" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600316</t>
+        </is>
+      </c>
+      <c r="E476" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">洪都航空</t>
+        </is>
+      </c>
+      <c r="F476" s="0">
+        <v>33.66</v>
+      </c>
+      <c r="G476" s="4">
+        <v>0.0974894033257252</v>
+      </c>
+      <c r="H476" s="4">
+        <v>0.04548386662981035</v>
+      </c>
+      <c r="I476" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no_verified_event</t>
+        </is>
+      </c>
+      <c r="J476" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">事件证据层未找到与当日涨停直接匹配的公告或新闻；系统不把概念标签、技术形态或主观猜测当成涨停原因。</t>
+        </is>
+      </c>
+      <c r="K476" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">截至运行时成交量约为20日均量的 2.4 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 64 家涨停，其中首板 53 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L476" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
         </is>

--- a/docs/downloads/latest.xlsx
+++ b/docs/downloads/latest.xlsx
@@ -93,7 +93,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L476"/>
+  <dimension ref="A1:L495"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -25753,13 +25753,1039 @@
         </is>
       </c>
     </row>
+    <row r="477">
+      <c r="A477" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="B477" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="C477" s="0">
+        <v>1</v>
+      </c>
+      <c r="D477" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605189</t>
+        </is>
+      </c>
+      <c r="E477" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">富春染织</t>
+        </is>
+      </c>
+      <c r="F477" s="0">
+        <v>16.23</v>
+      </c>
+      <c r="G477" s="4">
+        <v>0.10033898305084744</v>
+      </c>
+      <c r="H477" s="4">
+        <v>0.4690460120324792</v>
+      </c>
+      <c r="I477" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J477" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 富春染织（605189）归入“业绩预增+筒子纱+染料+PEEK材料”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K477" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 10.0%）。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 34 家涨停，其中首板 19 家、2板及以上 15 家。</t>
+        </is>
+      </c>
+      <c r="L477" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="B478" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="C478" s="0">
+        <v>2</v>
+      </c>
+      <c r="D478" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002552</t>
+        </is>
+      </c>
+      <c r="E478" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">宝鼎科技</t>
+        </is>
+      </c>
+      <c r="F478" s="0">
+        <v>45.8</v>
+      </c>
+      <c r="G478" s="4">
+        <v>0.09990393852065305</v>
+      </c>
+      <c r="H478" s="4">
+        <v>0.3562357309003657</v>
+      </c>
+      <c r="I478" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J478" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 宝鼎科技（002552）归入“业绩预增+覆铜板+黄金采选”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K478" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 10.0%）。截至运行时成交量约为20日均量的 0.2 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 34 家涨停，其中首板 19 家、2板及以上 15 家。</t>
+        </is>
+      </c>
+      <c r="L478" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="B479" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="C479" s="0">
+        <v>3</v>
+      </c>
+      <c r="D479" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600408</t>
+        </is>
+      </c>
+      <c r="E479" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">安泰集团</t>
+        </is>
+      </c>
+      <c r="F479" s="0">
+        <v>4.06</v>
+      </c>
+      <c r="G479" s="4">
+        <v>0.10027100271002709</v>
+      </c>
+      <c r="H479" s="4">
+        <v>0.18060969648200043</v>
+      </c>
+      <c r="I479" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J479" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 安泰集团（600408）归入“焦炭+焦炉煤气制氢+大型H型钢”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K479" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.3 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 34 家涨停，其中首板 19 家、2板及以上 15 家。</t>
+        </is>
+      </c>
+      <c r="L479" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="B480" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="C480" s="0">
+        <v>4</v>
+      </c>
+      <c r="D480" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002029</t>
+        </is>
+      </c>
+      <c r="E480" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">七 匹 狼</t>
+        </is>
+      </c>
+      <c r="F480" s="0">
+        <v>10.58</v>
+      </c>
+      <c r="G480" s="4">
+        <v>0.0997920997920998</v>
+      </c>
+      <c r="H480" s="4">
+        <v>0.1612680571847864</v>
+      </c>
+      <c r="I480" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J480" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 七 匹 狼（002029）归入“夹克男装+投资科技+基金备案+海峡两岸”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K480" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.4 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 34 家涨停，其中首板 19 家、2板及以上 15 家。</t>
+        </is>
+      </c>
+      <c r="L480" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="B481" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="C481" s="0">
+        <v>5</v>
+      </c>
+      <c r="D481" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601811</t>
+        </is>
+      </c>
+      <c r="E481" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新华文轩</t>
+        </is>
+      </c>
+      <c r="F481" s="0">
+        <v>23.25</v>
+      </c>
+      <c r="G481" s="4">
+        <v>0.09981078524124885</v>
+      </c>
+      <c r="H481" s="4">
+        <v>0.15996506872685262</v>
+      </c>
+      <c r="I481" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J481" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 新华文轩（601811）归入“出版传媒+数字教育+民族出版收购”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K481" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.2 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 34 家涨停，其中首板 19 家、2板及以上 15 家。</t>
+        </is>
+      </c>
+      <c r="L481" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="B482" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="C482" s="0">
+        <v>6</v>
+      </c>
+      <c r="D482" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603533</t>
+        </is>
+      </c>
+      <c r="E482" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">掌阅科技</t>
+        </is>
+      </c>
+      <c r="F482" s="0">
+        <v>29.92</v>
+      </c>
+      <c r="G482" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H482" s="4">
+        <v>0.14785416908689147</v>
+      </c>
+      <c r="I482" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J482" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 掌阅科技（603533）归入“AI短剧+短剧出海+数字阅读”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K482" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 34 家涨停，其中首板 19 家、2板及以上 15 家。</t>
+        </is>
+      </c>
+      <c r="L482" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="B483" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="C483" s="0">
+        <v>7</v>
+      </c>
+      <c r="D483" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600252</t>
+        </is>
+      </c>
+      <c r="E483" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中恒集团</t>
+        </is>
+      </c>
+      <c r="F483" s="0">
+        <v>2.48</v>
+      </c>
+      <c r="G483" s="4">
+        <v>0.10222222222222221</v>
+      </c>
+      <c r="H483" s="4">
+        <v>0.14715739912637602</v>
+      </c>
+      <c r="I483" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J483" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 中恒集团（600252）归入“中药创新药+医药制造+回购注销”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K483" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.0 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 34 家涨停，其中首板 19 家、2板及以上 15 家。</t>
+        </is>
+      </c>
+      <c r="L483" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="B484" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="C484" s="0">
+        <v>8</v>
+      </c>
+      <c r="D484" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001216</t>
+        </is>
+      </c>
+      <c r="E484" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华瓷股份</t>
+        </is>
+      </c>
+      <c r="F484" s="0">
+        <v>23.99</v>
+      </c>
+      <c r="G484" s="4">
+        <v>0.09995414947271897</v>
+      </c>
+      <c r="H484" s="4">
+        <v>0.14514134659248926</v>
+      </c>
+      <c r="I484" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J484" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华瓷股份（001216）归入“氧化锆粉体+MLCC验证+越南基地+日用陶瓷”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K484" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 34 家涨停，其中首板 19 家、2板及以上 15 家。</t>
+        </is>
+      </c>
+      <c r="L484" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="B485" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="C485" s="0">
+        <v>9</v>
+      </c>
+      <c r="D485" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603598</t>
+        </is>
+      </c>
+      <c r="E485" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">引力传媒</t>
+        </is>
+      </c>
+      <c r="F485" s="0">
+        <v>21.91</v>
+      </c>
+      <c r="G485" s="4">
+        <v>0.09989959839357422</v>
+      </c>
+      <c r="H485" s="4">
+        <v>0.14232001242373887</v>
+      </c>
+      <c r="I485" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J485" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 引力传媒（603598）归入“AI短剧+全域营销+AI用研”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K485" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.2 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 34 家涨停，其中首板 19 家、2板及以上 15 家。</t>
+        </is>
+      </c>
+      <c r="L485" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="B486" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="C486" s="0">
+        <v>10</v>
+      </c>
+      <c r="D486" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603258</t>
+        </is>
+      </c>
+      <c r="E486" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">电魂网络</t>
+        </is>
+      </c>
+      <c r="F486" s="0">
+        <v>16.15</v>
+      </c>
+      <c r="G486" s="4">
+        <v>0.10013623978201626</v>
+      </c>
+      <c r="H486" s="4">
+        <v>0.12975245547645378</v>
+      </c>
+      <c r="I486" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J486" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 电魂网络（603258）归入“AI游戏+修仙时代+梦三国IP”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K486" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.2 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 34 家涨停，其中首板 19 家、2板及以上 15 家。</t>
+        </is>
+      </c>
+      <c r="L486" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="B487" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="C487" s="0">
+        <v>11</v>
+      </c>
+      <c r="D487" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600121</t>
+        </is>
+      </c>
+      <c r="E487" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">郑州煤电</t>
+        </is>
+      </c>
+      <c r="F487" s="0">
+        <v>5.86</v>
+      </c>
+      <c r="G487" s="4">
+        <v>0.09943714821763618</v>
+      </c>
+      <c r="H487" s="4">
+        <v>0.12300346423392788</v>
+      </c>
+      <c r="I487" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J487" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 郑州煤电（600121）归入“煤炭涨价+煤炭主业+国企控股”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K487" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 34 家涨停，其中首板 19 家、2板及以上 15 家。</t>
+        </is>
+      </c>
+      <c r="L487" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="B488" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="C488" s="0">
+        <v>12</v>
+      </c>
+      <c r="D488" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002469</t>
+        </is>
+      </c>
+      <c r="E488" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">三维化学</t>
+        </is>
+      </c>
+      <c r="F488" s="0">
+        <v>6.86</v>
+      </c>
+      <c r="G488" s="4">
+        <v>0.09935897435897445</v>
+      </c>
+      <c r="H488" s="4">
+        <v>0.11332966635264342</v>
+      </c>
+      <c r="I488" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J488" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 三维化学（002469）归入“异辛酸项目+储能工程+硫磺回收”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K488" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.0 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 34 家涨停，其中首板 19 家、2板及以上 15 家。</t>
+        </is>
+      </c>
+      <c r="L488" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="B489" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="C489" s="0">
+        <v>13</v>
+      </c>
+      <c r="D489" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601858</t>
+        </is>
+      </c>
+      <c r="E489" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中国科传</t>
+        </is>
+      </c>
+      <c r="F489" s="0">
+        <v>26.11</v>
+      </c>
+      <c r="G489" s="4">
+        <v>0.09983150800336983</v>
+      </c>
+      <c r="H489" s="4">
+        <v>0.1116770927298065</v>
+      </c>
+      <c r="I489" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J489" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 中国科传（601858）归入“AI应用+数字教育+出版+央企”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K489" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.7 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 34 家涨停，其中首板 19 家、2板及以上 15 家。</t>
+        </is>
+      </c>
+      <c r="L489" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="B490" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="C490" s="0">
+        <v>14</v>
+      </c>
+      <c r="D490" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603992</t>
+        </is>
+      </c>
+      <c r="E490" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">松霖科技</t>
+        </is>
+      </c>
+      <c r="F490" s="0">
+        <v>24.61</v>
+      </c>
+      <c r="G490" s="4">
+        <v>0.10013410818059887</v>
+      </c>
+      <c r="H490" s="4">
+        <v>0.10398028532865275</v>
+      </c>
+      <c r="I490" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J490" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 松霖科技（603992）归入“服务机器人+大健康硬件+智能厨卫”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K490" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.2 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 34 家涨停，其中首板 19 家、2板及以上 15 家。</t>
+        </is>
+      </c>
+      <c r="L490" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="B491" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="C491" s="0">
+        <v>15</v>
+      </c>
+      <c r="D491" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000601</t>
+        </is>
+      </c>
+      <c r="E491" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">韶能股份</t>
+        </is>
+      </c>
+      <c r="F491" s="0">
+        <v>6.82</v>
+      </c>
+      <c r="G491" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H491" s="4">
+        <v>0.1038856738819736</v>
+      </c>
+      <c r="I491" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J491" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 韶能股份（000601）归入“清洁能源+算电协同+三季报预增”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K491" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.0 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 34 家涨停，其中首板 19 家、2板及以上 15 家。</t>
+        </is>
+      </c>
+      <c r="L491" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="B492" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="C492" s="0">
+        <v>16</v>
+      </c>
+      <c r="D492" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001299</t>
+        </is>
+      </c>
+      <c r="E492" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">美能能源</t>
+        </is>
+      </c>
+      <c r="F492" s="0">
+        <v>10.92</v>
+      </c>
+      <c r="G492" s="4">
+        <v>0.09969788519637458</v>
+      </c>
+      <c r="H492" s="4">
+        <v>0.10061330812944588</v>
+      </c>
+      <c r="I492" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J492" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 美能能源（001299）归入“城镇燃气+智慧燃气+工商业储能”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K492" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 34 家涨停，其中首板 19 家、2板及以上 15 家。</t>
+        </is>
+      </c>
+      <c r="L492" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="B493" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="C493" s="0">
+        <v>17</v>
+      </c>
+      <c r="D493" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600097</t>
+        </is>
+      </c>
+      <c r="E493" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">开创国际</t>
+        </is>
+      </c>
+      <c r="F493" s="0">
+        <v>10.2</v>
+      </c>
+      <c r="G493" s="4">
+        <v>0.10032362459546927</v>
+      </c>
+      <c r="H493" s="4">
+        <v>0.0923635741944264</v>
+      </c>
+      <c r="I493" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J493" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 开创国际（600097）归入“远洋捕捞+金枪鱼+南极磷虾”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K493" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.7 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 34 家涨停，其中首板 19 家、2板及以上 15 家。</t>
+        </is>
+      </c>
+      <c r="L493" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="B494" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="C494" s="0">
+        <v>18</v>
+      </c>
+      <c r="D494" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000573</t>
+        </is>
+      </c>
+      <c r="E494" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">粤宏远Ａ</t>
+        </is>
+      </c>
+      <c r="F494" s="0">
+        <v>4.33</v>
+      </c>
+      <c r="G494" s="4">
+        <v>0.09898477157360407</v>
+      </c>
+      <c r="H494" s="4">
+        <v>0.0881926035511687</v>
+      </c>
+      <c r="I494" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J494" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 粤宏远Ａ（000573）归入“东莞地产+再生铅+产业转型”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K494" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.4 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 34 家涨停，其中首板 19 家、2板及以上 15 家。</t>
+        </is>
+      </c>
+      <c r="L494" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="B495" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="C495" s="0">
+        <v>19</v>
+      </c>
+      <c r="D495" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603656</t>
+        </is>
+      </c>
+      <c r="E495" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">泰禾智能</t>
+        </is>
+      </c>
+      <c r="F495" s="0">
+        <v>19.06</v>
+      </c>
+      <c r="G495" s="4">
+        <v>0.09982688978649733</v>
+      </c>
+      <c r="H495" s="4">
+        <v>0.08250281610165097</v>
+      </c>
+      <c r="I495" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J495" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 泰禾智能（603656）归入“增持+储能+智能分选”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K495" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 5.0 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 34 家涨停，其中首板 19 家、2板及以上 15 家。</t>
+        </is>
+      </c>
+      <c r="L495" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M93"/>
+  <dimension ref="A1:M103"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -31182,6 +32208,596 @@
       <c r="M93" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">3.72</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="B94" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C94" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D94" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002917</t>
+        </is>
+      </c>
+      <c r="E94" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金奥博</t>
+        </is>
+      </c>
+      <c r="F94" s="4">
+        <v>0.2532364290908264</v>
+      </c>
+      <c r="G94" s="4">
+        <v>0.06909090909090909</v>
+      </c>
+      <c r="H94" s="4">
+        <v>0.09999999999999987</v>
+      </c>
+      <c r="I94" s="4">
+        <v>0.09999999999999987</v>
+      </c>
+      <c r="J94" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K94" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +10.00%</t>
+        </is>
+      </c>
+      <c r="L94" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M94" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="B95" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C95" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D95" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002322</t>
+        </is>
+      </c>
+      <c r="E95" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">理工能科</t>
+        </is>
+      </c>
+      <c r="F95" s="4">
+        <v>0.24909064874301617</v>
+      </c>
+      <c r="G95" s="4">
+        <v>0.002293577981651307</v>
+      </c>
+      <c r="H95" s="4">
+        <v>0.01911314984709489</v>
+      </c>
+      <c r="I95" s="4">
+        <v>-0.04587155963302747</v>
+      </c>
+      <c r="J95" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K95" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -4.59%</t>
+        </is>
+      </c>
+      <c r="L95" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M95" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="B96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="D96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603188</t>
+        </is>
+      </c>
+      <c r="E96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">亚邦股份</t>
+        </is>
+      </c>
+      <c r="F96" s="4">
+        <v>0.18066471930035738</v>
+      </c>
+      <c r="G96" s="4">
+        <v>0.1007326007326006</v>
+      </c>
+      <c r="H96" s="4">
+        <v>0.1007326007326006</v>
+      </c>
+      <c r="I96" s="4">
+        <v>-0.056776556776556686</v>
+      </c>
+      <c r="J96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -5.68%</t>
+        </is>
+      </c>
+      <c r="L96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="B97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="D97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600847</t>
+        </is>
+      </c>
+      <c r="E97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">万里股份</t>
+        </is>
+      </c>
+      <c r="F97" s="4">
+        <v>0.17154647722411606</v>
+      </c>
+      <c r="G97" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H97" s="4">
+        <v>0.09978617248752686</v>
+      </c>
+      <c r="I97" s="4">
+        <v>0.09978617248752686</v>
+      </c>
+      <c r="J97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +9.98%</t>
+        </is>
+      </c>
+      <c r="L97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="B98" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C98" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="D98" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002811</t>
+        </is>
+      </c>
+      <c r="E98" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">郑中设计</t>
+        </is>
+      </c>
+      <c r="F98" s="4">
+        <v>0.1680074240151696</v>
+      </c>
+      <c r="G98" s="4">
+        <v>0.021213616181549044</v>
+      </c>
+      <c r="H98" s="4">
+        <v>0.08090774543660584</v>
+      </c>
+      <c r="I98" s="4">
+        <v>0.021213616181549044</v>
+      </c>
+      <c r="J98" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K98" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +2.12%</t>
+        </is>
+      </c>
+      <c r="L98" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M98" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="B99" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C99" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="D99" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603980</t>
+        </is>
+      </c>
+      <c r="E99" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">吉华集团</t>
+        </is>
+      </c>
+      <c r="F99" s="4">
+        <v>0.16537005312848457</v>
+      </c>
+      <c r="G99" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H99" s="4">
+        <v>0.0534208059981256</v>
+      </c>
+      <c r="I99" s="4">
+        <v>-0.05529522024367384</v>
+      </c>
+      <c r="J99" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K99" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -5.53%</t>
+        </is>
+      </c>
+      <c r="L99" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M99" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="B100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="D100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603386</t>
+        </is>
+      </c>
+      <c r="E100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">骏亚科技</t>
+        </is>
+      </c>
+      <c r="F100" s="4">
+        <v>0.16262410879927341</v>
+      </c>
+      <c r="G100" s="4">
+        <v>0.024613623354321712</v>
+      </c>
+      <c r="H100" s="4">
+        <v>0.08643388666285068</v>
+      </c>
+      <c r="I100" s="4">
+        <v>0.05380652547223819</v>
+      </c>
+      <c r="J100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +5.38%</t>
+        </is>
+      </c>
+      <c r="L100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18.41</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="B101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="D101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001318</t>
+        </is>
+      </c>
+      <c r="E101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">阳光乳业</t>
+        </is>
+      </c>
+      <c r="F101" s="4">
+        <v>0.1583942009374842</v>
+      </c>
+      <c r="G101" s="4">
+        <v>0.09978617248752686</v>
+      </c>
+      <c r="H101" s="4">
+        <v>0.09978617248752686</v>
+      </c>
+      <c r="I101" s="4">
+        <v>0.09978617248752686</v>
+      </c>
+      <c r="J101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +9.98%</t>
+        </is>
+      </c>
+      <c r="L101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="B102" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C102" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="D102" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605058</t>
+        </is>
+      </c>
+      <c r="E102" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">澳弘电子</t>
+        </is>
+      </c>
+      <c r="F102" s="4">
+        <v>0.1554379886943238</v>
+      </c>
+      <c r="G102" s="4">
+        <v>0.03692664348402053</v>
+      </c>
+      <c r="H102" s="4">
+        <v>0.10001655903295248</v>
+      </c>
+      <c r="I102" s="4">
+        <v>0.06110283159463492</v>
+      </c>
+      <c r="J102" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K102" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +6.11%</t>
+        </is>
+      </c>
+      <c r="L102" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M102" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="B103" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="C103" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="D103" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600802</t>
+        </is>
+      </c>
+      <c r="E103" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">福建水泥</t>
+        </is>
+      </c>
+      <c r="F103" s="4">
+        <v>0.15266801915501513</v>
+      </c>
+      <c r="G103" s="4">
+        <v>-0.025139664804469275</v>
+      </c>
+      <c r="H103" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I103" s="4">
+        <v>-0.06424581005586594</v>
+      </c>
+      <c r="J103" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K103" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -6.42%</t>
+        </is>
+      </c>
+      <c r="L103" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M103" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.7</t>
         </is>
       </c>
     </row>
@@ -31273,28 +32889,28 @@
         </is>
       </c>
       <c r="B3" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" s="4">
-        <v>0.3333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="F3" s="4">
-        <v>0.2413793103448276</v>
+        <v>0.1509433962264151</v>
       </c>
       <c r="G3" s="0">
-        <v>1.3809523809523807</v>
+        <v>2.6500000000000004</v>
       </c>
       <c r="H3" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3" s="4">
-        <v>0.3333333333333333</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="4">
@@ -31304,28 +32920,28 @@
         </is>
       </c>
       <c r="B4" s="0">
+        <v>10</v>
+      </c>
+      <c r="C4" s="0">
+        <v>30</v>
+      </c>
+      <c r="D4" s="0">
         <v>9</v>
       </c>
-      <c r="C4" s="0">
-        <v>27</v>
-      </c>
-      <c r="D4" s="0">
-        <v>8</v>
-      </c>
       <c r="E4" s="4">
-        <v>0.2962962962962963</v>
+        <v>0.3</v>
       </c>
       <c r="F4" s="4">
-        <v>0.2413793103448276</v>
+        <v>0.1509433962264151</v>
       </c>
       <c r="G4" s="0">
-        <v>1.2275132275132274</v>
+        <v>1.9875</v>
       </c>
       <c r="H4" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I4" s="4">
-        <v>0.5555555555555556</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="5">
@@ -31335,28 +32951,28 @@
         </is>
       </c>
       <c r="B5" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" s="0">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D5" s="0">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E5" s="4">
-        <v>0.25925925925925924</v>
+        <v>0.26666666666666666</v>
       </c>
       <c r="F5" s="4">
-        <v>0.2413793103448276</v>
+        <v>0.1509433962264151</v>
       </c>
       <c r="G5" s="0">
-        <v>1.074074074074074</v>
+        <v>1.7666666666666666</v>
       </c>
       <c r="H5" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I5" s="4">
-        <v>0.7777777777777778</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="6">
@@ -31366,28 +32982,28 @@
         </is>
       </c>
       <c r="B6" s="0">
+        <v>10</v>
+      </c>
+      <c r="C6" s="0">
+        <v>100</v>
+      </c>
+      <c r="D6" s="0">
+        <v>23</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0.23</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.1509433962264151</v>
+      </c>
+      <c r="G6" s="0">
+        <v>1.5237500000000002</v>
+      </c>
+      <c r="H6" s="0">
         <v>9</v>
       </c>
-      <c r="C6" s="0">
-        <v>90</v>
-      </c>
-      <c r="D6" s="0">
-        <v>20</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0.2222222222222222</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0.2413793103448276</v>
-      </c>
-      <c r="G6" s="0">
-        <v>0.9206349206349206</v>
-      </c>
-      <c r="H6" s="0">
-        <v>8</v>
-      </c>
       <c r="I6" s="4">
-        <v>0.8888888888888888</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="7">

--- a/docs/downloads/latest.xlsx
+++ b/docs/downloads/latest.xlsx
@@ -93,7 +93,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L495"/>
+  <dimension ref="A1:L523"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -26779,13 +26779,1525 @@
         </is>
       </c>
     </row>
+    <row r="496">
+      <c r="A496" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B496" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C496" s="0">
+        <v>1</v>
+      </c>
+      <c r="D496" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002815</t>
+        </is>
+      </c>
+      <c r="E496" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">崇达技术</t>
+        </is>
+      </c>
+      <c r="F496" s="0">
+        <v>23.25</v>
+      </c>
+      <c r="G496" s="4">
+        <v>0.09981078524124885</v>
+      </c>
+      <c r="H496" s="4">
+        <v>0.39049809086069387</v>
+      </c>
+      <c r="I496" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J496" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 崇达技术（002815）归入“业绩预增+高端PCB+服务器PCB”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K496" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 10.0%）。截至运行时成交量约为20日均量的 0.2 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 34 家涨停，其中首板 28 家、2板及以上 6 家。</t>
+        </is>
+      </c>
+      <c r="L496" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B497" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C497" s="0">
+        <v>2</v>
+      </c>
+      <c r="D497" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000626</t>
+        </is>
+      </c>
+      <c r="E497" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">远大控股</t>
+        </is>
+      </c>
+      <c r="F497" s="0">
+        <v>9.15</v>
+      </c>
+      <c r="G497" s="4">
+        <v>0.09975961538461542</v>
+      </c>
+      <c r="H497" s="4">
+        <v>0.3424049153221247</v>
+      </c>
+      <c r="I497" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J497" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 远大控股（000626）归入“业绩预增+大宗贸易+中药材种业”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K497" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 9.6%）。截至运行时成交量约为20日均量的 2.3 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 34 家涨停，其中首板 28 家、2板及以上 6 家。</t>
+        </is>
+      </c>
+      <c r="L497" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B498" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C498" s="0">
+        <v>3</v>
+      </c>
+      <c r="D498" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605058</t>
+        </is>
+      </c>
+      <c r="E498" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">澳弘电子</t>
+        </is>
+      </c>
+      <c r="F498" s="0">
+        <v>70.49</v>
+      </c>
+      <c r="G498" s="4">
+        <v>0.1000312109862671</v>
+      </c>
+      <c r="H498" s="4">
+        <v>0.22159529829690788</v>
+      </c>
+      <c r="I498" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J498" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 澳弘电子（605058）归入“PCB+AI服务器电源+汽车电子”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K498" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 34 家涨停，其中首板 28 家、2板及以上 6 家。</t>
+        </is>
+      </c>
+      <c r="L498" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大；近5日涨幅偏高，短线获利盘压力更大</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B499" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C499" s="0">
+        <v>4</v>
+      </c>
+      <c r="D499" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600812</t>
+        </is>
+      </c>
+      <c r="E499" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华北制药</t>
+        </is>
+      </c>
+      <c r="F499" s="0">
+        <v>6.57</v>
+      </c>
+      <c r="G499" s="4">
+        <v>0.10050251256281406</v>
+      </c>
+      <c r="H499" s="4">
+        <v>0.1599164699009189</v>
+      </c>
+      <c r="I499" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J499" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华北制药（600812）归入“抗感染药+鼠疫适应症+创新药研发”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K499" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.4 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 34 家涨停，其中首板 28 家、2板及以上 6 家。</t>
+        </is>
+      </c>
+      <c r="L499" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B500" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C500" s="0">
+        <v>5</v>
+      </c>
+      <c r="D500" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603200</t>
+        </is>
+      </c>
+      <c r="E500" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上海洗霸</t>
+        </is>
+      </c>
+      <c r="F500" s="0">
+        <v>53.35</v>
+      </c>
+      <c r="G500" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H500" s="4">
+        <v>0.15164598119971337</v>
+      </c>
+      <c r="I500" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J500" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 上海洗霸（603200）归入“固态电池+水处理+数据中心液冷”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K500" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.8 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 34 家涨停，其中首板 28 家、2板及以上 6 家。</t>
+        </is>
+      </c>
+      <c r="L500" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B501" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C501" s="0">
+        <v>6</v>
+      </c>
+      <c r="D501" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603230</t>
+        </is>
+      </c>
+      <c r="E501" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">内蒙新华</t>
+        </is>
+      </c>
+      <c r="F501" s="0">
+        <v>14.52</v>
+      </c>
+      <c r="G501" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H501" s="4">
+        <v>0.1447166312496263</v>
+      </c>
+      <c r="I501" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J501" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 内蒙新华（603230）归入“出版发行+教材教辅+文化消费”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K501" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 34 家涨停，其中首板 28 家、2板及以上 6 家。</t>
+        </is>
+      </c>
+      <c r="L501" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B502" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C502" s="0">
+        <v>7</v>
+      </c>
+      <c r="D502" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000995</t>
+        </is>
+      </c>
+      <c r="E502" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">皇台酒业</t>
+        </is>
+      </c>
+      <c r="F502" s="0">
+        <v>13.37</v>
+      </c>
+      <c r="G502" s="4">
+        <v>0.10041152263374474</v>
+      </c>
+      <c r="H502" s="4">
+        <v>0.1423334266019338</v>
+      </c>
+      <c r="I502" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J502" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 皇台酒业（000995）归入“白酒+区域品牌+老窖池”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K502" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.9 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 34 家涨停，其中首板 28 家、2板及以上 6 家。</t>
+        </is>
+      </c>
+      <c r="L502" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B503" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C503" s="0">
+        <v>8</v>
+      </c>
+      <c r="D503" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002543</t>
+        </is>
+      </c>
+      <c r="E503" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">万和电气</t>
+        </is>
+      </c>
+      <c r="F503" s="0">
+        <v>7.88</v>
+      </c>
+      <c r="G503" s="4">
+        <v>0.1005586592178771</v>
+      </c>
+      <c r="H503" s="4">
+        <v>0.1390992504383719</v>
+      </c>
+      <c r="I503" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J503" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 万和电气（002543）归入“热水采暖+空气能热泵+海外布局”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K503" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 34 家涨停，其中首板 28 家、2板及以上 6 家。</t>
+        </is>
+      </c>
+      <c r="L503" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B504" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C504" s="0">
+        <v>9</v>
+      </c>
+      <c r="D504" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">003029</t>
+        </is>
+      </c>
+      <c r="E504" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">吉大正元</t>
+        </is>
+      </c>
+      <c r="F504" s="0">
+        <v>19.99</v>
+      </c>
+      <c r="G504" s="4">
+        <v>0.10016510731975758</v>
+      </c>
+      <c r="H504" s="4">
+        <v>0.13865700805167439</v>
+      </c>
+      <c r="I504" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J504" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 吉大正元（003029）归入“密码安全+数字货币+商业航天”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K504" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 34 家涨停，其中首板 28 家、2板及以上 6 家。</t>
+        </is>
+      </c>
+      <c r="L504" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B505" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C505" s="0">
+        <v>10</v>
+      </c>
+      <c r="D505" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603999</t>
+        </is>
+      </c>
+      <c r="E505" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">读者传媒</t>
+        </is>
+      </c>
+      <c r="F505" s="0">
+        <v>7.62</v>
+      </c>
+      <c r="G505" s="4">
+        <v>0.09956709956709965</v>
+      </c>
+      <c r="H505" s="4">
+        <v>0.13699222573492967</v>
+      </c>
+      <c r="I505" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J505" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 读者传媒（603999）归入“出版发行+人工智能+读者品牌”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K505" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.7 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 34 家涨停，其中首板 28 家、2板及以上 6 家。</t>
+        </is>
+      </c>
+      <c r="L505" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B506" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C506" s="0">
+        <v>11</v>
+      </c>
+      <c r="D506" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603386</t>
+        </is>
+      </c>
+      <c r="E506" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">骏亚科技</t>
+        </is>
+      </c>
+      <c r="F506" s="0">
+        <v>20.25</v>
+      </c>
+      <c r="G506" s="4">
+        <v>0.09994568169473105</v>
+      </c>
+      <c r="H506" s="4">
+        <v>0.1264906713910392</v>
+      </c>
+      <c r="I506" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J506" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 骏亚科技（603386）归入“PCB+高多层HDI+人形机器人”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K506" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 34 家涨停，其中首板 28 家、2板及以上 6 家。</t>
+        </is>
+      </c>
+      <c r="L506" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B507" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C507" s="0">
+        <v>12</v>
+      </c>
+      <c r="D507" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603172</t>
+        </is>
+      </c>
+      <c r="E507" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">万丰股份</t>
+        </is>
+      </c>
+      <c r="F507" s="0">
+        <v>20.53</v>
+      </c>
+      <c r="G507" s="4">
+        <v>0.10021436227224022</v>
+      </c>
+      <c r="H507" s="4">
+        <v>0.12400135963900435</v>
+      </c>
+      <c r="I507" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J507" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 万丰股份（603172）归入“分散染料+产能翻番+业绩增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K507" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 34 家涨停，其中首板 28 家、2板及以上 6 家。</t>
+        </is>
+      </c>
+      <c r="L507" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B508" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C508" s="0">
+        <v>13</v>
+      </c>
+      <c r="D508" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605003</t>
+        </is>
+      </c>
+      <c r="E508" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">众望布艺</t>
+        </is>
+      </c>
+      <c r="F508" s="0">
+        <v>25.96</v>
+      </c>
+      <c r="G508" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H508" s="4">
+        <v>0.12187163353831604</v>
+      </c>
+      <c r="I508" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J508" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 众望布艺（605003）归入“装饰面料+外销+股权激励”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K508" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.2 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 34 家涨停，其中首板 28 家、2板及以上 6 家。</t>
+        </is>
+      </c>
+      <c r="L508" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B509" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C509" s="0">
+        <v>14</v>
+      </c>
+      <c r="D509" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001225</t>
+        </is>
+      </c>
+      <c r="E509" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">和泰机电</t>
+        </is>
+      </c>
+      <c r="F509" s="0">
+        <v>38.5</v>
+      </c>
+      <c r="G509" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H509" s="4">
+        <v>0.12175142170285376</v>
+      </c>
+      <c r="I509" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J509" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 和泰机电（001225）归入“物料输送设备+一带一路+水泥建材”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K509" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.8 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 34 家涨停，其中首板 28 家、2板及以上 6 家。</t>
+        </is>
+      </c>
+      <c r="L509" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B510" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C510" s="0">
+        <v>15</v>
+      </c>
+      <c r="D510" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600721</t>
+        </is>
+      </c>
+      <c r="E510" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">百花医药</t>
+        </is>
+      </c>
+      <c r="F510" s="0">
+        <v>12.05</v>
+      </c>
+      <c r="G510" s="4">
+        <v>0.10045662100456632</v>
+      </c>
+      <c r="H510" s="4">
+        <v>0.12162519808710137</v>
+      </c>
+      <c r="I510" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J510" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 百花医药（600721）归入“医药研发+复杂制剂+金华国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K510" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.6 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 34 家涨停，其中首板 28 家、2板及以上 6 家。</t>
+        </is>
+      </c>
+      <c r="L510" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B511" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C511" s="0">
+        <v>16</v>
+      </c>
+      <c r="D511" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000722</t>
+        </is>
+      </c>
+      <c r="E511" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湖南发展</t>
+        </is>
+      </c>
+      <c r="F511" s="0">
+        <v>13.95</v>
+      </c>
+      <c r="G511" s="4">
+        <v>0.10015772870662465</v>
+      </c>
+      <c r="H511" s="4">
+        <v>0.10883831522075572</v>
+      </c>
+      <c r="I511" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J511" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 湖南发展（000722）归入“业绩预增+水力发电”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K511" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.8 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 34 家涨停，其中首板 28 家、2板及以上 6 家。</t>
+        </is>
+      </c>
+      <c r="L511" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B512" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C512" s="0">
+        <v>17</v>
+      </c>
+      <c r="D512" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002836</t>
+        </is>
+      </c>
+      <c r="E512" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新宏泽</t>
+        </is>
+      </c>
+      <c r="F512" s="0">
+        <v>11.85</v>
+      </c>
+      <c r="G512" s="4">
+        <v>0.10027855153203348</v>
+      </c>
+      <c r="H512" s="4">
+        <v>0.10587935074710868</v>
+      </c>
+      <c r="I512" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J512" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 新宏泽（002836）归入“烟标印刷+多元化布局+未减持”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K512" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.7 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 34 家涨停，其中首板 28 家、2板及以上 6 家。</t>
+        </is>
+      </c>
+      <c r="L512" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B513" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C513" s="0">
+        <v>18</v>
+      </c>
+      <c r="D513" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603535</t>
+        </is>
+      </c>
+      <c r="E513" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">嘉诚国际</t>
+        </is>
+      </c>
+      <c r="F513" s="0">
+        <v>6.73</v>
+      </c>
+      <c r="G513" s="4">
+        <v>0.09967320261437917</v>
+      </c>
+      <c r="H513" s="4">
+        <v>0.10286424763079623</v>
+      </c>
+      <c r="I513" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J513" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 嘉诚国际（603535）归入“跨境物流+海南仓储+高端制造”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K513" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.5 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 34 家涨停，其中首板 28 家、2板及以上 6 家。</t>
+        </is>
+      </c>
+      <c r="L513" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B514" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C514" s="0">
+        <v>19</v>
+      </c>
+      <c r="D514" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002103</t>
+        </is>
+      </c>
+      <c r="E514" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">广博股份</t>
+        </is>
+      </c>
+      <c r="F514" s="0">
+        <v>7.5</v>
+      </c>
+      <c r="G514" s="4">
+        <v>0.0997067448680351</v>
+      </c>
+      <c r="H514" s="4">
+        <v>0.0985135257416399</v>
+      </c>
+      <c r="I514" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J514" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 广博股份（002103）归入“国网入围+IP卡牌+文教用品”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K514" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.4 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 34 家涨停，其中首板 28 家、2板及以上 6 家。</t>
+        </is>
+      </c>
+      <c r="L514" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B515" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C515" s="0">
+        <v>20</v>
+      </c>
+      <c r="D515" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002748</t>
+        </is>
+      </c>
+      <c r="E515" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">世龙实业</t>
+        </is>
+      </c>
+      <c r="F515" s="0">
+        <v>13.65</v>
+      </c>
+      <c r="G515" s="4">
+        <v>0.09991941982272357</v>
+      </c>
+      <c r="H515" s="4">
+        <v>0.09820372731691965</v>
+      </c>
+      <c r="I515" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J515" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 世龙实业（002748）归入“染料产业链+氯化亚砜+中报增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K515" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.1 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 34 家涨停，其中首板 28 家、2板及以上 6 家。</t>
+        </is>
+      </c>
+      <c r="L515" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B516" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C516" s="0">
+        <v>21</v>
+      </c>
+      <c r="D516" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603690</t>
+        </is>
+      </c>
+      <c r="E516" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">至纯科技</t>
+        </is>
+      </c>
+      <c r="F516" s="0">
+        <v>23.77</v>
+      </c>
+      <c r="G516" s="4">
+        <v>0.09995372512725599</v>
+      </c>
+      <c r="H516" s="4">
+        <v>0.09720463751615065</v>
+      </c>
+      <c r="I516" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J516" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 至纯科技（603690）归入“半导体湿法设备+HBM+高纯工艺系统”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K516" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 34 家涨停，其中首板 28 家、2板及以上 6 家。</t>
+        </is>
+      </c>
+      <c r="L516" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B517" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C517" s="0">
+        <v>22</v>
+      </c>
+      <c r="D517" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600281</t>
+        </is>
+      </c>
+      <c r="E517" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华阳新材</t>
+        </is>
+      </c>
+      <c r="F517" s="0">
+        <v>5.21</v>
+      </c>
+      <c r="G517" s="4">
+        <v>0.09915611814345994</v>
+      </c>
+      <c r="H517" s="4">
+        <v>0.09495633633755451</v>
+      </c>
+      <c r="I517" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J517" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华阳新材（600281）归入“贵金属回收+新品研发+山西国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K517" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.9 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 34 家涨停，其中首板 28 家、2板及以上 6 家。</t>
+        </is>
+      </c>
+      <c r="L517" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B518" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C518" s="0">
+        <v>23</v>
+      </c>
+      <c r="D518" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603237</t>
+        </is>
+      </c>
+      <c r="E518" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">五芳斋</t>
+        </is>
+      </c>
+      <c r="F518" s="0">
+        <v>16.47</v>
+      </c>
+      <c r="G518" s="4">
+        <v>0.10020040080160308</v>
+      </c>
+      <c r="H518" s="4">
+        <v>0.0933571210324888</v>
+      </c>
+      <c r="I518" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J518" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 五芳斋（603237）归入“粽子+中华老字号+业绩韧性”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K518" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.9 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 34 家涨停，其中首板 28 家、2板及以上 6 家。</t>
+        </is>
+      </c>
+      <c r="L518" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B519" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C519" s="0">
+        <v>24</v>
+      </c>
+      <c r="D519" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002134</t>
+        </is>
+      </c>
+      <c r="E519" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天津普林</t>
+        </is>
+      </c>
+      <c r="F519" s="0">
+        <v>24.34</v>
+      </c>
+      <c r="G519" s="4">
+        <v>0.09986443741527351</v>
+      </c>
+      <c r="H519" s="4">
+        <v>0.09223115888996407</v>
+      </c>
+      <c r="I519" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J519" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 天津普林（002134）归入“PCB+股票期权+产能释放”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K519" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 34 家涨停，其中首板 28 家、2板及以上 6 家。</t>
+        </is>
+      </c>
+      <c r="L519" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B520" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C520" s="0">
+        <v>25</v>
+      </c>
+      <c r="D520" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603329</t>
+        </is>
+      </c>
+      <c r="E520" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上海雅仕</t>
+        </is>
+      </c>
+      <c r="F520" s="0">
+        <v>11.33</v>
+      </c>
+      <c r="G520" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H520" s="4">
+        <v>0.08806869365376585</v>
+      </c>
+      <c r="I520" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J520" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 上海雅仕（603329）归入“供应链物流+硫磺涨价+业绩增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K520" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 5.4 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 34 家涨停，其中首板 28 家、2板及以上 6 家。</t>
+        </is>
+      </c>
+      <c r="L520" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B521" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C521" s="0">
+        <v>26</v>
+      </c>
+      <c r="D521" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600668</t>
+        </is>
+      </c>
+      <c r="E521" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">尖峰集团</t>
+        </is>
+      </c>
+      <c r="F521" s="0">
+        <v>7.99</v>
+      </c>
+      <c r="G521" s="4">
+        <v>0.1005509641873279</v>
+      </c>
+      <c r="H521" s="4">
+        <v>0.08096844376044074</v>
+      </c>
+      <c r="I521" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J521" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 尖峰集团（600668）归入“医药+水泥熟料+原料药”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K521" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 6.6 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 34 家涨停，其中首板 28 家、2板及以上 6 家。</t>
+        </is>
+      </c>
+      <c r="L521" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B522" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C522" s="0">
+        <v>27</v>
+      </c>
+      <c r="D522" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002889</t>
+        </is>
+      </c>
+      <c r="E522" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东方嘉盛</t>
+        </is>
+      </c>
+      <c r="F522" s="0">
+        <v>13.01</v>
+      </c>
+      <c r="G522" s="4">
+        <v>0.09974640743871512</v>
+      </c>
+      <c r="H522" s="4">
+        <v>0.07751282379109807</v>
+      </c>
+      <c r="I522" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J522" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 东方嘉盛（002889）归入“半导体设备服务+跨境物流+智能报关”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K522" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 5.6 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 34 家涨停，其中首板 28 家、2板及以上 6 家。</t>
+        </is>
+      </c>
+      <c r="L522" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B523" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C523" s="0">
+        <v>28</v>
+      </c>
+      <c r="D523" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002945</t>
+        </is>
+      </c>
+      <c r="E523" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华林证券</t>
+        </is>
+      </c>
+      <c r="F523" s="0">
+        <v>15.39</v>
+      </c>
+      <c r="G523" s="4">
+        <v>0.10007147962830597</v>
+      </c>
+      <c r="H523" s="4">
+        <v>0.07633561086680034</v>
+      </c>
+      <c r="I523" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J523" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华林证券（002945）归入“西藏券商+财富管理+AI金融”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K523" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 5.1 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 34 家涨停，其中首板 28 家、2板及以上 6 家。</t>
+        </is>
+      </c>
+      <c r="L523" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M103"/>
+  <dimension ref="A1:M113"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -32798,6 +34310,596 @@
       <c r="M103" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">6.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B104" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="C104" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D104" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605189</t>
+        </is>
+      </c>
+      <c r="E104" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">富春染织</t>
+        </is>
+      </c>
+      <c r="F104" s="4">
+        <v>0.4690460120324792</v>
+      </c>
+      <c r="G104" s="4">
+        <v>0.09981515711645117</v>
+      </c>
+      <c r="H104" s="4">
+        <v>0.09981515711645117</v>
+      </c>
+      <c r="I104" s="4">
+        <v>0.09981515711645117</v>
+      </c>
+      <c r="J104" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K104" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +9.98%</t>
+        </is>
+      </c>
+      <c r="L104" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M104" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="C105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002552</t>
+        </is>
+      </c>
+      <c r="E105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">宝鼎科技</t>
+        </is>
+      </c>
+      <c r="F105" s="4">
+        <v>0.3562357309003657</v>
+      </c>
+      <c r="G105" s="4">
+        <v>0.048034934497816595</v>
+      </c>
+      <c r="H105" s="4">
+        <v>0.09061135371179052</v>
+      </c>
+      <c r="I105" s="4">
+        <v>0.020305676855895127</v>
+      </c>
+      <c r="J105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +2.03%</t>
+        </is>
+      </c>
+      <c r="L105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="C106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="D106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600408</t>
+        </is>
+      </c>
+      <c r="E106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">安泰集团</t>
+        </is>
+      </c>
+      <c r="F106" s="4">
+        <v>0.18060969648200043</v>
+      </c>
+      <c r="G106" s="4">
+        <v>-0.059113300492610765</v>
+      </c>
+      <c r="H106" s="4">
+        <v>-0.009852216748768461</v>
+      </c>
+      <c r="I106" s="4">
+        <v>-0.08128078817733986</v>
+      </c>
+      <c r="J106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -8.13%</t>
+        </is>
+      </c>
+      <c r="L106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B107" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="C107" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="D107" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002029</t>
+        </is>
+      </c>
+      <c r="E107" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">七 匹 狼</t>
+        </is>
+      </c>
+      <c r="F107" s="4">
+        <v>0.1612680571847864</v>
+      </c>
+      <c r="G107" s="4">
+        <v>-0.03780718336483935</v>
+      </c>
+      <c r="H107" s="4">
+        <v>0.06805293005671076</v>
+      </c>
+      <c r="I107" s="4">
+        <v>-0.07939508506616255</v>
+      </c>
+      <c r="J107" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K107" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -7.94%</t>
+        </is>
+      </c>
+      <c r="L107" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M107" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9.74</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="C108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="D108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601811</t>
+        </is>
+      </c>
+      <c r="E108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新华文轩</t>
+        </is>
+      </c>
+      <c r="F108" s="4">
+        <v>0.15996506872685262</v>
+      </c>
+      <c r="G108" s="4">
+        <v>-0.022365591397849438</v>
+      </c>
+      <c r="H108" s="4">
+        <v>0.10021505376344075</v>
+      </c>
+      <c r="I108" s="4">
+        <v>0.10021505376344075</v>
+      </c>
+      <c r="J108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +10.02%</t>
+        </is>
+      </c>
+      <c r="L108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="C109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="D109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603533</t>
+        </is>
+      </c>
+      <c r="E109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">掌阅科技</t>
+        </is>
+      </c>
+      <c r="F109" s="4">
+        <v>0.14785416908689147</v>
+      </c>
+      <c r="G109" s="4">
+        <v>-0.013703208556149704</v>
+      </c>
+      <c r="H109" s="4">
+        <v>0.09993315508021383</v>
+      </c>
+      <c r="I109" s="4">
+        <v>-0.03041443850267378</v>
+      </c>
+      <c r="J109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -3.04%</t>
+        </is>
+      </c>
+      <c r="L109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="C110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="D110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600252</t>
+        </is>
+      </c>
+      <c r="E110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中恒集团</t>
+        </is>
+      </c>
+      <c r="F110" s="4">
+        <v>0.14715739912637602</v>
+      </c>
+      <c r="G110" s="4">
+        <v>-0.012096774193548265</v>
+      </c>
+      <c r="H110" s="4">
+        <v>0.0040322580645162365</v>
+      </c>
+      <c r="I110" s="4">
+        <v>-0.07258064516129037</v>
+      </c>
+      <c r="J110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -7.26%</t>
+        </is>
+      </c>
+      <c r="L110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="C111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="D111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001216</t>
+        </is>
+      </c>
+      <c r="E111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华瓷股份</t>
+        </is>
+      </c>
+      <c r="F111" s="4">
+        <v>0.14514134659248926</v>
+      </c>
+      <c r="G111" s="4">
+        <v>-0.06002501042100872</v>
+      </c>
+      <c r="H111" s="4">
+        <v>0.053772405168820425</v>
+      </c>
+      <c r="I111" s="4">
+        <v>0.018340975406419435</v>
+      </c>
+      <c r="J111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +1.83%</t>
+        </is>
+      </c>
+      <c r="L111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="C112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="D112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603598</t>
+        </is>
+      </c>
+      <c r="E112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">引力传媒</t>
+        </is>
+      </c>
+      <c r="F112" s="4">
+        <v>0.14232001242373887</v>
+      </c>
+      <c r="G112" s="4">
+        <v>-0.04153354632587858</v>
+      </c>
+      <c r="H112" s="4">
+        <v>0.05659516202647197</v>
+      </c>
+      <c r="I112" s="4">
+        <v>-0.06709265175718848</v>
+      </c>
+      <c r="J112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -6.71%</t>
+        </is>
+      </c>
+      <c r="L112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="C113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="D113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603258</t>
+        </is>
+      </c>
+      <c r="E113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">电魂网络</t>
+        </is>
+      </c>
+      <c r="F113" s="4">
+        <v>0.12975245547645378</v>
+      </c>
+      <c r="G113" s="4">
+        <v>0.06811145510835925</v>
+      </c>
+      <c r="H113" s="4">
+        <v>0.10030959752322</v>
+      </c>
+      <c r="I113" s="4">
+        <v>0.04086687306501546</v>
+      </c>
+      <c r="J113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +4.09%</t>
+        </is>
+      </c>
+      <c r="L113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16.81</t>
         </is>
       </c>
     </row>
@@ -32889,28 +34991,28 @@
         </is>
       </c>
       <c r="B3" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" s="4">
-        <v>0.4</v>
+        <v>0.45454545454545453</v>
       </c>
       <c r="F3" s="4">
-        <v>0.1509433962264151</v>
+        <v>0.10526315789473684</v>
       </c>
       <c r="G3" s="0">
-        <v>2.6500000000000004</v>
+        <v>4.318181818181818</v>
       </c>
       <c r="H3" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I3" s="4">
-        <v>0.4</v>
+        <v>0.45454545454545453</v>
       </c>
     </row>
     <row r="4">
@@ -32920,28 +35022,28 @@
         </is>
       </c>
       <c r="B4" s="0">
+        <v>11</v>
+      </c>
+      <c r="C4" s="0">
+        <v>33</v>
+      </c>
+      <c r="D4" s="0">
         <v>10</v>
       </c>
-      <c r="C4" s="0">
-        <v>30</v>
-      </c>
-      <c r="D4" s="0">
-        <v>9</v>
-      </c>
       <c r="E4" s="4">
-        <v>0.3</v>
+        <v>0.30303030303030304</v>
       </c>
       <c r="F4" s="4">
-        <v>0.1509433962264151</v>
+        <v>0.10526315789473684</v>
       </c>
       <c r="G4" s="0">
-        <v>1.9875</v>
+        <v>2.878787878787879</v>
       </c>
       <c r="H4" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I4" s="4">
-        <v>0.6</v>
+        <v>0.6363636363636364</v>
       </c>
     </row>
     <row r="5">
@@ -32951,28 +35053,28 @@
         </is>
       </c>
       <c r="B5" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="0">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D5" s="0">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E5" s="4">
-        <v>0.26666666666666666</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="F5" s="4">
-        <v>0.1509433962264151</v>
+        <v>0.10526315789473684</v>
       </c>
       <c r="G5" s="0">
-        <v>1.7666666666666666</v>
+        <v>2.590909090909091</v>
       </c>
       <c r="H5" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" s="4">
-        <v>0.8</v>
+        <v>0.8181818181818182</v>
       </c>
     </row>
     <row r="6">
@@ -32982,28 +35084,28 @@
         </is>
       </c>
       <c r="B6" s="0">
+        <v>11</v>
+      </c>
+      <c r="C6" s="0">
+        <v>110</v>
+      </c>
+      <c r="D6" s="0">
+        <v>25</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0.22727272727272727</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.10526315789473684</v>
+      </c>
+      <c r="G6" s="0">
+        <v>2.159090909090909</v>
+      </c>
+      <c r="H6" s="0">
         <v>10</v>
       </c>
-      <c r="C6" s="0">
-        <v>100</v>
-      </c>
-      <c r="D6" s="0">
-        <v>23</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0.23</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0.1509433962264151</v>
-      </c>
-      <c r="G6" s="0">
-        <v>1.5237500000000002</v>
-      </c>
-      <c r="H6" s="0">
-        <v>9</v>
-      </c>
       <c r="I6" s="4">
-        <v>0.9</v>
+        <v>0.9090909090909091</v>
       </c>
     </row>
     <row r="7">

--- a/docs/downloads/latest.xlsx
+++ b/docs/downloads/latest.xlsx
@@ -93,7 +93,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L523"/>
+  <dimension ref="A1:L572"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -28291,13 +28291,2659 @@
         </is>
       </c>
     </row>
+    <row r="524">
+      <c r="A524" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B524" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C524" s="0">
+        <v>1</v>
+      </c>
+      <c r="D524" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000573</t>
+        </is>
+      </c>
+      <c r="E524" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">粤宏远Ａ</t>
+        </is>
+      </c>
+      <c r="F524" s="0">
+        <v>4.47</v>
+      </c>
+      <c r="G524" s="4">
+        <v>0.10098522167487702</v>
+      </c>
+      <c r="H524" s="4">
+        <v>0.5561338603103911</v>
+      </c>
+      <c r="I524" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J524" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 粤宏远Ａ（000573）归入“股权收购+精密传动+高端自动化+东莞地产”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K524" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 10.1%）。截至运行时成交量约为20日均量的 0.4 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L524" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B525" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C525" s="0">
+        <v>2</v>
+      </c>
+      <c r="D525" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000607</t>
+        </is>
+      </c>
+      <c r="E525" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华媒控股</t>
+        </is>
+      </c>
+      <c r="F525" s="0">
+        <v>4.61</v>
+      </c>
+      <c r="G525" s="4">
+        <v>0.10023866348448696</v>
+      </c>
+      <c r="H525" s="4">
+        <v>0.46902663960991436</v>
+      </c>
+      <c r="I525" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J525" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华媒控股（000607）归入“文化传媒+AI漫剧+杭州日报”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K525" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 10.0%）。截至运行时成交量约为20日均量的 0.4 倍，量能未出现极端放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L525" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B526" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C526" s="0">
+        <v>3</v>
+      </c>
+      <c r="D526" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603636</t>
+        </is>
+      </c>
+      <c r="E526" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南威软件</t>
+        </is>
+      </c>
+      <c r="F526" s="0">
+        <v>8.04</v>
+      </c>
+      <c r="G526" s="4">
+        <v>0.09986320109439116</v>
+      </c>
+      <c r="H526" s="4">
+        <v>0.45851327077169657</v>
+      </c>
+      <c r="I526" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J526" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 南威软件（603636）归入“AI短剧+游戏出海+政务智能体”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K526" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 10.0%）。截至运行时成交量约为20日均量的 0.3 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L526" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B527" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C527" s="0">
+        <v>4</v>
+      </c>
+      <c r="D527" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601999</t>
+        </is>
+      </c>
+      <c r="E527" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">出版传媒</t>
+        </is>
+      </c>
+      <c r="F527" s="0">
+        <v>8.25</v>
+      </c>
+      <c r="G527" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H527" s="4">
+        <v>0.43589983648879155</v>
+      </c>
+      <c r="I527" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J527" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 出版传媒（601999）归入“出版发行+AI应用+数智基金”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K527" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 8.7%）。截至运行时成交量约为20日均量的 0.7 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L527" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B528" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C528" s="0">
+        <v>5</v>
+      </c>
+      <c r="D528" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002869</t>
+        </is>
+      </c>
+      <c r="E528" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金溢科技</t>
+        </is>
+      </c>
+      <c r="F528" s="0">
+        <v>20.58</v>
+      </c>
+      <c r="G528" s="4">
+        <v>0.099946552645644</v>
+      </c>
+      <c r="H528" s="4">
+        <v>0.21955091541710792</v>
+      </c>
+      <c r="I528" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J528" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 金溢科技（002869）归入“车路云+低空智联+智慧交通”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K528" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L528" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B529" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C529" s="0">
+        <v>6</v>
+      </c>
+      <c r="D529" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002949</t>
+        </is>
+      </c>
+      <c r="E529" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华阳国际</t>
+        </is>
+      </c>
+      <c r="F529" s="0">
+        <v>14.14</v>
+      </c>
+      <c r="G529" s="4">
+        <v>0.10038910505836585</v>
+      </c>
+      <c r="H529" s="4">
+        <v>0.17919275945522975</v>
+      </c>
+      <c r="I529" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J529" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华阳国际（002949）归入“微短剧+低空规划+建筑设计+AI设计”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K529" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L529" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B530" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C530" s="0">
+        <v>7</v>
+      </c>
+      <c r="D530" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600802</t>
+        </is>
+      </c>
+      <c r="E530" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">福建水泥</t>
+        </is>
+      </c>
+      <c r="F530" s="0">
+        <v>6.78</v>
+      </c>
+      <c r="G530" s="4">
+        <v>0.10064935064935066</v>
+      </c>
+      <c r="H530" s="4">
+        <v>0.17391493472727537</v>
+      </c>
+      <c r="I530" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J530" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 福建水泥（600802）归入“水泥熟料+重点工程+福建国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K530" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L530" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B531" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C531" s="0">
+        <v>8</v>
+      </c>
+      <c r="D531" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600843</t>
+        </is>
+      </c>
+      <c r="E531" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上工申贝</t>
+        </is>
+      </c>
+      <c r="F531" s="0">
+        <v>8.94</v>
+      </c>
+      <c r="G531" s="4">
+        <v>0.09963099630996286</v>
+      </c>
+      <c r="H531" s="4">
+        <v>0.17372557078632242</v>
+      </c>
+      <c r="I531" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J531" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 上工申贝（600843）归入“低空经济+轻型飞机+机器人缝制+工业缝纫机”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K531" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.9 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L531" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B532" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C532" s="0">
+        <v>9</v>
+      </c>
+      <c r="D532" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600418</t>
+        </is>
+      </c>
+      <c r="E532" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">江淮汽车</t>
+        </is>
+      </c>
+      <c r="F532" s="0">
+        <v>22.37</v>
+      </c>
+      <c r="G532" s="4">
+        <v>0.09980334316617512</v>
+      </c>
+      <c r="H532" s="4">
+        <v>0.16843463872664013</v>
+      </c>
+      <c r="I532" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J532" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 江淮汽车（600418）归入“三部门联合调查+尊界V800”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K532" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.4 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L532" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B533" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C533" s="0">
+        <v>10</v>
+      </c>
+      <c r="D533" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002724</t>
+        </is>
+      </c>
+      <c r="E533" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">海洋王</t>
+        </is>
+      </c>
+      <c r="F533" s="0">
+        <v>7.65</v>
+      </c>
+      <c r="G533" s="4">
+        <v>0.10071942446043171</v>
+      </c>
+      <c r="H533" s="4">
+        <v>0.16660761423662987</v>
+      </c>
+      <c r="I533" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J533" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 海洋王（002724）归入“AI照明+工业照明+应急救援+“羊”字辈”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K533" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L533" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B534" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C534" s="0">
+        <v>11</v>
+      </c>
+      <c r="D534" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600319</t>
+        </is>
+      </c>
+      <c r="E534" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">亚星化学</t>
+        </is>
+      </c>
+      <c r="F534" s="0">
+        <v>6.9</v>
+      </c>
+      <c r="G534" s="4">
+        <v>0.10047846889952172</v>
+      </c>
+      <c r="H534" s="4">
+        <v>0.1633800296948416</v>
+      </c>
+      <c r="I534" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J534" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 亚星化学（600319）归入“PVDC新材料+氯碱化工+CPE”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K534" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.0 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L534" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B535" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C535" s="0">
+        <v>12</v>
+      </c>
+      <c r="D535" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002917</t>
+        </is>
+      </c>
+      <c r="E535" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金奥博</t>
+        </is>
+      </c>
+      <c r="F535" s="0">
+        <v>11.98</v>
+      </c>
+      <c r="G535" s="4">
+        <v>0.10009182736455458</v>
+      </c>
+      <c r="H535" s="4">
+        <v>0.15481090901747072</v>
+      </c>
+      <c r="I535" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J535" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 金奥博（002917）归入“军工并购+民爆装备+工业机器人”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K535" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.9 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L535" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B536" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C536" s="0">
+        <v>13</v>
+      </c>
+      <c r="D536" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002614</t>
+        </is>
+      </c>
+      <c r="E536" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奥佳华</t>
+        </is>
+      </c>
+      <c r="F536" s="0">
+        <v>8.77</v>
+      </c>
+      <c r="G536" s="4">
+        <v>0.10037641154328725</v>
+      </c>
+      <c r="H536" s="4">
+        <v>0.13848640305799503</v>
+      </c>
+      <c r="I536" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J536" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 奥佳华（002614）归入“按摩椅+智能按摩+机器人”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K536" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L536" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B537" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C537" s="0">
+        <v>14</v>
+      </c>
+      <c r="D537" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000420</t>
+        </is>
+      </c>
+      <c r="E537" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">吉林化纤</t>
+        </is>
+      </c>
+      <c r="F537" s="0">
+        <v>3.88</v>
+      </c>
+      <c r="G537" s="4">
+        <v>0.09915014164305959</v>
+      </c>
+      <c r="H537" s="4">
+        <v>0.1374326686620946</v>
+      </c>
+      <c r="I537" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J537" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 吉林化纤（000420）归入“低空经济+冰雪产业+碳纤维+粘胶长丝”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K537" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.2 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L537" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B538" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C538" s="0">
+        <v>15</v>
+      </c>
+      <c r="D538" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603239</t>
+        </is>
+      </c>
+      <c r="E538" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">浙江仙通</t>
+        </is>
+      </c>
+      <c r="F538" s="0">
+        <v>14.43</v>
+      </c>
+      <c r="G538" s="4">
+        <v>0.09984756097560975</v>
+      </c>
+      <c r="H538" s="4">
+        <v>0.13174228345517022</v>
+      </c>
+      <c r="I538" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J538" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 浙江仙通（603239）归入“机器人+汽车密封条+无边框密封条”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K538" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.8 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L538" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B539" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C539" s="0">
+        <v>16</v>
+      </c>
+      <c r="D539" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603278</t>
+        </is>
+      </c>
+      <c r="E539" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大业股份</t>
+        </is>
+      </c>
+      <c r="F539" s="0">
+        <v>9.91</v>
+      </c>
+      <c r="G539" s="4">
+        <v>0.0998890122086571</v>
+      </c>
+      <c r="H539" s="4">
+        <v>0.13025711700961373</v>
+      </c>
+      <c r="I539" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J539" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 大业股份（603278）归入“人形机器人+胎圈钢丝+全球销售”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K539" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.7 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L539" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B540" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C540" s="0">
+        <v>17</v>
+      </c>
+      <c r="D540" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002531</t>
+        </is>
+      </c>
+      <c r="E540" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天顺风能</t>
+        </is>
+      </c>
+      <c r="F540" s="0">
+        <v>7.41</v>
+      </c>
+      <c r="G540" s="4">
+        <v>0.09940652818991103</v>
+      </c>
+      <c r="H540" s="4">
+        <v>0.13010848283203524</v>
+      </c>
+      <c r="I540" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no_verified_event</t>
+        </is>
+      </c>
+      <c r="J540" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">事件证据层未找到与当日涨停直接匹配的公告或新闻；系统不把概念标签、技术形态或主观猜测当成涨停原因。</t>
+        </is>
+      </c>
+      <c r="K540" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L540" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B541" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C541" s="0">
+        <v>18</v>
+      </c>
+      <c r="D541" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000099</t>
+        </is>
+      </c>
+      <c r="E541" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中信海直</t>
+        </is>
+      </c>
+      <c r="F541" s="0">
+        <v>14.75</v>
+      </c>
+      <c r="G541" s="4">
+        <v>0.09992542878448907</v>
+      </c>
+      <c r="H541" s="4">
+        <v>0.12984121566386247</v>
+      </c>
+      <c r="I541" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J541" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 中信海直（000099）归入“低空经济+无人机物流+海上油气”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K541" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.8 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L541" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B542" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C542" s="0">
+        <v>19</v>
+      </c>
+      <c r="D542" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600699</t>
+        </is>
+      </c>
+      <c r="E542" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">均胜电子</t>
+        </is>
+      </c>
+      <c r="F542" s="0">
+        <v>20.3</v>
+      </c>
+      <c r="G542" s="4">
+        <v>0.10027100271002709</v>
+      </c>
+      <c r="H542" s="4">
+        <v>0.12858037898912641</v>
+      </c>
+      <c r="I542" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J542" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 均胜电子（600699）归入“低空经济+特斯拉机器人+智能驾驶”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K542" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L542" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B543" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C543" s="0">
+        <v>20</v>
+      </c>
+      <c r="D543" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603173</t>
+        </is>
+      </c>
+      <c r="E543" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">福斯达</t>
+        </is>
+      </c>
+      <c r="F543" s="0">
+        <v>30.05</v>
+      </c>
+      <c r="G543" s="4">
+        <v>0.09992679355783318</v>
+      </c>
+      <c r="H543" s="4">
+        <v>0.1265307607904216</v>
+      </c>
+      <c r="I543" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J543" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 福斯达（603173）归入“深冷装备+空气分离设备+海外业务”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K543" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.5 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L543" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B544" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C544" s="0">
+        <v>21</v>
+      </c>
+      <c r="D544" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605178</t>
+        </is>
+      </c>
+      <c r="E544" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时空科技</t>
+        </is>
+      </c>
+      <c r="F544" s="0">
+        <v>61.44</v>
+      </c>
+      <c r="G544" s="4">
+        <v>0.10008952551477159</v>
+      </c>
+      <c r="H544" s="4">
+        <v>0.1256124188636361</v>
+      </c>
+      <c r="I544" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J544" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 时空科技（605178）归入“半导体存储+重组审核中止+智慧城市”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K544" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L544" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B545" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C545" s="0">
+        <v>22</v>
+      </c>
+      <c r="D545" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000576</t>
+        </is>
+      </c>
+      <c r="E545" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">甘化科工</t>
+        </is>
+      </c>
+      <c r="F545" s="0">
+        <v>8.77</v>
+      </c>
+      <c r="G545" s="4">
+        <v>0.10037641154328725</v>
+      </c>
+      <c r="H545" s="4">
+        <v>0.12361560252852334</v>
+      </c>
+      <c r="I545" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J545" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 甘化科工（000576）归入“军工电源+光电成像+特种合金+参股锴威特半导体”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K545" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.5 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L545" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B546" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C546" s="0">
+        <v>23</v>
+      </c>
+      <c r="D546" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603197</t>
+        </is>
+      </c>
+      <c r="E546" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">保隆科技</t>
+        </is>
+      </c>
+      <c r="F546" s="0">
+        <v>29.39</v>
+      </c>
+      <c r="G546" s="4">
+        <v>0.09992514970059885</v>
+      </c>
+      <c r="H546" s="4">
+        <v>0.12011695115617363</v>
+      </c>
+      <c r="I546" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J546" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 保隆科技（603197）归入“飞行汽车+特斯拉概念+机器人传感器”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K546" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L546" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B547" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C547" s="0">
+        <v>24</v>
+      </c>
+      <c r="D547" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603955</t>
+        </is>
+      </c>
+      <c r="E547" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大千生态</t>
+        </is>
+      </c>
+      <c r="F547" s="0">
+        <v>23.57</v>
+      </c>
+      <c r="G547" s="4">
+        <v>0.09986000933271111</v>
+      </c>
+      <c r="H547" s="4">
+        <v>0.11789519253084348</v>
+      </c>
+      <c r="I547" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J547" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 大千生态（603955）归入“宠物消费+生态建设+文旅运营”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K547" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L547" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B548" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C548" s="0">
+        <v>25</v>
+      </c>
+      <c r="D548" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002085</t>
+        </is>
+      </c>
+      <c r="E548" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">万丰奥威</t>
+        </is>
+      </c>
+      <c r="F548" s="0">
+        <v>9.91</v>
+      </c>
+      <c r="G548" s="4">
+        <v>0.0998890122086571</v>
+      </c>
+      <c r="H548" s="4">
+        <v>0.11574449343791246</v>
+      </c>
+      <c r="I548" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J548" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 万丰奥威（002085）归入“低空经济+汽车轻量化+通航飞机”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K548" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.4 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L548" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B549" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C549" s="0">
+        <v>26</v>
+      </c>
+      <c r="D549" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002535</t>
+        </is>
+      </c>
+      <c r="E549" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">林州重机</t>
+        </is>
+      </c>
+      <c r="F549" s="0">
+        <v>2.54</v>
+      </c>
+      <c r="G549" s="4">
+        <v>0.09956709956709965</v>
+      </c>
+      <c r="H549" s="4">
+        <v>0.11483559182383364</v>
+      </c>
+      <c r="I549" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J549" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 林州重机（002535）归入“军工配套+煤矿机械”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K549" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L549" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B550" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C550" s="0">
+        <v>27</v>
+      </c>
+      <c r="D550" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000678</t>
+        </is>
+      </c>
+      <c r="E550" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">襄阳轴承</t>
+        </is>
+      </c>
+      <c r="F550" s="0">
+        <v>10.93</v>
+      </c>
+      <c r="G550" s="4">
+        <v>0.09959758551307839</v>
+      </c>
+      <c r="H550" s="4">
+        <v>0.11468882880317778</v>
+      </c>
+      <c r="I550" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no_verified_event</t>
+        </is>
+      </c>
+      <c r="J550" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">事件证据层未找到与当日涨停直接匹配的公告或新闻；系统不把概念标签、技术形态或主观猜测当成涨停原因。</t>
+        </is>
+      </c>
+      <c r="K550" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L550" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B551" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C551" s="0">
+        <v>28</v>
+      </c>
+      <c r="D551" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001358</t>
+        </is>
+      </c>
+      <c r="E551" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">兴欣新材</t>
+        </is>
+      </c>
+      <c r="F551" s="0">
+        <v>24.92</v>
+      </c>
+      <c r="G551" s="4">
+        <v>0.10022075055187664</v>
+      </c>
+      <c r="H551" s="4">
+        <v>0.11438585556251096</v>
+      </c>
+      <c r="I551" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J551" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 兴欣新材（001358）归入“光刻胶原料+电子化学品+有机胺”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K551" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.8 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L551" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B552" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C552" s="0">
+        <v>29</v>
+      </c>
+      <c r="D552" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603348</t>
+        </is>
+      </c>
+      <c r="E552" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文灿股份</t>
+        </is>
+      </c>
+      <c r="F552" s="0">
+        <v>15.31</v>
+      </c>
+      <c r="G552" s="4">
+        <v>0.09985632183908046</v>
+      </c>
+      <c r="H552" s="4">
+        <v>0.11357919490435181</v>
+      </c>
+      <c r="I552" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J552" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 文灿股份（603348）归入“一体化压铸+特斯拉概念+机器人概念+飞行汽车”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K552" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.2 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L552" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B553" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C553" s="0">
+        <v>30</v>
+      </c>
+      <c r="D553" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603668</t>
+        </is>
+      </c>
+      <c r="E553" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天马科技</t>
+        </is>
+      </c>
+      <c r="F553" s="0">
+        <v>7.55</v>
+      </c>
+      <c r="G553" s="4">
+        <v>0.10058309037900859</v>
+      </c>
+      <c r="H553" s="4">
+        <v>0.10941524464223762</v>
+      </c>
+      <c r="I553" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J553" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 天马科技（603668）归入“鳗鱼全产业链+水产饲料+债务展期”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K553" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.2 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L553" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B554" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C554" s="0">
+        <v>31</v>
+      </c>
+      <c r="D554" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001319</t>
+        </is>
+      </c>
+      <c r="E554" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">铭科精技</t>
+        </is>
+      </c>
+      <c r="F554" s="0">
+        <v>21.4</v>
+      </c>
+      <c r="G554" s="4">
+        <v>0.10025706940874034</v>
+      </c>
+      <c r="H554" s="4">
+        <v>0.10680601645740849</v>
+      </c>
+      <c r="I554" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J554" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 铭科精技（001319）归入“工业机器人+飞行汽车+汽车零部件+智能装备”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K554" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.5 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L554" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B555" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C555" s="0">
+        <v>32</v>
+      </c>
+      <c r="D555" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600148</t>
+        </is>
+      </c>
+      <c r="E555" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">长春一东</t>
+        </is>
+      </c>
+      <c r="F555" s="0">
+        <v>16.28</v>
+      </c>
+      <c r="G555" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H555" s="4">
+        <v>0.10493085047783421</v>
+      </c>
+      <c r="I555" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J555" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 长春一东（600148）归入“军工概念+AMT系统+新能源汽车+国企改革”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K555" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.9 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L555" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B556" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C556" s="0">
+        <v>33</v>
+      </c>
+      <c r="D556" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601606</t>
+        </is>
+      </c>
+      <c r="E556" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">长城军工</t>
+        </is>
+      </c>
+      <c r="F556" s="0">
+        <v>31.92</v>
+      </c>
+      <c r="G556" s="4">
+        <v>0.09993108201240532</v>
+      </c>
+      <c r="H556" s="4">
+        <v>0.10132435287447225</v>
+      </c>
+      <c r="I556" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J556" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 长城军工（601606）归入“弹药装备+订单交付+军民协同”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K556" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L556" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B557" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C557" s="0">
+        <v>34</v>
+      </c>
+      <c r="D557" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002933</t>
+        </is>
+      </c>
+      <c r="E557" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新兴装备</t>
+        </is>
+      </c>
+      <c r="F557" s="0">
+        <v>27.75</v>
+      </c>
+      <c r="G557" s="4">
+        <v>0.0998810939357908</v>
+      </c>
+      <c r="H557" s="4">
+        <v>0.10014919463567057</v>
+      </c>
+      <c r="I557" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J557" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 新兴装备（002933）归入“航空装备+机器人”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K557" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.9 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L557" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B558" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C558" s="0">
+        <v>35</v>
+      </c>
+      <c r="D558" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000701</t>
+        </is>
+      </c>
+      <c r="E558" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">厦门信达</t>
+        </is>
+      </c>
+      <c r="F558" s="0">
+        <v>5.36</v>
+      </c>
+      <c r="G558" s="4">
+        <v>0.10061601642710481</v>
+      </c>
+      <c r="H558" s="4">
+        <v>0.09994999683950205</v>
+      </c>
+      <c r="I558" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J558" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 厦门信达（000701）归入“大宗商品贸易+算力布局+厦门国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K558" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.4 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L558" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B559" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C559" s="0">
+        <v>36</v>
+      </c>
+      <c r="D559" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603168</t>
+        </is>
+      </c>
+      <c r="E559" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">莎普爱思</t>
+        </is>
+      </c>
+      <c r="F559" s="0">
+        <v>6.24</v>
+      </c>
+      <c r="G559" s="4">
+        <v>0.10052910052910068</v>
+      </c>
+      <c r="H559" s="4">
+        <v>0.09992372416662967</v>
+      </c>
+      <c r="I559" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J559" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 莎普爱思（603168）归入“眼科用药+新品获批+医疗服务”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K559" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.1 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L559" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B560" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C560" s="0">
+        <v>37</v>
+      </c>
+      <c r="D560" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002767</t>
+        </is>
+      </c>
+      <c r="E560" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">先锋电子</t>
+        </is>
+      </c>
+      <c r="F560" s="0">
+        <v>18.04</v>
+      </c>
+      <c r="G560" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H560" s="4">
+        <v>0.0993695618252819</v>
+      </c>
+      <c r="I560" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J560" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 先锋电子（002767）归入“智慧燃气+机器人+MEMS传感器”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K560" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L560" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B561" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C561" s="0">
+        <v>38</v>
+      </c>
+      <c r="D561" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600178</t>
+        </is>
+      </c>
+      <c r="E561" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东安动力</t>
+        </is>
+      </c>
+      <c r="F561" s="0">
+        <v>10.25</v>
+      </c>
+      <c r="G561" s="4">
+        <v>0.09978540772532195</v>
+      </c>
+      <c r="H561" s="4">
+        <v>0.09927052965559578</v>
+      </c>
+      <c r="I561" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J561" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 东安动力（600178）归入“飞行汽车+增程动力+定点协议+兵装重组”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K561" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.8 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L561" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B562" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C562" s="0">
+        <v>39</v>
+      </c>
+      <c r="D562" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002683</t>
+        </is>
+      </c>
+      <c r="E562" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">广东宏大</t>
+        </is>
+      </c>
+      <c r="F562" s="0">
+        <v>27.9</v>
+      </c>
+      <c r="G562" s="4">
+        <v>0.10015772870662465</v>
+      </c>
+      <c r="H562" s="4">
+        <v>0.09794129580778496</v>
+      </c>
+      <c r="I562" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J562" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 广东宏大（002683）归入“防务装备+卫星星座+矿服民爆”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K562" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L562" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B563" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C563" s="0">
+        <v>40</v>
+      </c>
+      <c r="D563" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000887</t>
+        </is>
+      </c>
+      <c r="E563" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中鼎股份</t>
+        </is>
+      </c>
+      <c r="F563" s="0">
+        <v>17.72</v>
+      </c>
+      <c r="G563" s="4">
+        <v>0.09993792675356916</v>
+      </c>
+      <c r="H563" s="4">
+        <v>0.09428416659072528</v>
+      </c>
+      <c r="I563" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J563" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 中鼎股份（000887）归入“飞行汽车+人形机器人+数据中心液冷+汽车零部件”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K563" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.7 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L563" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B564" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C564" s="0">
+        <v>41</v>
+      </c>
+      <c r="D564" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001696</t>
+        </is>
+      </c>
+      <c r="E564" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">宗申动力</t>
+        </is>
+      </c>
+      <c r="F564" s="0">
+        <v>15.87</v>
+      </c>
+      <c r="G564" s="4">
+        <v>0.0997920997920998</v>
+      </c>
+      <c r="H564" s="4">
+        <v>0.09325828309782437</v>
+      </c>
+      <c r="I564" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J564" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 宗申动力（001696）归入“低空经济+通用机械”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K564" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L564" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B565" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C565" s="0">
+        <v>42</v>
+      </c>
+      <c r="D565" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603015</t>
+        </is>
+      </c>
+      <c r="E565" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">弘讯科技</t>
+        </is>
+      </c>
+      <c r="F565" s="0">
+        <v>10.8</v>
+      </c>
+      <c r="G565" s="4">
+        <v>0.0997963340122201</v>
+      </c>
+      <c r="H565" s="4">
+        <v>0.09207109559110416</v>
+      </c>
+      <c r="I565" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J565" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 弘讯科技（603015）归入“台湾资产出售+核聚变电源+工业自动化”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K565" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.4 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L565" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B566" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C566" s="0">
+        <v>43</v>
+      </c>
+      <c r="D566" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002076</t>
+        </is>
+      </c>
+      <c r="E566" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">星光股份</t>
+        </is>
+      </c>
+      <c r="F566" s="0">
+        <v>2.17</v>
+      </c>
+      <c r="G566" s="4">
+        <v>0.10152284263959398</v>
+      </c>
+      <c r="H566" s="4">
+        <v>0.09162427428321451</v>
+      </c>
+      <c r="I566" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J566" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 星光股份（002076）归入“LED封装+量子科技+光伏组件”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K566" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.2 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L566" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B567" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C567" s="0">
+        <v>44</v>
+      </c>
+      <c r="D567" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603013</t>
+        </is>
+      </c>
+      <c r="E567" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">亚普股份</t>
+        </is>
+      </c>
+      <c r="F567" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="G567" s="4">
+        <v>0.0997067448680351</v>
+      </c>
+      <c r="H567" s="4">
+        <v>0.09134132920473553</v>
+      </c>
+      <c r="I567" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J567" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 亚普股份（603013）归入“汽车零部件+机器人+储氢系统”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K567" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.0 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L567" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B568" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C568" s="0">
+        <v>45</v>
+      </c>
+      <c r="D568" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600860</t>
+        </is>
+      </c>
+      <c r="E568" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">京城股份</t>
+        </is>
+      </c>
+      <c r="F568" s="0">
+        <v>7.91</v>
+      </c>
+      <c r="G568" s="4">
+        <v>0.1001390820584145</v>
+      </c>
+      <c r="H568" s="4">
+        <v>0.09076358048263514</v>
+      </c>
+      <c r="I568" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J568" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 京城股份（600860）归入“气体储运+氢能装备+机器人集成”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K568" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.2 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L568" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B569" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C569" s="0">
+        <v>46</v>
+      </c>
+      <c r="D569" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603305</t>
+        </is>
+      </c>
+      <c r="E569" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旭升集团</t>
+        </is>
+      </c>
+      <c r="F569" s="0">
+        <v>10.88</v>
+      </c>
+      <c r="G569" s="4">
+        <v>0.10010111223458029</v>
+      </c>
+      <c r="H569" s="4">
+        <v>0.09053928887104029</v>
+      </c>
+      <c r="I569" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J569" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 旭升集团（603305）归入“汽车轻量化+特斯拉概念+人形机器人+商业航天”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K569" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.2 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L569" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B570" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C570" s="0">
+        <v>47</v>
+      </c>
+      <c r="D570" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600501</t>
+        </is>
+      </c>
+      <c r="E570" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">航天晨光</t>
+        </is>
+      </c>
+      <c r="F570" s="0">
+        <v>15.33</v>
+      </c>
+      <c r="G570" s="4">
+        <v>0.09971305595408907</v>
+      </c>
+      <c r="H570" s="4">
+        <v>0.08807033690234048</v>
+      </c>
+      <c r="I570" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J570" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 航天晨光（600501）归入“特种装备+商业航天+可控核聚变”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K570" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.3 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L570" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B571" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C571" s="0">
+        <v>48</v>
+      </c>
+      <c r="D571" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002510</t>
+        </is>
+      </c>
+      <c r="E571" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天汽模</t>
+        </is>
+      </c>
+      <c r="F571" s="0">
+        <v>5.96</v>
+      </c>
+      <c r="G571" s="4">
+        <v>0.09963099630996307</v>
+      </c>
+      <c r="H571" s="4">
+        <v>0.08465077564864514</v>
+      </c>
+      <c r="I571" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J571" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 天汽模（002510）归入“低空经济+航空零部件+汽车模具”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K571" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.5 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L571" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B572" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C572" s="0">
+        <v>49</v>
+      </c>
+      <c r="D572" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002976</t>
+        </is>
+      </c>
+      <c r="E572" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瑞玛精密</t>
+        </is>
+      </c>
+      <c r="F572" s="0">
+        <v>19.91</v>
+      </c>
+      <c r="G572" s="4">
+        <v>0.0951595159515952</v>
+      </c>
+      <c r="H572" s="4">
+        <v>0.03647097106520894</v>
+      </c>
+      <c r="I572" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no_verified_event</t>
+        </is>
+      </c>
+      <c r="J572" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">事件证据层未找到与当日涨停直接匹配的公告或新闻；系统不把概念标签、技术形态或主观猜测当成涨停原因。</t>
+        </is>
+      </c>
+      <c r="K572" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 56 家涨停，其中首板 49 家、2板及以上 7 家。</t>
+        </is>
+      </c>
+      <c r="L572" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M113"/>
+  <dimension ref="A1:M123"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -34900,6 +37546,596 @@
       <c r="M113" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">16.81</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002815</t>
+        </is>
+      </c>
+      <c r="E114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">崇达技术</t>
+        </is>
+      </c>
+      <c r="F114" s="4">
+        <v>0.39049809086069387</v>
+      </c>
+      <c r="G114" s="4">
+        <v>0.10021505376344075</v>
+      </c>
+      <c r="H114" s="4">
+        <v>0.10021505376344075</v>
+      </c>
+      <c r="I114" s="4">
+        <v>0.009462365591397903</v>
+      </c>
+      <c r="J114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +0.95%</t>
+        </is>
+      </c>
+      <c r="L114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000626</t>
+        </is>
+      </c>
+      <c r="E115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">远大控股</t>
+        </is>
+      </c>
+      <c r="F115" s="4">
+        <v>0.3424049153221247</v>
+      </c>
+      <c r="G115" s="4">
+        <v>-0.022950819672131195</v>
+      </c>
+      <c r="H115" s="4">
+        <v>-0.004371584699453646</v>
+      </c>
+      <c r="I115" s="4">
+        <v>-0.09945355191256833</v>
+      </c>
+      <c r="J115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -9.95%</t>
+        </is>
+      </c>
+      <c r="L115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="D116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605058</t>
+        </is>
+      </c>
+      <c r="E116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">澳弘电子</t>
+        </is>
+      </c>
+      <c r="F116" s="4">
+        <v>0.22159529829690788</v>
+      </c>
+      <c r="G116" s="4">
+        <v>0.017165555397928856</v>
+      </c>
+      <c r="H116" s="4">
+        <v>0.01858419633990649</v>
+      </c>
+      <c r="I116" s="4">
+        <v>-0.06610866789615544</v>
+      </c>
+      <c r="J116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -6.61%</t>
+        </is>
+      </c>
+      <c r="L116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B117" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C117" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="D117" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600812</t>
+        </is>
+      </c>
+      <c r="E117" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华北制药</t>
+        </is>
+      </c>
+      <c r="F117" s="4">
+        <v>0.1599164699009189</v>
+      </c>
+      <c r="G117" s="4">
+        <v>-0.0365296803652968</v>
+      </c>
+      <c r="H117" s="4">
+        <v>0.05022831050228316</v>
+      </c>
+      <c r="I117" s="4">
+        <v>-0.04718417047184176</v>
+      </c>
+      <c r="J117" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K117" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -4.72%</t>
+        </is>
+      </c>
+      <c r="L117" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M117" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B118" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C118" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="D118" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603200</t>
+        </is>
+      </c>
+      <c r="E118" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上海洗霸</t>
+        </is>
+      </c>
+      <c r="F118" s="4">
+        <v>0.15164598119971337</v>
+      </c>
+      <c r="G118" s="4">
+        <v>0.008059981255857496</v>
+      </c>
+      <c r="H118" s="4">
+        <v>0.08716026241799435</v>
+      </c>
+      <c r="I118" s="4">
+        <v>0.04048734770384255</v>
+      </c>
+      <c r="J118" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K118" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +4.05%</t>
+        </is>
+      </c>
+      <c r="L118" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M118" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55.51</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B119" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C119" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="D119" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603230</t>
+        </is>
+      </c>
+      <c r="E119" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">内蒙新华</t>
+        </is>
+      </c>
+      <c r="F119" s="4">
+        <v>0.1447166312496263</v>
+      </c>
+      <c r="G119" s="4">
+        <v>-0.0027548209366390353</v>
+      </c>
+      <c r="H119" s="4">
+        <v>0.04958677685950419</v>
+      </c>
+      <c r="I119" s="4">
+        <v>-0.05509641873278226</v>
+      </c>
+      <c r="J119" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K119" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -5.51%</t>
+        </is>
+      </c>
+      <c r="L119" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M119" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13.72</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B120" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C120" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="D120" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000995</t>
+        </is>
+      </c>
+      <c r="E120" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">皇台酒业</t>
+        </is>
+      </c>
+      <c r="F120" s="4">
+        <v>0.1423334266019338</v>
+      </c>
+      <c r="G120" s="4">
+        <v>-0.005235602094240677</v>
+      </c>
+      <c r="H120" s="4">
+        <v>0.10022438294689606</v>
+      </c>
+      <c r="I120" s="4">
+        <v>0.0680628272251309</v>
+      </c>
+      <c r="J120" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K120" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +6.81%</t>
+        </is>
+      </c>
+      <c r="L120" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M120" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B121" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C121" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="D121" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002543</t>
+        </is>
+      </c>
+      <c r="E121" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">万和电气</t>
+        </is>
+      </c>
+      <c r="F121" s="4">
+        <v>0.1390992504383719</v>
+      </c>
+      <c r="G121" s="4">
+        <v>0.010152284263959421</v>
+      </c>
+      <c r="H121" s="4">
+        <v>0.03426395939086291</v>
+      </c>
+      <c r="I121" s="4">
+        <v>-0.03299492385786795</v>
+      </c>
+      <c r="J121" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K121" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -3.30%</t>
+        </is>
+      </c>
+      <c r="L121" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M121" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B122" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C122" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="D122" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">003029</t>
+        </is>
+      </c>
+      <c r="E122" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">吉大正元</t>
+        </is>
+      </c>
+      <c r="F122" s="4">
+        <v>0.13865700805167439</v>
+      </c>
+      <c r="G122" s="4">
+        <v>0.05052526263131574</v>
+      </c>
+      <c r="H122" s="4">
+        <v>0.10005002501250626</v>
+      </c>
+      <c r="I122" s="4">
+        <v>0.10005002501250626</v>
+      </c>
+      <c r="J122" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K122" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +10.01%</t>
+        </is>
+      </c>
+      <c r="L122" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M122" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B123" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="C123" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="D123" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603999</t>
+        </is>
+      </c>
+      <c r="E123" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">读者传媒</t>
+        </is>
+      </c>
+      <c r="F123" s="4">
+        <v>0.13699222573492967</v>
+      </c>
+      <c r="G123" s="4">
+        <v>0.09973753280839914</v>
+      </c>
+      <c r="H123" s="4">
+        <v>0.09973753280839914</v>
+      </c>
+      <c r="I123" s="4">
+        <v>0.09973753280839914</v>
+      </c>
+      <c r="J123" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K123" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +9.97%</t>
+        </is>
+      </c>
+      <c r="L123" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M123" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8.38</t>
         </is>
       </c>
     </row>
@@ -34991,28 +38227,28 @@
         </is>
       </c>
       <c r="B3" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="0">
         <v>5</v>
       </c>
       <c r="E3" s="4">
-        <v>0.45454545454545453</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="F3" s="4">
-        <v>0.10526315789473684</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="G3" s="0">
-        <v>4.318181818181818</v>
+        <v>2.916666666666667</v>
       </c>
       <c r="H3" s="0">
         <v>5</v>
       </c>
       <c r="I3" s="4">
-        <v>0.45454545454545453</v>
+        <v>0.4166666666666667</v>
       </c>
     </row>
     <row r="4">
@@ -35022,28 +38258,28 @@
         </is>
       </c>
       <c r="B4" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" s="0">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D4" s="0">
         <v>10</v>
       </c>
       <c r="E4" s="4">
-        <v>0.30303030303030304</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="F4" s="4">
-        <v>0.10526315789473684</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="G4" s="0">
-        <v>2.878787878787879</v>
+        <v>1.9444444444444446</v>
       </c>
       <c r="H4" s="0">
         <v>7</v>
       </c>
       <c r="I4" s="4">
-        <v>0.6363636363636364</v>
+        <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="5">
@@ -35053,28 +38289,28 @@
         </is>
       </c>
       <c r="B5" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="0">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D5" s="0">
         <v>18</v>
       </c>
       <c r="E5" s="4">
-        <v>0.2727272727272727</v>
+        <v>0.25</v>
       </c>
       <c r="F5" s="4">
-        <v>0.10526315789473684</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="G5" s="0">
-        <v>2.590909090909091</v>
+        <v>1.75</v>
       </c>
       <c r="H5" s="0">
         <v>9</v>
       </c>
       <c r="I5" s="4">
-        <v>0.8181818181818182</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="6">
@@ -35084,28 +38320,28 @@
         </is>
       </c>
       <c r="B6" s="0">
+        <v>12</v>
+      </c>
+      <c r="C6" s="0">
+        <v>120</v>
+      </c>
+      <c r="D6" s="0">
+        <v>27</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0.225</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="G6" s="0">
+        <v>1.5750000000000002</v>
+      </c>
+      <c r="H6" s="0">
         <v>11</v>
       </c>
-      <c r="C6" s="0">
-        <v>110</v>
-      </c>
-      <c r="D6" s="0">
-        <v>25</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0.22727272727272727</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0.10526315789473684</v>
-      </c>
-      <c r="G6" s="0">
-        <v>2.159090909090909</v>
-      </c>
-      <c r="H6" s="0">
-        <v>10</v>
-      </c>
       <c r="I6" s="4">
-        <v>0.9090909090909091</v>
+        <v>0.9166666666666666</v>
       </c>
     </row>
     <row r="7">

--- a/docs/downloads/latest.xlsx
+++ b/docs/downloads/latest.xlsx
@@ -93,7 +93,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L572"/>
+  <dimension ref="A1:L601"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -30937,13 +30937,1579 @@
         </is>
       </c>
     </row>
+    <row r="573">
+      <c r="A573" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B573" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C573" s="0">
+        <v>1</v>
+      </c>
+      <c r="D573" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600267</t>
+        </is>
+      </c>
+      <c r="E573" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">海正药业</t>
+        </is>
+      </c>
+      <c r="F573" s="0">
+        <v>12.06</v>
+      </c>
+      <c r="G573" s="4">
+        <v>0.10036496350364965</v>
+      </c>
+      <c r="H573" s="4">
+        <v>0.38026543952368536</v>
+      </c>
+      <c r="I573" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J573" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 海正药业（600267）归入“业绩增长+宠物药+受托生产”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K573" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 10.0%）。截至运行时成交量约为20日均量的 0.5 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 40 家涨停，其中首板 29 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L573" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B574" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C574" s="0">
+        <v>2</v>
+      </c>
+      <c r="D574" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002929</t>
+        </is>
+      </c>
+      <c r="E574" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">润建股份</t>
+        </is>
+      </c>
+      <c r="F574" s="0">
+        <v>46.4</v>
+      </c>
+      <c r="G574" s="4">
+        <v>0.10004741583688957</v>
+      </c>
+      <c r="H574" s="4">
+        <v>0.27451746995296095</v>
+      </c>
+      <c r="I574" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J574" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 润建股份（002929）归入“签境外词元大单+算力网络+通信运维”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K574" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 10.0%）。截至运行时成交量约为20日均量的 0.8 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 40 家涨停，其中首板 29 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L574" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B575" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C575" s="0">
+        <v>3</v>
+      </c>
+      <c r="D575" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605058</t>
+        </is>
+      </c>
+      <c r="E575" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">澳弘电子</t>
+        </is>
+      </c>
+      <c r="F575" s="0">
+        <v>72.41</v>
+      </c>
+      <c r="G575" s="4">
+        <v>0.09995442807230749</v>
+      </c>
+      <c r="H575" s="4">
+        <v>0.2572671229753334</v>
+      </c>
+      <c r="I575" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J575" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 澳弘电子（605058）归入“PCB+AI服务器+HDI板”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K575" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 40 家涨停，其中首板 29 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L575" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B576" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C576" s="0">
+        <v>4</v>
+      </c>
+      <c r="D576" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001216</t>
+        </is>
+      </c>
+      <c r="E576" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华瓷股份</t>
+        </is>
+      </c>
+      <c r="F576" s="0">
+        <v>24.31</v>
+      </c>
+      <c r="G576" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H576" s="4">
+        <v>0.21801929711927776</v>
+      </c>
+      <c r="I576" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J576" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华瓷股份（001216）归入“MLCC粉体+酒器+日用陶瓷”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K576" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.5 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 40 家涨停，其中首板 29 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L576" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B577" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C577" s="0">
+        <v>5</v>
+      </c>
+      <c r="D577" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002343</t>
+        </is>
+      </c>
+      <c r="E577" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">慈文传媒</t>
+        </is>
+      </c>
+      <c r="F577" s="0">
+        <v>10.26</v>
+      </c>
+      <c r="G577" s="4">
+        <v>0.09967845659163978</v>
+      </c>
+      <c r="H577" s="4">
+        <v>0.17538137752230215</v>
+      </c>
+      <c r="I577" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J577" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 慈文传媒（002343）归入“微短剧+影视剧获奖+影视IP”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K577" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 5.1 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 40 家涨停，其中首板 29 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L577" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大；近5日涨幅偏高，短线获利盘压力更大；近10日涨幅偏高</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B578" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C578" s="0">
+        <v>6</v>
+      </c>
+      <c r="D578" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605258</t>
+        </is>
+      </c>
+      <c r="E578" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">协和电子</t>
+        </is>
+      </c>
+      <c r="F578" s="0">
+        <v>42.9</v>
+      </c>
+      <c r="G578" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H578" s="4">
+        <v>0.17135203553013012</v>
+      </c>
+      <c r="I578" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J578" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 协和电子（605258）归入“PCB+汽车电子+新能源”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K578" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 40 家涨停，其中首板 29 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L578" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B579" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C579" s="0">
+        <v>7</v>
+      </c>
+      <c r="D579" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603188</t>
+        </is>
+      </c>
+      <c r="E579" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">亚邦股份</t>
+        </is>
+      </c>
+      <c r="F579" s="0">
+        <v>5.56</v>
+      </c>
+      <c r="G579" s="4">
+        <v>0.10099009900990087</v>
+      </c>
+      <c r="H579" s="4">
+        <v>0.15333242713688605</v>
+      </c>
+      <c r="I579" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J579" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 亚邦股份（603188）归入“染料中间体+染料产业链+业绩修复”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K579" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.3 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 40 家涨停，其中首板 29 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L579" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B580" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C580" s="0">
+        <v>8</v>
+      </c>
+      <c r="D580" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002164</t>
+        </is>
+      </c>
+      <c r="E580" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">宁波东力</t>
+        </is>
+      </c>
+      <c r="F580" s="0">
+        <v>14.69</v>
+      </c>
+      <c r="G580" s="4">
+        <v>0.10037453183520606</v>
+      </c>
+      <c r="H580" s="4">
+        <v>0.1412654558907599</v>
+      </c>
+      <c r="I580" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J580" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 宁波东力（002164）归入“精密减速器+控股股东增持+齿轮传动”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K580" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.5 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 40 家涨停，其中首板 29 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L580" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B581" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C581" s="0">
+        <v>9</v>
+      </c>
+      <c r="D581" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603286</t>
+        </is>
+      </c>
+      <c r="E581" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">日盈电子</t>
+        </is>
+      </c>
+      <c r="F581" s="0">
+        <v>42.74</v>
+      </c>
+      <c r="G581" s="4">
+        <v>0.10012870012870012</v>
+      </c>
+      <c r="H581" s="4">
+        <v>0.13931294314475332</v>
+      </c>
+      <c r="I581" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J581" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 日盈电子（603286）归入“人形机器人+汽车电子+北美工厂”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K581" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.4 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 40 家涨停，其中首板 29 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L581" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B582" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C582" s="0">
+        <v>10</v>
+      </c>
+      <c r="D582" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603626</t>
+        </is>
+      </c>
+      <c r="E582" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">科森科技</t>
+        </is>
+      </c>
+      <c r="F582" s="0">
+        <v>22.21</v>
+      </c>
+      <c r="G582" s="4">
+        <v>0.10004952947003452</v>
+      </c>
+      <c r="H582" s="4">
+        <v>0.12665051633931382</v>
+      </c>
+      <c r="I582" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J582" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 科森科技（603626）归入“机器人结构件+苹果供应链+智能终端结构件”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K582" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 40 家涨停，其中首板 29 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L582" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B583" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C583" s="0">
+        <v>11</v>
+      </c>
+      <c r="D583" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603693</t>
+        </is>
+      </c>
+      <c r="E583" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">江苏新能</t>
+        </is>
+      </c>
+      <c r="F583" s="0">
+        <v>13.53</v>
+      </c>
+      <c r="G583" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H583" s="4">
+        <v>0.12600387585985984</v>
+      </c>
+      <c r="I583" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J583" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 江苏新能（603693）归入“海上风电+新能源发电+江苏国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K583" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.4 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 40 家涨停，其中首板 29 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L583" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B584" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C584" s="0">
+        <v>12</v>
+      </c>
+      <c r="D584" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605488</t>
+        </is>
+      </c>
+      <c r="E584" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">福莱新材</t>
+        </is>
+      </c>
+      <c r="F584" s="0">
+        <v>28.17</v>
+      </c>
+      <c r="G584" s="4">
+        <v>0.09996095275283112</v>
+      </c>
+      <c r="H584" s="4">
+        <v>0.11590188006869712</v>
+      </c>
+      <c r="I584" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J584" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 福莱新材（605488）归入“人形机器人+柔性传感器+功能性涂布”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K584" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 40 家涨停，其中首板 29 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L584" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B585" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C585" s="0">
+        <v>13</v>
+      </c>
+      <c r="D585" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600032</t>
+        </is>
+      </c>
+      <c r="E585" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">浙江新能</t>
+        </is>
+      </c>
+      <c r="F585" s="0">
+        <v>7.79</v>
+      </c>
+      <c r="G585" s="4">
+        <v>0.10028248587570632</v>
+      </c>
+      <c r="H585" s="4">
+        <v>0.11576904360210803</v>
+      </c>
+      <c r="I585" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J585" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 浙江新能（600032）归入“电力市场化+风光水电”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K585" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 40 家涨停，其中首板 29 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L585" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B586" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C586" s="0">
+        <v>14</v>
+      </c>
+      <c r="D586" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603330</t>
+        </is>
+      </c>
+      <c r="E586" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天洋新材</t>
+        </is>
+      </c>
+      <c r="F586" s="0">
+        <v>9.43</v>
+      </c>
+      <c r="G586" s="4">
+        <v>0.10035005834305721</v>
+      </c>
+      <c r="H586" s="4">
+        <v>0.11506839655460274</v>
+      </c>
+      <c r="I586" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J586" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 天洋新材（603330）归入“电子胶+热熔胶+业绩扭亏”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K586" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 40 家涨停，其中首板 29 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L586" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B587" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C587" s="0">
+        <v>15</v>
+      </c>
+      <c r="D587" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001211</t>
+        </is>
+      </c>
+      <c r="E587" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">双枪科技</t>
+        </is>
+      </c>
+      <c r="F587" s="0">
+        <v>28.74</v>
+      </c>
+      <c r="G587" s="4">
+        <v>0.09988518943742818</v>
+      </c>
+      <c r="H587" s="4">
+        <v>0.11035191511017992</v>
+      </c>
+      <c r="I587" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J587" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 双枪科技（001211）归入“竹制餐厨具+以竹代塑+餐饮客户”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K587" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 40 家涨停，其中首板 29 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L587" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B588" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C588" s="0">
+        <v>16</v>
+      </c>
+      <c r="D588" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601778</t>
+        </is>
+      </c>
+      <c r="E588" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晶科科技</t>
+        </is>
+      </c>
+      <c r="F588" s="0">
+        <v>3.58</v>
+      </c>
+      <c r="G588" s="4">
+        <v>0.10153846153846156</v>
+      </c>
+      <c r="H588" s="4">
+        <v>0.1100582785245948</v>
+      </c>
+      <c r="I588" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J588" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 晶科科技（601778）归入“算力服务+算电协同+光伏储能”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K588" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.5 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 40 家涨停，其中首板 29 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L588" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B589" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C589" s="0">
+        <v>17</v>
+      </c>
+      <c r="D589" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002886</t>
+        </is>
+      </c>
+      <c r="E589" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">沃特股份</t>
+        </is>
+      </c>
+      <c r="F589" s="0">
+        <v>24.01</v>
+      </c>
+      <c r="G589" s="4">
+        <v>0.09986257443884572</v>
+      </c>
+      <c r="H589" s="4">
+        <v>0.10988559632808906</v>
+      </c>
+      <c r="I589" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J589" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 沃特股份（002886）归入“PTFE薄膜+PCB材料+机器人材料+低空经济”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K589" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 40 家涨停，其中首板 29 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L589" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B590" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C590" s="0">
+        <v>18</v>
+      </c>
+      <c r="D590" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001323</t>
+        </is>
+      </c>
+      <c r="E590" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">慕思股份</t>
+        </is>
+      </c>
+      <c r="F590" s="0">
+        <v>20.21</v>
+      </c>
+      <c r="G590" s="4">
+        <v>0.1001633097441481</v>
+      </c>
+      <c r="H590" s="4">
+        <v>0.10649323149978213</v>
+      </c>
+      <c r="I590" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J590" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 慕思股份（001323）归入“智能睡眠+端侧智能+鸿蒙生态”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K590" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.3 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 40 家涨停，其中首板 29 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L590" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B591" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C591" s="0">
+        <v>19</v>
+      </c>
+      <c r="D591" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600487</t>
+        </is>
+      </c>
+      <c r="E591" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">亨通光电</t>
+        </is>
+      </c>
+      <c r="F591" s="0">
+        <v>50.25</v>
+      </c>
+      <c r="G591" s="4">
+        <v>0.10004378283712789</v>
+      </c>
+      <c r="H591" s="4">
+        <v>0.10594308901215406</v>
+      </c>
+      <c r="I591" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J591" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 亨通光电（600487）归入“光通信+业绩预增+海底光缆”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K591" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.4 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 40 家涨停，其中首板 29 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L591" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B592" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C592" s="0">
+        <v>20</v>
+      </c>
+      <c r="D592" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603040</t>
+        </is>
+      </c>
+      <c r="E592" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新坐标</t>
+        </is>
+      </c>
+      <c r="F592" s="0">
+        <v>40.6</v>
+      </c>
+      <c r="G592" s="4">
+        <v>0.09997290707125452</v>
+      </c>
+      <c r="H592" s="4">
+        <v>0.09527687037789599</v>
+      </c>
+      <c r="I592" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J592" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 新坐标（603040）归入“行星滚柱丝杠+汽车零部件”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K592" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 40 家涨停，其中首板 29 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L592" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B593" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C593" s="0">
+        <v>21</v>
+      </c>
+      <c r="D593" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603119</t>
+        </is>
+      </c>
+      <c r="E593" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">浙江荣泰</t>
+        </is>
+      </c>
+      <c r="F593" s="0">
+        <v>45.87</v>
+      </c>
+      <c r="G593" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H593" s="4">
+        <v>0.09516862448988318</v>
+      </c>
+      <c r="I593" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J593" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 浙江荣泰（603119）归入“人形机器人+精密结构件+云母制品”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K593" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 40 家涨停，其中首板 29 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L593" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B594" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C594" s="0">
+        <v>22</v>
+      </c>
+      <c r="D594" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600329</t>
+        </is>
+      </c>
+      <c r="E594" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">达仁堂</t>
+        </is>
+      </c>
+      <c r="F594" s="0">
+        <v>40.92</v>
+      </c>
+      <c r="G594" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H594" s="4">
+        <v>0.09221820848958964</v>
+      </c>
+      <c r="I594" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J594" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 达仁堂（600329）归入“速效救心丸+中药+高股息”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K594" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 5.1 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 40 家涨停，其中首板 29 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L594" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B595" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C595" s="0">
+        <v>23</v>
+      </c>
+      <c r="D595" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603859</t>
+        </is>
+      </c>
+      <c r="E595" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">能科科技</t>
+        </is>
+      </c>
+      <c r="F595" s="0">
+        <v>38.82</v>
+      </c>
+      <c r="G595" s="4">
+        <v>0.10002833663927468</v>
+      </c>
+      <c r="H595" s="4">
+        <v>0.08787015635582135</v>
+      </c>
+      <c r="I595" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J595" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 能科科技（603859）归入“物理AI+具身智能+定制服务器”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K595" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.4 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 40 家涨停，其中首板 29 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L595" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B596" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C596" s="0">
+        <v>24</v>
+      </c>
+      <c r="D596" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603337</t>
+        </is>
+      </c>
+      <c r="E596" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">杰克科技</t>
+        </is>
+      </c>
+      <c r="F596" s="0">
+        <v>34.46</v>
+      </c>
+      <c r="G596" s="4">
+        <v>0.09990424513246099</v>
+      </c>
+      <c r="H596" s="4">
+        <v>0.08735969622558681</v>
+      </c>
+      <c r="I596" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no_verified_event</t>
+        </is>
+      </c>
+      <c r="J596" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">事件证据层未找到与当日涨停直接匹配的公告或新闻；系统不把概念标签、技术形态或主观猜测当成涨停原因。</t>
+        </is>
+      </c>
+      <c r="K596" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 40 家涨停，其中首板 29 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L596" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B597" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C597" s="0">
+        <v>25</v>
+      </c>
+      <c r="D597" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">003021</t>
+        </is>
+      </c>
+      <c r="E597" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">兆威机电</t>
+        </is>
+      </c>
+      <c r="F597" s="0">
+        <v>67.22</v>
+      </c>
+      <c r="G597" s="4">
+        <v>0.09998363606611038</v>
+      </c>
+      <c r="H597" s="4">
+        <v>0.086852457670962</v>
+      </c>
+      <c r="I597" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J597" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 兆威机电（003021）归入“人形机器人+灵巧手+微型传动”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K597" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.9 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 40 家涨停，其中首板 29 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L597" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B598" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C598" s="0">
+        <v>26</v>
+      </c>
+      <c r="D598" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002368</t>
+        </is>
+      </c>
+      <c r="E598" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太极股份</t>
+        </is>
+      </c>
+      <c r="F598" s="0">
+        <v>12.75</v>
+      </c>
+      <c r="G598" s="4">
+        <v>0.10008628127696294</v>
+      </c>
+      <c r="H598" s="4">
+        <v>0.08579219549763964</v>
+      </c>
+      <c r="I598" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J598" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 太极股份（002368）归入“数据库+央企+云数服务”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K598" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 40 家涨停，其中首板 29 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L598" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B599" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C599" s="0">
+        <v>27</v>
+      </c>
+      <c r="D599" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600686</t>
+        </is>
+      </c>
+      <c r="E599" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金龙汽车</t>
+        </is>
+      </c>
+      <c r="F599" s="0">
+        <v>10.35</v>
+      </c>
+      <c r="G599" s="4">
+        <v>0.09989373007438897</v>
+      </c>
+      <c r="H599" s="4">
+        <v>0.08467491207936885</v>
+      </c>
+      <c r="I599" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J599" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 金龙汽车（600686）归入“客车制造+储氢系统+客车出口+仲裁澄清”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K599" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 40 家涨停，其中首板 29 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L599" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B600" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C600" s="0">
+        <v>28</v>
+      </c>
+      <c r="D600" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605255</t>
+        </is>
+      </c>
+      <c r="E600" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天普股份</t>
+        </is>
+      </c>
+      <c r="F600" s="0">
+        <v>55.88</v>
+      </c>
+      <c r="G600" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H600" s="4">
+        <v>0.08118884897341923</v>
+      </c>
+      <c r="I600" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J600" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 天普股份（605255）归入“汽车零部件+中昊芯英”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K600" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 40 家涨停，其中首板 29 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L600" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B601" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C601" s="0">
+        <v>29</v>
+      </c>
+      <c r="D601" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002626</t>
+        </is>
+      </c>
+      <c r="E601" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金达威</t>
+        </is>
+      </c>
+      <c r="F601" s="0">
+        <v>18.38</v>
+      </c>
+      <c r="G601" s="4">
+        <v>0.09994015559545177</v>
+      </c>
+      <c r="H601" s="4">
+        <v>0.0738688523791117</v>
+      </c>
+      <c r="I601" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J601" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 金达威（002626）归入“巴西甜蛋白+辅酶Q10+藻油”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K601" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 5.7 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 40 家涨停，其中首板 29 家、2板及以上 11 家。</t>
+        </is>
+      </c>
+      <c r="L601" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M123"/>
+  <dimension ref="A1:M133"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -38136,6 +39702,596 @@
       <c r="M123" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">8.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B124" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C124" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D124" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000573</t>
+        </is>
+      </c>
+      <c r="E124" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">粤宏远Ａ</t>
+        </is>
+      </c>
+      <c r="F124" s="4">
+        <v>0.5561338603103911</v>
+      </c>
+      <c r="G124" s="4">
+        <v>0.05145413870246096</v>
+      </c>
+      <c r="H124" s="4">
+        <v>0.055928411633109576</v>
+      </c>
+      <c r="I124" s="4">
+        <v>-0.03579418344519014</v>
+      </c>
+      <c r="J124" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K124" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -3.58%</t>
+        </is>
+      </c>
+      <c r="L124" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M124" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B125" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C125" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D125" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000607</t>
+        </is>
+      </c>
+      <c r="E125" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华媒控股</t>
+        </is>
+      </c>
+      <c r="F125" s="4">
+        <v>0.46902663960991436</v>
+      </c>
+      <c r="G125" s="4">
+        <v>-0.015184381778741929</v>
+      </c>
+      <c r="H125" s="4">
+        <v>-0.015184381778741929</v>
+      </c>
+      <c r="I125" s="4">
+        <v>-0.09978308026030369</v>
+      </c>
+      <c r="J125" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K125" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -9.98%</t>
+        </is>
+      </c>
+      <c r="L125" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M125" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B126" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C126" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="D126" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603636</t>
+        </is>
+      </c>
+      <c r="E126" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南威软件</t>
+        </is>
+      </c>
+      <c r="F126" s="4">
+        <v>0.45851327077169657</v>
+      </c>
+      <c r="G126" s="4">
+        <v>-0.02985074626865658</v>
+      </c>
+      <c r="H126" s="4">
+        <v>0.05845771144278622</v>
+      </c>
+      <c r="I126" s="4">
+        <v>0.004975124378109541</v>
+      </c>
+      <c r="J126" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K126" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +0.50%</t>
+        </is>
+      </c>
+      <c r="L126" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M126" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B127" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C127" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="D127" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601999</t>
+        </is>
+      </c>
+      <c r="E127" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">出版传媒</t>
+        </is>
+      </c>
+      <c r="F127" s="4">
+        <v>0.43589983648879155</v>
+      </c>
+      <c r="G127" s="4">
+        <v>-0.09939393939393948</v>
+      </c>
+      <c r="H127" s="4">
+        <v>-0.042424242424242364</v>
+      </c>
+      <c r="I127" s="4">
+        <v>-0.09939393939393948</v>
+      </c>
+      <c r="J127" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K127" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -9.94%</t>
+        </is>
+      </c>
+      <c r="L127" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M127" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B128" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C128" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="D128" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002869</t>
+        </is>
+      </c>
+      <c r="E128" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金溢科技</t>
+        </is>
+      </c>
+      <c r="F128" s="4">
+        <v>0.21955091541710792</v>
+      </c>
+      <c r="G128" s="4">
+        <v>-0.02526724975704564</v>
+      </c>
+      <c r="H128" s="4">
+        <v>-0.020408163265306034</v>
+      </c>
+      <c r="I128" s="4">
+        <v>-0.0714285714285714</v>
+      </c>
+      <c r="J128" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K128" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -7.14%</t>
+        </is>
+      </c>
+      <c r="L128" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M128" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B129" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C129" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="D129" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002949</t>
+        </is>
+      </c>
+      <c r="E129" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华阳国际</t>
+        </is>
+      </c>
+      <c r="F129" s="4">
+        <v>0.17919275945522975</v>
+      </c>
+      <c r="G129" s="4">
+        <v>-0.0021216407355022504</v>
+      </c>
+      <c r="H129" s="4">
+        <v>-0.0021216407355022504</v>
+      </c>
+      <c r="I129" s="4">
+        <v>-0.06364922206506363</v>
+      </c>
+      <c r="J129" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K129" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -6.36%</t>
+        </is>
+      </c>
+      <c r="L129" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M129" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B130" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C130" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="D130" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600802</t>
+        </is>
+      </c>
+      <c r="E130" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">福建水泥</t>
+        </is>
+      </c>
+      <c r="F130" s="4">
+        <v>0.17391493472727537</v>
+      </c>
+      <c r="G130" s="4">
+        <v>0.014749262536873031</v>
+      </c>
+      <c r="H130" s="4">
+        <v>0.10029498525073732</v>
+      </c>
+      <c r="I130" s="4">
+        <v>0.025073746312684442</v>
+      </c>
+      <c r="J130" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K130" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +2.51%</t>
+        </is>
+      </c>
+      <c r="L130" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M130" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B131" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C131" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="D131" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600843</t>
+        </is>
+      </c>
+      <c r="E131" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上工申贝</t>
+        </is>
+      </c>
+      <c r="F131" s="4">
+        <v>0.17372557078632242</v>
+      </c>
+      <c r="G131" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H131" s="4">
+        <v>0.06935123042505609</v>
+      </c>
+      <c r="I131" s="4">
+        <v>0.004474272930648837</v>
+      </c>
+      <c r="J131" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K131" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +0.45%</t>
+        </is>
+      </c>
+      <c r="L131" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M131" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B132" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C132" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="D132" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600418</t>
+        </is>
+      </c>
+      <c r="E132" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">江淮汽车</t>
+        </is>
+      </c>
+      <c r="F132" s="4">
+        <v>0.16843463872664013</v>
+      </c>
+      <c r="G132" s="4">
+        <v>0.0281627179257935</v>
+      </c>
+      <c r="H132" s="4">
+        <v>0.05498435404559676</v>
+      </c>
+      <c r="I132" s="4">
+        <v>-0.01341081805990163</v>
+      </c>
+      <c r="J132" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K132" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -1.34%</t>
+        </is>
+      </c>
+      <c r="L132" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M132" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B133" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C133" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="D133" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002724</t>
+        </is>
+      </c>
+      <c r="E133" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">海洋王</t>
+        </is>
+      </c>
+      <c r="F133" s="4">
+        <v>0.16660761423662987</v>
+      </c>
+      <c r="G133" s="4">
+        <v>0.1006535947712417</v>
+      </c>
+      <c r="H133" s="4">
+        <v>0.1006535947712417</v>
+      </c>
+      <c r="I133" s="4">
+        <v>0.1006535947712417</v>
+      </c>
+      <c r="J133" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K133" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +10.07%</t>
+        </is>
+      </c>
+      <c r="L133" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M133" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8.42</t>
         </is>
       </c>
     </row>
@@ -38227,28 +40383,28 @@
         </is>
       </c>
       <c r="B3" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" s="0">
         <v>5</v>
       </c>
       <c r="E3" s="4">
-        <v>0.4166666666666667</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="F3" s="4">
-        <v>0.14285714285714285</v>
+        <v>0.1836734693877551</v>
       </c>
       <c r="G3" s="0">
-        <v>2.916666666666667</v>
+        <v>2.094017094017094</v>
       </c>
       <c r="H3" s="0">
         <v>5</v>
       </c>
       <c r="I3" s="4">
-        <v>0.4166666666666667</v>
+        <v>0.38461538461538464</v>
       </c>
     </row>
     <row r="4">
@@ -38258,28 +40414,28 @@
         </is>
       </c>
       <c r="B4" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="0">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D4" s="0">
         <v>10</v>
       </c>
       <c r="E4" s="4">
-        <v>0.2777777777777778</v>
+        <v>0.2564102564102564</v>
       </c>
       <c r="F4" s="4">
-        <v>0.14285714285714285</v>
+        <v>0.1836734693877551</v>
       </c>
       <c r="G4" s="0">
-        <v>1.9444444444444446</v>
+        <v>1.3960113960113958</v>
       </c>
       <c r="H4" s="0">
         <v>7</v>
       </c>
       <c r="I4" s="4">
-        <v>0.5833333333333334</v>
+        <v>0.5384615384615384</v>
       </c>
     </row>
     <row r="5">
@@ -38289,28 +40445,28 @@
         </is>
       </c>
       <c r="B5" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="0">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D5" s="0">
         <v>18</v>
       </c>
       <c r="E5" s="4">
-        <v>0.25</v>
+        <v>0.23076923076923078</v>
       </c>
       <c r="F5" s="4">
-        <v>0.14285714285714285</v>
+        <v>0.1836734693877551</v>
       </c>
       <c r="G5" s="0">
-        <v>1.75</v>
+        <v>1.2564102564102564</v>
       </c>
       <c r="H5" s="0">
         <v>9</v>
       </c>
       <c r="I5" s="4">
-        <v>0.75</v>
+        <v>0.6923076923076923</v>
       </c>
     </row>
     <row r="6">
@@ -38320,28 +40476,28 @@
         </is>
       </c>
       <c r="B6" s="0">
+        <v>13</v>
+      </c>
+      <c r="C6" s="0">
+        <v>130</v>
+      </c>
+      <c r="D6" s="0">
+        <v>28</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0.2153846153846154</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.1836734693877551</v>
+      </c>
+      <c r="G6" s="0">
+        <v>1.1726495726495727</v>
+      </c>
+      <c r="H6" s="0">
         <v>12</v>
       </c>
-      <c r="C6" s="0">
-        <v>120</v>
-      </c>
-      <c r="D6" s="0">
-        <v>27</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0.225</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0.14285714285714285</v>
-      </c>
-      <c r="G6" s="0">
-        <v>1.5750000000000002</v>
-      </c>
-      <c r="H6" s="0">
-        <v>11</v>
-      </c>
       <c r="I6" s="4">
-        <v>0.9166666666666666</v>
+        <v>0.9230769230769231</v>
       </c>
     </row>
     <row r="7">

--- a/docs/downloads/latest.xlsx
+++ b/docs/downloads/latest.xlsx
@@ -93,7 +93,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L601"/>
+  <dimension ref="A1:L634"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -32503,13 +32503,1795 @@
         </is>
       </c>
     </row>
+    <row r="602">
+      <c r="A602" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B602" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C602" s="0">
+        <v>1</v>
+      </c>
+      <c r="D602" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600293</t>
+        </is>
+      </c>
+      <c r="E602" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">三峡新材</t>
+        </is>
+      </c>
+      <c r="F602" s="0">
+        <v>4.32</v>
+      </c>
+      <c r="G602" s="4">
+        <v>0.0992366412213741</v>
+      </c>
+      <c r="H602" s="4">
+        <v>0.49325922604066574</v>
+      </c>
+      <c r="I602" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J602" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 三峡新材（600293）归入“重大重组+锂电电解液+汽车电子玻璃”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K602" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 9.9%）。截至运行时成交量约为20日均量的 0.1 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L602" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B603" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C603" s="0">
+        <v>2</v>
+      </c>
+      <c r="D603" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600661</t>
+        </is>
+      </c>
+      <c r="E603" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">昂立教育</t>
+        </is>
+      </c>
+      <c r="F603" s="0">
+        <v>10.12</v>
+      </c>
+      <c r="G603" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H603" s="4">
+        <v>0.377716353603891</v>
+      </c>
+      <c r="I603" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J603" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 昂立教育（600661）归入“业绩增长+教育培训+银发经济”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K603" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 10.0%）。截至运行时成交量约为20日均量的 1.5 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L603" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B604" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C604" s="0">
+        <v>3</v>
+      </c>
+      <c r="D604" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002835</t>
+        </is>
+      </c>
+      <c r="E604" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同为股份</t>
+        </is>
+      </c>
+      <c r="F604" s="0">
+        <v>14.16</v>
+      </c>
+      <c r="G604" s="4">
+        <v>0.10023310023310028</v>
+      </c>
+      <c r="H604" s="4">
+        <v>0.3607361459733703</v>
+      </c>
+      <c r="I604" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J604" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 同为股份（002835）归入“视频监控+人工智能安防+海外业务+AI ISP”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K604" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 10.0%）。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L604" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B605" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C605" s="0">
+        <v>4</v>
+      </c>
+      <c r="D605" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603386</t>
+        </is>
+      </c>
+      <c r="E605" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">骏亚科技</t>
+        </is>
+      </c>
+      <c r="F605" s="0">
+        <v>21.71</v>
+      </c>
+      <c r="G605" s="4">
+        <v>0.0997973657548128</v>
+      </c>
+      <c r="H605" s="4">
+        <v>0.20609861909129093</v>
+      </c>
+      <c r="I605" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J605" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 骏亚科技（603386）归入“业绩增长+PCB+AI算力+人形机器人”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K605" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L605" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B606" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C606" s="0">
+        <v>5</v>
+      </c>
+      <c r="D606" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002242</t>
+        </is>
+      </c>
+      <c r="E606" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">九阳股份</t>
+        </is>
+      </c>
+      <c r="F606" s="0">
+        <v>20.56</v>
+      </c>
+      <c r="G606" s="4">
+        <v>0.10005350454788653</v>
+      </c>
+      <c r="H606" s="4">
+        <v>0.1779488932694022</v>
+      </c>
+      <c r="I606" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J606" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 九阳股份（002242）归入“机器人投资+厨房小家电+豆浆机+“羊”字辈”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K606" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.9 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L606" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">近10日涨幅偏高</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B607" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C607" s="0">
+        <v>6</v>
+      </c>
+      <c r="D607" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002696</t>
+        </is>
+      </c>
+      <c r="E607" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">百洋股份</t>
+        </is>
+      </c>
+      <c r="F607" s="0">
+        <v>9.56</v>
+      </c>
+      <c r="G607" s="4">
+        <v>0.10011507479861927</v>
+      </c>
+      <c r="H607" s="4">
+        <v>0.15956189939395546</v>
+      </c>
+      <c r="I607" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J607" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 百洋股份（002696）归入“水产饲料+鱼粉涨价+青岛国资+“羊”字辈”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K607" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.7 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L607" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B608" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C608" s="0">
+        <v>7</v>
+      </c>
+      <c r="D608" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002181</t>
+        </is>
+      </c>
+      <c r="E608" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">粤 传 媒</t>
+        </is>
+      </c>
+      <c r="F608" s="0">
+        <v>10.13</v>
+      </c>
+      <c r="G608" s="4">
+        <v>0.09989142236699244</v>
+      </c>
+      <c r="H608" s="4">
+        <v>0.12768374689007497</v>
+      </c>
+      <c r="I608" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J608" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 粤 传 媒（002181）归入“微短剧+人工智能内容+媒体经营”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K608" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.5 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L608" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B609" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C609" s="0">
+        <v>8</v>
+      </c>
+      <c r="D609" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001283</t>
+        </is>
+      </c>
+      <c r="E609" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">豪鹏科技</t>
+        </is>
+      </c>
+      <c r="F609" s="0">
+        <v>51.06</v>
+      </c>
+      <c r="G609" s="4">
+        <v>0.09995691512279192</v>
+      </c>
+      <c r="H609" s="4">
+        <v>0.11158442269103547</v>
+      </c>
+      <c r="I609" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J609" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 豪鹏科技（001283）归入“消费电子电池+机器人电池+AI眼镜+三季报预增”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K609" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L609" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B610" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C610" s="0">
+        <v>9</v>
+      </c>
+      <c r="D610" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002479</t>
+        </is>
+      </c>
+      <c r="E610" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">富春环保</t>
+        </is>
+      </c>
+      <c r="F610" s="0">
+        <v>6.01</v>
+      </c>
+      <c r="G610" s="4">
+        <v>0.10073260073260058</v>
+      </c>
+      <c r="H610" s="4">
+        <v>0.10710833270729568</v>
+      </c>
+      <c r="I610" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J610" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 富春环保（002479）归入“业绩增长+有色回收+热电联产”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K610" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L610" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B611" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C611" s="0">
+        <v>10</v>
+      </c>
+      <c r="D611" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603068</t>
+        </is>
+      </c>
+      <c r="E611" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">博通集成</t>
+        </is>
+      </c>
+      <c r="F611" s="0">
+        <v>41.67</v>
+      </c>
+      <c r="G611" s="4">
+        <v>0.100052798310454</v>
+      </c>
+      <c r="H611" s="4">
+        <v>0.10249669648913741</v>
+      </c>
+      <c r="I611" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J611" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 博通集成（603068）归入“端侧AI+无线芯片+AIoT量产”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K611" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.8 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L611" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B612" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C612" s="0">
+        <v>11</v>
+      </c>
+      <c r="D612" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603366</t>
+        </is>
+      </c>
+      <c r="E612" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">日出东方</t>
+        </is>
+      </c>
+      <c r="F612" s="0">
+        <v>7.84</v>
+      </c>
+      <c r="G612" s="4">
+        <v>0.09957924263674611</v>
+      </c>
+      <c r="H612" s="4">
+        <v>0.10087482497603961</v>
+      </c>
+      <c r="I612" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J612" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 日出东方（603366）归入“空气能热泵+储能+太阳能光热”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K612" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.7 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L612" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B613" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C613" s="0">
+        <v>12</v>
+      </c>
+      <c r="D613" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001288</t>
+        </is>
+      </c>
+      <c r="E613" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">运机集团</t>
+        </is>
+      </c>
+      <c r="F613" s="0">
+        <v>30.48</v>
+      </c>
+      <c r="G613" s="4">
+        <v>0.09996391194514608</v>
+      </c>
+      <c r="H613" s="4">
+        <v>0.10056282829595273</v>
+      </c>
+      <c r="I613" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J613" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 运机集团（001288）归入“矿山机器人+输送机械+华为合作+海外订单”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K613" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L613" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B614" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C614" s="0">
+        <v>13</v>
+      </c>
+      <c r="D614" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603636</t>
+        </is>
+      </c>
+      <c r="E614" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南威软件</t>
+        </is>
+      </c>
+      <c r="F614" s="0">
+        <v>8.89</v>
+      </c>
+      <c r="G614" s="4">
+        <v>0.10024752475247523</v>
+      </c>
+      <c r="H614" s="4">
+        <v>0.09795196889036352</v>
+      </c>
+      <c r="I614" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J614" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 南威软件（603636）归入“AI短剧+政务智能体+游戏出海”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K614" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.9 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L614" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B615" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C615" s="0">
+        <v>14</v>
+      </c>
+      <c r="D615" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002881</t>
+        </is>
+      </c>
+      <c r="E615" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">美格智能</t>
+        </is>
+      </c>
+      <c r="F615" s="0">
+        <v>38.51</v>
+      </c>
+      <c r="G615" s="4">
+        <v>0.0999714367323621</v>
+      </c>
+      <c r="H615" s="4">
+        <v>0.09617910717956009</v>
+      </c>
+      <c r="I615" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J615" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 美格智能（002881）归入“物理AI+高算力模组+无线网关+光通信”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K615" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.9 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L615" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B616" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C616" s="0">
+        <v>15</v>
+      </c>
+      <c r="D616" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603893</t>
+        </is>
+      </c>
+      <c r="E616" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瑞芯微</t>
+        </is>
+      </c>
+      <c r="F616" s="0">
+        <v>189.04</v>
+      </c>
+      <c r="G616" s="4">
+        <v>0.10002909514111134</v>
+      </c>
+      <c r="H616" s="4">
+        <v>0.09244086641749111</v>
+      </c>
+      <c r="I616" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J616" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 瑞芯微（603893）归入“端侧AI+机器人+业绩增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K616" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L616" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B617" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C617" s="0">
+        <v>16</v>
+      </c>
+      <c r="D617" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603657</t>
+        </is>
+      </c>
+      <c r="E617" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">春光科技</t>
+        </is>
+      </c>
+      <c r="F617" s="0">
+        <v>32.74</v>
+      </c>
+      <c r="G617" s="4">
+        <v>0.1001344086021505</v>
+      </c>
+      <c r="H617" s="4">
+        <v>0.09168671881289056</v>
+      </c>
+      <c r="I617" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J617" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 春光科技（603657）归入“家庭机器人+清洁电器+小米客户”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K617" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.8 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L617" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B618" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C618" s="0">
+        <v>17</v>
+      </c>
+      <c r="D618" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001239</t>
+        </is>
+      </c>
+      <c r="E618" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">永达股份</t>
+        </is>
+      </c>
+      <c r="F618" s="0">
+        <v>13.4</v>
+      </c>
+      <c r="G618" s="4">
+        <v>0.10016420361247945</v>
+      </c>
+      <c r="H618" s="4">
+        <v>0.09060070784614646</v>
+      </c>
+      <c r="I618" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J618" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 永达股份（001239）归入“盾构机+风电+重组”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K618" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L618" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B619" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C619" s="0">
+        <v>18</v>
+      </c>
+      <c r="D619" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603400</t>
+        </is>
+      </c>
+      <c r="E619" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华之杰</t>
+        </is>
+      </c>
+      <c r="F619" s="0">
+        <v>42.46</v>
+      </c>
+      <c r="G619" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H619" s="4">
+        <v>0.09054812906965173</v>
+      </c>
+      <c r="I619" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J619" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华之杰（603400）归入“机器人+液冷+电子水泵+新能源汽车”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K619" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L619" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B620" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C620" s="0">
+        <v>19</v>
+      </c>
+      <c r="D620" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002347</t>
+        </is>
+      </c>
+      <c r="E620" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">泰尔股份</t>
+        </is>
+      </c>
+      <c r="F620" s="0">
+        <v>6.61</v>
+      </c>
+      <c r="G620" s="4">
+        <v>0.09983361064891859</v>
+      </c>
+      <c r="H620" s="4">
+        <v>0.08961756803979332</v>
+      </c>
+      <c r="I620" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J620" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 泰尔股份（002347）归入“工业机器人+冶金装备”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K620" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.4 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L620" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B621" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C621" s="0">
+        <v>20</v>
+      </c>
+      <c r="D621" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605389</t>
+        </is>
+      </c>
+      <c r="E621" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">长龄液压</t>
+        </is>
+      </c>
+      <c r="F621" s="0">
+        <v>57.97</v>
+      </c>
+      <c r="G621" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H621" s="4">
+        <v>0.08842852542219998</v>
+      </c>
+      <c r="I621" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J621" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 长龄液压（605389）归入“回购提议+AGV减速器+液压元件+工程机械”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K621" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L621" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B622" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C622" s="0">
+        <v>21</v>
+      </c>
+      <c r="D622" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603407</t>
+        </is>
+      </c>
+      <c r="E622" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">长裕集团</t>
+        </is>
+      </c>
+      <c r="F622" s="0">
+        <v>48.29</v>
+      </c>
+      <c r="G622" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H622" s="4">
+        <v>0.08320529871351713</v>
+      </c>
+      <c r="I622" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J622" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 长裕集团（603407）归入“锆基材料+半导体材料+氧氯化锆+次新股”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K622" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L622" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B623" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C623" s="0">
+        <v>22</v>
+      </c>
+      <c r="D623" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603236</t>
+        </is>
+      </c>
+      <c r="E623" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">移远通信</t>
+        </is>
+      </c>
+      <c r="F623" s="0">
+        <v>76.11</v>
+      </c>
+      <c r="G623" s="4">
+        <v>0.10001445295562948</v>
+      </c>
+      <c r="H623" s="4">
+        <v>0.08116416370209867</v>
+      </c>
+      <c r="I623" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J623" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 移远通信（603236）归入“业绩增长+端侧AI+通信模组+机器人”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K623" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.8 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L623" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B624" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C624" s="0">
+        <v>23</v>
+      </c>
+      <c r="D624" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603341</t>
+        </is>
+      </c>
+      <c r="E624" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">龙旗科技</t>
+        </is>
+      </c>
+      <c r="F624" s="0">
+        <v>38.26</v>
+      </c>
+      <c r="G624" s="4">
+        <v>0.10005750431282333</v>
+      </c>
+      <c r="H624" s="4">
+        <v>0.08083640629768317</v>
+      </c>
+      <c r="I624" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J624" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 龙旗科技（603341）归入“AI眼镜+AI PC+机器人+智能终端”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K624" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.9 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L624" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B625" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C625" s="0">
+        <v>24</v>
+      </c>
+      <c r="D625" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002403</t>
+        </is>
+      </c>
+      <c r="E625" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">爱仕达</t>
+        </is>
+      </c>
+      <c r="F625" s="0">
+        <v>11.15</v>
+      </c>
+      <c r="G625" s="4">
+        <v>0.09960552268244571</v>
+      </c>
+      <c r="H625" s="4">
+        <v>0.08024257562845843</v>
+      </c>
+      <c r="I625" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J625" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 爱仕达（002403）归入“人形机器人+工业机器人+炊具小家电”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K625" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L625" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B626" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C626" s="0">
+        <v>25</v>
+      </c>
+      <c r="D626" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002313</t>
+        </is>
+      </c>
+      <c r="E626" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">日海智能</t>
+        </is>
+      </c>
+      <c r="F626" s="0">
+        <v>8.8</v>
+      </c>
+      <c r="G626" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H626" s="4">
+        <v>0.07993937948717046</v>
+      </c>
+      <c r="I626" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J626" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 日海智能（002313）归入“无线模组+机器人应用+股权调整”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K626" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L626" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B627" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C627" s="0">
+        <v>26</v>
+      </c>
+      <c r="D627" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605177</t>
+        </is>
+      </c>
+      <c r="E627" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东亚药业</t>
+        </is>
+      </c>
+      <c r="F627" s="0">
+        <v>24.4</v>
+      </c>
+      <c r="G627" s="4">
+        <v>0.10009017132551845</v>
+      </c>
+      <c r="H627" s="4">
+        <v>0.07831464155723772</v>
+      </c>
+      <c r="I627" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J627" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 东亚药业（605177）归入“头孢克洛+化学原料药+制剂获批”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K627" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L627" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B628" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C628" s="0">
+        <v>27</v>
+      </c>
+      <c r="D628" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002940</t>
+        </is>
+      </c>
+      <c r="E628" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">昂利康</t>
+        </is>
+      </c>
+      <c r="F628" s="0">
+        <v>23.63</v>
+      </c>
+      <c r="G628" s="4">
+        <v>0.10009310986964604</v>
+      </c>
+      <c r="H628" s="4">
+        <v>0.07799839745411838</v>
+      </c>
+      <c r="I628" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J628" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 昂利康（002940）归入“创新药+化学制药+集采拟中选”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K628" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L628" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B629" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C629" s="0">
+        <v>28</v>
+      </c>
+      <c r="D629" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603696</t>
+        </is>
+      </c>
+      <c r="E629" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">安记食品</t>
+        </is>
+      </c>
+      <c r="F629" s="0">
+        <v>13.6</v>
+      </c>
+      <c r="G629" s="4">
+        <v>0.10032362459546927</v>
+      </c>
+      <c r="H629" s="4">
+        <v>0.07716850592862498</v>
+      </c>
+      <c r="I629" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J629" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 安记食品（603696）归入“复合调味品+对台贸易+业绩增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K629" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.7 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L629" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B630" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C630" s="0">
+        <v>29</v>
+      </c>
+      <c r="D630" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603683</t>
+        </is>
+      </c>
+      <c r="E630" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晶华新材</t>
+        </is>
+      </c>
+      <c r="F630" s="0">
+        <v>14.64</v>
+      </c>
+      <c r="G630" s="4">
+        <v>0.09992486851990989</v>
+      </c>
+      <c r="H630" s="4">
+        <v>0.0740539115286885</v>
+      </c>
+      <c r="I630" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J630" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 晶华新材（603683）归入“人形机器人+柔性传感+胶粘材料+股份回购”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K630" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L630" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B631" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C631" s="0">
+        <v>30</v>
+      </c>
+      <c r="D631" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002088</t>
+        </is>
+      </c>
+      <c r="E631" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">鲁阳节能</t>
+        </is>
+      </c>
+      <c r="F631" s="0">
+        <v>8.49</v>
+      </c>
+      <c r="G631" s="4">
+        <v>0.09974093264248719</v>
+      </c>
+      <c r="H631" s="4">
+        <v>0.06649825607125058</v>
+      </c>
+      <c r="I631" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J631" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 鲁阳节能（002088）归入“锂电隔热+陶瓷纤维”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K631" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.8 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L631" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B632" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C632" s="0">
+        <v>31</v>
+      </c>
+      <c r="D632" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001388</t>
+        </is>
+      </c>
+      <c r="E632" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">信通电子</t>
+        </is>
+      </c>
+      <c r="F632" s="0">
+        <v>20.37</v>
+      </c>
+      <c r="G632" s="4">
+        <v>0.09989200863930892</v>
+      </c>
+      <c r="H632" s="4">
+        <v>0.06473686358850095</v>
+      </c>
+      <c r="I632" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J632" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 信通电子（001388）归入“物理AI+除冰机器人+具身智能+电力巡检”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K632" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.7 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L632" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B633" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C633" s="0">
+        <v>32</v>
+      </c>
+      <c r="D633" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002596</t>
+        </is>
+      </c>
+      <c r="E633" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">海南瑞泽</t>
+        </is>
+      </c>
+      <c r="F633" s="0">
+        <v>3.43</v>
+      </c>
+      <c r="G633" s="4">
+        <v>0.09935897435897445</v>
+      </c>
+      <c r="H633" s="4">
+        <v>0.0646094109111168</v>
+      </c>
+      <c r="I633" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J633" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 海南瑞泽（002596）归入“商品混凝土+海南自贸港+智算布局+市政环卫”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K633" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.8 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L633" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B634" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C634" s="0">
+        <v>33</v>
+      </c>
+      <c r="D634" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002076</t>
+        </is>
+      </c>
+      <c r="E634" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">星光股份</t>
+        </is>
+      </c>
+      <c r="F634" s="0">
+        <v>2.23</v>
+      </c>
+      <c r="G634" s="4">
+        <v>0.09852216748768484</v>
+      </c>
+      <c r="H634" s="4">
+        <v>0.05835123254543685</v>
+      </c>
+      <c r="I634" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J634" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 星光股份（002076）归入“LED封装+量子科技+信息安全+光伏组件”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K634" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.5 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 46 家涨停，其中首板 33 家、2板及以上 13 家。</t>
+        </is>
+      </c>
+      <c r="L634" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M133"/>
+  <dimension ref="A1:M143"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -40292,6 +42074,596 @@
       <c r="M133" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">8.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B134" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C134" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D134" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600267</t>
+        </is>
+      </c>
+      <c r="E134" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">海正药业</t>
+        </is>
+      </c>
+      <c r="F134" s="4">
+        <v>0.38026543952368536</v>
+      </c>
+      <c r="G134" s="4">
+        <v>0.10033167495854056</v>
+      </c>
+      <c r="H134" s="4">
+        <v>0.10033167495854056</v>
+      </c>
+      <c r="I134" s="4">
+        <v>0.10033167495854056</v>
+      </c>
+      <c r="J134" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K134" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +10.03%</t>
+        </is>
+      </c>
+      <c r="L134" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M134" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13.27</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B135" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C135" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D135" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002929</t>
+        </is>
+      </c>
+      <c r="E135" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">润建股份</t>
+        </is>
+      </c>
+      <c r="F135" s="4">
+        <v>0.27451746995296095</v>
+      </c>
+      <c r="G135" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H135" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="I135" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="J135" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K135" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +10.00%</t>
+        </is>
+      </c>
+      <c r="L135" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M135" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B136" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C136" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="D136" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605058</t>
+        </is>
+      </c>
+      <c r="E136" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">澳弘电子</t>
+        </is>
+      </c>
+      <c r="F136" s="4">
+        <v>0.2572671229753334</v>
+      </c>
+      <c r="G136" s="4">
+        <v>-0.034939925424665064</v>
+      </c>
+      <c r="H136" s="4">
+        <v>0.052064631956912244</v>
+      </c>
+      <c r="I136" s="4">
+        <v>-0.023063112829719623</v>
+      </c>
+      <c r="J136" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K136" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -2.31%</t>
+        </is>
+      </c>
+      <c r="L136" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M136" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70.74</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B137" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C137" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="D137" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001216</t>
+        </is>
+      </c>
+      <c r="E137" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华瓷股份</t>
+        </is>
+      </c>
+      <c r="F137" s="4">
+        <v>0.21801929711927776</v>
+      </c>
+      <c r="G137" s="4">
+        <v>0.013163307280954273</v>
+      </c>
+      <c r="H137" s="4">
+        <v>0.026326614561908768</v>
+      </c>
+      <c r="I137" s="4">
+        <v>-0.05758946935417519</v>
+      </c>
+      <c r="J137" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K137" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -5.76%</t>
+        </is>
+      </c>
+      <c r="L137" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M137" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B138" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C138" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="D138" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002343</t>
+        </is>
+      </c>
+      <c r="E138" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">慈文传媒</t>
+        </is>
+      </c>
+      <c r="F138" s="4">
+        <v>0.17538137752230215</v>
+      </c>
+      <c r="G138" s="4">
+        <v>-0.006822612085770063</v>
+      </c>
+      <c r="H138" s="4">
+        <v>0.02729044834307981</v>
+      </c>
+      <c r="I138" s="4">
+        <v>-0.0009746588693957392</v>
+      </c>
+      <c r="J138" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K138" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -0.10%</t>
+        </is>
+      </c>
+      <c r="L138" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M138" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B139" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C139" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="D139" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605258</t>
+        </is>
+      </c>
+      <c r="E139" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">协和电子</t>
+        </is>
+      </c>
+      <c r="F139" s="4">
+        <v>0.17135203553013012</v>
+      </c>
+      <c r="G139" s="4">
+        <v>-0.0034965034965034336</v>
+      </c>
+      <c r="H139" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="I139" s="4">
+        <v>0.07365967365967374</v>
+      </c>
+      <c r="J139" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K139" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +7.37%</t>
+        </is>
+      </c>
+      <c r="L139" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M139" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B140" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C140" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="D140" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603188</t>
+        </is>
+      </c>
+      <c r="E140" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">亚邦股份</t>
+        </is>
+      </c>
+      <c r="F140" s="4">
+        <v>0.15333242713688605</v>
+      </c>
+      <c r="G140" s="4">
+        <v>-0.01978417266187038</v>
+      </c>
+      <c r="H140" s="4">
+        <v>-0.003597122302158251</v>
+      </c>
+      <c r="I140" s="4">
+        <v>-0.04856115107913661</v>
+      </c>
+      <c r="J140" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K140" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -4.86%</t>
+        </is>
+      </c>
+      <c r="L140" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M140" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B141" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C141" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="D141" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002164</t>
+        </is>
+      </c>
+      <c r="E141" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">宁波东力</t>
+        </is>
+      </c>
+      <c r="F141" s="4">
+        <v>0.1412654558907599</v>
+      </c>
+      <c r="G141" s="4">
+        <v>0.03335602450646702</v>
+      </c>
+      <c r="H141" s="4">
+        <v>0.10006807351940106</v>
+      </c>
+      <c r="I141" s="4">
+        <v>0.10006807351940106</v>
+      </c>
+      <c r="J141" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K141" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +10.01%</t>
+        </is>
+      </c>
+      <c r="L141" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M141" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B142" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C142" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="D142" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603286</t>
+        </is>
+      </c>
+      <c r="E142" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">日盈电子</t>
+        </is>
+      </c>
+      <c r="F142" s="4">
+        <v>0.13931294314475332</v>
+      </c>
+      <c r="G142" s="4">
+        <v>-0.010060832943378561</v>
+      </c>
+      <c r="H142" s="4">
+        <v>0.09639681796911548</v>
+      </c>
+      <c r="I142" s="4">
+        <v>0.0645765091249415</v>
+      </c>
+      <c r="J142" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K142" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +6.46%</t>
+        </is>
+      </c>
+      <c r="L142" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M142" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B143" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C143" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="D143" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603626</t>
+        </is>
+      </c>
+      <c r="E143" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">科森科技</t>
+        </is>
+      </c>
+      <c r="F143" s="4">
+        <v>0.12665051633931382</v>
+      </c>
+      <c r="G143" s="4">
+        <v>0.0274651058081945</v>
+      </c>
+      <c r="H143" s="4">
+        <v>0.09995497523637997</v>
+      </c>
+      <c r="I143" s="4">
+        <v>0.09995497523637997</v>
+      </c>
+      <c r="J143" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K143" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +10.00%</t>
+        </is>
+      </c>
+      <c r="L143" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M143" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24.43</t>
         </is>
       </c>
     </row>
@@ -40383,28 +42755,28 @@
         </is>
       </c>
       <c r="B3" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" s="4">
-        <v>0.38461538461538464</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="F3" s="4">
-        <v>0.1836734693877551</v>
+        <v>0.2413793103448276</v>
       </c>
       <c r="G3" s="0">
-        <v>2.094017094017094</v>
+        <v>1.7755102040816324</v>
       </c>
       <c r="H3" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I3" s="4">
-        <v>0.38461538461538464</v>
+        <v>0.42857142857142855</v>
       </c>
     </row>
     <row r="4">
@@ -40414,28 +42786,28 @@
         </is>
       </c>
       <c r="B4" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="0">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D4" s="0">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E4" s="4">
-        <v>0.2564102564102564</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="F4" s="4">
-        <v>0.1836734693877551</v>
+        <v>0.2413793103448276</v>
       </c>
       <c r="G4" s="0">
-        <v>1.3960113960113958</v>
+        <v>1.183673469387755</v>
       </c>
       <c r="H4" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I4" s="4">
-        <v>0.5384615384615384</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="5">
@@ -40445,28 +42817,28 @@
         </is>
       </c>
       <c r="B5" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="0">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D5" s="0">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E5" s="4">
-        <v>0.23076923076923078</v>
+        <v>0.23809523809523808</v>
       </c>
       <c r="F5" s="4">
-        <v>0.1836734693877551</v>
+        <v>0.2413793103448276</v>
       </c>
       <c r="G5" s="0">
-        <v>1.2564102564102564</v>
+        <v>0.9863945578231291</v>
       </c>
       <c r="H5" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I5" s="4">
-        <v>0.6923076923076923</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="6">
@@ -40476,28 +42848,28 @@
         </is>
       </c>
       <c r="B6" s="0">
+        <v>14</v>
+      </c>
+      <c r="C6" s="0">
+        <v>140</v>
+      </c>
+      <c r="D6" s="0">
+        <v>32</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0.22857142857142856</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.2413793103448276</v>
+      </c>
+      <c r="G6" s="0">
+        <v>0.946938775510204</v>
+      </c>
+      <c r="H6" s="0">
         <v>13</v>
       </c>
-      <c r="C6" s="0">
-        <v>130</v>
-      </c>
-      <c r="D6" s="0">
-        <v>28</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0.2153846153846154</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0.1836734693877551</v>
-      </c>
-      <c r="G6" s="0">
-        <v>1.1726495726495727</v>
-      </c>
-      <c r="H6" s="0">
-        <v>12</v>
-      </c>
       <c r="I6" s="4">
-        <v>0.9230769230769231</v>
+        <v>0.9285714285714286</v>
       </c>
     </row>
     <row r="7">

--- a/docs/downloads/latest.xlsx
+++ b/docs/downloads/latest.xlsx
@@ -93,7 +93,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L634"/>
+  <dimension ref="A1:L662"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -34285,13 +34285,1525 @@
         </is>
       </c>
     </row>
+    <row r="635">
+      <c r="A635" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B635" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C635" s="0">
+        <v>1</v>
+      </c>
+      <c r="D635" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603332</t>
+        </is>
+      </c>
+      <c r="E635" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">苏州龙杰</t>
+        </is>
+      </c>
+      <c r="F635" s="0">
+        <v>12.69</v>
+      </c>
+      <c r="G635" s="4">
+        <v>0.09965337954939348</v>
+      </c>
+      <c r="H635" s="4">
+        <v>0.2731668867270573</v>
+      </c>
+      <c r="I635" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J635" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 苏州龙杰（603332）归入“三季报增长+差别化涤纶长丝+仿皮草纤维”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K635" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 8.8%）。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 44 家涨停，其中首板 28 家、2板及以上 16 家。</t>
+        </is>
+      </c>
+      <c r="L635" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B636" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C636" s="0">
+        <v>2</v>
+      </c>
+      <c r="D636" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601999</t>
+        </is>
+      </c>
+      <c r="E636" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">出版传媒</t>
+        </is>
+      </c>
+      <c r="F636" s="0">
+        <v>7.8</v>
+      </c>
+      <c r="G636" s="4">
+        <v>0.10014104372355437</v>
+      </c>
+      <c r="H636" s="4">
+        <v>0.1337057619479028</v>
+      </c>
+      <c r="I636" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J636" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 出版传媒（601999）归入“出版发行+AI应用+数智基金”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K636" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.5 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 44 家涨停，其中首板 28 家、2板及以上 16 家。</t>
+        </is>
+      </c>
+      <c r="L636" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B637" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C637" s="0">
+        <v>3</v>
+      </c>
+      <c r="D637" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600252</t>
+        </is>
+      </c>
+      <c r="E637" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中恒集团</t>
+        </is>
+      </c>
+      <c r="F637" s="0">
+        <v>2.38</v>
+      </c>
+      <c r="G637" s="4">
+        <v>0.10185185185185164</v>
+      </c>
+      <c r="H637" s="4">
+        <v>0.12817547110907151</v>
+      </c>
+      <c r="I637" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J637" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 中恒集团（600252）归入“中药创新药+医药制造+回购注销”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K637" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.2 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 44 家涨停，其中首板 28 家、2板及以上 16 家。</t>
+        </is>
+      </c>
+      <c r="L637" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B638" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C638" s="0">
+        <v>4</v>
+      </c>
+      <c r="D638" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002639</t>
+        </is>
+      </c>
+      <c r="E638" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雪人集团</t>
+        </is>
+      </c>
+      <c r="F638" s="0">
+        <v>15.18</v>
+      </c>
+      <c r="G638" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H638" s="4">
+        <v>0.11366237061683727</v>
+      </c>
+      <c r="I638" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J638" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 雪人集团（002639）归入“数据中心冷却+压缩机+制冰系统”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K638" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 44 家涨停，其中首板 28 家、2板及以上 16 家。</t>
+        </is>
+      </c>
+      <c r="L638" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B639" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C639" s="0">
+        <v>5</v>
+      </c>
+      <c r="D639" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603999</t>
+        </is>
+      </c>
+      <c r="E639" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">读者传媒</t>
+        </is>
+      </c>
+      <c r="F639" s="0">
+        <v>7.47</v>
+      </c>
+      <c r="G639" s="4">
+        <v>0.10014727540500722</v>
+      </c>
+      <c r="H639" s="4">
+        <v>0.1104456483125589</v>
+      </c>
+      <c r="I639" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J639" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 读者传媒（603999）归入“出版发行+数字出版+人工智能”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K639" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.4 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 44 家涨停，其中首板 28 家、2板及以上 16 家。</t>
+        </is>
+      </c>
+      <c r="L639" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B640" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C640" s="0">
+        <v>6</v>
+      </c>
+      <c r="D640" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002811</t>
+        </is>
+      </c>
+      <c r="E640" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">郑中设计</t>
+        </is>
+      </c>
+      <c r="F640" s="0">
+        <v>24.16</v>
+      </c>
+      <c r="G640" s="4">
+        <v>0.10018214936247727</v>
+      </c>
+      <c r="H640" s="4">
+        <v>0.11011957034588603</v>
+      </c>
+      <c r="I640" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J640" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 郑中设计（002811）归入“半导体入股+AI设计+室内设计”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K640" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 44 家涨停，其中首板 28 家、2板及以上 16 家。</t>
+        </is>
+      </c>
+      <c r="L640" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B641" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C641" s="0">
+        <v>7</v>
+      </c>
+      <c r="D641" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002086</t>
+        </is>
+      </c>
+      <c r="E641" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东方海洋</t>
+        </is>
+      </c>
+      <c r="F641" s="0">
+        <v>2.39</v>
+      </c>
+      <c r="G641" s="4">
+        <v>0.10138248847926266</v>
+      </c>
+      <c r="H641" s="4">
+        <v>0.10815742561777428</v>
+      </c>
+      <c r="I641" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J641" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 东方海洋（002086）归入“质谱诊断+体外诊断+海参养殖+“羊”字辈”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K641" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.0 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 44 家涨停，其中首板 28 家、2板及以上 16 家。</t>
+        </is>
+      </c>
+      <c r="L641" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B642" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C642" s="0">
+        <v>8</v>
+      </c>
+      <c r="D642" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001216</t>
+        </is>
+      </c>
+      <c r="E642" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华瓷股份</t>
+        </is>
+      </c>
+      <c r="F642" s="0">
+        <v>25.2</v>
+      </c>
+      <c r="G642" s="4">
+        <v>0.09995635093845469</v>
+      </c>
+      <c r="H642" s="4">
+        <v>0.10713056827800874</v>
+      </c>
+      <c r="I642" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J642" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华瓷股份（001216）归入“MLCC粉体+酒器+日用陶瓷”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K642" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.8 倍，量能未出现极端放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 44 家涨停，其中首板 28 家、2板及以上 16 家。</t>
+        </is>
+      </c>
+      <c r="L642" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B643" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C643" s="0">
+        <v>9</v>
+      </c>
+      <c r="D643" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600802</t>
+        </is>
+      </c>
+      <c r="E643" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">福建水泥</t>
+        </is>
+      </c>
+      <c r="F643" s="0">
+        <v>7.04</v>
+      </c>
+      <c r="G643" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H643" s="4">
+        <v>0.10578262488191269</v>
+      </c>
+      <c r="I643" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J643" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 福建水泥（600802）归入“水泥熟料+重点工程+福建国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K643" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.8 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 44 家涨停，其中首板 28 家、2板及以上 16 家。</t>
+        </is>
+      </c>
+      <c r="L643" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B644" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C644" s="0">
+        <v>10</v>
+      </c>
+      <c r="D644" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605388</t>
+        </is>
+      </c>
+      <c r="E644" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">均瑶健康</t>
+        </is>
+      </c>
+      <c r="F644" s="0">
+        <v>7.32</v>
+      </c>
+      <c r="G644" s="4">
+        <v>0.10075187969924816</v>
+      </c>
+      <c r="H644" s="4">
+        <v>0.10032219501457071</v>
+      </c>
+      <c r="I644" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J644" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 均瑶健康（605388）归入“益生菌食品+益生菌出海+菌株研发”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K644" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 44 家涨停，其中首板 28 家、2板及以上 16 家。</t>
+        </is>
+      </c>
+      <c r="L644" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B645" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C645" s="0">
+        <v>11</v>
+      </c>
+      <c r="D645" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002591</t>
+        </is>
+      </c>
+      <c r="E645" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">恒大高新</t>
+        </is>
+      </c>
+      <c r="F645" s="0">
+        <v>6.88</v>
+      </c>
+      <c r="G645" s="4">
+        <v>0.1008</v>
+      </c>
+      <c r="H645" s="4">
+        <v>0.09708333617709634</v>
+      </c>
+      <c r="I645" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J645" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 恒大高新（002591）归入“AI算力服务器+钠电材料+硅碳负极”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K645" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.9 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 44 家涨停，其中首板 28 家、2板及以上 16 家。</t>
+        </is>
+      </c>
+      <c r="L645" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B646" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C646" s="0">
+        <v>12</v>
+      </c>
+      <c r="D646" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002792</t>
+        </is>
+      </c>
+      <c r="E646" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通宇通讯</t>
+        </is>
+      </c>
+      <c r="F646" s="0">
+        <v>32.09</v>
+      </c>
+      <c r="G646" s="4">
+        <v>0.10010284538909842</v>
+      </c>
+      <c r="H646" s="4">
+        <v>0.09582024746121753</v>
+      </c>
+      <c r="I646" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J646" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 通宇通讯（002792）归入“卫星通信+SpaceX+海外客户”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K646" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 44 家涨停，其中首板 28 家、2板及以上 16 家。</t>
+        </is>
+      </c>
+      <c r="L646" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B647" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C647" s="0">
+        <v>13</v>
+      </c>
+      <c r="D647" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603721</t>
+        </is>
+      </c>
+      <c r="E647" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中广天择</t>
+        </is>
+      </c>
+      <c r="F647" s="0">
+        <v>20.82</v>
+      </c>
+      <c r="G647" s="4">
+        <v>0.09984152139461176</v>
+      </c>
+      <c r="H647" s="4">
+        <v>0.09180969340642303</v>
+      </c>
+      <c r="I647" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J647" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 中广天择（603721）归入“AI语料+AI漫剧+传媒内容”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K647" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.4 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 44 家涨停，其中首板 28 家、2板及以上 16 家。</t>
+        </is>
+      </c>
+      <c r="L647" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B648" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C648" s="0">
+        <v>14</v>
+      </c>
+      <c r="D648" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603138</t>
+        </is>
+      </c>
+      <c r="E648" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">海量数据</t>
+        </is>
+      </c>
+      <c r="F648" s="0">
+        <v>15.38</v>
+      </c>
+      <c r="G648" s="4">
+        <v>0.10014306151645203</v>
+      </c>
+      <c r="H648" s="4">
+        <v>0.09084064839870581</v>
+      </c>
+      <c r="I648" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J648" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 海量数据（603138）归入“数据库+AI应用+定增注册”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K648" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 44 家涨停，其中首板 28 家、2板及以上 16 家。</t>
+        </is>
+      </c>
+      <c r="L648" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B649" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C649" s="0">
+        <v>15</v>
+      </c>
+      <c r="D649" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600202</t>
+        </is>
+      </c>
+      <c r="E649" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">哈空调</t>
+        </is>
+      </c>
+      <c r="F649" s="0">
+        <v>5.57</v>
+      </c>
+      <c r="G649" s="4">
+        <v>0.10079051383399218</v>
+      </c>
+      <c r="H649" s="4">
+        <v>0.0871180135090181</v>
+      </c>
+      <c r="I649" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J649" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 哈空调（600202）归入“空冷器+飞翼空冷器+股东增持”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K649" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.6 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 44 家涨停，其中首板 28 家、2板及以上 16 家。</t>
+        </is>
+      </c>
+      <c r="L649" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B650" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C650" s="0">
+        <v>16</v>
+      </c>
+      <c r="D650" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002565</t>
+        </is>
+      </c>
+      <c r="E650" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">顺灏股份</t>
+        </is>
+      </c>
+      <c r="F650" s="0">
+        <v>8.48</v>
+      </c>
+      <c r="G650" s="4">
+        <v>0.09987029831387817</v>
+      </c>
+      <c r="H650" s="4">
+        <v>0.0860988745262843</v>
+      </c>
+      <c r="I650" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J650" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 顺灏股份（002565）归入“太空算力+新型烟草+环保包装”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K650" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.4 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 44 家涨停，其中首板 28 家、2板及以上 16 家。</t>
+        </is>
+      </c>
+      <c r="L650" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B651" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C651" s="0">
+        <v>17</v>
+      </c>
+      <c r="D651" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603330</t>
+        </is>
+      </c>
+      <c r="E651" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天洋新材</t>
+        </is>
+      </c>
+      <c r="F651" s="0">
+        <v>10.09</v>
+      </c>
+      <c r="G651" s="4">
+        <v>0.1003271537622683</v>
+      </c>
+      <c r="H651" s="4">
+        <v>0.08359824094544945</v>
+      </c>
+      <c r="I651" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J651" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 天洋新材（603330）归入“电子胶+光模块胶+热熔胶+“羊”字辈”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K651" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.9 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 44 家涨停，其中首板 28 家、2板及以上 16 家。</t>
+        </is>
+      </c>
+      <c r="L651" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B652" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C652" s="0">
+        <v>18</v>
+      </c>
+      <c r="D652" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600271</t>
+        </is>
+      </c>
+      <c r="E652" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">航天信息</t>
+        </is>
+      </c>
+      <c r="F652" s="0">
+        <v>7.4</v>
+      </c>
+      <c r="G652" s="4">
+        <v>0.09955423476968805</v>
+      </c>
+      <c r="H652" s="4">
+        <v>0.079380964755925</v>
+      </c>
+      <c r="I652" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J652" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 航天信息（600271）归入“数字财税+AI财税+数据要素”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K652" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.2 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 44 家涨停，其中首板 28 家、2板及以上 16 家。</t>
+        </is>
+      </c>
+      <c r="L652" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B653" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C653" s="0">
+        <v>19</v>
+      </c>
+      <c r="D653" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002238</t>
+        </is>
+      </c>
+      <c r="E653" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天威视讯</t>
+        </is>
+      </c>
+      <c r="F653" s="0">
+        <v>7.61</v>
+      </c>
+      <c r="G653" s="4">
+        <v>0.0997109826589595</v>
+      </c>
+      <c r="H653" s="4">
+        <v>0.07888950571639111</v>
+      </c>
+      <c r="I653" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J653" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 天威视讯（002238）归入“广电网络+数据中心+网络安全”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K653" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 44 家涨停，其中首板 28 家、2板及以上 16 家。</t>
+        </is>
+      </c>
+      <c r="L653" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B654" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C654" s="0">
+        <v>20</v>
+      </c>
+      <c r="D654" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601566</t>
+        </is>
+      </c>
+      <c r="E654" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">九牧王</t>
+        </is>
+      </c>
+      <c r="F654" s="0">
+        <v>10.24</v>
+      </c>
+      <c r="G654" s="4">
+        <v>0.09989258861439311</v>
+      </c>
+      <c r="H654" s="4">
+        <v>0.07830108179032136</v>
+      </c>
+      <c r="I654" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J654" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 九牧王（601566）归入“羊毛羊绒+男裤+太空裤+海峡两岸”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K654" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 44 家涨停，其中首板 28 家、2板及以上 16 家。</t>
+        </is>
+      </c>
+      <c r="L654" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B655" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C655" s="0">
+        <v>21</v>
+      </c>
+      <c r="D655" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001201</t>
+        </is>
+      </c>
+      <c r="E655" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东瑞股份</t>
+        </is>
+      </c>
+      <c r="F655" s="0">
+        <v>15.96</v>
+      </c>
+      <c r="G655" s="4">
+        <v>0.09993108201240532</v>
+      </c>
+      <c r="H655" s="4">
+        <v>0.07755120997997389</v>
+      </c>
+      <c r="I655" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J655" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 东瑞股份（001201）归入“生猪养殖+供港活猪+降本增效”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K655" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 44 家涨停，其中首板 28 家、2板及以上 16 家。</t>
+        </is>
+      </c>
+      <c r="L655" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B656" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C656" s="0">
+        <v>22</v>
+      </c>
+      <c r="D656" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600838</t>
+        </is>
+      </c>
+      <c r="E656" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上海九百</t>
+        </is>
+      </c>
+      <c r="F656" s="0">
+        <v>9.09</v>
+      </c>
+      <c r="G656" s="4">
+        <v>0.1004842615012107</v>
+      </c>
+      <c r="H656" s="4">
+        <v>0.07378515868583208</v>
+      </c>
+      <c r="I656" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J656" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 上海九百（600838）归入“商业地产+商贸零售+洗染服务”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K656" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 44 家涨停，其中首板 28 家、2板及以上 16 家。</t>
+        </is>
+      </c>
+      <c r="L656" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B657" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C657" s="0">
+        <v>23</v>
+      </c>
+      <c r="D657" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002368</t>
+        </is>
+      </c>
+      <c r="E657" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太极股份</t>
+        </is>
+      </c>
+      <c r="F657" s="0">
+        <v>14.67</v>
+      </c>
+      <c r="G657" s="4">
+        <v>0.09970014992503738</v>
+      </c>
+      <c r="H657" s="4">
+        <v>0.06759732588032061</v>
+      </c>
+      <c r="I657" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J657" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 太极股份（002368）归入“数据库+云数服务+央企”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K657" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.4 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 44 家涨停，其中首板 28 家、2板及以上 16 家。</t>
+        </is>
+      </c>
+      <c r="L657" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B658" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C658" s="0">
+        <v>24</v>
+      </c>
+      <c r="D658" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603629</t>
+        </is>
+      </c>
+      <c r="E658" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">利通电子</t>
+        </is>
+      </c>
+      <c r="F658" s="0">
+        <v>92.03</v>
+      </c>
+      <c r="G658" s="4">
+        <v>0.10004781257470728</v>
+      </c>
+      <c r="H658" s="4">
+        <v>0.06747538293085012</v>
+      </c>
+      <c r="I658" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J658" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 利通电子（603629）归入“算力租赁+Token业务+英伟达合作”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K658" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 44 家涨停，其中首板 28 家、2板及以上 16 家。</t>
+        </is>
+      </c>
+      <c r="L658" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B659" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C659" s="0">
+        <v>25</v>
+      </c>
+      <c r="D659" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600715</t>
+        </is>
+      </c>
+      <c r="E659" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文投控股</t>
+        </is>
+      </c>
+      <c r="F659" s="0">
+        <v>1.87</v>
+      </c>
+      <c r="G659" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H659" s="4">
+        <v>0.06729639449955321</v>
+      </c>
+      <c r="I659" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J659" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 文投控股（600715）归入“AI漫剧+游戏+影院运营”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K659" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.9 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 44 家涨停，其中首板 28 家、2板及以上 16 家。</t>
+        </is>
+      </c>
+      <c r="L659" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B660" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C660" s="0">
+        <v>26</v>
+      </c>
+      <c r="D660" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000788</t>
+        </is>
+      </c>
+      <c r="E660" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">北大医药</t>
+        </is>
+      </c>
+      <c r="F660" s="0">
+        <v>5.86</v>
+      </c>
+      <c r="G660" s="4">
+        <v>0.09943714821763618</v>
+      </c>
+      <c r="H660" s="4">
+        <v>0.05825781890126133</v>
+      </c>
+      <c r="I660" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J660" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 北大医药（000788）归入“化学制药+降脂复方药+原料制剂一体化”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K660" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.6 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 44 家涨停，其中首板 28 家、2板及以上 16 家。</t>
+        </is>
+      </c>
+      <c r="L660" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B661" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C661" s="0">
+        <v>27</v>
+      </c>
+      <c r="D661" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000518</t>
+        </is>
+      </c>
+      <c r="E661" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">四环生物</t>
+        </is>
+      </c>
+      <c r="F661" s="0">
+        <v>3.63</v>
+      </c>
+      <c r="G661" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H661" s="4">
+        <v>0.056188625411313683</v>
+      </c>
+      <c r="I661" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J661" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 四环生物（000518）归入“长源并表+生物医药+中润收购”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K661" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.8 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 44 家涨停，其中首板 28 家、2板及以上 16 家。</t>
+        </is>
+      </c>
+      <c r="L661" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B662" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C662" s="0">
+        <v>28</v>
+      </c>
+      <c r="D662" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002112</t>
+        </is>
+      </c>
+      <c r="E662" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">三变科技</t>
+        </is>
+      </c>
+      <c r="F662" s="0">
+        <v>14.43</v>
+      </c>
+      <c r="G662" s="4">
+        <v>0.09984756097560975</v>
+      </c>
+      <c r="H662" s="4">
+        <v>0.05515659552613034</v>
+      </c>
+      <c r="I662" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J662" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 三变科技（002112）归入“变压器+AI算力+国企改革”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K662" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.7 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 44 家涨停，其中首板 28 家、2板及以上 16 家。</t>
+        </is>
+      </c>
+      <c r="L662" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M143"/>
+  <dimension ref="A1:M153"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -42664,6 +44176,596 @@
       <c r="M143" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">24.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B144" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C144" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D144" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600293</t>
+        </is>
+      </c>
+      <c r="E144" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">三峡新材</t>
+        </is>
+      </c>
+      <c r="F144" s="4">
+        <v>0.49325922604066574</v>
+      </c>
+      <c r="G144" s="4">
+        <v>0.09953703703703698</v>
+      </c>
+      <c r="H144" s="4">
+        <v>0.09953703703703698</v>
+      </c>
+      <c r="I144" s="4">
+        <v>0.09953703703703698</v>
+      </c>
+      <c r="J144" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K144" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +9.95%</t>
+        </is>
+      </c>
+      <c r="L144" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M144" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B145" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C145" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D145" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600661</t>
+        </is>
+      </c>
+      <c r="E145" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">昂立教育</t>
+        </is>
+      </c>
+      <c r="F145" s="4">
+        <v>0.377716353603891</v>
+      </c>
+      <c r="G145" s="4">
+        <v>-0.0009881422924901129</v>
+      </c>
+      <c r="H145" s="4">
+        <v>-0.0009881422924901129</v>
+      </c>
+      <c r="I145" s="4">
+        <v>-0.05533596837944654</v>
+      </c>
+      <c r="J145" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K145" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -5.53%</t>
+        </is>
+      </c>
+      <c r="L145" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M145" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B146" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C146" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="D146" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002835</t>
+        </is>
+      </c>
+      <c r="E146" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同为股份</t>
+        </is>
+      </c>
+      <c r="F146" s="4">
+        <v>0.3607361459733703</v>
+      </c>
+      <c r="G146" s="4">
+        <v>0.10028248587570632</v>
+      </c>
+      <c r="H146" s="4">
+        <v>0.10028248587570632</v>
+      </c>
+      <c r="I146" s="4">
+        <v>0.10028248587570632</v>
+      </c>
+      <c r="J146" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K146" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +10.03%</t>
+        </is>
+      </c>
+      <c r="L146" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M146" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B147" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C147" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="D147" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603386</t>
+        </is>
+      </c>
+      <c r="E147" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">骏亚科技</t>
+        </is>
+      </c>
+      <c r="F147" s="4">
+        <v>0.20609861909129093</v>
+      </c>
+      <c r="G147" s="4">
+        <v>0.013357899585444422</v>
+      </c>
+      <c r="H147" s="4">
+        <v>0.031782588668816114</v>
+      </c>
+      <c r="I147" s="4">
+        <v>-0.09212344541685857</v>
+      </c>
+      <c r="J147" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K147" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -9.21%</t>
+        </is>
+      </c>
+      <c r="L147" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M147" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19.71</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B148" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C148" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="D148" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002242</t>
+        </is>
+      </c>
+      <c r="E148" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">九阳股份</t>
+        </is>
+      </c>
+      <c r="F148" s="4">
+        <v>0.1779488932694022</v>
+      </c>
+      <c r="G148" s="4">
+        <v>0.018482490272373697</v>
+      </c>
+      <c r="H148" s="4">
+        <v>0.10019455252918297</v>
+      </c>
+      <c r="I148" s="4">
+        <v>0.10019455252918297</v>
+      </c>
+      <c r="J148" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K148" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +10.02%</t>
+        </is>
+      </c>
+      <c r="L148" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M148" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B149" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C149" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="D149" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002696</t>
+        </is>
+      </c>
+      <c r="E149" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">百洋股份</t>
+        </is>
+      </c>
+      <c r="F149" s="4">
+        <v>0.15956189939395546</v>
+      </c>
+      <c r="G149" s="4">
+        <v>0.039748953974895196</v>
+      </c>
+      <c r="H149" s="4">
+        <v>0.10041841004184082</v>
+      </c>
+      <c r="I149" s="4">
+        <v>0.10041841004184082</v>
+      </c>
+      <c r="J149" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K149" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +10.04%</t>
+        </is>
+      </c>
+      <c r="L149" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M149" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B150" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C150" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="D150" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002181</t>
+        </is>
+      </c>
+      <c r="E150" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">粤 传 媒</t>
+        </is>
+      </c>
+      <c r="F150" s="4">
+        <v>0.12768374689007497</v>
+      </c>
+      <c r="G150" s="4">
+        <v>0.04639684106614017</v>
+      </c>
+      <c r="H150" s="4">
+        <v>0.09970384995064152</v>
+      </c>
+      <c r="I150" s="4">
+        <v>0.09970384995064152</v>
+      </c>
+      <c r="J150" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K150" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +9.97%</t>
+        </is>
+      </c>
+      <c r="L150" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M150" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B151" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C151" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="D151" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001283</t>
+        </is>
+      </c>
+      <c r="E151" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">豪鹏科技</t>
+        </is>
+      </c>
+      <c r="F151" s="4">
+        <v>0.11158442269103547</v>
+      </c>
+      <c r="G151" s="4">
+        <v>0.0199764982373678</v>
+      </c>
+      <c r="H151" s="4">
+        <v>0.056991774383078564</v>
+      </c>
+      <c r="I151" s="4">
+        <v>0.008029768899334044</v>
+      </c>
+      <c r="J151" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K151" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +0.80%</t>
+        </is>
+      </c>
+      <c r="L151" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M151" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B152" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C152" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="D152" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002479</t>
+        </is>
+      </c>
+      <c r="E152" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">富春环保</t>
+        </is>
+      </c>
+      <c r="F152" s="4">
+        <v>0.10710833270729568</v>
+      </c>
+      <c r="G152" s="4">
+        <v>0.038269550748752046</v>
+      </c>
+      <c r="H152" s="4">
+        <v>0.038269550748752046</v>
+      </c>
+      <c r="I152" s="4">
+        <v>-0.0266222961730449</v>
+      </c>
+      <c r="J152" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K152" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -2.66%</t>
+        </is>
+      </c>
+      <c r="L152" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M152" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B153" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="C153" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="D153" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603068</t>
+        </is>
+      </c>
+      <c r="E153" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">博通集成</t>
+        </is>
+      </c>
+      <c r="F153" s="4">
+        <v>0.10249669648913741</v>
+      </c>
+      <c r="G153" s="4">
+        <v>0.022318214542836667</v>
+      </c>
+      <c r="H153" s="4">
+        <v>0.0556755459563234</v>
+      </c>
+      <c r="I153" s="4">
+        <v>0.036717062634989306</v>
+      </c>
+      <c r="J153" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K153" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +3.67%</t>
+        </is>
+      </c>
+      <c r="L153" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M153" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">43.2</t>
         </is>
       </c>
     </row>
@@ -42755,28 +44857,28 @@
         </is>
       </c>
       <c r="B3" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" s="4">
-        <v>0.42857142857142855</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="F3" s="4">
-        <v>0.2413793103448276</v>
+        <v>0.36363636363636365</v>
       </c>
       <c r="G3" s="0">
-        <v>1.7755102040816324</v>
+        <v>1.2833333333333332</v>
       </c>
       <c r="H3" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I3" s="4">
-        <v>0.42857142857142855</v>
+        <v>0.4666666666666667</v>
       </c>
     </row>
     <row r="4">
@@ -42786,28 +44888,28 @@
         </is>
       </c>
       <c r="B4" s="0">
+        <v>15</v>
+      </c>
+      <c r="C4" s="0">
+        <v>45</v>
+      </c>
+      <c r="D4" s="0">
         <v>14</v>
       </c>
-      <c r="C4" s="0">
-        <v>42</v>
-      </c>
-      <c r="D4" s="0">
-        <v>12</v>
-      </c>
       <c r="E4" s="4">
-        <v>0.2857142857142857</v>
+        <v>0.3111111111111111</v>
       </c>
       <c r="F4" s="4">
-        <v>0.2413793103448276</v>
+        <v>0.36363636363636365</v>
       </c>
       <c r="G4" s="0">
-        <v>1.183673469387755</v>
+        <v>0.8555555555555555</v>
       </c>
       <c r="H4" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I4" s="4">
-        <v>0.5714285714285714</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="5">
@@ -42817,28 +44919,28 @@
         </is>
       </c>
       <c r="B5" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="0">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D5" s="0">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E5" s="4">
-        <v>0.23809523809523808</v>
+        <v>0.26666666666666666</v>
       </c>
       <c r="F5" s="4">
-        <v>0.2413793103448276</v>
+        <v>0.36363636363636365</v>
       </c>
       <c r="G5" s="0">
-        <v>0.9863945578231291</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="H5" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" s="4">
-        <v>0.7142857142857143</v>
+        <v>0.7333333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -42848,28 +44950,28 @@
         </is>
       </c>
       <c r="B6" s="0">
+        <v>15</v>
+      </c>
+      <c r="C6" s="0">
+        <v>150</v>
+      </c>
+      <c r="D6" s="0">
+        <v>37</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0.24666666666666667</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.36363636363636365</v>
+      </c>
+      <c r="G6" s="0">
+        <v>0.6783333333333333</v>
+      </c>
+      <c r="H6" s="0">
         <v>14</v>
       </c>
-      <c r="C6" s="0">
-        <v>140</v>
-      </c>
-      <c r="D6" s="0">
-        <v>32</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0.22857142857142856</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0.2413793103448276</v>
-      </c>
-      <c r="G6" s="0">
-        <v>0.946938775510204</v>
-      </c>
-      <c r="H6" s="0">
-        <v>13</v>
-      </c>
       <c r="I6" s="4">
-        <v>0.9285714285714286</v>
+        <v>0.9333333333333333</v>
       </c>
     </row>
     <row r="7">

--- a/docs/downloads/latest.xlsx
+++ b/docs/downloads/latest.xlsx
@@ -93,7 +93,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L662"/>
+  <dimension ref="A1:L682"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -35797,13 +35797,1093 @@
         </is>
       </c>
     </row>
+    <row r="663">
+      <c r="A663" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="B663" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="C663" s="0">
+        <v>1</v>
+      </c>
+      <c r="D663" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001360</t>
+        </is>
+      </c>
+      <c r="E663" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南矿集团</t>
+        </is>
+      </c>
+      <c r="F663" s="0">
+        <v>18.58</v>
+      </c>
+      <c r="G663" s="4">
+        <v>0.10005920663114252</v>
+      </c>
+      <c r="H663" s="4">
+        <v>0.37658087427734366</v>
+      </c>
+      <c r="I663" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J663" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 南矿集团（001360）归入“矿山装备+金属矿山+智能运维”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K663" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 10.0%）。截至运行时成交量约为20日均量的 0.3 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L663" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="B664" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="C664" s="0">
+        <v>2</v>
+      </c>
+      <c r="D664" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002307</t>
+        </is>
+      </c>
+      <c r="E664" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">北新路桥</t>
+        </is>
+      </c>
+      <c r="F664" s="0">
+        <v>3.39</v>
+      </c>
+      <c r="G664" s="4">
+        <v>0.10064935064935066</v>
+      </c>
+      <c r="H664" s="4">
+        <v>0.25508571253242934</v>
+      </c>
+      <c r="I664" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J664" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 北新路桥（002307）归入“基建盘活+公路施工+海外布局”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K664" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 10.1%）。截至运行时成交量约为20日均量的 6.3 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L664" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="B665" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="C665" s="0">
+        <v>3</v>
+      </c>
+      <c r="D665" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000530</t>
+        </is>
+      </c>
+      <c r="E665" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">冰山冷热</t>
+        </is>
+      </c>
+      <c r="F665" s="0">
+        <v>9.49</v>
+      </c>
+      <c r="G665" s="4">
+        <v>0.09965237543453064</v>
+      </c>
+      <c r="H665" s="4">
+        <v>0.19525485289373729</v>
+      </c>
+      <c r="I665" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J665" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 冰山冷热（000530）归入“冰雪工程+数据中心液冷+军工+冷热设备”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K665" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.1 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L665" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；近5日涨幅偏高，短线获利盘压力更大；近10日涨幅偏高</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="B666" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="C666" s="0">
+        <v>4</v>
+      </c>
+      <c r="D666" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">003021</t>
+        </is>
+      </c>
+      <c r="E666" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">兆威机电</t>
+        </is>
+      </c>
+      <c r="F666" s="0">
+        <v>83.39</v>
+      </c>
+      <c r="G666" s="4">
+        <v>0.09998680912808332</v>
+      </c>
+      <c r="H666" s="4">
+        <v>0.16704846195301212</v>
+      </c>
+      <c r="I666" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J666" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 兆威机电（003021）归入“人形机器人+灵巧手+微型传动”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K666" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L666" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">近5日涨幅偏高，短线获利盘压力更大</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="B667" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="C667" s="0">
+        <v>5</v>
+      </c>
+      <c r="D667" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000678</t>
+        </is>
+      </c>
+      <c r="E667" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">襄阳轴承</t>
+        </is>
+      </c>
+      <c r="F667" s="0">
+        <v>12.03</v>
+      </c>
+      <c r="G667" s="4">
+        <v>0.09963436928702007</v>
+      </c>
+      <c r="H667" s="4">
+        <v>0.1576739438868268</v>
+      </c>
+      <c r="I667" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J667" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 襄阳轴承（000678）归入“机器人轴承+汽车轴承+湖北国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K667" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.4 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L667" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="B668" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="C668" s="0">
+        <v>6</v>
+      </c>
+      <c r="D668" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002535</t>
+        </is>
+      </c>
+      <c r="E668" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">林州重机</t>
+        </is>
+      </c>
+      <c r="F668" s="0">
+        <v>2.75</v>
+      </c>
+      <c r="G668" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H668" s="4">
+        <v>0.1402797809775325</v>
+      </c>
+      <c r="I668" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J668" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 林州重机（002535）归入“煤矿机械+煤矿服务+军工配套”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K668" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L668" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="B669" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="C669" s="0">
+        <v>7</v>
+      </c>
+      <c r="D669" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600261</t>
+        </is>
+      </c>
+      <c r="E669" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">阳光照明</t>
+        </is>
+      </c>
+      <c r="F669" s="0">
+        <v>3.6</v>
+      </c>
+      <c r="G669" s="4">
+        <v>0.10091743119266061</v>
+      </c>
+      <c r="H669" s="4">
+        <v>0.13147903779454578</v>
+      </c>
+      <c r="I669" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J669" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 阳光照明（600261）归入“照明业务+LED+激光通信投资+氢能装备”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K669" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.5 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L669" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="B670" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="C670" s="0">
+        <v>8</v>
+      </c>
+      <c r="D670" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603028</t>
+        </is>
+      </c>
+      <c r="E670" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">赛福天</t>
+        </is>
+      </c>
+      <c r="F670" s="0">
+        <v>7.76</v>
+      </c>
+      <c r="G670" s="4">
+        <v>0.10070921985815605</v>
+      </c>
+      <c r="H670" s="4">
+        <v>0.13134096849712956</v>
+      </c>
+      <c r="I670" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J670" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 赛福天（603028）归入“机器人腱绳+特种钢索”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K670" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L670" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="B671" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="C671" s="0">
+        <v>9</v>
+      </c>
+      <c r="D671" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603528</t>
+        </is>
+      </c>
+      <c r="E671" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">多伦科技</t>
+        </is>
+      </c>
+      <c r="F671" s="0">
+        <v>7.4</v>
+      </c>
+      <c r="G671" s="4">
+        <v>0.09955423476968805</v>
+      </c>
+      <c r="H671" s="4">
+        <v>0.12734537435682527</v>
+      </c>
+      <c r="I671" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J671" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 多伦科技（603528）归入“人形机器人+智慧交管+智慧驾培”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K671" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.9 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L671" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="B672" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="C672" s="0">
+        <v>10</v>
+      </c>
+      <c r="D672" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600192</t>
+        </is>
+      </c>
+      <c r="E672" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">长城电工</t>
+        </is>
+      </c>
+      <c r="F672" s="0">
+        <v>8.33</v>
+      </c>
+      <c r="G672" s="4">
+        <v>0.10039630118890353</v>
+      </c>
+      <c r="H672" s="4">
+        <v>0.12340875669574876</v>
+      </c>
+      <c r="I672" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J672" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 长城电工（600192）归入“输配电设备+核电项目+资产处置”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K672" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L672" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="B673" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="C673" s="0">
+        <v>11</v>
+      </c>
+      <c r="D673" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600698</t>
+        </is>
+      </c>
+      <c r="E673" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湖南天雁</t>
+        </is>
+      </c>
+      <c r="F673" s="0">
+        <v>7.59</v>
+      </c>
+      <c r="G673" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H673" s="4">
+        <v>0.11719843041385197</v>
+      </c>
+      <c r="I673" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J673" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 湖南天雁（600698）归入“涡轮增压器+电子水泵+汽车零部件”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K673" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.5 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L673" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="B674" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="C674" s="0">
+        <v>12</v>
+      </c>
+      <c r="D674" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603280</t>
+        </is>
+      </c>
+      <c r="E674" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南方路机</t>
+        </is>
+      </c>
+      <c r="F674" s="0">
+        <v>29.06</v>
+      </c>
+      <c r="G674" s="4">
+        <v>0.09992429977289931</v>
+      </c>
+      <c r="H674" s="4">
+        <v>0.10240851213918802</v>
+      </c>
+      <c r="I674" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J674" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 南方路机（603280）归入“工程搅拌+智能机器人+AI智能体”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K674" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.8 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L674" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="B675" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="C675" s="0">
+        <v>13</v>
+      </c>
+      <c r="D675" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002249</t>
+        </is>
+      </c>
+      <c r="E675" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大洋电机</t>
+        </is>
+      </c>
+      <c r="F675" s="0">
+        <v>7.06</v>
+      </c>
+      <c r="G675" s="4">
+        <v>0.09968847352024923</v>
+      </c>
+      <c r="H675" s="4">
+        <v>0.10181728752146808</v>
+      </c>
+      <c r="I675" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J675" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 大洋电机（002249）归入“机器人关节+电机业务+数据中心风机+“羊”字辈”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K675" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.2 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L675" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="B676" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="C676" s="0">
+        <v>14</v>
+      </c>
+      <c r="D676" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603728</t>
+        </is>
+      </c>
+      <c r="E676" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">鸣志电器</t>
+        </is>
+      </c>
+      <c r="F676" s="0">
+        <v>54.47</v>
+      </c>
+      <c r="G676" s="4">
+        <v>0.09995961227786744</v>
+      </c>
+      <c r="H676" s="4">
+        <v>0.09896501376316337</v>
+      </c>
+      <c r="I676" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J676" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 鸣志电器（603728）归入“人形机器人+运动控制+数据中心液冷”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K676" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.0 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L676" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="B677" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="C677" s="0">
+        <v>15</v>
+      </c>
+      <c r="D677" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002983</t>
+        </is>
+      </c>
+      <c r="E677" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">芯瑞达</t>
+        </is>
+      </c>
+      <c r="F677" s="0">
+        <v>23.43</v>
+      </c>
+      <c r="G677" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H677" s="4">
+        <v>0.09250536492864032</v>
+      </c>
+      <c r="I677" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J677" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 芯瑞达（002983）归入“Mini/Micro-LED+AR-AI显示+像素车灯”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K677" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.8 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L677" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="B678" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="C678" s="0">
+        <v>16</v>
+      </c>
+      <c r="D678" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002097</t>
+        </is>
+      </c>
+      <c r="E678" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">山河智能</t>
+        </is>
+      </c>
+      <c r="F678" s="0">
+        <v>7.26</v>
+      </c>
+      <c r="G678" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H678" s="4">
+        <v>0.09081505873628704</v>
+      </c>
+      <c r="I678" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J678" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 山河智能（002097）归入“工程机械+无人应急装备+机器人概念+电动化”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K678" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.3 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L678" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="B679" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="C679" s="0">
+        <v>17</v>
+      </c>
+      <c r="D679" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603933</t>
+        </is>
+      </c>
+      <c r="E679" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">睿能科技</t>
+        </is>
+      </c>
+      <c r="F679" s="0">
+        <v>19.04</v>
+      </c>
+      <c r="G679" s="4">
+        <v>0.09994222992489889</v>
+      </c>
+      <c r="H679" s="4">
+        <v>0.08990329182675048</v>
+      </c>
+      <c r="I679" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J679" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 睿能科技（603933）归入“人形机器人+工业自动化+IC分销”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K679" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L679" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="B680" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="C680" s="0">
+        <v>18</v>
+      </c>
+      <c r="D680" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603089</t>
+        </is>
+      </c>
+      <c r="E680" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正裕工业</t>
+        </is>
+      </c>
+      <c r="F680" s="0">
+        <v>10.81</v>
+      </c>
+      <c r="G680" s="4">
+        <v>0.09969481180061045</v>
+      </c>
+      <c r="H680" s="4">
+        <v>0.08179100377092884</v>
+      </c>
+      <c r="I680" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J680" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 正裕工业（603089）归入“机器人零部件+柔性触觉+汽车减震器”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K680" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.5 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L680" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="B681" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="C681" s="0">
+        <v>19</v>
+      </c>
+      <c r="D681" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603370</t>
+        </is>
+      </c>
+      <c r="E681" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华新精科</t>
+        </is>
+      </c>
+      <c r="F681" s="0">
+        <v>28.71</v>
+      </c>
+      <c r="G681" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H681" s="4">
+        <v>0.07961609372953983</v>
+      </c>
+      <c r="I681" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J681" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华新精科（603370）归入“人形机器人+精密铁芯”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K681" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.1 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L681" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="B682" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="C682" s="0">
+        <v>20</v>
+      </c>
+      <c r="D682" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603350</t>
+        </is>
+      </c>
+      <c r="E682" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">安乃达</t>
+        </is>
+      </c>
+      <c r="F682" s="0">
+        <v>29.48</v>
+      </c>
+      <c r="G682" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H682" s="4">
+        <v>0.07649682342231925</v>
+      </c>
+      <c r="I682" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J682" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 安乃达（603350）归入“具身智能+两轮电驱+系统集成”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K682" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.2 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 29 家涨停，其中首板 20 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L682" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M153"/>
+  <dimension ref="A1:M163"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -44766,6 +45846,596 @@
       <c r="M153" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">43.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="B154" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C154" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D154" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603332</t>
+        </is>
+      </c>
+      <c r="E154" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">苏州龙杰</t>
+        </is>
+      </c>
+      <c r="F154" s="4">
+        <v>0.2731668867270573</v>
+      </c>
+      <c r="G154" s="4">
+        <v>0.09771473601260827</v>
+      </c>
+      <c r="H154" s="4">
+        <v>0.0985027580772262</v>
+      </c>
+      <c r="I154" s="4">
+        <v>-0.03467297084318355</v>
+      </c>
+      <c r="J154" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K154" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -3.47%</t>
+        </is>
+      </c>
+      <c r="L154" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M154" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="B155" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C155" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D155" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601999</t>
+        </is>
+      </c>
+      <c r="E155" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">出版传媒</t>
+        </is>
+      </c>
+      <c r="F155" s="4">
+        <v>0.1337057619479028</v>
+      </c>
+      <c r="G155" s="4">
+        <v>0.05769230769230771</v>
+      </c>
+      <c r="H155" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="I155" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="J155" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K155" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +10.00%</t>
+        </is>
+      </c>
+      <c r="L155" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M155" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="B156" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C156" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="D156" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600252</t>
+        </is>
+      </c>
+      <c r="E156" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中恒集团</t>
+        </is>
+      </c>
+      <c r="F156" s="4">
+        <v>0.12817547110907151</v>
+      </c>
+      <c r="G156" s="4">
+        <v>-0.012605042016806678</v>
+      </c>
+      <c r="H156" s="4">
+        <v>0.004201680672269115</v>
+      </c>
+      <c r="I156" s="4">
+        <v>-0.054621848739495715</v>
+      </c>
+      <c r="J156" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K156" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -5.46%</t>
+        </is>
+      </c>
+      <c r="L156" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M156" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="B157" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C157" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="D157" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002639</t>
+        </is>
+      </c>
+      <c r="E157" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雪人集团</t>
+        </is>
+      </c>
+      <c r="F157" s="4">
+        <v>0.11366237061683727</v>
+      </c>
+      <c r="G157" s="4">
+        <v>-0.026350461133069825</v>
+      </c>
+      <c r="H157" s="4">
+        <v>0.04743083003952564</v>
+      </c>
+      <c r="I157" s="4">
+        <v>-0.011857707509881354</v>
+      </c>
+      <c r="J157" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K157" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -1.19%</t>
+        </is>
+      </c>
+      <c r="L157" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M157" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="B158" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C158" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="D158" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603999</t>
+        </is>
+      </c>
+      <c r="E158" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">读者传媒</t>
+        </is>
+      </c>
+      <c r="F158" s="4">
+        <v>0.1104456483125589</v>
+      </c>
+      <c r="G158" s="4">
+        <v>-0.009370816599732157</v>
+      </c>
+      <c r="H158" s="4">
+        <v>-0.009370816599732157</v>
+      </c>
+      <c r="I158" s="4">
+        <v>-0.08032128514056225</v>
+      </c>
+      <c r="J158" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K158" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -8.03%</t>
+        </is>
+      </c>
+      <c r="L158" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M158" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.87</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="B159" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C159" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="D159" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002811</t>
+        </is>
+      </c>
+      <c r="E159" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">郑中设计</t>
+        </is>
+      </c>
+      <c r="F159" s="4">
+        <v>0.11011957034588603</v>
+      </c>
+      <c r="G159" s="4">
+        <v>0.002897350993377401</v>
+      </c>
+      <c r="H159" s="4">
+        <v>0.054635761589403975</v>
+      </c>
+      <c r="I159" s="4">
+        <v>0.020281456953642252</v>
+      </c>
+      <c r="J159" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K159" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +2.03%</t>
+        </is>
+      </c>
+      <c r="L159" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M159" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="B160" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C160" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="D160" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002086</t>
+        </is>
+      </c>
+      <c r="E160" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东方海洋</t>
+        </is>
+      </c>
+      <c r="F160" s="4">
+        <v>0.10815742561777428</v>
+      </c>
+      <c r="G160" s="4">
+        <v>-0.008368200836820106</v>
+      </c>
+      <c r="H160" s="4">
+        <v>0.046025104602510414</v>
+      </c>
+      <c r="I160" s="4">
+        <v>-0.06694560669456073</v>
+      </c>
+      <c r="J160" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K160" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -6.69%</t>
+        </is>
+      </c>
+      <c r="L160" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M160" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.23</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="B161" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C161" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="D161" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001216</t>
+        </is>
+      </c>
+      <c r="E161" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华瓷股份</t>
+        </is>
+      </c>
+      <c r="F161" s="4">
+        <v>0.10713056827800874</v>
+      </c>
+      <c r="G161" s="4">
+        <v>0.047222222222222276</v>
+      </c>
+      <c r="H161" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="I161" s="4">
+        <v>0.014285714285714235</v>
+      </c>
+      <c r="J161" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K161" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +1.43%</t>
+        </is>
+      </c>
+      <c r="L161" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M161" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="B162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="D162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600802</t>
+        </is>
+      </c>
+      <c r="E162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">福建水泥</t>
+        </is>
+      </c>
+      <c r="F162" s="4">
+        <v>0.10578262488191269</v>
+      </c>
+      <c r="G162" s="4">
+        <v>0.019886363636363535</v>
+      </c>
+      <c r="H162" s="4">
+        <v>0.09943181818181812</v>
+      </c>
+      <c r="I162" s="4">
+        <v>-0.0028409090909091717</v>
+      </c>
+      <c r="J162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -0.28%</t>
+        </is>
+      </c>
+      <c r="L162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="B163" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="C163" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="D163" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605388</t>
+        </is>
+      </c>
+      <c r="E163" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">均瑶健康</t>
+        </is>
+      </c>
+      <c r="F163" s="4">
+        <v>0.10032219501457071</v>
+      </c>
+      <c r="G163" s="4">
+        <v>-0.009562841530054711</v>
+      </c>
+      <c r="H163" s="4">
+        <v>-0.009562841530054711</v>
+      </c>
+      <c r="I163" s="4">
+        <v>-0.08879781420765032</v>
+      </c>
+      <c r="J163" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K163" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -8.88%</t>
+        </is>
+      </c>
+      <c r="L163" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M163" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.67</t>
         </is>
       </c>
     </row>
@@ -44857,28 +46527,28 @@
         </is>
       </c>
       <c r="B3" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" s="0">
         <v>7</v>
       </c>
       <c r="E3" s="4">
-        <v>0.4666666666666667</v>
+        <v>0.4375</v>
       </c>
       <c r="F3" s="4">
-        <v>0.36363636363636365</v>
+        <v>0.17857142857142858</v>
       </c>
       <c r="G3" s="0">
-        <v>1.2833333333333332</v>
+        <v>2.4499999999999997</v>
       </c>
       <c r="H3" s="0">
         <v>7</v>
       </c>
       <c r="I3" s="4">
-        <v>0.4666666666666667</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="4">
@@ -44888,28 +46558,28 @@
         </is>
       </c>
       <c r="B4" s="0">
+        <v>16</v>
+      </c>
+      <c r="C4" s="0">
+        <v>48</v>
+      </c>
+      <c r="D4" s="0">
         <v>15</v>
       </c>
-      <c r="C4" s="0">
-        <v>45</v>
-      </c>
-      <c r="D4" s="0">
-        <v>14</v>
-      </c>
       <c r="E4" s="4">
-        <v>0.3111111111111111</v>
+        <v>0.3125</v>
       </c>
       <c r="F4" s="4">
-        <v>0.36363636363636365</v>
+        <v>0.17857142857142858</v>
       </c>
       <c r="G4" s="0">
-        <v>0.8555555555555555</v>
+        <v>1.75</v>
       </c>
       <c r="H4" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I4" s="4">
-        <v>0.6</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="5">
@@ -44919,28 +46589,28 @@
         </is>
       </c>
       <c r="B5" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="0">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D5" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" s="4">
-        <v>0.26666666666666666</v>
+        <v>0.2604166666666667</v>
       </c>
       <c r="F5" s="4">
-        <v>0.36363636363636365</v>
+        <v>0.17857142857142858</v>
       </c>
       <c r="G5" s="0">
-        <v>0.7333333333333333</v>
+        <v>1.4583333333333335</v>
       </c>
       <c r="H5" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I5" s="4">
-        <v>0.7333333333333333</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="6">
@@ -44950,28 +46620,28 @@
         </is>
       </c>
       <c r="B6" s="0">
+        <v>16</v>
+      </c>
+      <c r="C6" s="0">
+        <v>160</v>
+      </c>
+      <c r="D6" s="0">
+        <v>38</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0.2375</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.17857142857142858</v>
+      </c>
+      <c r="G6" s="0">
+        <v>1.3299999999999998</v>
+      </c>
+      <c r="H6" s="0">
         <v>15</v>
       </c>
-      <c r="C6" s="0">
-        <v>150</v>
-      </c>
-      <c r="D6" s="0">
-        <v>37</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0.24666666666666667</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0.36363636363636365</v>
-      </c>
-      <c r="G6" s="0">
-        <v>0.6783333333333333</v>
-      </c>
-      <c r="H6" s="0">
-        <v>14</v>
-      </c>
       <c r="I6" s="4">
-        <v>0.9333333333333333</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="7">

--- a/docs/downloads/latest.xlsx
+++ b/docs/downloads/latest.xlsx
@@ -93,7 +93,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L682"/>
+  <dimension ref="A1:L735"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -36877,13 +36877,2875 @@
         </is>
       </c>
     </row>
+    <row r="683">
+      <c r="A683" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B683" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C683" s="0">
+        <v>1</v>
+      </c>
+      <c r="D683" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002982</t>
+        </is>
+      </c>
+      <c r="E683" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湘佳股份</t>
+        </is>
+      </c>
+      <c r="F683" s="0">
+        <v>13.28</v>
+      </c>
+      <c r="G683" s="4">
+        <v>0.1002485501242749</v>
+      </c>
+      <c r="H683" s="4">
+        <v>0.26866405270242955</v>
+      </c>
+      <c r="I683" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J683" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 湘佳股份（002982）归入“业绩增长+黄羽肉鸡”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K683" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 10.0%）。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L683" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B684" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C684" s="0">
+        <v>2</v>
+      </c>
+      <c r="D684" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603341</t>
+        </is>
+      </c>
+      <c r="E684" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">龙旗科技</t>
+        </is>
+      </c>
+      <c r="F684" s="0">
+        <v>44.14</v>
+      </c>
+      <c r="G684" s="4">
+        <v>0.09992524296037875</v>
+      </c>
+      <c r="H684" s="4">
+        <v>0.13483459223852917</v>
+      </c>
+      <c r="I684" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J684" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 龙旗科技（603341）归入“AI眼镜+AI PC+机器人+智能终端”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K684" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.9 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L684" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大；近5日涨幅偏高，短线获利盘压力更大</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B685" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C685" s="0">
+        <v>3</v>
+      </c>
+      <c r="D685" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603466</t>
+        </is>
+      </c>
+      <c r="E685" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">风语筑</t>
+        </is>
+      </c>
+      <c r="F685" s="0">
+        <v>14.69</v>
+      </c>
+      <c r="G685" s="4">
+        <v>0.10037453183520606</v>
+      </c>
+      <c r="H685" s="4">
+        <v>0.12777766137320726</v>
+      </c>
+      <c r="I685" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J685" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 风语筑（603466）归入“物理AI+具身智能+数字展示”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K685" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L685" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B686" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C686" s="0">
+        <v>4</v>
+      </c>
+      <c r="D686" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603626</t>
+        </is>
+      </c>
+      <c r="E686" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">科森科技</t>
+        </is>
+      </c>
+      <c r="F686" s="0">
+        <v>26.52</v>
+      </c>
+      <c r="G686" s="4">
+        <v>0.09950248756218905</v>
+      </c>
+      <c r="H686" s="4">
+        <v>0.12516529392280473</v>
+      </c>
+      <c r="I686" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no_verified_event</t>
+        </is>
+      </c>
+      <c r="J686" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">事件证据层未找到与当日涨停直接匹配的公告或新闻；系统不把概念标签、技术形态或主观猜测当成涨停原因。</t>
+        </is>
+      </c>
+      <c r="K686" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L686" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B687" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C687" s="0">
+        <v>5</v>
+      </c>
+      <c r="D687" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001216</t>
+        </is>
+      </c>
+      <c r="E687" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华瓷股份</t>
+        </is>
+      </c>
+      <c r="F687" s="0">
+        <v>28.12</v>
+      </c>
+      <c r="G687" s="4">
+        <v>0.10015649452269182</v>
+      </c>
+      <c r="H687" s="4">
+        <v>0.12470748338467871</v>
+      </c>
+      <c r="I687" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J687" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华瓷股份（001216）归入“MLCC粉体+氧化锆微珠+日用陶瓷”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K687" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L687" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B688" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C688" s="0">
+        <v>6</v>
+      </c>
+      <c r="D688" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002343</t>
+        </is>
+      </c>
+      <c r="E688" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">慈文传媒</t>
+        </is>
+      </c>
+      <c r="F688" s="0">
+        <v>10.89</v>
+      </c>
+      <c r="G688" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H688" s="4">
+        <v>0.1246153603546378</v>
+      </c>
+      <c r="I688" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J688" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 慈文传媒（002343）归入“影视剧+微短剧+影视IP”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K688" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.8 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L688" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；近10日涨幅偏高</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B689" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C689" s="0">
+        <v>7</v>
+      </c>
+      <c r="D689" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603337</t>
+        </is>
+      </c>
+      <c r="E689" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">杰克科技</t>
+        </is>
+      </c>
+      <c r="F689" s="0">
+        <v>39.26</v>
+      </c>
+      <c r="G689" s="4">
+        <v>0.10002801905295611</v>
+      </c>
+      <c r="H689" s="4">
+        <v>0.12360592364964289</v>
+      </c>
+      <c r="I689" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J689" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 杰克科技（603337）归入“人形机器人+数字成套+工业缝纫机”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K689" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.1 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L689" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B690" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C690" s="0">
+        <v>8</v>
+      </c>
+      <c r="D690" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600303</t>
+        </is>
+      </c>
+      <c r="E690" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">曙光股份</t>
+        </is>
+      </c>
+      <c r="F690" s="0">
+        <v>3.14</v>
+      </c>
+      <c r="G690" s="4">
+        <v>0.10175438596491236</v>
+      </c>
+      <c r="H690" s="4">
+        <v>0.11950056052158037</v>
+      </c>
+      <c r="I690" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J690" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 曙光股份（600303）归入“新能源客车+汽车车桥+军工”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K690" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L690" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B691" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C691" s="0">
+        <v>9</v>
+      </c>
+      <c r="D691" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603721</t>
+        </is>
+      </c>
+      <c r="E691" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中广天择</t>
+        </is>
+      </c>
+      <c r="F691" s="0">
+        <v>21.77</v>
+      </c>
+      <c r="G691" s="4">
+        <v>0.10005053057099556</v>
+      </c>
+      <c r="H691" s="4">
+        <v>0.11609531002906623</v>
+      </c>
+      <c r="I691" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J691" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 中广天择（603721）归入“AI语料+AI漫剧+传媒内容”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K691" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.4 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L691" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B692" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C692" s="0">
+        <v>10</v>
+      </c>
+      <c r="D692" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603081</t>
+        </is>
+      </c>
+      <c r="E692" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大丰实业</t>
+        </is>
+      </c>
+      <c r="F692" s="0">
+        <v>10.65</v>
+      </c>
+      <c r="G692" s="4">
+        <v>0.100206611570248</v>
+      </c>
+      <c r="H692" s="4">
+        <v>0.11503060190142221</v>
+      </c>
+      <c r="I692" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J692" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 大丰实业（603081）归入“机器人+文体旅集成+机器人乐队”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K692" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.5 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L692" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B693" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C693" s="0">
+        <v>11</v>
+      </c>
+      <c r="D693" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605488</t>
+        </is>
+      </c>
+      <c r="E693" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">福莱新材</t>
+        </is>
+      </c>
+      <c r="F693" s="0">
+        <v>38.15</v>
+      </c>
+      <c r="G693" s="4">
+        <v>0.10005767012687429</v>
+      </c>
+      <c r="H693" s="4">
+        <v>0.11032220235140737</v>
+      </c>
+      <c r="I693" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J693" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 福莱新材（605488）归入“机器人触觉+柔性传感+广告喷墨”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K693" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.8 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L693" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大；近5日涨幅偏高，短线获利盘压力更大</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B694" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C694" s="0">
+        <v>12</v>
+      </c>
+      <c r="D694" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603286</t>
+        </is>
+      </c>
+      <c r="E694" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">日盈电子</t>
+        </is>
+      </c>
+      <c r="F694" s="0">
+        <v>50.89</v>
+      </c>
+      <c r="G694" s="4">
+        <v>0.10008646779074803</v>
+      </c>
+      <c r="H694" s="4">
+        <v>0.10972836471962272</v>
+      </c>
+      <c r="I694" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J694" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 日盈电子（603286）归入“人形机器人+汽车零部件+电子皮肤”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K694" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.9 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L694" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B695" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C695" s="0">
+        <v>13</v>
+      </c>
+      <c r="D695" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603713</t>
+        </is>
+      </c>
+      <c r="E695" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">密尔克卫</t>
+        </is>
+      </c>
+      <c r="F695" s="0">
+        <v>66.66</v>
+      </c>
+      <c r="G695" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H695" s="4">
+        <v>0.10923350107416353</v>
+      </c>
+      <c r="I695" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J695" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 密尔克卫（603713）归入“三季报增长+半导体物流+化工供应链”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K695" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L695" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B696" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C696" s="0">
+        <v>14</v>
+      </c>
+      <c r="D696" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001359</t>
+        </is>
+      </c>
+      <c r="E696" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">平安电工</t>
+        </is>
+      </c>
+      <c r="F696" s="0">
+        <v>74.91</v>
+      </c>
+      <c r="G696" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H696" s="4">
+        <v>0.10685334400633684</v>
+      </c>
+      <c r="I696" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J696" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 平安电工（001359）归入“电子布+PCB概念+泰国建厂”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K696" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L696" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B697" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C697" s="0">
+        <v>15</v>
+      </c>
+      <c r="D697" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000700</t>
+        </is>
+      </c>
+      <c r="E697" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">模塑科技</t>
+        </is>
+      </c>
+      <c r="F697" s="0">
+        <v>11.88</v>
+      </c>
+      <c r="G697" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H697" s="4">
+        <v>0.10366322880602358</v>
+      </c>
+      <c r="I697" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J697" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 模塑科技（000700）归入“人形机器人+汽车外饰件+毛利率提升”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K697" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.5 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L697" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B698" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C698" s="0">
+        <v>16</v>
+      </c>
+      <c r="D698" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002354</t>
+        </is>
+      </c>
+      <c r="E698" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天娱数科</t>
+        </is>
+      </c>
+      <c r="F698" s="0">
+        <v>8.03</v>
+      </c>
+      <c r="G698" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H698" s="4">
+        <v>0.1012863688784512</v>
+      </c>
+      <c r="I698" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J698" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 天娱数科（002354）归入“具身智能数据集+AI影视+AI营销+算力”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K698" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.4 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L698" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B699" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C699" s="0">
+        <v>17</v>
+      </c>
+      <c r="D699" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002988</t>
+        </is>
+      </c>
+      <c r="E699" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">豪美新材</t>
+        </is>
+      </c>
+      <c r="F699" s="0">
+        <v>31.24</v>
+      </c>
+      <c r="G699" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H699" s="4">
+        <v>0.10020604310131702</v>
+      </c>
+      <c r="I699" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J699" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 豪美新材（002988）归入“机器人轻量化+汽车轻量化+铝型材”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K699" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.9 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L699" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B700" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C700" s="0">
+        <v>18</v>
+      </c>
+      <c r="D700" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603171</t>
+        </is>
+      </c>
+      <c r="E700" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">税友股份</t>
+        </is>
+      </c>
+      <c r="F700" s="0">
+        <v>48.29</v>
+      </c>
+      <c r="G700" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H700" s="4">
+        <v>0.09894381465207504</v>
+      </c>
+      <c r="I700" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J700" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 税友股份（603171）归入“AI智能体+财税数字化+阿里云合作”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K700" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L700" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B701" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C701" s="0">
+        <v>19</v>
+      </c>
+      <c r="D701" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001283</t>
+        </is>
+      </c>
+      <c r="E701" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">豪鹏科技</t>
+        </is>
+      </c>
+      <c r="F701" s="0">
+        <v>57.27</v>
+      </c>
+      <c r="G701" s="4">
+        <v>0.10007683442182103</v>
+      </c>
+      <c r="H701" s="4">
+        <v>0.09135024315026469</v>
+      </c>
+      <c r="I701" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J701" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 豪鹏科技（001283）归入“机器人电池+智能眼镜电池+三季报增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K701" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.2 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L701" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B702" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C702" s="0">
+        <v>20</v>
+      </c>
+      <c r="D702" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002931</t>
+        </is>
+      </c>
+      <c r="E702" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">锋龙股份</t>
+        </is>
+      </c>
+      <c r="F702" s="0">
+        <v>38.52</v>
+      </c>
+      <c r="G702" s="4">
+        <v>0.09994288977727006</v>
+      </c>
+      <c r="H702" s="4">
+        <v>0.09121158171947082</v>
+      </c>
+      <c r="I702" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J702" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 锋龙股份（002931）归入“机器人概念+优必选入主+机电组件+电控产品”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K702" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.8 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L702" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B703" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C703" s="0">
+        <v>21</v>
+      </c>
+      <c r="D703" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603859</t>
+        </is>
+      </c>
+      <c r="E703" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">能科科技</t>
+        </is>
+      </c>
+      <c r="F703" s="0">
+        <v>43.56</v>
+      </c>
+      <c r="G703" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H703" s="4">
+        <v>0.09099632423889269</v>
+      </c>
+      <c r="I703" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J703" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 能科科技（603859）归入“具身智能+工业智能+工业软件”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K703" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.8 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L703" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B704" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C704" s="0">
+        <v>22</v>
+      </c>
+      <c r="D704" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603901</t>
+        </is>
+      </c>
+      <c r="E704" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">永创智能</t>
+        </is>
+      </c>
+      <c r="F704" s="0">
+        <v>9.66</v>
+      </c>
+      <c r="G704" s="4">
+        <v>0.10022779043280196</v>
+      </c>
+      <c r="H704" s="4">
+        <v>0.09005956364118008</v>
+      </c>
+      <c r="I704" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J704" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 永创智能（603901）归入“人形机器人+智能包装+半年报增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K704" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.5 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L704" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B705" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C705" s="0">
+        <v>23</v>
+      </c>
+      <c r="D705" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002474</t>
+        </is>
+      </c>
+      <c r="E705" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">榕基软件</t>
+        </is>
+      </c>
+      <c r="F705" s="0">
+        <v>7.11</v>
+      </c>
+      <c r="G705" s="4">
+        <v>0.10061919504643967</v>
+      </c>
+      <c r="H705" s="4">
+        <v>0.08817432645593115</v>
+      </c>
+      <c r="I705" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J705" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 榕基软件（002474）归入“AI政务+信创政务+数据要素”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K705" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.2 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L705" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B706" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C706" s="0">
+        <v>24</v>
+      </c>
+      <c r="D706" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000156</t>
+        </is>
+      </c>
+      <c r="E706" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华数传媒</t>
+        </is>
+      </c>
+      <c r="F706" s="0">
+        <v>7.71</v>
+      </c>
+      <c r="G706" s="4">
+        <v>0.09985734664764623</v>
+      </c>
+      <c r="H706" s="4">
+        <v>0.08794650575828467</v>
+      </c>
+      <c r="I706" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J706" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华数传媒（000156）归入“广电智能体+具身智能+智慧家庭+内容安全审核”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K706" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L706" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B707" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C707" s="0">
+        <v>25</v>
+      </c>
+      <c r="D707" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002421</t>
+        </is>
+      </c>
+      <c r="E707" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">达实智能</t>
+        </is>
+      </c>
+      <c r="F707" s="0">
+        <v>3.43</v>
+      </c>
+      <c r="G707" s="4">
+        <v>0.09935897435897445</v>
+      </c>
+      <c r="H707" s="4">
+        <v>0.08560263891036451</v>
+      </c>
+      <c r="I707" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J707" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 达实智能（002421）归入“AIoT+AI智能体+医疗物流机器人+新皇岗口岸”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K707" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.9 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L707" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B708" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C708" s="0">
+        <v>26</v>
+      </c>
+      <c r="D708" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001298</t>
+        </is>
+      </c>
+      <c r="E708" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">好上好</t>
+        </is>
+      </c>
+      <c r="F708" s="0">
+        <v>17.36</v>
+      </c>
+      <c r="G708" s="4">
+        <v>0.10012674271229403</v>
+      </c>
+      <c r="H708" s="4">
+        <v>0.08474794368991324</v>
+      </c>
+      <c r="I708" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J708" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 好上好（001298）归入“存储芯片+半导体分销+人形机器人”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K708" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.2 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L708" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B709" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C709" s="0">
+        <v>27</v>
+      </c>
+      <c r="D709" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000559</t>
+        </is>
+      </c>
+      <c r="E709" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">万向钱潮</t>
+        </is>
+      </c>
+      <c r="F709" s="0">
+        <v>11.55</v>
+      </c>
+      <c r="G709" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H709" s="4">
+        <v>0.08460514658624867</v>
+      </c>
+      <c r="I709" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J709" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 万向钱潮（000559）归入“机器人+轮毂单元+高速轴承”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K709" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.9 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L709" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B710" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C710" s="0">
+        <v>28</v>
+      </c>
+      <c r="D710" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002747</t>
+        </is>
+      </c>
+      <c r="E710" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">埃斯顿</t>
+        </is>
+      </c>
+      <c r="F710" s="0">
+        <v>29.18</v>
+      </c>
+      <c r="G710" s="4">
+        <v>0.09988692046739533</v>
+      </c>
+      <c r="H710" s="4">
+        <v>0.08433521400912258</v>
+      </c>
+      <c r="I710" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J710" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 埃斯顿（002747）归入“工业机器人+具身智能+人形机器人”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K710" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.5 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L710" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B711" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C711" s="0">
+        <v>29</v>
+      </c>
+      <c r="D711" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002380</t>
+        </is>
+      </c>
+      <c r="E711" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">科远智慧</t>
+        </is>
+      </c>
+      <c r="F711" s="0">
+        <v>27.67</v>
+      </c>
+      <c r="G711" s="4">
+        <v>0.10019880715705787</v>
+      </c>
+      <c r="H711" s="4">
+        <v>0.08346358969415874</v>
+      </c>
+      <c r="I711" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J711" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 科远智慧（002380）归入“机器人+工业人工智能+半年报增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K711" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.0 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L711" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B712" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C712" s="0">
+        <v>30</v>
+      </c>
+      <c r="D712" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002322</t>
+        </is>
+      </c>
+      <c r="E712" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">理工能科</t>
+        </is>
+      </c>
+      <c r="F712" s="0">
+        <v>13.67</v>
+      </c>
+      <c r="G712" s="4">
+        <v>0.09975864843121475</v>
+      </c>
+      <c r="H712" s="4">
+        <v>0.08304642061879493</v>
+      </c>
+      <c r="I712" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J712" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 理工能科（002322）归入“AI应用+电力软件+业绩预增”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K712" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.2 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L712" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B713" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C713" s="0">
+        <v>31</v>
+      </c>
+      <c r="D713" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002979</t>
+        </is>
+      </c>
+      <c r="E713" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雷赛智能</t>
+        </is>
+      </c>
+      <c r="F713" s="0">
+        <v>54.15</v>
+      </c>
+      <c r="G713" s="4">
+        <v>0.09993906154783684</v>
+      </c>
+      <c r="H713" s="4">
+        <v>0.08062347821578528</v>
+      </c>
+      <c r="I713" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J713" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 雷赛智能（002979）归入“三季报增长+人形机器人+伺服系统”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K713" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L713" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B714" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C714" s="0">
+        <v>32</v>
+      </c>
+      <c r="D714" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000972</t>
+        </is>
+      </c>
+      <c r="E714" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中基健康</t>
+        </is>
+      </c>
+      <c r="F714" s="0">
+        <v>4.06</v>
+      </c>
+      <c r="G714" s="4">
+        <v>0.10027100271002709</v>
+      </c>
+      <c r="H714" s="4">
+        <v>0.0787267368319264</v>
+      </c>
+      <c r="I714" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J714" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 中基健康（000972）归入“番茄制品+大消费+国企改革”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K714" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.4 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L714" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B715" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C715" s="0">
+        <v>33</v>
+      </c>
+      <c r="D715" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600785</t>
+        </is>
+      </c>
+      <c r="E715" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新华百货</t>
+        </is>
+      </c>
+      <c r="F715" s="0">
+        <v>12.56</v>
+      </c>
+      <c r="G715" s="4">
+        <v>0.09982486865148864</v>
+      </c>
+      <c r="H715" s="4">
+        <v>0.07672912220059563</v>
+      </c>
+      <c r="I715" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J715" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 新华百货（600785）归入“零售促销+股份回购+硬折扣”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K715" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L715" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B716" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C716" s="0">
+        <v>34</v>
+      </c>
+      <c r="D716" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603838</t>
+        </is>
+      </c>
+      <c r="E716" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">四通股份</t>
+        </is>
+      </c>
+      <c r="F716" s="0">
+        <v>14.72</v>
+      </c>
+      <c r="G716" s="4">
+        <v>0.1001494768310911</v>
+      </c>
+      <c r="H716" s="4">
+        <v>0.07500921064926327</v>
+      </c>
+      <c r="I716" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J716" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 四通股份（603838）归入“日用陶瓷+锆钛精炼+摘帽”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K716" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.3 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L716" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B717" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C717" s="0">
+        <v>35</v>
+      </c>
+      <c r="D717" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603160</t>
+        </is>
+      </c>
+      <c r="E717" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汇顶科技</t>
+        </is>
+      </c>
+      <c r="F717" s="0">
+        <v>56.49</v>
+      </c>
+      <c r="G717" s="4">
+        <v>0.10009737098344695</v>
+      </c>
+      <c r="H717" s="4">
+        <v>0.07470124184436926</v>
+      </c>
+      <c r="I717" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J717" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 汇顶科技（603160）归入“指纹识别+超声波指纹传感器+端侧安全+折叠屏”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K717" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.8 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L717" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B718" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C718" s="0">
+        <v>36</v>
+      </c>
+      <c r="D718" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002241</t>
+        </is>
+      </c>
+      <c r="E718" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">歌尔股份</t>
+        </is>
+      </c>
+      <c r="F718" s="0">
+        <v>23.11</v>
+      </c>
+      <c r="G718" s="4">
+        <v>0.09995240361732494</v>
+      </c>
+      <c r="H718" s="4">
+        <v>0.07458303206779954</v>
+      </c>
+      <c r="I718" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J718" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 歌尔股份（002241）归入“机器人+智能眼镜+精密零组件”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K718" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L718" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B719" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C719" s="0">
+        <v>37</v>
+      </c>
+      <c r="D719" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002945</t>
+        </is>
+      </c>
+      <c r="E719" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华林证券</t>
+        </is>
+      </c>
+      <c r="F719" s="0">
+        <v>15.36</v>
+      </c>
+      <c r="G719" s="4">
+        <v>0.10028653295128918</v>
+      </c>
+      <c r="H719" s="4">
+        <v>0.07399871251231008</v>
+      </c>
+      <c r="I719" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J719" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华林证券（002945）归入“AI金融+证券业务+西藏券商”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K719" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.3 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L719" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B720" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C720" s="0">
+        <v>38</v>
+      </c>
+      <c r="D720" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000810</t>
+        </is>
+      </c>
+      <c r="E720" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">创维数字</t>
+        </is>
+      </c>
+      <c r="F720" s="0">
+        <v>10.02</v>
+      </c>
+      <c r="G720" s="4">
+        <v>0.09989023051591663</v>
+      </c>
+      <c r="H720" s="4">
+        <v>0.07383501881136549</v>
+      </c>
+      <c r="I720" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J720" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 创维数字（000810）归入“智能终端+谷歌合作+AI眼镜”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K720" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.3 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L720" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B721" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C721" s="0">
+        <v>39</v>
+      </c>
+      <c r="D721" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600215</t>
+        </is>
+      </c>
+      <c r="E721" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">派斯林</t>
+        </is>
+      </c>
+      <c r="F721" s="0">
+        <v>6.34</v>
+      </c>
+      <c r="G721" s="4">
+        <v>0.10069444444444443</v>
+      </c>
+      <c r="H721" s="4">
+        <v>0.07365582534245828</v>
+      </c>
+      <c r="I721" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J721" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 派斯林（600215）归入“仿生机器人+工业自动化+北美订单”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K721" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.1 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L721" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B722" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C722" s="0">
+        <v>40</v>
+      </c>
+      <c r="D722" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601519</t>
+        </is>
+      </c>
+      <c r="E722" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大智慧</t>
+        </is>
+      </c>
+      <c r="F722" s="0">
+        <v>9.25</v>
+      </c>
+      <c r="G722" s="4">
+        <v>0.0998810939357908</v>
+      </c>
+      <c r="H722" s="4">
+        <v>0.06756408372066333</v>
+      </c>
+      <c r="I722" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J722" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 大智慧（601519）归入“互联网金融+AI投研+并购重组”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K722" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.5 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L722" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B723" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C723" s="0">
+        <v>41</v>
+      </c>
+      <c r="D723" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002009</t>
+        </is>
+      </c>
+      <c r="E723" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天奇股份</t>
+        </is>
+      </c>
+      <c r="F723" s="0">
+        <v>17.3</v>
+      </c>
+      <c r="G723" s="4">
+        <v>0.09980928162746337</v>
+      </c>
+      <c r="H723" s="4">
+        <v>0.06750283835501147</v>
+      </c>
+      <c r="I723" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J723" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 天奇股份（002009）归入“具身智能+工业机器人+产业合作+优必选”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K723" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.6 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L723" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B724" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C724" s="0">
+        <v>42</v>
+      </c>
+      <c r="D724" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001328</t>
+        </is>
+      </c>
+      <c r="E724" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">登康口腔</t>
+        </is>
+      </c>
+      <c r="F724" s="0">
+        <v>32.51</v>
+      </c>
+      <c r="G724" s="4">
+        <v>0.10016920473773251</v>
+      </c>
+      <c r="H724" s="4">
+        <v>0.06613909387992098</v>
+      </c>
+      <c r="I724" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J724" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 登康口腔（001328）归入“三季报增长+抗敏牙膏+智能口腔”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K724" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.4 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L724" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B725" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C725" s="0">
+        <v>43</v>
+      </c>
+      <c r="D725" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002077</t>
+        </is>
+      </c>
+      <c r="E725" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大港股份</t>
+        </is>
+      </c>
+      <c r="F725" s="0">
+        <v>13.08</v>
+      </c>
+      <c r="G725" s="4">
+        <v>0.1000841042893188</v>
+      </c>
+      <c r="H725" s="4">
+        <v>0.0658211108962103</v>
+      </c>
+      <c r="I725" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J725" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 大港股份（002077）归入“集成电路测试+股权转让议案+半年报增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K725" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L725" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B726" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C726" s="0">
+        <v>44</v>
+      </c>
+      <c r="D726" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002687</t>
+        </is>
+      </c>
+      <c r="E726" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">乔治白</t>
+        </is>
+      </c>
+      <c r="F726" s="0">
+        <v>6.75</v>
+      </c>
+      <c r="G726" s="4">
+        <v>0.09934853420195446</v>
+      </c>
+      <c r="H726" s="4">
+        <v>0.06564107612993672</v>
+      </c>
+      <c r="I726" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J726" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 乔治白（002687）归入“职业装+校服+股东户数下降”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K726" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L726" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B727" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C727" s="0">
+        <v>45</v>
+      </c>
+      <c r="D727" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600094</t>
+        </is>
+      </c>
+      <c r="E727" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大名城</t>
+        </is>
+      </c>
+      <c r="F727" s="0">
+        <v>4.39</v>
+      </c>
+      <c r="G727" s="4">
+        <v>0.1002506265664158</v>
+      </c>
+      <c r="H727" s="4">
+        <v>0.06454321607921036</v>
+      </c>
+      <c r="I727" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J727" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 大名城（600094）归入“房地产开发+低空经济+算力运营+6G通信”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K727" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L727" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B728" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C728" s="0">
+        <v>46</v>
+      </c>
+      <c r="D728" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002026</t>
+        </is>
+      </c>
+      <c r="E728" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">山东威达</t>
+        </is>
+      </c>
+      <c r="F728" s="0">
+        <v>11.04</v>
+      </c>
+      <c r="G728" s="4">
+        <v>0.09960159362549792</v>
+      </c>
+      <c r="H728" s="4">
+        <v>0.06451303893527173</v>
+      </c>
+      <c r="I728" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J728" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 山东威达（002026）归入“机器人+换电站+电动工具”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K728" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L728" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B729" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C729" s="0">
+        <v>47</v>
+      </c>
+      <c r="D729" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002612</t>
+        </is>
+      </c>
+      <c r="E729" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">朗姿股份</t>
+        </is>
+      </c>
+      <c r="F729" s="0">
+        <v>16.93</v>
+      </c>
+      <c r="G729" s="4">
+        <v>0.1000649772579596</v>
+      </c>
+      <c r="H729" s="4">
+        <v>0.06355660497437132</v>
+      </c>
+      <c r="I729" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J729" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 朗姿股份（002612）归入“医疗美容+时尚女装+中韩自贸区”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K729" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L729" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B730" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C730" s="0">
+        <v>48</v>
+      </c>
+      <c r="D730" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603677</t>
+        </is>
+      </c>
+      <c r="E730" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奇精机械</t>
+        </is>
+      </c>
+      <c r="F730" s="0">
+        <v>16.3</v>
+      </c>
+      <c r="G730" s="4">
+        <v>0.09986504723346833</v>
+      </c>
+      <c r="H730" s="4">
+        <v>0.06237416723269314</v>
+      </c>
+      <c r="I730" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J730" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 奇精机械（603677）归入“机器人零部件+光模块+洗衣机离合器”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K730" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.5 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L730" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B731" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C731" s="0">
+        <v>49</v>
+      </c>
+      <c r="D731" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002812</t>
+        </is>
+      </c>
+      <c r="E731" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">恩捷股份</t>
+        </is>
+      </c>
+      <c r="F731" s="0">
+        <v>46.92</v>
+      </c>
+      <c r="G731" s="4">
+        <v>0.10011723329425572</v>
+      </c>
+      <c r="H731" s="4">
+        <v>0.061694027176683576</v>
+      </c>
+      <c r="I731" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J731" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 恩捷股份（002812）归入“锂电池隔膜+业绩扭亏+固态电池材料”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K731" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.5 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L731" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B732" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C732" s="0">
+        <v>50</v>
+      </c>
+      <c r="D732" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001301</t>
+        </is>
+      </c>
+      <c r="E732" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">尚太科技</t>
+        </is>
+      </c>
+      <c r="F732" s="0">
+        <v>45.71</v>
+      </c>
+      <c r="G732" s="4">
+        <v>0.10012033694344179</v>
+      </c>
+      <c r="H732" s="4">
+        <v>0.06134781552431813</v>
+      </c>
+      <c r="I732" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J732" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 尚太科技（001301）归入“负极材料+三季度增长+产能扩建”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K732" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.9 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L732" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B733" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C733" s="0">
+        <v>51</v>
+      </c>
+      <c r="D733" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600506</t>
+        </is>
+      </c>
+      <c r="E733" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">统一股份</t>
+        </is>
+      </c>
+      <c r="F733" s="0">
+        <v>16.83</v>
+      </c>
+      <c r="G733" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H733" s="4">
+        <v>0.060216984697411276</v>
+      </c>
+      <c r="I733" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J733" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 统一股份（600506）归入“液冷+润滑油脂+业绩增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K733" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L733" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B734" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C734" s="0">
+        <v>52</v>
+      </c>
+      <c r="D734" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002439</t>
+        </is>
+      </c>
+      <c r="E734" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">启明星辰</t>
+        </is>
+      </c>
+      <c r="F734" s="0">
+        <v>15.05</v>
+      </c>
+      <c r="G734" s="4">
+        <v>0.10014619883040954</v>
+      </c>
+      <c r="H734" s="4">
+        <v>0.05804771906583506</v>
+      </c>
+      <c r="I734" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J734" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 启明星辰（002439）归入“AI安全+数据安全+中移动协同”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K734" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L734" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B735" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C735" s="0">
+        <v>53</v>
+      </c>
+      <c r="D735" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600865</t>
+        </is>
+      </c>
+      <c r="E735" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">百大集团</t>
+        </is>
+      </c>
+      <c r="F735" s="0">
+        <v>11.04</v>
+      </c>
+      <c r="G735" s="4">
+        <v>0.09960159362549792</v>
+      </c>
+      <c r="H735" s="4">
+        <v>0.05804153870383121</v>
+      </c>
+      <c r="I735" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J735" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 百大集团（600865）归入“商业零售+净利润增长+信托股权交易”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K735" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 65 家涨停，其中首板 53 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L735" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M163"/>
+  <dimension ref="A1:M173"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -46436,6 +49298,596 @@
       <c r="M163" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">6.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B164" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="C164" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D164" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001360</t>
+        </is>
+      </c>
+      <c r="E164" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南矿集团</t>
+        </is>
+      </c>
+      <c r="F164" s="4">
+        <v>0.37658087427734366</v>
+      </c>
+      <c r="G164" s="4">
+        <v>0.1001076426264802</v>
+      </c>
+      <c r="H164" s="4">
+        <v>0.1001076426264802</v>
+      </c>
+      <c r="I164" s="4">
+        <v>-0.03767491926803013</v>
+      </c>
+      <c r="J164" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K164" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -3.77%</t>
+        </is>
+      </c>
+      <c r="L164" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M164" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B165" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="C165" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D165" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002307</t>
+        </is>
+      </c>
+      <c r="E165" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">北新路桥</t>
+        </is>
+      </c>
+      <c r="F165" s="4">
+        <v>0.25508571253242934</v>
+      </c>
+      <c r="G165" s="4">
+        <v>0.06194690265486735</v>
+      </c>
+      <c r="H165" s="4">
+        <v>0.10029498525073732</v>
+      </c>
+      <c r="I165" s="4">
+        <v>0.020648967551622377</v>
+      </c>
+      <c r="J165" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K165" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +2.06%</t>
+        </is>
+      </c>
+      <c r="L165" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M165" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B166" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="C166" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="D166" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000530</t>
+        </is>
+      </c>
+      <c r="E166" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">冰山冷热</t>
+        </is>
+      </c>
+      <c r="F166" s="4">
+        <v>0.19525485289373729</v>
+      </c>
+      <c r="G166" s="4">
+        <v>-0.07165437302423605</v>
+      </c>
+      <c r="H166" s="4">
+        <v>0.004214963119072657</v>
+      </c>
+      <c r="I166" s="4">
+        <v>0.004214963119072657</v>
+      </c>
+      <c r="J166" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K166" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +0.42%</t>
+        </is>
+      </c>
+      <c r="L166" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M166" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B167" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="C167" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="D167" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">003021</t>
+        </is>
+      </c>
+      <c r="E167" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">兆威机电</t>
+        </is>
+      </c>
+      <c r="F167" s="4">
+        <v>0.16704846195301212</v>
+      </c>
+      <c r="G167" s="4">
+        <v>0.01930687132749731</v>
+      </c>
+      <c r="H167" s="4">
+        <v>0.1000119918455451</v>
+      </c>
+      <c r="I167" s="4">
+        <v>0.1000119918455451</v>
+      </c>
+      <c r="J167" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K167" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +10.00%</t>
+        </is>
+      </c>
+      <c r="L167" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M167" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B168" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="C168" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="D168" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000678</t>
+        </is>
+      </c>
+      <c r="E168" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">襄阳轴承</t>
+        </is>
+      </c>
+      <c r="F168" s="4">
+        <v>0.1576739438868268</v>
+      </c>
+      <c r="G168" s="4">
+        <v>-0.029093931837073983</v>
+      </c>
+      <c r="H168" s="4">
+        <v>0.09975062344139651</v>
+      </c>
+      <c r="I168" s="4">
+        <v>0.09975062344139651</v>
+      </c>
+      <c r="J168" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K168" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +9.98%</t>
+        </is>
+      </c>
+      <c r="L168" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M168" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13.23</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B169" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="C169" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="D169" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002535</t>
+        </is>
+      </c>
+      <c r="E169" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">林州重机</t>
+        </is>
+      </c>
+      <c r="F169" s="4">
+        <v>0.1402797809775325</v>
+      </c>
+      <c r="G169" s="4">
+        <v>0.09454545454545449</v>
+      </c>
+      <c r="H169" s="4">
+        <v>0.10181818181818181</v>
+      </c>
+      <c r="I169" s="4">
+        <v>0.10181818181818181</v>
+      </c>
+      <c r="J169" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K169" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +10.18%</t>
+        </is>
+      </c>
+      <c r="L169" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M169" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B170" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="C170" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="D170" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600261</t>
+        </is>
+      </c>
+      <c r="E170" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">阳光照明</t>
+        </is>
+      </c>
+      <c r="F170" s="4">
+        <v>0.13147903779454578</v>
+      </c>
+      <c r="G170" s="4">
+        <v>-0.05555555555555558</v>
+      </c>
+      <c r="H170" s="4">
+        <v>0.002777777777777768</v>
+      </c>
+      <c r="I170" s="4">
+        <v>-0.04166666666666663</v>
+      </c>
+      <c r="J170" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K170" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -4.17%</t>
+        </is>
+      </c>
+      <c r="L170" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M170" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B171" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="C171" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="D171" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603028</t>
+        </is>
+      </c>
+      <c r="E171" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">赛福天</t>
+        </is>
+      </c>
+      <c r="F171" s="4">
+        <v>0.13134096849712956</v>
+      </c>
+      <c r="G171" s="4">
+        <v>0.10051546391752564</v>
+      </c>
+      <c r="H171" s="4">
+        <v>0.10051546391752564</v>
+      </c>
+      <c r="I171" s="4">
+        <v>0.10051546391752564</v>
+      </c>
+      <c r="J171" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K171" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +10.05%</t>
+        </is>
+      </c>
+      <c r="L171" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M171" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8.54</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B172" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="C172" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="D172" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603528</t>
+        </is>
+      </c>
+      <c r="E172" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">多伦科技</t>
+        </is>
+      </c>
+      <c r="F172" s="4">
+        <v>0.12734537435682527</v>
+      </c>
+      <c r="G172" s="4">
+        <v>-0.04189189189189191</v>
+      </c>
+      <c r="H172" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="I172" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="J172" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K172" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +10.00%</t>
+        </is>
+      </c>
+      <c r="L172" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M172" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="B173" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="C173" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="D173" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600192</t>
+        </is>
+      </c>
+      <c r="E173" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">长城电工</t>
+        </is>
+      </c>
+      <c r="F173" s="4">
+        <v>0.12340875669574876</v>
+      </c>
+      <c r="G173" s="4">
+        <v>-0.038415366146458574</v>
+      </c>
+      <c r="H173" s="4">
+        <v>0.054021608643457286</v>
+      </c>
+      <c r="I173" s="4">
+        <v>0.024009603841536498</v>
+      </c>
+      <c r="J173" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K173" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +2.40%</t>
+        </is>
+      </c>
+      <c r="L173" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M173" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8.53</t>
         </is>
       </c>
     </row>
@@ -46527,28 +49979,28 @@
         </is>
       </c>
       <c r="B3" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" s="0">
         <v>7</v>
       </c>
       <c r="E3" s="4">
-        <v>0.4375</v>
+        <v>0.4117647058823529</v>
       </c>
       <c r="F3" s="4">
-        <v>0.17857142857142858</v>
+        <v>0.45</v>
       </c>
       <c r="G3" s="0">
-        <v>2.4499999999999997</v>
+        <v>0.9150326797385621</v>
       </c>
       <c r="H3" s="0">
         <v>7</v>
       </c>
       <c r="I3" s="4">
-        <v>0.4375</v>
+        <v>0.4117647058823529</v>
       </c>
     </row>
     <row r="4">
@@ -46558,28 +50010,28 @@
         </is>
       </c>
       <c r="B4" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" s="0">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D4" s="0">
         <v>15</v>
       </c>
       <c r="E4" s="4">
-        <v>0.3125</v>
+        <v>0.29411764705882354</v>
       </c>
       <c r="F4" s="4">
-        <v>0.17857142857142858</v>
+        <v>0.45</v>
       </c>
       <c r="G4" s="0">
-        <v>1.75</v>
+        <v>0.6535947712418301</v>
       </c>
       <c r="H4" s="0">
         <v>10</v>
       </c>
       <c r="I4" s="4">
-        <v>0.625</v>
+        <v>0.5882352941176471</v>
       </c>
     </row>
     <row r="5">
@@ -46589,28 +50041,28 @@
         </is>
       </c>
       <c r="B5" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" s="0">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D5" s="0">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E5" s="4">
-        <v>0.2604166666666667</v>
+        <v>0.27450980392156865</v>
       </c>
       <c r="F5" s="4">
-        <v>0.17857142857142858</v>
+        <v>0.45</v>
       </c>
       <c r="G5" s="0">
-        <v>1.4583333333333335</v>
+        <v>0.6100217864923748</v>
       </c>
       <c r="H5" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I5" s="4">
-        <v>0.75</v>
+        <v>0.7647058823529411</v>
       </c>
     </row>
     <row r="6">
@@ -46620,28 +50072,28 @@
         </is>
       </c>
       <c r="B6" s="0">
+        <v>17</v>
+      </c>
+      <c r="C6" s="0">
+        <v>170</v>
+      </c>
+      <c r="D6" s="0">
+        <v>43</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0.2529411764705882</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.45</v>
+      </c>
+      <c r="G6" s="0">
+        <v>0.5620915032679739</v>
+      </c>
+      <c r="H6" s="0">
         <v>16</v>
       </c>
-      <c r="C6" s="0">
-        <v>160</v>
-      </c>
-      <c r="D6" s="0">
-        <v>38</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0.2375</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0.17857142857142858</v>
-      </c>
-      <c r="G6" s="0">
-        <v>1.3299999999999998</v>
-      </c>
-      <c r="H6" s="0">
-        <v>15</v>
-      </c>
       <c r="I6" s="4">
-        <v>0.9375</v>
+        <v>0.9411764705882353</v>
       </c>
     </row>
     <row r="7">

--- a/docs/downloads/latest.xlsx
+++ b/docs/downloads/latest.xlsx
@@ -93,7 +93,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L735"/>
+  <dimension ref="A1:L768"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -39739,13 +39739,1795 @@
         </is>
       </c>
     </row>
+    <row r="736">
+      <c r="A736" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B736" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C736" s="0">
+        <v>1</v>
+      </c>
+      <c r="D736" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603138</t>
+        </is>
+      </c>
+      <c r="E736" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">海量数据</t>
+        </is>
+      </c>
+      <c r="F736" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="G736" s="4">
+        <v>0.10032362459546927</v>
+      </c>
+      <c r="H736" s="4">
+        <v>0.21136860330600002</v>
+      </c>
+      <c r="I736" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J736" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 海量数据（603138）归入“数据库+智能体应用+定增注册”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K736" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 47 家涨停，其中首板 33 家、2板及以上 14 家。</t>
+        </is>
+      </c>
+      <c r="L736" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B737" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C737" s="0">
+        <v>2</v>
+      </c>
+      <c r="D737" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002086</t>
+        </is>
+      </c>
+      <c r="E737" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东方海洋</t>
+        </is>
+      </c>
+      <c r="F737" s="0">
+        <v>2.3</v>
+      </c>
+      <c r="G737" s="4">
+        <v>0.10047846889952151</v>
+      </c>
+      <c r="H737" s="4">
+        <v>0.17484223089925563</v>
+      </c>
+      <c r="I737" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J737" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 东方海洋（002086）归入“质谱诊断+体外诊断+海参养殖+“羊”字辈”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K737" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 47 家涨停，其中首板 33 家、2板及以上 14 家。</t>
+        </is>
+      </c>
+      <c r="L737" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B738" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C738" s="0">
+        <v>3</v>
+      </c>
+      <c r="D738" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600558</t>
+        </is>
+      </c>
+      <c r="E738" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大西洋</t>
+        </is>
+      </c>
+      <c r="F738" s="0">
+        <v>5.56</v>
+      </c>
+      <c r="G738" s="4">
+        <v>0.10099009900990087</v>
+      </c>
+      <c r="H738" s="4">
+        <v>0.1597778079514366</v>
+      </c>
+      <c r="I738" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J738" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 大西洋（600558）归入“高端焊材+核聚变焊材+航空航天+“羊”字辈”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K738" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.5 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 47 家涨停，其中首板 33 家、2板及以上 14 家。</t>
+        </is>
+      </c>
+      <c r="L738" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B739" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C739" s="0">
+        <v>4</v>
+      </c>
+      <c r="D739" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002696</t>
+        </is>
+      </c>
+      <c r="E739" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">百洋股份</t>
+        </is>
+      </c>
+      <c r="F739" s="0">
+        <v>11.28</v>
+      </c>
+      <c r="G739" s="4">
+        <v>0.10048780487804866</v>
+      </c>
+      <c r="H739" s="4">
+        <v>0.1565660335789215</v>
+      </c>
+      <c r="I739" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J739" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 百洋股份（002696）归入“水产加工+鱼粉鱼油+“羊”字辈”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K739" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.8 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 47 家涨停，其中首板 33 家、2板及以上 14 家。</t>
+        </is>
+      </c>
+      <c r="L739" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B740" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C740" s="0">
+        <v>5</v>
+      </c>
+      <c r="D740" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002869</t>
+        </is>
+      </c>
+      <c r="E740" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金溢科技</t>
+        </is>
+      </c>
+      <c r="F740" s="0">
+        <v>20.04</v>
+      </c>
+      <c r="G740" s="4">
+        <v>0.09989023051591663</v>
+      </c>
+      <c r="H740" s="4">
+        <v>0.1448393945901521</v>
+      </c>
+      <c r="I740" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J740" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 金溢科技（002869）归入“车路协同+智慧交通+机器人应用”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K740" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.4 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 47 家涨停，其中首板 33 家、2板及以上 14 家。</t>
+        </is>
+      </c>
+      <c r="L740" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B741" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C741" s="0">
+        <v>6</v>
+      </c>
+      <c r="D741" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603683</t>
+        </is>
+      </c>
+      <c r="E741" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晶华新材</t>
+        </is>
+      </c>
+      <c r="F741" s="0">
+        <v>17.16</v>
+      </c>
+      <c r="G741" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H741" s="4">
+        <v>0.1297255703289531</v>
+      </c>
+      <c r="I741" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J741" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 晶华新材（603683）归入“人形机器人+柔性传感+胶粘材料+股份回购”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K741" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.7 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 47 家涨停，其中首板 33 家、2板及以上 14 家。</t>
+        </is>
+      </c>
+      <c r="L741" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B742" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C742" s="0">
+        <v>7</v>
+      </c>
+      <c r="D742" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600826</t>
+        </is>
+      </c>
+      <c r="E742" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">兰生股份</t>
+        </is>
+      </c>
+      <c r="F742" s="0">
+        <v>8.22</v>
+      </c>
+      <c r="G742" s="4">
+        <v>0.10040160642570296</v>
+      </c>
+      <c r="H742" s="4">
+        <v>0.12959225203486155</v>
+      </c>
+      <c r="I742" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J742" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 兰生股份（600826）归入“机器人展区+AI科技+会展服务”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K742" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 47 家涨停，其中首板 33 家、2板及以上 14 家。</t>
+        </is>
+      </c>
+      <c r="L742" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B743" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C743" s="0">
+        <v>8</v>
+      </c>
+      <c r="D743" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603200</t>
+        </is>
+      </c>
+      <c r="E743" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上海洗霸</t>
+        </is>
+      </c>
+      <c r="F743" s="0">
+        <v>50.41</v>
+      </c>
+      <c r="G743" s="4">
+        <v>0.09993454069386853</v>
+      </c>
+      <c r="H743" s="4">
+        <v>0.12906163499695802</v>
+      </c>
+      <c r="I743" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J743" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 上海洗霸（603200）归入“固态电池+水处理+数据中心液冷”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K743" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 47 家涨停，其中首板 33 家、2板及以上 14 家。</t>
+        </is>
+      </c>
+      <c r="L743" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B744" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C744" s="0">
+        <v>9</v>
+      </c>
+      <c r="D744" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001318</t>
+        </is>
+      </c>
+      <c r="E744" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">阳光乳业</t>
+        </is>
+      </c>
+      <c r="F744" s="0">
+        <v>12.1</v>
+      </c>
+      <c r="G744" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H744" s="4">
+        <v>0.12872104253861616</v>
+      </c>
+      <c r="I744" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J744" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 阳光乳业（001318）归入“乳制品+南昌产业链+冷链配送”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K744" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 47 家涨停，其中首板 33 家、2板及以上 14 家。</t>
+        </is>
+      </c>
+      <c r="L744" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B745" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C745" s="0">
+        <v>10</v>
+      </c>
+      <c r="D745" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002178</t>
+        </is>
+      </c>
+      <c r="E745" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">延华智能</t>
+        </is>
+      </c>
+      <c r="F745" s="0">
+        <v>5.34</v>
+      </c>
+      <c r="G745" s="4">
+        <v>0.10103092783505163</v>
+      </c>
+      <c r="H745" s="4">
+        <v>0.1267668102675446</v>
+      </c>
+      <c r="I745" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J745" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 延华智能（002178）归入“AI医疗+智慧城市+医院智能化”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K745" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.8 倍，量能未出现极端放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 47 家涨停，其中首板 33 家、2板及以上 14 家。</t>
+        </is>
+      </c>
+      <c r="L745" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B746" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C746" s="0">
+        <v>11</v>
+      </c>
+      <c r="D746" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601900</t>
+        </is>
+      </c>
+      <c r="E746" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南方传媒</t>
+        </is>
+      </c>
+      <c r="F746" s="0">
+        <v>14.28</v>
+      </c>
+      <c r="G746" s="4">
+        <v>0.10015408320493059</v>
+      </c>
+      <c r="H746" s="4">
+        <v>0.11970638805964744</v>
+      </c>
+      <c r="I746" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J746" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 南方传媒（601900）归入“三季报增长+出版发行+AI教育+AI影视”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K746" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 47 家涨停，其中首板 33 家、2板及以上 14 家。</t>
+        </is>
+      </c>
+      <c r="L746" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B747" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C747" s="0">
+        <v>12</v>
+      </c>
+      <c r="D747" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002093</t>
+        </is>
+      </c>
+      <c r="E747" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">国脉科技</t>
+        </is>
+      </c>
+      <c r="F747" s="0">
+        <v>7.21</v>
+      </c>
+      <c r="G747" s="4">
+        <v>0.10076335877862608</v>
+      </c>
+      <c r="H747" s="4">
+        <v>0.11887149943691412</v>
+      </c>
+      <c r="I747" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J747" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 国脉科技（002093）归入“AI应用+通信服务+养老AI+身联网”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K747" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，量能未出现极端放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 47 家涨停，其中首板 33 家、2板及以上 14 家。</t>
+        </is>
+      </c>
+      <c r="L747" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B748" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C748" s="0">
+        <v>13</v>
+      </c>
+      <c r="D748" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603258</t>
+        </is>
+      </c>
+      <c r="E748" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">电魂网络</t>
+        </is>
+      </c>
+      <c r="F748" s="0">
+        <v>15.3</v>
+      </c>
+      <c r="G748" s="4">
+        <v>0.09992810927390373</v>
+      </c>
+      <c r="H748" s="4">
+        <v>0.11695628972129726</v>
+      </c>
+      <c r="I748" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J748" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 电魂网络（603258）归入“AI游戏+游戏研运+IP衍生”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K748" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.5 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 47 家涨停，其中首板 33 家、2板及以上 14 家。</t>
+        </is>
+      </c>
+      <c r="L748" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B749" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C749" s="0">
+        <v>14</v>
+      </c>
+      <c r="D749" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002820</t>
+        </is>
+      </c>
+      <c r="E749" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">桂发祥</t>
+        </is>
+      </c>
+      <c r="F749" s="0">
+        <v>10.19</v>
+      </c>
+      <c r="G749" s="4">
+        <v>0.10043196544276455</v>
+      </c>
+      <c r="H749" s="4">
+        <v>0.11454485103628749</v>
+      </c>
+      <c r="I749" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J749" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 桂发祥（002820）归入“休闲食品+非遗麻花+休闲新品”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K749" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.8 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 47 家涨停，其中首板 33 家、2板及以上 14 家。</t>
+        </is>
+      </c>
+      <c r="L749" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B750" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C750" s="0">
+        <v>15</v>
+      </c>
+      <c r="D750" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000995</t>
+        </is>
+      </c>
+      <c r="E750" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">皇台酒业</t>
+        </is>
+      </c>
+      <c r="F750" s="0">
+        <v>13.37</v>
+      </c>
+      <c r="G750" s="4">
+        <v>0.10041152263374474</v>
+      </c>
+      <c r="H750" s="4">
+        <v>0.11248942238784138</v>
+      </c>
+      <c r="I750" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J750" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 皇台酒业（000995）归入“白酒+老窖池+葡萄酒”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K750" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 47 家涨停，其中首板 33 家、2板及以上 14 家。</t>
+        </is>
+      </c>
+      <c r="L750" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B751" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C751" s="0">
+        <v>16</v>
+      </c>
+      <c r="D751" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603716</t>
+        </is>
+      </c>
+      <c r="E751" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">塞力医疗</t>
+        </is>
+      </c>
+      <c r="F751" s="0">
+        <v>16.06</v>
+      </c>
+      <c r="G751" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H751" s="4">
+        <v>0.11100964675722115</v>
+      </c>
+      <c r="I751" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J751" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 塞力医疗（603716）归入“高血压疫苗+AI诊断+医疗SPD”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K751" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 47 家涨停，其中首板 33 家、2板及以上 14 家。</t>
+        </is>
+      </c>
+      <c r="L751" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B752" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C752" s="0">
+        <v>17</v>
+      </c>
+      <c r="D752" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603657</t>
+        </is>
+      </c>
+      <c r="E752" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">春光科技</t>
+        </is>
+      </c>
+      <c r="F752" s="0">
+        <v>33.88</v>
+      </c>
+      <c r="G752" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H752" s="4">
+        <v>0.1107901567453505</v>
+      </c>
+      <c r="I752" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J752" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 春光科技（603657）归入“家庭机器人+清洁电器+品牌客户”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K752" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，量能未出现极端放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 47 家涨停，其中首板 33 家、2板及以上 14 家。</t>
+        </is>
+      </c>
+      <c r="L752" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B753" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C753" s="0">
+        <v>18</v>
+      </c>
+      <c r="D753" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001317</t>
+        </is>
+      </c>
+      <c r="E753" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">三羊马</t>
+        </is>
+      </c>
+      <c r="F753" s="0">
+        <v>53.68</v>
+      </c>
+      <c r="G753" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H753" s="4">
+        <v>0.11029124696330683</v>
+      </c>
+      <c r="I753" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J753" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 三羊马（001317）归入““羊”字辈+汽车物流+多式联运”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K753" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 47 家涨停，其中首板 33 家、2板及以上 14 家。</t>
+        </is>
+      </c>
+      <c r="L753" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B754" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C754" s="0">
+        <v>19</v>
+      </c>
+      <c r="D754" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002095</t>
+        </is>
+      </c>
+      <c r="E754" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">生 意 宝</t>
+        </is>
+      </c>
+      <c r="F754" s="0">
+        <v>16.48</v>
+      </c>
+      <c r="G754" s="4">
+        <v>0.1001335113484647</v>
+      </c>
+      <c r="H754" s="4">
+        <v>0.10271043050473161</v>
+      </c>
+      <c r="I754" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J754" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 生 意 宝（002095）归入“大宗电商+商品数据+AI应用”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K754" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 47 家涨停，其中首板 33 家、2板及以上 14 家。</t>
+        </is>
+      </c>
+      <c r="L754" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B755" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C755" s="0">
+        <v>20</v>
+      </c>
+      <c r="D755" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002708</t>
+        </is>
+      </c>
+      <c r="E755" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">光洋股份</t>
+        </is>
+      </c>
+      <c r="F755" s="0">
+        <v>15.65</v>
+      </c>
+      <c r="G755" s="4">
+        <v>0.09978917779339413</v>
+      </c>
+      <c r="H755" s="4">
+        <v>0.10177855907022217</v>
+      </c>
+      <c r="I755" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J755" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 光洋股份（002708）归入“人形机器人+PCB+汽车零部件”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K755" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.4 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 47 家涨停，其中首板 33 家、2板及以上 14 家。</t>
+        </is>
+      </c>
+      <c r="L755" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B756" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C756" s="0">
+        <v>21</v>
+      </c>
+      <c r="D756" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600980</t>
+        </is>
+      </c>
+      <c r="E756" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">北矿科技</t>
+        </is>
+      </c>
+      <c r="F756" s="0">
+        <v>18.95</v>
+      </c>
+      <c r="G756" s="4">
+        <v>0.09982588508415556</v>
+      </c>
+      <c r="H756" s="4">
+        <v>0.10159438470732392</v>
+      </c>
+      <c r="I756" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J756" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 北矿科技（600980）归入“矿冶机器人+三季报增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K756" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.8 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 47 家涨停，其中首板 33 家、2板及以上 14 家。</t>
+        </is>
+      </c>
+      <c r="L756" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B757" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C757" s="0">
+        <v>22</v>
+      </c>
+      <c r="D757" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603955</t>
+        </is>
+      </c>
+      <c r="E757" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大千生态</t>
+        </is>
+      </c>
+      <c r="F757" s="0">
+        <v>27.05</v>
+      </c>
+      <c r="G757" s="4">
+        <v>0.10004066693777958</v>
+      </c>
+      <c r="H757" s="4">
+        <v>0.1015003274479558</v>
+      </c>
+      <c r="I757" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J757" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 大千生态（603955）归入“羽毛球机器人+宠物服务”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K757" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.2 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 47 家涨停，其中首板 33 家、2板及以上 14 家。</t>
+        </is>
+      </c>
+      <c r="L757" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B758" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C758" s="0">
+        <v>23</v>
+      </c>
+      <c r="D758" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001331</t>
+        </is>
+      </c>
+      <c r="E758" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">胜通能源</t>
+        </is>
+      </c>
+      <c r="F758" s="0">
+        <v>35.02</v>
+      </c>
+      <c r="G758" s="4">
+        <v>0.09987437185929648</v>
+      </c>
+      <c r="H758" s="4">
+        <v>0.09812824626482379</v>
+      </c>
+      <c r="I758" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J758" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 胜通能源（001331）归入“机器人产业链+LNG运贸”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K758" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 47 家涨停，其中首板 33 家、2板及以上 14 家。</t>
+        </is>
+      </c>
+      <c r="L758" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B759" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C759" s="0">
+        <v>24</v>
+      </c>
+      <c r="D759" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605333</t>
+        </is>
+      </c>
+      <c r="E759" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">沪光股份</t>
+        </is>
+      </c>
+      <c r="F759" s="0">
+        <v>18.1</v>
+      </c>
+      <c r="G759" s="4">
+        <v>0.10030395136778125</v>
+      </c>
+      <c r="H759" s="4">
+        <v>0.09779824929644043</v>
+      </c>
+      <c r="I759" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J759" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 沪光股份（605333）归入“机器人线束+理想汽车+汽车线束”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K759" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.4 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 47 家涨停，其中首板 33 家、2板及以上 14 家。</t>
+        </is>
+      </c>
+      <c r="L759" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B760" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C760" s="0">
+        <v>25</v>
+      </c>
+      <c r="D760" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002795</t>
+        </is>
+      </c>
+      <c r="E760" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">永和智控</t>
+        </is>
+      </c>
+      <c r="F760" s="0">
+        <v>6.9</v>
+      </c>
+      <c r="G760" s="4">
+        <v>0.10047846889952172</v>
+      </c>
+      <c r="H760" s="4">
+        <v>0.09606494134514676</v>
+      </c>
+      <c r="I760" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J760" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 永和智控（002795）归入“水暖阀门+肿瘤放疗+资产出售”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K760" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 47 家涨停，其中首板 33 家、2板及以上 14 家。</t>
+        </is>
+      </c>
+      <c r="L760" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B761" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C761" s="0">
+        <v>26</v>
+      </c>
+      <c r="D761" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000635</t>
+        </is>
+      </c>
+      <c r="E761" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">英 力 特</t>
+        </is>
+      </c>
+      <c r="F761" s="0">
+        <v>8.02</v>
+      </c>
+      <c r="G761" s="4">
+        <v>0.10013717421124824</v>
+      </c>
+      <c r="H761" s="4">
+        <v>0.09527458168696759</v>
+      </c>
+      <c r="I761" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J761" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 英 力 特（000635）归入“控制权变更+氯碱化工+热电协同”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K761" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 47 家涨停，其中首板 33 家、2板及以上 14 家。</t>
+        </is>
+      </c>
+      <c r="L761" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B762" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C762" s="0">
+        <v>27</v>
+      </c>
+      <c r="D762" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001219</t>
+        </is>
+      </c>
+      <c r="E762" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">青岛食品</t>
+        </is>
+      </c>
+      <c r="F762" s="0">
+        <v>13.62</v>
+      </c>
+      <c r="G762" s="4">
+        <v>0.10016155088852985</v>
+      </c>
+      <c r="H762" s="4">
+        <v>0.09459506188237386</v>
+      </c>
+      <c r="I762" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J762" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 青岛食品（001219）归入“饼干食品+三季报增长+渠道拓展”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K762" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.5 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 47 家涨停，其中首板 33 家、2板及以上 14 家。</t>
+        </is>
+      </c>
+      <c r="L762" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B763" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C763" s="0">
+        <v>28</v>
+      </c>
+      <c r="D763" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001225</t>
+        </is>
+      </c>
+      <c r="E763" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">和泰机电</t>
+        </is>
+      </c>
+      <c r="F763" s="0">
+        <v>31.08</v>
+      </c>
+      <c r="G763" s="4">
+        <v>0.10017699115044243</v>
+      </c>
+      <c r="H763" s="4">
+        <v>0.09234515150385195</v>
+      </c>
+      <c r="I763" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J763" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 和泰机电（001225）归入“物料输送设备+海外拓展+输送链”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K763" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 47 家涨停，其中首板 33 家、2板及以上 14 家。</t>
+        </is>
+      </c>
+      <c r="L763" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B764" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C764" s="0">
+        <v>29</v>
+      </c>
+      <c r="D764" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002578</t>
+        </is>
+      </c>
+      <c r="E764" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">闽发铝业</t>
+        </is>
+      </c>
+      <c r="F764" s="0">
+        <v>3.6</v>
+      </c>
+      <c r="G764" s="4">
+        <v>0.10091743119266061</v>
+      </c>
+      <c r="H764" s="4">
+        <v>0.09027139078976171</v>
+      </c>
+      <c r="I764" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J764" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 闽发铝业（002578）归入“机器人布局+液冷铝材+工业铝型材”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K764" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.0 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 47 家涨停，其中首板 33 家、2板及以上 14 家。</t>
+        </is>
+      </c>
+      <c r="L764" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B765" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C765" s="0">
+        <v>30</v>
+      </c>
+      <c r="D765" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000411</t>
+        </is>
+      </c>
+      <c r="E765" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">英特集团</t>
+        </is>
+      </c>
+      <c r="F765" s="0">
+        <v>10.52</v>
+      </c>
+      <c r="G765" s="4">
+        <v>0.10041841004184082</v>
+      </c>
+      <c r="H765" s="4">
+        <v>0.0845898930807266</v>
+      </c>
+      <c r="I765" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J765" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 英特集团（000411）归入“三季报单季增长+医药流通+医药物流”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K765" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.3 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 47 家涨停，其中首板 33 家、2板及以上 14 家。</t>
+        </is>
+      </c>
+      <c r="L765" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B766" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C766" s="0">
+        <v>31</v>
+      </c>
+      <c r="D766" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600822</t>
+        </is>
+      </c>
+      <c r="E766" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上海物贸</t>
+        </is>
+      </c>
+      <c r="F766" s="0">
+        <v>9.37</v>
+      </c>
+      <c r="G766" s="4">
+        <v>0.0997652582159625</v>
+      </c>
+      <c r="H766" s="4">
+        <v>0.0820334141327618</v>
+      </c>
+      <c r="I766" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J766" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 上海物贸（600822）归入“数据要素+汽车贸易+黑色金属供应链”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K766" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.9 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 47 家涨停，其中首板 33 家、2板及以上 14 家。</t>
+        </is>
+      </c>
+      <c r="L766" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B767" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C767" s="0">
+        <v>32</v>
+      </c>
+      <c r="D767" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603719</t>
+        </is>
+      </c>
+      <c r="E767" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">良品铺子</t>
+        </is>
+      </c>
+      <c r="F767" s="0">
+        <v>9.39</v>
+      </c>
+      <c r="G767" s="4">
+        <v>0.09953161592505877</v>
+      </c>
+      <c r="H767" s="4">
+        <v>0.0760865065525716</v>
+      </c>
+      <c r="I767" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J767" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 良品铺子（603719）归入“休闲食品+一品一链+业绩扭亏”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K767" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.5 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 47 家涨停，其中首板 33 家、2板及以上 14 家。</t>
+        </is>
+      </c>
+      <c r="L767" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B768" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C768" s="0">
+        <v>33</v>
+      </c>
+      <c r="D768" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603331</t>
+        </is>
+      </c>
+      <c r="E768" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">百达精工</t>
+        </is>
+      </c>
+      <c r="F768" s="0">
+        <v>12.91</v>
+      </c>
+      <c r="G768" s="4">
+        <v>0.09965928449744466</v>
+      </c>
+      <c r="H768" s="4">
+        <v>0.06644401815926189</v>
+      </c>
+      <c r="I768" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J768" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 百达精工（603331）归入“人形机器人+银河通用+汽车零部件”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K768" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 6.3 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 47 家涨停，其中首板 33 家、2板及以上 14 家。</t>
+        </is>
+      </c>
+      <c r="L768" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M173"/>
+  <dimension ref="A1:M183"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -49888,6 +51670,596 @@
       <c r="M173" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">8.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B174" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C174" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D174" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002982</t>
+        </is>
+      </c>
+      <c r="E174" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湘佳股份</t>
+        </is>
+      </c>
+      <c r="F174" s="4">
+        <v>0.26866405270242955</v>
+      </c>
+      <c r="G174" s="4">
+        <v>0.04593373493975905</v>
+      </c>
+      <c r="H174" s="4">
+        <v>0.0918674698795181</v>
+      </c>
+      <c r="I174" s="4">
+        <v>0.01957831325301207</v>
+      </c>
+      <c r="J174" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K174" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +1.96%</t>
+        </is>
+      </c>
+      <c r="L174" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M174" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13.54</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B175" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C175" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D175" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603341</t>
+        </is>
+      </c>
+      <c r="E175" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">龙旗科技</t>
+        </is>
+      </c>
+      <c r="F175" s="4">
+        <v>0.13483459223852917</v>
+      </c>
+      <c r="G175" s="4">
+        <v>-0.03035795197100144</v>
+      </c>
+      <c r="H175" s="4">
+        <v>-0.01925690983235162</v>
+      </c>
+      <c r="I175" s="4">
+        <v>-0.037154508382419626</v>
+      </c>
+      <c r="J175" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K175" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -3.72%</t>
+        </is>
+      </c>
+      <c r="L175" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M175" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B176" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C176" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="D176" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603466</t>
+        </is>
+      </c>
+      <c r="E176" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">风语筑</t>
+        </is>
+      </c>
+      <c r="F176" s="4">
+        <v>0.12777766137320726</v>
+      </c>
+      <c r="G176" s="4">
+        <v>0.060585432266848205</v>
+      </c>
+      <c r="H176" s="4">
+        <v>0.08781484002722939</v>
+      </c>
+      <c r="I176" s="4">
+        <v>0.002722940776038074</v>
+      </c>
+      <c r="J176" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K176" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +0.27%</t>
+        </is>
+      </c>
+      <c r="L176" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M176" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B177" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C177" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="D177" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603626</t>
+        </is>
+      </c>
+      <c r="E177" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">科森科技</t>
+        </is>
+      </c>
+      <c r="F177" s="4">
+        <v>0.12516529392280473</v>
+      </c>
+      <c r="G177" s="4">
+        <v>-0.03167420814479638</v>
+      </c>
+      <c r="H177" s="4">
+        <v>0.010558069381598756</v>
+      </c>
+      <c r="I177" s="4">
+        <v>-0.02262443438914019</v>
+      </c>
+      <c r="J177" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K177" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -2.26%</t>
+        </is>
+      </c>
+      <c r="L177" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M177" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B178" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C178" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="D178" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001216</t>
+        </is>
+      </c>
+      <c r="E178" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华瓷股份</t>
+        </is>
+      </c>
+      <c r="F178" s="4">
+        <v>0.12470748338467871</v>
+      </c>
+      <c r="G178" s="4">
+        <v>-0.02204836415362732</v>
+      </c>
+      <c r="H178" s="4">
+        <v>-0.016002844950213313</v>
+      </c>
+      <c r="I178" s="4">
+        <v>-0.09992887624466584</v>
+      </c>
+      <c r="J178" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K178" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -9.99%</t>
+        </is>
+      </c>
+      <c r="L178" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M178" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B179" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C179" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="D179" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002343</t>
+        </is>
+      </c>
+      <c r="E179" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">慈文传媒</t>
+        </is>
+      </c>
+      <c r="F179" s="4">
+        <v>0.1246153603546378</v>
+      </c>
+      <c r="G179" s="4">
+        <v>-0.0560146923783289</v>
+      </c>
+      <c r="H179" s="4">
+        <v>-0.04040404040404055</v>
+      </c>
+      <c r="I179" s="4">
+        <v>-0.10009182736455458</v>
+      </c>
+      <c r="J179" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K179" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -10.01%</t>
+        </is>
+      </c>
+      <c r="L179" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M179" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B180" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C180" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="D180" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603337</t>
+        </is>
+      </c>
+      <c r="E180" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">杰克科技</t>
+        </is>
+      </c>
+      <c r="F180" s="4">
+        <v>0.12360592364964289</v>
+      </c>
+      <c r="G180" s="4">
+        <v>0.09984717269485488</v>
+      </c>
+      <c r="H180" s="4">
+        <v>0.10010188487009675</v>
+      </c>
+      <c r="I180" s="4">
+        <v>0.10010188487009675</v>
+      </c>
+      <c r="J180" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K180" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +10.01%</t>
+        </is>
+      </c>
+      <c r="L180" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M180" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">43.19</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B181" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C181" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="D181" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600303</t>
+        </is>
+      </c>
+      <c r="E181" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">曙光股份</t>
+        </is>
+      </c>
+      <c r="F181" s="4">
+        <v>0.11950056052158037</v>
+      </c>
+      <c r="G181" s="4">
+        <v>-0.01273885350318471</v>
+      </c>
+      <c r="H181" s="4">
+        <v>0.0031847133757960666</v>
+      </c>
+      <c r="I181" s="4">
+        <v>-0.0987261146496815</v>
+      </c>
+      <c r="J181" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K181" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -9.87%</t>
+        </is>
+      </c>
+      <c r="L181" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M181" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B182" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C182" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="D182" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603721</t>
+        </is>
+      </c>
+      <c r="E182" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中广天择</t>
+        </is>
+      </c>
+      <c r="F182" s="4">
+        <v>0.11609531002906623</v>
+      </c>
+      <c r="G182" s="4">
+        <v>0.05558107487367936</v>
+      </c>
+      <c r="H182" s="4">
+        <v>0.10013780431786867</v>
+      </c>
+      <c r="I182" s="4">
+        <v>-0.0078089113458887915</v>
+      </c>
+      <c r="J182" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K182" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -0.78%</t>
+        </is>
+      </c>
+      <c r="L182" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M182" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="B183" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-26</t>
+        </is>
+      </c>
+      <c r="C183" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="D183" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603081</t>
+        </is>
+      </c>
+      <c r="E183" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大丰实业</t>
+        </is>
+      </c>
+      <c r="F183" s="4">
+        <v>0.11503060190142221</v>
+      </c>
+      <c r="G183" s="4">
+        <v>0.10046948356807506</v>
+      </c>
+      <c r="H183" s="4">
+        <v>0.10046948356807506</v>
+      </c>
+      <c r="I183" s="4">
+        <v>0.06103286384976525</v>
+      </c>
+      <c r="J183" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K183" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +6.10%</t>
+        </is>
+      </c>
+      <c r="L183" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M183" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.3</t>
         </is>
       </c>
     </row>
@@ -49979,28 +52351,28 @@
         </is>
       </c>
       <c r="B3" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" s="0">
         <v>7</v>
       </c>
       <c r="E3" s="4">
-        <v>0.4117647058823529</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="F3" s="4">
-        <v>0.45</v>
+        <v>0.1509433962264151</v>
       </c>
       <c r="G3" s="0">
-        <v>0.9150326797385621</v>
+        <v>2.576388888888889</v>
       </c>
       <c r="H3" s="0">
         <v>7</v>
       </c>
       <c r="I3" s="4">
-        <v>0.4117647058823529</v>
+        <v>0.3888888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -50010,28 +52382,28 @@
         </is>
       </c>
       <c r="B4" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" s="0">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D4" s="0">
         <v>15</v>
       </c>
       <c r="E4" s="4">
-        <v>0.29411764705882354</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="F4" s="4">
-        <v>0.45</v>
+        <v>0.1509433962264151</v>
       </c>
       <c r="G4" s="0">
-        <v>0.6535947712418301</v>
+        <v>1.840277777777778</v>
       </c>
       <c r="H4" s="0">
         <v>10</v>
       </c>
       <c r="I4" s="4">
-        <v>0.5882352941176471</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="5">
@@ -50041,28 +52413,28 @@
         </is>
       </c>
       <c r="B5" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" s="0">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D5" s="0">
         <v>28</v>
       </c>
       <c r="E5" s="4">
-        <v>0.27450980392156865</v>
+        <v>0.25925925925925924</v>
       </c>
       <c r="F5" s="4">
-        <v>0.45</v>
+        <v>0.1509433962264151</v>
       </c>
       <c r="G5" s="0">
-        <v>0.6100217864923748</v>
+        <v>1.7175925925925926</v>
       </c>
       <c r="H5" s="0">
         <v>13</v>
       </c>
       <c r="I5" s="4">
-        <v>0.7647058823529411</v>
+        <v>0.7222222222222222</v>
       </c>
     </row>
     <row r="6">
@@ -50072,28 +52444,28 @@
         </is>
       </c>
       <c r="B6" s="0">
+        <v>18</v>
+      </c>
+      <c r="C6" s="0">
+        <v>180</v>
+      </c>
+      <c r="D6" s="0">
+        <v>44</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0.24444444444444444</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.1509433962264151</v>
+      </c>
+      <c r="G6" s="0">
+        <v>1.6194444444444445</v>
+      </c>
+      <c r="H6" s="0">
         <v>17</v>
       </c>
-      <c r="C6" s="0">
-        <v>170</v>
-      </c>
-      <c r="D6" s="0">
-        <v>43</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0.2529411764705882</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0.45</v>
-      </c>
-      <c r="G6" s="0">
-        <v>0.5620915032679739</v>
-      </c>
-      <c r="H6" s="0">
-        <v>16</v>
-      </c>
       <c r="I6" s="4">
-        <v>0.9411764705882353</v>
+        <v>0.9444444444444444</v>
       </c>
     </row>
     <row r="7">

--- a/docs/downloads/latest.xlsx
+++ b/docs/downloads/latest.xlsx
@@ -93,7 +93,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L768"/>
+  <dimension ref="A1:L794"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -41521,13 +41521,1417 @@
         </is>
       </c>
     </row>
+    <row r="769">
+      <c r="A769" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B769" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C769" s="0">
+        <v>1</v>
+      </c>
+      <c r="D769" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000058</t>
+        </is>
+      </c>
+      <c r="E769" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">深 赛 格</t>
+        </is>
+      </c>
+      <c r="F769" s="0">
+        <v>7.87</v>
+      </c>
+      <c r="G769" s="4">
+        <v>0.10069930069930066</v>
+      </c>
+      <c r="H769" s="4">
+        <v>0.36780440226879885</v>
+      </c>
+      <c r="I769" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J769" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 深 赛 格（000058）归入“布局半导体检测+罗山基地+检验检测+电子市场”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K769" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 10.1%）。截至运行时成交量约为20日均量的 0.5 倍，量能未出现极端放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 38 家涨停，其中首板 26 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L769" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B770" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C770" s="0">
+        <v>2</v>
+      </c>
+      <c r="D770" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002011</t>
+        </is>
+      </c>
+      <c r="E770" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">盾安环境</t>
+        </is>
+      </c>
+      <c r="F770" s="0">
+        <v>11.37</v>
+      </c>
+      <c r="G770" s="4">
+        <v>0.099613152804642</v>
+      </c>
+      <c r="H770" s="4">
+        <v>0.24538257026484128</v>
+      </c>
+      <c r="I770" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J770" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 盾安环境（002011）归入“三季报增长+数据中心温控+半导体温控+汽车热管理”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K770" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 8.6%）。截至运行时成交量约为20日均量的 0.8 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 38 家涨停，其中首板 26 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L770" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B771" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C771" s="0">
+        <v>3</v>
+      </c>
+      <c r="D771" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002724</t>
+        </is>
+      </c>
+      <c r="E771" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">海洋王</t>
+        </is>
+      </c>
+      <c r="F771" s="0">
+        <v>13.09</v>
+      </c>
+      <c r="G771" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H771" s="4">
+        <v>0.1601691132452417</v>
+      </c>
+      <c r="I771" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J771" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 海洋王（002724）归入“三季报增长+专业照明+AI智慧照明+“羊”字辈”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K771" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.8 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 38 家涨停，其中首板 26 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L771" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；近5日涨幅偏高，短线获利盘压力更大；近10日涨幅偏高</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B772" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C772" s="0">
+        <v>4</v>
+      </c>
+      <c r="D772" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002249</t>
+        </is>
+      </c>
+      <c r="E772" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大洋电机</t>
+        </is>
+      </c>
+      <c r="F772" s="0">
+        <v>7.7</v>
+      </c>
+      <c r="G772" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H772" s="4">
+        <v>0.12748515196083518</v>
+      </c>
+      <c r="I772" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J772" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 大洋电机（002249）归入“机器人关节+电机业务+数据中心风机+“羊”字辈”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K772" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.3 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 38 家涨停，其中首板 26 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L772" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B773" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C773" s="0">
+        <v>5</v>
+      </c>
+      <c r="D773" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601566</t>
+        </is>
+      </c>
+      <c r="E773" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">九牧王</t>
+        </is>
+      </c>
+      <c r="F773" s="0">
+        <v>10.32</v>
+      </c>
+      <c r="G773" s="4">
+        <v>0.10021321961620465</v>
+      </c>
+      <c r="H773" s="4">
+        <v>0.12298825069422419</v>
+      </c>
+      <c r="I773" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J773" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 九牧王（601566）归入“羊毛羊绒+男裤+太空裤+海峡两岸”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K773" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 38 家涨停，其中首板 26 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L773" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B774" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C774" s="0">
+        <v>6</v>
+      </c>
+      <c r="D774" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600715</t>
+        </is>
+      </c>
+      <c r="E774" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文投控股</t>
+        </is>
+      </c>
+      <c r="F774" s="0">
+        <v>1.87</v>
+      </c>
+      <c r="G774" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H774" s="4">
+        <v>0.11467916778520654</v>
+      </c>
+      <c r="I774" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J774" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 文投控股（600715）归入“AI漫剧+游戏运营+影院运营”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K774" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.9 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 38 家涨停，其中首板 26 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L774" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B775" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C775" s="0">
+        <v>7</v>
+      </c>
+      <c r="D775" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001400</t>
+        </is>
+      </c>
+      <c r="E775" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">江顺科技</t>
+        </is>
+      </c>
+      <c r="F775" s="0">
+        <v>80.28</v>
+      </c>
+      <c r="G775" s="4">
+        <v>0.10002740476842975</v>
+      </c>
+      <c r="H775" s="4">
+        <v>0.11278706724186846</v>
+      </c>
+      <c r="I775" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J775" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 江顺科技（001400）归入“3D打印+液冷+商业航天+铝挤压模具”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K775" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.6 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 38 家涨停，其中首板 26 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L775" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B776" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C776" s="0">
+        <v>8</v>
+      </c>
+      <c r="D776" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600785</t>
+        </is>
+      </c>
+      <c r="E776" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新华百货</t>
+        </is>
+      </c>
+      <c r="F776" s="0">
+        <v>13.9</v>
+      </c>
+      <c r="G776" s="4">
+        <v>0.09968354430379754</v>
+      </c>
+      <c r="H776" s="4">
+        <v>0.1098932170248941</v>
+      </c>
+      <c r="I776" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J776" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 新华百货（600785）归入“零售促销+股份回购+硬折扣”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K776" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 38 家涨停，其中首板 26 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L776" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B777" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C777" s="0">
+        <v>9</v>
+      </c>
+      <c r="D777" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603565</t>
+        </is>
+      </c>
+      <c r="E777" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中谷物流</t>
+        </is>
+      </c>
+      <c r="F777" s="0">
+        <v>12.58</v>
+      </c>
+      <c r="G777" s="4">
+        <v>0.09965034965034981</v>
+      </c>
+      <c r="H777" s="4">
+        <v>0.10185336549614955</v>
+      </c>
+      <c r="I777" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J777" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 中谷物流（603565）归入“三季报增长+股权激励+集装箱物流”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K777" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 38 家涨停，其中首板 26 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L777" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B778" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C778" s="0">
+        <v>10</v>
+      </c>
+      <c r="D778" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603037</t>
+        </is>
+      </c>
+      <c r="E778" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">凯众股份</t>
+        </is>
+      </c>
+      <c r="F778" s="0">
+        <v>11.87</v>
+      </c>
+      <c r="G778" s="4">
+        <v>0.1000926784059315</v>
+      </c>
+      <c r="H778" s="4">
+        <v>0.09852707452562856</v>
+      </c>
+      <c r="I778" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J778" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 凯众股份（603037）归入“机器人零部件+汽车减震+拟收购拓盛”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K778" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.6 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 38 家涨停，其中首板 26 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L778" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B779" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C779" s="0">
+        <v>11</v>
+      </c>
+      <c r="D779" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600828</t>
+        </is>
+      </c>
+      <c r="E779" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">茂业商业</t>
+        </is>
+      </c>
+      <c r="F779" s="0">
+        <v>4.47</v>
+      </c>
+      <c r="G779" s="4">
+        <v>0.10098522167487702</v>
+      </c>
+      <c r="H779" s="4">
+        <v>0.09643263406584941</v>
+      </c>
+      <c r="I779" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J779" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 茂业商业（600828）归入“百货零售+全渠道运营+自有物业”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K779" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 38 家涨停，其中首板 26 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L779" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B780" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C780" s="0">
+        <v>12</v>
+      </c>
+      <c r="D780" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603370</t>
+        </is>
+      </c>
+      <c r="E780" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华新精科</t>
+        </is>
+      </c>
+      <c r="F780" s="0">
+        <v>30.81</v>
+      </c>
+      <c r="G780" s="4">
+        <v>0.09996429846483391</v>
+      </c>
+      <c r="H780" s="4">
+        <v>0.09478824095338971</v>
+      </c>
+      <c r="I780" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J780" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 华新精科（603370）归入“人形机器人+关节电机铁芯+新能源车铁芯”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K780" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.3 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 38 家涨停，其中首板 26 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L780" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B781" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C781" s="0">
+        <v>13</v>
+      </c>
+      <c r="D781" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600865</t>
+        </is>
+      </c>
+      <c r="E781" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">百大集团</t>
+        </is>
+      </c>
+      <c r="F781" s="0">
+        <v>12.62</v>
+      </c>
+      <c r="G781" s="4">
+        <v>0.10026155187445497</v>
+      </c>
+      <c r="H781" s="4">
+        <v>0.0942646444631716</v>
+      </c>
+      <c r="I781" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no_verified_event</t>
+        </is>
+      </c>
+      <c r="J781" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">事件证据层未找到与当日涨停直接匹配的公告或新闻；系统不把概念标签、技术形态或主观猜测当成涨停原因。</t>
+        </is>
+      </c>
+      <c r="K781" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.8 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 38 家涨停，其中首板 26 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L781" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B782" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C782" s="0">
+        <v>14</v>
+      </c>
+      <c r="D782" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002623</t>
+        </is>
+      </c>
+      <c r="E782" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">亚玛顿</t>
+        </is>
+      </c>
+      <c r="F782" s="0">
+        <v>18.78</v>
+      </c>
+      <c r="G782" s="4">
+        <v>0.10017574692442889</v>
+      </c>
+      <c r="H782" s="4">
+        <v>0.08941175607825945</v>
+      </c>
+      <c r="I782" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J782" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 亚玛顿（002623）归入“玻璃基板+光伏玻璃+钙钛矿玻璃”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K782" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 38 家涨停，其中首板 26 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L782" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B783" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C783" s="0">
+        <v>15</v>
+      </c>
+      <c r="D783" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002205</t>
+        </is>
+      </c>
+      <c r="E783" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">国统股份</t>
+        </is>
+      </c>
+      <c r="F783" s="0">
+        <v>11.4</v>
+      </c>
+      <c r="G783" s="4">
+        <v>0.10038610038610042</v>
+      </c>
+      <c r="H783" s="4">
+        <v>0.08929591040778645</v>
+      </c>
+      <c r="I783" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J783" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 国统股份（002205）归入“PCCP管道+风电混塔+央企控股”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K783" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 38 家涨停，其中首板 26 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L783" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B784" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C784" s="0">
+        <v>16</v>
+      </c>
+      <c r="D784" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603758</t>
+        </is>
+      </c>
+      <c r="E784" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">秦安股份</t>
+        </is>
+      </c>
+      <c r="F784" s="0">
+        <v>10.73</v>
+      </c>
+      <c r="G784" s="4">
+        <v>0.10051282051282051</v>
+      </c>
+      <c r="H784" s="4">
+        <v>0.08714495934299193</v>
+      </c>
+      <c r="I784" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J784" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 秦安股份（603758）归入“柔性压力传感器+参投墨现科技+真空镀膜+汽车零部件”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K784" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 38 家涨停，其中首板 26 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L784" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B785" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C785" s="0">
+        <v>17</v>
+      </c>
+      <c r="D785" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002187</t>
+        </is>
+      </c>
+      <c r="E785" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">广百股份</t>
+        </is>
+      </c>
+      <c r="F785" s="0">
+        <v>5.92</v>
+      </c>
+      <c r="G785" s="4">
+        <v>0.1003717472118959</v>
+      </c>
+      <c r="H785" s="4">
+        <v>0.08496349585010778</v>
+      </c>
+      <c r="I785" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J785" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 广百股份（002187）归入“百货零售+免税退税+新零售业态”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K785" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.3 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 38 家涨停，其中首板 26 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L785" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B786" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C786" s="0">
+        <v>18</v>
+      </c>
+      <c r="D786" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601956</t>
+        </is>
+      </c>
+      <c r="E786" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东贝集团</t>
+        </is>
+      </c>
+      <c r="F786" s="0">
+        <v>5.54</v>
+      </c>
+      <c r="G786" s="4">
+        <v>0.0992063492063493</v>
+      </c>
+      <c r="H786" s="4">
+        <v>0.08431332569010228</v>
+      </c>
+      <c r="I786" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J786" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 东贝集团（601956）归入“汽车零部件+机器人电机+制冷压缩机”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K786" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 38 家涨停，其中首板 26 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L786" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B787" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C787" s="0">
+        <v>19</v>
+      </c>
+      <c r="D787" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002284</t>
+        </is>
+      </c>
+      <c r="E787" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">亚太股份</t>
+        </is>
+      </c>
+      <c r="F787" s="0">
+        <v>9.67</v>
+      </c>
+      <c r="G787" s="4">
+        <v>0.10011376564277598</v>
+      </c>
+      <c r="H787" s="4">
+        <v>0.08320833688261114</v>
+      </c>
+      <c r="I787" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J787" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 亚太股份（002284）归入“股权受让+业绩增长+汽车制动+机器人模组”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K787" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.4 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 38 家涨停，其中首板 26 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L787" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B788" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C788" s="0">
+        <v>20</v>
+      </c>
+      <c r="D788" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600303</t>
+        </is>
+      </c>
+      <c r="E788" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">曙光股份</t>
+        </is>
+      </c>
+      <c r="F788" s="0">
+        <v>3.11</v>
+      </c>
+      <c r="G788" s="4">
+        <v>0.09893992932862193</v>
+      </c>
+      <c r="H788" s="4">
+        <v>0.08225369528342659</v>
+      </c>
+      <c r="I788" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J788" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 曙光股份（600303）归入“汽车车桥+新能源客车+军用方舱”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K788" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.4 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 38 家涨停，其中首板 26 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L788" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B789" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C789" s="0">
+        <v>21</v>
+      </c>
+      <c r="D789" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601086</t>
+        </is>
+      </c>
+      <c r="E789" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">国芳集团</t>
+        </is>
+      </c>
+      <c r="F789" s="0">
+        <v>12.62</v>
+      </c>
+      <c r="G789" s="4">
+        <v>0.10026155187445497</v>
+      </c>
+      <c r="H789" s="4">
+        <v>0.07997850430996496</v>
+      </c>
+      <c r="I789" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J789" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 国芳集团（601086）归入“连锁零售+消费场景+区域优势”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K789" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.5 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 38 家涨停，其中首板 26 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L789" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B790" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C790" s="0">
+        <v>22</v>
+      </c>
+      <c r="D790" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002823</t>
+        </is>
+      </c>
+      <c r="E790" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">凯中精密</t>
+        </is>
+      </c>
+      <c r="F790" s="0">
+        <v>13.49</v>
+      </c>
+      <c r="G790" s="4">
+        <v>0.1003262642740621</v>
+      </c>
+      <c r="H790" s="4">
+        <v>0.07819916015239078</v>
+      </c>
+      <c r="I790" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J790" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 凯中精密（002823）归入“精密零组件+机器人布局+汽车连接器”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K790" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.6 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 38 家涨停，其中首板 26 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L790" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B791" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C791" s="0">
+        <v>23</v>
+      </c>
+      <c r="D791" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603813</t>
+        </is>
+      </c>
+      <c r="E791" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">原尚股份</t>
+        </is>
+      </c>
+      <c r="F791" s="0">
+        <v>24.2</v>
+      </c>
+      <c r="G791" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H791" s="4">
+        <v>0.07390580621990123</v>
+      </c>
+      <c r="I791" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J791" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 原尚股份（603813）归入“汽车物流+仓储资源”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K791" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.2 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 38 家涨停，其中首板 26 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L791" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B792" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C792" s="0">
+        <v>24</v>
+      </c>
+      <c r="D792" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000888</t>
+        </is>
+      </c>
+      <c r="E792" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">峨眉山Ａ</t>
+        </is>
+      </c>
+      <c r="F792" s="0">
+        <v>10.1</v>
+      </c>
+      <c r="G792" s="4">
+        <v>0.1002178649237473</v>
+      </c>
+      <c r="H792" s="4">
+        <v>0.07227267569418287</v>
+      </c>
+      <c r="I792" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J792" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 峨眉山Ａ（000888）归入“景区索道+文旅产业+冰雪旅游”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K792" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 6.1 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 38 家涨停，其中首板 26 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L792" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B793" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C793" s="0">
+        <v>25</v>
+      </c>
+      <c r="D793" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603376</t>
+        </is>
+      </c>
+      <c r="E793" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大明电子</t>
+        </is>
+      </c>
+      <c r="F793" s="0">
+        <v>26.3</v>
+      </c>
+      <c r="G793" s="4">
+        <v>0.09995817649519022</v>
+      </c>
+      <c r="H793" s="4">
+        <v>0.07054288964301864</v>
+      </c>
+      <c r="I793" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J793" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 大明电子（603376）归入“汽车电子+驾驶辅助+新能源车型”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K793" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 38 家涨停，其中首板 26 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L793" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B794" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C794" s="0">
+        <v>26</v>
+      </c>
+      <c r="D794" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600626</t>
+        </is>
+      </c>
+      <c r="E794" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">申达股份</t>
+        </is>
+      </c>
+      <c r="F794" s="0">
+        <v>3.94</v>
+      </c>
+      <c r="G794" s="4">
+        <v>0.1005586592178771</v>
+      </c>
+      <c r="H794" s="4">
+        <v>0.06945430348035994</v>
+      </c>
+      <c r="I794" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J794" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 申达股份（600626）归入“汽车内饰+整车配套+中报扭亏+上海国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K794" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.3 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 38 家涨停，其中首板 26 家、2板及以上 12 家。</t>
+        </is>
+      </c>
+      <c r="L794" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M183"/>
+  <dimension ref="A1:M193"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -52260,6 +53664,596 @@
       <c r="M183" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">11.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B184" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C184" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D184" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603138</t>
+        </is>
+      </c>
+      <c r="E184" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">海量数据</t>
+        </is>
+      </c>
+      <c r="F184" s="4">
+        <v>0.21136860330600002</v>
+      </c>
+      <c r="G184" s="4">
+        <v>-0.03529411764705892</v>
+      </c>
+      <c r="H184" s="4">
+        <v>0.08176470588235296</v>
+      </c>
+      <c r="I184" s="4">
+        <v>-0.017058823529411682</v>
+      </c>
+      <c r="J184" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K184" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -1.71%</t>
+        </is>
+      </c>
+      <c r="L184" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M184" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16.71</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B185" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C185" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D185" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002086</t>
+        </is>
+      </c>
+      <c r="E185" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东方海洋</t>
+        </is>
+      </c>
+      <c r="F185" s="4">
+        <v>0.17484223089925563</v>
+      </c>
+      <c r="G185" s="4">
+        <v>0.04782608695652191</v>
+      </c>
+      <c r="H185" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="I185" s="4">
+        <v>0.039130434782608914</v>
+      </c>
+      <c r="J185" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K185" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +3.91%</t>
+        </is>
+      </c>
+      <c r="L185" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M185" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B186" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C186" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="D186" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600558</t>
+        </is>
+      </c>
+      <c r="E186" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大西洋</t>
+        </is>
+      </c>
+      <c r="F186" s="4">
+        <v>0.1597778079514366</v>
+      </c>
+      <c r="G186" s="4">
+        <v>0.1007194244604317</v>
+      </c>
+      <c r="H186" s="4">
+        <v>0.1007194244604317</v>
+      </c>
+      <c r="I186" s="4">
+        <v>0.02877697841726623</v>
+      </c>
+      <c r="J186" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K186" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +2.88%</t>
+        </is>
+      </c>
+      <c r="L186" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M186" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.72</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B187" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C187" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="D187" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002696</t>
+        </is>
+      </c>
+      <c r="E187" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">百洋股份</t>
+        </is>
+      </c>
+      <c r="F187" s="4">
+        <v>0.1565660335789215</v>
+      </c>
+      <c r="G187" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H187" s="4">
+        <v>0.09929078014184411</v>
+      </c>
+      <c r="I187" s="4">
+        <v>-0.0514184397163121</v>
+      </c>
+      <c r="J187" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K187" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -5.14%</t>
+        </is>
+      </c>
+      <c r="L187" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M187" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B188" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C188" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="D188" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002869</t>
+        </is>
+      </c>
+      <c r="E188" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金溢科技</t>
+        </is>
+      </c>
+      <c r="F188" s="4">
+        <v>0.1448393945901521</v>
+      </c>
+      <c r="G188" s="4">
+        <v>-0.030439121756486998</v>
+      </c>
+      <c r="H188" s="4">
+        <v>0.022954091816367317</v>
+      </c>
+      <c r="I188" s="4">
+        <v>-0.09630738522954085</v>
+      </c>
+      <c r="J188" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K188" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -9.63%</t>
+        </is>
+      </c>
+      <c r="L188" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M188" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B189" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C189" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="D189" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603683</t>
+        </is>
+      </c>
+      <c r="E189" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晶华新材</t>
+        </is>
+      </c>
+      <c r="F189" s="4">
+        <v>0.1297255703289531</v>
+      </c>
+      <c r="G189" s="4">
+        <v>-0.004079254079254135</v>
+      </c>
+      <c r="H189" s="4">
+        <v>0.07517482517482521</v>
+      </c>
+      <c r="I189" s="4">
+        <v>0.00815850815850827</v>
+      </c>
+      <c r="J189" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K189" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +0.82%</t>
+        </is>
+      </c>
+      <c r="L189" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M189" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B190" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C190" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="D190" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600826</t>
+        </is>
+      </c>
+      <c r="E190" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">兰生股份</t>
+        </is>
+      </c>
+      <c r="F190" s="4">
+        <v>0.12959225203486155</v>
+      </c>
+      <c r="G190" s="4">
+        <v>0.09732360097323589</v>
+      </c>
+      <c r="H190" s="4">
+        <v>0.09975669099756668</v>
+      </c>
+      <c r="I190" s="4">
+        <v>0.09975669099756668</v>
+      </c>
+      <c r="J190" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K190" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +9.98%</t>
+        </is>
+      </c>
+      <c r="L190" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M190" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B191" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C191" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="D191" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603200</t>
+        </is>
+      </c>
+      <c r="E191" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上海洗霸</t>
+        </is>
+      </c>
+      <c r="F191" s="4">
+        <v>0.12906163499695802</v>
+      </c>
+      <c r="G191" s="4">
+        <v>-0.002578853402102621</v>
+      </c>
+      <c r="H191" s="4">
+        <v>0.06764530847054173</v>
+      </c>
+      <c r="I191" s="4">
+        <v>-0.0245982939892877</v>
+      </c>
+      <c r="J191" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K191" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -2.46%</t>
+        </is>
+      </c>
+      <c r="L191" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M191" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">49.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B192" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C192" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="D192" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001318</t>
+        </is>
+      </c>
+      <c r="E192" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">阳光乳业</t>
+        </is>
+      </c>
+      <c r="F192" s="4">
+        <v>0.12872104253861616</v>
+      </c>
+      <c r="G192" s="4">
+        <v>-0.018181818181818077</v>
+      </c>
+      <c r="H192" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="I192" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="J192" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K192" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +10.00%</t>
+        </is>
+      </c>
+      <c r="L192" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M192" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="B193" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-27</t>
+        </is>
+      </c>
+      <c r="C193" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="D193" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002178</t>
+        </is>
+      </c>
+      <c r="E193" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">延华智能</t>
+        </is>
+      </c>
+      <c r="F193" s="4">
+        <v>0.1267668102675446</v>
+      </c>
+      <c r="G193" s="4">
+        <v>0.08614232209737827</v>
+      </c>
+      <c r="H193" s="4">
+        <v>0.08614232209737827</v>
+      </c>
+      <c r="I193" s="4">
+        <v>-0.029962546816479474</v>
+      </c>
+      <c r="J193" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K193" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -3.00%</t>
+        </is>
+      </c>
+      <c r="L193" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M193" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.18</t>
         </is>
       </c>
     </row>
@@ -52351,28 +54345,28 @@
         </is>
       </c>
       <c r="B3" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" s="0">
         <v>7</v>
       </c>
       <c r="E3" s="4">
-        <v>0.3888888888888889</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="F3" s="4">
-        <v>0.1509433962264151</v>
+        <v>0.24242424242424243</v>
       </c>
       <c r="G3" s="0">
-        <v>2.576388888888889</v>
+        <v>1.519736842105263</v>
       </c>
       <c r="H3" s="0">
         <v>7</v>
       </c>
       <c r="I3" s="4">
-        <v>0.3888888888888889</v>
+        <v>0.3684210526315789</v>
       </c>
     </row>
     <row r="4">
@@ -52382,28 +54376,28 @@
         </is>
       </c>
       <c r="B4" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="0">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D4" s="0">
         <v>15</v>
       </c>
       <c r="E4" s="4">
-        <v>0.2777777777777778</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="F4" s="4">
-        <v>0.1509433962264151</v>
+        <v>0.24242424242424243</v>
       </c>
       <c r="G4" s="0">
-        <v>1.840277777777778</v>
+        <v>1.0855263157894737</v>
       </c>
       <c r="H4" s="0">
         <v>10</v>
       </c>
       <c r="I4" s="4">
-        <v>0.5555555555555556</v>
+        <v>0.5263157894736842</v>
       </c>
     </row>
     <row r="5">
@@ -52413,28 +54407,28 @@
         </is>
       </c>
       <c r="B5" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" s="0">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D5" s="0">
         <v>28</v>
       </c>
       <c r="E5" s="4">
-        <v>0.25925925925925924</v>
+        <v>0.24561403508771928</v>
       </c>
       <c r="F5" s="4">
-        <v>0.1509433962264151</v>
+        <v>0.24242424242424243</v>
       </c>
       <c r="G5" s="0">
-        <v>1.7175925925925926</v>
+        <v>1.013157894736842</v>
       </c>
       <c r="H5" s="0">
         <v>13</v>
       </c>
       <c r="I5" s="4">
-        <v>0.7222222222222222</v>
+        <v>0.6842105263157895</v>
       </c>
     </row>
     <row r="6">
@@ -52444,28 +54438,28 @@
         </is>
       </c>
       <c r="B6" s="0">
+        <v>19</v>
+      </c>
+      <c r="C6" s="0">
+        <v>190</v>
+      </c>
+      <c r="D6" s="0">
+        <v>46</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0.24210526315789474</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.24242424242424243</v>
+      </c>
+      <c r="G6" s="0">
+        <v>0.9986842105263157</v>
+      </c>
+      <c r="H6" s="0">
         <v>18</v>
       </c>
-      <c r="C6" s="0">
-        <v>180</v>
-      </c>
-      <c r="D6" s="0">
-        <v>44</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0.24444444444444444</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0.1509433962264151</v>
-      </c>
-      <c r="G6" s="0">
-        <v>1.6194444444444445</v>
-      </c>
-      <c r="H6" s="0">
-        <v>17</v>
-      </c>
       <c r="I6" s="4">
-        <v>0.9444444444444444</v>
+        <v>0.9473684210526315</v>
       </c>
     </row>
     <row r="7">

--- a/docs/downloads/latest.xlsx
+++ b/docs/downloads/latest.xlsx
@@ -93,7 +93,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L794"/>
+  <dimension ref="A1:L848"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -42925,13 +42925,2929 @@
         </is>
       </c>
     </row>
+    <row r="795">
+      <c r="A795" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B795" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C795" s="0">
+        <v>1</v>
+      </c>
+      <c r="D795" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603006</t>
+        </is>
+      </c>
+      <c r="E795" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">联明股份</t>
+        </is>
+      </c>
+      <c r="F795" s="0">
+        <v>10.74</v>
+      </c>
+      <c r="G795" s="4">
+        <v>0.10040983606557387</v>
+      </c>
+      <c r="H795" s="4">
+        <v>0.3613343549815</v>
+      </c>
+      <c r="I795" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J795" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 联明股份（603006）归入“三季报增长+新能源水冷板+供应链服务”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K795" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 9.9%）。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L795" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B796" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C796" s="0">
+        <v>2</v>
+      </c>
+      <c r="D796" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002696</t>
+        </is>
+      </c>
+      <c r="E796" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">百洋股份</t>
+        </is>
+      </c>
+      <c r="F796" s="0">
+        <v>11.77</v>
+      </c>
+      <c r="G796" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H796" s="4">
+        <v>0.26320499986951934</v>
+      </c>
+      <c r="I796" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J796" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 百洋股份（002696）归入“水产加工+鱼粉鱼油+“羊”字辈”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K796" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.9 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L796" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B797" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C797" s="0">
+        <v>3</v>
+      </c>
+      <c r="D797" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002636</t>
+        </is>
+      </c>
+      <c r="E797" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金安国纪</t>
+        </is>
+      </c>
+      <c r="F797" s="0">
+        <v>58.59</v>
+      </c>
+      <c r="G797" s="4">
+        <v>0.1000751032669922</v>
+      </c>
+      <c r="H797" s="4">
+        <v>0.24200829735231447</v>
+      </c>
+      <c r="I797" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J797" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 金安国纪（002636）归入“覆铜板+三季报高增+产能扩张”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K797" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 10.0%）。截至运行时成交量约为20日均量的 0.6 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L797" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B798" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C798" s="0">
+        <v>4</v>
+      </c>
+      <c r="D798" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605488</t>
+        </is>
+      </c>
+      <c r="E798" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">福莱新材</t>
+        </is>
+      </c>
+      <c r="F798" s="0">
+        <v>48.61</v>
+      </c>
+      <c r="G798" s="4">
+        <v>0.10002262955419772</v>
+      </c>
+      <c r="H798" s="4">
+        <v>0.19689428706717046</v>
+      </c>
+      <c r="I798" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no_verified_event</t>
+        </is>
+      </c>
+      <c r="J798" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">事件证据层未找到与当日涨停直接匹配的公告或新闻；系统不把概念标签、技术形态或主观猜测当成涨停原因。</t>
+        </is>
+      </c>
+      <c r="K798" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.9 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L798" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；近5日涨幅偏高，短线获利盘压力更大；近10日涨幅偏高</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B799" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C799" s="0">
+        <v>5</v>
+      </c>
+      <c r="D799" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002164</t>
+        </is>
+      </c>
+      <c r="E799" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">宁波东力</t>
+        </is>
+      </c>
+      <c r="F799" s="0">
+        <v>16.9</v>
+      </c>
+      <c r="G799" s="4">
+        <v>0.10026041666666652</v>
+      </c>
+      <c r="H799" s="4">
+        <v>0.19152289947585938</v>
+      </c>
+      <c r="I799" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J799" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 宁波东力（002164）归入“三季报增长+精密减速器+齿轮传动+机器人”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K799" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.5 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L799" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B800" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C800" s="0">
+        <v>6</v>
+      </c>
+      <c r="D800" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000559</t>
+        </is>
+      </c>
+      <c r="E800" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">万向钱潮</t>
+        </is>
+      </c>
+      <c r="F800" s="0">
+        <v>13.18</v>
+      </c>
+      <c r="G800" s="4">
+        <v>0.10016694490818034</v>
+      </c>
+      <c r="H800" s="4">
+        <v>0.18278591762224275</v>
+      </c>
+      <c r="I800" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J800" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 万向钱潮（000559）归入“人形机器人+精密减速器+汽车零部件”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K800" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.5 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L800" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B801" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C801" s="0">
+        <v>7</v>
+      </c>
+      <c r="D801" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603081</t>
+        </is>
+      </c>
+      <c r="E801" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大丰实业</t>
+        </is>
+      </c>
+      <c r="F801" s="0">
+        <v>11.31</v>
+      </c>
+      <c r="G801" s="4">
+        <v>0.10019455252918297</v>
+      </c>
+      <c r="H801" s="4">
+        <v>0.16806355804875964</v>
+      </c>
+      <c r="I801" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J801" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 大丰实业（603081）归入“具身智能+文体旅集成+舞台机械”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K801" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.9 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L801" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B802" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C802" s="0">
+        <v>8</v>
+      </c>
+      <c r="D802" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600078</t>
+        </is>
+      </c>
+      <c r="E802" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">澄星股份</t>
+        </is>
+      </c>
+      <c r="F802" s="0">
+        <v>9.42</v>
+      </c>
+      <c r="G802" s="4">
+        <v>0.10046728971962615</v>
+      </c>
+      <c r="H802" s="4">
+        <v>0.1618231986949855</v>
+      </c>
+      <c r="I802" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J802" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 澄星股份（600078）归入“三季报增长+磷化工+电子级磷酸”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K802" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 8.2%）。截至运行时成交量约为20日均量的 3.4 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L802" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B803" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C803" s="0">
+        <v>9</v>
+      </c>
+      <c r="D803" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603626</t>
+        </is>
+      </c>
+      <c r="E803" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">科森科技</t>
+        </is>
+      </c>
+      <c r="F803" s="0">
+        <v>27.83</v>
+      </c>
+      <c r="G803" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H803" s="4">
+        <v>0.1508285549013406</v>
+      </c>
+      <c r="I803" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J803" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 科森科技（603626）归入“机器人结构件+消费电子结构件+三季报扭亏”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K803" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L803" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B804" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C804" s="0">
+        <v>10</v>
+      </c>
+      <c r="D804" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603337</t>
+        </is>
+      </c>
+      <c r="E804" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">杰克科技</t>
+        </is>
+      </c>
+      <c r="F804" s="0">
+        <v>48.83</v>
+      </c>
+      <c r="G804" s="4">
+        <v>0.10002252759630537</v>
+      </c>
+      <c r="H804" s="4">
+        <v>0.1499749807700219</v>
+      </c>
+      <c r="I804" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J804" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 杰克科技（603337）归入“人形机器人+数字成套+工业缝纫机”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K804" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.6 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L804" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B805" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C805" s="0">
+        <v>11</v>
+      </c>
+      <c r="D805" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002526</t>
+        </is>
+      </c>
+      <c r="E805" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">山东矿机</t>
+        </is>
+      </c>
+      <c r="F805" s="0">
+        <v>2.98</v>
+      </c>
+      <c r="G805" s="4">
+        <v>0.09963099630996307</v>
+      </c>
+      <c r="H805" s="4">
+        <v>0.14856285680949674</v>
+      </c>
+      <c r="I805" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J805" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 山东矿机（002526）归入“煤炭机械+焊接机器人+第三季度业绩增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K805" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L805" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B806" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C806" s="0">
+        <v>12</v>
+      </c>
+      <c r="D806" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603868</t>
+        </is>
+      </c>
+      <c r="E806" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">飞科电器</t>
+        </is>
+      </c>
+      <c r="F806" s="0">
+        <v>34.22</v>
+      </c>
+      <c r="G806" s="4">
+        <v>0.0999678559948569</v>
+      </c>
+      <c r="H806" s="4">
+        <v>0.14168234058033974</v>
+      </c>
+      <c r="I806" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J806" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 飞科电器（603868）归入“三季报增长+个护电器”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K806" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L806" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B807" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C807" s="0">
+        <v>13</v>
+      </c>
+      <c r="D807" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603667</t>
+        </is>
+      </c>
+      <c r="E807" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">五洲新春</t>
+        </is>
+      </c>
+      <c r="F807" s="0">
+        <v>49.98</v>
+      </c>
+      <c r="G807" s="4">
+        <v>0.09991197183098599</v>
+      </c>
+      <c r="H807" s="4">
+        <v>0.13718115399525926</v>
+      </c>
+      <c r="I807" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J807" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 五洲新春（603667）归入“三季报业绩+机器人丝杠+轴承主业”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K807" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L807" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B808" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C808" s="0">
+        <v>14</v>
+      </c>
+      <c r="D808" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605566</t>
+        </is>
+      </c>
+      <c r="E808" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">福莱蒽特</t>
+        </is>
+      </c>
+      <c r="F808" s="0">
+        <v>28.6</v>
+      </c>
+      <c r="G808" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H808" s="4">
+        <v>0.12899265276767596</v>
+      </c>
+      <c r="I808" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J808" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 福莱蒽特（605566）归入“三季报增长+机器人传感+服务器采购+分散染料”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K808" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L808" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B809" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C809" s="0">
+        <v>15</v>
+      </c>
+      <c r="D809" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002265</t>
+        </is>
+      </c>
+      <c r="E809" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">建设工业</t>
+        </is>
+      </c>
+      <c r="F809" s="0">
+        <v>20.92</v>
+      </c>
+      <c r="G809" s="4">
+        <v>0.09989484752891699</v>
+      </c>
+      <c r="H809" s="4">
+        <v>0.1249627792979653</v>
+      </c>
+      <c r="I809" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J809" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 建设工业（002265）归入“机器人装备+三季报增长+兵装重组”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K809" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L809" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B810" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C810" s="0">
+        <v>16</v>
+      </c>
+      <c r="D810" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603897</t>
+        </is>
+      </c>
+      <c r="E810" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">长城科技</t>
+        </is>
+      </c>
+      <c r="F810" s="0">
+        <v>26.43</v>
+      </c>
+      <c r="G810" s="4">
+        <v>0.09987515605493137</v>
+      </c>
+      <c r="H810" s="4">
+        <v>0.12350802441953393</v>
+      </c>
+      <c r="I810" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J810" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 长城科技（603897）归入“三季报增长+机器人应用+电磁线”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K810" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.6 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L810" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B811" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C811" s="0">
+        <v>17</v>
+      </c>
+      <c r="D811" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603219</t>
+        </is>
+      </c>
+      <c r="E811" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">富佳股份</t>
+        </is>
+      </c>
+      <c r="F811" s="0">
+        <v>13.21</v>
+      </c>
+      <c r="G811" s="4">
+        <v>0.09991673605328909</v>
+      </c>
+      <c r="H811" s="4">
+        <v>0.12340516318411006</v>
+      </c>
+      <c r="I811" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J811" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 富佳股份（603219）归入“三季报增长+粮仓机器人+清洁家电”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K811" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.8 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L811" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B812" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C812" s="0">
+        <v>18</v>
+      </c>
+      <c r="D812" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002943</t>
+        </is>
+      </c>
+      <c r="E812" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">宇晶股份</t>
+        </is>
+      </c>
+      <c r="F812" s="0">
+        <v>25.11</v>
+      </c>
+      <c r="G812" s="4">
+        <v>0.0998685939553221</v>
+      </c>
+      <c r="H812" s="4">
+        <v>0.1231238620469723</v>
+      </c>
+      <c r="I812" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J812" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 宇晶股份（002943）归入“机器人+切磨抛设备+碳化硅设备”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K812" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L812" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B813" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C813" s="0">
+        <v>19</v>
+      </c>
+      <c r="D813" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603533</t>
+        </is>
+      </c>
+      <c r="E813" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">掌阅科技</t>
+        </is>
+      </c>
+      <c r="F813" s="0">
+        <v>28.03</v>
+      </c>
+      <c r="G813" s="4">
+        <v>0.10007849293563575</v>
+      </c>
+      <c r="H813" s="4">
+        <v>0.12186275553151751</v>
+      </c>
+      <c r="I813" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J813" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 掌阅科技（603533）归入“AI短剧+短剧出海+数字阅读”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K813" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L813" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B814" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C814" s="0">
+        <v>20</v>
+      </c>
+      <c r="D814" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002889</t>
+        </is>
+      </c>
+      <c r="E814" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东方嘉盛</t>
+        </is>
+      </c>
+      <c r="F814" s="0">
+        <v>15.44</v>
+      </c>
+      <c r="G814" s="4">
+        <v>0.09971509971509974</v>
+      </c>
+      <c r="H814" s="4">
+        <v>0.11759893247468753</v>
+      </c>
+      <c r="I814" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J814" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 东方嘉盛（002889）归入“半导体供应链+光刻机保税寄售维修+智慧仓储+机器人概念”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K814" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L814" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B815" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C815" s="0">
+        <v>21</v>
+      </c>
+      <c r="D815" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603992</t>
+        </is>
+      </c>
+      <c r="E815" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">松霖科技</t>
+        </is>
+      </c>
+      <c r="F815" s="0">
+        <v>22.67</v>
+      </c>
+      <c r="G815" s="4">
+        <v>0.09995147986414367</v>
+      </c>
+      <c r="H815" s="4">
+        <v>0.11581656976471681</v>
+      </c>
+      <c r="I815" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J815" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 松霖科技（603992）归入“服务机器人+智能厨卫+业绩预增”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K815" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L815" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B816" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C816" s="0">
+        <v>22</v>
+      </c>
+      <c r="D816" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605288</t>
+        </is>
+      </c>
+      <c r="E816" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">凯迪股份</t>
+        </is>
+      </c>
+      <c r="F816" s="0">
+        <v>65.4</v>
+      </c>
+      <c r="G816" s="4">
+        <v>0.1000841042893188</v>
+      </c>
+      <c r="H816" s="4">
+        <v>0.11326494398744616</v>
+      </c>
+      <c r="I816" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J816" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 凯迪股份（605288）归入“具身机器人送样+线性驱动+汽车零部件”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K816" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L816" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B817" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C817" s="0">
+        <v>23</v>
+      </c>
+      <c r="D817" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002962</t>
+        </is>
+      </c>
+      <c r="E817" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">五方光电</t>
+        </is>
+      </c>
+      <c r="F817" s="0">
+        <v>12.83</v>
+      </c>
+      <c r="G817" s="4">
+        <v>0.10034305317324188</v>
+      </c>
+      <c r="H817" s="4">
+        <v>0.11296993604946137</v>
+      </c>
+      <c r="I817" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J817" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 五方光电（002962）归入“三季报增长+TGV光学+红外截止滤光片”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K817" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L817" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B818" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C818" s="0">
+        <v>24</v>
+      </c>
+      <c r="D818" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000670</t>
+        </is>
+      </c>
+      <c r="E818" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">盈方微</t>
+        </is>
+      </c>
+      <c r="F818" s="0">
+        <v>7.08</v>
+      </c>
+      <c r="G818" s="4">
+        <v>0.09937888198757762</v>
+      </c>
+      <c r="H818" s="4">
+        <v>0.11053931962237087</v>
+      </c>
+      <c r="I818" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J818" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 盈方微（000670）归入“三季度增长+存储芯片+元器件分销”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K818" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.8 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L818" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B819" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C819" s="0">
+        <v>25</v>
+      </c>
+      <c r="D819" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600173</t>
+        </is>
+      </c>
+      <c r="E819" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">卧龙新能</t>
+        </is>
+      </c>
+      <c r="F819" s="0">
+        <v>5.45</v>
+      </c>
+      <c r="G819" s="4">
+        <v>0.10101010101010101</v>
+      </c>
+      <c r="H819" s="4">
+        <v>0.10912660495586642</v>
+      </c>
+      <c r="I819" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J819" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 卧龙新能（600173）归入“储能并网+海外储能+氢能”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K819" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.5 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L819" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B820" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C820" s="0">
+        <v>26</v>
+      </c>
+      <c r="D820" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605060</t>
+        </is>
+      </c>
+      <c r="E820" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">联德股份</t>
+        </is>
+      </c>
+      <c r="F820" s="0">
+        <v>32.16</v>
+      </c>
+      <c r="G820" s="4">
+        <v>0.09986320109439116</v>
+      </c>
+      <c r="H820" s="4">
+        <v>0.10828597914081632</v>
+      </c>
+      <c r="I820" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J820" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 联德股份（605060）归入“三季报增长+数据中心温控+燃气轮机”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K820" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L820" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B821" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C821" s="0">
+        <v>27</v>
+      </c>
+      <c r="D821" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002862</t>
+        </is>
+      </c>
+      <c r="E821" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">实丰文化</t>
+        </is>
+      </c>
+      <c r="F821" s="0">
+        <v>15.38</v>
+      </c>
+      <c r="G821" s="4">
+        <v>0.10014306151645203</v>
+      </c>
+      <c r="H821" s="4">
+        <v>0.10828397227132391</v>
+      </c>
+      <c r="I821" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J821" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 实丰文化（002862）归入“AI玩具+IP潮玩+玩具出海”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K821" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L821" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B822" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C822" s="0">
+        <v>28</v>
+      </c>
+      <c r="D822" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603135</t>
+        </is>
+      </c>
+      <c r="E822" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中重科技</t>
+        </is>
+      </c>
+      <c r="F822" s="0">
+        <v>8.64</v>
+      </c>
+      <c r="G822" s="4">
+        <v>0.10063694267515944</v>
+      </c>
+      <c r="H822" s="4">
+        <v>0.10820688437505953</v>
+      </c>
+      <c r="I822" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J822" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 中重科技（603135）归入“工业机器人+冶金装备+海外项目”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K822" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L822" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B823" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C823" s="0">
+        <v>29</v>
+      </c>
+      <c r="D823" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001270</t>
+        </is>
+      </c>
+      <c r="E823" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">铖昌科技</t>
+        </is>
+      </c>
+      <c r="F823" s="0">
+        <v>80.0</v>
+      </c>
+      <c r="G823" s="4">
+        <v>0.09995875154681698</v>
+      </c>
+      <c r="H823" s="4">
+        <v>0.10671596921570554</v>
+      </c>
+      <c r="I823" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J823" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 铖昌科技（001270）归入“卫星通信+相控阵T/R芯片+订单交付”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K823" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.8 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L823" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B824" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C824" s="0">
+        <v>30</v>
+      </c>
+      <c r="D824" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600601</t>
+        </is>
+      </c>
+      <c r="E824" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">方正科技</t>
+        </is>
+      </c>
+      <c r="F824" s="0">
+        <v>10.32</v>
+      </c>
+      <c r="G824" s="4">
+        <v>0.10021321961620465</v>
+      </c>
+      <c r="H824" s="4">
+        <v>0.10667860049949147</v>
+      </c>
+      <c r="I824" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J824" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 方正科技（600601）归入“PCB+业绩高增+AI扩产”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K824" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L824" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B825" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C825" s="0">
+        <v>31</v>
+      </c>
+      <c r="D825" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603633</t>
+        </is>
+      </c>
+      <c r="E825" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">徕木股份</t>
+        </is>
+      </c>
+      <c r="F825" s="0">
+        <v>6.36</v>
+      </c>
+      <c r="G825" s="4">
+        <v>0.10034602076124566</v>
+      </c>
+      <c r="H825" s="4">
+        <v>0.10666052857562515</v>
+      </c>
+      <c r="I825" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J825" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 徕木股份（603633）归入“人形机器人+汽车连接器”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K825" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.8 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L825" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B826" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C826" s="0">
+        <v>32</v>
+      </c>
+      <c r="D826" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603612</t>
+        </is>
+      </c>
+      <c r="E826" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">索通发展</t>
+        </is>
+      </c>
+      <c r="F826" s="0">
+        <v>15.88</v>
+      </c>
+      <c r="G826" s="4">
+        <v>0.09972299168975084</v>
+      </c>
+      <c r="H826" s="4">
+        <v>0.10463635724683916</v>
+      </c>
+      <c r="I826" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J826" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 索通发展（603612）归入“三季报增长+预焙阳极+炭材料项目”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K826" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L826" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B827" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C827" s="0">
+        <v>33</v>
+      </c>
+      <c r="D827" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002741</t>
+        </is>
+      </c>
+      <c r="E827" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">光华科技</t>
+        </is>
+      </c>
+      <c r="F827" s="0">
+        <v>20.25</v>
+      </c>
+      <c r="G827" s="4">
+        <v>0.09994568169473105</v>
+      </c>
+      <c r="H827" s="4">
+        <v>0.10409549686410041</v>
+      </c>
+      <c r="I827" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J827" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 光华科技（002741）归入“PCB化学品+硫化锂+业绩增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K827" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.5 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L827" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B828" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C828" s="0">
+        <v>34</v>
+      </c>
+      <c r="D828" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">003028</t>
+        </is>
+      </c>
+      <c r="E828" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">振邦智能</t>
+        </is>
+      </c>
+      <c r="F828" s="0">
+        <v>25.91</v>
+      </c>
+      <c r="G828" s="4">
+        <v>0.10021231422505306</v>
+      </c>
+      <c r="H828" s="4">
+        <v>0.10359025480724741</v>
+      </c>
+      <c r="I828" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J828" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 振邦智能（003028）归入“三季报+人形机器人+智能控制器”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K828" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.1 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L828" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B829" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C829" s="0">
+        <v>35</v>
+      </c>
+      <c r="D829" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002172</t>
+        </is>
+      </c>
+      <c r="E829" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">澳洋健康</t>
+        </is>
+      </c>
+      <c r="F829" s="0">
+        <v>4.88</v>
+      </c>
+      <c r="G829" s="4">
+        <v>0.09909909909909898</v>
+      </c>
+      <c r="H829" s="4">
+        <v>0.10318290518270856</v>
+      </c>
+      <c r="I829" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J829" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 澳洋健康（002172）归入“脑机接口+医疗服务+国资控股+“羊”字辈”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K829" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L829" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B830" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C830" s="0">
+        <v>36</v>
+      </c>
+      <c r="D830" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603680</t>
+        </is>
+      </c>
+      <c r="E830" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">今创集团</t>
+        </is>
+      </c>
+      <c r="F830" s="0">
+        <v>11.33</v>
+      </c>
+      <c r="G830" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H830" s="4">
+        <v>0.1030395809396138</v>
+      </c>
+      <c r="I830" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J830" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 今创集团（603680）归入“轨道交通+港口起重+商业航天”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K830" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.6 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L830" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B831" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C831" s="0">
+        <v>37</v>
+      </c>
+      <c r="D831" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002975</t>
+        </is>
+      </c>
+      <c r="E831" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">博杰股份</t>
+        </is>
+      </c>
+      <c r="F831" s="0">
+        <v>85.12</v>
+      </c>
+      <c r="G831" s="4">
+        <v>0.1000258464719568</v>
+      </c>
+      <c r="H831" s="4">
+        <v>0.10285533714716226</v>
+      </c>
+      <c r="I831" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J831" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 博杰股份（002975）归入“机器人测试+磷化铟+MLCC设备+液冷测试”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K831" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L831" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B832" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C832" s="0">
+        <v>38</v>
+      </c>
+      <c r="D832" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603418</t>
+        </is>
+      </c>
+      <c r="E832" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">友升股份</t>
+        </is>
+      </c>
+      <c r="F832" s="0">
+        <v>44.99</v>
+      </c>
+      <c r="G832" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H832" s="4">
+        <v>0.10250952721048456</v>
+      </c>
+      <c r="I832" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J832" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 友升股份（603418）归入“机器人业务+汽车轻量化+特斯拉客户”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K832" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L832" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B833" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C833" s="0">
+        <v>39</v>
+      </c>
+      <c r="D833" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603061</t>
+        </is>
+      </c>
+      <c r="E833" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金海通</t>
+        </is>
+      </c>
+      <c r="F833" s="0">
+        <v>260.15</v>
+      </c>
+      <c r="G833" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H833" s="4">
+        <v>0.100265707556219</v>
+      </c>
+      <c r="I833" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J833" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 金海通（603061）归入“半导体测试分选机+三季报增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K833" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L833" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B834" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C834" s="0">
+        <v>40</v>
+      </c>
+      <c r="D834" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002879</t>
+        </is>
+      </c>
+      <c r="E834" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">长缆科技</t>
+        </is>
+      </c>
+      <c r="F834" s="0">
+        <v>14.95</v>
+      </c>
+      <c r="G834" s="4">
+        <v>0.10007358351729213</v>
+      </c>
+      <c r="H834" s="4">
+        <v>0.09922064637519754</v>
+      </c>
+      <c r="I834" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J834" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 长缆科技（002879）归入“管道机器人+浸没液冷+电缆附件+三季报”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K834" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L834" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B835" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C835" s="0">
+        <v>41</v>
+      </c>
+      <c r="D835" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603226</t>
+        </is>
+      </c>
+      <c r="E835" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">菲林格尔</t>
+        </is>
+      </c>
+      <c r="F835" s="0">
+        <v>24.26</v>
+      </c>
+      <c r="G835" s="4">
+        <v>0.10022675736961449</v>
+      </c>
+      <c r="H835" s="4">
+        <v>0.09919331819065186</v>
+      </c>
+      <c r="I835" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J835" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 菲林格尔（603226）归入“PCB设备+英伟达+木地板”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K835" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L835" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B836" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C836" s="0">
+        <v>42</v>
+      </c>
+      <c r="D836" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603131</t>
+        </is>
+      </c>
+      <c r="E836" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上海沪工</t>
+        </is>
+      </c>
+      <c r="F836" s="0">
+        <v>14.5</v>
+      </c>
+      <c r="G836" s="4">
+        <v>0.1001517450682854</v>
+      </c>
+      <c r="H836" s="4">
+        <v>0.09752385817975125</v>
+      </c>
+      <c r="I836" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J836" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 上海沪工（603131）归入“三季报扭亏+焊接机器人+商业航天+焊接切割设备”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K836" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.1 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L836" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B837" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C837" s="0">
+        <v>43</v>
+      </c>
+      <c r="D837" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603926</t>
+        </is>
+      </c>
+      <c r="E837" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">铁流股份</t>
+        </is>
+      </c>
+      <c r="F837" s="0">
+        <v>17.06</v>
+      </c>
+      <c r="G837" s="4">
+        <v>0.09993552546744035</v>
+      </c>
+      <c r="H837" s="4">
+        <v>0.09701749143883119</v>
+      </c>
+      <c r="I837" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J837" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 铁流股份（603926）归入“三季报净利增长+机器人部件+电机轴”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K837" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.0 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L837" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B838" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C838" s="0">
+        <v>44</v>
+      </c>
+      <c r="D838" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603920</t>
+        </is>
+      </c>
+      <c r="E838" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">世运电路</t>
+        </is>
+      </c>
+      <c r="F838" s="0">
+        <v>37.85</v>
+      </c>
+      <c r="G838" s="4">
+        <v>0.09997093868061624</v>
+      </c>
+      <c r="H838" s="4">
+        <v>0.09620708704199264</v>
+      </c>
+      <c r="I838" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J838" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 世运电路（603920）归入“机器人PCB+算力PCB+调价落地”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K838" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L838" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B839" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C839" s="0">
+        <v>45</v>
+      </c>
+      <c r="D839" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605366</t>
+        </is>
+      </c>
+      <c r="E839" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">宏柏新材</t>
+        </is>
+      </c>
+      <c r="F839" s="0">
+        <v>7.74</v>
+      </c>
+      <c r="G839" s="4">
+        <v>0.09943181818181814</v>
+      </c>
+      <c r="H839" s="4">
+        <v>0.09513345171309266</v>
+      </c>
+      <c r="I839" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J839" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 宏柏新材（605366）归入“光纤级四氯化硅+功能性硅烷+电子级材料”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K839" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.6 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L839" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B840" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C840" s="0">
+        <v>46</v>
+      </c>
+      <c r="D840" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603303</t>
+        </is>
+      </c>
+      <c r="E840" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">得邦照明</t>
+        </is>
+      </c>
+      <c r="F840" s="0">
+        <v>29.76</v>
+      </c>
+      <c r="G840" s="4">
+        <v>0.10018484288354902</v>
+      </c>
+      <c r="H840" s="4">
+        <v>0.0936954231636827</v>
+      </c>
+      <c r="I840" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J840" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 得邦照明（603303）归入“车载照明+收购嘉利+通用照明”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K840" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.0 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L840" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B841" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C841" s="0">
+        <v>47</v>
+      </c>
+      <c r="D841" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002915</t>
+        </is>
+      </c>
+      <c r="E841" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中欣氟材</t>
+        </is>
+      </c>
+      <c r="F841" s="0">
+        <v>16.02</v>
+      </c>
+      <c r="G841" s="4">
+        <v>0.10027472527472515</v>
+      </c>
+      <c r="H841" s="4">
+        <v>0.08854363485683862</v>
+      </c>
+      <c r="I841" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J841" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 中欣氟材（002915）归入“PEEK材料+新能源材料+氟化工+萤石”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K841" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.5 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L841" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B842" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C842" s="0">
+        <v>48</v>
+      </c>
+      <c r="D842" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001296</t>
+        </is>
+      </c>
+      <c r="E842" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">长江材料</t>
+        </is>
+      </c>
+      <c r="F842" s="0">
+        <v>20.23</v>
+      </c>
+      <c r="G842" s="4">
+        <v>0.10005437737901035</v>
+      </c>
+      <c r="H842" s="4">
+        <v>0.08839257716099137</v>
+      </c>
+      <c r="I842" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J842" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 长江材料（001296）归入“3D打印砂+覆膜砂+油气勘探”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K842" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.1 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L842" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B843" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C843" s="0">
+        <v>49</v>
+      </c>
+      <c r="D843" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002534</t>
+        </is>
+      </c>
+      <c r="E843" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">西子洁能</t>
+        </is>
+      </c>
+      <c r="F843" s="0">
+        <v>15.4</v>
+      </c>
+      <c r="G843" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H843" s="4">
+        <v>0.08725295040674962</v>
+      </c>
+      <c r="I843" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J843" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 西子洁能（002534）归入“订单增长+燃机余热锅炉+算力储能”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K843" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.4 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L843" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B844" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C844" s="0">
+        <v>50</v>
+      </c>
+      <c r="D844" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000554</t>
+        </is>
+      </c>
+      <c r="E844" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">泰山石油</t>
+        </is>
+      </c>
+      <c r="F844" s="0">
+        <v>6.63</v>
+      </c>
+      <c r="G844" s="4">
+        <v>0.09950248756218905</v>
+      </c>
+      <c r="H844" s="4">
+        <v>0.08094413662610753</v>
+      </c>
+      <c r="I844" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J844" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 泰山石油（000554）归入“三季报增长+成品油+充换电”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K844" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.1 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L844" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B845" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C845" s="0">
+        <v>51</v>
+      </c>
+      <c r="D845" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603699</t>
+        </is>
+      </c>
+      <c r="E845" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">纽威股份</t>
+        </is>
+      </c>
+      <c r="F845" s="0">
+        <v>38.39</v>
+      </c>
+      <c r="G845" s="4">
+        <v>0.09968490403895736</v>
+      </c>
+      <c r="H845" s="4">
+        <v>0.07728164092241377</v>
+      </c>
+      <c r="I845" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no_verified_event</t>
+        </is>
+      </c>
+      <c r="J845" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">事件证据层未找到与当日涨停直接匹配的公告或新闻；系统不把概念标签、技术形态或主观猜测当成涨停原因。</t>
+        </is>
+      </c>
+      <c r="K845" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.2 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L845" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B846" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C846" s="0">
+        <v>52</v>
+      </c>
+      <c r="D846" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603109</t>
+        </is>
+      </c>
+      <c r="E846" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神驰机电</t>
+        </is>
+      </c>
+      <c r="F846" s="0">
+        <v>17.93</v>
+      </c>
+      <c r="G846" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H846" s="4">
+        <v>0.07550563789673498</v>
+      </c>
+      <c r="I846" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J846" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 神驰机电（603109）归入“机器人+小型发电机+户用储能”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K846" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.4 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L846" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B847" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C847" s="0">
+        <v>53</v>
+      </c>
+      <c r="D847" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600252</t>
+        </is>
+      </c>
+      <c r="E847" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中恒集团</t>
+        </is>
+      </c>
+      <c r="F847" s="0">
+        <v>2.3</v>
+      </c>
+      <c r="G847" s="4">
+        <v>0.09523809523809511</v>
+      </c>
+      <c r="H847" s="4">
+        <v>0.03672806127015913</v>
+      </c>
+      <c r="I847" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no_verified_event</t>
+        </is>
+      </c>
+      <c r="J847" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">事件证据层未找到与当日涨停直接匹配的公告或新闻；系统不把概念标签、技术形态或主观猜测当成涨停原因。</t>
+        </is>
+      </c>
+      <c r="K847" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L847" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B848" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C848" s="0">
+        <v>54</v>
+      </c>
+      <c r="D848" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002150</t>
+        </is>
+      </c>
+      <c r="E848" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正泰电源</t>
+        </is>
+      </c>
+      <c r="F848" s="0">
+        <v>18.76</v>
+      </c>
+      <c r="G848" s="4">
+        <v>0.09643483343074234</v>
+      </c>
+      <c r="H848" s="4">
+        <v>0.03633321277896297</v>
+      </c>
+      <c r="I848" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no_verified_event</t>
+        </is>
+      </c>
+      <c r="J848" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">事件证据层未找到与当日涨停直接匹配的公告或新闻；系统不把概念标签、技术形态或主观猜测当成涨停原因。</t>
+        </is>
+      </c>
+      <c r="K848" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">截至运行时成交量约为20日均量的 2.6 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 62 家涨停，其中首板 54 家、2板及以上 8 家。</t>
+        </is>
+      </c>
+      <c r="L848" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M193"/>
+  <dimension ref="A1:M203"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -54254,6 +57170,596 @@
       <c r="M193" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">5.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B194" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C194" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D194" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000058</t>
+        </is>
+      </c>
+      <c r="E194" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">深 赛 格</t>
+        </is>
+      </c>
+      <c r="F194" s="4">
+        <v>0.36780440226879885</v>
+      </c>
+      <c r="G194" s="4">
+        <v>0.10038119440914861</v>
+      </c>
+      <c r="H194" s="4">
+        <v>0.10038119440914861</v>
+      </c>
+      <c r="I194" s="4">
+        <v>0.04066073697585759</v>
+      </c>
+      <c r="J194" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K194" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +4.07%</t>
+        </is>
+      </c>
+      <c r="L194" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M194" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8.19</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B195" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C195" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D195" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002011</t>
+        </is>
+      </c>
+      <c r="E195" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">盾安环境</t>
+        </is>
+      </c>
+      <c r="F195" s="4">
+        <v>0.24538257026484128</v>
+      </c>
+      <c r="G195" s="4">
+        <v>-0.009674582233948903</v>
+      </c>
+      <c r="H195" s="4">
+        <v>0.02990325417766071</v>
+      </c>
+      <c r="I195" s="4">
+        <v>0.012313104661389573</v>
+      </c>
+      <c r="J195" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K195" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +1.23%</t>
+        </is>
+      </c>
+      <c r="L195" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M195" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.51</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B196" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C196" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="D196" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002724</t>
+        </is>
+      </c>
+      <c r="E196" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">海洋王</t>
+        </is>
+      </c>
+      <c r="F196" s="4">
+        <v>0.1601691132452417</v>
+      </c>
+      <c r="G196" s="4">
+        <v>-0.06035141329258975</v>
+      </c>
+      <c r="H196" s="4">
+        <v>0.03361344537815114</v>
+      </c>
+      <c r="I196" s="4">
+        <v>0.023682200152788324</v>
+      </c>
+      <c r="J196" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K196" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +2.37%</t>
+        </is>
+      </c>
+      <c r="L196" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M196" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B197" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C197" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="D197" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002249</t>
+        </is>
+      </c>
+      <c r="E197" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大洋电机</t>
+        </is>
+      </c>
+      <c r="F197" s="4">
+        <v>0.12748515196083518</v>
+      </c>
+      <c r="G197" s="4">
+        <v>0.01558441558441559</v>
+      </c>
+      <c r="H197" s="4">
+        <v>0.09870129870129873</v>
+      </c>
+      <c r="I197" s="4">
+        <v>0.04155844155844157</v>
+      </c>
+      <c r="J197" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K197" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +4.16%</t>
+        </is>
+      </c>
+      <c r="L197" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M197" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B198" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C198" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="D198" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601566</t>
+        </is>
+      </c>
+      <c r="E198" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">九牧王</t>
+        </is>
+      </c>
+      <c r="F198" s="4">
+        <v>0.12298825069422419</v>
+      </c>
+      <c r="G198" s="4">
+        <v>-0.02131782945736438</v>
+      </c>
+      <c r="H198" s="4">
+        <v>-0.02131782945736438</v>
+      </c>
+      <c r="I198" s="4">
+        <v>-0.05135658914728691</v>
+      </c>
+      <c r="J198" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K198" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -5.14%</t>
+        </is>
+      </c>
+      <c r="L198" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M198" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9.79</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B199" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C199" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="D199" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600715</t>
+        </is>
+      </c>
+      <c r="E199" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文投控股</t>
+        </is>
+      </c>
+      <c r="F199" s="4">
+        <v>0.11467916778520654</v>
+      </c>
+      <c r="G199" s="4">
+        <v>-0.016042780748663166</v>
+      </c>
+      <c r="H199" s="4">
+        <v>0.10160427807486627</v>
+      </c>
+      <c r="I199" s="4">
+        <v>0.10160427807486627</v>
+      </c>
+      <c r="J199" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K199" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +10.16%</t>
+        </is>
+      </c>
+      <c r="L199" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M199" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B200" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C200" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="D200" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001400</t>
+        </is>
+      </c>
+      <c r="E200" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">江顺科技</t>
+        </is>
+      </c>
+      <c r="F200" s="4">
+        <v>0.11278706724186846</v>
+      </c>
+      <c r="G200" s="4">
+        <v>0.08395615346287988</v>
+      </c>
+      <c r="H200" s="4">
+        <v>0.10002491280518178</v>
+      </c>
+      <c r="I200" s="4">
+        <v>0.10002491280518178</v>
+      </c>
+      <c r="J200" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K200" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +10.00%</t>
+        </is>
+      </c>
+      <c r="L200" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M200" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B201" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C201" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="D201" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600785</t>
+        </is>
+      </c>
+      <c r="E201" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新华百货</t>
+        </is>
+      </c>
+      <c r="F201" s="4">
+        <v>0.1098932170248941</v>
+      </c>
+      <c r="G201" s="4">
+        <v>-0.060431654676258995</v>
+      </c>
+      <c r="H201" s="4">
+        <v>0.07625899280575532</v>
+      </c>
+      <c r="I201" s="4">
+        <v>0.006474820143884896</v>
+      </c>
+      <c r="J201" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K201" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +0.65%</t>
+        </is>
+      </c>
+      <c r="L201" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M201" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B202" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C202" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="D202" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603565</t>
+        </is>
+      </c>
+      <c r="E202" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中谷物流</t>
+        </is>
+      </c>
+      <c r="F202" s="4">
+        <v>0.10185336549614955</v>
+      </c>
+      <c r="G202" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H202" s="4">
+        <v>0.02384737678855342</v>
+      </c>
+      <c r="I202" s="4">
+        <v>0.008744038155802825</v>
+      </c>
+      <c r="J202" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K202" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +0.87%</t>
+        </is>
+      </c>
+      <c r="L202" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M202" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12.69</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="B203" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-28</t>
+        </is>
+      </c>
+      <c r="C203" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="D203" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603037</t>
+        </is>
+      </c>
+      <c r="E203" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">凯众股份</t>
+        </is>
+      </c>
+      <c r="F203" s="4">
+        <v>0.09852707452562856</v>
+      </c>
+      <c r="G203" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H203" s="4">
+        <v>0.10025273799494538</v>
+      </c>
+      <c r="I203" s="4">
+        <v>0.10025273799494538</v>
+      </c>
+      <c r="J203" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K203" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +10.03%</t>
+        </is>
+      </c>
+      <c r="L203" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M203" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13.06</t>
         </is>
       </c>
     </row>
@@ -54345,28 +57851,28 @@
         </is>
       </c>
       <c r="B3" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" s="0">
         <v>7</v>
       </c>
       <c r="E3" s="4">
-        <v>0.3684210526315789</v>
+        <v>0.35</v>
       </c>
       <c r="F3" s="4">
-        <v>0.24242424242424243</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="G3" s="0">
-        <v>1.519736842105263</v>
+        <v>1.8199999999999998</v>
       </c>
       <c r="H3" s="0">
         <v>7</v>
       </c>
       <c r="I3" s="4">
-        <v>0.3684210526315789</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="4">
@@ -54376,28 +57882,28 @@
         </is>
       </c>
       <c r="B4" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" s="0">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D4" s="0">
         <v>15</v>
       </c>
       <c r="E4" s="4">
-        <v>0.2631578947368421</v>
+        <v>0.25</v>
       </c>
       <c r="F4" s="4">
-        <v>0.24242424242424243</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="G4" s="0">
-        <v>1.0855263157894737</v>
+        <v>1.2999999999999998</v>
       </c>
       <c r="H4" s="0">
         <v>10</v>
       </c>
       <c r="I4" s="4">
-        <v>0.5263157894736842</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
@@ -54407,28 +57913,28 @@
         </is>
       </c>
       <c r="B5" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" s="0">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D5" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5" s="4">
-        <v>0.24561403508771928</v>
+        <v>0.24166666666666667</v>
       </c>
       <c r="F5" s="4">
-        <v>0.24242424242424243</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="G5" s="0">
-        <v>1.013157894736842</v>
+        <v>1.2566666666666666</v>
       </c>
       <c r="H5" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I5" s="4">
-        <v>0.6842105263157895</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="6">
@@ -54438,28 +57944,28 @@
         </is>
       </c>
       <c r="B6" s="0">
+        <v>20</v>
+      </c>
+      <c r="C6" s="0">
+        <v>200</v>
+      </c>
+      <c r="D6" s="0">
+        <v>49</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0.245</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.19230769230769232</v>
+      </c>
+      <c r="G6" s="0">
+        <v>1.2739999999999998</v>
+      </c>
+      <c r="H6" s="0">
         <v>19</v>
       </c>
-      <c r="C6" s="0">
-        <v>190</v>
-      </c>
-      <c r="D6" s="0">
-        <v>46</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0.24210526315789474</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0.24242424242424243</v>
-      </c>
-      <c r="G6" s="0">
-        <v>0.9986842105263157</v>
-      </c>
-      <c r="H6" s="0">
-        <v>18</v>
-      </c>
       <c r="I6" s="4">
-        <v>0.9473684210526315</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="7">

--- a/docs/downloads/latest.xlsx
+++ b/docs/downloads/latest.xlsx
@@ -93,7 +93,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L848"/>
+  <dimension ref="A1:L876"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -45841,13 +45841,1525 @@
         </is>
       </c>
     </row>
+    <row r="849">
+      <c r="A849" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B849" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C849" s="0">
+        <v>1</v>
+      </c>
+      <c r="D849" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600592</t>
+        </is>
+      </c>
+      <c r="E849" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">龙溪股份</t>
+        </is>
+      </c>
+      <c r="F849" s="0">
+        <v>17.41</v>
+      </c>
+      <c r="G849" s="4">
+        <v>0.09981048641819325</v>
+      </c>
+      <c r="H849" s="4">
+        <v>0.1609386153080981</v>
+      </c>
+      <c r="I849" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J849" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 龙溪股份（600592）归入“关节轴承+人形机器人+智元机器人”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K849" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 38 家涨停，其中首板 28 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L849" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B850" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C850" s="0">
+        <v>2</v>
+      </c>
+      <c r="D850" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000530</t>
+        </is>
+      </c>
+      <c r="E850" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">冰山冷热</t>
+        </is>
+      </c>
+      <c r="F850" s="0">
+        <v>8.23</v>
+      </c>
+      <c r="G850" s="4">
+        <v>0.10026737967914447</v>
+      </c>
+      <c r="H850" s="4">
+        <v>0.15491976721626927</v>
+      </c>
+      <c r="I850" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J850" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 冰山冷热（000530）归入“冰雪工程+数据中心液冷+船舶制冷”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K850" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 38 家涨停，其中首板 28 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L850" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B851" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C851" s="0">
+        <v>3</v>
+      </c>
+      <c r="D851" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600501</t>
+        </is>
+      </c>
+      <c r="E851" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">航天晨光</t>
+        </is>
+      </c>
+      <c r="F851" s="0">
+        <v>16.89</v>
+      </c>
+      <c r="G851" s="4">
+        <v>0.10032573289902282</v>
+      </c>
+      <c r="H851" s="4">
+        <v>0.14784817614002382</v>
+      </c>
+      <c r="I851" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J851" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 航天晨光（600501）归入“商业航天+特种装备+可控核聚变”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K851" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 38 家涨停，其中首板 28 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L851" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B852" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C852" s="0">
+        <v>4</v>
+      </c>
+      <c r="D852" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600261</t>
+        </is>
+      </c>
+      <c r="E852" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">阳光照明</t>
+        </is>
+      </c>
+      <c r="F852" s="0">
+        <v>3.72</v>
+      </c>
+      <c r="G852" s="4">
+        <v>0.10059171597633142</v>
+      </c>
+      <c r="H852" s="4">
+        <v>0.13943404406029228</v>
+      </c>
+      <c r="I852" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J852" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 阳光照明（600261）归入“商业航天+激光通信投资+LED照明+“羊”字辈”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K852" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 38 家涨停，其中首板 28 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L852" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B853" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C853" s="0">
+        <v>5</v>
+      </c>
+      <c r="D853" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603103</t>
+        </is>
+      </c>
+      <c r="E853" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">横店影视</t>
+        </is>
+      </c>
+      <c r="F853" s="0">
+        <v>17.44</v>
+      </c>
+      <c r="G853" s="4">
+        <v>0.10031545741324921</v>
+      </c>
+      <c r="H853" s="4">
+        <v>0.13852161937185611</v>
+      </c>
+      <c r="I853" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J853" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 横店影视（603103）归入“AI短剧+影视全产业链+电影放映”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K853" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.5 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 38 家涨停，其中首板 28 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L853" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B854" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C854" s="0">
+        <v>6</v>
+      </c>
+      <c r="D854" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603703</t>
+        </is>
+      </c>
+      <c r="E854" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">盛洋科技</t>
+        </is>
+      </c>
+      <c r="F854" s="0">
+        <v>10.86</v>
+      </c>
+      <c r="G854" s="4">
+        <v>0.10030395136778125</v>
+      </c>
+      <c r="H854" s="4">
+        <v>0.13814927673533048</v>
+      </c>
+      <c r="I854" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J854" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 盛洋科技（603703）归入“卫星通信终端+高速铜缆+“羊”字辈”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K854" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 38 家涨停，其中首板 28 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L854" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B855" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C855" s="0">
+        <v>7</v>
+      </c>
+      <c r="D855" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601188</t>
+        </is>
+      </c>
+      <c r="E855" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">龙江交通</t>
+        </is>
+      </c>
+      <c r="F855" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="G855" s="4">
+        <v>0.10062893081761004</v>
+      </c>
+      <c r="H855" s="4">
+        <v>0.1372815231417681</v>
+      </c>
+      <c r="I855" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J855" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 龙江交通（601188）归入“冰雪旅游保障+高速公路运营”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K855" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 38 家涨停，其中首板 28 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L855" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B856" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C856" s="0">
+        <v>8</v>
+      </c>
+      <c r="D856" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600428</t>
+        </is>
+      </c>
+      <c r="E856" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中远海特</t>
+        </is>
+      </c>
+      <c r="F856" s="0">
+        <v>11.39</v>
+      </c>
+      <c r="G856" s="4">
+        <v>0.10048309178743974</v>
+      </c>
+      <c r="H856" s="4">
+        <v>0.13683558312342736</v>
+      </c>
+      <c r="I856" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J856" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 中远海特（600428）归入“三季报增长+特种运输+重吊船”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K856" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 38 家涨停，其中首板 28 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L856" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B857" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C857" s="0">
+        <v>9</v>
+      </c>
+      <c r="D857" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002679</t>
+        </is>
+      </c>
+      <c r="E857" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">福建金森</t>
+        </is>
+      </c>
+      <c r="F857" s="0">
+        <v>10.65</v>
+      </c>
+      <c r="G857" s="4">
+        <v>0.100206611570248</v>
+      </c>
+      <c r="H857" s="4">
+        <v>0.13272709492661408</v>
+      </c>
+      <c r="I857" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J857" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 福建金森（002679）归入“三季报增长+林业+FSC森林认证+海峡两岸”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K857" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.6 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 38 家涨停，其中首板 28 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L857" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B858" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C858" s="0">
+        <v>10</v>
+      </c>
+      <c r="D858" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002277</t>
+        </is>
+      </c>
+      <c r="E858" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">友阿股份</t>
+        </is>
+      </c>
+      <c r="F858" s="0">
+        <v>5.53</v>
+      </c>
+      <c r="G858" s="4">
+        <v>0.09940357852882699</v>
+      </c>
+      <c r="H858" s="4">
+        <v>0.12605868103564385</v>
+      </c>
+      <c r="I858" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J858" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 友阿股份（002277）归入“尚阳通重组+功率半导体+百货零售”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K858" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.3 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 38 家涨停，其中首板 28 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L858" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B859" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C859" s="0">
+        <v>11</v>
+      </c>
+      <c r="D859" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603536</t>
+        </is>
+      </c>
+      <c r="E859" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">惠发食品</t>
+        </is>
+      </c>
+      <c r="F859" s="0">
+        <v>10.44</v>
+      </c>
+      <c r="G859" s="4">
+        <v>0.1001053740779767</v>
+      </c>
+      <c r="H859" s="4">
+        <v>0.12517638065667908</v>
+      </c>
+      <c r="I859" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J859" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 惠发食品（603536）归入“预制菜+速冻调理肉制品”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K859" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.3 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 38 家涨停，其中首板 28 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L859" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B860" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C860" s="0">
+        <v>12</v>
+      </c>
+      <c r="D860" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000701</t>
+        </is>
+      </c>
+      <c r="E860" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">厦门信达</t>
+        </is>
+      </c>
+      <c r="F860" s="0">
+        <v>5.62</v>
+      </c>
+      <c r="G860" s="4">
+        <v>0.09980430528375737</v>
+      </c>
+      <c r="H860" s="4">
+        <v>0.12281816287257281</v>
+      </c>
+      <c r="I860" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J860" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 厦门信达（000701）归入“大宗商品+算力业务+三季报增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K860" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.8 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 38 家涨停，其中首板 28 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L860" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B861" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C861" s="0">
+        <v>13</v>
+      </c>
+      <c r="D861" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600643</t>
+        </is>
+      </c>
+      <c r="E861" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">爱建集团</t>
+        </is>
+      </c>
+      <c r="F861" s="0">
+        <v>4.25</v>
+      </c>
+      <c r="G861" s="4">
+        <v>0.10103626943005196</v>
+      </c>
+      <c r="H861" s="4">
+        <v>0.12129955930064491</v>
+      </c>
+      <c r="I861" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J861" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 爱建集团（600643）归入“三季报增长+多元金融+金融科技”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K861" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.3 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 38 家涨停，其中首板 28 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L861" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B862" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C862" s="0">
+        <v>14</v>
+      </c>
+      <c r="D862" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002086</t>
+        </is>
+      </c>
+      <c r="E862" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东方海洋</t>
+        </is>
+      </c>
+      <c r="F862" s="0">
+        <v>2.57</v>
+      </c>
+      <c r="G862" s="4">
+        <v>0.09829059829059839</v>
+      </c>
+      <c r="H862" s="4">
+        <v>0.11803213163992232</v>
+      </c>
+      <c r="I862" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J862" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 东方海洋（002086）归入““羊”字辈+体外诊断+海参养殖+水溶性维生素试剂”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K862" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.9 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 38 家涨停，其中首板 28 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L862" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B863" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C863" s="0">
+        <v>15</v>
+      </c>
+      <c r="D863" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605179</t>
+        </is>
+      </c>
+      <c r="E863" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一鸣食品</t>
+        </is>
+      </c>
+      <c r="F863" s="0">
+        <v>23.77</v>
+      </c>
+      <c r="G863" s="4">
+        <v>0.09995372512725599</v>
+      </c>
+      <c r="H863" s="4">
+        <v>0.11494400816620201</v>
+      </c>
+      <c r="I863" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J863" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 一鸣食品（605179）归入“低温乳品+烘焙食品+米制鲜食”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K863" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.2 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 38 家涨停，其中首板 28 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L863" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B864" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C864" s="0">
+        <v>16</v>
+      </c>
+      <c r="D864" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">003032</t>
+        </is>
+      </c>
+      <c r="E864" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">传智教育</t>
+        </is>
+      </c>
+      <c r="F864" s="0">
+        <v>9.05</v>
+      </c>
+      <c r="G864" s="4">
+        <v>0.09963547995139743</v>
+      </c>
+      <c r="H864" s="4">
+        <v>0.11383397680344937</v>
+      </c>
+      <c r="I864" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J864" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 传智教育（003032）归入“三季报增长+AI职业教育+具身智能培训”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K864" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.9 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 38 家涨停，其中首板 28 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L864" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B865" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C865" s="0">
+        <v>17</v>
+      </c>
+      <c r="D865" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001225</t>
+        </is>
+      </c>
+      <c r="E865" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">和泰机电</t>
+        </is>
+      </c>
+      <c r="F865" s="0">
+        <v>32.92</v>
+      </c>
+      <c r="G865" s="4">
+        <v>0.09989976612094885</v>
+      </c>
+      <c r="H865" s="4">
+        <v>0.1137413608736618</v>
+      </c>
+      <c r="I865" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J865" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 和泰机电（001225）归入“物料输送设备+输送链+海外拓展”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K865" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 38 家涨停，其中首板 28 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L865" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B866" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C866" s="0">
+        <v>18</v>
+      </c>
+      <c r="D866" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605598</t>
+        </is>
+      </c>
+      <c r="E866" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上海港湾</t>
+        </is>
+      </c>
+      <c r="F866" s="0">
+        <v>24.9</v>
+      </c>
+      <c r="G866" s="4">
+        <v>0.09982332155477014</v>
+      </c>
+      <c r="H866" s="4">
+        <v>0.11363684630571125</v>
+      </c>
+      <c r="I866" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J866" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 上海港湾（605598）归入“商业航天+卫星能源+钙钛矿电池”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K866" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.1 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 38 家涨停，其中首板 28 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L866" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B867" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C867" s="0">
+        <v>19</v>
+      </c>
+      <c r="D867" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600997</t>
+        </is>
+      </c>
+      <c r="E867" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">开滦股份</t>
+        </is>
+      </c>
+      <c r="F867" s="0">
+        <v>5.39</v>
+      </c>
+      <c r="G867" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H867" s="4">
+        <v>0.11314199035343989</v>
+      </c>
+      <c r="I867" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J867" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 开滦股份（600997）归入“第三季度净利增长+炼焦煤+煤化工”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K867" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.8 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 38 家涨停，其中首板 28 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L867" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B868" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C868" s="0">
+        <v>20</v>
+      </c>
+      <c r="D868" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002531</t>
+        </is>
+      </c>
+      <c r="E868" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天顺风能</t>
+        </is>
+      </c>
+      <c r="F868" s="0">
+        <v>7.06</v>
+      </c>
+      <c r="G868" s="4">
+        <v>0.09968847352024923</v>
+      </c>
+      <c r="H868" s="4">
+        <v>0.10584703476151766</v>
+      </c>
+      <c r="I868" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J868" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 天顺风能（002531）归入“三季报增长+海上风电+油气船舶”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K868" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.1 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 38 家涨停，其中首板 28 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L868" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B869" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C869" s="0">
+        <v>21</v>
+      </c>
+      <c r="D869" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002865</t>
+        </is>
+      </c>
+      <c r="E869" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">钧达股份</t>
+        </is>
+      </c>
+      <c r="F869" s="0">
+        <v>38.62</v>
+      </c>
+      <c r="G869" s="4">
+        <v>0.09997151808601522</v>
+      </c>
+      <c r="H869" s="4">
+        <v>0.10313453546112634</v>
+      </c>
+      <c r="I869" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J869" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 钧达股份（002865）归入“商业航天+光伏电池+土耳其产能”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K869" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.2 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 38 家涨停，其中首板 28 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L869" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B870" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C870" s="0">
+        <v>22</v>
+      </c>
+      <c r="D870" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605338</t>
+        </is>
+      </c>
+      <c r="E870" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">巴比食品</t>
+        </is>
+      </c>
+      <c r="F870" s="0">
+        <v>18.98</v>
+      </c>
+      <c r="G870" s="4">
+        <v>0.10028985507246378</v>
+      </c>
+      <c r="H870" s="4">
+        <v>0.10306382365311766</v>
+      </c>
+      <c r="I870" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J870" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 巴比食品（605338）归入“三季报净利增+中式面点+中期分红+小笼包扩张”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K870" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.2 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 38 家涨停，其中首板 28 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L870" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B871" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C871" s="0">
+        <v>23</v>
+      </c>
+      <c r="D871" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600576</t>
+        </is>
+      </c>
+      <c r="E871" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">祥源文旅</t>
+        </is>
+      </c>
+      <c r="F871" s="0">
+        <v>5.38</v>
+      </c>
+      <c r="G871" s="4">
+        <v>0.10020449897750507</v>
+      </c>
+      <c r="H871" s="4">
+        <v>0.09918786177573685</v>
+      </c>
+      <c r="I871" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J871" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 祥源文旅（600576）归入“旅游景区+冰雪产业+低空文旅”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K871" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.9 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 38 家涨停，其中首板 28 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L871" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B872" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C872" s="0">
+        <v>24</v>
+      </c>
+      <c r="D872" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002565</t>
+        </is>
+      </c>
+      <c r="E872" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">顺灏股份</t>
+        </is>
+      </c>
+      <c r="F872" s="0">
+        <v>8.14</v>
+      </c>
+      <c r="G872" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H872" s="4">
+        <v>0.09584321675758496</v>
+      </c>
+      <c r="I872" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J872" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 顺灏股份（002565）归入“太空算力+特种纸印刷+新型烟草”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K872" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 38 家涨停，其中首板 28 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L872" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B873" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C873" s="0">
+        <v>25</v>
+      </c>
+      <c r="D873" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600118</t>
+        </is>
+      </c>
+      <c r="E873" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中国卫星</t>
+        </is>
+      </c>
+      <c r="F873" s="0">
+        <v>55.9</v>
+      </c>
+      <c r="G873" s="4">
+        <v>0.0999606454151909</v>
+      </c>
+      <c r="H873" s="4">
+        <v>0.09240326612406655</v>
+      </c>
+      <c r="I873" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J873" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 中国卫星（600118）归入“三季报增长+卫星制造+商业航天”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K873" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.8 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 38 家涨停，其中首板 28 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L873" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B874" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C874" s="0">
+        <v>26</v>
+      </c>
+      <c r="D874" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002275</t>
+        </is>
+      </c>
+      <c r="E874" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">桂林三金</t>
+        </is>
+      </c>
+      <c r="F874" s="0">
+        <v>13.62</v>
+      </c>
+      <c r="G874" s="4">
+        <v>0.10016155088852985</v>
+      </c>
+      <c r="H874" s="4">
+        <v>0.08458463092280565</v>
+      </c>
+      <c r="I874" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J874" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 桂林三金（002275）归入“三季报增长+中成药+西瓜霜+抗体研发”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K874" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 8.7 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 38 家涨停，其中首板 28 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L874" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B875" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C875" s="0">
+        <v>27</v>
+      </c>
+      <c r="D875" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002149</t>
+        </is>
+      </c>
+      <c r="E875" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">西部材料</t>
+        </is>
+      </c>
+      <c r="F875" s="0">
+        <v>32.31</v>
+      </c>
+      <c r="G875" s="4">
+        <v>0.10010214504596536</v>
+      </c>
+      <c r="H875" s="4">
+        <v>0.08297764446012586</v>
+      </c>
+      <c r="I875" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J875" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 西部材料（002149）归入“商业航天+航天铌合金+稀贵金属+超导”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K875" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.5 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 38 家涨停，其中首板 28 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L875" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B876" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C876" s="0">
+        <v>28</v>
+      </c>
+      <c r="D876" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603382</t>
+        </is>
+      </c>
+      <c r="E876" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">海阳科技</t>
+        </is>
+      </c>
+      <c r="F876" s="0">
+        <v>19.87</v>
+      </c>
+      <c r="G876" s="4">
+        <v>0.10022148394241427</v>
+      </c>
+      <c r="H876" s="4">
+        <v>0.08154648225623173</v>
+      </c>
+      <c r="I876" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J876" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 海阳科技（603382）归入“尼龙6+帘子布+涤纶工业丝+“羊”字辈”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K876" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.1 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 38 家涨停，其中首板 28 家、2板及以上 10 家。</t>
+        </is>
+      </c>
+      <c r="L876" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M203"/>
+  <dimension ref="A1:M213"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -57760,6 +59272,596 @@
       <c r="M203" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">13.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B204" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C204" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D204" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603006</t>
+        </is>
+      </c>
+      <c r="E204" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">联明股份</t>
+        </is>
+      </c>
+      <c r="F204" s="4">
+        <v>0.3613343549815</v>
+      </c>
+      <c r="G204" s="4">
+        <v>0.07076350093109873</v>
+      </c>
+      <c r="H204" s="4">
+        <v>0.09962756052141519</v>
+      </c>
+      <c r="I204" s="4">
+        <v>0.09962756052141519</v>
+      </c>
+      <c r="J204" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K204" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +9.96%</t>
+        </is>
+      </c>
+      <c r="L204" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M204" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.81</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B205" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C205" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D205" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002696</t>
+        </is>
+      </c>
+      <c r="E205" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">百洋股份</t>
+        </is>
+      </c>
+      <c r="F205" s="4">
+        <v>0.26320499986951934</v>
+      </c>
+      <c r="G205" s="4">
+        <v>-0.03823279524214096</v>
+      </c>
+      <c r="H205" s="4">
+        <v>0.0994052676295667</v>
+      </c>
+      <c r="I205" s="4">
+        <v>0.049277824978759543</v>
+      </c>
+      <c r="J205" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K205" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +4.93%</t>
+        </is>
+      </c>
+      <c r="L205" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M205" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B206" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C206" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="D206" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002636</t>
+        </is>
+      </c>
+      <c r="E206" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金安国纪</t>
+        </is>
+      </c>
+      <c r="F206" s="4">
+        <v>0.24200829735231447</v>
+      </c>
+      <c r="G206" s="4">
+        <v>0.041133299197815276</v>
+      </c>
+      <c r="H206" s="4">
+        <v>0.07407407407407396</v>
+      </c>
+      <c r="I206" s="4">
+        <v>-0.01194743130227005</v>
+      </c>
+      <c r="J206" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K206" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -1.19%</t>
+        </is>
+      </c>
+      <c r="L206" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M206" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B207" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C207" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="D207" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605488</t>
+        </is>
+      </c>
+      <c r="E207" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">福莱新材</t>
+        </is>
+      </c>
+      <c r="F207" s="4">
+        <v>0.19689428706717046</v>
+      </c>
+      <c r="G207" s="4">
+        <v>-0.03929232668175264</v>
+      </c>
+      <c r="H207" s="4">
+        <v>0.018308989919769703</v>
+      </c>
+      <c r="I207" s="4">
+        <v>-0.019749022834807617</v>
+      </c>
+      <c r="J207" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K207" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -1.97%</t>
+        </is>
+      </c>
+      <c r="L207" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M207" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B208" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C208" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="D208" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002164</t>
+        </is>
+      </c>
+      <c r="E208" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">宁波东力</t>
+        </is>
+      </c>
+      <c r="F208" s="4">
+        <v>0.19152289947585938</v>
+      </c>
+      <c r="G208" s="4">
+        <v>-0.01597633136094667</v>
+      </c>
+      <c r="H208" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="I208" s="4">
+        <v>0.06449704142011825</v>
+      </c>
+      <c r="J208" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K208" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +6.45%</t>
+        </is>
+      </c>
+      <c r="L208" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M208" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B209" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C209" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="D209" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000559</t>
+        </is>
+      </c>
+      <c r="E209" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">万向钱潮</t>
+        </is>
+      </c>
+      <c r="F209" s="4">
+        <v>0.18278591762224275</v>
+      </c>
+      <c r="G209" s="4">
+        <v>0.01669195751138086</v>
+      </c>
+      <c r="H209" s="4">
+        <v>0.04855842185128978</v>
+      </c>
+      <c r="I209" s="4">
+        <v>-0.012139605462822445</v>
+      </c>
+      <c r="J209" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K209" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -1.21%</t>
+        </is>
+      </c>
+      <c r="L209" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M209" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B210" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C210" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="D210" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603081</t>
+        </is>
+      </c>
+      <c r="E210" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大丰实业</t>
+        </is>
+      </c>
+      <c r="F210" s="4">
+        <v>0.16806355804875964</v>
+      </c>
+      <c r="G210" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H210" s="4">
+        <v>0.09991158267020328</v>
+      </c>
+      <c r="I210" s="4">
+        <v>-0.0008841732979664174</v>
+      </c>
+      <c r="J210" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K210" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -0.09%</t>
+        </is>
+      </c>
+      <c r="L210" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M210" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B211" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C211" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="D211" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600078</t>
+        </is>
+      </c>
+      <c r="E211" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">澄星股份</t>
+        </is>
+      </c>
+      <c r="F211" s="4">
+        <v>0.1618231986949855</v>
+      </c>
+      <c r="G211" s="4">
+        <v>0.03821656050955413</v>
+      </c>
+      <c r="H211" s="4">
+        <v>0.04989384288747356</v>
+      </c>
+      <c r="I211" s="4">
+        <v>-0.007430997876857748</v>
+      </c>
+      <c r="J211" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K211" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -0.74%</t>
+        </is>
+      </c>
+      <c r="L211" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M211" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B212" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C212" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="D212" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603626</t>
+        </is>
+      </c>
+      <c r="E212" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">科森科技</t>
+        </is>
+      </c>
+      <c r="F212" s="4">
+        <v>0.1508285549013406</v>
+      </c>
+      <c r="G212" s="4">
+        <v>0.012935680919870851</v>
+      </c>
+      <c r="H212" s="4">
+        <v>0.04886812791951134</v>
+      </c>
+      <c r="I212" s="4">
+        <v>-0.016528925619834656</v>
+      </c>
+      <c r="J212" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K212" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -1.65%</t>
+        </is>
+      </c>
+      <c r="L212" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M212" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27.37</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="B213" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29</t>
+        </is>
+      </c>
+      <c r="C213" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="D213" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603337</t>
+        </is>
+      </c>
+      <c r="E213" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">杰克科技</t>
+        </is>
+      </c>
+      <c r="F213" s="4">
+        <v>0.1499749807700219</v>
+      </c>
+      <c r="G213" s="4">
+        <v>0.04443989350808941</v>
+      </c>
+      <c r="H213" s="4">
+        <v>0.09727626459143979</v>
+      </c>
+      <c r="I213" s="4">
+        <v>0.06901494982592671</v>
+      </c>
+      <c r="J213" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K213" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +6.90%</t>
+        </is>
+      </c>
+      <c r="L213" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M213" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52.2</t>
         </is>
       </c>
     </row>
@@ -57851,28 +59953,28 @@
         </is>
       </c>
       <c r="B3" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" s="4">
-        <v>0.35</v>
+        <v>0.38095238095238093</v>
       </c>
       <c r="F3" s="4">
-        <v>0.19230769230769232</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="G3" s="0">
-        <v>1.8199999999999998</v>
+        <v>3.4285714285714284</v>
       </c>
       <c r="H3" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I3" s="4">
-        <v>0.35</v>
+        <v>0.38095238095238093</v>
       </c>
     </row>
     <row r="4">
@@ -57882,28 +59984,28 @@
         </is>
       </c>
       <c r="B4" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" s="0">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D4" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4" s="4">
-        <v>0.25</v>
+        <v>0.25396825396825395</v>
       </c>
       <c r="F4" s="4">
-        <v>0.19230769230769232</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="G4" s="0">
-        <v>1.2999999999999998</v>
+        <v>2.2857142857142856</v>
       </c>
       <c r="H4" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I4" s="4">
-        <v>0.5</v>
+        <v>0.5238095238095238</v>
       </c>
     </row>
     <row r="5">
@@ -57913,28 +60015,28 @@
         </is>
       </c>
       <c r="B5" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" s="0">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D5" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5" s="4">
-        <v>0.24166666666666667</v>
+        <v>0.23809523809523808</v>
       </c>
       <c r="F5" s="4">
-        <v>0.19230769230769232</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="G5" s="0">
-        <v>1.2566666666666666</v>
+        <v>2.142857142857143</v>
       </c>
       <c r="H5" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I5" s="4">
-        <v>0.7</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="6">
@@ -57944,28 +60046,28 @@
         </is>
       </c>
       <c r="B6" s="0">
+        <v>21</v>
+      </c>
+      <c r="C6" s="0">
+        <v>210</v>
+      </c>
+      <c r="D6" s="0">
+        <v>50</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0.23809523809523808</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="G6" s="0">
+        <v>2.142857142857143</v>
+      </c>
+      <c r="H6" s="0">
         <v>20</v>
       </c>
-      <c r="C6" s="0">
-        <v>200</v>
-      </c>
-      <c r="D6" s="0">
-        <v>49</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0.245</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0.19230769230769232</v>
-      </c>
-      <c r="G6" s="0">
-        <v>1.2739999999999998</v>
-      </c>
-      <c r="H6" s="0">
-        <v>19</v>
-      </c>
       <c r="I6" s="4">
-        <v>0.95</v>
+        <v>0.9523809523809523</v>
       </c>
     </row>
     <row r="7">

--- a/docs/downloads/latest.xlsx
+++ b/docs/downloads/latest.xlsx
@@ -93,7 +93,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L876"/>
+  <dimension ref="A1:L909"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -47353,13 +47353,1795 @@
         </is>
       </c>
     </row>
+    <row r="877">
+      <c r="A877" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B877" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-02</t>
+        </is>
+      </c>
+      <c r="C877" s="0">
+        <v>1</v>
+      </c>
+      <c r="D877" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000897</t>
+        </is>
+      </c>
+      <c r="E877" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">津滨发展</t>
+        </is>
+      </c>
+      <c r="F877" s="0">
+        <v>1.84</v>
+      </c>
+      <c r="G877" s="4">
+        <v>0.10179640718562875</v>
+      </c>
+      <c r="H877" s="4">
+        <v>0.34748637615647743</v>
+      </c>
+      <c r="I877" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J877" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 津滨发展（000897）归入“三季报增长+房地产开发+天津国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K877" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 9.6%）。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 42 家涨停，其中首板 33 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L877" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B878" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-02</t>
+        </is>
+      </c>
+      <c r="C878" s="0">
+        <v>2</v>
+      </c>
+      <c r="D878" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002365</t>
+        </is>
+      </c>
+      <c r="E878" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">永安药业</t>
+        </is>
+      </c>
+      <c r="F878" s="0">
+        <v>12.23</v>
+      </c>
+      <c r="G878" s="4">
+        <v>0.09982014388489224</v>
+      </c>
+      <c r="H878" s="4">
+        <v>0.3290027924121621</v>
+      </c>
+      <c r="I878" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J878" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 永安药业（002365）归入“三季报大增+牛磺酸+量价齐升”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K878" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 9.7%）。截至运行时成交量约为20日均量的 0.8 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 42 家涨停，其中首板 33 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L878" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B879" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-02</t>
+        </is>
+      </c>
+      <c r="C879" s="0">
+        <v>3</v>
+      </c>
+      <c r="D879" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603029</t>
+        </is>
+      </c>
+      <c r="E879" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天鹅股份</t>
+        </is>
+      </c>
+      <c r="F879" s="0">
+        <v>16.05</v>
+      </c>
+      <c r="G879" s="4">
+        <v>0.10006854009595623</v>
+      </c>
+      <c r="H879" s="4">
+        <v>0.30675409445889723</v>
+      </c>
+      <c r="I879" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J879" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 天鹅股份（603029）归入“三季报增长+采棉机+供销社”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K879" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 9.0%）。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 42 家涨停，其中首板 33 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L879" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B880" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-02</t>
+        </is>
+      </c>
+      <c r="C880" s="0">
+        <v>4</v>
+      </c>
+      <c r="D880" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000716</t>
+        </is>
+      </c>
+      <c r="E880" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黑芝麻</t>
+        </is>
+      </c>
+      <c r="F880" s="0">
+        <v>5.24</v>
+      </c>
+      <c r="G880" s="4">
+        <v>0.10084033613445387</v>
+      </c>
+      <c r="H880" s="4">
+        <v>0.23686751953176996</v>
+      </c>
+      <c r="I880" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J880" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 黑芝麻（000716）归入“三季报大增+黑色食养+药食同源”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K880" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 8.2%）。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 42 家涨停，其中首板 33 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L880" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B881" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-02</t>
+        </is>
+      </c>
+      <c r="C881" s="0">
+        <v>5</v>
+      </c>
+      <c r="D881" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605169</t>
+        </is>
+      </c>
+      <c r="E881" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">洪通燃气</t>
+        </is>
+      </c>
+      <c r="F881" s="0">
+        <v>12.78</v>
+      </c>
+      <c r="G881" s="4">
+        <v>0.09982788296041312</v>
+      </c>
+      <c r="H881" s="4">
+        <v>0.2334438001682608</v>
+      </c>
+      <c r="I881" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J881" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 洪通燃气（605169）归入“三季报高增+天然气+新疆燃气”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K881" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 9.8%）。截至运行时成交量约为20日均量的 0.8 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 42 家涨停，其中首板 33 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L881" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B882" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-02</t>
+        </is>
+      </c>
+      <c r="C882" s="0">
+        <v>6</v>
+      </c>
+      <c r="D882" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600285</t>
+        </is>
+      </c>
+      <c r="E882" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">羚锐制药</t>
+        </is>
+      </c>
+      <c r="F882" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="G882" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H882" s="4">
+        <v>0.19891865436670025</v>
+      </c>
+      <c r="I882" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J882" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 羚锐制药（600285）归入“三季报增长+中药+高股息”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K882" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 8.3%）。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 42 家涨停，其中首板 33 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L882" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B883" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-02</t>
+        </is>
+      </c>
+      <c r="C883" s="0">
+        <v>7</v>
+      </c>
+      <c r="D883" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001287</t>
+        </is>
+      </c>
+      <c r="E883" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中电港</t>
+        </is>
+      </c>
+      <c r="F883" s="0">
+        <v>20.24</v>
+      </c>
+      <c r="G883" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H883" s="4">
+        <v>0.17489183361063462</v>
+      </c>
+      <c r="I883" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J883" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 中电港（001287）归入“三季报大增+存储分销+分销龙头”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K883" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。今日开盘已接近涨停价，开盘强度较高（开盘涨幅 8.3%）。截至运行时成交量约为20日均量的 1.9 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 42 家涨停，其中首板 33 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L883" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B884" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-02</t>
+        </is>
+      </c>
+      <c r="C884" s="0">
+        <v>8</v>
+      </c>
+      <c r="D884" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000995</t>
+        </is>
+      </c>
+      <c r="E884" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">皇台酒业</t>
+        </is>
+      </c>
+      <c r="F884" s="0">
+        <v>14.18</v>
+      </c>
+      <c r="G884" s="4">
+        <v>0.10007757951900696</v>
+      </c>
+      <c r="H884" s="4">
+        <v>0.1391169085377165</v>
+      </c>
+      <c r="I884" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J884" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 皇台酒业（000995）归入“白酒+老窖池+葡萄酒”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K884" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.5 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 42 家涨停，其中首板 33 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L884" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B885" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-02</t>
+        </is>
+      </c>
+      <c r="C885" s="0">
+        <v>9</v>
+      </c>
+      <c r="D885" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603200</t>
+        </is>
+      </c>
+      <c r="E885" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上海洗霸</t>
+        </is>
+      </c>
+      <c r="F885" s="0">
+        <v>51.72</v>
+      </c>
+      <c r="G885" s="4">
+        <v>0.09995746490854952</v>
+      </c>
+      <c r="H885" s="4">
+        <v>0.12267205495737249</v>
+      </c>
+      <c r="I885" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J885" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 上海洗霸（603200）归入“固态电池+数据中心液冷+水处理”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K885" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 42 家涨停，其中首板 33 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L885" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B886" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-02</t>
+        </is>
+      </c>
+      <c r="C886" s="0">
+        <v>10</v>
+      </c>
+      <c r="D886" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603198</t>
+        </is>
+      </c>
+      <c r="E886" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">迎驾贡酒</t>
+        </is>
+      </c>
+      <c r="F886" s="0">
+        <v>44.47</v>
+      </c>
+      <c r="G886" s="4">
+        <v>0.09992579767499388</v>
+      </c>
+      <c r="H886" s="4">
+        <v>0.12251739395590794</v>
+      </c>
+      <c r="I886" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J886" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 迎驾贡酒（603198）归入“三季报增长+徽酒代表+中高档白酒”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K886" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.8 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 42 家涨停，其中首板 33 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L886" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B887" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-02</t>
+        </is>
+      </c>
+      <c r="C887" s="0">
+        <v>11</v>
+      </c>
+      <c r="D887" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605058</t>
+        </is>
+      </c>
+      <c r="E887" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">澳弘电子</t>
+        </is>
+      </c>
+      <c r="F887" s="0">
+        <v>50.26</v>
+      </c>
+      <c r="G887" s="4">
+        <v>0.10002188662727086</v>
+      </c>
+      <c r="H887" s="4">
+        <v>0.11399927028501583</v>
+      </c>
+      <c r="I887" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J887" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 澳弘电子（605058）归入“PCB+HDI板+AI服务器+三季报增长”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K887" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 0.8 倍，量能未出现极端放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 42 家涨停，其中首板 33 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L887" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B888" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-02</t>
+        </is>
+      </c>
+      <c r="C888" s="0">
+        <v>12</v>
+      </c>
+      <c r="D888" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000410</t>
+        </is>
+      </c>
+      <c r="E888" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">沈阳机床</t>
+        </is>
+      </c>
+      <c r="F888" s="0">
+        <v>5.37</v>
+      </c>
+      <c r="G888" s="4">
+        <v>0.10040983606557387</v>
+      </c>
+      <c r="H888" s="4">
+        <v>0.11168633738882873</v>
+      </c>
+      <c r="I888" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J888" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 沈阳机床（000410）归入“扭亏+工业母机+航空航天+购买资产”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K888" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 42 家涨停，其中首板 33 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L888" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B889" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-02</t>
+        </is>
+      </c>
+      <c r="C889" s="0">
+        <v>13</v>
+      </c>
+      <c r="D889" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002946</t>
+        </is>
+      </c>
+      <c r="E889" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新乳业</t>
+        </is>
+      </c>
+      <c r="F889" s="0">
+        <v>15.82</v>
+      </c>
+      <c r="G889" s="4">
+        <v>0.1001390820584145</v>
+      </c>
+      <c r="H889" s="4">
+        <v>0.11051955557428056</v>
+      </c>
+      <c r="I889" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J889" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 新乳业（002946）归入“三季报增长+低温鲜奶+大消费”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K889" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.8 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 42 家涨停，其中首板 33 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L889" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B890" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-02</t>
+        </is>
+      </c>
+      <c r="C890" s="0">
+        <v>14</v>
+      </c>
+      <c r="D890" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600721</t>
+        </is>
+      </c>
+      <c r="E890" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">百花医药</t>
+        </is>
+      </c>
+      <c r="F890" s="0">
+        <v>9.83</v>
+      </c>
+      <c r="G890" s="4">
+        <v>0.0995525727069353</v>
+      </c>
+      <c r="H890" s="4">
+        <v>0.11035269424917372</v>
+      </c>
+      <c r="I890" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J890" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 百花医药（600721）归入“医药外包+复杂制剂+控制权变更”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K890" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.2 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 42 家涨停，其中首板 33 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L890" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B891" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-02</t>
+        </is>
+      </c>
+      <c r="C891" s="0">
+        <v>15</v>
+      </c>
+      <c r="D891" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603233</t>
+        </is>
+      </c>
+      <c r="E891" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大参林</t>
+        </is>
+      </c>
+      <c r="F891" s="0">
+        <v>20.26</v>
+      </c>
+      <c r="G891" s="4">
+        <v>0.09989142236699244</v>
+      </c>
+      <c r="H891" s="4">
+        <v>0.11034122764811909</v>
+      </c>
+      <c r="I891" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J891" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 大参林（603233）归入“三季报增长+回购注销+医药零售”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K891" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.9 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 42 家涨停，其中首板 33 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L891" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B892" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-02</t>
+        </is>
+      </c>
+      <c r="C892" s="0">
+        <v>16</v>
+      </c>
+      <c r="D892" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000417</t>
+        </is>
+      </c>
+      <c r="E892" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合百集团</t>
+        </is>
+      </c>
+      <c r="F892" s="0">
+        <v>5.7</v>
+      </c>
+      <c r="G892" s="4">
+        <v>0.10038610038610042</v>
+      </c>
+      <c r="H892" s="4">
+        <v>0.10546964548580286</v>
+      </c>
+      <c r="I892" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J892" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 合百集团（000417）归入“三季报大增+间接投资长鑫科技+百货零售”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K892" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 42 家涨停，其中首板 33 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L892" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B893" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-02</t>
+        </is>
+      </c>
+      <c r="C893" s="0">
+        <v>17</v>
+      </c>
+      <c r="D893" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603273</t>
+        </is>
+      </c>
+      <c r="E893" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天元智能</t>
+        </is>
+      </c>
+      <c r="F893" s="0">
+        <v>15.6</v>
+      </c>
+      <c r="G893" s="4">
+        <v>0.10014104372355437</v>
+      </c>
+      <c r="H893" s="4">
+        <v>0.10095248182929105</v>
+      </c>
+      <c r="I893" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J893" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 天元智能（603273）归入“机器人集成+混凝土装备+三季报落地”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K893" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.3 倍，存在明显放量。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 42 家涨停，其中首板 33 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L893" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B894" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-02</t>
+        </is>
+      </c>
+      <c r="C894" s="0">
+        <v>18</v>
+      </c>
+      <c r="D894" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601083</t>
+        </is>
+      </c>
+      <c r="E894" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">锦江航运</t>
+        </is>
+      </c>
+      <c r="F894" s="0">
+        <v>13.93</v>
+      </c>
+      <c r="G894" s="4">
+        <v>0.10031595576619277</v>
+      </c>
+      <c r="H894" s="4">
+        <v>0.10018406543084098</v>
+      </c>
+      <c r="I894" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J894" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 锦江航运（601083）归入“三季报增长+集装箱航运+东南亚航线”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K894" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.0 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 42 家涨停，其中首板 33 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L894" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B895" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-02</t>
+        </is>
+      </c>
+      <c r="C895" s="0">
+        <v>19</v>
+      </c>
+      <c r="D895" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000568</t>
+        </is>
+      </c>
+      <c r="E895" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">泸州老窖</t>
+        </is>
+      </c>
+      <c r="F895" s="0">
+        <v>77.07</v>
+      </c>
+      <c r="G895" s="4">
+        <v>0.10005709391949737</v>
+      </c>
+      <c r="H895" s="4">
+        <v>0.09970948715445206</v>
+      </c>
+      <c r="I895" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J895" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 泸州老窖（000568）归入“业绩环增+高端白酒+库存去化”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K895" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.0 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 42 家涨停，其中首板 33 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L895" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B896" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-02</t>
+        </is>
+      </c>
+      <c r="C896" s="0">
+        <v>20</v>
+      </c>
+      <c r="D896" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600189</t>
+        </is>
+      </c>
+      <c r="E896" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">泉阳泉</t>
+        </is>
+      </c>
+      <c r="F896" s="0">
+        <v>8.84</v>
+      </c>
+      <c r="G896" s="4">
+        <v>0.09950248756218905</v>
+      </c>
+      <c r="H896" s="4">
+        <v>0.09625757312962833</v>
+      </c>
+      <c r="I896" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J896" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 泉阳泉（600189）归入“矿泉水+大消费+三季报增长+仓储”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K896" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.0 倍，量能未出现极端放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 42 家涨停，其中首板 33 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L896" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B897" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-02</t>
+        </is>
+      </c>
+      <c r="C897" s="0">
+        <v>21</v>
+      </c>
+      <c r="D897" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002652</t>
+        </is>
+      </c>
+      <c r="E897" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">扬子新材</t>
+        </is>
+      </c>
+      <c r="F897" s="0">
+        <v>3.91</v>
+      </c>
+      <c r="G897" s="4">
+        <v>0.10140845070422543</v>
+      </c>
+      <c r="H897" s="4">
+        <v>0.0949776959744851</v>
+      </c>
+      <c r="I897" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J897" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 扬子新材（002652）归入“有机涂层板+高洁净板+三季报减亏”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K897" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.7 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 42 家涨停，其中首板 33 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L897" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B898" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-02</t>
+        </is>
+      </c>
+      <c r="C898" s="0">
+        <v>22</v>
+      </c>
+      <c r="D898" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000676</t>
+        </is>
+      </c>
+      <c r="E898" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">智度股份</t>
+        </is>
+      </c>
+      <c r="F898" s="0">
+        <v>6.61</v>
+      </c>
+      <c r="G898" s="4">
+        <v>0.09983361064891859</v>
+      </c>
+      <c r="H898" s="4">
+        <v>0.09376225797926349</v>
+      </c>
+      <c r="I898" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J898" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 智度股份（000676）归入“三季报增长+数字营销+鲸鸿动能”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K898" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.5 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 42 家涨停，其中首板 33 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L898" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B899" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-02</t>
+        </is>
+      </c>
+      <c r="C899" s="0">
+        <v>23</v>
+      </c>
+      <c r="D899" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600113</t>
+        </is>
+      </c>
+      <c r="E899" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">浙江东日</t>
+        </is>
+      </c>
+      <c r="F899" s="0">
+        <v>24.62</v>
+      </c>
+      <c r="G899" s="4">
+        <v>0.10008936550491508</v>
+      </c>
+      <c r="H899" s="4">
+        <v>0.08967632072200399</v>
+      </c>
+      <c r="I899" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J899" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 浙江东日（600113）归入“农批市场+大消费+温州国资”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K899" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.2 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 42 家涨停，其中首板 33 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L899" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B900" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-02</t>
+        </is>
+      </c>
+      <c r="C900" s="0">
+        <v>24</v>
+      </c>
+      <c r="D900" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600258</t>
+        </is>
+      </c>
+      <c r="E900" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">首旅酒店</t>
+        </is>
+      </c>
+      <c r="F900" s="0">
+        <v>12.43</v>
+      </c>
+      <c r="G900" s="4">
+        <v>0.09999999999999985</v>
+      </c>
+      <c r="H900" s="4">
+        <v>0.08843657164532957</v>
+      </c>
+      <c r="I900" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J900" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 首旅酒店（600258）归入“三季报净利增长+酒店扩张+大消费”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K900" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 4.9 倍，资金参与度显著放大。短中期均线保持多头排列，价格结构与趋势方向一致。截至本次运行，市场共有 42 家涨停，其中首板 33 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L900" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B901" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-02</t>
+        </is>
+      </c>
+      <c r="C901" s="0">
+        <v>25</v>
+      </c>
+      <c r="D901" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002432</t>
+        </is>
+      </c>
+      <c r="E901" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">九安医疗</t>
+        </is>
+      </c>
+      <c r="F901" s="0">
+        <v>56.24</v>
+      </c>
+      <c r="G901" s="4">
+        <v>0.09994132603168392</v>
+      </c>
+      <c r="H901" s="4">
+        <v>0.08727038728515776</v>
+      </c>
+      <c r="I901" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J901" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 九安医疗（002432）归入“三季报大增+科创投资+糖尿病照护”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K901" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.9 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 42 家涨停，其中首板 33 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L901" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B902" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-02</t>
+        </is>
+      </c>
+      <c r="C902" s="0">
+        <v>26</v>
+      </c>
+      <c r="D902" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000596</t>
+        </is>
+      </c>
+      <c r="E902" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">古井贡酒</t>
+        </is>
+      </c>
+      <c r="F902" s="0">
+        <v>95.7</v>
+      </c>
+      <c r="G902" s="4">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="H902" s="4">
+        <v>0.08630440439028896</v>
+      </c>
+      <c r="I902" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J902" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 古井贡酒（000596）归入“中期分红+三季报+白酒”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K902" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.7 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 42 家涨停，其中首板 33 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L902" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B903" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-02</t>
+        </is>
+      </c>
+      <c r="C903" s="0">
+        <v>27</v>
+      </c>
+      <c r="D903" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603587</t>
+        </is>
+      </c>
+      <c r="E903" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地素时尚</t>
+        </is>
+      </c>
+      <c r="F903" s="0">
+        <v>12.9</v>
+      </c>
+      <c r="G903" s="4">
+        <v>0.09974424552429673</v>
+      </c>
+      <c r="H903" s="4">
+        <v>0.08461527525089262</v>
+      </c>
+      <c r="I903" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J903" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 地素时尚（603587）归入“三季报增长+高端女装+经销回暖”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K903" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.9 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 42 家涨停，其中首板 33 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L903" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要风险来自次日板块分歧与个股承接强弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B904" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-02</t>
+        </is>
+      </c>
+      <c r="C904" s="0">
+        <v>28</v>
+      </c>
+      <c r="D904" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600510</t>
+        </is>
+      </c>
+      <c r="E904" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黑牡丹</t>
+        </is>
+      </c>
+      <c r="F904" s="0">
+        <v>6.46</v>
+      </c>
+      <c r="G904" s="4">
+        <v>0.10051107325383303</v>
+      </c>
+      <c r="H904" s="4">
+        <v>0.08378645683588778</v>
+      </c>
+      <c r="I904" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J904" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 黑牡丹（600510）归入“牛仔布+新型城镇化+园区运营”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K904" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.5 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 42 家涨停，其中首板 33 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L904" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B905" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-02</t>
+        </is>
+      </c>
+      <c r="C905" s="0">
+        <v>29</v>
+      </c>
+      <c r="D905" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002088</t>
+        </is>
+      </c>
+      <c r="E905" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">鲁阳节能</t>
+        </is>
+      </c>
+      <c r="F905" s="0">
+        <v>7.74</v>
+      </c>
+      <c r="G905" s="4">
+        <v>0.09943181818181814</v>
+      </c>
+      <c r="H905" s="4">
+        <v>0.08203691899067252</v>
+      </c>
+      <c r="I905" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J905" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 鲁阳节能（002088）归入“陶瓷纤维+锂电隔热+“羊”字辈+超跌反弹”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K905" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 2.2 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 42 家涨停，其中首板 33 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L905" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B906" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-02</t>
+        </is>
+      </c>
+      <c r="C906" s="0">
+        <v>30</v>
+      </c>
+      <c r="D906" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600215</t>
+        </is>
+      </c>
+      <c r="E906" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">派斯林</t>
+        </is>
+      </c>
+      <c r="F906" s="0">
+        <v>6.37</v>
+      </c>
+      <c r="G906" s="4">
+        <v>0.10017271157167527</v>
+      </c>
+      <c r="H906" s="4">
+        <v>0.08046467878927067</v>
+      </c>
+      <c r="I906" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J906" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 派斯林（600215）归入“自动化+减亏+北美订单+仿生机器人”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K906" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.3 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 42 家涨停，其中首板 33 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L906" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分；当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B907" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-02</t>
+        </is>
+      </c>
+      <c r="C907" s="0">
+        <v>31</v>
+      </c>
+      <c r="D907" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000525</t>
+        </is>
+      </c>
+      <c r="E907" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">红太阳</t>
+        </is>
+      </c>
+      <c r="F907" s="0">
+        <v>4.49</v>
+      </c>
+      <c r="G907" s="4">
+        <v>0.10049019607843146</v>
+      </c>
+      <c r="H907" s="4">
+        <v>0.07609523419574146</v>
+      </c>
+      <c r="I907" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J907" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 红太阳（000525）归入“百草枯+农业无人机+三季报扭亏+国企改革”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K907" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 3.0 倍，资金参与度显著放大。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 42 家涨停，其中首板 33 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L907" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B908" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-02</t>
+        </is>
+      </c>
+      <c r="C908" s="0">
+        <v>32</v>
+      </c>
+      <c r="D908" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002636</t>
+        </is>
+      </c>
+      <c r="E908" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金安国纪</t>
+        </is>
+      </c>
+      <c r="F908" s="0">
+        <v>63.68</v>
+      </c>
+      <c r="G908" s="4">
+        <v>0.10001727414061158</v>
+      </c>
+      <c r="H908" s="4">
+        <v>0.07277100907579935</v>
+      </c>
+      <c r="I908" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J908" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 金安国纪（002636）归入“三季报高增+覆铜板+AI服务器”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K908" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 1.6 倍，存在明显放量。短期均线未形成明显多头排列，趋势确认度相对有限。截至本次运行，市场共有 42 家涨停，其中首板 33 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L908" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日振幅较大</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B909" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-02</t>
+        </is>
+      </c>
+      <c r="C909" s="0">
+        <v>33</v>
+      </c>
+      <c r="D909" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002582</t>
+        </is>
+      </c>
+      <c r="E909" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">好想你</t>
+        </is>
+      </c>
+      <c r="F909" s="0">
+        <v>9.93</v>
+      </c>
+      <c r="G909" s="4">
+        <v>0.09966777408637872</v>
+      </c>
+      <c r="H909" s="4">
+        <v>0.06624134894057768</v>
+      </c>
+      <c r="I909" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theme_only</t>
+        </is>
+      </c>
+      <c r="J909" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">题材归因标签只能说明当日市场将 好想你（002582）归入“三季报扭亏+红枣龙头+大消费+鸣鸣很忙”这一交易线索，不能单独证明涨停的直接原因。需要结合公告、新闻或公司披露进一步确认。</t>
+        </is>
+      </c>
+      <c r="K909" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收盘贴近日内最高价，说明涨停日尾盘价格维持强势。截至运行时成交量约为20日均量的 5.6 倍，资金参与度显著放大。5日均线仍高于10日均线，但中期趋势强度一般。截至本次运行，市场共有 42 家涨停，其中首板 33 家、2板及以上 9 家。</t>
+        </is>
+      </c>
+      <c r="L909" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当日成交量明显放大，筹码交换较充分</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M213"/>
+  <dimension ref="A1:M223"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -59862,6 +61644,596 @@
       <c r="M213" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">52.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B214" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C214" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D214" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600592</t>
+        </is>
+      </c>
+      <c r="E214" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">龙溪股份</t>
+        </is>
+      </c>
+      <c r="F214" s="4">
+        <v>0.1609386153080981</v>
+      </c>
+      <c r="G214" s="4">
+        <v>0.0798391728891441</v>
+      </c>
+      <c r="H214" s="4">
+        <v>0.09017805858701888</v>
+      </c>
+      <c r="I214" s="4">
+        <v>-0.09936817920735208</v>
+      </c>
+      <c r="J214" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K214" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -9.94%</t>
+        </is>
+      </c>
+      <c r="L214" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M214" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15.68</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B215" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C215" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D215" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000530</t>
+        </is>
+      </c>
+      <c r="E215" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">冰山冷热</t>
+        </is>
+      </c>
+      <c r="F215" s="4">
+        <v>0.15491976721626927</v>
+      </c>
+      <c r="G215" s="4">
+        <v>0.013365735115431265</v>
+      </c>
+      <c r="H215" s="4">
+        <v>0.06925880923450789</v>
+      </c>
+      <c r="I215" s="4">
+        <v>-0.0376670716889429</v>
+      </c>
+      <c r="J215" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K215" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -3.77%</t>
+        </is>
+      </c>
+      <c r="L215" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M215" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B216" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C216" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="D216" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600501</t>
+        </is>
+      </c>
+      <c r="E216" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">航天晨光</t>
+        </is>
+      </c>
+      <c r="F216" s="4">
+        <v>0.14784817614002382</v>
+      </c>
+      <c r="G216" s="4">
+        <v>0.023682652457075015</v>
+      </c>
+      <c r="H216" s="4">
+        <v>0.09532267613972767</v>
+      </c>
+      <c r="I216" s="4">
+        <v>-0.034931912374185914</v>
+      </c>
+      <c r="J216" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K216" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -3.49%</t>
+        </is>
+      </c>
+      <c r="L216" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M216" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B217" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C217" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="D217" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600261</t>
+        </is>
+      </c>
+      <c r="E217" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">阳光照明</t>
+        </is>
+      </c>
+      <c r="F217" s="4">
+        <v>0.13943404406029228</v>
+      </c>
+      <c r="G217" s="4">
+        <v>0.09946236559139776</v>
+      </c>
+      <c r="H217" s="4">
+        <v>0.09946236559139776</v>
+      </c>
+      <c r="I217" s="4">
+        <v>0.09946236559139776</v>
+      </c>
+      <c r="J217" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K217" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +9.95%</t>
+        </is>
+      </c>
+      <c r="L217" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M217" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.09</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B218" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C218" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="D218" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603103</t>
+        </is>
+      </c>
+      <c r="E218" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">横店影视</t>
+        </is>
+      </c>
+      <c r="F218" s="4">
+        <v>0.13852161937185611</v>
+      </c>
+      <c r="G218" s="4">
+        <v>-0.025229357798165264</v>
+      </c>
+      <c r="H218" s="4">
+        <v>-0.025229357798165264</v>
+      </c>
+      <c r="I218" s="4">
+        <v>-0.09977064220183496</v>
+      </c>
+      <c r="J218" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K218" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -9.98%</t>
+        </is>
+      </c>
+      <c r="L218" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M218" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B219" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C219" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="D219" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603703</t>
+        </is>
+      </c>
+      <c r="E219" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">盛洋科技</t>
+        </is>
+      </c>
+      <c r="F219" s="4">
+        <v>0.13814927673533048</v>
+      </c>
+      <c r="G219" s="4">
+        <v>0.10036832412523022</v>
+      </c>
+      <c r="H219" s="4">
+        <v>0.10036832412523022</v>
+      </c>
+      <c r="I219" s="4">
+        <v>0.10036832412523022</v>
+      </c>
+      <c r="J219" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="K219" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晋级二板；次日收盘相对首板收盘 +10.04%</t>
+        </is>
+      </c>
+      <c r="L219" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M219" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B220" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C220" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="D220" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601188</t>
+        </is>
+      </c>
+      <c r="E220" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">龙江交通</t>
+        </is>
+      </c>
+      <c r="F220" s="4">
+        <v>0.1372815231417681</v>
+      </c>
+      <c r="G220" s="4">
+        <v>-0.008571428571428563</v>
+      </c>
+      <c r="H220" s="4">
+        <v>0.014285714285714235</v>
+      </c>
+      <c r="I220" s="4">
+        <v>-0.06857142857142862</v>
+      </c>
+      <c r="J220" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K220" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -6.86%</t>
+        </is>
+      </c>
+      <c r="L220" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M220" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B221" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C221" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="D221" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600428</t>
+        </is>
+      </c>
+      <c r="E221" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中远海特</t>
+        </is>
+      </c>
+      <c r="F221" s="4">
+        <v>0.13683558312342736</v>
+      </c>
+      <c r="G221" s="4">
+        <v>0.027216856892010366</v>
+      </c>
+      <c r="H221" s="4">
+        <v>0.03511852502194901</v>
+      </c>
+      <c r="I221" s="4">
+        <v>0.0070237050043897575</v>
+      </c>
+      <c r="J221" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K221" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 +0.70%</t>
+        </is>
+      </c>
+      <c r="L221" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M221" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B222" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C222" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="D222" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002679</t>
+        </is>
+      </c>
+      <c r="E222" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">福建金森</t>
+        </is>
+      </c>
+      <c r="F222" s="4">
+        <v>0.13272709492661408</v>
+      </c>
+      <c r="G222" s="4">
+        <v>0.008450704225352101</v>
+      </c>
+      <c r="H222" s="4">
+        <v>0.008450704225352101</v>
+      </c>
+      <c r="I222" s="4">
+        <v>-0.0995305164319249</v>
+      </c>
+      <c r="J222" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K222" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -9.95%</t>
+        </is>
+      </c>
+      <c r="L222" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M222" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="B223" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="C223" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="D223" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">002277</t>
+        </is>
+      </c>
+      <c r="E223" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">友阿股份</t>
+        </is>
+      </c>
+      <c r="F223" s="4">
+        <v>0.12605868103564385</v>
+      </c>
+      <c r="G223" s="4">
+        <v>-0.048824593128390714</v>
+      </c>
+      <c r="H223" s="4">
+        <v>0.03616636528028927</v>
+      </c>
+      <c r="I223" s="4">
+        <v>-0.03616636528028938</v>
+      </c>
+      <c r="J223" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">否</t>
+        </is>
+      </c>
+      <c r="K223" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未晋级二板；次日收盘相对首板收盘 -3.62%</t>
+        </is>
+      </c>
+      <c r="L223" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verified</t>
+        </is>
+      </c>
+      <c r="M223" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.33</t>
         </is>
       </c>
     </row>
@@ -59953,28 +62325,28 @@
         </is>
       </c>
       <c r="B3" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="0">
         <v>8</v>
       </c>
       <c r="E3" s="4">
-        <v>0.38095238095238093</v>
+        <v>0.36363636363636365</v>
       </c>
       <c r="F3" s="4">
-        <v>0.1111111111111111</v>
+        <v>0.21428571428571427</v>
       </c>
       <c r="G3" s="0">
-        <v>3.4285714285714284</v>
+        <v>1.696969696969697</v>
       </c>
       <c r="H3" s="0">
         <v>8</v>
       </c>
       <c r="I3" s="4">
-        <v>0.38095238095238093</v>
+        <v>0.36363636363636365</v>
       </c>
     </row>
     <row r="4">
@@ -59984,28 +62356,28 @@
         </is>
       </c>
       <c r="B4" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="0">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D4" s="0">
         <v>16</v>
       </c>
       <c r="E4" s="4">
-        <v>0.25396825396825395</v>
+        <v>0.24242424242424243</v>
       </c>
       <c r="F4" s="4">
-        <v>0.1111111111111111</v>
+        <v>0.21428571428571427</v>
       </c>
       <c r="G4" s="0">
-        <v>2.2857142857142856</v>
+        <v>1.1313131313131315</v>
       </c>
       <c r="H4" s="0">
         <v>11</v>
       </c>
       <c r="I4" s="4">
-        <v>0.5238095238095238</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
@@ -60015,28 +62387,28 @@
         </is>
       </c>
       <c r="B5" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" s="0">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D5" s="0">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E5" s="4">
-        <v>0.23809523809523808</v>
+        <v>0.24242424242424243</v>
       </c>
       <c r="F5" s="4">
-        <v>0.1111111111111111</v>
+        <v>0.21428571428571427</v>
       </c>
       <c r="G5" s="0">
-        <v>2.142857142857143</v>
+        <v>1.1313131313131315</v>
       </c>
       <c r="H5" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I5" s="4">
-        <v>0.7142857142857143</v>
+        <v>0.7272727272727273</v>
       </c>
     </row>
     <row r="6">
@@ -60046,28 +62418,28 @@
         </is>
       </c>
       <c r="B6" s="0">
+        <v>22</v>
+      </c>
+      <c r="C6" s="0">
+        <v>220</v>
+      </c>
+      <c r="D6" s="0">
+        <v>52</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0.23636363636363636</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.21428571428571427</v>
+      </c>
+      <c r="G6" s="0">
+        <v>1.103030303030303</v>
+      </c>
+      <c r="H6" s="0">
         <v>21</v>
       </c>
-      <c r="C6" s="0">
-        <v>210</v>
-      </c>
-      <c r="D6" s="0">
-        <v>50</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0.23809523809523808</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="G6" s="0">
-        <v>2.142857142857143</v>
-      </c>
-      <c r="H6" s="0">
-        <v>20</v>
-      </c>
       <c r="I6" s="4">
-        <v>0.9523809523809523</v>
+        <v>0.9545454545454546</v>
       </c>
     </row>
     <row r="7">
